--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Q84"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="64" min="1" max="1"/>
@@ -1562,6 +1562,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="65">
       <c r="B17" s="80" t="inlineStr">
         <is>
@@ -1733,6 +1734,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="15" customHeight="1" s="65">
       <c r="B26" s="79" t="inlineStr">
         <is>
@@ -2345,6 +2347,7 @@
       <c r="F68" s="85" t="n"/>
       <c r="G68" s="85" t="n"/>
     </row>
+    <row r="69"/>
     <row r="70" ht="15" customHeight="1" s="65">
       <c r="B70" s="90" t="inlineStr">
         <is>
@@ -2429,6 +2432,7 @@
         </is>
       </c>
     </row>
+    <row r="82"/>
     <row r="83" ht="15" customHeight="1" s="65">
       <c r="B83" s="103" t="inlineStr">
         <is>
@@ -2560,6 +2564,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="15" customHeight="1" s="65">
       <c r="A7" s="105" t="inlineStr">
         <is>
@@ -2834,13 +2839,11 @@
           <t>TICK_ARCHIVE_ENABLED</t>
         </is>
       </c>
-      <c r="B19" s="76">
-        <f>TRUE()</f>
-        <v/>
-      </c>
-      <c r="C19" s="84">
-        <f>TRUE()</f>
-        <v/>
+      <c r="B19" s="76" t="b">
+        <v>1</v>
+      </c>
+      <c r="C19" s="84" t="b">
+        <v>1</v>
       </c>
       <c r="D19" s="84" t="inlineStr">
         <is>
@@ -2895,6 +2898,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="65">
       <c r="A23" s="105" t="inlineStr">
         <is>
@@ -3071,6 +3075,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="65">
       <c r="A32" s="105" t="inlineStr">
         <is>
@@ -3178,6 +3183,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38" ht="15" customHeight="1" s="65">
       <c r="A38" s="105" t="inlineStr">
         <is>
@@ -3354,6 +3360,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47" ht="15" customHeight="1" s="65">
       <c r="A47" s="105" t="inlineStr">
         <is>
@@ -3398,13 +3405,11 @@
           <t>ALERT_ENABLED</t>
         </is>
       </c>
-      <c r="B49" s="76">
-        <f>TRUE()</f>
-        <v/>
-      </c>
-      <c r="C49" s="84">
-        <f>TRUE()</f>
-        <v/>
+      <c r="B49" s="76" t="b">
+        <v>1</v>
+      </c>
+      <c r="C49" s="84" t="b">
+        <v>1</v>
       </c>
       <c r="D49" s="84" t="inlineStr">
         <is>
@@ -3523,13 +3528,11 @@
           <t>ALERT_ONLY_IF_EDGE_PASSES</t>
         </is>
       </c>
-      <c r="B54" s="76">
-        <f>TRUE()</f>
-        <v/>
-      </c>
-      <c r="C54" s="84">
-        <f>TRUE()</f>
-        <v/>
+      <c r="B54" s="76" t="b">
+        <v>1</v>
+      </c>
+      <c r="C54" s="84" t="b">
+        <v>1</v>
       </c>
       <c r="D54" s="84" t="inlineStr">
         <is>
@@ -3548,13 +3551,11 @@
           <t>ALERT_SPEAK</t>
         </is>
       </c>
-      <c r="B55" s="76">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-      <c r="C55" s="84">
-        <f>FALSE()</f>
-        <v/>
+      <c r="B55" s="76" t="b">
+        <v>0</v>
+      </c>
+      <c r="C55" s="84" t="b">
+        <v>0</v>
       </c>
       <c r="D55" s="84" t="inlineStr">
         <is>
@@ -3567,6 +3568,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57" ht="15" customHeight="1" s="65">
       <c r="A57" s="105" t="inlineStr">
         <is>
@@ -3611,13 +3613,11 @@
           <t>WARM_START_ENABLED</t>
         </is>
       </c>
-      <c r="B59" s="76">
-        <f>TRUE()</f>
-        <v/>
-      </c>
-      <c r="C59" s="84">
-        <f>TRUE()</f>
-        <v/>
+      <c r="B59" s="76" t="b">
+        <v>1</v>
+      </c>
+      <c r="C59" s="84" t="b">
+        <v>1</v>
       </c>
       <c r="D59" s="84" t="inlineStr">
         <is>
@@ -3659,13 +3659,11 @@
           <t>LOG_ENABLED</t>
         </is>
       </c>
-      <c r="B61" s="76">
-        <f>TRUE()</f>
-        <v/>
-      </c>
-      <c r="C61" s="84">
-        <f>TRUE()</f>
-        <v/>
+      <c r="B61" s="76" t="b">
+        <v>1</v>
+      </c>
+      <c r="C61" s="84" t="b">
+        <v>1</v>
       </c>
       <c r="D61" s="84" t="inlineStr">
         <is>
@@ -3701,6 +3699,7 @@
         </is>
       </c>
     </row>
+    <row r="63"/>
     <row r="64" ht="15" customHeight="1" s="65">
       <c r="A64" s="105" t="inlineStr">
         <is>
@@ -3809,6 +3808,7 @@
         </is>
       </c>
     </row>
+    <row r="70"/>
     <row r="71" ht="15" customHeight="1" s="65">
       <c r="A71" s="105" t="inlineStr">
         <is>
@@ -3896,9 +3896,8 @@
           <t>SPREAD_1</t>
         </is>
       </c>
-      <c r="B74" s="76">
-        <f>TRUE()</f>
-        <v/>
+      <c r="B74" s="76" t="b">
+        <v>1</v>
       </c>
       <c r="C74" s="108" t="inlineStr">
         <is>
@@ -3942,9 +3941,8 @@
           <t>SPREAD_2</t>
         </is>
       </c>
-      <c r="B75" s="76">
-        <f>TRUE()</f>
-        <v/>
+      <c r="B75" s="76" t="b">
+        <v>1</v>
       </c>
       <c r="C75" s="108" t="inlineStr">
         <is>
@@ -3988,9 +3986,8 @@
           <t>SPREAD_3</t>
         </is>
       </c>
-      <c r="B76" s="76">
-        <f>TRUE()</f>
-        <v/>
+      <c r="B76" s="76" t="b">
+        <v>1</v>
       </c>
       <c r="C76" s="108" t="inlineStr">
         <is>
@@ -4034,9 +4031,8 @@
           <t>SPREAD_4</t>
         </is>
       </c>
-      <c r="B77" s="76">
-        <f>TRUE()</f>
-        <v/>
+      <c r="B77" s="76" t="b">
+        <v>1</v>
       </c>
       <c r="C77" s="108" t="inlineStr">
         <is>
@@ -4074,6 +4070,7 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
     <row r="79" ht="15" customHeight="1" s="65">
       <c r="A79" s="116" t="inlineStr">
         <is>
@@ -4142,6 +4139,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="65">
       <c r="A5" s="119" t="inlineStr">
         <is>
@@ -4424,6 +4422,9 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="65">
       <c r="A15" s="119" t="inlineStr">
         <is>
@@ -4596,6 +4597,8 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="65">
       <c r="A23" s="122" t="inlineStr">
         <is>
@@ -4847,6 +4850,7 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="65">
       <c r="A34" s="122" t="inlineStr">
         <is>
@@ -4921,6 +4925,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41" ht="15" customHeight="1" s="65">
       <c r="A41" s="67" t="inlineStr">
         <is>
@@ -5300,7 +5305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="64" min="1" max="1"/>
@@ -5316,6 +5321,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1" s="65">
       <c r="B3" s="124" t="inlineStr">
         <is>
@@ -5372,6 +5378,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="65">
       <c r="B12" s="80" t="inlineStr">
         <is>
@@ -5421,6 +5428,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="65">
       <c r="B20" s="80" t="inlineStr">
         <is>
@@ -5453,6 +5461,7 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="22.35" customHeight="1" s="65">
       <c r="B24" s="79" t="inlineStr">
         <is>
@@ -5526,6 +5535,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="65">
       <c r="B28" s="67" t="inlineStr">
         <is>
@@ -5540,6 +5550,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="65">
       <c r="B31" s="80" t="inlineStr">
         <is>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -15,7 +15,9 @@
     <sheet name="Log" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Setup" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dashboard'!$A$2:$A$18</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -23,13 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="53">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -55,9 +57,194 @@
     <font>
       <name val="Arial"/>
       <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF111318"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFB8860B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
       <family val="0"/>
       <b val="1"/>
-      <color rgb="FF1F3864"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF0E7C7B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="32"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF111318"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color rgb="FF6B7280"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF111318"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF127A34"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1257A6"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF127A34"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF127A34"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF111318"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF111318"/>
       <sz val="16"/>
     </font>
     <font>
@@ -65,8 +252,54 @@
       <charset val="1"/>
       <family val="0"/>
       <b val="1"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF111318"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF111318"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF111318"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="28"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF111318"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <color rgb="FF6B7280"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -81,29 +314,6 @@
       <charset val="1"/>
       <family val="0"/>
       <b val="1"/>
-      <color rgb="FFC00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
       <color rgb="FF1F3864"/>
       <sz val="11"/>
     </font>
@@ -112,48 +322,8 @@
       <charset val="1"/>
       <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF1F3864"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFC00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <i val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF1F3864"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF1F3864"/>
-      <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -180,10 +350,33 @@
       <name val="Arial"/>
       <charset val="1"/>
       <family val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
       <i val="1"/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -199,8 +392,8 @@
       <charset val="1"/>
       <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -224,6 +417,14 @@
       <family val="0"/>
       <b val="1"/>
       <color rgb="FF1F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
       <sz val="12"/>
     </font>
     <font>
@@ -233,12 +434,48 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF17375E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.25"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -254,8 +491,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -264,31 +501,22 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333333"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF2FA"/>
-        <bgColor rgb="FFE7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFE7E6E6"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF0F1E33"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -307,36 +535,59 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
+      <left style="thin"/>
       <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -350,398 +601,849 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="167" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="168" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="41" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="167" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="168" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="41" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -753,7 +1455,63 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF595959"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -828,18 +1586,18 @@
       <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FFB8860B"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0E7C7B"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFEDF2FA"/>
+      <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF1257A6"/>
       <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -847,10 +1605,10 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF127A34"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -863,16 +1621,16 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FF6B7280"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF17375E"/>
       <rgbColor rgb="FF006100"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF0F1E33"/>
+      <rgbColor rgb="FF111318"/>
       <rgbColor rgb="FF9C5700"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FF1F3864"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1059,779 +1817,957 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:V51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="3" customWidth="1" style="66" min="1" max="1"/>
-    <col width="34" customWidth="1" style="66" min="2" max="2"/>
-    <col width="13" customWidth="1" style="66" min="3" max="4"/>
-    <col width="15" customWidth="1" style="66" min="5" max="5"/>
-    <col width="3" customWidth="1" style="66" min="6" max="6"/>
-    <col width="19" customWidth="1" style="66" min="7" max="7"/>
-    <col width="15" customWidth="1" style="66" min="8" max="8"/>
-    <col width="3" customWidth="1" style="66" min="9" max="9"/>
-    <col width="20" customWidth="1" style="66" min="10" max="10"/>
-    <col width="18" customWidth="1" style="66" min="11" max="11"/>
-    <col width="3" customWidth="1" style="66" min="12" max="12"/>
-    <col width="46" customWidth="1" style="66" min="13" max="13"/>
+    <col hidden="1" width="2.14" customWidth="1" style="141" min="1" max="1"/>
+    <col hidden="1" width="11" customWidth="1" style="141" min="2" max="2"/>
+    <col hidden="1" width="30.43" customWidth="1" style="141" min="3" max="3"/>
+    <col width="3.43" customWidth="1" style="141" min="4" max="5"/>
+    <col width="16.14" customWidth="1" style="142" min="6" max="6"/>
+    <col hidden="1" width="30.57" customWidth="1" style="141" min="7" max="7"/>
+    <col width="17" customWidth="1" style="141" min="8" max="10"/>
+    <col width="17.43" customWidth="1" style="141" min="11" max="12"/>
+    <col width="2" customWidth="1" style="141" min="13" max="13"/>
+    <col width="17.57" customWidth="1" style="141" min="14" max="14"/>
+    <col hidden="1" width="16.72" customWidth="1" style="141" min="15" max="15"/>
+    <col width="18.29" customWidth="1" style="141" min="16" max="18"/>
+    <col width="16.43" customWidth="1" style="141" min="19" max="20"/>
+    <col width="17.29" customWidth="1" style="141" min="24" max="24"/>
+    <col width="14.29" customWidth="1" style="141" min="25" max="26"/>
+    <col width="11.43" customWidth="1" style="141" min="27" max="27"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.7" customHeight="1" s="67">
-      <c r="B1" s="68" t="inlineStr">
-        <is>
-          <t>TT RTD Z-SCORE MONITOR</t>
-        </is>
-      </c>
-      <c r="J1" s="69" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="68.25" customHeight="1" s="143">
+      <c r="A2" s="144" t="n"/>
+      <c r="B2" s="145" t="n"/>
+      <c r="C2" s="146" t="inlineStr">
+        <is>
+          <t>ENERGY FUTURES BID / ASK SPREAD MONITOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" s="143">
+      <c r="A3" s="144" t="n"/>
+      <c r="B3" s="147" t="n"/>
+      <c r="C3" s="148" t="n"/>
+      <c r="F3" s="149" t="n"/>
+      <c r="G3" s="150" t="n"/>
+      <c r="L3" s="151" t="n"/>
+    </row>
+    <row r="4" ht="6.75" customHeight="1" s="143">
+      <c r="A4" s="144" t="n"/>
+      <c r="B4" s="152" t="inlineStr">
+        <is>
+          <t>TT MARKET</t>
+        </is>
+      </c>
+      <c r="C4" s="152" t="inlineStr">
+        <is>
+          <t>CME</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="6.75" customHeight="1" s="143">
+      <c r="A5" s="144" t="n"/>
+      <c r="B5" s="153" t="inlineStr">
+        <is>
+          <t>TT SHORT NAME</t>
+        </is>
+      </c>
+      <c r="C5" s="153" t="inlineStr">
+        <is>
+          <t>INSTRUMENT ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="23.25" customHeight="1" s="143">
+      <c r="A6" s="144" t="n"/>
+      <c r="B6" s="152" t="inlineStr">
+        <is>
+          <t>RBV6</t>
+        </is>
+      </c>
+      <c r="C6" s="154" t="n"/>
+      <c r="F6" s="155" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="G6" s="156" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="H6" s="156" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="I6" s="156" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="J6" s="156" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="K6" s="156" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L6" s="157" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M6" s="158" t="n"/>
+      <c r="N6" s="155" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="O6" s="156" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="P6" s="156" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="Q6" s="156" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="R6" s="156" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="S6" s="156" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T6" s="157" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="U6" s="159" t="n"/>
+      <c r="V6" s="159" t="n"/>
+    </row>
+    <row r="7" ht="55.5" customHeight="1" s="143">
+      <c r="A7" s="144" t="n"/>
+      <c r="B7" s="152" t="inlineStr">
+        <is>
+          <t>HOV6</t>
+        </is>
+      </c>
+      <c r="C7" s="154" t="n"/>
+      <c r="D7" s="160" t="n"/>
+      <c r="E7" s="160" t="n"/>
+      <c r="F7" s="161" t="inlineStr">
+        <is>
+          <t>HOV26
+HO Oct 26</t>
+        </is>
+      </c>
+      <c r="G7" s="162" t="inlineStr">
+        <is>
+          <t>HO Oct 26</t>
+        </is>
+      </c>
+      <c r="H7" s="163" t="n"/>
+      <c r="I7" s="164" t="n"/>
+      <c r="J7" s="165" t="n"/>
+      <c r="K7" s="166" t="n"/>
+      <c r="L7" s="167" t="n"/>
+      <c r="M7" s="168" t="n"/>
+      <c r="N7" s="161" t="inlineStr">
+        <is>
+          <t>BZV26
+BZ Oct 26</t>
+        </is>
+      </c>
+      <c r="O7" s="162" t="inlineStr">
+        <is>
+          <t>BZ Oct 26</t>
+        </is>
+      </c>
+      <c r="P7" s="163" t="n"/>
+      <c r="Q7" s="163" t="n"/>
+      <c r="R7" s="169" t="n"/>
+      <c r="S7" s="166" t="n"/>
+      <c r="T7" s="167" t="n"/>
+      <c r="U7" s="159" t="n"/>
+      <c r="V7" s="159" t="n"/>
+    </row>
+    <row r="8" ht="55.5" customHeight="1" s="143">
+      <c r="A8" s="144" t="n"/>
+      <c r="B8" s="152" t="inlineStr">
+        <is>
+          <t>BZV6</t>
+        </is>
+      </c>
+      <c r="C8" s="154" t="n"/>
+      <c r="D8" s="160" t="n"/>
+      <c r="E8" s="160" t="n"/>
+      <c r="F8" s="170" t="inlineStr">
+        <is>
+          <t>CLV26
+CL Oct 26</t>
+        </is>
+      </c>
+      <c r="G8" s="171" t="inlineStr">
+        <is>
+          <t>CL Oct 26</t>
+        </is>
+      </c>
+      <c r="H8" s="172" t="n"/>
+      <c r="I8" s="172" t="n"/>
+      <c r="J8" s="173" t="n"/>
+      <c r="K8" s="174" t="n"/>
+      <c r="L8" s="175" t="n"/>
+      <c r="M8" s="168" t="n"/>
+      <c r="N8" s="170" t="inlineStr">
+        <is>
+          <t>CLV26
+CL Oct 26</t>
+        </is>
+      </c>
+      <c r="O8" s="171" t="inlineStr">
+        <is>
+          <t>CL Oct 26</t>
+        </is>
+      </c>
+      <c r="P8" s="172" t="n"/>
+      <c r="Q8" s="172" t="n"/>
+      <c r="R8" s="173" t="n"/>
+      <c r="S8" s="174" t="n"/>
+      <c r="T8" s="175" t="n"/>
+      <c r="U8" s="159" t="n"/>
+      <c r="V8" s="159" t="n"/>
+    </row>
+    <row r="9" ht="55.5" customHeight="1" s="143">
+      <c r="A9" s="144" t="n"/>
+      <c r="B9" s="152" t="inlineStr">
+        <is>
+          <t>CLV6</t>
+        </is>
+      </c>
+      <c r="C9" s="154" t="n"/>
+      <c r="D9" s="160" t="n"/>
+      <c r="E9" s="160" t="n"/>
+      <c r="F9" s="176" t="inlineStr">
+        <is>
+          <t>HO | CL Oct 26 Crack</t>
+        </is>
+      </c>
+      <c r="G9" s="177" t="n"/>
+      <c r="H9" s="178" t="n"/>
+      <c r="I9" s="178" t="n"/>
+      <c r="J9" s="179" t="n"/>
+      <c r="K9" s="178" t="n"/>
+      <c r="L9" s="180" t="n"/>
+      <c r="M9" s="168" t="n"/>
+      <c r="N9" s="181" t="inlineStr">
+        <is>
+          <t>BZ - CL</t>
+        </is>
+      </c>
+      <c r="O9" s="182" t="n"/>
+      <c r="P9" s="178" t="n"/>
+      <c r="Q9" s="178" t="n"/>
+      <c r="R9" s="179" t="n"/>
+      <c r="S9" s="178" t="n"/>
+      <c r="T9" s="180" t="n"/>
+      <c r="U9" s="159" t="n"/>
+      <c r="V9" s="159" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="143">
+      <c r="A10" s="144" t="n"/>
+      <c r="B10" s="183" t="inlineStr">
+        <is>
+          <t>CL Oct26 - BZ Oct26 Inter-Product</t>
+        </is>
+      </c>
+      <c r="C10" s="154" t="n"/>
+      <c r="D10" s="160" t="n"/>
+      <c r="E10" s="160" t="n"/>
+      <c r="F10" s="168" t="n"/>
+      <c r="G10" s="168" t="n"/>
+      <c r="H10" s="168" t="n"/>
+      <c r="I10" s="168" t="n"/>
+      <c r="J10" s="168" t="n"/>
+      <c r="K10" s="168" t="n"/>
+      <c r="L10" s="168" t="n"/>
+      <c r="M10" s="168" t="n"/>
+      <c r="N10" s="159" t="n"/>
+      <c r="O10" s="159" t="n"/>
+      <c r="P10" s="159" t="n"/>
+      <c r="Q10" s="159" t="n"/>
+      <c r="R10" s="159" t="n"/>
+      <c r="S10" s="159" t="n"/>
+      <c r="T10" s="159" t="n"/>
+      <c r="U10" s="159" t="n"/>
+      <c r="V10" s="159" t="n"/>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="143">
+      <c r="A11" s="144" t="n"/>
+      <c r="B11" s="183" t="n"/>
+      <c r="C11" s="154" t="n"/>
+      <c r="D11" s="160" t="n"/>
+      <c r="E11" s="160" t="n"/>
+      <c r="F11" s="155" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="G11" s="156" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="H11" s="156" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="I11" s="156" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="J11" s="156" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="K11" s="156" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L11" s="157" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M11" s="168" t="n"/>
+      <c r="N11" s="184" t="n"/>
+      <c r="O11" s="185" t="n"/>
+      <c r="P11" s="186" t="n"/>
+      <c r="Q11" s="186" t="n"/>
+      <c r="R11" s="173" t="n"/>
+      <c r="S11" s="187" t="n"/>
+      <c r="T11" s="187" t="n"/>
+      <c r="U11" s="159" t="n"/>
+      <c r="V11" s="159" t="n"/>
+    </row>
+    <row r="12" ht="50.25" customHeight="1" s="143">
+      <c r="A12" s="144" t="n"/>
+      <c r="B12" s="183" t="inlineStr">
+        <is>
+          <t>Oct26 HO-CL Crack</t>
+        </is>
+      </c>
+      <c r="C12" s="154" t="n"/>
+      <c r="D12" s="160" t="n"/>
+      <c r="E12" s="160" t="n"/>
+      <c r="F12" s="188" t="inlineStr">
+        <is>
+          <t>RBV26</t>
+        </is>
+      </c>
+      <c r="G12" s="162" t="inlineStr">
+        <is>
+          <t>RB Oct 26</t>
+        </is>
+      </c>
+      <c r="H12" s="163" t="n"/>
+      <c r="I12" s="163" t="n"/>
+      <c r="J12" s="165" t="n"/>
+      <c r="K12" s="166" t="n"/>
+      <c r="L12" s="167" t="n"/>
+      <c r="M12" s="168" t="n"/>
+      <c r="N12" s="168" t="n"/>
+      <c r="O12" s="168" t="n"/>
+      <c r="P12" s="168" t="n"/>
+      <c r="Q12" s="168" t="n"/>
+      <c r="R12" s="168" t="n"/>
+      <c r="S12" s="189" t="n"/>
+      <c r="T12" s="189" t="n"/>
+      <c r="U12" s="159" t="n"/>
+      <c r="V12" s="159" t="n"/>
+    </row>
+    <row r="13" ht="50.25" customHeight="1" s="143">
+      <c r="A13" s="144" t="n"/>
+      <c r="D13" s="160" t="n"/>
+      <c r="E13" s="160" t="n"/>
+      <c r="F13" s="190" t="inlineStr">
+        <is>
+          <t>HOV26</t>
+        </is>
+      </c>
+      <c r="G13" s="171" t="inlineStr">
+        <is>
+          <t>HO Oct 26</t>
+        </is>
+      </c>
+      <c r="H13" s="172" t="n"/>
+      <c r="I13" s="172" t="n"/>
+      <c r="J13" s="191" t="n"/>
+      <c r="K13" s="174" t="n"/>
+      <c r="L13" s="175" t="n"/>
+      <c r="M13" s="168" t="n"/>
+      <c r="N13" s="192" t="n"/>
+      <c r="O13" s="192" t="n"/>
+      <c r="P13" s="192" t="n"/>
+      <c r="Q13" s="192" t="n"/>
+      <c r="R13" s="192" t="n"/>
+      <c r="S13" s="192" t="n"/>
+      <c r="T13" s="192" t="n"/>
+      <c r="U13" s="159" t="n"/>
+      <c r="V13" s="159" t="n"/>
+    </row>
+    <row r="14" ht="50.25" customHeight="1" s="143">
+      <c r="A14" s="144" t="n"/>
+      <c r="D14" s="160" t="n"/>
+      <c r="E14" s="160" t="n"/>
+      <c r="F14" s="188" t="inlineStr">
+        <is>
+          <t>CLV26</t>
+        </is>
+      </c>
+      <c r="G14" s="162" t="inlineStr">
+        <is>
+          <t>CL Oct 26</t>
+        </is>
+      </c>
+      <c r="H14" s="163" t="n"/>
+      <c r="I14" s="163" t="n"/>
+      <c r="J14" s="169" t="n"/>
+      <c r="K14" s="166" t="n"/>
+      <c r="L14" s="167" t="n"/>
+      <c r="M14" s="168" t="n"/>
+      <c r="N14" s="193" t="n"/>
+      <c r="O14" s="194" t="n"/>
+      <c r="P14" s="195" t="n"/>
+      <c r="Q14" s="195" t="n"/>
+      <c r="R14" s="196" t="n"/>
+      <c r="S14" s="197" t="n"/>
+      <c r="T14" s="197" t="n"/>
+      <c r="U14" s="159" t="n"/>
+      <c r="V14" s="159" t="n"/>
+    </row>
+    <row r="15" ht="50.25" customHeight="1" s="143">
+      <c r="A15" s="144" t="n"/>
+      <c r="D15" s="160" t="n"/>
+      <c r="E15" s="160" t="n"/>
+      <c r="F15" s="198" t="inlineStr">
+        <is>
+          <t>3:2:1</t>
+        </is>
+      </c>
+      <c r="G15" s="199" t="n"/>
+      <c r="H15" s="200" t="n"/>
+      <c r="I15" s="200" t="n"/>
+      <c r="J15" s="201" t="n"/>
+      <c r="K15" s="200" t="n"/>
+      <c r="L15" s="202" t="n"/>
+      <c r="M15" s="168" t="n"/>
+      <c r="N15" s="193" t="n"/>
+      <c r="O15" s="194" t="n"/>
+      <c r="P15" s="195" t="n"/>
+      <c r="Q15" s="195" t="n"/>
+      <c r="R15" s="196" t="n"/>
+      <c r="S15" s="197" t="n"/>
+      <c r="T15" s="197" t="n"/>
+      <c r="U15" s="159" t="n"/>
+      <c r="V15" s="159" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="143">
+      <c r="A16" s="144" t="n"/>
+      <c r="D16" s="160" t="n"/>
+      <c r="E16" s="160" t="n"/>
+      <c r="F16" s="203" t="n"/>
+      <c r="G16" s="204" t="n"/>
+      <c r="H16" s="204" t="n"/>
+      <c r="I16" s="204" t="n"/>
+      <c r="J16" s="204" t="n"/>
+      <c r="K16" s="204" t="n"/>
+      <c r="L16" s="204" t="n"/>
+      <c r="M16" s="204" t="n"/>
+      <c r="S16" s="205" t="n"/>
+      <c r="T16" s="205" t="n"/>
+    </row>
+    <row r="17" ht="44.25" customHeight="1" s="143">
+      <c r="A17" s="144" t="n"/>
+      <c r="F17" s="206" t="inlineStr">
+        <is>
+          <t>Z-SCORE MONITOR      z is for ENTRIES only - exits act on money, never on z.      The chime fires on the CROSSING of ENTRY_Z, once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="23.25" customHeight="1" s="143">
+      <c r="A18" s="144" t="n"/>
+      <c r="F18" s="207" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="H18" s="207" t="inlineStr">
+        <is>
+          <t>Z-score</t>
+        </is>
+      </c>
+      <c r="I18" s="207" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="J18" s="207" t="inlineStr">
+        <is>
+          <t>Std Dev</t>
+        </is>
+      </c>
+      <c r="K18" s="207" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="L18" s="207" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="N18" s="207" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="P18" s="207" t="inlineStr">
+        <is>
+          <t>Costs $</t>
+        </is>
+      </c>
+      <c r="Q18" s="207" t="inlineStr">
+        <is>
+          <t>Win $</t>
+        </is>
+      </c>
+      <c r="R18" s="207" t="inlineStr">
+        <is>
+          <t>TAKE PROFIT</t>
+        </is>
+      </c>
+      <c r="S18" s="207" t="inlineStr">
+        <is>
+          <t>TP in sigma</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50.25" customHeight="1" s="143">
+      <c r="A19" s="144" t="n"/>
+      <c r="F19" s="208" t="inlineStr">
+        <is>
+          <t>HO | CL Crack</t>
+        </is>
+      </c>
+      <c r="H19" s="209" t="n"/>
+      <c r="I19" s="210" t="n"/>
+      <c r="J19" s="210" t="n"/>
+      <c r="K19" s="211" t="n"/>
+      <c r="L19" s="211" t="n"/>
+      <c r="N19" s="212" t="n"/>
+      <c r="P19" s="213" t="n"/>
+      <c r="Q19" s="213" t="n"/>
+      <c r="R19" s="214" t="n"/>
+      <c r="S19" s="215" t="n"/>
+    </row>
+    <row r="20" ht="50.25" customHeight="1" s="143">
+      <c r="A20" s="144" t="n"/>
+      <c r="F20" s="208" t="inlineStr">
+        <is>
+          <t>BZ - CL</t>
+        </is>
+      </c>
+      <c r="H20" s="209" t="n"/>
+      <c r="I20" s="210" t="n"/>
+      <c r="J20" s="210" t="n"/>
+      <c r="K20" s="211" t="n"/>
+      <c r="L20" s="211" t="n"/>
+      <c r="N20" s="212" t="n"/>
+      <c r="P20" s="213" t="n"/>
+      <c r="Q20" s="213" t="n"/>
+      <c r="R20" s="214" t="n"/>
+      <c r="S20" s="215" t="n"/>
+    </row>
+    <row r="21" ht="50.25" customHeight="1" s="143">
+      <c r="A21" s="144" t="n"/>
+      <c r="F21" s="216" t="inlineStr">
+        <is>
+          <t>3:2:1</t>
+        </is>
+      </c>
+      <c r="H21" s="217" t="n"/>
+      <c r="I21" s="218" t="n"/>
+      <c r="J21" s="218" t="n"/>
+      <c r="K21" s="219" t="n"/>
+      <c r="L21" s="219" t="n"/>
+      <c r="N21" s="220" t="n"/>
+      <c r="P21" s="221" t="n"/>
+      <c r="Q21" s="221" t="n"/>
+      <c r="R21" s="222" t="n"/>
+      <c r="S21" s="223" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="143">
+      <c r="A22" s="144" t="n"/>
+      <c r="F22" s="224" t="n"/>
+      <c r="G22" s="225" t="n"/>
+      <c r="H22" s="225" t="n"/>
+      <c r="I22" s="225" t="n"/>
+      <c r="J22" s="225" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="143">
+      <c r="A23" s="144" t="n"/>
+      <c r="F23" s="226" t="inlineStr">
+        <is>
+          <t>STOPPED</t>
+        </is>
+      </c>
+      <c r="G23" s="225" t="n"/>
+      <c r="H23" s="227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" s="225" t="n"/>
+      <c r="J23" s="225" t="n"/>
+      <c r="N23" s="228" t="inlineStr">
         <is>
           <t xml:space="preserve">  &gt;  START  </t>
         </is>
       </c>
-      <c r="K1" s="70" t="inlineStr">
+      <c r="P23" s="229" t="inlineStr">
         <is>
           <t xml:space="preserve">  #  STOP  </t>
         </is>
       </c>
-      <c r="M1" s="71" t="inlineStr">
-        <is>
-          <t>Assign macros to shapes over these two cells: StartMonitor / StopMonitor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="67">
-      <c r="B2" s="72" t="inlineStr">
-        <is>
-          <t>z is for ENTRIES only.  Exits act on MONEY, never on z.   All execution is manual in TT - this workbook never places an order.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="67">
-      <c r="B3" s="73" t="inlineStr">
-        <is>
-          <t>Monitor</t>
-        </is>
-      </c>
-      <c r="C3" s="74" t="inlineStr">
-        <is>
-          <t>STOPPED</t>
-        </is>
-      </c>
-      <c r="E3" s="73" t="inlineStr">
-        <is>
-          <t>Rates</t>
-        </is>
-      </c>
-      <c r="F3" s="75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" s="76" t="n"/>
-      <c r="H3" s="76" t="n"/>
-      <c r="I3" s="76" t="n"/>
-      <c r="J3" s="76" t="n"/>
-      <c r="K3" s="76" t="n"/>
-      <c r="M3" s="71" t="inlineStr">
-        <is>
-          <t>Thresholds, costs and the take-profit rule all live on Config and take effect without a restart.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="67">
-      <c r="B4" s="73" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="C4" s="77" t="inlineStr">
-        <is>
-          <t>CME</t>
-        </is>
-      </c>
-      <c r="E4" s="73" t="inlineStr">
-        <is>
-          <t>Clock</t>
-        </is>
-      </c>
-      <c r="F4" s="78" t="inlineStr">
-        <is>
-          <t>--:--:--</t>
-        </is>
-      </c>
-      <c r="H4" s="73" t="inlineStr">
-        <is>
-          <t>Session</t>
-        </is>
-      </c>
-      <c r="J4" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" s="71" t="inlineStr">
-        <is>
-          <t>Costs, break-even, warm-up gates, feed rate and the edge filter are on the Detail sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6" ht="15" customHeight="1" s="67">
-      <c r="B6" s="80" t="inlineStr">
-        <is>
-          <t>BRENT / WTI</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="67">
-      <c r="B7" s="81" t="inlineStr">
-        <is>
-          <t>Instrument</t>
-        </is>
-      </c>
-      <c r="C7" s="81" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
-      <c r="D7" s="81" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="E7" s="81" t="inlineStr">
-        <is>
-          <t>Bid-Ask Gap</t>
-        </is>
-      </c>
-      <c r="G7" s="81" t="inlineStr">
-        <is>
-          <t>Statistic</t>
-        </is>
-      </c>
-      <c r="H7" s="81" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="J7" s="81" t="inlineStr">
-        <is>
-          <t>Trade</t>
-        </is>
-      </c>
-      <c r="K7" s="81" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="67">
-      <c r="B8" s="82" t="inlineStr">
-        <is>
-          <t>BZV6</t>
-        </is>
-      </c>
-      <c r="C8" s="83" t="n"/>
-      <c r="D8" s="83" t="n"/>
-      <c r="E8" s="83" t="n"/>
-      <c r="G8" s="84" t="inlineStr">
-        <is>
-          <t>Live Z-score</t>
-        </is>
-      </c>
-      <c r="H8" s="85" t="n"/>
-      <c r="J8" s="86" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="K8" s="78" t="n"/>
-      <c r="M8" s="71" t="inlineStr">
-        <is>
-          <t>Brent Last Day Financial Oct26</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="67">
-      <c r="B9" s="82" t="inlineStr">
-        <is>
-          <t>CLV6</t>
-        </is>
-      </c>
-      <c r="C9" s="83" t="n"/>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="83" t="n"/>
-      <c r="G9" s="86" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="H9" s="83" t="n"/>
-      <c r="J9" s="86" t="inlineStr">
-        <is>
-          <t>Entry (touch)</t>
-        </is>
-      </c>
-      <c r="K9" s="83" t="n"/>
-      <c r="M9" s="71" t="inlineStr">
-        <is>
-          <t>WTI Crude Oct26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="67">
-      <c r="B10" s="87" t="inlineStr">
-        <is>
-          <t>BZ - CL   SPREAD</t>
-        </is>
-      </c>
-      <c r="C10" s="88" t="n"/>
-      <c r="D10" s="88" t="n"/>
-      <c r="E10" s="88" t="n"/>
-      <c r="G10" s="86" t="inlineStr">
-        <is>
-          <t>Std Dev</t>
-        </is>
-      </c>
-      <c r="H10" s="83" t="n"/>
-      <c r="J10" s="84" t="inlineStr">
-        <is>
-          <t>TAKE PROFIT</t>
-        </is>
-      </c>
-      <c r="K10" s="89" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="67">
-      <c r="G11" s="86" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="H11" s="90" t="n"/>
-      <c r="J11" s="86" t="inlineStr">
-        <is>
-          <t>TP in sigma</t>
-        </is>
-      </c>
-      <c r="K11" s="91" t="n"/>
-    </row>
-    <row r="12"/>
-    <row r="13" ht="15" customHeight="1" s="67">
-      <c r="B13" s="80" t="inlineStr">
-        <is>
-          <t>ULSD / WTI   (HO/CL crack, $/bbl)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="67">
-      <c r="B14" s="81" t="inlineStr">
-        <is>
-          <t>Instrument</t>
-        </is>
-      </c>
-      <c r="C14" s="81" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
-      <c r="D14" s="81" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="E14" s="81" t="inlineStr">
-        <is>
-          <t>Bid-Ask Gap</t>
-        </is>
-      </c>
-      <c r="G14" s="81" t="inlineStr">
-        <is>
-          <t>Statistic</t>
-        </is>
-      </c>
-      <c r="H14" s="81" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="J14" s="81" t="inlineStr">
-        <is>
-          <t>Trade</t>
-        </is>
-      </c>
-      <c r="K14" s="81" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="67">
-      <c r="B15" s="82" t="inlineStr">
-        <is>
-          <t>HOV6</t>
-        </is>
-      </c>
-      <c r="C15" s="83" t="n"/>
-      <c r="D15" s="83" t="n"/>
-      <c r="E15" s="83" t="n"/>
-      <c r="G15" s="84" t="inlineStr">
-        <is>
-          <t>Live Z-score</t>
-        </is>
-      </c>
-      <c r="H15" s="85" t="n"/>
-      <c r="J15" s="86" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="K15" s="78" t="n"/>
-      <c r="M15" s="71" t="inlineStr">
-        <is>
-          <t>NY Harbor ULSD Oct26  (x42)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="67">
-      <c r="B16" s="82" t="inlineStr">
-        <is>
-          <t>CLV6</t>
-        </is>
-      </c>
-      <c r="C16" s="83" t="n"/>
-      <c r="D16" s="83" t="n"/>
-      <c r="E16" s="83" t="n"/>
-      <c r="G16" s="86" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="H16" s="83" t="n"/>
-      <c r="J16" s="86" t="inlineStr">
-        <is>
-          <t>Entry (touch)</t>
-        </is>
-      </c>
-      <c r="K16" s="83" t="n"/>
-      <c r="M16" s="71" t="inlineStr">
-        <is>
-          <t>WTI Crude Oct26</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="67">
-      <c r="B17" s="87" t="inlineStr">
-        <is>
-          <t>HO - CL   CRACK SPREAD</t>
-        </is>
-      </c>
-      <c r="C17" s="88" t="n"/>
-      <c r="D17" s="88" t="n"/>
-      <c r="E17" s="88" t="n"/>
-      <c r="G17" s="86" t="inlineStr">
-        <is>
-          <t>Std Dev</t>
-        </is>
-      </c>
-      <c r="H17" s="83" t="n"/>
-      <c r="J17" s="84" t="inlineStr">
-        <is>
-          <t>TAKE PROFIT</t>
-        </is>
-      </c>
-      <c r="K17" s="89" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="67">
-      <c r="G18" s="86" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="H18" s="90" t="n"/>
-      <c r="J18" s="86" t="inlineStr">
-        <is>
-          <t>TP in sigma</t>
-        </is>
-      </c>
-      <c r="K18" s="91" t="n"/>
-    </row>
-    <row r="19"/>
-    <row r="20" ht="15" customHeight="1" s="67">
-      <c r="B20" s="80" t="inlineStr">
-        <is>
-          <t>3:2:1 CRACK   ((2 x RB + 1 x HO) x 42 / 3) - CL,  $/bbl</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="67">
-      <c r="B21" s="81" t="inlineStr">
-        <is>
-          <t>Instrument</t>
-        </is>
-      </c>
-      <c r="C21" s="81" t="inlineStr">
-        <is>
-          <t>Bid</t>
-        </is>
-      </c>
-      <c r="D21" s="81" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="E21" s="81" t="inlineStr">
-        <is>
-          <t>Bid-Ask Gap</t>
-        </is>
-      </c>
-      <c r="G21" s="81" t="inlineStr">
-        <is>
-          <t>Statistic</t>
-        </is>
-      </c>
-      <c r="H21" s="81" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="J21" s="81" t="inlineStr">
-        <is>
-          <t>Trade</t>
-        </is>
-      </c>
-      <c r="K21" s="81" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="67">
-      <c r="B22" s="82" t="inlineStr">
-        <is>
-          <t>RBV6</t>
-        </is>
-      </c>
-      <c r="C22" s="83" t="n"/>
-      <c r="D22" s="83" t="n"/>
-      <c r="E22" s="83" t="n"/>
-      <c r="G22" s="84" t="inlineStr">
-        <is>
-          <t>Live Z-score</t>
-        </is>
-      </c>
-      <c r="H22" s="85" t="n"/>
-      <c r="J22" s="86" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="K22" s="78" t="n"/>
-      <c r="M22" s="71" t="inlineStr">
-        <is>
-          <t>RBOB Gasoline Oct26  (x42, weight 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="67">
-      <c r="B23" s="82" t="inlineStr">
-        <is>
-          <t>HOV6</t>
-        </is>
-      </c>
-      <c r="C23" s="83" t="n"/>
-      <c r="D23" s="83" t="n"/>
-      <c r="E23" s="83" t="n"/>
-      <c r="G23" s="86" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="H23" s="83" t="n"/>
-      <c r="J23" s="86" t="inlineStr">
-        <is>
-          <t>Entry (touch)</t>
-        </is>
-      </c>
-      <c r="K23" s="83" t="n"/>
-      <c r="M23" s="71" t="inlineStr">
-        <is>
-          <t>NY Harbor ULSD Oct26  (x42, weight 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="67">
-      <c r="B24" s="82" t="inlineStr">
-        <is>
-          <t>CLV6</t>
-        </is>
-      </c>
-      <c r="C24" s="83" t="n"/>
-      <c r="D24" s="83" t="n"/>
-      <c r="E24" s="83" t="n"/>
-      <c r="G24" s="86" t="inlineStr">
-        <is>
-          <t>Std Dev</t>
-        </is>
-      </c>
-      <c r="H24" s="83" t="n"/>
-      <c r="J24" s="84" t="inlineStr">
-        <is>
-          <t>TAKE PROFIT</t>
-        </is>
-      </c>
-      <c r="K24" s="89" t="n"/>
-      <c r="M24" s="71" t="inlineStr">
-        <is>
-          <t>WTI Crude Oct26  (weight 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="67">
-      <c r="B25" s="87" t="inlineStr">
-        <is>
-          <t>3:2:1   CRACK SPREAD</t>
-        </is>
-      </c>
-      <c r="C25" s="88" t="n"/>
-      <c r="D25" s="88" t="n"/>
-      <c r="E25" s="88" t="n"/>
-      <c r="G25" s="86" t="inlineStr">
-        <is>
-          <t>Window</t>
-        </is>
-      </c>
-      <c r="H25" s="90" t="n"/>
-      <c r="J25" s="86" t="inlineStr">
-        <is>
-          <t>TP in sigma</t>
-        </is>
-      </c>
-      <c r="K25" s="91" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27" ht="15" customHeight="1" s="67">
-      <c r="B27" s="80" t="inlineStr">
-        <is>
-          <t>TAKE-PROFIT RULE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="67">
-      <c r="B28" s="92" t="inlineStr">
-        <is>
-          <t>Take Profit  =  Entry  +  Costs  +  (WIN_PCT x Notional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="67">
-      <c r="B29" s="71" t="inlineStr">
-        <is>
-          <t>Signed by direction: a short-spread trade takes profit BELOW entry, a long-spread trade above it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="67">
-      <c r="B30" s="71" t="inlineStr">
-        <is>
-          <t>Costs = commission + crossing, from the Config rate card. Both are shown in full on the Detail sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="67">
-      <c r="B31" s="71" t="inlineStr">
-        <is>
-          <t>WIN_PCT and NOTIONAL_BASIS are Config cells. NOTIONAL_BASIS decides what the percentage is taken OF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="67">
-      <c r="B32" s="71" t="inlineStr">
-        <is>
-          <t>TP in sigma is the reachability check: how far the target sits from entry, in standard deviations. It turns amber when that exceeds the live |z| - meaning the target is PAST the mean, so it needs the spread to overshoot rather than merely revert. That is a different bet from the one z measured.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34" ht="15" customHeight="1" s="67">
-      <c r="B34" s="93" t="inlineStr">
-        <is>
-          <t>READ THIS BEFORE TRADING FROM IT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="67">
-      <c r="B35" s="94" t="inlineStr">
-        <is>
-          <t>z is for ENTRIES only. Exits act on MONEY, never on z. The TAKE PROFIT cell, not the z, tells you when to get out.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="67">
-      <c r="B36" s="94" t="inlineStr">
-        <is>
-          <t>z WILL STEP at each stats refresh. That is expected, not a fault - mean and sigma are recomputed every STATS_REFRESH_MIN minutes and held frozen in between.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="67">
-      <c r="B37" s="94" t="inlineStr">
-        <is>
-          <t>Freezing the reference is a feature. A continuously-updating mean chases the spread, so an open position's z drifts back toward zero without the price ever paying you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="67">
-      <c r="B38" s="94" t="inlineStr">
-        <is>
-          <t>A blank z means the window is not usable yet - warming up, degenerate, or the feed is stale. A blank is honest; a number would not be.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="67">
-      <c r="B39" s="94" t="inlineStr">
-        <is>
-          <t>The chime fires on the CROSSING of ENTRY_Z, once, not continuously while the condition holds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="67">
-      <c r="B40" s="93" t="inlineStr">
-        <is>
-          <t>SIGMA ON THESE SPREADS HAS NEVER BEEN MEASURED. Every cost and take-profit threshold is contingent on it. Measuring it is a main purpose of this tool.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="67">
-      <c r="B41" s="94" t="inlineStr">
-        <is>
-          <t>Brent/WTI is a RELATED pair, not a basis pair - two different crudes, no arbitrage tying them, so no theoretical fair value. The only anchor is the spread's own empirical mean.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="67">
-      <c r="B42" s="95" t="inlineStr">
-        <is>
-          <t>NO CELL ON THIS SHEET IS A FORMULA. Every value is written by VBA only when it differs from what is already there - that is what stops the display flashing on every uptick.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="67">
-      <c r="B43" s="71" t="inlineStr">
-        <is>
-          <t>All RTD() formulas live on the hidden Feed sheet. There is no volatile function anywhere in this workbook.</t>
-        </is>
-      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="143">
+      <c r="A24" s="144" t="n"/>
+      <c r="F24" s="224" t="n"/>
+      <c r="G24" s="225" t="n"/>
+      <c r="H24" s="225" t="n"/>
+      <c r="I24" s="225" t="n"/>
+      <c r="J24" s="225" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="A25" s="144" t="n"/>
+    </row>
+    <row r="26" ht="39.75" customHeight="1" s="143">
+      <c r="A26" s="144" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="143">
+      <c r="A27" s="144" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="A28" s="144" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="143">
+      <c r="A29" s="144" t="n"/>
+      <c r="F29" s="224" t="n"/>
+      <c r="G29" s="225" t="n"/>
+      <c r="H29" s="225" t="n"/>
+      <c r="I29" s="225" t="n"/>
+      <c r="J29" s="225" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1" s="143">
+      <c r="A30" s="144" t="n"/>
+      <c r="F30" s="224" t="n"/>
+      <c r="G30" s="225" t="n"/>
+      <c r="H30" s="225" t="n"/>
+      <c r="I30" s="225" t="n"/>
+      <c r="J30" s="225" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="143">
+      <c r="A31" s="144" t="n"/>
+      <c r="F31" s="224" t="n"/>
+      <c r="G31" s="225" t="n"/>
+      <c r="H31" s="225" t="n"/>
+      <c r="I31" s="225" t="n"/>
+      <c r="J31" s="225" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="143">
+      <c r="A32" s="144" t="n"/>
+      <c r="F32" s="224" t="n"/>
+      <c r="G32" s="225" t="n"/>
+      <c r="H32" s="225" t="n"/>
+      <c r="I32" s="225" t="n"/>
+      <c r="J32" s="225" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1" s="143">
+      <c r="A33" s="144" t="n"/>
+      <c r="F33" s="224" t="n"/>
+      <c r="G33" s="225" t="n"/>
+      <c r="H33" s="225" t="n"/>
+      <c r="I33" s="225" t="n"/>
+      <c r="J33" s="225" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="143">
+      <c r="A34" s="144" t="n"/>
+      <c r="F34" s="224" t="n"/>
+      <c r="G34" s="225" t="n"/>
+      <c r="H34" s="225" t="n"/>
+      <c r="I34" s="225" t="n"/>
+      <c r="J34" s="225" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="143">
+      <c r="A35" s="144" t="n"/>
+      <c r="F35" s="224" t="n"/>
+      <c r="G35" s="225" t="n"/>
+      <c r="H35" s="225" t="n"/>
+      <c r="I35" s="225" t="n"/>
+      <c r="J35" s="225" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1" s="143">
+      <c r="A36" s="144" t="n"/>
+      <c r="F36" s="224" t="n"/>
+      <c r="G36" s="225" t="n"/>
+      <c r="H36" s="225" t="n"/>
+      <c r="I36" s="225" t="n"/>
+      <c r="J36" s="225" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1" s="143">
+      <c r="A37" s="144" t="n"/>
+      <c r="F37" s="224" t="n"/>
+      <c r="G37" s="225" t="n"/>
+      <c r="H37" s="225" t="n"/>
+      <c r="I37" s="225" t="n"/>
+      <c r="J37" s="225" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1" s="143">
+      <c r="A38" s="144" t="n"/>
+      <c r="F38" s="224" t="n"/>
+      <c r="G38" s="225" t="n"/>
+      <c r="H38" s="225" t="n"/>
+      <c r="I38" s="225" t="n"/>
+      <c r="J38" s="225" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="143">
+      <c r="A39" s="144" t="n"/>
+      <c r="F39" s="224" t="n"/>
+      <c r="G39" s="225" t="n"/>
+      <c r="H39" s="225" t="n"/>
+      <c r="I39" s="225" t="n"/>
+      <c r="J39" s="225" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="143">
+      <c r="F40" s="224" t="n"/>
+      <c r="G40" s="225" t="n"/>
+      <c r="H40" s="225" t="n"/>
+      <c r="I40" s="225" t="n"/>
+      <c r="J40" s="225" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1" s="143">
+      <c r="F41" s="224" t="n"/>
+      <c r="G41" s="225" t="n"/>
+      <c r="H41" s="225" t="n"/>
+      <c r="I41" s="225" t="n"/>
+      <c r="J41" s="225" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="143">
+      <c r="F42" s="224" t="n"/>
+      <c r="G42" s="225" t="n"/>
+      <c r="H42" s="225" t="n"/>
+      <c r="I42" s="225" t="n"/>
+      <c r="J42" s="225" t="n"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" s="143">
+      <c r="F43" s="224" t="n"/>
+      <c r="G43" s="225" t="n"/>
+      <c r="H43" s="225" t="n"/>
+      <c r="I43" s="225" t="n"/>
+      <c r="J43" s="225" t="n"/>
+    </row>
+    <row r="44" ht="36" customHeight="1" s="143">
+      <c r="F44" s="224" t="n"/>
+      <c r="G44" s="225" t="n"/>
+      <c r="H44" s="225" t="n"/>
+      <c r="I44" s="225" t="n"/>
+      <c r="J44" s="225" t="n"/>
+    </row>
+    <row r="45" ht="36" customHeight="1" s="143">
+      <c r="F45" s="224" t="n"/>
+      <c r="G45" s="225" t="n"/>
+      <c r="H45" s="225" t="n"/>
+      <c r="I45" s="225" t="n"/>
+      <c r="J45" s="225" t="n"/>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="143">
+      <c r="F46" s="224" t="n"/>
+      <c r="G46" s="225" t="n"/>
+      <c r="H46" s="225" t="n"/>
+      <c r="I46" s="225" t="n"/>
+      <c r="J46" s="225" t="n"/>
+    </row>
+    <row r="47" ht="36" customHeight="1" s="143">
+      <c r="F47" s="224" t="n"/>
+      <c r="G47" s="225" t="n"/>
+      <c r="H47" s="225" t="n"/>
+      <c r="I47" s="225" t="n"/>
+      <c r="J47" s="225" t="n"/>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="143">
+      <c r="F48" s="224" t="n"/>
+      <c r="G48" s="225" t="n"/>
+      <c r="H48" s="225" t="n"/>
+      <c r="I48" s="225" t="n"/>
+      <c r="J48" s="225" t="n"/>
+    </row>
+    <row r="49" ht="36" customHeight="1" s="143">
+      <c r="F49" s="224" t="n"/>
+      <c r="G49" s="225" t="n"/>
+      <c r="H49" s="225" t="n"/>
+      <c r="I49" s="225" t="n"/>
+      <c r="J49" s="225" t="n"/>
+    </row>
+    <row r="50" ht="36" customHeight="1" s="143">
+      <c r="F50" s="224" t="n"/>
+      <c r="G50" s="225" t="n"/>
+      <c r="H50" s="225" t="n"/>
+      <c r="I50" s="225" t="n"/>
+      <c r="J50" s="225" t="n"/>
+    </row>
+    <row r="51" ht="36" customHeight="1" s="143">
+      <c r="F51" s="224" t="n"/>
+      <c r="G51" s="225" t="n"/>
+      <c r="H51" s="225" t="n"/>
+      <c r="I51" s="225" t="n"/>
+      <c r="J51" s="225" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="F3:K3"/>
+  <mergeCells count="4">
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:T2"/>
+    <mergeCell ref="F17:T17"/>
   </mergeCells>
-  <conditionalFormatting sqref="H8">
+  <conditionalFormatting sqref="H19">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$8="NO USABLE Z",$K$8="STALE FEED")</formula>
+      <formula>OR($K$19="NO USABLE Z",$K$19="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$8="WARMING UP"</formula>
+      <formula>$K$19="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$8="ABOVE CEILING"</formula>
+      <formula>$K$19="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$8="ENTRY BAND"</formula>
+      <formula>$K$19="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8">
+  <conditionalFormatting sqref="K19">
     <cfRule type="expression" rank="0" priority="6" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$8="NO USABLE Z",$K$8="STALE FEED")</formula>
+      <formula>OR($K$19="NO USABLE Z",$K$19="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="7" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$8="WARMING UP"</formula>
+      <formula>$K$19="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="8" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$8="ABOVE CEILING"</formula>
+      <formula>$K$19="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="9" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$8="ENTRY BAND"</formula>
+      <formula>$K$19="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11">
+  <conditionalFormatting sqref="S19">
     <cfRule type="expression" rank="0" priority="10" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>AND(ISNUMBER($K$11),ISNUMBER($H$8),$K$11&gt;ABS($H$8))</formula>
+      <formula>AND(ISNUMBER($S$19),ISNUMBER($H$19),$S$19&gt;ABS($H$19))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
+  <conditionalFormatting sqref="H20">
     <cfRule type="expression" rank="0" priority="11" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$15="NO USABLE Z",$K$15="STALE FEED")</formula>
+      <formula>OR($K$20="NO USABLE Z",$K$20="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="12" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$15="WARMING UP"</formula>
+      <formula>$K$20="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="13" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$15="ABOVE CEILING"</formula>
+      <formula>$K$20="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="14" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$15="ENTRY BAND"</formula>
+      <formula>$K$20="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K15">
+  <conditionalFormatting sqref="K20">
     <cfRule type="expression" rank="0" priority="15" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$15="NO USABLE Z",$K$15="STALE FEED")</formula>
+      <formula>OR($K$20="NO USABLE Z",$K$20="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="16" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$15="WARMING UP"</formula>
+      <formula>$K$20="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="17" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$15="ABOVE CEILING"</formula>
+      <formula>$K$20="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="18" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$15="ENTRY BAND"</formula>
+      <formula>$K$20="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K18">
+  <conditionalFormatting sqref="S20">
     <cfRule type="expression" rank="0" priority="19" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>AND(ISNUMBER($K$18),ISNUMBER($H$15),$K$18&gt;ABS($H$15))</formula>
+      <formula>AND(ISNUMBER($S$20),ISNUMBER($H$20),$S$20&gt;ABS($H$20))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22">
+  <conditionalFormatting sqref="H21">
     <cfRule type="expression" rank="0" priority="20" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$22="NO USABLE Z",$K$22="STALE FEED")</formula>
+      <formula>OR($K$21="NO USABLE Z",$K$21="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="21" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$22="WARMING UP"</formula>
+      <formula>$K$21="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="22" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$22="ABOVE CEILING"</formula>
+      <formula>$K$21="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="23" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$22="ENTRY BAND"</formula>
+      <formula>$K$21="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K22">
+  <conditionalFormatting sqref="K21">
     <cfRule type="expression" rank="0" priority="24" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$22="NO USABLE Z",$K$22="STALE FEED")</formula>
+      <formula>OR($K$21="NO USABLE Z",$K$21="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="25" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$22="WARMING UP"</formula>
+      <formula>$K$21="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="26" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$22="ABOVE CEILING"</formula>
+      <formula>$K$21="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="27" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$22="ENTRY BAND"</formula>
+      <formula>$K$21="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K25">
+  <conditionalFormatting sqref="S21">
     <cfRule type="expression" rank="0" priority="28" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>AND(ISNUMBER($K$25),ISNUMBER($H$22),$K$25&gt;ABS($H$22))</formula>
+      <formula>AND(ISNUMBER($S$21),ISNUMBER($H$21),$S$21&gt;ABS($H$21))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3">
+  <conditionalFormatting sqref="F23">
     <cfRule type="expression" rank="0" priority="29" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>C3="RUNNING"</formula>
+      <formula>F23="RUNNING"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" scale="91" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1844,1025 +2780,1025 @@
   <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="3" customWidth="1" style="66" min="1" max="1"/>
-    <col width="32" customWidth="1" style="66" min="2" max="2"/>
-    <col width="20" customWidth="1" style="66" min="3" max="3"/>
-    <col width="18" customWidth="1" style="66" min="4" max="7"/>
-    <col width="12" customWidth="1" style="66" min="8" max="11"/>
-    <col width="14" customWidth="1" style="66" min="12" max="12"/>
-    <col width="46" customWidth="1" style="66" min="13" max="13"/>
+    <col width="3" customWidth="1" style="141" min="1" max="1"/>
+    <col width="32" customWidth="1" style="141" min="2" max="2"/>
+    <col width="20" customWidth="1" style="141" min="3" max="3"/>
+    <col width="18" customWidth="1" style="141" min="4" max="7"/>
+    <col width="12" customWidth="1" style="141" min="8" max="11"/>
+    <col width="14" customWidth="1" style="141" min="12" max="12"/>
+    <col width="46" customWidth="1" style="141" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.35" customHeight="1" s="67">
-      <c r="B1" s="96" t="inlineStr">
+    <row r="1" ht="17.35" customHeight="1" s="143">
+      <c r="B1" s="230" t="inlineStr">
         <is>
           <t>DETAIL   -   full breakdown behind the Dashboard</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="67">
-      <c r="B2" s="71" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="B2" s="231" t="inlineStr">
         <is>
           <t>Same engine, same numbers. The Dashboard shows the three spreads you trade from; this sheet shows everything that stands behind them, for all four slots.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="15" customHeight="1" s="67">
-      <c r="B4" s="80" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="143">
+      <c r="B4" s="232" t="inlineStr">
         <is>
           <t>OUTRIGHT LEGS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="67">
-      <c r="B5" s="81" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="B5" s="233" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C5" s="81" t="inlineStr">
+      <c r="C5" s="233" t="inlineStr">
         <is>
           <t>Instrument ID</t>
         </is>
       </c>
-      <c r="D5" s="81" t="inlineStr">
+      <c r="D5" s="233" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="81" t="inlineStr">
+      <c r="E5" s="233" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H5" s="81" t="inlineStr">
+      <c r="H5" s="233" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I5" s="81" t="inlineStr">
+      <c r="I5" s="233" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J5" s="81" t="inlineStr">
+      <c r="J5" s="233" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K5" s="81" t="inlineStr">
+      <c r="K5" s="233" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L5" s="81" t="inlineStr">
+      <c r="L5" s="233" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="M5" s="81" t="inlineStr">
+      <c r="M5" s="233" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="67">
-      <c r="B6" s="82" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="143">
+      <c r="B6" s="234" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="C6" s="97" t="n"/>
-      <c r="D6" s="98" t="inlineStr">
+      <c r="C6" s="235" t="n"/>
+      <c r="D6" s="236" t="inlineStr">
         <is>
           <t>RBOB Gasoline Oct26</t>
         </is>
       </c>
-      <c r="E6" s="99" t="inlineStr">
+      <c r="E6" s="237" t="inlineStr">
         <is>
           <t>42,000 gal</t>
         </is>
       </c>
-      <c r="H6" s="83" t="n"/>
-      <c r="I6" s="83" t="n"/>
-      <c r="J6" s="83" t="n"/>
-      <c r="K6" s="83" t="n"/>
-      <c r="L6" s="83" t="n"/>
-      <c r="M6" s="83" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="67">
-      <c r="B7" s="82" t="inlineStr">
+      <c r="H6" s="238" t="n"/>
+      <c r="I6" s="238" t="n"/>
+      <c r="J6" s="238" t="n"/>
+      <c r="K6" s="238" t="n"/>
+      <c r="L6" s="238" t="n"/>
+      <c r="M6" s="238" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="143">
+      <c r="B7" s="234" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="C7" s="97" t="n"/>
-      <c r="D7" s="98" t="inlineStr">
+      <c r="C7" s="235" t="n"/>
+      <c r="D7" s="236" t="inlineStr">
         <is>
           <t>NY Harbor ULSD Oct26</t>
         </is>
       </c>
-      <c r="E7" s="99" t="inlineStr">
+      <c r="E7" s="237" t="inlineStr">
         <is>
           <t>42,000 gal</t>
         </is>
       </c>
-      <c r="H7" s="83" t="n"/>
-      <c r="I7" s="83" t="n"/>
-      <c r="J7" s="83" t="n"/>
-      <c r="K7" s="83" t="n"/>
-      <c r="L7" s="83" t="n"/>
-      <c r="M7" s="83" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="67">
-      <c r="B8" s="82" t="inlineStr">
+      <c r="H7" s="238" t="n"/>
+      <c r="I7" s="238" t="n"/>
+      <c r="J7" s="238" t="n"/>
+      <c r="K7" s="238" t="n"/>
+      <c r="L7" s="238" t="n"/>
+      <c r="M7" s="238" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="143">
+      <c r="B8" s="234" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="C8" s="97" t="n"/>
-      <c r="D8" s="98" t="inlineStr">
+      <c r="C8" s="235" t="n"/>
+      <c r="D8" s="236" t="inlineStr">
         <is>
           <t>WTI Crude Oct26</t>
         </is>
       </c>
-      <c r="E8" s="99" t="inlineStr">
+      <c r="E8" s="237" t="inlineStr">
         <is>
           <t>1,000 bbl</t>
         </is>
       </c>
-      <c r="H8" s="83" t="n"/>
-      <c r="I8" s="83" t="n"/>
-      <c r="J8" s="83" t="n"/>
-      <c r="K8" s="83" t="n"/>
-      <c r="L8" s="83" t="n"/>
-      <c r="M8" s="83" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="67">
-      <c r="B9" s="82" t="inlineStr">
+      <c r="H8" s="238" t="n"/>
+      <c r="I8" s="238" t="n"/>
+      <c r="J8" s="238" t="n"/>
+      <c r="K8" s="238" t="n"/>
+      <c r="L8" s="238" t="n"/>
+      <c r="M8" s="238" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="B9" s="234" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="C9" s="97" t="n"/>
-      <c r="D9" s="98" t="inlineStr">
+      <c r="C9" s="235" t="n"/>
+      <c r="D9" s="236" t="inlineStr">
         <is>
           <t>Brent Last Day Fin Oct26</t>
         </is>
       </c>
-      <c r="E9" s="99" t="inlineStr">
+      <c r="E9" s="237" t="inlineStr">
         <is>
           <t>1,000 bbl</t>
         </is>
       </c>
-      <c r="H9" s="83" t="n"/>
-      <c r="I9" s="83" t="n"/>
-      <c r="J9" s="83" t="n"/>
-      <c r="K9" s="83" t="n"/>
-      <c r="L9" s="83" t="n"/>
-      <c r="M9" s="83" t="n"/>
+      <c r="H9" s="238" t="n"/>
+      <c r="I9" s="238" t="n"/>
+      <c r="J9" s="238" t="n"/>
+      <c r="K9" s="238" t="n"/>
+      <c r="L9" s="238" t="n"/>
+      <c r="M9" s="238" t="n"/>
     </row>
     <row r="10"/>
-    <row r="11" ht="15" customHeight="1" s="67">
-      <c r="B11" s="80" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="143">
+      <c r="B11" s="232" t="inlineStr">
         <is>
           <t>DERIVED &amp; LISTED SPREADS</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="67">
-      <c r="B12" s="81" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="143">
+      <c r="B12" s="233" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C12" s="81" t="inlineStr">
+      <c r="C12" s="233" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="D12" s="81" t="inlineStr">
+      <c r="D12" s="233" t="inlineStr">
         <is>
           <t>Crossing convention</t>
         </is>
       </c>
-      <c r="H12" s="81" t="inlineStr">
+      <c r="H12" s="233" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I12" s="81" t="inlineStr">
+      <c r="I12" s="233" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="L12" s="81" t="inlineStr">
+      <c r="L12" s="233" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="M12" s="81" t="inlineStr">
+      <c r="M12" s="233" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="67">
-      <c r="B13" s="82" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="143">
+      <c r="B13" s="234" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="C13" s="99" t="inlineStr">
+      <c r="C13" s="237" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D13" s="100" t="inlineStr">
+      <c r="D13" s="239" t="inlineStr">
         <is>
           <t>bid = BZ bid - CL ask ; ask = BZ ask - CL bid</t>
         </is>
       </c>
-      <c r="H13" s="83" t="n"/>
-      <c r="I13" s="83" t="n"/>
-      <c r="L13" s="83" t="n"/>
-      <c r="M13" s="83" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="67">
-      <c r="B14" s="82" t="inlineStr">
+      <c r="H13" s="238" t="n"/>
+      <c r="I13" s="238" t="n"/>
+      <c r="L13" s="238" t="n"/>
+      <c r="M13" s="238" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="143">
+      <c r="B14" s="234" t="inlineStr">
         <is>
           <t>HO/CL crack</t>
         </is>
       </c>
-      <c r="C14" s="99" t="inlineStr">
+      <c r="C14" s="237" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D14" s="100" t="inlineStr">
+      <c r="D14" s="239" t="inlineStr">
         <is>
           <t>bid = HO bid x42 - CL ask ; ask = HO ask x42 - CL bid</t>
         </is>
       </c>
-      <c r="H14" s="83" t="n"/>
-      <c r="I14" s="83" t="n"/>
-      <c r="L14" s="83" t="n"/>
-      <c r="M14" s="83" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="67">
-      <c r="B15" s="82" t="inlineStr">
+      <c r="H14" s="238" t="n"/>
+      <c r="I14" s="238" t="n"/>
+      <c r="L14" s="238" t="n"/>
+      <c r="M14" s="238" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="143">
+      <c r="B15" s="234" t="inlineStr">
         <is>
           <t>3:2:1 crack</t>
         </is>
       </c>
-      <c r="C15" s="99" t="inlineStr">
+      <c r="C15" s="237" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D15" s="100" t="inlineStr">
+      <c r="D15" s="239" t="inlineStr">
         <is>
           <t>bid sells products at the bid and buys crude at the ask; ask mirrors it</t>
         </is>
       </c>
-      <c r="H15" s="83" t="n"/>
-      <c r="I15" s="83" t="n"/>
-      <c r="L15" s="83" t="n"/>
-      <c r="M15" s="83" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="67">
-      <c r="B16" s="82" t="inlineStr">
+      <c r="H15" s="238" t="n"/>
+      <c r="I15" s="238" t="n"/>
+      <c r="L15" s="238" t="n"/>
+      <c r="M15" s="238" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="143">
+      <c r="B16" s="234" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="C16" s="99" t="inlineStr">
+      <c r="C16" s="237" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="D16" s="100" t="inlineStr">
+      <c r="D16" s="239" t="inlineStr">
         <is>
           <t>exchange-listed - one quote, no leg risk</t>
         </is>
       </c>
-      <c r="H16" s="83" t="n"/>
-      <c r="I16" s="83" t="n"/>
-      <c r="L16" s="83" t="n"/>
-      <c r="M16" s="83" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="67">
-      <c r="B17" s="82" t="inlineStr">
+      <c r="H16" s="238" t="n"/>
+      <c r="I16" s="238" t="n"/>
+      <c r="L16" s="238" t="n"/>
+      <c r="M16" s="238" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="143">
+      <c r="B17" s="234" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="C17" s="99" t="inlineStr">
+      <c r="C17" s="237" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="D17" s="100" t="inlineStr">
+      <c r="D17" s="239" t="inlineStr">
         <is>
           <t>exchange-listed - one quote, no leg risk</t>
         </is>
       </c>
-      <c r="H17" s="83" t="n"/>
-      <c r="I17" s="83" t="n"/>
-      <c r="L17" s="83" t="n"/>
-      <c r="M17" s="83" t="n"/>
+      <c r="H17" s="238" t="n"/>
+      <c r="I17" s="238" t="n"/>
+      <c r="L17" s="238" t="n"/>
+      <c r="M17" s="238" t="n"/>
     </row>
     <row r="18"/>
-    <row r="19" ht="15" customHeight="1" s="67">
-      <c r="B19" s="80" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="143">
+      <c r="B19" s="232" t="inlineStr">
         <is>
           <t>PER-SPREAD BREAKDOWN</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="67">
-      <c r="B20" s="81" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="143">
+      <c r="B20" s="233" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C20" s="81" t="inlineStr">
+      <c r="C20" s="233" t="inlineStr">
         <is>
           <t>Unit / note</t>
         </is>
       </c>
-      <c r="D20" s="81" t="inlineStr">
+      <c r="D20" s="233" t="inlineStr">
         <is>
           <t>SPREAD 1</t>
         </is>
       </c>
-      <c r="E20" s="81" t="inlineStr">
+      <c r="E20" s="233" t="inlineStr">
         <is>
           <t>SPREAD 2</t>
         </is>
       </c>
-      <c r="F20" s="81" t="inlineStr">
+      <c r="F20" s="233" t="inlineStr">
         <is>
           <t>SPREAD 3</t>
         </is>
       </c>
-      <c r="G20" s="81" t="inlineStr">
+      <c r="G20" s="233" t="inlineStr">
         <is>
           <t>SPREAD 4</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="67">
-      <c r="B21" s="86" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="143">
+      <c r="B21" s="240" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C21" s="100" t="n"/>
-      <c r="D21" s="90" t="n"/>
-      <c r="E21" s="90" t="n"/>
-      <c r="F21" s="90" t="n"/>
-      <c r="G21" s="90" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="67">
-      <c r="B22" s="86" t="inlineStr">
+      <c r="C21" s="239" t="n"/>
+      <c r="D21" s="241" t="n"/>
+      <c r="E21" s="241" t="n"/>
+      <c r="F21" s="241" t="n"/>
+      <c r="G21" s="241" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="143">
+      <c r="B22" s="240" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C22" s="100" t="inlineStr">
+      <c r="C22" s="239" t="inlineStr">
         <is>
           <t>LegB - beta x LegA</t>
         </is>
       </c>
-      <c r="D22" s="90" t="n"/>
-      <c r="E22" s="90" t="n"/>
-      <c r="F22" s="90" t="n"/>
-      <c r="G22" s="90" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="67">
-      <c r="B23" s="86" t="inlineStr">
+      <c r="D22" s="241" t="n"/>
+      <c r="E22" s="241" t="n"/>
+      <c r="F22" s="241" t="n"/>
+      <c r="G22" s="241" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="143">
+      <c r="B23" s="240" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="C23" s="100" t="n"/>
-      <c r="D23" s="90" t="n"/>
-      <c r="E23" s="90" t="n"/>
-      <c r="F23" s="90" t="n"/>
-      <c r="G23" s="90" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="67">
-      <c r="B24" s="86" t="inlineStr">
+      <c r="C23" s="239" t="n"/>
+      <c r="D23" s="241" t="n"/>
+      <c r="E23" s="241" t="n"/>
+      <c r="F23" s="241" t="n"/>
+      <c r="G23" s="241" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="143">
+      <c r="B24" s="240" t="inlineStr">
         <is>
           <t>HEDGE_RATIO (beta)</t>
         </is>
       </c>
-      <c r="C24" s="100" t="inlineStr">
+      <c r="C24" s="239" t="inlineStr">
         <is>
           <t>stamped pair -&gt;</t>
         </is>
       </c>
-      <c r="D24" s="90" t="n"/>
-      <c r="E24" s="90" t="n"/>
-      <c r="F24" s="90" t="n"/>
-      <c r="G24" s="90" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="67">
-      <c r="B25" s="86" t="inlineStr">
+      <c r="D24" s="241" t="n"/>
+      <c r="E24" s="241" t="n"/>
+      <c r="F24" s="241" t="n"/>
+      <c r="G24" s="241" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="B25" s="240" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread</t>
         </is>
       </c>
-      <c r="C25" s="100" t="inlineStr">
+      <c r="C25" s="239" t="inlineStr">
         <is>
           <t>per lot</t>
         </is>
       </c>
-      <c r="D25" s="101" t="n"/>
-      <c r="E25" s="101" t="n"/>
-      <c r="F25" s="101" t="n"/>
-      <c r="G25" s="101" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="67">
-      <c r="B26" s="102" t="inlineStr">
+      <c r="D25" s="242" t="n"/>
+      <c r="E25" s="242" t="n"/>
+      <c r="F25" s="242" t="n"/>
+      <c r="G25" s="242" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="143">
+      <c r="B26" s="243" t="inlineStr">
         <is>
           <t>MARKET  (touch, shown separately from the statistic)</t>
         </is>
       </c>
-      <c r="C26" s="103" t="n"/>
-      <c r="D26" s="103" t="n"/>
-      <c r="E26" s="103" t="n"/>
-      <c r="F26" s="103" t="n"/>
-      <c r="G26" s="103" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="67">
-      <c r="B27" s="86" t="inlineStr">
+      <c r="C26" s="244" t="n"/>
+      <c r="D26" s="244" t="n"/>
+      <c r="E26" s="244" t="n"/>
+      <c r="F26" s="244" t="n"/>
+      <c r="G26" s="244" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="143">
+      <c r="B27" s="240" t="inlineStr">
         <is>
           <t>Spread bid</t>
         </is>
       </c>
-      <c r="C27" s="100" t="n"/>
-      <c r="D27" s="83" t="n"/>
-      <c r="E27" s="83" t="n"/>
-      <c r="F27" s="83" t="n"/>
-      <c r="G27" s="83" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="67">
-      <c r="B28" s="86" t="inlineStr">
+      <c r="C27" s="239" t="n"/>
+      <c r="D27" s="238" t="n"/>
+      <c r="E27" s="238" t="n"/>
+      <c r="F27" s="238" t="n"/>
+      <c r="G27" s="238" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="B28" s="240" t="inlineStr">
         <is>
           <t>Spread ask</t>
         </is>
       </c>
-      <c r="C28" s="100" t="n"/>
-      <c r="D28" s="83" t="n"/>
-      <c r="E28" s="83" t="n"/>
-      <c r="F28" s="83" t="n"/>
-      <c r="G28" s="83" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="67">
-      <c r="B29" s="86" t="inlineStr">
+      <c r="C28" s="239" t="n"/>
+      <c r="D28" s="238" t="n"/>
+      <c r="E28" s="238" t="n"/>
+      <c r="F28" s="238" t="n"/>
+      <c r="G28" s="238" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="143">
+      <c r="B29" s="240" t="inlineStr">
         <is>
           <t>Spread mid   &lt;- feeds the statistic</t>
         </is>
       </c>
-      <c r="C29" s="100" t="n"/>
-      <c r="D29" s="83" t="n"/>
-      <c r="E29" s="83" t="n"/>
-      <c r="F29" s="83" t="n"/>
-      <c r="G29" s="83" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="67">
-      <c r="B30" s="86" t="inlineStr">
+      <c r="C29" s="239" t="n"/>
+      <c r="D29" s="238" t="n"/>
+      <c r="E29" s="238" t="n"/>
+      <c r="F29" s="238" t="n"/>
+      <c r="G29" s="238" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="143">
+      <c r="B30" s="240" t="inlineStr">
         <is>
           <t>Bid-Ask Gap</t>
         </is>
       </c>
-      <c r="C30" s="100" t="inlineStr">
+      <c r="C30" s="239" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D30" s="83" t="n"/>
-      <c r="E30" s="83" t="n"/>
-      <c r="F30" s="83" t="n"/>
-      <c r="G30" s="83" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="67">
-      <c r="B31" s="102" t="inlineStr">
+      <c r="D30" s="238" t="n"/>
+      <c r="E30" s="238" t="n"/>
+      <c r="F30" s="238" t="n"/>
+      <c r="G30" s="238" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="143">
+      <c r="B31" s="243" t="inlineStr">
         <is>
           <t>WINDOW</t>
         </is>
       </c>
-      <c r="C31" s="103" t="n"/>
-      <c r="D31" s="103" t="n"/>
-      <c r="E31" s="103" t="n"/>
-      <c r="F31" s="103" t="n"/>
-      <c r="G31" s="103" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="67">
-      <c r="B32" s="86" t="inlineStr">
+      <c r="C31" s="244" t="n"/>
+      <c r="D31" s="244" t="n"/>
+      <c r="E31" s="244" t="n"/>
+      <c r="F31" s="244" t="n"/>
+      <c r="G31" s="244" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="143">
+      <c r="B32" s="240" t="inlineStr">
         <is>
           <t>Stored samples in window</t>
         </is>
       </c>
-      <c r="C32" s="100" t="inlineStr">
+      <c r="C32" s="239" t="inlineStr">
         <is>
           <t>after dedupe + store gate</t>
         </is>
       </c>
-      <c r="D32" s="101" t="n"/>
-      <c r="E32" s="101" t="n"/>
-      <c r="F32" s="101" t="n"/>
-      <c r="G32" s="101" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="67">
-      <c r="B33" s="86" t="inlineStr">
+      <c r="D32" s="242" t="n"/>
+      <c r="E32" s="242" t="n"/>
+      <c r="F32" s="242" t="n"/>
+      <c r="G32" s="242" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="143">
+      <c r="B33" s="240" t="inlineStr">
         <is>
           <t>Window elapsed</t>
         </is>
       </c>
-      <c r="C33" s="100" t="inlineStr">
+      <c r="C33" s="239" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D33" s="91" t="n"/>
-      <c r="E33" s="91" t="n"/>
-      <c r="F33" s="91" t="n"/>
-      <c r="G33" s="91" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="67">
-      <c r="B34" s="86" t="inlineStr">
+      <c r="D33" s="245" t="n"/>
+      <c r="E33" s="245" t="n"/>
+      <c r="F33" s="245" t="n"/>
+      <c r="G33" s="245" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="143">
+      <c r="B34" s="240" t="inlineStr">
         <is>
           <t>Warm-up gate</t>
         </is>
       </c>
-      <c r="C34" s="100" t="inlineStr">
+      <c r="C34" s="239" t="inlineStr">
         <is>
           <t>binding gate</t>
         </is>
       </c>
-      <c r="D34" s="90" t="n"/>
-      <c r="E34" s="90" t="n"/>
-      <c r="F34" s="90" t="n"/>
-      <c r="G34" s="90" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="67">
-      <c r="B35" s="86" t="inlineStr">
+      <c r="D34" s="241" t="n"/>
+      <c r="E34" s="241" t="n"/>
+      <c r="F34" s="241" t="n"/>
+      <c r="G34" s="241" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="143">
+      <c r="B35" s="240" t="inlineStr">
         <is>
           <t>Feed rate</t>
         </is>
       </c>
-      <c r="C35" s="100" t="inlineStr">
+      <c r="C35" s="239" t="inlineStr">
         <is>
           <t>quote CHANGES / min</t>
         </is>
       </c>
-      <c r="D35" s="104" t="n"/>
-      <c r="E35" s="104" t="n"/>
-      <c r="F35" s="104" t="n"/>
-      <c r="G35" s="104" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="67">
-      <c r="B36" s="86" t="inlineStr">
+      <c r="D35" s="246" t="n"/>
+      <c r="E35" s="246" t="n"/>
+      <c r="F35" s="246" t="n"/>
+      <c r="G35" s="246" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="143">
+      <c r="B36" s="240" t="inlineStr">
         <is>
           <t>Feed status</t>
         </is>
       </c>
-      <c r="C36" s="100" t="n"/>
-      <c r="D36" s="90" t="n"/>
-      <c r="E36" s="90" t="n"/>
-      <c r="F36" s="90" t="n"/>
-      <c r="G36" s="90" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="67">
-      <c r="B37" s="102" t="inlineStr">
+      <c r="C36" s="239" t="n"/>
+      <c r="D36" s="241" t="n"/>
+      <c r="E36" s="241" t="n"/>
+      <c r="F36" s="241" t="n"/>
+      <c r="G36" s="241" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="143">
+      <c r="B37" s="243" t="inlineStr">
         <is>
           <t>STATISTICS  (FROZEN - republished every STATS_REFRESH_MIN)</t>
         </is>
       </c>
-      <c r="C37" s="103" t="n"/>
-      <c r="D37" s="103" t="n"/>
-      <c r="E37" s="103" t="n"/>
-      <c r="F37" s="103" t="n"/>
-      <c r="G37" s="103" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="67">
-      <c r="B38" s="86" t="inlineStr">
+      <c r="C37" s="244" t="n"/>
+      <c r="D37" s="244" t="n"/>
+      <c r="E37" s="244" t="n"/>
+      <c r="F37" s="244" t="n"/>
+      <c r="G37" s="244" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="143">
+      <c r="B38" s="240" t="inlineStr">
         <is>
           <t>Mean (frozen)</t>
         </is>
       </c>
-      <c r="C38" s="100" t="n"/>
-      <c r="D38" s="83" t="n"/>
-      <c r="E38" s="83" t="n"/>
-      <c r="F38" s="83" t="n"/>
-      <c r="G38" s="83" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="67">
-      <c r="B39" s="86" t="inlineStr">
+      <c r="C38" s="239" t="n"/>
+      <c r="D38" s="238" t="n"/>
+      <c r="E38" s="238" t="n"/>
+      <c r="F38" s="238" t="n"/>
+      <c r="G38" s="238" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="143">
+      <c r="B39" s="240" t="inlineStr">
         <is>
           <t>Std Dev (frozen)</t>
         </is>
       </c>
-      <c r="C39" s="100" t="n"/>
-      <c r="D39" s="83" t="n"/>
-      <c r="E39" s="83" t="n"/>
-      <c r="F39" s="83" t="n"/>
-      <c r="G39" s="83" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="67">
-      <c r="B40" s="86" t="inlineStr">
+      <c r="C39" s="239" t="n"/>
+      <c r="D39" s="238" t="n"/>
+      <c r="E39" s="238" t="n"/>
+      <c r="F39" s="238" t="n"/>
+      <c r="G39" s="238" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="143">
+      <c r="B40" s="240" t="inlineStr">
         <is>
           <t>Std Dev in dollars</t>
         </is>
       </c>
-      <c r="C40" s="100" t="inlineStr">
+      <c r="C40" s="239" t="inlineStr">
         <is>
           <t>sigma x USD/pt x LOTS</t>
         </is>
       </c>
-      <c r="D40" s="105" t="n"/>
-      <c r="E40" s="105" t="n"/>
-      <c r="F40" s="105" t="n"/>
-      <c r="G40" s="105" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="67">
-      <c r="B41" s="86" t="inlineStr">
+      <c r="D40" s="247" t="n"/>
+      <c r="E40" s="247" t="n"/>
+      <c r="F40" s="247" t="n"/>
+      <c r="G40" s="247" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="143">
+      <c r="B41" s="240" t="inlineStr">
         <is>
           <t>Stats age / next refresh</t>
         </is>
       </c>
-      <c r="C41" s="100" t="inlineStr">
+      <c r="C41" s="239" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D41" s="90" t="n"/>
-      <c r="E41" s="90" t="n"/>
-      <c r="F41" s="90" t="n"/>
-      <c r="G41" s="90" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="67">
-      <c r="B42" s="84" t="inlineStr">
+      <c r="D41" s="241" t="n"/>
+      <c r="E41" s="241" t="n"/>
+      <c r="F41" s="241" t="n"/>
+      <c r="G41" s="241" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="143">
+      <c r="B42" s="248" t="inlineStr">
         <is>
           <t>Z  (live, vs frozen mean &amp; sigma)</t>
         </is>
       </c>
-      <c r="C42" s="100" t="n"/>
-      <c r="D42" s="85" t="n"/>
-      <c r="E42" s="85" t="n"/>
-      <c r="F42" s="85" t="n"/>
-      <c r="G42" s="85" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="67">
-      <c r="B43" s="84" t="inlineStr">
+      <c r="C42" s="239" t="n"/>
+      <c r="D42" s="249" t="n"/>
+      <c r="E42" s="249" t="n"/>
+      <c r="F42" s="249" t="n"/>
+      <c r="G42" s="249" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="143">
+      <c r="B43" s="248" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="C43" s="100" t="n"/>
-      <c r="D43" s="78" t="n"/>
-      <c r="E43" s="78" t="n"/>
-      <c r="F43" s="78" t="n"/>
-      <c r="G43" s="78" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="67">
-      <c r="B44" s="102" t="inlineStr">
+      <c r="C43" s="239" t="n"/>
+      <c r="D43" s="250" t="n"/>
+      <c r="E43" s="250" t="n"/>
+      <c r="F43" s="250" t="n"/>
+      <c r="G43" s="250" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="143">
+      <c r="B44" s="243" t="inlineStr">
         <is>
           <t>COST OF THE ROUND TRIP</t>
         </is>
       </c>
-      <c r="C44" s="103" t="n"/>
-      <c r="D44" s="103" t="n"/>
-      <c r="E44" s="103" t="n"/>
-      <c r="F44" s="103" t="n"/>
-      <c r="G44" s="103" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="67">
-      <c r="B45" s="86" t="inlineStr">
+      <c r="C44" s="244" t="n"/>
+      <c r="D44" s="244" t="n"/>
+      <c r="E44" s="244" t="n"/>
+      <c r="F44" s="244" t="n"/>
+      <c r="G44" s="244" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="143">
+      <c r="B45" s="240" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C45" s="100" t="n"/>
-      <c r="D45" s="90" t="n"/>
-      <c r="E45" s="90" t="n"/>
-      <c r="F45" s="90" t="n"/>
-      <c r="G45" s="90" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="67">
-      <c r="B46" s="86" t="inlineStr">
+      <c r="C45" s="239" t="n"/>
+      <c r="D45" s="241" t="n"/>
+      <c r="E45" s="241" t="n"/>
+      <c r="F45" s="241" t="n"/>
+      <c r="G45" s="241" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="143">
+      <c r="B46" s="240" t="inlineStr">
         <is>
           <t>Entry reference (touch)</t>
         </is>
       </c>
-      <c r="C46" s="100" t="n"/>
-      <c r="D46" s="83" t="n"/>
-      <c r="E46" s="83" t="n"/>
-      <c r="F46" s="83" t="n"/>
-      <c r="G46" s="83" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="67">
-      <c r="B47" s="86" t="inlineStr">
+      <c r="C46" s="239" t="n"/>
+      <c r="D46" s="238" t="n"/>
+      <c r="E46" s="238" t="n"/>
+      <c r="F46" s="238" t="n"/>
+      <c r="G46" s="238" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="143">
+      <c r="B47" s="240" t="inlineStr">
         <is>
           <t>Commission</t>
         </is>
       </c>
-      <c r="C47" s="100" t="inlineStr">
+      <c r="C47" s="239" t="inlineStr">
         <is>
           <t>contracts x rate x LOTS</t>
         </is>
       </c>
-      <c r="D47" s="105" t="n"/>
-      <c r="E47" s="105" t="n"/>
-      <c r="F47" s="105" t="n"/>
-      <c r="G47" s="105" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="67">
-      <c r="B48" s="86" t="inlineStr">
+      <c r="D47" s="247" t="n"/>
+      <c r="E47" s="247" t="n"/>
+      <c r="F47" s="247" t="n"/>
+      <c r="G47" s="247" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="143">
+      <c r="B48" s="240" t="inlineStr">
         <is>
           <t>Crossing cost - LEGGING</t>
         </is>
       </c>
-      <c r="C48" s="100" t="n"/>
-      <c r="D48" s="105" t="n"/>
-      <c r="E48" s="105" t="n"/>
-      <c r="F48" s="105" t="n"/>
-      <c r="G48" s="105" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="67">
-      <c r="B49" s="86" t="inlineStr">
+      <c r="C48" s="239" t="n"/>
+      <c r="D48" s="247" t="n"/>
+      <c r="E48" s="247" t="n"/>
+      <c r="F48" s="247" t="n"/>
+      <c r="G48" s="247" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="143">
+      <c r="B49" s="240" t="inlineStr">
         <is>
           <t>Crossing cost - LISTED</t>
         </is>
       </c>
-      <c r="C49" s="100" t="n"/>
-      <c r="D49" s="105" t="n"/>
-      <c r="E49" s="105" t="n"/>
-      <c r="F49" s="105" t="n"/>
-      <c r="G49" s="105" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="67">
-      <c r="B50" s="84" t="inlineStr">
+      <c r="C49" s="239" t="n"/>
+      <c r="D49" s="247" t="n"/>
+      <c r="E49" s="247" t="n"/>
+      <c r="F49" s="247" t="n"/>
+      <c r="G49" s="247" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="143">
+      <c r="B50" s="248" t="inlineStr">
         <is>
           <t>TOTAL COST (this mode)</t>
         </is>
       </c>
-      <c r="C50" s="100" t="n"/>
-      <c r="D50" s="106" t="n"/>
-      <c r="E50" s="106" t="n"/>
-      <c r="F50" s="106" t="n"/>
-      <c r="G50" s="106" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="67">
-      <c r="B51" s="102" t="inlineStr">
+      <c r="C50" s="239" t="n"/>
+      <c r="D50" s="251" t="n"/>
+      <c r="E50" s="251" t="n"/>
+      <c r="F50" s="251" t="n"/>
+      <c r="G50" s="251" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="143">
+      <c r="B51" s="243" t="inlineStr">
         <is>
           <t>TAKE PROFIT  (exits act on MONEY, never on z)</t>
         </is>
       </c>
-      <c r="C51" s="103" t="n"/>
-      <c r="D51" s="103" t="n"/>
-      <c r="E51" s="103" t="n"/>
-      <c r="F51" s="103" t="n"/>
-      <c r="G51" s="103" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="67">
-      <c r="B52" s="86" t="inlineStr">
+      <c r="C51" s="244" t="n"/>
+      <c r="D51" s="244" t="n"/>
+      <c r="E51" s="244" t="n"/>
+      <c r="F51" s="244" t="n"/>
+      <c r="G51" s="244" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="143">
+      <c r="B52" s="240" t="inlineStr">
         <is>
           <t>TP rule in force</t>
         </is>
       </c>
-      <c r="C52" s="100" t="n"/>
-      <c r="D52" s="90" t="n"/>
-      <c r="E52" s="90" t="n"/>
-      <c r="F52" s="90" t="n"/>
-      <c r="G52" s="90" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="67">
-      <c r="B53" s="86" t="inlineStr">
+      <c r="C52" s="239" t="n"/>
+      <c r="D52" s="241" t="n"/>
+      <c r="E52" s="241" t="n"/>
+      <c r="F52" s="241" t="n"/>
+      <c r="G52" s="241" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="143">
+      <c r="B53" s="240" t="inlineStr">
         <is>
           <t>Notional (per NOTIONAL_BASIS)</t>
         </is>
       </c>
-      <c r="C53" s="100" t="n"/>
-      <c r="D53" s="105" t="n"/>
-      <c r="E53" s="105" t="n"/>
-      <c r="F53" s="105" t="n"/>
-      <c r="G53" s="105" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="67">
-      <c r="B54" s="86" t="inlineStr">
+      <c r="C53" s="239" t="n"/>
+      <c r="D53" s="247" t="n"/>
+      <c r="E53" s="247" t="n"/>
+      <c r="F53" s="247" t="n"/>
+      <c r="G53" s="247" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="143">
+      <c r="B54" s="240" t="inlineStr">
         <is>
           <t>Win target (WIN_PCT x notional)</t>
         </is>
       </c>
-      <c r="C54" s="100" t="n"/>
-      <c r="D54" s="105" t="n"/>
-      <c r="E54" s="105" t="n"/>
-      <c r="F54" s="105" t="n"/>
-      <c r="G54" s="105" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="67">
-      <c r="B55" s="86" t="inlineStr">
+      <c r="C54" s="239" t="n"/>
+      <c r="D54" s="247" t="n"/>
+      <c r="E54" s="247" t="n"/>
+      <c r="F54" s="247" t="n"/>
+      <c r="G54" s="247" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="143">
+      <c r="B55" s="240" t="inlineStr">
         <is>
           <t>Costs in spread units</t>
         </is>
       </c>
-      <c r="C55" s="100" t="n"/>
-      <c r="D55" s="83" t="n"/>
-      <c r="E55" s="83" t="n"/>
-      <c r="F55" s="83" t="n"/>
-      <c r="G55" s="83" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="67">
-      <c r="B56" s="86" t="inlineStr">
+      <c r="C55" s="239" t="n"/>
+      <c r="D55" s="238" t="n"/>
+      <c r="E55" s="238" t="n"/>
+      <c r="F55" s="238" t="n"/>
+      <c r="G55" s="238" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="143">
+      <c r="B56" s="240" t="inlineStr">
         <is>
           <t>Win in spread units</t>
         </is>
       </c>
-      <c r="C56" s="100" t="n"/>
-      <c r="D56" s="83" t="n"/>
-      <c r="E56" s="83" t="n"/>
-      <c r="F56" s="83" t="n"/>
-      <c r="G56" s="83" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="67">
-      <c r="B57" s="86" t="inlineStr">
+      <c r="C56" s="239" t="n"/>
+      <c r="D56" s="238" t="n"/>
+      <c r="E56" s="238" t="n"/>
+      <c r="F56" s="238" t="n"/>
+      <c r="G56" s="238" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="143">
+      <c r="B57" s="240" t="inlineStr">
         <is>
           <t>Break-even spread</t>
         </is>
       </c>
-      <c r="C57" s="100" t="inlineStr">
+      <c r="C57" s="239" t="inlineStr">
         <is>
           <t>absolute level</t>
         </is>
       </c>
-      <c r="D57" s="83" t="n"/>
-      <c r="E57" s="83" t="n"/>
-      <c r="F57" s="83" t="n"/>
-      <c r="G57" s="83" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="67">
-      <c r="B58" s="84" t="inlineStr">
+      <c r="D57" s="238" t="n"/>
+      <c r="E57" s="238" t="n"/>
+      <c r="F57" s="238" t="n"/>
+      <c r="G57" s="238" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="143">
+      <c r="B58" s="248" t="inlineStr">
         <is>
           <t>TAKE-PROFIT spread</t>
         </is>
       </c>
-      <c r="C58" s="100" t="inlineStr">
+      <c r="C58" s="239" t="inlineStr">
         <is>
           <t>absolute level</t>
         </is>
       </c>
-      <c r="D58" s="89" t="n"/>
-      <c r="E58" s="89" t="n"/>
-      <c r="F58" s="89" t="n"/>
-      <c r="G58" s="89" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="67">
-      <c r="B59" s="86" t="inlineStr">
+      <c r="D58" s="252" t="n"/>
+      <c r="E58" s="252" t="n"/>
+      <c r="F58" s="252" t="n"/>
+      <c r="G58" s="252" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="143">
+      <c r="B59" s="240" t="inlineStr">
         <is>
           <t>TP distance</t>
         </is>
       </c>
-      <c r="C59" s="100" t="inlineStr">
+      <c r="C59" s="239" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D59" s="83" t="n"/>
-      <c r="E59" s="83" t="n"/>
-      <c r="F59" s="83" t="n"/>
-      <c r="G59" s="83" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="67">
-      <c r="B60" s="86" t="inlineStr">
+      <c r="D59" s="238" t="n"/>
+      <c r="E59" s="238" t="n"/>
+      <c r="F59" s="238" t="n"/>
+      <c r="G59" s="238" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="143">
+      <c r="B60" s="240" t="inlineStr">
         <is>
           <t>TP in sigma</t>
         </is>
       </c>
-      <c r="C60" s="100" t="inlineStr">
+      <c r="C60" s="239" t="inlineStr">
         <is>
           <t>x sigma</t>
         </is>
       </c>
-      <c r="D60" s="91" t="n"/>
-      <c r="E60" s="91" t="n"/>
-      <c r="F60" s="91" t="n"/>
-      <c r="G60" s="91" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="67">
-      <c r="B61" s="86" t="inlineStr">
+      <c r="D60" s="245" t="n"/>
+      <c r="E60" s="245" t="n"/>
+      <c r="F60" s="245" t="n"/>
+      <c r="G60" s="245" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="143">
+      <c r="B61" s="240" t="inlineStr">
         <is>
           <t>Target z</t>
         </is>
       </c>
-      <c r="C61" s="100" t="inlineStr">
+      <c r="C61" s="239" t="inlineStr">
         <is>
           <t>z at the TP level</t>
         </is>
       </c>
-      <c r="D61" s="91" t="n"/>
-      <c r="E61" s="91" t="n"/>
-      <c r="F61" s="91" t="n"/>
-      <c r="G61" s="91" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="67">
-      <c r="B62" s="86" t="inlineStr">
+      <c r="D61" s="245" t="n"/>
+      <c r="E61" s="245" t="n"/>
+      <c r="F61" s="245" t="n"/>
+      <c r="G61" s="245" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="143">
+      <c r="B62" s="240" t="inlineStr">
         <is>
           <t>TP beyond the mean?</t>
         </is>
       </c>
-      <c r="C62" s="100" t="n"/>
-      <c r="D62" s="90" t="n"/>
-      <c r="E62" s="90" t="n"/>
-      <c r="F62" s="90" t="n"/>
-      <c r="G62" s="90" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="67">
-      <c r="B63" s="102" t="inlineStr">
+      <c r="C62" s="239" t="n"/>
+      <c r="D62" s="241" t="n"/>
+      <c r="E62" s="241" t="n"/>
+      <c r="F62" s="241" t="n"/>
+      <c r="G62" s="241" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="143">
+      <c r="B63" s="243" t="inlineStr">
         <is>
           <t>EDGE FILTER  (a separate gate from ENTRY_Z)</t>
         </is>
       </c>
-      <c r="C63" s="103" t="n"/>
-      <c r="D63" s="103" t="n"/>
-      <c r="E63" s="103" t="n"/>
-      <c r="F63" s="103" t="n"/>
-      <c r="G63" s="103" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="67">
-      <c r="B64" s="86" t="inlineStr">
+      <c r="C63" s="244" t="n"/>
+      <c r="D63" s="244" t="n"/>
+      <c r="E63" s="244" t="n"/>
+      <c r="F63" s="244" t="n"/>
+      <c r="G63" s="244" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="143">
+      <c r="B64" s="240" t="inlineStr">
         <is>
           <t>Expected capture</t>
         </is>
       </c>
-      <c r="C64" s="100" t="inlineStr">
+      <c r="C64" s="239" t="inlineStr">
         <is>
           <t>0.5 x |z| x sigma x USD/pt x LOTS</t>
         </is>
       </c>
-      <c r="D64" s="105" t="n"/>
-      <c r="E64" s="105" t="n"/>
-      <c r="F64" s="105" t="n"/>
-      <c r="G64" s="105" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="67">
-      <c r="B65" s="86" t="inlineStr">
+      <c r="D64" s="247" t="n"/>
+      <c r="E64" s="247" t="n"/>
+      <c r="F64" s="247" t="n"/>
+      <c r="G64" s="247" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="143">
+      <c r="B65" s="240" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C65" s="100" t="inlineStr">
+      <c r="C65" s="239" t="inlineStr">
         <is>
           <t>EDGE_MULTIPLE x total cost</t>
         </is>
       </c>
-      <c r="D65" s="105" t="n"/>
-      <c r="E65" s="105" t="n"/>
-      <c r="F65" s="105" t="n"/>
-      <c r="G65" s="105" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="67">
-      <c r="B66" s="84" t="inlineStr">
+      <c r="D65" s="247" t="n"/>
+      <c r="E65" s="247" t="n"/>
+      <c r="F65" s="247" t="n"/>
+      <c r="G65" s="247" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="143">
+      <c r="B66" s="248" t="inlineStr">
         <is>
           <t>EDGE VERDICT</t>
         </is>
       </c>
-      <c r="C66" s="100" t="n"/>
-      <c r="D66" s="78" t="n"/>
-      <c r="E66" s="78" t="n"/>
-      <c r="F66" s="78" t="n"/>
-      <c r="G66" s="78" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="67">
-      <c r="B67" s="86" t="inlineStr">
+      <c r="C66" s="239" t="n"/>
+      <c r="D66" s="250" t="n"/>
+      <c r="E66" s="250" t="n"/>
+      <c r="F66" s="250" t="n"/>
+      <c r="G66" s="250" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="143">
+      <c r="B67" s="240" t="inlineStr">
         <is>
           <t>Min sigma to pass at live z</t>
         </is>
       </c>
-      <c r="C67" s="100" t="inlineStr">
+      <c r="C67" s="239" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D67" s="83" t="n"/>
-      <c r="E67" s="83" t="n"/>
-      <c r="F67" s="83" t="n"/>
-      <c r="G67" s="83" t="n"/>
+      <c r="D67" s="238" t="n"/>
+      <c r="E67" s="238" t="n"/>
+      <c r="F67" s="238" t="n"/>
+      <c r="G67" s="238" t="n"/>
     </row>
     <row r="68"/>
-    <row r="69" ht="15" customHeight="1" s="67">
-      <c r="B69" s="107" t="inlineStr">
+    <row r="69" ht="15" customHeight="1" s="143">
+      <c r="B69" s="253" t="inlineStr">
         <is>
           <t>The EDGE FILTER is a different gate from ENTRY_Z. ENTRY_Z decides when the chime fires; the edge filter asks whether the expected capture clears the round trip by EDGE_MULTIPLE. A highlighted z that fails the edge filter is still not a trade worth taking.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="67">
-      <c r="B70" s="71" t="inlineStr">
+    <row r="70" ht="15" customHeight="1" s="143">
+      <c r="B70" s="231" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES on Config decides whether a failing edge filter also silences the chime. It ships FALSE, so the chime follows ENTRY_Z alone.</t>
         </is>
@@ -2870,45 +3806,45 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D42:G43">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="4" text="" percent="0" bottom="0">
       <formula>OR(D$43="NO USABLE Z",D$43="STALE FEED")</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="5" text="" percent="0" bottom="0">
       <formula>D$43="WARMING UP"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>D$43="ABOVE CEILING"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
       <formula>D$43="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D66:G66">
-    <cfRule type="expression" rank="0" priority="6" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="6" equalAverage="0" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
       <formula>D66="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="7" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="7" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>D66="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D36:G36">
-    <cfRule type="expression" rank="0" priority="8" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="8" equalAverage="0" aboveAverage="0" dxfId="4" text="" percent="0" bottom="0">
       <formula>D36="STALE"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="9" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="9" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>D36="THIN"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="10" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="10" equalAverage="0" aboveAverage="0" dxfId="7" text="" percent="0" bottom="0">
       <formula>D36="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D34:G34">
-    <cfRule type="expression" rank="0" priority="11" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="11" equalAverage="0" aboveAverage="0" dxfId="5" text="" percent="0" bottom="0">
       <formula>D34&lt;&gt;"ready"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D62:G62">
-    <cfRule type="expression" rank="0" priority="12" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" rank="0" priority="12" equalAverage="0" aboveAverage="0" dxfId="6" text="" percent="0" bottom="0">
       <formula>LEFT(D62,3)="YES"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2924,1678 +3860,1705 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="66" min="1" max="1"/>
-    <col width="34" customWidth="1" style="66" min="2" max="2"/>
-    <col width="14" customWidth="1" style="66" min="3" max="3"/>
-    <col width="10" customWidth="1" style="66" min="4" max="4"/>
-    <col width="96" customWidth="1" style="66" min="5" max="5"/>
-    <col width="30" customWidth="1" style="66" min="6" max="6"/>
-    <col width="12" customWidth="1" style="66" min="7" max="8"/>
-    <col width="10" customWidth="1" style="66" min="9" max="9"/>
-    <col width="8" customWidth="1" style="66" min="10" max="10"/>
-    <col width="34" customWidth="1" style="66" min="11" max="11"/>
+    <col width="30" customWidth="1" style="141" min="1" max="1"/>
+    <col width="34" customWidth="1" style="141" min="2" max="2"/>
+    <col width="14" customWidth="1" style="141" min="3" max="3"/>
+    <col width="10" customWidth="1" style="141" min="4" max="4"/>
+    <col width="96" customWidth="1" style="141" min="5" max="5"/>
+    <col width="30" customWidth="1" style="141" min="6" max="6"/>
+    <col width="12" customWidth="1" style="141" min="7" max="8"/>
+    <col width="10" customWidth="1" style="141" min="9" max="9"/>
+    <col width="8" customWidth="1" style="141" min="10" max="10"/>
+    <col width="34" customWidth="1" style="141" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.7" customHeight="1" s="67">
-      <c r="A1" s="68" t="inlineStr">
+    <row r="1" ht="19.7" customHeight="1" s="143">
+      <c r="A1" s="254" t="inlineStr">
         <is>
           <t>CONFIG  -  every parameter in its own labelled cell</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="67">
-      <c r="A2" s="108" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="A2" s="255" t="inlineStr">
         <is>
           <t>LEGEND:  yellow / blue = EDIT THESE.  black = formula, do not edit.  A changed value takes effect on the NEXT TIMER TICK - no restart, no VBA edit.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="67">
-      <c r="A3" s="71" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="143">
+      <c r="A3" s="231" t="inlineStr">
         <is>
           <t>Exception: LOOKBACK_MIN redefines the window, so stored history is re-evaluated against the new width on the next stats refresh and the warm-up gates re-apply.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="67">
-      <c r="A4" s="71" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="143">
+      <c r="A4" s="231" t="inlineStr">
         <is>
           <t>VBA finds a parameter by matching column A exactly, so you may insert or reorder rows freely - but never rename a parameter in column A.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="67">
-      <c r="A5" s="108" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="A5" s="255" t="inlineStr">
         <is>
           <t>FOUR DECOUPLED RATES:  CAPTURE_MS (poll for a changed quote)  &gt;  STORE_MIN_INTERVAL_MS (what reaches the window)  &gt;  PRICE_REFRESH_MS (what repaints)  &gt;  STATS_REFRESH_MIN (when mean and sigma are republished).  Capturing fast buys alert latency, not a better sigma.</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="7" ht="15" customHeight="1" s="67">
-      <c r="A7" s="109" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="143">
+      <c r="A7" s="256" t="inlineStr">
         <is>
           <t>ENGINE  /  SAMPLING</t>
         </is>
       </c>
-      <c r="B7" s="109" t="n"/>
-      <c r="C7" s="109" t="n"/>
-      <c r="D7" s="109" t="n"/>
-      <c r="E7" s="109" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="67">
-      <c r="A8" s="110" t="inlineStr">
+      <c r="B7" s="256" t="n"/>
+      <c r="C7" s="256" t="n"/>
+      <c r="D7" s="256" t="n"/>
+      <c r="E7" s="256" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="143">
+      <c r="A8" s="257" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B8" s="110" t="inlineStr">
+      <c r="B8" s="257" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C8" s="110" t="inlineStr">
+      <c r="C8" s="257" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D8" s="110" t="inlineStr">
+      <c r="D8" s="257" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E8" s="110" t="inlineStr">
+      <c r="E8" s="257" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="67">
-      <c r="A9" s="84" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="A9" s="248" t="inlineStr">
         <is>
           <t>CAPTURE_MS</t>
         </is>
       </c>
-      <c r="B9" s="77" t="n">
+      <c r="B9" s="258" t="n">
         <v>100</v>
       </c>
-      <c r="C9" s="99" t="n">
+      <c r="C9" s="237" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="99" t="inlineStr">
+      <c r="D9" s="237" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E9" s="111" t="inlineStr">
+      <c r="E9" s="259" t="inlineStr">
         <is>
           <t>RATE 1 of 4. How often the feed is POLLED for a changed quote. Drives latency to the chime, NOT sigma - after dedupe the window holds quote changes, not poll ticks. Sub-second needs the user32 timer; at 1000+ the module falls back to Application.OnTime.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="67">
-      <c r="A10" s="84" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="143">
+      <c r="A10" s="248" t="inlineStr">
         <is>
           <t>STORE_MIN_INTERVAL_MS</t>
         </is>
       </c>
-      <c r="B10" s="77" t="n">
+      <c r="B10" s="258" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="99" t="n">
+      <c r="C10" s="237" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="99" t="inlineStr">
+      <c r="D10" s="237" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E10" s="111" t="inlineStr">
+      <c r="E10" s="259" t="inlineStr">
         <is>
           <t>RATE 2 of 4. Minimum spacing between STORED samples. 0 = full fidelity. Leave it at 0 for the first week or two to characterise the microstructure, then set 250-1000: subsampling a mean-reverting level series is unbiased, so it is 3-10x less memory for the same mean and sigma.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="67">
-      <c r="A11" s="84" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="143">
+      <c r="A11" s="248" t="inlineStr">
         <is>
           <t>PRICE_REFRESH_MS</t>
         </is>
       </c>
-      <c r="B11" s="77" t="n">
+      <c r="B11" s="258" t="n">
         <v>500</v>
       </c>
-      <c r="C11" s="99" t="n">
+      <c r="C11" s="237" t="n">
         <v>500</v>
       </c>
-      <c r="D11" s="99" t="inlineStr">
+      <c r="D11" s="237" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E11" s="111" t="inlineStr">
+      <c r="E11" s="259" t="inlineStr">
         <is>
           <t>RATE 3 of 4. How often the display may repaint. Independent of capture and of storage - a number showing more digits than the market moves in will appear to change constantly.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="67">
-      <c r="A12" s="84" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="143">
+      <c r="A12" s="248" t="inlineStr">
         <is>
           <t>CONFIG_REFRESH_MS</t>
         </is>
       </c>
-      <c r="B12" s="77" t="n">
+      <c r="B12" s="258" t="n">
         <v>1000</v>
       </c>
-      <c r="C12" s="99" t="n">
+      <c r="C12" s="237" t="n">
         <v>1000</v>
       </c>
-      <c r="D12" s="99" t="inlineStr">
+      <c r="D12" s="237" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E12" s="111" t="inlineStr">
+      <c r="E12" s="259" t="inlineStr">
         <is>
           <t>How often this sheet is re-read. A value changed here takes effect within this long - no restart, no VBA edit.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="67">
-      <c r="A13" s="84" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="143">
+      <c r="A13" s="248" t="inlineStr">
         <is>
           <t>RTD_THROTTLE_MS</t>
         </is>
       </c>
-      <c r="B13" s="77" t="n">
+      <c r="B13" s="258" t="n">
         <v>100</v>
       </c>
-      <c r="C13" s="99" t="n">
+      <c r="C13" s="237" t="n">
         <v>100</v>
       </c>
-      <c r="D13" s="99" t="inlineStr">
+      <c r="D13" s="237" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E13" s="111" t="inlineStr">
+      <c r="E13" s="259" t="inlineStr">
         <is>
           <t>Application.RTD.ThrottleInterval set on start. Match it to CAPTURE_MS. Excel's default is 2000.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="67">
-      <c r="A14" s="84" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="143">
+      <c r="A14" s="248" t="inlineStr">
         <is>
           <t>WATCHDOG_SEC</t>
         </is>
       </c>
-      <c r="B14" s="77" t="n">
+      <c r="B14" s="258" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="99" t="n">
+      <c r="C14" s="237" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="99" t="inlineStr">
+      <c r="D14" s="237" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E14" s="111" t="inlineStr">
+      <c r="E14" s="259" t="inlineStr">
         <is>
           <t>Application.OnTime watchdog. Re-arms the high-resolution timer if Excel killed it (a modal dialog will) and picks up a changed CAPTURE_MS.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="67">
-      <c r="A15" s="84" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="143">
+      <c r="A15" s="248" t="inlineStr">
         <is>
           <t>STALE_SEC</t>
         </is>
       </c>
-      <c r="B15" s="77" t="n">
+      <c r="B15" s="258" t="n">
         <v>15</v>
       </c>
-      <c r="C15" s="99" t="n">
+      <c r="C15" s="237" t="n">
         <v>15</v>
       </c>
-      <c r="D15" s="99" t="inlineStr">
+      <c r="D15" s="237" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E15" s="111" t="inlineStr">
+      <c r="E15" s="259" t="inlineStr">
         <is>
           <t>No new quote id for this long =&gt; feed marked STALE and alerts go silent.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="67">
-      <c r="A16" s="84" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="143">
+      <c r="A16" s="248" t="inlineStr">
         <is>
           <t>FLUSH_SEC</t>
         </is>
       </c>
-      <c r="B16" s="77" t="n">
+      <c r="B16" s="258" t="n">
         <v>60</v>
       </c>
-      <c r="C16" s="99" t="n">
+      <c r="C16" s="237" t="n">
         <v>60</v>
       </c>
-      <c r="D16" s="99" t="inlineStr">
+      <c r="D16" s="237" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E16" s="111" t="inlineStr">
+      <c r="E16" s="259" t="inlineStr">
         <is>
           <t>How often the recovery snapshot is written to the hidden Buffer sheet.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="67">
-      <c r="A17" s="84" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="143">
+      <c r="A17" s="248" t="inlineStr">
         <is>
           <t>FLUSH_DECIMATE_MS</t>
         </is>
       </c>
-      <c r="B17" s="77" t="n">
+      <c r="B17" s="258" t="n">
         <v>1000</v>
       </c>
-      <c r="C17" s="99" t="n">
+      <c r="C17" s="237" t="n">
         <v>1000</v>
       </c>
-      <c r="D17" s="99" t="inlineStr">
+      <c r="D17" s="237" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E17" s="111" t="inlineStr">
+      <c r="E17" s="259" t="inlineStr">
         <is>
           <t>The recovery snapshot is decimated to this spacing. Unbiased for mean and sigma, and it keeps a 120-minute window near 7,200 rows instead of tens of thousands.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="67">
-      <c r="A18" s="84" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="143">
+      <c r="A18" s="248" t="inlineStr">
         <is>
           <t>BUFFER_CAPACITY</t>
         </is>
       </c>
-      <c r="B18" s="77" t="n">
+      <c r="B18" s="258" t="n">
         <v>80000</v>
       </c>
-      <c r="C18" s="99" t="n">
+      <c r="C18" s="237" t="n">
         <v>80000</v>
       </c>
-      <c r="D18" s="99" t="inlineStr">
+      <c r="D18" s="237" t="inlineStr">
         <is>
           <t>samples</t>
         </is>
       </c>
-      <c r="E18" s="111" t="inlineStr">
+      <c r="E18" s="259" t="inlineStr">
         <is>
           <t>Circular-buffer capacity per spread. 4 spreads x 80,000 x 16 bytes is about 5 MB of VBA array, held in memory, not in cells.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="67">
-      <c r="A19" s="84" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="143">
+      <c r="A19" s="248" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_ENABLED</t>
         </is>
       </c>
-      <c r="B19" s="77" t="b">
+      <c r="B19" s="258" t="b">
         <v>1</v>
       </c>
-      <c r="C19" s="99" t="b">
+      <c r="C19" s="237" t="b">
         <v>1</v>
       </c>
-      <c r="D19" s="99" t="inlineStr">
+      <c r="D19" s="237" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E19" s="111" t="inlineStr">
+      <c r="E19" s="259" t="inlineStr">
         <is>
           <t>Write every CHANGED quote to a CSV on disk. This is the one chance to characterise the spread's microstructure and to verify that coarser storage loses nothing real. Turn it off once STORE_MIN_INTERVAL_MS is set.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="67">
-      <c r="A20" s="84" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="143">
+      <c r="A20" s="248" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_PATH</t>
         </is>
       </c>
-      <c r="B20" s="112" t="n"/>
-      <c r="C20" s="99" t="n"/>
-      <c r="D20" s="99" t="inlineStr">
+      <c r="B20" s="260" t="n"/>
+      <c r="C20" s="237" t="n"/>
+      <c r="D20" s="237" t="inlineStr">
         <is>
           <t>folder</t>
         </is>
       </c>
-      <c r="E20" s="111" t="inlineStr">
+      <c r="E20" s="259" t="inlineStr">
         <is>
           <t>Folder for the tick CSVs. Blank = a 'ticks' folder beside the workbook. One file per spread per day.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="67">
-      <c r="A21" s="84" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="143">
+      <c r="A21" s="248" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_BATCH</t>
         </is>
       </c>
-      <c r="B21" s="77" t="n">
+      <c r="B21" s="258" t="n">
         <v>500</v>
       </c>
-      <c r="C21" s="99" t="n">
+      <c r="C21" s="237" t="n">
         <v>500</v>
       </c>
-      <c r="D21" s="99" t="inlineStr">
+      <c r="D21" s="237" t="inlineStr">
         <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="E21" s="111" t="inlineStr">
+      <c r="E21" s="259" t="inlineStr">
         <is>
           <t>Lines buffered in memory before a file write, so archiving never stalls the capture timer.</t>
         </is>
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="15" customHeight="1" s="67">
-      <c r="A23" s="109" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="143">
+      <c r="A23" s="256" t="inlineStr">
         <is>
           <t>WINDOW  /  STATISTICS</t>
         </is>
       </c>
-      <c r="B23" s="109" t="n"/>
-      <c r="C23" s="109" t="n"/>
-      <c r="D23" s="109" t="n"/>
-      <c r="E23" s="109" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="67">
-      <c r="A24" s="110" t="inlineStr">
+      <c r="B23" s="256" t="n"/>
+      <c r="C23" s="256" t="n"/>
+      <c r="D23" s="256" t="n"/>
+      <c r="E23" s="256" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="143">
+      <c r="A24" s="257" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B24" s="110" t="inlineStr">
+      <c r="B24" s="257" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C24" s="110" t="inlineStr">
+      <c r="C24" s="257" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D24" s="110" t="inlineStr">
+      <c r="D24" s="257" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E24" s="110" t="inlineStr">
+      <c r="E24" s="257" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="67">
-      <c r="A25" s="84" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="A25" s="248" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="B25" s="77" t="n">
+      <c r="B25" s="258" t="n">
         <v>120</v>
       </c>
-      <c r="C25" s="99" t="n">
+      <c r="C25" s="237" t="n">
         <v>120</v>
       </c>
-      <c r="D25" s="99" t="inlineStr">
+      <c r="D25" s="237" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E25" s="111" t="inlineStr">
+      <c r="E25" s="259" t="inlineStr">
         <is>
           <t>Rolling window width (90 or 120). Changing it re-evaluates stored history on the next stats refresh and re-applies the warm-up gates.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="67">
-      <c r="A26" s="84" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="143">
+      <c r="A26" s="248" t="inlineStr">
         <is>
           <t>STATS_REFRESH_MIN</t>
         </is>
       </c>
-      <c r="B26" s="77" t="n">
+      <c r="B26" s="258" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="99" t="n">
+      <c r="C26" s="237" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="99" t="inlineStr">
+      <c r="D26" s="237" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E26" s="111" t="inlineStr">
+      <c r="E26" s="259" t="inlineStr">
         <is>
           <t>How often mean/sigma are recomputed and re-published. Held FROZEN in between; live z is measured against the frozen values.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="67">
-      <c r="A27" s="84" t="inlineStr">
+    <row r="27" ht="15" customHeight="1" s="143">
+      <c r="A27" s="248" t="inlineStr">
         <is>
           <t>MIN_SAMPLES</t>
         </is>
       </c>
-      <c r="B27" s="77" t="n">
+      <c r="B27" s="258" t="n">
         <v>300</v>
       </c>
-      <c r="C27" s="99" t="n">
+      <c r="C27" s="237" t="n">
         <v>300</v>
       </c>
-      <c r="D27" s="99" t="inlineStr">
+      <c r="D27" s="237" t="inlineStr">
         <is>
           <t>quotes</t>
         </is>
       </c>
-      <c r="E27" s="111" t="inlineStr">
+      <c r="E27" s="259" t="inlineStr">
         <is>
           <t>Warm-up gate 1. Quotes needed before any z is shown.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="67">
-      <c r="A28" s="84" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="A28" s="248" t="inlineStr">
         <is>
           <t>MIN_HISTORY_MIN</t>
         </is>
       </c>
-      <c r="B28" s="77" t="n">
+      <c r="B28" s="258" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="99" t="n">
+      <c r="C28" s="237" t="n">
         <v>120</v>
       </c>
-      <c r="D28" s="99" t="inlineStr">
+      <c r="D28" s="237" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E28" s="111" t="inlineStr">
+      <c r="E28" s="259" t="inlineStr">
         <is>
           <t>Warm-up gate 2. Elapsed collection needed before any z is shown. BOTH gates must pass.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="67">
-      <c r="A29" s="84" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="143">
+      <c r="A29" s="248" t="inlineStr">
         <is>
           <t>MIN_SIGMA</t>
         </is>
       </c>
-      <c r="B29" s="77" t="n">
+      <c r="B29" s="258" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="99" t="n">
+      <c r="C29" s="237" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="99" t="inlineStr">
+      <c r="D29" s="237" t="inlineStr">
         <is>
           <t>spread</t>
         </is>
       </c>
-      <c r="E29" s="111" t="inlineStr">
+      <c r="E29" s="259" t="inlineStr">
         <is>
           <t>Sigma floor. Below this the window is degenerate and NO z is shown. Set once sigma has actually been measured.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="67">
-      <c r="A30" s="84" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="143">
+      <c r="A30" s="248" t="inlineStr">
         <is>
           <t>MAX_ABS_Z</t>
         </is>
       </c>
-      <c r="B30" s="77" t="n">
+      <c r="B30" s="258" t="n">
         <v>25</v>
       </c>
-      <c r="C30" s="99" t="n">
+      <c r="C30" s="237" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="99" t="inlineStr">
+      <c r="D30" s="237" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E30" s="111" t="inlineStr">
+      <c r="E30" s="259" t="inlineStr">
         <is>
           <t>Absurd-z guard. Above this, show 'no usable z' rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="31"/>
-    <row r="32" ht="15" customHeight="1" s="67">
-      <c r="A32" s="109" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="143">
+      <c r="A32" s="256" t="inlineStr">
         <is>
           <t>SIGNAL THRESHOLDS</t>
         </is>
       </c>
-      <c r="B32" s="109" t="n"/>
-      <c r="C32" s="109" t="n"/>
-      <c r="D32" s="109" t="n"/>
-      <c r="E32" s="109" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="67">
-      <c r="A33" s="110" t="inlineStr">
+      <c r="B32" s="256" t="n"/>
+      <c r="C32" s="256" t="n"/>
+      <c r="D32" s="256" t="n"/>
+      <c r="E32" s="256" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="143">
+      <c r="A33" s="257" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B33" s="110" t="inlineStr">
+      <c r="B33" s="257" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C33" s="110" t="inlineStr">
+      <c r="C33" s="257" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D33" s="110" t="inlineStr">
+      <c r="D33" s="257" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E33" s="110" t="inlineStr">
+      <c r="E33" s="257" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="67">
-      <c r="A34" s="84" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="143">
+      <c r="A34" s="248" t="inlineStr">
         <is>
           <t>ENTRY_Z</t>
         </is>
       </c>
-      <c r="B34" s="113" t="n">
+      <c r="B34" s="261" t="n">
         <v>2.5</v>
       </c>
-      <c r="C34" s="114" t="n">
+      <c r="C34" s="262" t="n">
         <v>2.5</v>
       </c>
-      <c r="D34" s="99" t="inlineStr">
+      <c r="D34" s="237" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E34" s="111" t="inlineStr">
+      <c r="E34" s="259" t="inlineStr">
         <is>
           <t>Highlight and chime at or above this |z|. 2.0 and 2.5 are both reasonable; 2.0 fires more often and needs a larger sigma to stay worth trading.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="67">
-      <c r="A35" s="84" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="143">
+      <c r="A35" s="248" t="inlineStr">
         <is>
           <t>MAX_ENTRY_Z</t>
         </is>
       </c>
-      <c r="B35" s="113" t="n">
+      <c r="B35" s="261" t="n">
         <v>4.5</v>
       </c>
-      <c r="C35" s="114" t="n">
+      <c r="C35" s="262" t="n">
         <v>4.5</v>
       </c>
-      <c r="D35" s="99" t="inlineStr">
+      <c r="D35" s="237" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E35" s="111" t="inlineStr">
+      <c r="E35" s="259" t="inlineStr">
         <is>
           <t>Entry CEILING. At or above this, do NOT highlight - that is a momentum spike, not a reversion setup. Keep the band at least 1 sigma wide.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="67">
-      <c r="A36" s="84" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="143">
+      <c r="A36" s="248" t="inlineStr">
         <is>
           <t>THIN_FEED_QPM</t>
         </is>
       </c>
-      <c r="B36" s="77" t="n">
+      <c r="B36" s="258" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="99" t="n">
+      <c r="C36" s="237" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="99" t="inlineStr">
+      <c r="D36" s="237" t="inlineStr">
         <is>
           <t>q/min</t>
         </is>
       </c>
-      <c r="E36" s="111" t="inlineStr">
+      <c r="E36" s="259" t="inlineStr">
         <is>
           <t>Feed rate at or below which the quotes/min display turns amber.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38" ht="15" customHeight="1" s="67">
-      <c r="A38" s="109" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="143">
+      <c r="A37" s="248" t="inlineStr">
+        <is>
+          <t>SPREAD_QUOTE_CONVENTION</t>
+        </is>
+      </c>
+      <c r="B37" s="260" t="inlineStr">
+        <is>
+          <t>CROSSING</t>
+        </is>
+      </c>
+      <c r="C37" s="237" t="inlineStr">
+        <is>
+          <t>CROSSING</t>
+        </is>
+      </c>
+      <c r="D37" s="237" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E37" s="259" t="inlineStr">
+        <is>
+          <t>How the spread rows on Dashboard quote Bid and Ask. CROSSING: sell LegB at the bid and buy LegA at the ask, mirrored for the ask - the Gap is then the true cost of crossing and is always positive. SAME_SIDE: bid-minus-bid and ask-minus-ask, as the original sheet's rows 9 computed. Under SAME_SIDE the Gap is a DIFFERENCE of gaps, which understates the crossing cost and can go negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39" ht="15" customHeight="1" s="143">
+      <c r="A39" s="256" t="inlineStr">
         <is>
           <t>SIZING  /  COSTS</t>
         </is>
       </c>
-      <c r="B38" s="109" t="n"/>
-      <c r="C38" s="109" t="n"/>
-      <c r="D38" s="109" t="n"/>
-      <c r="E38" s="109" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="67">
-      <c r="A39" s="110" t="inlineStr">
+      <c r="B39" s="256" t="n"/>
+      <c r="C39" s="256" t="n"/>
+      <c r="D39" s="256" t="n"/>
+      <c r="E39" s="256" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="143">
+      <c r="A40" s="257" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B39" s="110" t="inlineStr">
+      <c r="B40" s="257" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C39" s="110" t="inlineStr">
+      <c r="C40" s="257" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D39" s="110" t="inlineStr">
+      <c r="D40" s="257" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E39" s="110" t="inlineStr">
+      <c r="E40" s="257" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="67">
-      <c r="A40" s="84" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="143">
+      <c r="A41" s="248" t="inlineStr">
         <is>
           <t>LOTS</t>
         </is>
       </c>
-      <c r="B40" s="77" t="n">
+      <c r="B41" s="258" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="99" t="n">
+      <c r="C41" s="237" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="99" t="inlineStr">
+      <c r="D41" s="237" t="inlineStr">
         <is>
           <t>lots</t>
         </is>
       </c>
-      <c r="E40" s="111" t="inlineStr">
+      <c r="E41" s="259" t="inlineStr">
         <is>
           <t>Contracts per leg, for the cost and take-profit maths.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="67">
-      <c r="A41" s="84" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="143">
+      <c r="A42" s="248" t="inlineStr">
         <is>
           <t>TP_MODE</t>
         </is>
       </c>
-      <c r="B41" s="112" t="inlineStr">
+      <c r="B42" s="260" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL</t>
         </is>
       </c>
-      <c r="C41" s="99" t="inlineStr">
+      <c r="C42" s="237" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL</t>
         </is>
       </c>
-      <c r="D41" s="99" t="inlineStr">
+      <c r="D42" s="237" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E41" s="111" t="inlineStr">
+      <c r="E42" s="259" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL: Take Profit = Entry + Costs + (WIN_PCT x Notional). TARGET_USD: the older rule, Take Profit = Entry + Costs + TARGET_NET_USD.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="67">
-      <c r="A42" s="84" t="inlineStr">
+    <row r="43" ht="15" customHeight="1" s="143">
+      <c r="A43" s="248" t="inlineStr">
         <is>
           <t>WIN_PCT</t>
         </is>
       </c>
-      <c r="B42" s="113" t="n">
+      <c r="B43" s="261" t="n">
         <v>0.01</v>
       </c>
-      <c r="C42" s="114" t="n">
+      <c r="C43" s="262" t="n">
         <v>0.01</v>
       </c>
-      <c r="D42" s="99" t="inlineStr">
+      <c r="D43" s="237" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="E42" s="111" t="inlineStr">
+      <c r="E43" s="259" t="inlineStr">
         <is>
           <t>Percentage win, as a FRACTION - 0.01 is 1%, 0.02 is 2%. Used only when TP_MODE = PCT_NOTIONAL.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="67">
-      <c r="A43" s="84" t="inlineStr">
+    <row r="44" ht="15" customHeight="1" s="143">
+      <c r="A44" s="248" t="inlineStr">
         <is>
           <t>NOTIONAL_BASIS</t>
         </is>
       </c>
-      <c r="B43" s="112" t="inlineStr">
+      <c r="B44" s="260" t="inlineStr">
         <is>
           <t>SPREAD_VALUE</t>
         </is>
       </c>
-      <c r="C43" s="99" t="inlineStr">
+      <c r="C44" s="237" t="inlineStr">
         <is>
           <t>SPREAD_VALUE</t>
         </is>
       </c>
-      <c r="D43" s="99" t="inlineStr">
+      <c r="D44" s="237" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E43" s="111" t="inlineStr">
+      <c r="E44" s="259" t="inlineStr">
         <is>
           <t>What WIN_PCT is taken OF. SPREAD_VALUE = |spread| x USD/pt x LOTS. ONE_LEG = the crude leg's full contract value. BOTH_LEGS = both legs' contract value added. These differ by roughly 10x - read the note below the table before changing it.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="67">
-      <c r="A44" s="84" t="inlineStr">
+    <row r="45" ht="15" customHeight="1" s="143">
+      <c r="A45" s="248" t="inlineStr">
         <is>
           <t>TARGET_NET_USD</t>
         </is>
       </c>
-      <c r="B44" s="77" t="n">
+      <c r="B45" s="258" t="n">
         <v>150</v>
       </c>
-      <c r="C44" s="99" t="n">
+      <c r="C45" s="237" t="n">
         <v>150</v>
       </c>
-      <c r="D44" s="99" t="inlineStr">
+      <c r="D45" s="237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E44" s="111" t="inlineStr">
+      <c r="E45" s="259" t="inlineStr">
         <is>
           <t>Desired profit AFTER all costs. Used only when TP_MODE = TARGET_USD.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="67">
-      <c r="A45" s="84" t="inlineStr">
+    <row r="46" ht="15" customHeight="1" s="143">
+      <c r="A46" s="248" t="inlineStr">
         <is>
           <t>EDGE_MULTIPLE</t>
         </is>
       </c>
-      <c r="B45" s="113" t="n">
+      <c r="B46" s="261" t="n">
         <v>1.5</v>
       </c>
-      <c r="C45" s="114" t="n">
+      <c r="C46" s="262" t="n">
         <v>1.5</v>
       </c>
-      <c r="D45" s="99" t="inlineStr">
+      <c r="D46" s="237" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E45" s="111" t="inlineStr">
+      <c r="E46" s="259" t="inlineStr">
         <is>
           <t>Expected capture must clear the round trip by this multiple.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="67">
-      <c r="A46" s="84" t="inlineStr">
+    <row r="47" ht="15" customHeight="1" s="143">
+      <c r="A47" s="248" t="inlineStr">
         <is>
           <t>RATE_ORIENT_PER_SIDE</t>
         </is>
       </c>
-      <c r="B46" s="113" t="n">
+      <c r="B47" s="261" t="n">
         <v>0.35</v>
       </c>
-      <c r="C46" s="114" t="n">
+      <c r="C47" s="262" t="n">
         <v>0.35</v>
       </c>
-      <c r="D46" s="99" t="inlineStr">
+      <c r="D47" s="237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E46" s="111" t="inlineStr">
+      <c r="E47" s="259" t="inlineStr">
         <is>
           <t>Orient clearing + execution, per contract per side. Source: Orient rate card 2026-08-21, Ver.26.8.17.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="67">
-      <c r="A47" s="84" t="inlineStr">
+    <row r="48" ht="15" customHeight="1" s="143">
+      <c r="A48" s="248" t="inlineStr">
         <is>
           <t>RATE_FIX_PER_SIDE</t>
         </is>
       </c>
-      <c r="B47" s="113" t="n">
+      <c r="B48" s="261" t="n">
         <v>0.06</v>
       </c>
-      <c r="C47" s="114" t="n">
+      <c r="C48" s="262" t="n">
         <v>0.06</v>
       </c>
-      <c r="D47" s="99" t="inlineStr">
+      <c r="D48" s="237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E47" s="111" t="inlineStr">
+      <c r="E48" s="259" t="inlineStr">
         <is>
           <t>FIX / platform transaction fee, per contract per side. Same rate card.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="67">
-      <c r="A48" s="84" t="inlineStr">
+    <row r="49" ht="15" customHeight="1" s="143">
+      <c r="A49" s="248" t="inlineStr">
         <is>
           <t>RATE_CME_PER_SIDE</t>
         </is>
       </c>
-      <c r="B48" s="113" t="n">
+      <c r="B49" s="261" t="n">
         <v>1.5</v>
       </c>
-      <c r="C48" s="114" t="n">
+      <c r="C49" s="262" t="n">
         <v>1.5</v>
       </c>
-      <c r="D48" s="99" t="inlineStr">
+      <c r="D49" s="237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E48" s="111" t="inlineStr">
+      <c r="E49" s="259" t="inlineStr">
         <is>
           <t>CME exchange + clearing, per contract per side. Same rate card.</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50" ht="15" customHeight="1" s="67">
-      <c r="A50" s="109" t="inlineStr">
+    <row r="50"/>
+    <row r="51" ht="15" customHeight="1" s="143">
+      <c r="A51" s="256" t="inlineStr">
         <is>
           <t>AUDIBLE ALERT</t>
         </is>
       </c>
-      <c r="B50" s="109" t="n"/>
-      <c r="C50" s="109" t="n"/>
-      <c r="D50" s="109" t="n"/>
-      <c r="E50" s="109" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="67">
-      <c r="A51" s="110" t="inlineStr">
+      <c r="B51" s="256" t="n"/>
+      <c r="C51" s="256" t="n"/>
+      <c r="D51" s="256" t="n"/>
+      <c r="E51" s="256" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="143">
+      <c r="A52" s="257" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B51" s="110" t="inlineStr">
+      <c r="B52" s="257" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C51" s="110" t="inlineStr">
+      <c r="C52" s="257" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D51" s="110" t="inlineStr">
+      <c r="D52" s="257" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E51" s="110" t="inlineStr">
+      <c r="E52" s="257" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="67">
-      <c r="A52" s="84" t="inlineStr">
+    <row r="53" ht="15" customHeight="1" s="143">
+      <c r="A53" s="248" t="inlineStr">
         <is>
           <t>ALERT_ENABLED</t>
         </is>
       </c>
-      <c r="B52" s="77" t="b">
+      <c r="B53" s="258" t="b">
         <v>1</v>
       </c>
-      <c r="C52" s="99" t="b">
+      <c r="C53" s="237" t="b">
         <v>1</v>
       </c>
-      <c r="D52" s="99" t="inlineStr">
+      <c r="D53" s="237" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E52" s="111" t="inlineStr">
+      <c r="E53" s="259" t="inlineStr">
         <is>
           <t>MASTER MUTE. FALSE silences every sound.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="67">
-      <c r="A53" s="84" t="inlineStr">
+    <row r="54" ht="15" customHeight="1" s="143">
+      <c r="A54" s="248" t="inlineStr">
         <is>
           <t>ALERT_SOUND_PATH</t>
         </is>
       </c>
-      <c r="B53" s="112" t="inlineStr">
+      <c r="B54" s="260" t="inlineStr">
         <is>
           <t>C:\Windows\Media\chimes.wav</t>
         </is>
       </c>
-      <c r="C53" s="99" t="inlineStr">
+      <c r="C54" s="237" t="inlineStr">
         <is>
           <t>C:\Windows\Media\chimes.wav</t>
         </is>
       </c>
-      <c r="D53" s="99" t="inlineStr">
+      <c r="D54" s="237" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E53" s="111" t="inlineStr">
+      <c r="E54" s="259" t="inlineStr">
         <is>
           <t>Single short 'ting' played on an entry-band crossing.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="67">
-      <c r="A54" s="84" t="inlineStr">
+    <row r="55" ht="15" customHeight="1" s="143">
+      <c r="A55" s="248" t="inlineStr">
         <is>
           <t>ALERT_SOUND_PATH_CEILING</t>
         </is>
       </c>
-      <c r="B54" s="112" t="inlineStr">
+      <c r="B55" s="260" t="inlineStr">
         <is>
           <t>C:\Windows\Media\notify.wav</t>
         </is>
       </c>
-      <c r="C54" s="99" t="inlineStr">
+      <c r="C55" s="237" t="inlineStr">
         <is>
           <t>C:\Windows\Media\notify.wav</t>
         </is>
       </c>
-      <c r="D54" s="99" t="inlineStr">
+      <c r="D55" s="237" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E54" s="111" t="inlineStr">
+      <c r="E55" s="259" t="inlineStr">
         <is>
           <t>Distinct tone for crossing MAX_ENTRY_Z. That is 'stand down', not 'get in'.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="67">
-      <c r="A55" s="84" t="inlineStr">
+    <row r="56" ht="15" customHeight="1" s="143">
+      <c r="A56" s="248" t="inlineStr">
         <is>
           <t>ALERT_REARM_MARGIN</t>
         </is>
       </c>
-      <c r="B55" s="113" t="n">
+      <c r="B56" s="261" t="n">
         <v>0.25</v>
       </c>
-      <c r="C55" s="114" t="n">
+      <c r="C56" s="262" t="n">
         <v>0.25</v>
       </c>
-      <c r="D55" s="99" t="inlineStr">
+      <c r="D56" s="237" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E55" s="111" t="inlineStr">
+      <c r="E56" s="259" t="inlineStr">
         <is>
           <t>Hysteresis. Do not re-arm until |z| falls back below ENTRY_Z - this margin.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="67">
-      <c r="A56" s="84" t="inlineStr">
+    <row r="57" ht="15" customHeight="1" s="143">
+      <c r="A57" s="248" t="inlineStr">
         <is>
           <t>ALERT_COOLDOWN_SEC</t>
         </is>
       </c>
-      <c r="B56" s="77" t="n">
+      <c r="B57" s="258" t="n">
         <v>60</v>
       </c>
-      <c r="C56" s="99" t="n">
+      <c r="C57" s="237" t="n">
         <v>60</v>
       </c>
-      <c r="D56" s="99" t="inlineStr">
+      <c r="D57" s="237" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E56" s="111" t="inlineStr">
+      <c r="E57" s="259" t="inlineStr">
         <is>
           <t>Minimum seconds between alerts for the same spread.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="67">
-      <c r="A57" s="84" t="inlineStr">
+    <row r="58" ht="15" customHeight="1" s="143">
+      <c r="A58" s="248" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES</t>
         </is>
       </c>
-      <c r="B57" s="77" t="b">
+      <c r="B58" s="258" t="b">
         <v>0</v>
       </c>
-      <c r="C57" s="99" t="b">
+      <c r="C58" s="237" t="b">
         <v>0</v>
       </c>
-      <c r="D57" s="99" t="inlineStr">
+      <c r="D58" s="237" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E57" s="111" t="inlineStr">
+      <c r="E58" s="259" t="inlineStr">
         <is>
           <t>FALSE = the chime follows ENTRY_Z alone. TRUE = also stay silent when the edge filter fails, on the argument that a sound for a trade you should not take trains you to ignore the sound. Ships FALSE by request; the edge verdict is still shown on Detail.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="67">
-      <c r="A58" s="84" t="inlineStr">
+    <row r="59" ht="15" customHeight="1" s="143">
+      <c r="A59" s="248" t="inlineStr">
         <is>
           <t>ALERT_SPEAK</t>
         </is>
       </c>
-      <c r="B58" s="77" t="b">
+      <c r="B59" s="258" t="b">
         <v>0</v>
       </c>
-      <c r="C58" s="99" t="b">
+      <c r="C59" s="237" t="b">
         <v>0</v>
       </c>
-      <c r="D58" s="99" t="inlineStr">
+      <c r="D59" s="237" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E58" s="111" t="inlineStr">
+      <c r="E59" s="259" t="inlineStr">
         <is>
           <t>TRUE also speaks the spread name (Application.Speech). Useful when watching four at once.</t>
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60" ht="15" customHeight="1" s="67">
-      <c r="A60" s="109" t="inlineStr">
+    <row r="60"/>
+    <row r="61" ht="15" customHeight="1" s="143">
+      <c r="A61" s="256" t="inlineStr">
         <is>
           <t>PERSISTENCE  /  LOGGING</t>
         </is>
       </c>
-      <c r="B60" s="109" t="n"/>
-      <c r="C60" s="109" t="n"/>
-      <c r="D60" s="109" t="n"/>
-      <c r="E60" s="109" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="67">
-      <c r="A61" s="110" t="inlineStr">
+      <c r="B61" s="256" t="n"/>
+      <c r="C61" s="256" t="n"/>
+      <c r="D61" s="256" t="n"/>
+      <c r="E61" s="256" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="143">
+      <c r="A62" s="257" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B61" s="110" t="inlineStr">
+      <c r="B62" s="257" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C61" s="110" t="inlineStr">
+      <c r="C62" s="257" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D61" s="110" t="inlineStr">
+      <c r="D62" s="257" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E61" s="110" t="inlineStr">
+      <c r="E62" s="257" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="67">
-      <c r="A62" s="84" t="inlineStr">
+    <row r="63" ht="15" customHeight="1" s="143">
+      <c r="A63" s="248" t="inlineStr">
         <is>
           <t>WARM_START_ENABLED</t>
         </is>
       </c>
-      <c r="B62" s="77" t="b">
+      <c r="B63" s="258" t="b">
         <v>1</v>
       </c>
-      <c r="C62" s="99" t="b">
+      <c r="C63" s="237" t="b">
         <v>1</v>
       </c>
-      <c r="D62" s="99" t="inlineStr">
+      <c r="D63" s="237" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E62" s="111" t="inlineStr">
+      <c r="E63" s="259" t="inlineStr">
         <is>
           <t>On open, reload the flushed buffer so a restart does not cost another two hours of warm-up.</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="67">
-      <c r="A63" s="84" t="inlineStr">
+    <row r="64" ht="15" customHeight="1" s="143">
+      <c r="A64" s="248" t="inlineStr">
         <is>
           <t>WARM_START_MAX_AGE_MIN</t>
         </is>
       </c>
-      <c r="B63" s="77" t="n">
+      <c r="B64" s="258" t="n">
         <v>180</v>
       </c>
-      <c r="C63" s="99" t="n">
+      <c r="C64" s="237" t="n">
         <v>180</v>
       </c>
-      <c r="D63" s="99" t="inlineStr">
+      <c r="D64" s="237" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E63" s="111" t="inlineStr">
+      <c r="E64" s="259" t="inlineStr">
         <is>
           <t>Only reload if the newest saved sample is younger than this.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="67">
-      <c r="A64" s="84" t="inlineStr">
+    <row r="65" ht="15" customHeight="1" s="143">
+      <c r="A65" s="248" t="inlineStr">
         <is>
           <t>LOG_ENABLED</t>
         </is>
       </c>
-      <c r="B64" s="77" t="b">
+      <c r="B65" s="258" t="b">
         <v>1</v>
       </c>
-      <c r="C64" s="99" t="b">
+      <c r="C65" s="237" t="b">
         <v>1</v>
       </c>
-      <c r="D64" s="99" t="inlineStr">
+      <c r="D65" s="237" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E64" s="111" t="inlineStr">
+      <c r="E65" s="259" t="inlineStr">
         <is>
           <t>Write signal events to the Log sheet.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="67">
-      <c r="A65" s="84" t="inlineStr">
+    <row r="66" ht="15" customHeight="1" s="143">
+      <c r="A66" s="248" t="inlineStr">
         <is>
           <t>LOG_MAX_ROWS</t>
         </is>
       </c>
-      <c r="B65" s="77" t="n">
+      <c r="B66" s="258" t="n">
         <v>20000</v>
       </c>
-      <c r="C65" s="99" t="n">
+      <c r="C66" s="237" t="n">
         <v>20000</v>
       </c>
-      <c r="D65" s="99" t="inlineStr">
+      <c r="D66" s="237" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="E65" s="111" t="inlineStr">
+      <c r="E66" s="259" t="inlineStr">
         <is>
           <t>Log is trimmed to this many rows.</t>
         </is>
       </c>
     </row>
-    <row r="66"/>
-    <row r="67" ht="15" customHeight="1" s="67">
-      <c r="A67" s="109" t="inlineStr">
+    <row r="67"/>
+    <row r="68" ht="15" customHeight="1" s="143">
+      <c r="A68" s="256" t="inlineStr">
         <is>
           <t>DERIVED COMMISSION  (formulas - do not edit)</t>
         </is>
       </c>
-      <c r="B67" s="115" t="n"/>
-      <c r="C67" s="115" t="n"/>
-      <c r="D67" s="115" t="n"/>
-      <c r="E67" s="115" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="67">
-      <c r="A68" s="110" t="inlineStr">
+      <c r="B68" s="263" t="n"/>
+      <c r="C68" s="263" t="n"/>
+      <c r="D68" s="263" t="n"/>
+      <c r="E68" s="263" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="143">
+      <c r="A69" s="257" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B68" s="110" t="inlineStr">
+      <c r="B69" s="257" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C68" s="110" t="inlineStr">
+      <c r="C69" s="257" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D68" s="110" t="inlineStr">
+      <c r="D69" s="257" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E68" s="110" t="inlineStr">
+      <c r="E69" s="257" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="67">
-      <c r="A69" s="84" t="inlineStr">
+    <row r="70" ht="15" customHeight="1" s="143">
+      <c r="A70" s="248" t="inlineStr">
         <is>
           <t>COMMISSION_CONSERVATIVE</t>
         </is>
       </c>
-      <c r="B69" s="85">
-        <f>2*(B46+B47+B48)</f>
-        <v/>
-      </c>
-      <c r="E69" s="116" t="inlineStr">
+      <c r="B70" s="249">
+        <f>2*(B47+B48+B49)</f>
+        <v/>
+      </c>
+      <c r="E70" s="264" t="inlineStr">
         <is>
           <t>Per lot PER LEG, round turn, reading CME's 1.50 as per SIDE. This is the conservative reading and the one to use.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="67">
-      <c r="A70" s="84" t="inlineStr">
+    <row r="71" ht="15" customHeight="1" s="143">
+      <c r="A71" s="248" t="inlineStr">
         <is>
           <t>COMMISSION_IF_CME_PER_RT</t>
         </is>
       </c>
-      <c r="B70" s="91">
-        <f>2*(B46+B47)+B48</f>
-        <v/>
-      </c>
-      <c r="E70" s="116" t="inlineStr">
+      <c r="B71" s="245">
+        <f>2*(B47+B48)+B49</f>
+        <v/>
+      </c>
+      <c r="E71" s="264" t="inlineStr">
         <is>
           <t>The same figure if CME's 1.50 turns out to be per ROUND TURN rather than per side.</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="67">
-      <c r="A71" s="84" t="inlineStr">
+    <row r="72" ht="15" customHeight="1" s="143">
+      <c r="A72" s="248" t="inlineStr">
         <is>
           <t>COMMISSION_BASIS</t>
         </is>
       </c>
-      <c r="B71" s="77" t="inlineStr">
+      <c r="B72" s="258" t="inlineStr">
         <is>
           <t>CONSERVATIVE</t>
         </is>
       </c>
-      <c r="C71" s="99" t="inlineStr">
+      <c r="C72" s="237" t="inlineStr">
         <is>
           <t>CONSERVATIVE</t>
         </is>
       </c>
-      <c r="E71" s="116" t="inlineStr">
+      <c r="E72" s="264" t="inlineStr">
         <is>
           <t>CONSERVATIVE or CME_PER_RT. An understated cost model approves losing trades invisibly; an overstated one only refuses trades, visibly. Leave it on CONSERVATIVE.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="67">
-      <c r="A72" s="84" t="inlineStr">
+    <row r="73" ht="15" customHeight="1" s="143">
+      <c r="A73" s="248" t="inlineStr">
         <is>
           <t>COMMISSION_PER_LOT_ROUND_TURN</t>
         </is>
       </c>
-      <c r="B72" s="85">
-        <f>IF(B71="CME_PER_RT",B70,B69)</f>
-        <v/>
-      </c>
-      <c r="E72" s="116" t="inlineStr">
+      <c r="B73" s="249">
+        <f>IF(B72="CME_PER_RT",B71,B70)</f>
+        <v/>
+      </c>
+      <c r="E73" s="264" t="inlineStr">
         <is>
           <t>USD per lot per leg, round turn. This is what the cost model actually uses.</t>
         </is>
       </c>
     </row>
-    <row r="73"/>
-    <row r="74" ht="15" customHeight="1" s="67">
-      <c r="A74" s="109" t="inlineStr">
+    <row r="74"/>
+    <row r="75" ht="15" customHeight="1" s="143">
+      <c r="A75" s="256" t="inlineStr">
         <is>
           <t>SPREAD_TABLE_START   -   up to 4 monitored spreads, one buffer each</t>
         </is>
       </c>
-      <c r="B74" s="115" t="n"/>
-      <c r="C74" s="115" t="n"/>
-      <c r="D74" s="115" t="n"/>
-      <c r="E74" s="115" t="n"/>
-      <c r="F74" s="115" t="n"/>
-      <c r="G74" s="115" t="n"/>
-      <c r="H74" s="115" t="n"/>
-      <c r="I74" s="115" t="n"/>
-      <c r="J74" s="115" t="n"/>
-      <c r="K74" s="115" t="n"/>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="67">
-      <c r="A75" s="71" t="inlineStr">
+      <c r="B75" s="263" t="n"/>
+      <c r="C75" s="263" t="n"/>
+      <c r="D75" s="263" t="n"/>
+      <c r="E75" s="263" t="n"/>
+      <c r="F75" s="263" t="n"/>
+      <c r="G75" s="263" t="n"/>
+      <c r="H75" s="263" t="n"/>
+      <c r="I75" s="263" t="n"/>
+      <c r="J75" s="263" t="n"/>
+      <c r="K75" s="263" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="143">
+      <c r="A76" s="231" t="inlineStr">
         <is>
           <t>Leg COMPOSITION (which instruments, and their weights) is defined by the labelled formulas in the MONITOR LEGS block on the hidden Feed sheet. Everything below is hot-reloaded each tick.</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="32.8" customHeight="1" s="67">
-      <c r="A76" s="110" t="inlineStr">
+    <row r="77" ht="32.8" customHeight="1" s="143">
+      <c r="A77" s="257" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B76" s="110" t="inlineStr">
+      <c r="B77" s="257" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="C76" s="110" t="inlineStr">
+      <c r="C77" s="257" t="inlineStr">
         <is>
           <t>Display name</t>
         </is>
       </c>
-      <c r="D76" s="110" t="inlineStr">
+      <c r="D77" s="257" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="E76" s="110" t="inlineStr">
+      <c r="E77" s="257" t="inlineStr">
         <is>
           <t>HEDGE_RATIO (beta)</t>
         </is>
       </c>
-      <c r="F76" s="110" t="inlineStr">
+      <c r="F77" s="257" t="inlineStr">
         <is>
           <t>Beta stamped for pair</t>
         </is>
       </c>
-      <c r="G76" s="110" t="inlineStr">
+      <c r="G77" s="257" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread, per lot</t>
         </is>
       </c>
-      <c r="H76" s="110" t="inlineStr">
+      <c r="H77" s="257" t="inlineStr">
         <is>
           <t>Contracts charged commission</t>
         </is>
       </c>
-      <c r="I76" s="110" t="inlineStr">
+      <c r="I77" s="257" t="inlineStr">
         <is>
           <t>Tick size</t>
         </is>
       </c>
-      <c r="J76" s="110" t="inlineStr">
+      <c r="J77" s="257" t="inlineStr">
         <is>
           <t>Decimals</t>
         </is>
       </c>
-      <c r="K76" s="110" t="inlineStr">
+      <c r="K77" s="257" t="inlineStr">
         <is>
           <t>Listed equivalent (cost comparison)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="67">
-      <c r="A77" s="78" t="inlineStr">
+    <row r="78" ht="15" customHeight="1" s="143">
+      <c r="A78" s="250" t="inlineStr">
         <is>
           <t>SPREAD_1</t>
         </is>
       </c>
-      <c r="B77" s="77" t="b">
+      <c r="B78" s="258" t="b">
         <v>1</v>
       </c>
-      <c r="C77" s="112" t="inlineStr">
+      <c r="C78" s="260" t="inlineStr">
         <is>
           <t>BZ - CL  (Brent LDF - WTI)</t>
         </is>
       </c>
-      <c r="D77" s="77" t="inlineStr">
+      <c r="D78" s="258" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E77" s="117" t="n">
+      <c r="E78" s="265" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="112" t="inlineStr">
+      <c r="F78" s="260" t="inlineStr">
         <is>
           <t>BZV6 / CLV6, derived 2026-08 (RELATED pair - no fair value, empirical mean only)</t>
         </is>
       </c>
-      <c r="G77" s="118" t="n">
+      <c r="G78" s="266" t="n">
         <v>1000</v>
       </c>
-      <c r="H77" s="119" t="n">
+      <c r="H78" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="117" t="n">
+      <c r="I78" s="265" t="n">
         <v>0.01</v>
       </c>
-      <c r="J77" s="119" t="n">
+      <c r="J78" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="K77" s="100" t="inlineStr">
+      <c r="K78" s="239" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="67">
-      <c r="A78" s="78" t="inlineStr">
+    <row r="79" ht="15" customHeight="1" s="143">
+      <c r="A79" s="250" t="inlineStr">
         <is>
           <t>SPREAD_2</t>
         </is>
       </c>
-      <c r="B78" s="77" t="b">
+      <c r="B79" s="258" t="b">
         <v>1</v>
       </c>
-      <c r="C78" s="112" t="inlineStr">
+      <c r="C79" s="260" t="inlineStr">
         <is>
           <t>HO/CL crack  (ULSD - WTI)</t>
         </is>
       </c>
-      <c r="D78" s="77" t="inlineStr">
+      <c r="D79" s="258" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E78" s="117" t="n">
+      <c r="E79" s="265" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="112" t="inlineStr">
+      <c r="F79" s="260" t="inlineStr">
         <is>
           <t>HOV6 x42 / CLV6, 1:1 by design (crack, not a fitted beta)</t>
         </is>
       </c>
-      <c r="G78" s="118" t="n">
+      <c r="G79" s="266" t="n">
         <v>1000</v>
       </c>
-      <c r="H78" s="119" t="n">
+      <c r="H79" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="117" t="n">
+      <c r="I79" s="265" t="n">
         <v>0.01</v>
       </c>
-      <c r="J78" s="119" t="n">
+      <c r="J79" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="K78" s="100" t="inlineStr">
+      <c r="K79" s="239" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="67">
-      <c r="A79" s="78" t="inlineStr">
+    <row r="80" ht="15" customHeight="1" s="143">
+      <c r="A80" s="250" t="inlineStr">
         <is>
           <t>SPREAD_3</t>
         </is>
       </c>
-      <c r="B79" s="77" t="b">
+      <c r="B80" s="258" t="b">
         <v>1</v>
       </c>
-      <c r="C79" s="112" t="inlineStr">
+      <c r="C80" s="260" t="inlineStr">
         <is>
           <t>3:2:1 crack  (2RB+1HO-3CL)/3</t>
         </is>
       </c>
-      <c r="D79" s="77" t="inlineStr">
+      <c r="D80" s="258" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E79" s="117" t="n">
+      <c r="E80" s="265" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="112" t="inlineStr">
+      <c r="F80" s="260" t="inlineStr">
         <is>
           <t>RBV6/HOV6/CLV6, structural 3:2:1 - not a fitted beta</t>
         </is>
       </c>
-      <c r="G79" s="118" t="n">
+      <c r="G80" s="266" t="n">
         <v>3000</v>
       </c>
-      <c r="H79" s="119" t="n">
+      <c r="H80" s="267" t="n">
         <v>6</v>
       </c>
-      <c r="I79" s="117" t="n">
+      <c r="I80" s="265" t="n">
         <v>0.01</v>
       </c>
-      <c r="J79" s="119" t="n">
+      <c r="J80" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="K79" s="100" t="inlineStr">
+      <c r="K80" s="239" t="inlineStr">
         <is>
           <t>(none listed)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="67">
-      <c r="A80" s="78" t="inlineStr">
+    <row r="81" ht="15" customHeight="1" s="143">
+      <c r="A81" s="250" t="inlineStr">
         <is>
           <t>SPREAD_4</t>
         </is>
       </c>
-      <c r="B80" s="77" t="b">
+      <c r="B81" s="258" t="b">
         <v>1</v>
       </c>
-      <c r="C80" s="112" t="inlineStr">
+      <c r="C81" s="260" t="inlineStr">
         <is>
           <t>CL-BZ Inter-Product (listed)</t>
         </is>
       </c>
-      <c r="D80" s="77" t="inlineStr">
+      <c r="D81" s="258" t="inlineStr">
         <is>
           <t>LISTED</t>
         </is>
       </c>
-      <c r="E80" s="117" t="n">
+      <c r="E81" s="265" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="112" t="inlineStr">
+      <c r="F81" s="260" t="inlineStr">
         <is>
           <t>Exchange-listed spread - beta not applicable</t>
         </is>
       </c>
-      <c r="G80" s="118" t="n">
+      <c r="G81" s="266" t="n">
         <v>1000</v>
       </c>
-      <c r="H80" s="119" t="n">
+      <c r="H81" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="I80" s="117" t="n">
+      <c r="I81" s="265" t="n">
         <v>0.01</v>
       </c>
-      <c r="J80" s="119" t="n">
+      <c r="J81" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="K80" s="100" t="inlineStr">
+      <c r="K81" s="239" t="inlineStr">
         <is>
           <t>n/a - this IS the listed spread</t>
         </is>
       </c>
     </row>
-    <row r="81"/>
-    <row r="82" ht="15" customHeight="1" s="67">
-      <c r="A82" s="107" t="inlineStr">
+    <row r="82"/>
+    <row r="83" ht="15" customHeight="1" s="143">
+      <c r="A83" s="253" t="inlineStr">
         <is>
           <t>HEDGE RATIO BELONGS TO THE PAIR. If the instruments change, beta must be re-derived - a stale beta silently redefines the series. Column F stamps what each beta was computed for.</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="67">
-      <c r="A83" s="71" t="inlineStr">
+    <row r="84" ht="15" customHeight="1" s="143">
+      <c r="A84" s="231" t="inlineStr">
         <is>
           <t>Contracts charged: BZ-CL and the listed spread are 2 contracts per lot (one per leg); the 3:2:1 crack is 6 (2 RB + 1 HO + 3 CL).</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="67">
-      <c r="A84" s="71" t="inlineStr">
+    <row r="85" ht="15" customHeight="1" s="143">
+      <c r="A85" s="231" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread: NYMEX energy contracts are 1,000 bbl, so one cent of differential is $10 per leg per lot, i.e. $1,000 per 1.00.</t>
         </is>
       </c>
     </row>
-    <row r="85"/>
-    <row r="86" ht="15" customHeight="1" s="67">
-      <c r="A86" s="107" t="inlineStr">
+    <row r="86"/>
+    <row r="87" ht="15" customHeight="1" s="143">
+      <c r="A87" s="253" t="inlineStr">
         <is>
           <t>NOTIONAL_BASIS - read this before changing it:</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="67">
-      <c r="A87" s="71" t="inlineStr">
+    <row r="88" ht="15" customHeight="1" s="143">
+      <c r="A88" s="231" t="inlineStr">
         <is>
           <t>A spread is not an outright, so 'notional' has no single meaning. At 1 lot with CL near $60 and BZ-CL near $7.20:  SPREAD_VALUE ~ $7,200, ONE_LEG ~ $60,000, BOTH_LEGS ~ $127,000.</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="67">
-      <c r="A88" s="120" t="inlineStr">
+    <row r="89" ht="15" customHeight="1" s="143">
+      <c r="A89" s="268" t="inlineStr">
         <is>
           <t>1% of those is $72, $600 and $1,270. If sigma on this spread turns out to be ~5 cents ($50), only the first is reachable - the others need the spread to travel 12 or 25 sigma, which it will not do. Watch the TP-in-sigma cell on the Dashboard: above about 1 sigma it turns amber.</t>
         </is>
@@ -4617,315 +5580,315 @@
   <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="40" customWidth="1" style="66" min="1" max="1"/>
-    <col width="34" customWidth="1" style="66" min="2" max="2"/>
-    <col width="13" customWidth="1" style="66" min="3" max="8"/>
-    <col width="60" customWidth="1" style="66" min="9" max="9"/>
+    <col width="40" customWidth="1" style="141" min="1" max="1"/>
+    <col width="34" customWidth="1" style="141" min="2" max="2"/>
+    <col width="13" customWidth="1" style="141" min="3" max="8"/>
+    <col width="60" customWidth="1" style="141" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="67">
-      <c r="A1" s="121" t="inlineStr">
+    <row r="1" ht="16.15" customHeight="1" s="143">
+      <c r="A1" s="269" t="inlineStr">
         <is>
           <t>FEED  -  hidden.  Every RTD() formula lives here.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="67">
-      <c r="A2" s="73" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="A2" s="270" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B2" s="122">
+      <c r="B2" s="271">
         <f>Dashboard!$C$4</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="67">
-      <c r="A3" s="107" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="143">
+      <c r="A3" s="253" t="inlineStr">
         <is>
           <t>Never put an RTD() formula on Dashboard: a cell holding one repaints whenever the feed moves, and that cannot be prevented while the formula is in the cell.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5" ht="15" customHeight="1" s="67">
-      <c r="A5" s="123" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="A5" s="272" t="inlineStr">
         <is>
           <t>INSTRUMENTS</t>
         </is>
       </c>
-      <c r="B5" s="81" t="inlineStr">
+      <c r="B5" s="233" t="inlineStr">
         <is>
           <t>Instrument ID</t>
         </is>
       </c>
-      <c r="C5" s="81" t="inlineStr">
+      <c r="C5" s="233" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="D5" s="81" t="inlineStr">
+      <c r="D5" s="233" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="E5" s="81" t="inlineStr">
+      <c r="E5" s="233" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="81" t="inlineStr">
+      <c r="F5" s="233" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G5" s="81" t="inlineStr">
+      <c r="G5" s="233" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="H5" s="81" t="inlineStr">
+      <c r="H5" s="233" t="inlineStr">
         <is>
           <t>Width</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="67">
-      <c r="A6" s="82" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="143">
+      <c r="A6" s="234" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="B6" s="124">
+      <c r="B6" s="273">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A6)</f>
         <v/>
       </c>
-      <c r="C6" s="124">
+      <c r="C6" s="273">
         <f>IFERROR(IF($B6="","",VALUE(RTD("tt.rtd",,$B6,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D6" s="124">
+      <c r="D6" s="273">
         <f>IFERROR(IF($B6="","",VALUE(RTD("tt.rtd",,$B6,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E6" s="124">
+      <c r="E6" s="273">
         <f>IFERROR(IF($B6="","",VALUE(RTD("tt.rtd",,$B6,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="124">
+      <c r="F6" s="273">
         <f>IFERROR(IF($B6="","",VALUE(RTD("tt.rtd",,$B6,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G6" s="124">
+      <c r="G6" s="273">
         <f>IF(OR($C6="",$D6=""),"",($C6+$D6)/2)</f>
         <v/>
       </c>
-      <c r="H6" s="124">
+      <c r="H6" s="273">
         <f>IF(OR($C6="",$D6=""),"",$D6-$C6)</f>
         <v/>
       </c>
-      <c r="I6" s="125" t="inlineStr">
+      <c r="I6" s="274" t="inlineStr">
         <is>
           <t>RBOB Gasoline Oct26</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="67">
-      <c r="A7" s="82" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="143">
+      <c r="A7" s="234" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="B7" s="124">
+      <c r="B7" s="273">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A7)</f>
         <v/>
       </c>
-      <c r="C7" s="124">
+      <c r="C7" s="273">
         <f>IFERROR(IF($B7="","",VALUE(RTD("tt.rtd",,$B7,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D7" s="124">
+      <c r="D7" s="273">
         <f>IFERROR(IF($B7="","",VALUE(RTD("tt.rtd",,$B7,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E7" s="124">
+      <c r="E7" s="273">
         <f>IFERROR(IF($B7="","",VALUE(RTD("tt.rtd",,$B7,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="124">
+      <c r="F7" s="273">
         <f>IFERROR(IF($B7="","",VALUE(RTD("tt.rtd",,$B7,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G7" s="124">
+      <c r="G7" s="273">
         <f>IF(OR($C7="",$D7=""),"",($C7+$D7)/2)</f>
         <v/>
       </c>
-      <c r="H7" s="124">
+      <c r="H7" s="273">
         <f>IF(OR($C7="",$D7=""),"",$D7-$C7)</f>
         <v/>
       </c>
-      <c r="I7" s="125" t="inlineStr">
+      <c r="I7" s="274" t="inlineStr">
         <is>
           <t>NY Harbor ULSD Oct26</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="67">
-      <c r="A8" s="82" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="143">
+      <c r="A8" s="234" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="B8" s="124">
+      <c r="B8" s="273">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A8)</f>
         <v/>
       </c>
-      <c r="C8" s="124">
+      <c r="C8" s="273">
         <f>IFERROR(IF($B8="","",VALUE(RTD("tt.rtd",,$B8,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D8" s="124">
+      <c r="D8" s="273">
         <f>IFERROR(IF($B8="","",VALUE(RTD("tt.rtd",,$B8,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E8" s="124">
+      <c r="E8" s="273">
         <f>IFERROR(IF($B8="","",VALUE(RTD("tt.rtd",,$B8,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="124">
+      <c r="F8" s="273">
         <f>IFERROR(IF($B8="","",VALUE(RTD("tt.rtd",,$B8,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G8" s="124">
+      <c r="G8" s="273">
         <f>IF(OR($C8="",$D8=""),"",($C8+$D8)/2)</f>
         <v/>
       </c>
-      <c r="H8" s="124">
+      <c r="H8" s="273">
         <f>IF(OR($C8="",$D8=""),"",$D8-$C8)</f>
         <v/>
       </c>
-      <c r="I8" s="125" t="inlineStr">
+      <c r="I8" s="274" t="inlineStr">
         <is>
           <t>WTI Crude Oct26</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="67">
-      <c r="A9" s="82" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="A9" s="234" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="B9" s="124">
+      <c r="B9" s="273">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A9)</f>
         <v/>
       </c>
-      <c r="C9" s="124">
+      <c r="C9" s="273">
         <f>IFERROR(IF($B9="","",VALUE(RTD("tt.rtd",,$B9,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D9" s="124">
+      <c r="D9" s="273">
         <f>IFERROR(IF($B9="","",VALUE(RTD("tt.rtd",,$B9,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E9" s="124">
+      <c r="E9" s="273">
         <f>IFERROR(IF($B9="","",VALUE(RTD("tt.rtd",,$B9,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="124">
+      <c r="F9" s="273">
         <f>IFERROR(IF($B9="","",VALUE(RTD("tt.rtd",,$B9,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G9" s="124">
+      <c r="G9" s="273">
         <f>IF(OR($C9="",$D9=""),"",($C9+$D9)/2)</f>
         <v/>
       </c>
-      <c r="H9" s="124">
+      <c r="H9" s="273">
         <f>IF(OR($C9="",$D9=""),"",$D9-$C9)</f>
         <v/>
       </c>
-      <c r="I9" s="125" t="inlineStr">
+      <c r="I9" s="274" t="inlineStr">
         <is>
           <t>Brent Last Day Financial Oct26</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="67">
-      <c r="A10" s="82" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="143">
+      <c r="A10" s="234" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="B10" s="124">
+      <c r="B10" s="273">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A10)</f>
         <v/>
       </c>
-      <c r="C10" s="124">
+      <c r="C10" s="273">
         <f>IFERROR(IF($B10="","",VALUE(RTD("tt.rtd",,$B10,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D10" s="124">
+      <c r="D10" s="273">
         <f>IFERROR(IF($B10="","",VALUE(RTD("tt.rtd",,$B10,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E10" s="124">
+      <c r="E10" s="273">
         <f>IFERROR(IF($B10="","",VALUE(RTD("tt.rtd",,$B10,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="124">
+      <c r="F10" s="273">
         <f>IFERROR(IF($B10="","",VALUE(RTD("tt.rtd",,$B10,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G10" s="124">
+      <c r="G10" s="273">
         <f>IF(OR($C10="",$D10=""),"",($C10+$D10)/2)</f>
         <v/>
       </c>
-      <c r="H10" s="124">
+      <c r="H10" s="273">
         <f>IF(OR($C10="",$D10=""),"",$D10-$C10)</f>
         <v/>
       </c>
-      <c r="I10" s="125" t="inlineStr">
+      <c r="I10" s="274" t="inlineStr">
         <is>
           <t>Exchange-listed inter-product spread</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="67">
-      <c r="A11" s="82" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="143">
+      <c r="A11" s="234" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="B11" s="124">
+      <c r="B11" s="273">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A11)</f>
         <v/>
       </c>
-      <c r="C11" s="124">
+      <c r="C11" s="273">
         <f>IFERROR(IF($B11="","",VALUE(RTD("tt.rtd",,$B11,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D11" s="124">
+      <c r="D11" s="273">
         <f>IFERROR(IF($B11="","",VALUE(RTD("tt.rtd",,$B11,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E11" s="124">
+      <c r="E11" s="273">
         <f>IFERROR(IF($B11="","",VALUE(RTD("tt.rtd",,$B11,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="124">
+      <c r="F11" s="273">
         <f>IFERROR(IF($B11="","",VALUE(RTD("tt.rtd",,$B11,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G11" s="124">
+      <c r="G11" s="273">
         <f>IF(OR($C11="",$D11=""),"",($C11+$D11)/2)</f>
         <v/>
       </c>
-      <c r="H11" s="124">
+      <c r="H11" s="273">
         <f>IF(OR($C11="",$D11=""),"",$D11-$C11)</f>
         <v/>
       </c>
-      <c r="I11" s="125" t="inlineStr">
+      <c r="I11" s="274" t="inlineStr">
         <is>
           <t>Exchange-listed crack spread</t>
         </is>
@@ -4934,516 +5897,516 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
-    <row r="15" ht="15" customHeight="1" s="67">
-      <c r="A15" s="123" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="143">
+      <c r="A15" s="272" t="inlineStr">
         <is>
           <t>DERIVED &amp; LISTED SPREADS (display)</t>
         </is>
       </c>
-      <c r="B15" s="81" t="inlineStr">
+      <c r="B15" s="233" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="C15" s="81" t="inlineStr">
+      <c r="C15" s="233" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="D15" s="81" t="inlineStr">
+      <c r="D15" s="233" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="E15" s="81" t="inlineStr">
+      <c r="E15" s="233" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="F15" s="81" t="inlineStr">
+      <c r="F15" s="233" t="inlineStr">
         <is>
           <t>Width</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="67">
-      <c r="A16" s="82" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="143">
+      <c r="A16" s="234" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="B16" s="90" t="inlineStr">
+      <c r="B16" s="241" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C16" s="124">
+      <c r="C16" s="273">
         <f>IF(OR($C$9="",$D$8=""),"",$C$9-$D$8)</f>
         <v/>
       </c>
-      <c r="D16" s="124">
+      <c r="D16" s="273">
         <f>IF(OR($D$9="",$C$8=""),"",$D$9-$C$8)</f>
         <v/>
       </c>
-      <c r="E16" s="124">
+      <c r="E16" s="273">
         <f>IF(OR($G$9="",$G$8=""),"",$G$9-$G$8)</f>
         <v/>
       </c>
-      <c r="F16" s="124">
+      <c r="F16" s="273">
         <f>IF(OR($C16="",$D16=""),"",$D16-$C16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="67">
-      <c r="A17" s="82" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="143">
+      <c r="A17" s="234" t="inlineStr">
         <is>
           <t>HO/CL crack</t>
         </is>
       </c>
-      <c r="B17" s="90" t="inlineStr">
+      <c r="B17" s="241" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C17" s="124">
+      <c r="C17" s="273">
         <f>IF(OR($C$7="",$D$8=""),"",$C$7*42-$D$8)</f>
         <v/>
       </c>
-      <c r="D17" s="124">
+      <c r="D17" s="273">
         <f>IF(OR($D$7="",$C$8=""),"",$D$7*42-$C$8)</f>
         <v/>
       </c>
-      <c r="E17" s="124">
+      <c r="E17" s="273">
         <f>IF(OR($G$7="",$G$8=""),"",$G$7*42-$G$8)</f>
         <v/>
       </c>
-      <c r="F17" s="124">
+      <c r="F17" s="273">
         <f>IF(OR($C17="",$D17=""),"",$D17-$C17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="67">
-      <c r="A18" s="82" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="143">
+      <c r="A18" s="234" t="inlineStr">
         <is>
           <t>3:2:1 crack</t>
         </is>
       </c>
-      <c r="B18" s="90" t="inlineStr">
+      <c r="B18" s="241" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C18" s="124">
+      <c r="C18" s="273">
         <f>IF(OR($C$6="",$C$7="",$D$8=""),"",(($C$6*2*42)+($C$7*1*42)-($D$8*3))/3)</f>
         <v/>
       </c>
-      <c r="D18" s="124">
+      <c r="D18" s="273">
         <f>IF(OR($D$6="",$D$7="",$C$8=""),"",(($D$6*2*42)+($D$7*1*42)-($C$8*3))/3)</f>
         <v/>
       </c>
-      <c r="E18" s="124">
+      <c r="E18" s="273">
         <f>IF(OR($G$6="",$G$7="",$G$8=""),"",(($G$6*2*42)+($G$7*1*42)-($G$8*3))/3)</f>
         <v/>
       </c>
-      <c r="F18" s="124">
+      <c r="F18" s="273">
         <f>IF(OR($C18="",$D18=""),"",$D18-$C18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="67">
-      <c r="A19" s="82" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="143">
+      <c r="A19" s="234" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="B19" s="90" t="inlineStr">
+      <c r="B19" s="241" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="C19" s="124">
+      <c r="C19" s="273">
         <f>$C$10</f>
         <v/>
       </c>
-      <c r="D19" s="124">
+      <c r="D19" s="273">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="E19" s="124">
+      <c r="E19" s="273">
         <f>$G$10</f>
         <v/>
       </c>
-      <c r="F19" s="124">
+      <c r="F19" s="273">
         <f>IF(OR($C19="",$D19=""),"",$D19-$C19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="67">
-      <c r="A20" s="82" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="143">
+      <c r="A20" s="234" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="B20" s="90" t="inlineStr">
+      <c r="B20" s="241" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="C20" s="124">
+      <c r="C20" s="273">
         <f>$C$11</f>
         <v/>
       </c>
-      <c r="D20" s="124">
+      <c r="D20" s="273">
         <f>$D$11</f>
         <v/>
       </c>
-      <c r="E20" s="124">
+      <c r="E20" s="273">
         <f>$G$11</f>
         <v/>
       </c>
-      <c r="F20" s="124">
+      <c r="F20" s="273">
         <f>IF(OR($C20="",$D20=""),"",$D20-$C20)</f>
         <v/>
       </c>
     </row>
     <row r="21"/>
     <row r="22"/>
-    <row r="23" ht="15" customHeight="1" s="67">
-      <c r="A23" s="92" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="143">
+      <c r="A23" s="275" t="inlineStr">
         <is>
           <t>MONITOR LEGS</t>
         </is>
       </c>
-      <c r="B23" s="71" t="inlineStr">
+      <c r="B23" s="231" t="inlineStr">
         <is>
           <t>Edit these formulas to redefine what a monitored spread is made of. spread = LegB - HEDGE_RATIO x LegA, and nothing else - no carry, no fair-value term.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="67">
-      <c r="A24" s="81" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="143">
+      <c r="A24" s="233" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B24" s="81" t="inlineStr">
+      <c r="B24" s="233" t="inlineStr">
         <is>
           <t>Side</t>
         </is>
       </c>
-      <c r="C24" s="81" t="inlineStr">
+      <c r="C24" s="233" t="inlineStr">
         <is>
           <t>Composition</t>
         </is>
       </c>
-      <c r="D24" s="81" t="inlineStr">
+      <c r="D24" s="233" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="E24" s="81" t="inlineStr">
+      <c r="E24" s="233" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="F24" s="81" t="inlineStr">
+      <c r="F24" s="233" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="67">
-      <c r="A25" s="126" t="n">
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="A25" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="78" t="inlineStr">
+      <c r="B25" s="250" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C25" s="79" t="inlineStr">
+      <c r="C25" s="277" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D25" s="124">
+      <c r="D25" s="273">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E25" s="124">
+      <c r="E25" s="273">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F25" s="124">
+      <c r="F25" s="273">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="67">
-      <c r="A26" s="126" t="n">
+    <row r="26" ht="15" customHeight="1" s="143">
+      <c r="A26" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="78" t="inlineStr">
+      <c r="B26" s="250" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C26" s="79" t="inlineStr">
+      <c r="C26" s="277" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="D26" s="124">
+      <c r="D26" s="273">
         <f>$C$9</f>
         <v/>
       </c>
-      <c r="E26" s="124">
+      <c r="E26" s="273">
         <f>$D$9</f>
         <v/>
       </c>
-      <c r="F26" s="124">
+      <c r="F26" s="273">
         <f>$G$9</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="67">
-      <c r="A27" s="126" t="n">
+    <row r="27" ht="15" customHeight="1" s="143">
+      <c r="A27" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="78" t="inlineStr">
+      <c r="B27" s="250" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C27" s="79" t="inlineStr">
+      <c r="C27" s="277" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D27" s="124">
+      <c r="D27" s="273">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E27" s="124">
+      <c r="E27" s="273">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F27" s="124">
+      <c r="F27" s="273">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="67">
-      <c r="A28" s="126" t="n">
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="A28" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="78" t="inlineStr">
+      <c r="B28" s="250" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C28" s="79" t="inlineStr">
+      <c r="C28" s="277" t="inlineStr">
         <is>
           <t>HOV6 x 42</t>
         </is>
       </c>
-      <c r="D28" s="124">
+      <c r="D28" s="273">
         <f>IF($C$7="","",$C$7*42)</f>
         <v/>
       </c>
-      <c r="E28" s="124">
+      <c r="E28" s="273">
         <f>IF($D$7="","",$D$7*42)</f>
         <v/>
       </c>
-      <c r="F28" s="124">
+      <c r="F28" s="273">
         <f>IF($G$7="","",$G$7*42)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="67">
-      <c r="A29" s="126" t="n">
+    <row r="29" ht="15" customHeight="1" s="143">
+      <c r="A29" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="78" t="inlineStr">
+      <c r="B29" s="250" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C29" s="79" t="inlineStr">
+      <c r="C29" s="277" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D29" s="124">
+      <c r="D29" s="273">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E29" s="124">
+      <c r="E29" s="273">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F29" s="124">
+      <c r="F29" s="273">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="67">
-      <c r="A30" s="126" t="n">
+    <row r="30" ht="15" customHeight="1" s="143">
+      <c r="A30" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="78" t="inlineStr">
+      <c r="B30" s="250" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C30" s="79" t="inlineStr">
+      <c r="C30" s="277" t="inlineStr">
         <is>
           <t>(2 x RBV6 + 1 x HOV6) x 42 / 3</t>
         </is>
       </c>
-      <c r="D30" s="124">
+      <c r="D30" s="273">
         <f>IF(OR($C$6="",$C$7=""),"",($C$6*2*42+$C$7*1*42)/3)</f>
         <v/>
       </c>
-      <c r="E30" s="124">
+      <c r="E30" s="273">
         <f>IF(OR($D$6="",$D$7=""),"",($D$6*2*42+$D$7*1*42)/3)</f>
         <v/>
       </c>
-      <c r="F30" s="124">
+      <c r="F30" s="273">
         <f>IF(OR($G$6="",$G$7=""),"",($G$6*2*42+$G$7*1*42)/3)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="67">
-      <c r="A31" s="126" t="n">
+    <row r="31" ht="15" customHeight="1" s="143">
+      <c r="A31" s="276" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="78" t="inlineStr">
+      <c r="B31" s="250" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C31" s="79" t="inlineStr">
+      <c r="C31" s="277" t="inlineStr">
         <is>
           <t>(none - LISTED spread)</t>
         </is>
       </c>
-      <c r="D31" s="124" t="inlineStr"/>
-      <c r="E31" s="124" t="inlineStr"/>
-      <c r="F31" s="124" t="inlineStr"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="67">
-      <c r="A32" s="126" t="n">
+      <c r="D31" s="273" t="inlineStr"/>
+      <c r="E31" s="273" t="inlineStr"/>
+      <c r="F31" s="273" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="143">
+      <c r="A32" s="276" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="78" t="inlineStr">
+      <c r="B32" s="250" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C32" s="79" t="inlineStr">
+      <c r="C32" s="277" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="D32" s="124">
+      <c r="D32" s="273">
         <f>$C$10</f>
         <v/>
       </c>
-      <c r="E32" s="124">
+      <c r="E32" s="273">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="F32" s="124">
+      <c r="F32" s="273">
         <f>$G$10</f>
         <v/>
       </c>
     </row>
     <row r="33"/>
-    <row r="34" ht="15" customHeight="1" s="67">
-      <c r="A34" s="92" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="143">
+      <c r="A34" s="275" t="inlineStr">
         <is>
           <t>LISTED-EQUIVALENT ROW PER SLOT  (for the side-by-side crossing-cost comparison)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="67">
-      <c r="A35" s="81" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="143">
+      <c r="A35" s="233" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B35" s="81" t="inlineStr">
+      <c r="B35" s="233" t="inlineStr">
         <is>
           <t>Feed derived row</t>
         </is>
       </c>
-      <c r="C35" s="81" t="inlineStr">
+      <c r="C35" s="233" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="67">
-      <c r="A36" s="126" t="n">
+    <row r="36" ht="15" customHeight="1" s="143">
+      <c r="A36" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="126" t="n">
+      <c r="B36" s="276" t="n">
         <v>19</v>
       </c>
-      <c r="C36" s="79" t="inlineStr">
+      <c r="C36" s="277" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="67">
-      <c r="A37" s="126" t="n">
+    <row r="37" ht="15" customHeight="1" s="143">
+      <c r="A37" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="126" t="n">
+      <c r="B37" s="276" t="n">
         <v>20</v>
       </c>
-      <c r="C37" s="79" t="inlineStr">
+      <c r="C37" s="277" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="67">
-      <c r="A38" s="126" t="n">
+    <row r="38" ht="15" customHeight="1" s="143">
+      <c r="A38" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="B38" s="126" t="n"/>
-      <c r="C38" s="79" t="inlineStr">
+      <c r="B38" s="276" t="n"/>
+      <c r="C38" s="277" t="inlineStr">
         <is>
           <t>(none)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="67">
-      <c r="A39" s="126" t="n">
+    <row r="39" ht="15" customHeight="1" s="143">
+      <c r="A39" s="276" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="126" t="n">
+      <c r="B39" s="276" t="n">
         <v>19</v>
       </c>
-      <c r="C39" s="79" t="inlineStr">
+      <c r="C39" s="277" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
     <row r="40"/>
-    <row r="41" ht="15" customHeight="1" s="67">
-      <c r="A41" s="71" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="143">
+      <c r="A41" s="231" t="inlineStr">
         <is>
           <t>Crossing convention used throughout:  spread bid = LegB bid - beta x LegA ask ; spread ask = LegB ask - beta x LegA bid ; spread mid = LegB mid - beta x LegA mid.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="67">
-      <c r="A42" s="71" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="143">
+      <c r="A42" s="231" t="inlineStr">
         <is>
           <t>For a LISTED slot LegA is empty and is treated as zero, so the listed quote passes straight through untouched.</t>
         </is>
@@ -5465,235 +6428,235 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="15" customWidth="1" style="66" min="1" max="2"/>
-    <col width="3" customWidth="1" style="66" min="3" max="3"/>
-    <col width="15" customWidth="1" style="66" min="4" max="5"/>
-    <col width="3" customWidth="1" style="66" min="6" max="6"/>
-    <col width="15" customWidth="1" style="66" min="7" max="8"/>
-    <col width="3" customWidth="1" style="66" min="9" max="9"/>
-    <col width="15" customWidth="1" style="66" min="10" max="11"/>
-    <col width="26" customWidth="1" style="66" min="13" max="13"/>
-    <col width="30" customWidth="1" style="66" min="14" max="14"/>
+    <col width="15" customWidth="1" style="141" min="1" max="2"/>
+    <col width="3" customWidth="1" style="141" min="3" max="3"/>
+    <col width="15" customWidth="1" style="141" min="4" max="5"/>
+    <col width="3" customWidth="1" style="141" min="6" max="6"/>
+    <col width="15" customWidth="1" style="141" min="7" max="8"/>
+    <col width="3" customWidth="1" style="141" min="9" max="9"/>
+    <col width="15" customWidth="1" style="141" min="10" max="11"/>
+    <col width="26" customWidth="1" style="141" min="13" max="13"/>
+    <col width="30" customWidth="1" style="141" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="67">
-      <c r="A1" s="127" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="143">
+      <c r="A1" s="278" t="inlineStr">
         <is>
           <t>BUFFER  -  hidden.  Flushed circular buffers (crash / restart recovery).</t>
         </is>
       </c>
-      <c r="M1" s="71" t="inlineStr">
+      <c r="M1" s="231" t="inlineStr">
         <is>
           <t>Written by VBA every FLUSH_SEC seconds, so a crash loses at most a minute.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="67">
-      <c r="M2" s="71" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="M2" s="231" t="inlineStr">
         <is>
           <t>On open, WarmStart reloads a slot only if its stamped LOOKBACK_MIN, HEDGE_RATIO and leg labels still match Config, and the newest sample is younger than WARM_START_MAX_AGE_MIN.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="67">
-      <c r="A3" s="92" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="143">
+      <c r="A3" s="275" t="inlineStr">
         <is>
           <t>SLOT 1</t>
         </is>
       </c>
-      <c r="D3" s="92" t="inlineStr">
+      <c r="D3" s="275" t="inlineStr">
         <is>
           <t>SLOT 2</t>
         </is>
       </c>
-      <c r="G3" s="92" t="inlineStr">
+      <c r="G3" s="275" t="inlineStr">
         <is>
           <t>SLOT 3</t>
         </is>
       </c>
-      <c r="J3" s="92" t="inlineStr">
+      <c r="J3" s="275" t="inlineStr">
         <is>
           <t>SLOT 4</t>
         </is>
       </c>
-      <c r="M3" s="71" t="inlineStr">
+      <c r="M3" s="231" t="inlineStr">
         <is>
           <t>Elapsed collection is credited from the OLDEST recovered sample - otherwise every restart costs another two hours before a usable z.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="67">
-      <c r="A4" s="125" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="143">
+      <c r="A4" s="274" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B4" s="124" t="n"/>
-      <c r="D4" s="125" t="inlineStr">
+      <c r="B4" s="273" t="n"/>
+      <c r="D4" s="274" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E4" s="124" t="n"/>
-      <c r="G4" s="125" t="inlineStr">
+      <c r="E4" s="273" t="n"/>
+      <c r="G4" s="274" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="H4" s="124" t="n"/>
-      <c r="J4" s="125" t="inlineStr">
+      <c r="H4" s="273" t="n"/>
+      <c r="J4" s="274" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K4" s="124" t="n"/>
-      <c r="M4" s="71" t="inlineStr">
+      <c r="K4" s="273" t="n"/>
+      <c r="M4" s="231" t="inlineStr">
         <is>
           <t>Seeding drops CONSECUTIVE identical values only. A spread genuinely revisiting a level is a real observation, not a duplicate.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="67">
-      <c r="A5" s="125" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="A5" s="274" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="B5" s="124" t="n"/>
-      <c r="D5" s="125" t="inlineStr">
+      <c r="B5" s="273" t="n"/>
+      <c r="D5" s="274" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="E5" s="124" t="n"/>
-      <c r="G5" s="125" t="inlineStr">
+      <c r="E5" s="273" t="n"/>
+      <c r="G5" s="274" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="H5" s="124" t="n"/>
-      <c r="J5" s="125" t="inlineStr">
+      <c r="H5" s="273" t="n"/>
+      <c r="J5" s="274" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="K5" s="124" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="67">
-      <c r="A6" s="125" t="inlineStr">
+      <c r="K5" s="273" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="143">
+      <c r="A6" s="274" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="B6" s="124" t="n"/>
-      <c r="D6" s="125" t="inlineStr">
+      <c r="B6" s="273" t="n"/>
+      <c r="D6" s="274" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="E6" s="124" t="n"/>
-      <c r="G6" s="125" t="inlineStr">
+      <c r="E6" s="273" t="n"/>
+      <c r="G6" s="274" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="H6" s="124" t="n"/>
-      <c r="J6" s="125" t="inlineStr">
+      <c r="H6" s="273" t="n"/>
+      <c r="J6" s="274" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="K6" s="124" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="67">
-      <c r="A7" s="125" t="inlineStr">
+      <c r="K6" s="273" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="143">
+      <c r="A7" s="274" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="B7" s="124" t="n"/>
-      <c r="D7" s="125" t="inlineStr">
+      <c r="B7" s="273" t="n"/>
+      <c r="D7" s="274" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="E7" s="124" t="n"/>
-      <c r="G7" s="125" t="inlineStr">
+      <c r="E7" s="273" t="n"/>
+      <c r="G7" s="274" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="H7" s="124" t="n"/>
-      <c r="J7" s="125" t="inlineStr">
+      <c r="H7" s="273" t="n"/>
+      <c r="J7" s="274" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="K7" s="124" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="67">
-      <c r="A8" s="125" t="inlineStr">
+      <c r="K7" s="273" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="143">
+      <c r="A8" s="274" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="B8" s="124" t="n"/>
-      <c r="D8" s="125" t="inlineStr">
+      <c r="B8" s="273" t="n"/>
+      <c r="D8" s="274" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="E8" s="124" t="n"/>
-      <c r="G8" s="125" t="inlineStr">
+      <c r="E8" s="273" t="n"/>
+      <c r="G8" s="274" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="H8" s="124" t="n"/>
-      <c r="J8" s="125" t="inlineStr">
+      <c r="H8" s="273" t="n"/>
+      <c r="J8" s="274" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="K8" s="124" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="67">
-      <c r="A9" s="81" t="inlineStr">
+      <c r="K8" s="273" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="A9" s="233" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="B9" s="81" t="inlineStr">
+      <c r="B9" s="233" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="D9" s="81" t="inlineStr">
+      <c r="D9" s="233" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="E9" s="81" t="inlineStr">
+      <c r="E9" s="233" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="G9" s="81" t="inlineStr">
+      <c r="G9" s="233" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="H9" s="81" t="inlineStr">
+      <c r="H9" s="233" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="J9" s="81" t="inlineStr">
+      <c r="J9" s="233" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="K9" s="81" t="inlineStr">
+      <c r="K9" s="233" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
@@ -5715,87 +6678,87 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="20" customWidth="1" style="66" min="1" max="1"/>
-    <col width="30" customWidth="1" style="66" min="2" max="2"/>
-    <col width="20" customWidth="1" style="66" min="3" max="3"/>
-    <col width="9" customWidth="1" style="66" min="4" max="4"/>
-    <col width="12" customWidth="1" style="66" min="5" max="9"/>
-    <col width="16" customWidth="1" style="66" min="10" max="10"/>
-    <col width="10" customWidth="1" style="66" min="11" max="11"/>
-    <col width="60" customWidth="1" style="66" min="12" max="12"/>
+    <col width="20" customWidth="1" style="141" min="1" max="1"/>
+    <col width="30" customWidth="1" style="141" min="2" max="2"/>
+    <col width="20" customWidth="1" style="141" min="3" max="3"/>
+    <col width="9" customWidth="1" style="141" min="4" max="4"/>
+    <col width="12" customWidth="1" style="141" min="5" max="9"/>
+    <col width="16" customWidth="1" style="141" min="10" max="10"/>
+    <col width="10" customWidth="1" style="141" min="11" max="11"/>
+    <col width="60" customWidth="1" style="141" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="67">
-      <c r="A1" s="127" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="143">
+      <c r="A1" s="278" t="inlineStr">
         <is>
           <t>LOG  -  timestamped signal events</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="67">
-      <c r="A2" s="71" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="A2" s="231" t="inlineStr">
         <is>
           <t>One line when a state STARTS and one when it CLEARS - never one per poll. Reviewable after the session.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="67">
-      <c r="A3" s="81" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="143">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B3" s="81" t="inlineStr">
+      <c r="B3" s="233" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C3" s="81" t="inlineStr">
+      <c r="C3" s="233" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D3" s="81" t="inlineStr">
+      <c r="D3" s="233" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E3" s="81" t="inlineStr">
+      <c r="E3" s="233" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="F3" s="81" t="inlineStr">
+      <c r="F3" s="233" t="inlineStr">
         <is>
           <t>Sigma</t>
         </is>
       </c>
-      <c r="G3" s="81" t="inlineStr">
+      <c r="G3" s="233" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="H3" s="81" t="inlineStr">
+      <c r="H3" s="233" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I3" s="81" t="inlineStr">
+      <c r="I3" s="233" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J3" s="81" t="inlineStr">
+      <c r="J3" s="233" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="K3" s="81" t="inlineStr">
+      <c r="K3" s="233" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="L3" s="81" t="inlineStr">
+      <c r="L3" s="233" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -5817,307 +6780,307 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="4" customWidth="1" style="66" min="1" max="1"/>
-    <col width="46" customWidth="1" style="66" min="2" max="2"/>
-    <col width="16" customWidth="1" style="66" min="3" max="6"/>
-    <col width="60" customWidth="1" style="66" min="7" max="7"/>
+    <col width="4" customWidth="1" style="141" min="1" max="1"/>
+    <col width="46" customWidth="1" style="141" min="2" max="2"/>
+    <col width="16" customWidth="1" style="141" min="3" max="6"/>
+    <col width="60" customWidth="1" style="141" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.7" customHeight="1" s="67">
-      <c r="B1" s="68" t="inlineStr">
+    <row r="1" ht="19.7" customHeight="1" s="143">
+      <c r="B1" s="254" t="inlineStr">
         <is>
           <t>SETUP  -  turning this .xlsx into the working .xlsm</t>
         </is>
       </c>
     </row>
     <row r="2"/>
-    <row r="3" ht="30" customHeight="1" s="67">
-      <c r="B3" s="128" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="143">
+      <c r="B3" s="279" t="inlineStr">
         <is>
           <t>openpyxl cannot author VBA, so this file ships as an .xlsx carrying all structure and formatting, plus a .bas module to import. Six steps, once.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="67">
-      <c r="B4" s="129" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="143">
+      <c r="B4" s="280" t="inlineStr">
         <is>
           <t>1.  Open TT_ZScore_Monitor.xlsx in Excel on the machine running TT and the TT RTD server.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="67">
-      <c r="B5" s="129" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="B5" s="280" t="inlineStr">
         <is>
           <t>2.  File &gt; Save As &gt; Excel Macro-Enabled Workbook (.xlsm). Keep the same folder.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="67">
-      <c r="B6" s="129" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="143">
+      <c r="B6" s="280" t="inlineStr">
         <is>
           <t>3.  Alt+F11 to open the VBA editor.  File &gt; Import File...  and choose TTZMonitor.bas.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="67">
-      <c r="B7" s="129" t="inlineStr">
+    <row r="7" ht="30" customHeight="1" s="143">
+      <c r="B7" s="280" t="inlineStr">
         <is>
           <t>4.  In the editor, double-click ThisWorkbook and paste the two-line Workbook_Open / Workbook_BeforeClose stub printed at the bottom of TTZMonitor.bas.  (Optional - it just auto-starts the monitor and warm-starts the buffers.)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="67">
-      <c r="B8" s="129" t="inlineStr">
+    <row r="8" ht="30" customHeight="1" s="143">
+      <c r="B8" s="280" t="inlineStr">
         <is>
           <t>5.  Back on Dashboard, insert two shapes over cells N2 and P2 (Insert &gt; Shapes &gt; Rectangle), right-click each &gt; Assign Macro &gt; StartMonitor and StopMonitor. Until you do, run them from Alt+F8.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="67">
-      <c r="B9" s="129" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="B9" s="280" t="inlineStr">
         <is>
           <t>6.  Save. Click START. The Feed sheet stays hidden; you never need to look at it.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="67">
-      <c r="B10" s="128" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="143">
+      <c r="B10" s="279" t="inlineStr">
         <is>
           <t>Step 4 is NOT optional here. The capture timer is a Windows user32 timer, and one that outlives the workbook keeps firing into a module that no longer has its sheets - which crashes Excel. Workbook_BeforeClose calls StopMonitor and kills it.</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="15" customHeight="1" s="67">
-      <c r="B12" s="80" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="143">
+      <c r="B12" s="232" t="inlineStr">
         <is>
           <t>WHAT TO CHECK ON THE FIRST RUN</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="25.5" customHeight="1" s="67">
-      <c r="B13" s="130" t="inlineStr">
+    <row r="13" ht="25.5" customHeight="1" s="143">
+      <c r="B13" s="281" t="inlineStr">
         <is>
           <t>-  Feed sheet column B (instrument ids) fills in. If it stays blank, the TT short name in Feed column A does not match TT, or the market in Dashboard!C4 is wrong.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="25.5" customHeight="1" s="67">
-      <c r="B14" s="130" t="inlineStr">
+    <row r="14" ht="25.5" customHeight="1" s="143">
+      <c r="B14" s="281" t="inlineStr">
         <is>
           <t>-  Dashboard prices move, but the sheet does NOT flash. If it flashes, something volatile has been reintroduced - search the workbook for NOW, TODAY, OFFSET, INDIRECT, RAND.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="25.5" customHeight="1" s="67">
-      <c r="B15" s="130" t="inlineStr">
+    <row r="15" ht="25.5" customHeight="1" s="143">
+      <c r="B15" s="281" t="inlineStr">
         <is>
           <t>-  The samples counter climbs at roughly the quotes/min rate, not at the timer rate. If it climbs at the timer rate, dedupe is not working and every z you see will be fiction.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="25.5" customHeight="1" s="67">
-      <c r="B16" s="130" t="inlineStr">
+    <row r="16" ht="25.5" customHeight="1" s="143">
+      <c r="B16" s="281" t="inlineStr">
         <is>
           <t>-  Warm-up takes MIN_HISTORY_MIN (default 120) minutes on a cold start. That is deliberate.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="25.5" customHeight="1" s="67">
-      <c r="B17" s="130" t="inlineStr">
+    <row r="17" ht="25.5" customHeight="1" s="143">
+      <c r="B17" s="281" t="inlineStr">
         <is>
           <t>-  A 'ticks' folder appears beside the workbook, one CSV per spread per day, holding every changed quote. That is the raw record - keep it for the first week or two.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="25.5" customHeight="1" s="67">
-      <c r="B18" s="130" t="inlineStr">
+    <row r="18" ht="25.5" customHeight="1" s="143">
+      <c r="B18" s="281" t="inlineStr">
         <is>
           <t>-  After a week, run Alt+F8 &gt; CheckSubsamplingLoss. It compares mean and sigma over the live window at full fidelity against 250 / 500 / 1000 / 2000 / 5000 ms subsampling and writes the comparison to the Log. If sigma is materially unchanged, set STORE_MIN_INTERVAL_MS and reclaim the memory.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20" ht="15" customHeight="1" s="67">
-      <c r="B20" s="80" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="143">
+      <c r="B20" s="232" t="inlineStr">
         <is>
           <t>WHAT SIGMA THIS SPREAD MUST HAVE TO BE WORTH TRADING</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="67">
-      <c r="B21" s="71" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="143">
+      <c r="B21" s="231" t="inlineStr">
         <is>
           <t>Live off Config. Edit the two assumed market widths below; everything else follows.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="67">
-      <c r="B22" s="116" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="143">
+      <c r="B22" s="264" t="inlineStr">
         <is>
           <t>Assumed width, each outright leg (spread units)</t>
         </is>
       </c>
-      <c r="C22" s="117" t="n">
+      <c r="C22" s="265" t="n">
         <v>0.02</v>
       </c>
-      <c r="E22" s="116" t="inlineStr">
+      <c r="E22" s="264" t="inlineStr">
         <is>
           <t>Assumed width, listed spread (spread units)</t>
         </is>
       </c>
-      <c r="F22" s="117" t="n">
+      <c r="F22" s="265" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="22.35" customHeight="1" s="67">
-      <c r="B24" s="81" t="inlineStr">
+    <row r="24" ht="22.35" customHeight="1" s="143">
+      <c r="B24" s="233" t="inlineStr">
         <is>
           <t>At LOTS from Config, per leg</t>
         </is>
       </c>
-      <c r="C24" s="81" t="inlineStr">
+      <c r="C24" s="233" t="inlineStr">
         <is>
           <t>Total cost</t>
         </is>
       </c>
-      <c r="D24" s="81" t="inlineStr">
+      <c r="D24" s="233" t="inlineStr">
         <is>
           <t>min sigma @ z = 3.0</t>
         </is>
       </c>
-      <c r="E24" s="81" t="inlineStr">
+      <c r="E24" s="233" t="inlineStr">
         <is>
           <t>min sigma @ z = 2.5</t>
         </is>
       </c>
-      <c r="F24" s="81" t="inlineStr">
+      <c r="F24" s="233" t="inlineStr">
         <is>
           <t>min sigma @ live ENTRY_Z</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="67">
-      <c r="B25" s="73" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="B25" s="270" t="inlineStr">
         <is>
           <t>Legging the outrights</t>
         </is>
       </c>
-      <c r="C25" s="131">
-        <f>2*Config!$B$72*Config!$B$40+(2*$C$22)*1000*Config!$B$40</f>
-        <v/>
-      </c>
-      <c r="D25" s="132">
-        <f>Config!$B$45*$C$25/(0.5*3*1000*Config!$B$40)</f>
-        <v/>
-      </c>
-      <c r="E25" s="132">
-        <f>Config!$B$45*$C$25/(0.5*2.5*1000*Config!$B$40)</f>
-        <v/>
-      </c>
-      <c r="F25" s="132">
-        <f>Config!$B$45*$C$25/(0.5*Config!$B$34*1000*Config!$B$40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="67">
-      <c r="B26" s="73" t="inlineStr">
+      <c r="C25" s="282">
+        <f>2*Config!$B$73*Config!$B$41+(2*$C$22)*1000*Config!$B$41</f>
+        <v/>
+      </c>
+      <c r="D25" s="283">
+        <f>Config!$B$46*$C$25/(0.5*3*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+      <c r="E25" s="283">
+        <f>Config!$B$46*$C$25/(0.5*2.5*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+      <c r="F25" s="283">
+        <f>Config!$B$46*$C$25/(0.5*Config!$B$34*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="143">
+      <c r="B26" s="270" t="inlineStr">
         <is>
           <t>Listed inter-product spread</t>
         </is>
       </c>
-      <c r="C26" s="131">
-        <f>2*Config!$B$72*Config!$B$40+$F$22*1000*Config!$B$40</f>
-        <v/>
-      </c>
-      <c r="D26" s="132">
-        <f>Config!$B$45*$C$26/(0.5*3*1000*Config!$B$40)</f>
-        <v/>
-      </c>
-      <c r="E26" s="132">
-        <f>Config!$B$45*$C$26/(0.5*2.5*1000*Config!$B$40)</f>
-        <v/>
-      </c>
-      <c r="F26" s="132">
-        <f>Config!$B$45*$C$26/(0.5*Config!$B$34*1000*Config!$B$40)</f>
+      <c r="C26" s="282">
+        <f>2*Config!$B$73*Config!$B$41+$F$22*1000*Config!$B$41</f>
+        <v/>
+      </c>
+      <c r="D26" s="283">
+        <f>Config!$B$46*$C$26/(0.5*3*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+      <c r="E26" s="283">
+        <f>Config!$B$46*$C$26/(0.5*2.5*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+      <c r="F26" s="283">
+        <f>Config!$B$46*$C$26/(0.5*Config!$B$34*1000*Config!$B$41)</f>
         <v/>
       </c>
     </row>
     <row r="27"/>
-    <row r="28" ht="15" customHeight="1" s="67">
-      <c r="B28" s="71" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="B28" s="231" t="inlineStr">
         <is>
           <t>capture = 0.5 x |z| x sigma x USD-per-point x LOTS.  An entry passes when capture &gt;= EDGE_MULTIPLE x total cost.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="67">
-      <c r="B29" s="107" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="143">
+      <c r="B29" s="253" t="inlineStr">
         <is>
           <t>A lower ENTRY_Z means less expected capture per entry, so it RAISES the sigma the spread must have. 2.5 instead of 3.0 raises it by about 20%.</t>
         </is>
       </c>
     </row>
     <row r="30"/>
-    <row r="31" ht="15" customHeight="1" s="67">
-      <c r="B31" s="80" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="143">
+      <c r="B31" s="232" t="inlineStr">
         <is>
           <t>ASSUMPTIONS MADE WHILE BUILDING THIS - CHECK THEM</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="39.75" customHeight="1" s="67">
-      <c r="B32" s="130" t="inlineStr">
+    <row r="32" ht="39.75" customHeight="1" s="143">
+      <c r="B32" s="281" t="inlineStr">
         <is>
           <t>-  The repository was empty, so the existing Dashboard layout was reconstructed from the cell references given in the spec (C4, B6, C7, H7/H8, P7/P8, H12/H13/H14/I14, L3). Those coordinates are honoured exactly; the surrounding rows are a best reconstruction. Compare against your live sheet before relying on it.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="39.75" customHeight="1" s="67">
-      <c r="B33" s="130" t="inlineStr">
+    <row r="33" ht="39.75" customHeight="1" s="143">
+      <c r="B33" s="281" t="inlineStr">
         <is>
           <t>-  The 3:2:1 ask row now mirrors the bid row: I15 uses H14 (CL BID), not I14. The bid row is unchanged. This is the convention the spec described; confirm it is the one you want.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="39.75" customHeight="1" s="67">
-      <c r="B34" s="130" t="inlineStr">
+    <row r="34" ht="39.75" customHeight="1" s="143">
+      <c r="B34" s="281" t="inlineStr">
         <is>
           <t>-  COMMISSION_BASIS defaults to CONSERVATIVE ($3.82 per lot per leg round turn, reading CME's $1.50 as per side). Switch it to CME_PER_RT on Config if the rate card proves otherwise.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="39.75" customHeight="1" s="67">
-      <c r="B35" s="130" t="inlineStr">
+    <row r="35" ht="39.75" customHeight="1" s="143">
+      <c r="B35" s="281" t="inlineStr">
         <is>
           <t>-  Contracts charged commission: 2 for BZ-CL and the listed spread, 6 for the 3:2:1 crack (2 RB + 1 HO + 3 CL). Change it in the Config spread table if your clearing differs.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="39.75" customHeight="1" s="67">
-      <c r="B36" s="130" t="inlineStr">
+    <row r="36" ht="39.75" customHeight="1" s="143">
+      <c r="B36" s="281" t="inlineStr">
         <is>
           <t>-  Slot 3 (3:2:1) has no exchange-listed equivalent, so its LISTED crossing-cost column reads n/a.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="39.75" customHeight="1" s="67">
-      <c r="B37" s="130" t="inlineStr">
+    <row r="37" ht="39.75" customHeight="1" s="143">
+      <c r="B37" s="281" t="inlineStr">
         <is>
           <t>-  MIN_SIGMA ships at 0 because sigma on these spreads has never been measured. Set it once you have a session of data - until then the degenerate-window guard rests on MAX_ABS_Z alone.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="39.75" customHeight="1" s="67">
-      <c r="B38" s="130" t="inlineStr">
+    <row r="38" ht="39.75" customHeight="1" s="143">
+      <c r="B38" s="281" t="inlineStr">
         <is>
           <t>-  Application.OnTime cannot go below about one second, so capture at 100 ms runs on a user32 SetTimer with an OnTime watchdog that re-arms it (Excel silently kills API timers when a modal dialog opens). If SetTimer is unavailable, CAPTURE_MS is clamped to 1000 and everything still works - only alert latency changes, not the statistics.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="39.75" customHeight="1" s="67">
-      <c r="B39" s="130" t="inlineStr">
+    <row r="39" ht="39.75" customHeight="1" s="143">
+      <c r="B39" s="281" t="inlineStr">
         <is>
           <t>-  Capturing at 100 ms does not mean storing at 100 ms, and after dedupe it does not change sigma either. The window holds quote CHANGES, not poll ticks; subsampling a mean-reverting level series is unbiased. 100 ms buys latency to the chime, which for manual execution is not measurable in human terms - so the real reason to capture fast is simply that no genuine quote change is missed.</t>
         </is>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -601,7 +601,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="284">
+  <cellXfs count="286">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -858,6 +858,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="33" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1284,6 +1287,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="33" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1820,840 +1826,845 @@
   <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col hidden="1" width="2.14" customWidth="1" style="141" min="1" max="1"/>
-    <col hidden="1" width="11" customWidth="1" style="141" min="2" max="2"/>
-    <col hidden="1" width="30.43" customWidth="1" style="141" min="3" max="3"/>
-    <col width="3.43" customWidth="1" style="141" min="4" max="5"/>
-    <col width="16.14" customWidth="1" style="142" min="6" max="6"/>
-    <col hidden="1" width="30.57" customWidth="1" style="141" min="7" max="7"/>
-    <col width="17" customWidth="1" style="141" min="8" max="10"/>
-    <col width="17.43" customWidth="1" style="141" min="11" max="12"/>
-    <col width="2" customWidth="1" style="141" min="13" max="13"/>
-    <col width="17.57" customWidth="1" style="141" min="14" max="14"/>
-    <col hidden="1" width="16.72" customWidth="1" style="141" min="15" max="15"/>
-    <col width="18.29" customWidth="1" style="141" min="16" max="18"/>
-    <col width="16.43" customWidth="1" style="141" min="19" max="20"/>
-    <col width="17.29" customWidth="1" style="141" min="24" max="24"/>
-    <col width="14.29" customWidth="1" style="141" min="25" max="26"/>
-    <col width="11.43" customWidth="1" style="141" min="27" max="27"/>
+    <col hidden="1" width="2.14" customWidth="1" style="142" min="1" max="1"/>
+    <col hidden="1" width="11" customWidth="1" style="142" min="2" max="2"/>
+    <col hidden="1" width="30.43" customWidth="1" style="142" min="3" max="3"/>
+    <col width="3.43" customWidth="1" style="142" min="4" max="5"/>
+    <col width="16.14" customWidth="1" style="143" min="6" max="6"/>
+    <col hidden="1" width="30.57" customWidth="1" style="142" min="7" max="7"/>
+    <col width="17" customWidth="1" style="142" min="8" max="10"/>
+    <col width="17.43" customWidth="1" style="142" min="11" max="12"/>
+    <col width="2" customWidth="1" style="142" min="13" max="13"/>
+    <col width="17.57" customWidth="1" style="142" min="14" max="14"/>
+    <col hidden="1" width="16.72" customWidth="1" style="142" min="15" max="15"/>
+    <col width="18.29" customWidth="1" style="142" min="16" max="18"/>
+    <col width="16.43" customWidth="1" style="142" min="19" max="20"/>
+    <col width="17.29" customWidth="1" style="142" min="24" max="24"/>
+    <col width="14.29" customWidth="1" style="142" min="25" max="26"/>
+    <col width="11.43" customWidth="1" style="142" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2" ht="68.25" customHeight="1" s="143">
-      <c r="A2" s="144" t="n"/>
-      <c r="B2" s="145" t="n"/>
-      <c r="C2" s="146" t="inlineStr">
+    <row r="2" ht="68.25" customHeight="1" s="144">
+      <c r="A2" s="145" t="n"/>
+      <c r="B2" s="146" t="n"/>
+      <c r="C2" s="147" t="inlineStr">
         <is>
           <t>ENERGY FUTURES BID / ASK SPREAD MONITOR</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="143">
-      <c r="A3" s="144" t="n"/>
-      <c r="B3" s="147" t="n"/>
-      <c r="C3" s="148" t="n"/>
-      <c r="F3" s="149" t="n"/>
-      <c r="G3" s="150" t="n"/>
-      <c r="L3" s="151" t="n"/>
-    </row>
-    <row r="4" ht="6.75" customHeight="1" s="143">
-      <c r="A4" s="144" t="n"/>
-      <c r="B4" s="152" t="inlineStr">
+    <row r="3" ht="21.75" customHeight="1" s="144">
+      <c r="A3" s="145" t="n"/>
+      <c r="B3" s="148" t="n"/>
+      <c r="C3" s="149" t="n"/>
+      <c r="F3" s="150" t="n"/>
+      <c r="G3" s="151" t="n"/>
+      <c r="L3" s="152" t="n"/>
+    </row>
+    <row r="4" ht="6.75" customHeight="1" s="144">
+      <c r="A4" s="145" t="n"/>
+      <c r="B4" s="153" t="inlineStr">
         <is>
           <t>TT MARKET</t>
         </is>
       </c>
-      <c r="C4" s="152" t="inlineStr">
+      <c r="C4" s="153" t="inlineStr">
         <is>
           <t>CME</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="6.75" customHeight="1" s="143">
-      <c r="A5" s="144" t="n"/>
-      <c r="B5" s="153" t="inlineStr">
+    <row r="5" ht="6.75" customHeight="1" s="144">
+      <c r="A5" s="145" t="n"/>
+      <c r="B5" s="154" t="inlineStr">
         <is>
           <t>TT SHORT NAME</t>
         </is>
       </c>
-      <c r="C5" s="153" t="inlineStr">
+      <c r="C5" s="154" t="inlineStr">
         <is>
           <t>INSTRUMENT ID</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="23.25" customHeight="1" s="143">
-      <c r="A6" s="144" t="n"/>
-      <c r="B6" s="152" t="inlineStr">
+    <row r="6" ht="23.25" customHeight="1" s="144">
+      <c r="A6" s="145" t="n"/>
+      <c r="B6" s="153" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="C6" s="154" t="n"/>
-      <c r="F6" s="155" t="inlineStr">
+      <c r="C6" s="155" t="n"/>
+      <c r="F6" s="156" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="G6" s="156" t="inlineStr">
+      <c r="G6" s="157" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H6" s="156" t="inlineStr">
+      <c r="H6" s="157" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I6" s="156" t="inlineStr">
+      <c r="I6" s="157" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J6" s="156" t="inlineStr">
+      <c r="J6" s="157" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="K6" s="156" t="inlineStr">
+      <c r="K6" s="157" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L6" s="157" t="inlineStr">
+      <c r="L6" s="158" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M6" s="158" t="n"/>
-      <c r="N6" s="155" t="inlineStr">
+      <c r="M6" s="159" t="n"/>
+      <c r="N6" s="156" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="O6" s="156" t="inlineStr">
+      <c r="O6" s="157" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="P6" s="156" t="inlineStr">
+      <c r="P6" s="157" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="Q6" s="156" t="inlineStr">
+      <c r="Q6" s="157" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="R6" s="156" t="inlineStr">
+      <c r="R6" s="157" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="S6" s="156" t="inlineStr">
+      <c r="S6" s="157" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T6" s="157" t="inlineStr">
+      <c r="T6" s="158" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U6" s="159" t="n"/>
-      <c r="V6" s="159" t="n"/>
-    </row>
-    <row r="7" ht="55.5" customHeight="1" s="143">
-      <c r="A7" s="144" t="n"/>
-      <c r="B7" s="152" t="inlineStr">
+      <c r="U6" s="160" t="n"/>
+      <c r="V6" s="160" t="n"/>
+    </row>
+    <row r="7" ht="55.5" customHeight="1" s="144">
+      <c r="A7" s="145" t="n"/>
+      <c r="B7" s="153" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="C7" s="154" t="n"/>
-      <c r="D7" s="160" t="n"/>
-      <c r="E7" s="160" t="n"/>
-      <c r="F7" s="161" t="inlineStr">
+      <c r="C7" s="155" t="n"/>
+      <c r="D7" s="161" t="n"/>
+      <c r="E7" s="161" t="n"/>
+      <c r="F7" s="162" t="inlineStr">
         <is>
           <t>HOV26
 HO Oct 26</t>
         </is>
       </c>
-      <c r="G7" s="162" t="inlineStr">
+      <c r="G7" s="163" t="inlineStr">
         <is>
           <t>HO Oct 26</t>
         </is>
       </c>
-      <c r="H7" s="163" t="n"/>
-      <c r="I7" s="164" t="n"/>
-      <c r="J7" s="165" t="n"/>
-      <c r="K7" s="166" t="n"/>
-      <c r="L7" s="167" t="n"/>
-      <c r="M7" s="168" t="n"/>
-      <c r="N7" s="161" t="inlineStr">
+      <c r="H7" s="164" t="n"/>
+      <c r="I7" s="165" t="n"/>
+      <c r="J7" s="166" t="n"/>
+      <c r="K7" s="167" t="n"/>
+      <c r="L7" s="168" t="n"/>
+      <c r="M7" s="169" t="n"/>
+      <c r="N7" s="162" t="inlineStr">
         <is>
           <t>BZV26
 BZ Oct 26</t>
         </is>
       </c>
-      <c r="O7" s="162" t="inlineStr">
+      <c r="O7" s="163" t="inlineStr">
         <is>
           <t>BZ Oct 26</t>
         </is>
       </c>
-      <c r="P7" s="163" t="n"/>
-      <c r="Q7" s="163" t="n"/>
-      <c r="R7" s="169" t="n"/>
-      <c r="S7" s="166" t="n"/>
-      <c r="T7" s="167" t="n"/>
-      <c r="U7" s="159" t="n"/>
-      <c r="V7" s="159" t="n"/>
-    </row>
-    <row r="8" ht="55.5" customHeight="1" s="143">
-      <c r="A8" s="144" t="n"/>
-      <c r="B8" s="152" t="inlineStr">
+      <c r="P7" s="164" t="n"/>
+      <c r="Q7" s="164" t="n"/>
+      <c r="R7" s="170" t="n"/>
+      <c r="S7" s="167" t="n"/>
+      <c r="T7" s="168" t="n"/>
+      <c r="U7" s="160" t="n"/>
+      <c r="V7" s="160" t="n"/>
+    </row>
+    <row r="8" ht="55.5" customHeight="1" s="144">
+      <c r="A8" s="145" t="n"/>
+      <c r="B8" s="153" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="C8" s="154" t="n"/>
-      <c r="D8" s="160" t="n"/>
-      <c r="E8" s="160" t="n"/>
-      <c r="F8" s="170" t="inlineStr">
+      <c r="C8" s="155" t="n"/>
+      <c r="D8" s="161" t="n"/>
+      <c r="E8" s="161" t="n"/>
+      <c r="F8" s="171" t="inlineStr">
         <is>
           <t>CLV26
 CL Oct 26</t>
         </is>
       </c>
-      <c r="G8" s="171" t="inlineStr">
+      <c r="G8" s="172" t="inlineStr">
         <is>
           <t>CL Oct 26</t>
         </is>
       </c>
-      <c r="H8" s="172" t="n"/>
-      <c r="I8" s="172" t="n"/>
-      <c r="J8" s="173" t="n"/>
-      <c r="K8" s="174" t="n"/>
-      <c r="L8" s="175" t="n"/>
-      <c r="M8" s="168" t="n"/>
-      <c r="N8" s="170" t="inlineStr">
+      <c r="H8" s="173" t="n"/>
+      <c r="I8" s="173" t="n"/>
+      <c r="J8" s="174" t="n"/>
+      <c r="K8" s="175" t="n"/>
+      <c r="L8" s="176" t="n"/>
+      <c r="M8" s="169" t="n"/>
+      <c r="N8" s="171" t="inlineStr">
         <is>
           <t>CLV26
 CL Oct 26</t>
         </is>
       </c>
-      <c r="O8" s="171" t="inlineStr">
+      <c r="O8" s="172" t="inlineStr">
         <is>
           <t>CL Oct 26</t>
         </is>
       </c>
-      <c r="P8" s="172" t="n"/>
-      <c r="Q8" s="172" t="n"/>
-      <c r="R8" s="173" t="n"/>
-      <c r="S8" s="174" t="n"/>
-      <c r="T8" s="175" t="n"/>
-      <c r="U8" s="159" t="n"/>
-      <c r="V8" s="159" t="n"/>
-    </row>
-    <row r="9" ht="55.5" customHeight="1" s="143">
-      <c r="A9" s="144" t="n"/>
-      <c r="B9" s="152" t="inlineStr">
+      <c r="P8" s="173" t="n"/>
+      <c r="Q8" s="173" t="n"/>
+      <c r="R8" s="174" t="n"/>
+      <c r="S8" s="175" t="n"/>
+      <c r="T8" s="176" t="n"/>
+      <c r="U8" s="160" t="n"/>
+      <c r="V8" s="160" t="n"/>
+    </row>
+    <row r="9" ht="55.5" customHeight="1" s="144">
+      <c r="A9" s="145" t="n"/>
+      <c r="B9" s="153" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="C9" s="154" t="n"/>
-      <c r="D9" s="160" t="n"/>
-      <c r="E9" s="160" t="n"/>
-      <c r="F9" s="176" t="inlineStr">
+      <c r="C9" s="155" t="n"/>
+      <c r="D9" s="161" t="n"/>
+      <c r="E9" s="161" t="n"/>
+      <c r="F9" s="177" t="inlineStr">
         <is>
           <t>HO | CL Oct 26 Crack</t>
         </is>
       </c>
-      <c r="G9" s="177" t="n"/>
-      <c r="H9" s="178" t="n"/>
-      <c r="I9" s="178" t="n"/>
-      <c r="J9" s="179" t="n"/>
-      <c r="K9" s="178" t="n"/>
-      <c r="L9" s="180" t="n"/>
-      <c r="M9" s="168" t="n"/>
-      <c r="N9" s="181" t="inlineStr">
+      <c r="G9" s="178" t="n"/>
+      <c r="H9" s="179" t="n"/>
+      <c r="I9" s="179" t="n"/>
+      <c r="J9" s="180" t="n"/>
+      <c r="K9" s="179" t="n"/>
+      <c r="L9" s="181" t="n"/>
+      <c r="M9" s="169" t="n"/>
+      <c r="N9" s="182" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="O9" s="182" t="n"/>
-      <c r="P9" s="178" t="n"/>
-      <c r="Q9" s="178" t="n"/>
-      <c r="R9" s="179" t="n"/>
-      <c r="S9" s="178" t="n"/>
-      <c r="T9" s="180" t="n"/>
-      <c r="U9" s="159" t="n"/>
-      <c r="V9" s="159" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="143">
-      <c r="A10" s="144" t="n"/>
-      <c r="B10" s="183" t="inlineStr">
+      <c r="O9" s="183" t="n"/>
+      <c r="P9" s="179" t="n"/>
+      <c r="Q9" s="179" t="n"/>
+      <c r="R9" s="180" t="n"/>
+      <c r="S9" s="179" t="n"/>
+      <c r="T9" s="181" t="n"/>
+      <c r="U9" s="160" t="n"/>
+      <c r="V9" s="160" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="144">
+      <c r="A10" s="145" t="n"/>
+      <c r="B10" s="184" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="C10" s="154" t="n"/>
-      <c r="D10" s="160" t="n"/>
-      <c r="E10" s="160" t="n"/>
-      <c r="F10" s="168" t="n"/>
-      <c r="G10" s="168" t="n"/>
-      <c r="H10" s="168" t="n"/>
-      <c r="I10" s="168" t="n"/>
-      <c r="J10" s="168" t="n"/>
-      <c r="K10" s="168" t="n"/>
-      <c r="L10" s="168" t="n"/>
-      <c r="M10" s="168" t="n"/>
-      <c r="N10" s="159" t="n"/>
-      <c r="O10" s="159" t="n"/>
-      <c r="P10" s="159" t="n"/>
-      <c r="Q10" s="159" t="n"/>
-      <c r="R10" s="159" t="n"/>
-      <c r="S10" s="159" t="n"/>
-      <c r="T10" s="159" t="n"/>
-      <c r="U10" s="159" t="n"/>
-      <c r="V10" s="159" t="n"/>
-    </row>
-    <row r="11" ht="42" customHeight="1" s="143">
-      <c r="A11" s="144" t="n"/>
-      <c r="B11" s="183" t="n"/>
-      <c r="C11" s="154" t="n"/>
-      <c r="D11" s="160" t="n"/>
-      <c r="E11" s="160" t="n"/>
-      <c r="F11" s="155" t="inlineStr">
+      <c r="C10" s="155" t="n"/>
+      <c r="D10" s="161" t="n"/>
+      <c r="E10" s="161" t="n"/>
+      <c r="F10" s="169" t="n"/>
+      <c r="G10" s="169" t="n"/>
+      <c r="H10" s="169" t="n"/>
+      <c r="I10" s="169" t="n"/>
+      <c r="J10" s="169" t="n"/>
+      <c r="K10" s="169" t="n"/>
+      <c r="L10" s="169" t="n"/>
+      <c r="M10" s="169" t="n"/>
+      <c r="N10" s="160" t="n"/>
+      <c r="O10" s="160" t="n"/>
+      <c r="P10" s="160" t="n"/>
+      <c r="Q10" s="160" t="n"/>
+      <c r="R10" s="160" t="n"/>
+      <c r="S10" s="160" t="n"/>
+      <c r="T10" s="160" t="n"/>
+      <c r="U10" s="160" t="n"/>
+      <c r="V10" s="160" t="n"/>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="144">
+      <c r="A11" s="145" t="n"/>
+      <c r="B11" s="184" t="n"/>
+      <c r="C11" s="155" t="n"/>
+      <c r="D11" s="161" t="n"/>
+      <c r="E11" s="161" t="n"/>
+      <c r="F11" s="156" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="G11" s="156" t="inlineStr">
+      <c r="G11" s="157" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H11" s="156" t="inlineStr">
+      <c r="H11" s="157" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I11" s="156" t="inlineStr">
+      <c r="I11" s="157" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J11" s="156" t="inlineStr">
+      <c r="J11" s="157" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="K11" s="156" t="inlineStr">
+      <c r="K11" s="157" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L11" s="157" t="inlineStr">
+      <c r="L11" s="158" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M11" s="168" t="n"/>
-      <c r="N11" s="184" t="n"/>
-      <c r="O11" s="185" t="n"/>
-      <c r="P11" s="186" t="n"/>
-      <c r="Q11" s="186" t="n"/>
-      <c r="R11" s="173" t="n"/>
-      <c r="S11" s="187" t="n"/>
-      <c r="T11" s="187" t="n"/>
-      <c r="U11" s="159" t="n"/>
-      <c r="V11" s="159" t="n"/>
-    </row>
-    <row r="12" ht="50.25" customHeight="1" s="143">
-      <c r="A12" s="144" t="n"/>
-      <c r="B12" s="183" t="inlineStr">
+      <c r="M11" s="169" t="n"/>
+      <c r="N11" s="185" t="n"/>
+      <c r="O11" s="186" t="n"/>
+      <c r="P11" s="187" t="n"/>
+      <c r="Q11" s="187" t="n"/>
+      <c r="R11" s="174" t="n"/>
+      <c r="S11" s="188" t="n"/>
+      <c r="T11" s="188" t="n"/>
+      <c r="U11" s="160" t="n"/>
+      <c r="V11" s="160" t="n"/>
+    </row>
+    <row r="12" ht="50.25" customHeight="1" s="144">
+      <c r="A12" s="145" t="n"/>
+      <c r="B12" s="184" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="C12" s="154" t="n"/>
-      <c r="D12" s="160" t="n"/>
-      <c r="E12" s="160" t="n"/>
-      <c r="F12" s="188" t="inlineStr">
+      <c r="C12" s="155" t="n"/>
+      <c r="D12" s="161" t="n"/>
+      <c r="E12" s="161" t="n"/>
+      <c r="F12" s="189" t="inlineStr">
         <is>
           <t>RBV26</t>
         </is>
       </c>
-      <c r="G12" s="162" t="inlineStr">
+      <c r="G12" s="163" t="inlineStr">
         <is>
           <t>RB Oct 26</t>
         </is>
       </c>
-      <c r="H12" s="163" t="n"/>
-      <c r="I12" s="163" t="n"/>
-      <c r="J12" s="165" t="n"/>
-      <c r="K12" s="166" t="n"/>
-      <c r="L12" s="167" t="n"/>
-      <c r="M12" s="168" t="n"/>
-      <c r="N12" s="168" t="n"/>
-      <c r="O12" s="168" t="n"/>
-      <c r="P12" s="168" t="n"/>
-      <c r="Q12" s="168" t="n"/>
-      <c r="R12" s="168" t="n"/>
-      <c r="S12" s="189" t="n"/>
-      <c r="T12" s="189" t="n"/>
-      <c r="U12" s="159" t="n"/>
-      <c r="V12" s="159" t="n"/>
-    </row>
-    <row r="13" ht="50.25" customHeight="1" s="143">
-      <c r="A13" s="144" t="n"/>
-      <c r="D13" s="160" t="n"/>
-      <c r="E13" s="160" t="n"/>
-      <c r="F13" s="190" t="inlineStr">
+      <c r="H12" s="164" t="n"/>
+      <c r="I12" s="164" t="n"/>
+      <c r="J12" s="166" t="n"/>
+      <c r="K12" s="167" t="n"/>
+      <c r="L12" s="168" t="n"/>
+      <c r="M12" s="169" t="n"/>
+      <c r="N12" s="169" t="n"/>
+      <c r="O12" s="169" t="n"/>
+      <c r="P12" s="169" t="n"/>
+      <c r="Q12" s="169" t="n"/>
+      <c r="R12" s="169" t="n"/>
+      <c r="S12" s="190" t="n"/>
+      <c r="T12" s="190" t="n"/>
+      <c r="U12" s="160" t="n"/>
+      <c r="V12" s="160" t="n"/>
+    </row>
+    <row r="13" ht="50.25" customHeight="1" s="144">
+      <c r="A13" s="145" t="n"/>
+      <c r="D13" s="161" t="n"/>
+      <c r="E13" s="161" t="n"/>
+      <c r="F13" s="191" t="inlineStr">
         <is>
           <t>HOV26</t>
         </is>
       </c>
-      <c r="G13" s="171" t="inlineStr">
+      <c r="G13" s="172" t="inlineStr">
         <is>
           <t>HO Oct 26</t>
         </is>
       </c>
-      <c r="H13" s="172" t="n"/>
-      <c r="I13" s="172" t="n"/>
-      <c r="J13" s="191" t="n"/>
-      <c r="K13" s="174" t="n"/>
-      <c r="L13" s="175" t="n"/>
-      <c r="M13" s="168" t="n"/>
-      <c r="N13" s="192" t="n"/>
-      <c r="O13" s="192" t="n"/>
-      <c r="P13" s="192" t="n"/>
-      <c r="Q13" s="192" t="n"/>
-      <c r="R13" s="192" t="n"/>
-      <c r="S13" s="192" t="n"/>
-      <c r="T13" s="192" t="n"/>
-      <c r="U13" s="159" t="n"/>
-      <c r="V13" s="159" t="n"/>
-    </row>
-    <row r="14" ht="50.25" customHeight="1" s="143">
-      <c r="A14" s="144" t="n"/>
-      <c r="D14" s="160" t="n"/>
-      <c r="E14" s="160" t="n"/>
-      <c r="F14" s="188" t="inlineStr">
+      <c r="H13" s="173" t="n"/>
+      <c r="I13" s="173" t="n"/>
+      <c r="J13" s="192" t="n"/>
+      <c r="K13" s="175" t="n"/>
+      <c r="L13" s="176" t="n"/>
+      <c r="M13" s="169" t="n"/>
+      <c r="N13" s="193" t="n"/>
+      <c r="O13" s="193" t="n"/>
+      <c r="P13" s="193" t="n"/>
+      <c r="Q13" s="193" t="n"/>
+      <c r="R13" s="193" t="n"/>
+      <c r="S13" s="193" t="n"/>
+      <c r="T13" s="193" t="n"/>
+      <c r="U13" s="160" t="n"/>
+      <c r="V13" s="160" t="n"/>
+    </row>
+    <row r="14" ht="50.25" customHeight="1" s="144">
+      <c r="A14" s="145" t="n"/>
+      <c r="D14" s="161" t="n"/>
+      <c r="E14" s="161" t="n"/>
+      <c r="F14" s="189" t="inlineStr">
         <is>
           <t>CLV26</t>
         </is>
       </c>
-      <c r="G14" s="162" t="inlineStr">
+      <c r="G14" s="163" t="inlineStr">
         <is>
           <t>CL Oct 26</t>
         </is>
       </c>
-      <c r="H14" s="163" t="n"/>
-      <c r="I14" s="163" t="n"/>
-      <c r="J14" s="169" t="n"/>
-      <c r="K14" s="166" t="n"/>
-      <c r="L14" s="167" t="n"/>
-      <c r="M14" s="168" t="n"/>
-      <c r="N14" s="193" t="n"/>
-      <c r="O14" s="194" t="n"/>
-      <c r="P14" s="195" t="n"/>
-      <c r="Q14" s="195" t="n"/>
-      <c r="R14" s="196" t="n"/>
-      <c r="S14" s="197" t="n"/>
-      <c r="T14" s="197" t="n"/>
-      <c r="U14" s="159" t="n"/>
-      <c r="V14" s="159" t="n"/>
-    </row>
-    <row r="15" ht="50.25" customHeight="1" s="143">
-      <c r="A15" s="144" t="n"/>
-      <c r="D15" s="160" t="n"/>
-      <c r="E15" s="160" t="n"/>
-      <c r="F15" s="198" t="inlineStr">
+      <c r="H14" s="164" t="n"/>
+      <c r="I14" s="164" t="n"/>
+      <c r="J14" s="170" t="n"/>
+      <c r="K14" s="167" t="n"/>
+      <c r="L14" s="168" t="n"/>
+      <c r="M14" s="169" t="n"/>
+      <c r="N14" s="194" t="n"/>
+      <c r="O14" s="195" t="n"/>
+      <c r="P14" s="196" t="n"/>
+      <c r="Q14" s="196" t="n"/>
+      <c r="R14" s="197" t="n"/>
+      <c r="S14" s="198" t="n"/>
+      <c r="T14" s="198" t="n"/>
+      <c r="U14" s="160" t="n"/>
+      <c r="V14" s="160" t="n"/>
+    </row>
+    <row r="15" ht="50.25" customHeight="1" s="144">
+      <c r="A15" s="145" t="n"/>
+      <c r="D15" s="161" t="n"/>
+      <c r="E15" s="161" t="n"/>
+      <c r="F15" s="199" t="inlineStr">
         <is>
           <t>3:2:1</t>
         </is>
       </c>
-      <c r="G15" s="199" t="n"/>
-      <c r="H15" s="200" t="n"/>
-      <c r="I15" s="200" t="n"/>
-      <c r="J15" s="201" t="n"/>
-      <c r="K15" s="200" t="n"/>
-      <c r="L15" s="202" t="n"/>
-      <c r="M15" s="168" t="n"/>
-      <c r="N15" s="193" t="n"/>
-      <c r="O15" s="194" t="n"/>
-      <c r="P15" s="195" t="n"/>
-      <c r="Q15" s="195" t="n"/>
-      <c r="R15" s="196" t="n"/>
-      <c r="S15" s="197" t="n"/>
-      <c r="T15" s="197" t="n"/>
-      <c r="U15" s="159" t="n"/>
-      <c r="V15" s="159" t="n"/>
-    </row>
-    <row r="16" ht="42" customHeight="1" s="143">
-      <c r="A16" s="144" t="n"/>
-      <c r="D16" s="160" t="n"/>
-      <c r="E16" s="160" t="n"/>
-      <c r="F16" s="203" t="n"/>
-      <c r="G16" s="204" t="n"/>
-      <c r="H16" s="204" t="n"/>
-      <c r="I16" s="204" t="n"/>
-      <c r="J16" s="204" t="n"/>
-      <c r="K16" s="204" t="n"/>
-      <c r="L16" s="204" t="n"/>
-      <c r="M16" s="204" t="n"/>
-      <c r="S16" s="205" t="n"/>
-      <c r="T16" s="205" t="n"/>
-    </row>
-    <row r="17" ht="44.25" customHeight="1" s="143">
-      <c r="A17" s="144" t="n"/>
-      <c r="F17" s="206" t="inlineStr">
+      <c r="G15" s="200" t="n"/>
+      <c r="H15" s="201" t="n"/>
+      <c r="I15" s="201" t="n"/>
+      <c r="J15" s="202" t="n"/>
+      <c r="K15" s="201" t="n"/>
+      <c r="L15" s="203" t="n"/>
+      <c r="M15" s="169" t="n"/>
+      <c r="N15" s="194" t="n"/>
+      <c r="O15" s="195" t="n"/>
+      <c r="P15" s="196" t="n"/>
+      <c r="Q15" s="196" t="n"/>
+      <c r="R15" s="197" t="n"/>
+      <c r="S15" s="198" t="n"/>
+      <c r="T15" s="198" t="n"/>
+      <c r="U15" s="160" t="n"/>
+      <c r="V15" s="160" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="144">
+      <c r="A16" s="145" t="n"/>
+      <c r="D16" s="161" t="n"/>
+      <c r="E16" s="161" t="n"/>
+      <c r="F16" s="204" t="n"/>
+      <c r="G16" s="205" t="n"/>
+      <c r="H16" s="205" t="n"/>
+      <c r="I16" s="205" t="n"/>
+      <c r="J16" s="205" t="n"/>
+      <c r="K16" s="205" t="n"/>
+      <c r="L16" s="205" t="n"/>
+      <c r="M16" s="205" t="n"/>
+      <c r="S16" s="206" t="n"/>
+      <c r="T16" s="206" t="n"/>
+    </row>
+    <row r="17" ht="44.25" customHeight="1" s="144">
+      <c r="A17" s="145" t="n"/>
+      <c r="F17" s="207" t="inlineStr">
         <is>
           <t>Z-SCORE MONITOR      z is for ENTRIES only - exits act on money, never on z.      The chime fires on the CROSSING of ENTRY_Z, once.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="23.25" customHeight="1" s="143">
-      <c r="A18" s="144" t="n"/>
-      <c r="F18" s="207" t="inlineStr">
+    <row r="18" ht="23.25" customHeight="1" s="144">
+      <c r="A18" s="145" t="n"/>
+      <c r="F18" s="208" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="H18" s="207" t="inlineStr">
+      <c r="H18" s="208" t="inlineStr">
         <is>
           <t>Z-score</t>
         </is>
       </c>
-      <c r="I18" s="207" t="inlineStr">
+      <c r="I18" s="208" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="J18" s="207" t="inlineStr">
+      <c r="J18" s="208" t="inlineStr">
         <is>
           <t>Std Dev</t>
         </is>
       </c>
-      <c r="K18" s="207" t="inlineStr">
+      <c r="K18" s="208" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="L18" s="207" t="inlineStr">
+      <c r="L18" s="208" t="inlineStr">
         <is>
           <t>Window</t>
         </is>
       </c>
-      <c r="N18" s="207" t="inlineStr">
+      <c r="N18" s="208" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="P18" s="207" t="inlineStr">
+      <c r="P18" s="208" t="inlineStr">
         <is>
           <t>Costs $</t>
         </is>
       </c>
-      <c r="Q18" s="207" t="inlineStr">
+      <c r="Q18" s="208" t="inlineStr">
         <is>
           <t>Win $</t>
         </is>
       </c>
-      <c r="R18" s="207" t="inlineStr">
+      <c r="R18" s="208" t="inlineStr">
         <is>
           <t>TAKE PROFIT</t>
         </is>
       </c>
-      <c r="S18" s="207" t="inlineStr">
+      <c r="S18" s="208" t="inlineStr">
         <is>
           <t>TP in sigma</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="50.25" customHeight="1" s="143">
-      <c r="A19" s="144" t="n"/>
-      <c r="F19" s="208" t="inlineStr">
+    <row r="19" ht="50.25" customHeight="1" s="144">
+      <c r="A19" s="145" t="n"/>
+      <c r="F19" s="209" t="inlineStr">
         <is>
           <t>HO | CL Crack</t>
         </is>
       </c>
-      <c r="H19" s="209" t="n"/>
-      <c r="I19" s="210" t="n"/>
-      <c r="J19" s="210" t="n"/>
-      <c r="K19" s="211" t="n"/>
-      <c r="L19" s="211" t="n"/>
-      <c r="N19" s="212" t="n"/>
-      <c r="P19" s="213" t="n"/>
-      <c r="Q19" s="213" t="n"/>
-      <c r="R19" s="214" t="n"/>
-      <c r="S19" s="215" t="n"/>
-    </row>
-    <row r="20" ht="50.25" customHeight="1" s="143">
-      <c r="A20" s="144" t="n"/>
-      <c r="F20" s="208" t="inlineStr">
+      <c r="H19" s="210" t="n"/>
+      <c r="I19" s="211" t="n"/>
+      <c r="J19" s="211" t="n"/>
+      <c r="K19" s="212" t="n"/>
+      <c r="L19" s="212" t="n"/>
+      <c r="N19" s="213" t="n"/>
+      <c r="P19" s="214" t="n"/>
+      <c r="Q19" s="214" t="n"/>
+      <c r="R19" s="215" t="n"/>
+      <c r="S19" s="216" t="n"/>
+    </row>
+    <row r="20" ht="50.25" customHeight="1" s="144">
+      <c r="A20" s="145" t="n"/>
+      <c r="F20" s="209" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="H20" s="209" t="n"/>
-      <c r="I20" s="210" t="n"/>
-      <c r="J20" s="210" t="n"/>
-      <c r="K20" s="211" t="n"/>
-      <c r="L20" s="211" t="n"/>
-      <c r="N20" s="212" t="n"/>
-      <c r="P20" s="213" t="n"/>
-      <c r="Q20" s="213" t="n"/>
-      <c r="R20" s="214" t="n"/>
-      <c r="S20" s="215" t="n"/>
-    </row>
-    <row r="21" ht="50.25" customHeight="1" s="143">
-      <c r="A21" s="144" t="n"/>
-      <c r="F21" s="216" t="inlineStr">
+      <c r="H20" s="210" t="n"/>
+      <c r="I20" s="211" t="n"/>
+      <c r="J20" s="211" t="n"/>
+      <c r="K20" s="212" t="n"/>
+      <c r="L20" s="212" t="n"/>
+      <c r="N20" s="213" t="n"/>
+      <c r="P20" s="214" t="n"/>
+      <c r="Q20" s="214" t="n"/>
+      <c r="R20" s="215" t="n"/>
+      <c r="S20" s="216" t="n"/>
+    </row>
+    <row r="21" ht="50.25" customHeight="1" s="144">
+      <c r="A21" s="145" t="n"/>
+      <c r="F21" s="217" t="inlineStr">
         <is>
           <t>3:2:1</t>
         </is>
       </c>
-      <c r="H21" s="217" t="n"/>
-      <c r="I21" s="218" t="n"/>
-      <c r="J21" s="218" t="n"/>
-      <c r="K21" s="219" t="n"/>
-      <c r="L21" s="219" t="n"/>
-      <c r="N21" s="220" t="n"/>
-      <c r="P21" s="221" t="n"/>
-      <c r="Q21" s="221" t="n"/>
-      <c r="R21" s="222" t="n"/>
-      <c r="S21" s="223" t="n"/>
-    </row>
-    <row r="22" ht="36" customHeight="1" s="143">
-      <c r="A22" s="144" t="n"/>
-      <c r="F22" s="224" t="n"/>
-      <c r="G22" s="225" t="n"/>
-      <c r="H22" s="225" t="n"/>
-      <c r="I22" s="225" t="n"/>
-      <c r="J22" s="225" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1" s="143">
-      <c r="A23" s="144" t="n"/>
-      <c r="F23" s="226" t="inlineStr">
+      <c r="H21" s="218" t="n"/>
+      <c r="I21" s="219" t="n"/>
+      <c r="J21" s="219" t="n"/>
+      <c r="K21" s="220" t="n"/>
+      <c r="L21" s="220" t="n"/>
+      <c r="N21" s="221" t="n"/>
+      <c r="P21" s="222" t="n"/>
+      <c r="Q21" s="222" t="n"/>
+      <c r="R21" s="223" t="n"/>
+      <c r="S21" s="224" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="144">
+      <c r="A22" s="145" t="n"/>
+      <c r="F22" s="225" t="n"/>
+      <c r="G22" s="226" t="n"/>
+      <c r="H22" s="226" t="n"/>
+      <c r="I22" s="226" t="n"/>
+      <c r="J22" s="226" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="144">
+      <c r="A23" s="145" t="n"/>
+      <c r="F23" s="227" t="inlineStr">
         <is>
           <t>STOPPED</t>
         </is>
       </c>
-      <c r="G23" s="225" t="n"/>
-      <c r="H23" s="227" t="inlineStr">
+      <c r="G23" s="226" t="n"/>
+      <c r="H23" s="228" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="225" t="n"/>
-      <c r="J23" s="225" t="n"/>
-      <c r="N23" s="228" t="inlineStr">
+      <c r="I23" s="226" t="n"/>
+      <c r="J23" s="226" t="n"/>
+      <c r="N23" s="229" t="inlineStr">
         <is>
           <t xml:space="preserve">  &gt;  START  </t>
         </is>
       </c>
-      <c r="P23" s="229" t="inlineStr">
+      <c r="P23" s="230" t="inlineStr">
         <is>
           <t xml:space="preserve">  #  STOP  </t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="36" customHeight="1" s="143">
-      <c r="A24" s="144" t="n"/>
-      <c r="F24" s="224" t="n"/>
-      <c r="G24" s="225" t="n"/>
-      <c r="H24" s="225" t="n"/>
-      <c r="I24" s="225" t="n"/>
-      <c r="J24" s="225" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="143">
-      <c r="A25" s="144" t="n"/>
-    </row>
-    <row r="26" ht="39.75" customHeight="1" s="143">
-      <c r="A26" s="144" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="143">
-      <c r="A27" s="144" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="143">
-      <c r="A28" s="144" t="n"/>
-    </row>
-    <row r="29" ht="36" customHeight="1" s="143">
-      <c r="A29" s="144" t="n"/>
-      <c r="F29" s="224" t="n"/>
-      <c r="G29" s="225" t="n"/>
-      <c r="H29" s="225" t="n"/>
-      <c r="I29" s="225" t="n"/>
-      <c r="J29" s="225" t="n"/>
-    </row>
-    <row r="30" ht="36" customHeight="1" s="143">
-      <c r="A30" s="144" t="n"/>
-      <c r="F30" s="224" t="n"/>
-      <c r="G30" s="225" t="n"/>
-      <c r="H30" s="225" t="n"/>
-      <c r="I30" s="225" t="n"/>
-      <c r="J30" s="225" t="n"/>
-    </row>
-    <row r="31" ht="36" customHeight="1" s="143">
-      <c r="A31" s="144" t="n"/>
-      <c r="F31" s="224" t="n"/>
-      <c r="G31" s="225" t="n"/>
-      <c r="H31" s="225" t="n"/>
-      <c r="I31" s="225" t="n"/>
-      <c r="J31" s="225" t="n"/>
-    </row>
-    <row r="32" ht="36" customHeight="1" s="143">
-      <c r="A32" s="144" t="n"/>
-      <c r="F32" s="224" t="n"/>
-      <c r="G32" s="225" t="n"/>
-      <c r="H32" s="225" t="n"/>
-      <c r="I32" s="225" t="n"/>
-      <c r="J32" s="225" t="n"/>
-    </row>
-    <row r="33" ht="36" customHeight="1" s="143">
-      <c r="A33" s="144" t="n"/>
-      <c r="F33" s="224" t="n"/>
-      <c r="G33" s="225" t="n"/>
-      <c r="H33" s="225" t="n"/>
-      <c r="I33" s="225" t="n"/>
-      <c r="J33" s="225" t="n"/>
-    </row>
-    <row r="34" ht="36" customHeight="1" s="143">
-      <c r="A34" s="144" t="n"/>
-      <c r="F34" s="224" t="n"/>
-      <c r="G34" s="225" t="n"/>
-      <c r="H34" s="225" t="n"/>
-      <c r="I34" s="225" t="n"/>
-      <c r="J34" s="225" t="n"/>
-    </row>
-    <row r="35" ht="36" customHeight="1" s="143">
-      <c r="A35" s="144" t="n"/>
-      <c r="F35" s="224" t="n"/>
-      <c r="G35" s="225" t="n"/>
-      <c r="H35" s="225" t="n"/>
-      <c r="I35" s="225" t="n"/>
-      <c r="J35" s="225" t="n"/>
-    </row>
-    <row r="36" ht="36" customHeight="1" s="143">
-      <c r="A36" s="144" t="n"/>
-      <c r="F36" s="224" t="n"/>
-      <c r="G36" s="225" t="n"/>
-      <c r="H36" s="225" t="n"/>
-      <c r="I36" s="225" t="n"/>
-      <c r="J36" s="225" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1" s="143">
-      <c r="A37" s="144" t="n"/>
-      <c r="F37" s="224" t="n"/>
-      <c r="G37" s="225" t="n"/>
-      <c r="H37" s="225" t="n"/>
-      <c r="I37" s="225" t="n"/>
-      <c r="J37" s="225" t="n"/>
-    </row>
-    <row r="38" ht="36" customHeight="1" s="143">
-      <c r="A38" s="144" t="n"/>
-      <c r="F38" s="224" t="n"/>
-      <c r="G38" s="225" t="n"/>
-      <c r="H38" s="225" t="n"/>
-      <c r="I38" s="225" t="n"/>
-      <c r="J38" s="225" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1" s="143">
-      <c r="A39" s="144" t="n"/>
-      <c r="F39" s="224" t="n"/>
-      <c r="G39" s="225" t="n"/>
-      <c r="H39" s="225" t="n"/>
-      <c r="I39" s="225" t="n"/>
-      <c r="J39" s="225" t="n"/>
-    </row>
-    <row r="40" ht="36" customHeight="1" s="143">
-      <c r="F40" s="224" t="n"/>
-      <c r="G40" s="225" t="n"/>
-      <c r="H40" s="225" t="n"/>
-      <c r="I40" s="225" t="n"/>
-      <c r="J40" s="225" t="n"/>
-    </row>
-    <row r="41" ht="36" customHeight="1" s="143">
-      <c r="F41" s="224" t="n"/>
-      <c r="G41" s="225" t="n"/>
-      <c r="H41" s="225" t="n"/>
-      <c r="I41" s="225" t="n"/>
-      <c r="J41" s="225" t="n"/>
-    </row>
-    <row r="42" ht="36" customHeight="1" s="143">
-      <c r="F42" s="224" t="n"/>
-      <c r="G42" s="225" t="n"/>
-      <c r="H42" s="225" t="n"/>
-      <c r="I42" s="225" t="n"/>
-      <c r="J42" s="225" t="n"/>
-    </row>
-    <row r="43" ht="36" customHeight="1" s="143">
-      <c r="F43" s="224" t="n"/>
-      <c r="G43" s="225" t="n"/>
-      <c r="H43" s="225" t="n"/>
-      <c r="I43" s="225" t="n"/>
-      <c r="J43" s="225" t="n"/>
-    </row>
-    <row r="44" ht="36" customHeight="1" s="143">
-      <c r="F44" s="224" t="n"/>
-      <c r="G44" s="225" t="n"/>
-      <c r="H44" s="225" t="n"/>
-      <c r="I44" s="225" t="n"/>
-      <c r="J44" s="225" t="n"/>
-    </row>
-    <row r="45" ht="36" customHeight="1" s="143">
-      <c r="F45" s="224" t="n"/>
-      <c r="G45" s="225" t="n"/>
-      <c r="H45" s="225" t="n"/>
-      <c r="I45" s="225" t="n"/>
-      <c r="J45" s="225" t="n"/>
-    </row>
-    <row r="46" ht="36" customHeight="1" s="143">
-      <c r="F46" s="224" t="n"/>
-      <c r="G46" s="225" t="n"/>
-      <c r="H46" s="225" t="n"/>
-      <c r="I46" s="225" t="n"/>
-      <c r="J46" s="225" t="n"/>
-    </row>
-    <row r="47" ht="36" customHeight="1" s="143">
-      <c r="F47" s="224" t="n"/>
-      <c r="G47" s="225" t="n"/>
-      <c r="H47" s="225" t="n"/>
-      <c r="I47" s="225" t="n"/>
-      <c r="J47" s="225" t="n"/>
-    </row>
-    <row r="48" ht="36" customHeight="1" s="143">
-      <c r="F48" s="224" t="n"/>
-      <c r="G48" s="225" t="n"/>
-      <c r="H48" s="225" t="n"/>
-      <c r="I48" s="225" t="n"/>
-      <c r="J48" s="225" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1" s="143">
-      <c r="F49" s="224" t="n"/>
-      <c r="G49" s="225" t="n"/>
-      <c r="H49" s="225" t="n"/>
-      <c r="I49" s="225" t="n"/>
-      <c r="J49" s="225" t="n"/>
-    </row>
-    <row r="50" ht="36" customHeight="1" s="143">
-      <c r="F50" s="224" t="n"/>
-      <c r="G50" s="225" t="n"/>
-      <c r="H50" s="225" t="n"/>
-      <c r="I50" s="225" t="n"/>
-      <c r="J50" s="225" t="n"/>
-    </row>
-    <row r="51" ht="36" customHeight="1" s="143">
-      <c r="F51" s="224" t="n"/>
-      <c r="G51" s="225" t="n"/>
-      <c r="H51" s="225" t="n"/>
-      <c r="I51" s="225" t="n"/>
-      <c r="J51" s="225" t="n"/>
+      <c r="R23" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TEST CHIME  </t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="144">
+      <c r="A24" s="145" t="n"/>
+      <c r="F24" s="225" t="n"/>
+      <c r="G24" s="226" t="n"/>
+      <c r="H24" s="226" t="n"/>
+      <c r="I24" s="226" t="n"/>
+      <c r="J24" s="226" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="144">
+      <c r="A25" s="145" t="n"/>
+    </row>
+    <row r="26" ht="39.75" customHeight="1" s="144">
+      <c r="A26" s="145" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="144">
+      <c r="A27" s="145" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="144">
+      <c r="A28" s="145" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="144">
+      <c r="A29" s="145" t="n"/>
+      <c r="F29" s="225" t="n"/>
+      <c r="G29" s="226" t="n"/>
+      <c r="H29" s="226" t="n"/>
+      <c r="I29" s="226" t="n"/>
+      <c r="J29" s="226" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1" s="144">
+      <c r="A30" s="145" t="n"/>
+      <c r="F30" s="225" t="n"/>
+      <c r="G30" s="226" t="n"/>
+      <c r="H30" s="226" t="n"/>
+      <c r="I30" s="226" t="n"/>
+      <c r="J30" s="226" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="144">
+      <c r="A31" s="145" t="n"/>
+      <c r="F31" s="225" t="n"/>
+      <c r="G31" s="226" t="n"/>
+      <c r="H31" s="226" t="n"/>
+      <c r="I31" s="226" t="n"/>
+      <c r="J31" s="226" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="144">
+      <c r="A32" s="145" t="n"/>
+      <c r="F32" s="225" t="n"/>
+      <c r="G32" s="226" t="n"/>
+      <c r="H32" s="226" t="n"/>
+      <c r="I32" s="226" t="n"/>
+      <c r="J32" s="226" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1" s="144">
+      <c r="A33" s="145" t="n"/>
+      <c r="F33" s="225" t="n"/>
+      <c r="G33" s="226" t="n"/>
+      <c r="H33" s="226" t="n"/>
+      <c r="I33" s="226" t="n"/>
+      <c r="J33" s="226" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="144">
+      <c r="A34" s="145" t="n"/>
+      <c r="F34" s="225" t="n"/>
+      <c r="G34" s="226" t="n"/>
+      <c r="H34" s="226" t="n"/>
+      <c r="I34" s="226" t="n"/>
+      <c r="J34" s="226" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="144">
+      <c r="A35" s="145" t="n"/>
+      <c r="F35" s="225" t="n"/>
+      <c r="G35" s="226" t="n"/>
+      <c r="H35" s="226" t="n"/>
+      <c r="I35" s="226" t="n"/>
+      <c r="J35" s="226" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1" s="144">
+      <c r="A36" s="145" t="n"/>
+      <c r="F36" s="225" t="n"/>
+      <c r="G36" s="226" t="n"/>
+      <c r="H36" s="226" t="n"/>
+      <c r="I36" s="226" t="n"/>
+      <c r="J36" s="226" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1" s="144">
+      <c r="A37" s="145" t="n"/>
+      <c r="F37" s="225" t="n"/>
+      <c r="G37" s="226" t="n"/>
+      <c r="H37" s="226" t="n"/>
+      <c r="I37" s="226" t="n"/>
+      <c r="J37" s="226" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1" s="144">
+      <c r="A38" s="145" t="n"/>
+      <c r="F38" s="225" t="n"/>
+      <c r="G38" s="226" t="n"/>
+      <c r="H38" s="226" t="n"/>
+      <c r="I38" s="226" t="n"/>
+      <c r="J38" s="226" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="144">
+      <c r="A39" s="145" t="n"/>
+      <c r="F39" s="225" t="n"/>
+      <c r="G39" s="226" t="n"/>
+      <c r="H39" s="226" t="n"/>
+      <c r="I39" s="226" t="n"/>
+      <c r="J39" s="226" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="144">
+      <c r="F40" s="225" t="n"/>
+      <c r="G40" s="226" t="n"/>
+      <c r="H40" s="226" t="n"/>
+      <c r="I40" s="226" t="n"/>
+      <c r="J40" s="226" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1" s="144">
+      <c r="F41" s="225" t="n"/>
+      <c r="G41" s="226" t="n"/>
+      <c r="H41" s="226" t="n"/>
+      <c r="I41" s="226" t="n"/>
+      <c r="J41" s="226" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="144">
+      <c r="F42" s="225" t="n"/>
+      <c r="G42" s="226" t="n"/>
+      <c r="H42" s="226" t="n"/>
+      <c r="I42" s="226" t="n"/>
+      <c r="J42" s="226" t="n"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" s="144">
+      <c r="F43" s="225" t="n"/>
+      <c r="G43" s="226" t="n"/>
+      <c r="H43" s="226" t="n"/>
+      <c r="I43" s="226" t="n"/>
+      <c r="J43" s="226" t="n"/>
+    </row>
+    <row r="44" ht="36" customHeight="1" s="144">
+      <c r="F44" s="225" t="n"/>
+      <c r="G44" s="226" t="n"/>
+      <c r="H44" s="226" t="n"/>
+      <c r="I44" s="226" t="n"/>
+      <c r="J44" s="226" t="n"/>
+    </row>
+    <row r="45" ht="36" customHeight="1" s="144">
+      <c r="F45" s="225" t="n"/>
+      <c r="G45" s="226" t="n"/>
+      <c r="H45" s="226" t="n"/>
+      <c r="I45" s="226" t="n"/>
+      <c r="J45" s="226" t="n"/>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="144">
+      <c r="F46" s="225" t="n"/>
+      <c r="G46" s="226" t="n"/>
+      <c r="H46" s="226" t="n"/>
+      <c r="I46" s="226" t="n"/>
+      <c r="J46" s="226" t="n"/>
+    </row>
+    <row r="47" ht="36" customHeight="1" s="144">
+      <c r="F47" s="225" t="n"/>
+      <c r="G47" s="226" t="n"/>
+      <c r="H47" s="226" t="n"/>
+      <c r="I47" s="226" t="n"/>
+      <c r="J47" s="226" t="n"/>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="144">
+      <c r="F48" s="225" t="n"/>
+      <c r="G48" s="226" t="n"/>
+      <c r="H48" s="226" t="n"/>
+      <c r="I48" s="226" t="n"/>
+      <c r="J48" s="226" t="n"/>
+    </row>
+    <row r="49" ht="36" customHeight="1" s="144">
+      <c r="F49" s="225" t="n"/>
+      <c r="G49" s="226" t="n"/>
+      <c r="H49" s="226" t="n"/>
+      <c r="I49" s="226" t="n"/>
+      <c r="J49" s="226" t="n"/>
+    </row>
+    <row r="50" ht="36" customHeight="1" s="144">
+      <c r="F50" s="225" t="n"/>
+      <c r="G50" s="226" t="n"/>
+      <c r="H50" s="226" t="n"/>
+      <c r="I50" s="226" t="n"/>
+      <c r="J50" s="226" t="n"/>
+    </row>
+    <row r="51" ht="36" customHeight="1" s="144">
+      <c r="F51" s="225" t="n"/>
+      <c r="G51" s="226" t="n"/>
+      <c r="H51" s="226" t="n"/>
+      <c r="I51" s="226" t="n"/>
+      <c r="J51" s="226" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2780,1025 +2791,1025 @@
   <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="3" customWidth="1" style="141" min="1" max="1"/>
-    <col width="32" customWidth="1" style="141" min="2" max="2"/>
-    <col width="20" customWidth="1" style="141" min="3" max="3"/>
-    <col width="18" customWidth="1" style="141" min="4" max="7"/>
-    <col width="12" customWidth="1" style="141" min="8" max="11"/>
-    <col width="14" customWidth="1" style="141" min="12" max="12"/>
-    <col width="46" customWidth="1" style="141" min="13" max="13"/>
+    <col width="3" customWidth="1" style="142" min="1" max="1"/>
+    <col width="32" customWidth="1" style="142" min="2" max="2"/>
+    <col width="20" customWidth="1" style="142" min="3" max="3"/>
+    <col width="18" customWidth="1" style="142" min="4" max="7"/>
+    <col width="12" customWidth="1" style="142" min="8" max="11"/>
+    <col width="14" customWidth="1" style="142" min="12" max="12"/>
+    <col width="46" customWidth="1" style="142" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.35" customHeight="1" s="143">
-      <c r="B1" s="230" t="inlineStr">
+    <row r="1" ht="17.35" customHeight="1" s="144">
+      <c r="B1" s="232" t="inlineStr">
         <is>
           <t>DETAIL   -   full breakdown behind the Dashboard</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="143">
-      <c r="B2" s="231" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="144">
+      <c r="B2" s="233" t="inlineStr">
         <is>
           <t>Same engine, same numbers. The Dashboard shows the three spreads you trade from; this sheet shows everything that stands behind them, for all four slots.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="15" customHeight="1" s="143">
-      <c r="B4" s="232" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="144">
+      <c r="B4" s="234" t="inlineStr">
         <is>
           <t>OUTRIGHT LEGS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="143">
-      <c r="B5" s="233" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="144">
+      <c r="B5" s="235" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C5" s="233" t="inlineStr">
+      <c r="C5" s="235" t="inlineStr">
         <is>
           <t>Instrument ID</t>
         </is>
       </c>
-      <c r="D5" s="233" t="inlineStr">
+      <c r="D5" s="235" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="233" t="inlineStr">
+      <c r="E5" s="235" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H5" s="233" t="inlineStr">
+      <c r="H5" s="235" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I5" s="233" t="inlineStr">
+      <c r="I5" s="235" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J5" s="233" t="inlineStr">
+      <c r="J5" s="235" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K5" s="233" t="inlineStr">
+      <c r="K5" s="235" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L5" s="233" t="inlineStr">
+      <c r="L5" s="235" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="M5" s="233" t="inlineStr">
+      <c r="M5" s="235" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="143">
-      <c r="B6" s="234" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="144">
+      <c r="B6" s="236" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="C6" s="235" t="n"/>
-      <c r="D6" s="236" t="inlineStr">
+      <c r="C6" s="237" t="n"/>
+      <c r="D6" s="238" t="inlineStr">
         <is>
           <t>RBOB Gasoline Oct26</t>
         </is>
       </c>
-      <c r="E6" s="237" t="inlineStr">
+      <c r="E6" s="239" t="inlineStr">
         <is>
           <t>42,000 gal</t>
         </is>
       </c>
-      <c r="H6" s="238" t="n"/>
-      <c r="I6" s="238" t="n"/>
-      <c r="J6" s="238" t="n"/>
-      <c r="K6" s="238" t="n"/>
-      <c r="L6" s="238" t="n"/>
-      <c r="M6" s="238" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="143">
-      <c r="B7" s="234" t="inlineStr">
+      <c r="H6" s="240" t="n"/>
+      <c r="I6" s="240" t="n"/>
+      <c r="J6" s="240" t="n"/>
+      <c r="K6" s="240" t="n"/>
+      <c r="L6" s="240" t="n"/>
+      <c r="M6" s="240" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="144">
+      <c r="B7" s="236" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="C7" s="235" t="n"/>
-      <c r="D7" s="236" t="inlineStr">
+      <c r="C7" s="237" t="n"/>
+      <c r="D7" s="238" t="inlineStr">
         <is>
           <t>NY Harbor ULSD Oct26</t>
         </is>
       </c>
-      <c r="E7" s="237" t="inlineStr">
+      <c r="E7" s="239" t="inlineStr">
         <is>
           <t>42,000 gal</t>
         </is>
       </c>
-      <c r="H7" s="238" t="n"/>
-      <c r="I7" s="238" t="n"/>
-      <c r="J7" s="238" t="n"/>
-      <c r="K7" s="238" t="n"/>
-      <c r="L7" s="238" t="n"/>
-      <c r="M7" s="238" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="143">
-      <c r="B8" s="234" t="inlineStr">
+      <c r="H7" s="240" t="n"/>
+      <c r="I7" s="240" t="n"/>
+      <c r="J7" s="240" t="n"/>
+      <c r="K7" s="240" t="n"/>
+      <c r="L7" s="240" t="n"/>
+      <c r="M7" s="240" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="144">
+      <c r="B8" s="236" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="C8" s="235" t="n"/>
-      <c r="D8" s="236" t="inlineStr">
+      <c r="C8" s="237" t="n"/>
+      <c r="D8" s="238" t="inlineStr">
         <is>
           <t>WTI Crude Oct26</t>
         </is>
       </c>
-      <c r="E8" s="237" t="inlineStr">
+      <c r="E8" s="239" t="inlineStr">
         <is>
           <t>1,000 bbl</t>
         </is>
       </c>
-      <c r="H8" s="238" t="n"/>
-      <c r="I8" s="238" t="n"/>
-      <c r="J8" s="238" t="n"/>
-      <c r="K8" s="238" t="n"/>
-      <c r="L8" s="238" t="n"/>
-      <c r="M8" s="238" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="143">
-      <c r="B9" s="234" t="inlineStr">
+      <c r="H8" s="240" t="n"/>
+      <c r="I8" s="240" t="n"/>
+      <c r="J8" s="240" t="n"/>
+      <c r="K8" s="240" t="n"/>
+      <c r="L8" s="240" t="n"/>
+      <c r="M8" s="240" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="144">
+      <c r="B9" s="236" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="C9" s="235" t="n"/>
-      <c r="D9" s="236" t="inlineStr">
+      <c r="C9" s="237" t="n"/>
+      <c r="D9" s="238" t="inlineStr">
         <is>
           <t>Brent Last Day Fin Oct26</t>
         </is>
       </c>
-      <c r="E9" s="237" t="inlineStr">
+      <c r="E9" s="239" t="inlineStr">
         <is>
           <t>1,000 bbl</t>
         </is>
       </c>
-      <c r="H9" s="238" t="n"/>
-      <c r="I9" s="238" t="n"/>
-      <c r="J9" s="238" t="n"/>
-      <c r="K9" s="238" t="n"/>
-      <c r="L9" s="238" t="n"/>
-      <c r="M9" s="238" t="n"/>
+      <c r="H9" s="240" t="n"/>
+      <c r="I9" s="240" t="n"/>
+      <c r="J9" s="240" t="n"/>
+      <c r="K9" s="240" t="n"/>
+      <c r="L9" s="240" t="n"/>
+      <c r="M9" s="240" t="n"/>
     </row>
     <row r="10"/>
-    <row r="11" ht="15" customHeight="1" s="143">
-      <c r="B11" s="232" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="144">
+      <c r="B11" s="234" t="inlineStr">
         <is>
           <t>DERIVED &amp; LISTED SPREADS</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="143">
-      <c r="B12" s="233" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="144">
+      <c r="B12" s="235" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C12" s="233" t="inlineStr">
+      <c r="C12" s="235" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="D12" s="233" t="inlineStr">
+      <c r="D12" s="235" t="inlineStr">
         <is>
           <t>Crossing convention</t>
         </is>
       </c>
-      <c r="H12" s="233" t="inlineStr">
+      <c r="H12" s="235" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I12" s="233" t="inlineStr">
+      <c r="I12" s="235" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="L12" s="233" t="inlineStr">
+      <c r="L12" s="235" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="M12" s="233" t="inlineStr">
+      <c r="M12" s="235" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="143">
-      <c r="B13" s="234" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="144">
+      <c r="B13" s="236" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="C13" s="237" t="inlineStr">
+      <c r="C13" s="239" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D13" s="239" t="inlineStr">
+      <c r="D13" s="241" t="inlineStr">
         <is>
           <t>bid = BZ bid - CL ask ; ask = BZ ask - CL bid</t>
         </is>
       </c>
-      <c r="H13" s="238" t="n"/>
-      <c r="I13" s="238" t="n"/>
-      <c r="L13" s="238" t="n"/>
-      <c r="M13" s="238" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="143">
-      <c r="B14" s="234" t="inlineStr">
+      <c r="H13" s="240" t="n"/>
+      <c r="I13" s="240" t="n"/>
+      <c r="L13" s="240" t="n"/>
+      <c r="M13" s="240" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="144">
+      <c r="B14" s="236" t="inlineStr">
         <is>
           <t>HO/CL crack</t>
         </is>
       </c>
-      <c r="C14" s="237" t="inlineStr">
+      <c r="C14" s="239" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D14" s="239" t="inlineStr">
+      <c r="D14" s="241" t="inlineStr">
         <is>
           <t>bid = HO bid x42 - CL ask ; ask = HO ask x42 - CL bid</t>
         </is>
       </c>
-      <c r="H14" s="238" t="n"/>
-      <c r="I14" s="238" t="n"/>
-      <c r="L14" s="238" t="n"/>
-      <c r="M14" s="238" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="143">
-      <c r="B15" s="234" t="inlineStr">
+      <c r="H14" s="240" t="n"/>
+      <c r="I14" s="240" t="n"/>
+      <c r="L14" s="240" t="n"/>
+      <c r="M14" s="240" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="144">
+      <c r="B15" s="236" t="inlineStr">
         <is>
           <t>3:2:1 crack</t>
         </is>
       </c>
-      <c r="C15" s="237" t="inlineStr">
+      <c r="C15" s="239" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D15" s="239" t="inlineStr">
+      <c r="D15" s="241" t="inlineStr">
         <is>
           <t>bid sells products at the bid and buys crude at the ask; ask mirrors it</t>
         </is>
       </c>
-      <c r="H15" s="238" t="n"/>
-      <c r="I15" s="238" t="n"/>
-      <c r="L15" s="238" t="n"/>
-      <c r="M15" s="238" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="143">
-      <c r="B16" s="234" t="inlineStr">
+      <c r="H15" s="240" t="n"/>
+      <c r="I15" s="240" t="n"/>
+      <c r="L15" s="240" t="n"/>
+      <c r="M15" s="240" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="144">
+      <c r="B16" s="236" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="C16" s="237" t="inlineStr">
+      <c r="C16" s="239" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="D16" s="239" t="inlineStr">
+      <c r="D16" s="241" t="inlineStr">
         <is>
           <t>exchange-listed - one quote, no leg risk</t>
         </is>
       </c>
-      <c r="H16" s="238" t="n"/>
-      <c r="I16" s="238" t="n"/>
-      <c r="L16" s="238" t="n"/>
-      <c r="M16" s="238" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="143">
-      <c r="B17" s="234" t="inlineStr">
+      <c r="H16" s="240" t="n"/>
+      <c r="I16" s="240" t="n"/>
+      <c r="L16" s="240" t="n"/>
+      <c r="M16" s="240" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="144">
+      <c r="B17" s="236" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="C17" s="237" t="inlineStr">
+      <c r="C17" s="239" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="D17" s="239" t="inlineStr">
+      <c r="D17" s="241" t="inlineStr">
         <is>
           <t>exchange-listed - one quote, no leg risk</t>
         </is>
       </c>
-      <c r="H17" s="238" t="n"/>
-      <c r="I17" s="238" t="n"/>
-      <c r="L17" s="238" t="n"/>
-      <c r="M17" s="238" t="n"/>
+      <c r="H17" s="240" t="n"/>
+      <c r="I17" s="240" t="n"/>
+      <c r="L17" s="240" t="n"/>
+      <c r="M17" s="240" t="n"/>
     </row>
     <row r="18"/>
-    <row r="19" ht="15" customHeight="1" s="143">
-      <c r="B19" s="232" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="144">
+      <c r="B19" s="234" t="inlineStr">
         <is>
           <t>PER-SPREAD BREAKDOWN</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="143">
-      <c r="B20" s="233" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="144">
+      <c r="B20" s="235" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C20" s="233" t="inlineStr">
+      <c r="C20" s="235" t="inlineStr">
         <is>
           <t>Unit / note</t>
         </is>
       </c>
-      <c r="D20" s="233" t="inlineStr">
+      <c r="D20" s="235" t="inlineStr">
         <is>
           <t>SPREAD 1</t>
         </is>
       </c>
-      <c r="E20" s="233" t="inlineStr">
+      <c r="E20" s="235" t="inlineStr">
         <is>
           <t>SPREAD 2</t>
         </is>
       </c>
-      <c r="F20" s="233" t="inlineStr">
+      <c r="F20" s="235" t="inlineStr">
         <is>
           <t>SPREAD 3</t>
         </is>
       </c>
-      <c r="G20" s="233" t="inlineStr">
+      <c r="G20" s="235" t="inlineStr">
         <is>
           <t>SPREAD 4</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="143">
-      <c r="B21" s="240" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="144">
+      <c r="B21" s="242" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C21" s="239" t="n"/>
-      <c r="D21" s="241" t="n"/>
-      <c r="E21" s="241" t="n"/>
-      <c r="F21" s="241" t="n"/>
-      <c r="G21" s="241" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="143">
-      <c r="B22" s="240" t="inlineStr">
+      <c r="C21" s="241" t="n"/>
+      <c r="D21" s="243" t="n"/>
+      <c r="E21" s="243" t="n"/>
+      <c r="F21" s="243" t="n"/>
+      <c r="G21" s="243" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="144">
+      <c r="B22" s="242" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C22" s="239" t="inlineStr">
+      <c r="C22" s="241" t="inlineStr">
         <is>
           <t>LegB - beta x LegA</t>
         </is>
       </c>
-      <c r="D22" s="241" t="n"/>
-      <c r="E22" s="241" t="n"/>
-      <c r="F22" s="241" t="n"/>
-      <c r="G22" s="241" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="143">
-      <c r="B23" s="240" t="inlineStr">
+      <c r="D22" s="243" t="n"/>
+      <c r="E22" s="243" t="n"/>
+      <c r="F22" s="243" t="n"/>
+      <c r="G22" s="243" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="144">
+      <c r="B23" s="242" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="C23" s="239" t="n"/>
-      <c r="D23" s="241" t="n"/>
-      <c r="E23" s="241" t="n"/>
-      <c r="F23" s="241" t="n"/>
-      <c r="G23" s="241" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="143">
-      <c r="B24" s="240" t="inlineStr">
+      <c r="C23" s="241" t="n"/>
+      <c r="D23" s="243" t="n"/>
+      <c r="E23" s="243" t="n"/>
+      <c r="F23" s="243" t="n"/>
+      <c r="G23" s="243" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="144">
+      <c r="B24" s="242" t="inlineStr">
         <is>
           <t>HEDGE_RATIO (beta)</t>
         </is>
       </c>
-      <c r="C24" s="239" t="inlineStr">
+      <c r="C24" s="241" t="inlineStr">
         <is>
           <t>stamped pair -&gt;</t>
         </is>
       </c>
-      <c r="D24" s="241" t="n"/>
-      <c r="E24" s="241" t="n"/>
-      <c r="F24" s="241" t="n"/>
-      <c r="G24" s="241" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="143">
-      <c r="B25" s="240" t="inlineStr">
+      <c r="D24" s="243" t="n"/>
+      <c r="E24" s="243" t="n"/>
+      <c r="F24" s="243" t="n"/>
+      <c r="G24" s="243" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="144">
+      <c r="B25" s="242" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread</t>
         </is>
       </c>
-      <c r="C25" s="239" t="inlineStr">
+      <c r="C25" s="241" t="inlineStr">
         <is>
           <t>per lot</t>
         </is>
       </c>
-      <c r="D25" s="242" t="n"/>
-      <c r="E25" s="242" t="n"/>
-      <c r="F25" s="242" t="n"/>
-      <c r="G25" s="242" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="143">
-      <c r="B26" s="243" t="inlineStr">
+      <c r="D25" s="244" t="n"/>
+      <c r="E25" s="244" t="n"/>
+      <c r="F25" s="244" t="n"/>
+      <c r="G25" s="244" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="144">
+      <c r="B26" s="245" t="inlineStr">
         <is>
           <t>MARKET  (touch, shown separately from the statistic)</t>
         </is>
       </c>
-      <c r="C26" s="244" t="n"/>
-      <c r="D26" s="244" t="n"/>
-      <c r="E26" s="244" t="n"/>
-      <c r="F26" s="244" t="n"/>
-      <c r="G26" s="244" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="143">
-      <c r="B27" s="240" t="inlineStr">
+      <c r="C26" s="246" t="n"/>
+      <c r="D26" s="246" t="n"/>
+      <c r="E26" s="246" t="n"/>
+      <c r="F26" s="246" t="n"/>
+      <c r="G26" s="246" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="144">
+      <c r="B27" s="242" t="inlineStr">
         <is>
           <t>Spread bid</t>
         </is>
       </c>
-      <c r="C27" s="239" t="n"/>
-      <c r="D27" s="238" t="n"/>
-      <c r="E27" s="238" t="n"/>
-      <c r="F27" s="238" t="n"/>
-      <c r="G27" s="238" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="143">
-      <c r="B28" s="240" t="inlineStr">
+      <c r="C27" s="241" t="n"/>
+      <c r="D27" s="240" t="n"/>
+      <c r="E27" s="240" t="n"/>
+      <c r="F27" s="240" t="n"/>
+      <c r="G27" s="240" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="144">
+      <c r="B28" s="242" t="inlineStr">
         <is>
           <t>Spread ask</t>
         </is>
       </c>
-      <c r="C28" s="239" t="n"/>
-      <c r="D28" s="238" t="n"/>
-      <c r="E28" s="238" t="n"/>
-      <c r="F28" s="238" t="n"/>
-      <c r="G28" s="238" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="143">
-      <c r="B29" s="240" t="inlineStr">
+      <c r="C28" s="241" t="n"/>
+      <c r="D28" s="240" t="n"/>
+      <c r="E28" s="240" t="n"/>
+      <c r="F28" s="240" t="n"/>
+      <c r="G28" s="240" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="144">
+      <c r="B29" s="242" t="inlineStr">
         <is>
           <t>Spread mid   &lt;- feeds the statistic</t>
         </is>
       </c>
-      <c r="C29" s="239" t="n"/>
-      <c r="D29" s="238" t="n"/>
-      <c r="E29" s="238" t="n"/>
-      <c r="F29" s="238" t="n"/>
-      <c r="G29" s="238" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="143">
-      <c r="B30" s="240" t="inlineStr">
+      <c r="C29" s="241" t="n"/>
+      <c r="D29" s="240" t="n"/>
+      <c r="E29" s="240" t="n"/>
+      <c r="F29" s="240" t="n"/>
+      <c r="G29" s="240" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="144">
+      <c r="B30" s="242" t="inlineStr">
         <is>
           <t>Bid-Ask Gap</t>
         </is>
       </c>
-      <c r="C30" s="239" t="inlineStr">
+      <c r="C30" s="241" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D30" s="238" t="n"/>
-      <c r="E30" s="238" t="n"/>
-      <c r="F30" s="238" t="n"/>
-      <c r="G30" s="238" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="143">
-      <c r="B31" s="243" t="inlineStr">
+      <c r="D30" s="240" t="n"/>
+      <c r="E30" s="240" t="n"/>
+      <c r="F30" s="240" t="n"/>
+      <c r="G30" s="240" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="144">
+      <c r="B31" s="245" t="inlineStr">
         <is>
           <t>WINDOW</t>
         </is>
       </c>
-      <c r="C31" s="244" t="n"/>
-      <c r="D31" s="244" t="n"/>
-      <c r="E31" s="244" t="n"/>
-      <c r="F31" s="244" t="n"/>
-      <c r="G31" s="244" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="143">
-      <c r="B32" s="240" t="inlineStr">
+      <c r="C31" s="246" t="n"/>
+      <c r="D31" s="246" t="n"/>
+      <c r="E31" s="246" t="n"/>
+      <c r="F31" s="246" t="n"/>
+      <c r="G31" s="246" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="144">
+      <c r="B32" s="242" t="inlineStr">
         <is>
           <t>Stored samples in window</t>
         </is>
       </c>
-      <c r="C32" s="239" t="inlineStr">
+      <c r="C32" s="241" t="inlineStr">
         <is>
           <t>after dedupe + store gate</t>
         </is>
       </c>
-      <c r="D32" s="242" t="n"/>
-      <c r="E32" s="242" t="n"/>
-      <c r="F32" s="242" t="n"/>
-      <c r="G32" s="242" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="143">
-      <c r="B33" s="240" t="inlineStr">
+      <c r="D32" s="244" t="n"/>
+      <c r="E32" s="244" t="n"/>
+      <c r="F32" s="244" t="n"/>
+      <c r="G32" s="244" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="144">
+      <c r="B33" s="242" t="inlineStr">
         <is>
           <t>Window elapsed</t>
         </is>
       </c>
-      <c r="C33" s="239" t="inlineStr">
+      <c r="C33" s="241" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D33" s="245" t="n"/>
-      <c r="E33" s="245" t="n"/>
-      <c r="F33" s="245" t="n"/>
-      <c r="G33" s="245" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="143">
-      <c r="B34" s="240" t="inlineStr">
+      <c r="D33" s="247" t="n"/>
+      <c r="E33" s="247" t="n"/>
+      <c r="F33" s="247" t="n"/>
+      <c r="G33" s="247" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="144">
+      <c r="B34" s="242" t="inlineStr">
         <is>
           <t>Warm-up gate</t>
         </is>
       </c>
-      <c r="C34" s="239" t="inlineStr">
+      <c r="C34" s="241" t="inlineStr">
         <is>
           <t>binding gate</t>
         </is>
       </c>
-      <c r="D34" s="241" t="n"/>
-      <c r="E34" s="241" t="n"/>
-      <c r="F34" s="241" t="n"/>
-      <c r="G34" s="241" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="143">
-      <c r="B35" s="240" t="inlineStr">
+      <c r="D34" s="243" t="n"/>
+      <c r="E34" s="243" t="n"/>
+      <c r="F34" s="243" t="n"/>
+      <c r="G34" s="243" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="144">
+      <c r="B35" s="242" t="inlineStr">
         <is>
           <t>Feed rate</t>
         </is>
       </c>
-      <c r="C35" s="239" t="inlineStr">
+      <c r="C35" s="241" t="inlineStr">
         <is>
           <t>quote CHANGES / min</t>
         </is>
       </c>
-      <c r="D35" s="246" t="n"/>
-      <c r="E35" s="246" t="n"/>
-      <c r="F35" s="246" t="n"/>
-      <c r="G35" s="246" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="143">
-      <c r="B36" s="240" t="inlineStr">
+      <c r="D35" s="248" t="n"/>
+      <c r="E35" s="248" t="n"/>
+      <c r="F35" s="248" t="n"/>
+      <c r="G35" s="248" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="144">
+      <c r="B36" s="242" t="inlineStr">
         <is>
           <t>Feed status</t>
         </is>
       </c>
-      <c r="C36" s="239" t="n"/>
-      <c r="D36" s="241" t="n"/>
-      <c r="E36" s="241" t="n"/>
-      <c r="F36" s="241" t="n"/>
-      <c r="G36" s="241" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="143">
-      <c r="B37" s="243" t="inlineStr">
+      <c r="C36" s="241" t="n"/>
+      <c r="D36" s="243" t="n"/>
+      <c r="E36" s="243" t="n"/>
+      <c r="F36" s="243" t="n"/>
+      <c r="G36" s="243" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="144">
+      <c r="B37" s="245" t="inlineStr">
         <is>
           <t>STATISTICS  (FROZEN - republished every STATS_REFRESH_MIN)</t>
         </is>
       </c>
-      <c r="C37" s="244" t="n"/>
-      <c r="D37" s="244" t="n"/>
-      <c r="E37" s="244" t="n"/>
-      <c r="F37" s="244" t="n"/>
-      <c r="G37" s="244" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="143">
-      <c r="B38" s="240" t="inlineStr">
+      <c r="C37" s="246" t="n"/>
+      <c r="D37" s="246" t="n"/>
+      <c r="E37" s="246" t="n"/>
+      <c r="F37" s="246" t="n"/>
+      <c r="G37" s="246" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="144">
+      <c r="B38" s="242" t="inlineStr">
         <is>
           <t>Mean (frozen)</t>
         </is>
       </c>
-      <c r="C38" s="239" t="n"/>
-      <c r="D38" s="238" t="n"/>
-      <c r="E38" s="238" t="n"/>
-      <c r="F38" s="238" t="n"/>
-      <c r="G38" s="238" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="143">
-      <c r="B39" s="240" t="inlineStr">
+      <c r="C38" s="241" t="n"/>
+      <c r="D38" s="240" t="n"/>
+      <c r="E38" s="240" t="n"/>
+      <c r="F38" s="240" t="n"/>
+      <c r="G38" s="240" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="144">
+      <c r="B39" s="242" t="inlineStr">
         <is>
           <t>Std Dev (frozen)</t>
         </is>
       </c>
-      <c r="C39" s="239" t="n"/>
-      <c r="D39" s="238" t="n"/>
-      <c r="E39" s="238" t="n"/>
-      <c r="F39" s="238" t="n"/>
-      <c r="G39" s="238" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="143">
-      <c r="B40" s="240" t="inlineStr">
+      <c r="C39" s="241" t="n"/>
+      <c r="D39" s="240" t="n"/>
+      <c r="E39" s="240" t="n"/>
+      <c r="F39" s="240" t="n"/>
+      <c r="G39" s="240" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="144">
+      <c r="B40" s="242" t="inlineStr">
         <is>
           <t>Std Dev in dollars</t>
         </is>
       </c>
-      <c r="C40" s="239" t="inlineStr">
+      <c r="C40" s="241" t="inlineStr">
         <is>
           <t>sigma x USD/pt x LOTS</t>
         </is>
       </c>
-      <c r="D40" s="247" t="n"/>
-      <c r="E40" s="247" t="n"/>
-      <c r="F40" s="247" t="n"/>
-      <c r="G40" s="247" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="143">
-      <c r="B41" s="240" t="inlineStr">
+      <c r="D40" s="249" t="n"/>
+      <c r="E40" s="249" t="n"/>
+      <c r="F40" s="249" t="n"/>
+      <c r="G40" s="249" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="144">
+      <c r="B41" s="242" t="inlineStr">
         <is>
           <t>Stats age / next refresh</t>
         </is>
       </c>
-      <c r="C41" s="239" t="inlineStr">
+      <c r="C41" s="241" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D41" s="241" t="n"/>
-      <c r="E41" s="241" t="n"/>
-      <c r="F41" s="241" t="n"/>
-      <c r="G41" s="241" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="143">
-      <c r="B42" s="248" t="inlineStr">
+      <c r="D41" s="243" t="n"/>
+      <c r="E41" s="243" t="n"/>
+      <c r="F41" s="243" t="n"/>
+      <c r="G41" s="243" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="144">
+      <c r="B42" s="250" t="inlineStr">
         <is>
           <t>Z  (live, vs frozen mean &amp; sigma)</t>
         </is>
       </c>
-      <c r="C42" s="239" t="n"/>
-      <c r="D42" s="249" t="n"/>
-      <c r="E42" s="249" t="n"/>
-      <c r="F42" s="249" t="n"/>
-      <c r="G42" s="249" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="143">
-      <c r="B43" s="248" t="inlineStr">
+      <c r="C42" s="241" t="n"/>
+      <c r="D42" s="251" t="n"/>
+      <c r="E42" s="251" t="n"/>
+      <c r="F42" s="251" t="n"/>
+      <c r="G42" s="251" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="144">
+      <c r="B43" s="250" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="C43" s="239" t="n"/>
-      <c r="D43" s="250" t="n"/>
-      <c r="E43" s="250" t="n"/>
-      <c r="F43" s="250" t="n"/>
-      <c r="G43" s="250" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="143">
-      <c r="B44" s="243" t="inlineStr">
+      <c r="C43" s="241" t="n"/>
+      <c r="D43" s="252" t="n"/>
+      <c r="E43" s="252" t="n"/>
+      <c r="F43" s="252" t="n"/>
+      <c r="G43" s="252" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="144">
+      <c r="B44" s="245" t="inlineStr">
         <is>
           <t>COST OF THE ROUND TRIP</t>
         </is>
       </c>
-      <c r="C44" s="244" t="n"/>
-      <c r="D44" s="244" t="n"/>
-      <c r="E44" s="244" t="n"/>
-      <c r="F44" s="244" t="n"/>
-      <c r="G44" s="244" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="143">
-      <c r="B45" s="240" t="inlineStr">
+      <c r="C44" s="246" t="n"/>
+      <c r="D44" s="246" t="n"/>
+      <c r="E44" s="246" t="n"/>
+      <c r="F44" s="246" t="n"/>
+      <c r="G44" s="246" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="144">
+      <c r="B45" s="242" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C45" s="239" t="n"/>
-      <c r="D45" s="241" t="n"/>
-      <c r="E45" s="241" t="n"/>
-      <c r="F45" s="241" t="n"/>
-      <c r="G45" s="241" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="143">
-      <c r="B46" s="240" t="inlineStr">
+      <c r="C45" s="241" t="n"/>
+      <c r="D45" s="243" t="n"/>
+      <c r="E45" s="243" t="n"/>
+      <c r="F45" s="243" t="n"/>
+      <c r="G45" s="243" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="144">
+      <c r="B46" s="242" t="inlineStr">
         <is>
           <t>Entry reference (touch)</t>
         </is>
       </c>
-      <c r="C46" s="239" t="n"/>
-      <c r="D46" s="238" t="n"/>
-      <c r="E46" s="238" t="n"/>
-      <c r="F46" s="238" t="n"/>
-      <c r="G46" s="238" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="143">
-      <c r="B47" s="240" t="inlineStr">
+      <c r="C46" s="241" t="n"/>
+      <c r="D46" s="240" t="n"/>
+      <c r="E46" s="240" t="n"/>
+      <c r="F46" s="240" t="n"/>
+      <c r="G46" s="240" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="144">
+      <c r="B47" s="242" t="inlineStr">
         <is>
           <t>Commission</t>
         </is>
       </c>
-      <c r="C47" s="239" t="inlineStr">
+      <c r="C47" s="241" t="inlineStr">
         <is>
           <t>contracts x rate x LOTS</t>
         </is>
       </c>
-      <c r="D47" s="247" t="n"/>
-      <c r="E47" s="247" t="n"/>
-      <c r="F47" s="247" t="n"/>
-      <c r="G47" s="247" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="143">
-      <c r="B48" s="240" t="inlineStr">
+      <c r="D47" s="249" t="n"/>
+      <c r="E47" s="249" t="n"/>
+      <c r="F47" s="249" t="n"/>
+      <c r="G47" s="249" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="144">
+      <c r="B48" s="242" t="inlineStr">
         <is>
           <t>Crossing cost - LEGGING</t>
         </is>
       </c>
-      <c r="C48" s="239" t="n"/>
-      <c r="D48" s="247" t="n"/>
-      <c r="E48" s="247" t="n"/>
-      <c r="F48" s="247" t="n"/>
-      <c r="G48" s="247" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="143">
-      <c r="B49" s="240" t="inlineStr">
+      <c r="C48" s="241" t="n"/>
+      <c r="D48" s="249" t="n"/>
+      <c r="E48" s="249" t="n"/>
+      <c r="F48" s="249" t="n"/>
+      <c r="G48" s="249" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="144">
+      <c r="B49" s="242" t="inlineStr">
         <is>
           <t>Crossing cost - LISTED</t>
         </is>
       </c>
-      <c r="C49" s="239" t="n"/>
-      <c r="D49" s="247" t="n"/>
-      <c r="E49" s="247" t="n"/>
-      <c r="F49" s="247" t="n"/>
-      <c r="G49" s="247" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="143">
-      <c r="B50" s="248" t="inlineStr">
+      <c r="C49" s="241" t="n"/>
+      <c r="D49" s="249" t="n"/>
+      <c r="E49" s="249" t="n"/>
+      <c r="F49" s="249" t="n"/>
+      <c r="G49" s="249" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="144">
+      <c r="B50" s="250" t="inlineStr">
         <is>
           <t>TOTAL COST (this mode)</t>
         </is>
       </c>
-      <c r="C50" s="239" t="n"/>
-      <c r="D50" s="251" t="n"/>
-      <c r="E50" s="251" t="n"/>
-      <c r="F50" s="251" t="n"/>
-      <c r="G50" s="251" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="143">
-      <c r="B51" s="243" t="inlineStr">
+      <c r="C50" s="241" t="n"/>
+      <c r="D50" s="253" t="n"/>
+      <c r="E50" s="253" t="n"/>
+      <c r="F50" s="253" t="n"/>
+      <c r="G50" s="253" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="144">
+      <c r="B51" s="245" t="inlineStr">
         <is>
           <t>TAKE PROFIT  (exits act on MONEY, never on z)</t>
         </is>
       </c>
-      <c r="C51" s="244" t="n"/>
-      <c r="D51" s="244" t="n"/>
-      <c r="E51" s="244" t="n"/>
-      <c r="F51" s="244" t="n"/>
-      <c r="G51" s="244" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="143">
-      <c r="B52" s="240" t="inlineStr">
+      <c r="C51" s="246" t="n"/>
+      <c r="D51" s="246" t="n"/>
+      <c r="E51" s="246" t="n"/>
+      <c r="F51" s="246" t="n"/>
+      <c r="G51" s="246" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="144">
+      <c r="B52" s="242" t="inlineStr">
         <is>
           <t>TP rule in force</t>
         </is>
       </c>
-      <c r="C52" s="239" t="n"/>
-      <c r="D52" s="241" t="n"/>
-      <c r="E52" s="241" t="n"/>
-      <c r="F52" s="241" t="n"/>
-      <c r="G52" s="241" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="143">
-      <c r="B53" s="240" t="inlineStr">
+      <c r="C52" s="241" t="n"/>
+      <c r="D52" s="243" t="n"/>
+      <c r="E52" s="243" t="n"/>
+      <c r="F52" s="243" t="n"/>
+      <c r="G52" s="243" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="144">
+      <c r="B53" s="242" t="inlineStr">
         <is>
           <t>Notional (per NOTIONAL_BASIS)</t>
         </is>
       </c>
-      <c r="C53" s="239" t="n"/>
-      <c r="D53" s="247" t="n"/>
-      <c r="E53" s="247" t="n"/>
-      <c r="F53" s="247" t="n"/>
-      <c r="G53" s="247" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="143">
-      <c r="B54" s="240" t="inlineStr">
+      <c r="C53" s="241" t="n"/>
+      <c r="D53" s="249" t="n"/>
+      <c r="E53" s="249" t="n"/>
+      <c r="F53" s="249" t="n"/>
+      <c r="G53" s="249" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="144">
+      <c r="B54" s="242" t="inlineStr">
         <is>
           <t>Win target (WIN_PCT x notional)</t>
         </is>
       </c>
-      <c r="C54" s="239" t="n"/>
-      <c r="D54" s="247" t="n"/>
-      <c r="E54" s="247" t="n"/>
-      <c r="F54" s="247" t="n"/>
-      <c r="G54" s="247" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="143">
-      <c r="B55" s="240" t="inlineStr">
+      <c r="C54" s="241" t="n"/>
+      <c r="D54" s="249" t="n"/>
+      <c r="E54" s="249" t="n"/>
+      <c r="F54" s="249" t="n"/>
+      <c r="G54" s="249" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="144">
+      <c r="B55" s="242" t="inlineStr">
         <is>
           <t>Costs in spread units</t>
         </is>
       </c>
-      <c r="C55" s="239" t="n"/>
-      <c r="D55" s="238" t="n"/>
-      <c r="E55" s="238" t="n"/>
-      <c r="F55" s="238" t="n"/>
-      <c r="G55" s="238" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="143">
-      <c r="B56" s="240" t="inlineStr">
+      <c r="C55" s="241" t="n"/>
+      <c r="D55" s="240" t="n"/>
+      <c r="E55" s="240" t="n"/>
+      <c r="F55" s="240" t="n"/>
+      <c r="G55" s="240" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="144">
+      <c r="B56" s="242" t="inlineStr">
         <is>
           <t>Win in spread units</t>
         </is>
       </c>
-      <c r="C56" s="239" t="n"/>
-      <c r="D56" s="238" t="n"/>
-      <c r="E56" s="238" t="n"/>
-      <c r="F56" s="238" t="n"/>
-      <c r="G56" s="238" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="143">
-      <c r="B57" s="240" t="inlineStr">
+      <c r="C56" s="241" t="n"/>
+      <c r="D56" s="240" t="n"/>
+      <c r="E56" s="240" t="n"/>
+      <c r="F56" s="240" t="n"/>
+      <c r="G56" s="240" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="144">
+      <c r="B57" s="242" t="inlineStr">
         <is>
           <t>Break-even spread</t>
         </is>
       </c>
-      <c r="C57" s="239" t="inlineStr">
+      <c r="C57" s="241" t="inlineStr">
         <is>
           <t>absolute level</t>
         </is>
       </c>
-      <c r="D57" s="238" t="n"/>
-      <c r="E57" s="238" t="n"/>
-      <c r="F57" s="238" t="n"/>
-      <c r="G57" s="238" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="143">
-      <c r="B58" s="248" t="inlineStr">
+      <c r="D57" s="240" t="n"/>
+      <c r="E57" s="240" t="n"/>
+      <c r="F57" s="240" t="n"/>
+      <c r="G57" s="240" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="144">
+      <c r="B58" s="250" t="inlineStr">
         <is>
           <t>TAKE-PROFIT spread</t>
         </is>
       </c>
-      <c r="C58" s="239" t="inlineStr">
+      <c r="C58" s="241" t="inlineStr">
         <is>
           <t>absolute level</t>
         </is>
       </c>
-      <c r="D58" s="252" t="n"/>
-      <c r="E58" s="252" t="n"/>
-      <c r="F58" s="252" t="n"/>
-      <c r="G58" s="252" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="143">
-      <c r="B59" s="240" t="inlineStr">
+      <c r="D58" s="254" t="n"/>
+      <c r="E58" s="254" t="n"/>
+      <c r="F58" s="254" t="n"/>
+      <c r="G58" s="254" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="144">
+      <c r="B59" s="242" t="inlineStr">
         <is>
           <t>TP distance</t>
         </is>
       </c>
-      <c r="C59" s="239" t="inlineStr">
+      <c r="C59" s="241" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D59" s="238" t="n"/>
-      <c r="E59" s="238" t="n"/>
-      <c r="F59" s="238" t="n"/>
-      <c r="G59" s="238" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="143">
-      <c r="B60" s="240" t="inlineStr">
+      <c r="D59" s="240" t="n"/>
+      <c r="E59" s="240" t="n"/>
+      <c r="F59" s="240" t="n"/>
+      <c r="G59" s="240" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="144">
+      <c r="B60" s="242" t="inlineStr">
         <is>
           <t>TP in sigma</t>
         </is>
       </c>
-      <c r="C60" s="239" t="inlineStr">
+      <c r="C60" s="241" t="inlineStr">
         <is>
           <t>x sigma</t>
         </is>
       </c>
-      <c r="D60" s="245" t="n"/>
-      <c r="E60" s="245" t="n"/>
-      <c r="F60" s="245" t="n"/>
-      <c r="G60" s="245" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="143">
-      <c r="B61" s="240" t="inlineStr">
+      <c r="D60" s="247" t="n"/>
+      <c r="E60" s="247" t="n"/>
+      <c r="F60" s="247" t="n"/>
+      <c r="G60" s="247" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="144">
+      <c r="B61" s="242" t="inlineStr">
         <is>
           <t>Target z</t>
         </is>
       </c>
-      <c r="C61" s="239" t="inlineStr">
+      <c r="C61" s="241" t="inlineStr">
         <is>
           <t>z at the TP level</t>
         </is>
       </c>
-      <c r="D61" s="245" t="n"/>
-      <c r="E61" s="245" t="n"/>
-      <c r="F61" s="245" t="n"/>
-      <c r="G61" s="245" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="143">
-      <c r="B62" s="240" t="inlineStr">
+      <c r="D61" s="247" t="n"/>
+      <c r="E61" s="247" t="n"/>
+      <c r="F61" s="247" t="n"/>
+      <c r="G61" s="247" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="144">
+      <c r="B62" s="242" t="inlineStr">
         <is>
           <t>TP beyond the mean?</t>
         </is>
       </c>
-      <c r="C62" s="239" t="n"/>
-      <c r="D62" s="241" t="n"/>
-      <c r="E62" s="241" t="n"/>
-      <c r="F62" s="241" t="n"/>
-      <c r="G62" s="241" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="143">
-      <c r="B63" s="243" t="inlineStr">
+      <c r="C62" s="241" t="n"/>
+      <c r="D62" s="243" t="n"/>
+      <c r="E62" s="243" t="n"/>
+      <c r="F62" s="243" t="n"/>
+      <c r="G62" s="243" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="144">
+      <c r="B63" s="245" t="inlineStr">
         <is>
           <t>EDGE FILTER  (a separate gate from ENTRY_Z)</t>
         </is>
       </c>
-      <c r="C63" s="244" t="n"/>
-      <c r="D63" s="244" t="n"/>
-      <c r="E63" s="244" t="n"/>
-      <c r="F63" s="244" t="n"/>
-      <c r="G63" s="244" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="143">
-      <c r="B64" s="240" t="inlineStr">
+      <c r="C63" s="246" t="n"/>
+      <c r="D63" s="246" t="n"/>
+      <c r="E63" s="246" t="n"/>
+      <c r="F63" s="246" t="n"/>
+      <c r="G63" s="246" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="144">
+      <c r="B64" s="242" t="inlineStr">
         <is>
           <t>Expected capture</t>
         </is>
       </c>
-      <c r="C64" s="239" t="inlineStr">
+      <c r="C64" s="241" t="inlineStr">
         <is>
           <t>0.5 x |z| x sigma x USD/pt x LOTS</t>
         </is>
       </c>
-      <c r="D64" s="247" t="n"/>
-      <c r="E64" s="247" t="n"/>
-      <c r="F64" s="247" t="n"/>
-      <c r="G64" s="247" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="143">
-      <c r="B65" s="240" t="inlineStr">
+      <c r="D64" s="249" t="n"/>
+      <c r="E64" s="249" t="n"/>
+      <c r="F64" s="249" t="n"/>
+      <c r="G64" s="249" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="144">
+      <c r="B65" s="242" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C65" s="239" t="inlineStr">
+      <c r="C65" s="241" t="inlineStr">
         <is>
           <t>EDGE_MULTIPLE x total cost</t>
         </is>
       </c>
-      <c r="D65" s="247" t="n"/>
-      <c r="E65" s="247" t="n"/>
-      <c r="F65" s="247" t="n"/>
-      <c r="G65" s="247" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="143">
-      <c r="B66" s="248" t="inlineStr">
+      <c r="D65" s="249" t="n"/>
+      <c r="E65" s="249" t="n"/>
+      <c r="F65" s="249" t="n"/>
+      <c r="G65" s="249" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="144">
+      <c r="B66" s="250" t="inlineStr">
         <is>
           <t>EDGE VERDICT</t>
         </is>
       </c>
-      <c r="C66" s="239" t="n"/>
-      <c r="D66" s="250" t="n"/>
-      <c r="E66" s="250" t="n"/>
-      <c r="F66" s="250" t="n"/>
-      <c r="G66" s="250" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="143">
-      <c r="B67" s="240" t="inlineStr">
+      <c r="C66" s="241" t="n"/>
+      <c r="D66" s="252" t="n"/>
+      <c r="E66" s="252" t="n"/>
+      <c r="F66" s="252" t="n"/>
+      <c r="G66" s="252" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="144">
+      <c r="B67" s="242" t="inlineStr">
         <is>
           <t>Min sigma to pass at live z</t>
         </is>
       </c>
-      <c r="C67" s="239" t="inlineStr">
+      <c r="C67" s="241" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D67" s="238" t="n"/>
-      <c r="E67" s="238" t="n"/>
-      <c r="F67" s="238" t="n"/>
-      <c r="G67" s="238" t="n"/>
+      <c r="D67" s="240" t="n"/>
+      <c r="E67" s="240" t="n"/>
+      <c r="F67" s="240" t="n"/>
+      <c r="G67" s="240" t="n"/>
     </row>
     <row r="68"/>
-    <row r="69" ht="15" customHeight="1" s="143">
-      <c r="B69" s="253" t="inlineStr">
+    <row r="69" ht="15" customHeight="1" s="144">
+      <c r="B69" s="255" t="inlineStr">
         <is>
           <t>The EDGE FILTER is a different gate from ENTRY_Z. ENTRY_Z decides when the chime fires; the edge filter asks whether the expected capture clears the round trip by EDGE_MULTIPLE. A highlighted z that fails the edge filter is still not a trade worth taking.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="143">
-      <c r="B70" s="231" t="inlineStr">
+    <row r="70" ht="15" customHeight="1" s="144">
+      <c r="B70" s="233" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES on Config decides whether a failing edge filter also silences the chime. It ships FALSE, so the chime follows ENTRY_Z alone.</t>
         </is>
@@ -3863,1702 +3874,1702 @@
   <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="141" min="1" max="1"/>
-    <col width="34" customWidth="1" style="141" min="2" max="2"/>
-    <col width="14" customWidth="1" style="141" min="3" max="3"/>
-    <col width="10" customWidth="1" style="141" min="4" max="4"/>
-    <col width="96" customWidth="1" style="141" min="5" max="5"/>
-    <col width="30" customWidth="1" style="141" min="6" max="6"/>
-    <col width="12" customWidth="1" style="141" min="7" max="8"/>
-    <col width="10" customWidth="1" style="141" min="9" max="9"/>
-    <col width="8" customWidth="1" style="141" min="10" max="10"/>
-    <col width="34" customWidth="1" style="141" min="11" max="11"/>
+    <col width="30" customWidth="1" style="142" min="1" max="1"/>
+    <col width="34" customWidth="1" style="142" min="2" max="2"/>
+    <col width="14" customWidth="1" style="142" min="3" max="3"/>
+    <col width="10" customWidth="1" style="142" min="4" max="4"/>
+    <col width="96" customWidth="1" style="142" min="5" max="5"/>
+    <col width="30" customWidth="1" style="142" min="6" max="6"/>
+    <col width="12" customWidth="1" style="142" min="7" max="8"/>
+    <col width="10" customWidth="1" style="142" min="9" max="9"/>
+    <col width="8" customWidth="1" style="142" min="10" max="10"/>
+    <col width="34" customWidth="1" style="142" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.7" customHeight="1" s="143">
-      <c r="A1" s="254" t="inlineStr">
+    <row r="1" ht="19.7" customHeight="1" s="144">
+      <c r="A1" s="256" t="inlineStr">
         <is>
           <t>CONFIG  -  every parameter in its own labelled cell</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="143">
-      <c r="A2" s="255" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="144">
+      <c r="A2" s="257" t="inlineStr">
         <is>
           <t>LEGEND:  yellow / blue = EDIT THESE.  black = formula, do not edit.  A changed value takes effect on the NEXT TIMER TICK - no restart, no VBA edit.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="143">
-      <c r="A3" s="231" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="144">
+      <c r="A3" s="233" t="inlineStr">
         <is>
           <t>Exception: LOOKBACK_MIN redefines the window, so stored history is re-evaluated against the new width on the next stats refresh and the warm-up gates re-apply.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="143">
-      <c r="A4" s="231" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="144">
+      <c r="A4" s="233" t="inlineStr">
         <is>
           <t>VBA finds a parameter by matching column A exactly, so you may insert or reorder rows freely - but never rename a parameter in column A.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="143">
-      <c r="A5" s="255" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="144">
+      <c r="A5" s="257" t="inlineStr">
         <is>
           <t>FOUR DECOUPLED RATES:  CAPTURE_MS (poll for a changed quote)  &gt;  STORE_MIN_INTERVAL_MS (what reaches the window)  &gt;  PRICE_REFRESH_MS (what repaints)  &gt;  STATS_REFRESH_MIN (when mean and sigma are republished).  Capturing fast buys alert latency, not a better sigma.</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="7" ht="15" customHeight="1" s="143">
-      <c r="A7" s="256" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="144">
+      <c r="A7" s="258" t="inlineStr">
         <is>
           <t>ENGINE  /  SAMPLING</t>
         </is>
       </c>
-      <c r="B7" s="256" t="n"/>
-      <c r="C7" s="256" t="n"/>
-      <c r="D7" s="256" t="n"/>
-      <c r="E7" s="256" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="143">
-      <c r="A8" s="257" t="inlineStr">
+      <c r="B7" s="258" t="n"/>
+      <c r="C7" s="258" t="n"/>
+      <c r="D7" s="258" t="n"/>
+      <c r="E7" s="258" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="144">
+      <c r="A8" s="259" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B8" s="257" t="inlineStr">
+      <c r="B8" s="259" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C8" s="257" t="inlineStr">
+      <c r="C8" s="259" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D8" s="257" t="inlineStr">
+      <c r="D8" s="259" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E8" s="257" t="inlineStr">
+      <c r="E8" s="259" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="143">
-      <c r="A9" s="248" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="144">
+      <c r="A9" s="250" t="inlineStr">
         <is>
           <t>CAPTURE_MS</t>
         </is>
       </c>
-      <c r="B9" s="258" t="n">
+      <c r="B9" s="260" t="n">
         <v>100</v>
       </c>
-      <c r="C9" s="237" t="n">
+      <c r="C9" s="239" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="237" t="inlineStr">
+      <c r="D9" s="239" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E9" s="259" t="inlineStr">
+      <c r="E9" s="261" t="inlineStr">
         <is>
           <t>RATE 1 of 4. How often the feed is POLLED for a changed quote. Drives latency to the chime, NOT sigma - after dedupe the window holds quote changes, not poll ticks. Sub-second needs the user32 timer; at 1000+ the module falls back to Application.OnTime.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="143">
-      <c r="A10" s="248" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="144">
+      <c r="A10" s="250" t="inlineStr">
         <is>
           <t>STORE_MIN_INTERVAL_MS</t>
         </is>
       </c>
-      <c r="B10" s="258" t="n">
+      <c r="B10" s="260" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="237" t="n">
+      <c r="C10" s="239" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="237" t="inlineStr">
+      <c r="D10" s="239" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E10" s="259" t="inlineStr">
+      <c r="E10" s="261" t="inlineStr">
         <is>
           <t>RATE 2 of 4. Minimum spacing between STORED samples. 0 = full fidelity. Leave it at 0 for the first week or two to characterise the microstructure, then set 250-1000: subsampling a mean-reverting level series is unbiased, so it is 3-10x less memory for the same mean and sigma.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="143">
-      <c r="A11" s="248" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="144">
+      <c r="A11" s="250" t="inlineStr">
         <is>
           <t>PRICE_REFRESH_MS</t>
         </is>
       </c>
-      <c r="B11" s="258" t="n">
+      <c r="B11" s="260" t="n">
         <v>500</v>
       </c>
-      <c r="C11" s="237" t="n">
+      <c r="C11" s="239" t="n">
         <v>500</v>
       </c>
-      <c r="D11" s="237" t="inlineStr">
+      <c r="D11" s="239" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E11" s="259" t="inlineStr">
+      <c r="E11" s="261" t="inlineStr">
         <is>
           <t>RATE 3 of 4. How often the display may repaint. Independent of capture and of storage - a number showing more digits than the market moves in will appear to change constantly.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="143">
-      <c r="A12" s="248" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="144">
+      <c r="A12" s="250" t="inlineStr">
         <is>
           <t>CONFIG_REFRESH_MS</t>
         </is>
       </c>
-      <c r="B12" s="258" t="n">
+      <c r="B12" s="260" t="n">
         <v>1000</v>
       </c>
-      <c r="C12" s="237" t="n">
+      <c r="C12" s="239" t="n">
         <v>1000</v>
       </c>
-      <c r="D12" s="237" t="inlineStr">
+      <c r="D12" s="239" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E12" s="259" t="inlineStr">
+      <c r="E12" s="261" t="inlineStr">
         <is>
           <t>How often this sheet is re-read. A value changed here takes effect within this long - no restart, no VBA edit.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="143">
-      <c r="A13" s="248" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="144">
+      <c r="A13" s="250" t="inlineStr">
         <is>
           <t>RTD_THROTTLE_MS</t>
         </is>
       </c>
-      <c r="B13" s="258" t="n">
+      <c r="B13" s="260" t="n">
         <v>100</v>
       </c>
-      <c r="C13" s="237" t="n">
+      <c r="C13" s="239" t="n">
         <v>100</v>
       </c>
-      <c r="D13" s="237" t="inlineStr">
+      <c r="D13" s="239" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E13" s="259" t="inlineStr">
+      <c r="E13" s="261" t="inlineStr">
         <is>
           <t>Application.RTD.ThrottleInterval set on start. Match it to CAPTURE_MS. Excel's default is 2000.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="143">
-      <c r="A14" s="248" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="144">
+      <c r="A14" s="250" t="inlineStr">
         <is>
           <t>WATCHDOG_SEC</t>
         </is>
       </c>
-      <c r="B14" s="258" t="n">
+      <c r="B14" s="260" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="237" t="n">
+      <c r="C14" s="239" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="237" t="inlineStr">
+      <c r="D14" s="239" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E14" s="259" t="inlineStr">
+      <c r="E14" s="261" t="inlineStr">
         <is>
           <t>Application.OnTime watchdog. Re-arms the high-resolution timer if Excel killed it (a modal dialog will) and picks up a changed CAPTURE_MS.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="143">
-      <c r="A15" s="248" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="144">
+      <c r="A15" s="250" t="inlineStr">
         <is>
           <t>STALE_SEC</t>
         </is>
       </c>
-      <c r="B15" s="258" t="n">
+      <c r="B15" s="260" t="n">
         <v>15</v>
       </c>
-      <c r="C15" s="237" t="n">
+      <c r="C15" s="239" t="n">
         <v>15</v>
       </c>
-      <c r="D15" s="237" t="inlineStr">
+      <c r="D15" s="239" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E15" s="259" t="inlineStr">
+      <c r="E15" s="261" t="inlineStr">
         <is>
           <t>No new quote id for this long =&gt; feed marked STALE and alerts go silent.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="143">
-      <c r="A16" s="248" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="144">
+      <c r="A16" s="250" t="inlineStr">
         <is>
           <t>FLUSH_SEC</t>
         </is>
       </c>
-      <c r="B16" s="258" t="n">
+      <c r="B16" s="260" t="n">
         <v>60</v>
       </c>
-      <c r="C16" s="237" t="n">
+      <c r="C16" s="239" t="n">
         <v>60</v>
       </c>
-      <c r="D16" s="237" t="inlineStr">
+      <c r="D16" s="239" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E16" s="259" t="inlineStr">
+      <c r="E16" s="261" t="inlineStr">
         <is>
           <t>How often the recovery snapshot is written to the hidden Buffer sheet.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="143">
-      <c r="A17" s="248" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="144">
+      <c r="A17" s="250" t="inlineStr">
         <is>
           <t>FLUSH_DECIMATE_MS</t>
         </is>
       </c>
-      <c r="B17" s="258" t="n">
+      <c r="B17" s="260" t="n">
         <v>1000</v>
       </c>
-      <c r="C17" s="237" t="n">
+      <c r="C17" s="239" t="n">
         <v>1000</v>
       </c>
-      <c r="D17" s="237" t="inlineStr">
+      <c r="D17" s="239" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E17" s="259" t="inlineStr">
+      <c r="E17" s="261" t="inlineStr">
         <is>
           <t>The recovery snapshot is decimated to this spacing. Unbiased for mean and sigma, and it keeps a 120-minute window near 7,200 rows instead of tens of thousands.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="143">
-      <c r="A18" s="248" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="144">
+      <c r="A18" s="250" t="inlineStr">
         <is>
           <t>BUFFER_CAPACITY</t>
         </is>
       </c>
-      <c r="B18" s="258" t="n">
+      <c r="B18" s="260" t="n">
         <v>80000</v>
       </c>
-      <c r="C18" s="237" t="n">
+      <c r="C18" s="239" t="n">
         <v>80000</v>
       </c>
-      <c r="D18" s="237" t="inlineStr">
+      <c r="D18" s="239" t="inlineStr">
         <is>
           <t>samples</t>
         </is>
       </c>
-      <c r="E18" s="259" t="inlineStr">
+      <c r="E18" s="261" t="inlineStr">
         <is>
           <t>Circular-buffer capacity per spread. 4 spreads x 80,000 x 16 bytes is about 5 MB of VBA array, held in memory, not in cells.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="143">
-      <c r="A19" s="248" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="144">
+      <c r="A19" s="250" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_ENABLED</t>
         </is>
       </c>
-      <c r="B19" s="258" t="b">
+      <c r="B19" s="260" t="b">
         <v>1</v>
       </c>
-      <c r="C19" s="237" t="b">
+      <c r="C19" s="239" t="b">
         <v>1</v>
       </c>
-      <c r="D19" s="237" t="inlineStr">
+      <c r="D19" s="239" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E19" s="259" t="inlineStr">
+      <c r="E19" s="261" t="inlineStr">
         <is>
           <t>Write every CHANGED quote to a CSV on disk. This is the one chance to characterise the spread's microstructure and to verify that coarser storage loses nothing real. Turn it off once STORE_MIN_INTERVAL_MS is set.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="143">
-      <c r="A20" s="248" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="144">
+      <c r="A20" s="250" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_PATH</t>
         </is>
       </c>
-      <c r="B20" s="260" t="n"/>
-      <c r="C20" s="237" t="n"/>
-      <c r="D20" s="237" t="inlineStr">
+      <c r="B20" s="262" t="n"/>
+      <c r="C20" s="239" t="n"/>
+      <c r="D20" s="239" t="inlineStr">
         <is>
           <t>folder</t>
         </is>
       </c>
-      <c r="E20" s="259" t="inlineStr">
+      <c r="E20" s="261" t="inlineStr">
         <is>
           <t>Folder for the tick CSVs. Blank = a 'ticks' folder beside the workbook. One file per spread per day.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="143">
-      <c r="A21" s="248" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="144">
+      <c r="A21" s="250" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_BATCH</t>
         </is>
       </c>
-      <c r="B21" s="258" t="n">
+      <c r="B21" s="260" t="n">
         <v>500</v>
       </c>
-      <c r="C21" s="237" t="n">
+      <c r="C21" s="239" t="n">
         <v>500</v>
       </c>
-      <c r="D21" s="237" t="inlineStr">
+      <c r="D21" s="239" t="inlineStr">
         <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="E21" s="259" t="inlineStr">
+      <c r="E21" s="261" t="inlineStr">
         <is>
           <t>Lines buffered in memory before a file write, so archiving never stalls the capture timer.</t>
         </is>
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="15" customHeight="1" s="143">
-      <c r="A23" s="256" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="144">
+      <c r="A23" s="258" t="inlineStr">
         <is>
           <t>WINDOW  /  STATISTICS</t>
         </is>
       </c>
-      <c r="B23" s="256" t="n"/>
-      <c r="C23" s="256" t="n"/>
-      <c r="D23" s="256" t="n"/>
-      <c r="E23" s="256" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="143">
-      <c r="A24" s="257" t="inlineStr">
+      <c r="B23" s="258" t="n"/>
+      <c r="C23" s="258" t="n"/>
+      <c r="D23" s="258" t="n"/>
+      <c r="E23" s="258" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="144">
+      <c r="A24" s="259" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B24" s="257" t="inlineStr">
+      <c r="B24" s="259" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C24" s="257" t="inlineStr">
+      <c r="C24" s="259" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D24" s="257" t="inlineStr">
+      <c r="D24" s="259" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E24" s="257" t="inlineStr">
+      <c r="E24" s="259" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="143">
-      <c r="A25" s="248" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="144">
+      <c r="A25" s="250" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="B25" s="258" t="n">
+      <c r="B25" s="260" t="n">
         <v>120</v>
       </c>
-      <c r="C25" s="237" t="n">
+      <c r="C25" s="239" t="n">
         <v>120</v>
       </c>
-      <c r="D25" s="237" t="inlineStr">
+      <c r="D25" s="239" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E25" s="259" t="inlineStr">
+      <c r="E25" s="261" t="inlineStr">
         <is>
           <t>Rolling window width (90 or 120). Changing it re-evaluates stored history on the next stats refresh and re-applies the warm-up gates.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="143">
-      <c r="A26" s="248" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="144">
+      <c r="A26" s="250" t="inlineStr">
         <is>
           <t>STATS_REFRESH_MIN</t>
         </is>
       </c>
-      <c r="B26" s="258" t="n">
+      <c r="B26" s="260" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="237" t="n">
+      <c r="C26" s="239" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="237" t="inlineStr">
+      <c r="D26" s="239" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E26" s="259" t="inlineStr">
+      <c r="E26" s="261" t="inlineStr">
         <is>
           <t>How often mean/sigma are recomputed and re-published. Held FROZEN in between; live z is measured against the frozen values.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="143">
-      <c r="A27" s="248" t="inlineStr">
+    <row r="27" ht="15" customHeight="1" s="144">
+      <c r="A27" s="250" t="inlineStr">
         <is>
           <t>MIN_SAMPLES</t>
         </is>
       </c>
-      <c r="B27" s="258" t="n">
+      <c r="B27" s="260" t="n">
         <v>300</v>
       </c>
-      <c r="C27" s="237" t="n">
+      <c r="C27" s="239" t="n">
         <v>300</v>
       </c>
-      <c r="D27" s="237" t="inlineStr">
+      <c r="D27" s="239" t="inlineStr">
         <is>
           <t>quotes</t>
         </is>
       </c>
-      <c r="E27" s="259" t="inlineStr">
+      <c r="E27" s="261" t="inlineStr">
         <is>
           <t>Warm-up gate 1. Quotes needed before any z is shown.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="143">
-      <c r="A28" s="248" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="144">
+      <c r="A28" s="250" t="inlineStr">
         <is>
           <t>MIN_HISTORY_MIN</t>
         </is>
       </c>
-      <c r="B28" s="258" t="n">
+      <c r="B28" s="260" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="237" t="n">
+      <c r="C28" s="239" t="n">
         <v>120</v>
       </c>
-      <c r="D28" s="237" t="inlineStr">
+      <c r="D28" s="239" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E28" s="259" t="inlineStr">
+      <c r="E28" s="261" t="inlineStr">
         <is>
           <t>Warm-up gate 2. Elapsed collection needed before any z is shown. BOTH gates must pass.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="143">
-      <c r="A29" s="248" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="144">
+      <c r="A29" s="250" t="inlineStr">
         <is>
           <t>MIN_SIGMA</t>
         </is>
       </c>
-      <c r="B29" s="258" t="n">
+      <c r="B29" s="260" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="237" t="n">
+      <c r="C29" s="239" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="237" t="inlineStr">
+      <c r="D29" s="239" t="inlineStr">
         <is>
           <t>spread</t>
         </is>
       </c>
-      <c r="E29" s="259" t="inlineStr">
+      <c r="E29" s="261" t="inlineStr">
         <is>
           <t>Sigma floor. Below this the window is degenerate and NO z is shown. Set once sigma has actually been measured.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="143">
-      <c r="A30" s="248" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="144">
+      <c r="A30" s="250" t="inlineStr">
         <is>
           <t>MAX_ABS_Z</t>
         </is>
       </c>
-      <c r="B30" s="258" t="n">
+      <c r="B30" s="260" t="n">
         <v>25</v>
       </c>
-      <c r="C30" s="237" t="n">
+      <c r="C30" s="239" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="237" t="inlineStr">
+      <c r="D30" s="239" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E30" s="259" t="inlineStr">
+      <c r="E30" s="261" t="inlineStr">
         <is>
           <t>Absurd-z guard. Above this, show 'no usable z' rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="31"/>
-    <row r="32" ht="15" customHeight="1" s="143">
-      <c r="A32" s="256" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="144">
+      <c r="A32" s="258" t="inlineStr">
         <is>
           <t>SIGNAL THRESHOLDS</t>
         </is>
       </c>
-      <c r="B32" s="256" t="n"/>
-      <c r="C32" s="256" t="n"/>
-      <c r="D32" s="256" t="n"/>
-      <c r="E32" s="256" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="143">
-      <c r="A33" s="257" t="inlineStr">
+      <c r="B32" s="258" t="n"/>
+      <c r="C32" s="258" t="n"/>
+      <c r="D32" s="258" t="n"/>
+      <c r="E32" s="258" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="144">
+      <c r="A33" s="259" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B33" s="257" t="inlineStr">
+      <c r="B33" s="259" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C33" s="257" t="inlineStr">
+      <c r="C33" s="259" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D33" s="257" t="inlineStr">
+      <c r="D33" s="259" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E33" s="257" t="inlineStr">
+      <c r="E33" s="259" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="143">
-      <c r="A34" s="248" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="144">
+      <c r="A34" s="250" t="inlineStr">
         <is>
           <t>ENTRY_Z</t>
         </is>
       </c>
-      <c r="B34" s="261" t="n">
+      <c r="B34" s="263" t="n">
         <v>2.5</v>
       </c>
-      <c r="C34" s="262" t="n">
+      <c r="C34" s="264" t="n">
         <v>2.5</v>
       </c>
-      <c r="D34" s="237" t="inlineStr">
+      <c r="D34" s="239" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E34" s="259" t="inlineStr">
+      <c r="E34" s="261" t="inlineStr">
         <is>
           <t>Highlight and chime at or above this |z|. 2.0 and 2.5 are both reasonable; 2.0 fires more often and needs a larger sigma to stay worth trading.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="143">
-      <c r="A35" s="248" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="144">
+      <c r="A35" s="250" t="inlineStr">
         <is>
           <t>MAX_ENTRY_Z</t>
         </is>
       </c>
-      <c r="B35" s="261" t="n">
+      <c r="B35" s="263" t="n">
         <v>4.5</v>
       </c>
-      <c r="C35" s="262" t="n">
+      <c r="C35" s="264" t="n">
         <v>4.5</v>
       </c>
-      <c r="D35" s="237" t="inlineStr">
+      <c r="D35" s="239" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E35" s="259" t="inlineStr">
+      <c r="E35" s="261" t="inlineStr">
         <is>
           <t>Entry CEILING. At or above this, do NOT highlight - that is a momentum spike, not a reversion setup. Keep the band at least 1 sigma wide.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="143">
-      <c r="A36" s="248" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="144">
+      <c r="A36" s="250" t="inlineStr">
         <is>
           <t>THIN_FEED_QPM</t>
         </is>
       </c>
-      <c r="B36" s="258" t="n">
+      <c r="B36" s="260" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="237" t="n">
+      <c r="C36" s="239" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="237" t="inlineStr">
+      <c r="D36" s="239" t="inlineStr">
         <is>
           <t>q/min</t>
         </is>
       </c>
-      <c r="E36" s="259" t="inlineStr">
+      <c r="E36" s="261" t="inlineStr">
         <is>
           <t>Feed rate at or below which the quotes/min display turns amber.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="143">
-      <c r="A37" s="248" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="144">
+      <c r="A37" s="250" t="inlineStr">
         <is>
           <t>SPREAD_QUOTE_CONVENTION</t>
         </is>
       </c>
-      <c r="B37" s="260" t="inlineStr">
+      <c r="B37" s="262" t="inlineStr">
         <is>
           <t>CROSSING</t>
         </is>
       </c>
-      <c r="C37" s="237" t="inlineStr">
+      <c r="C37" s="239" t="inlineStr">
         <is>
           <t>CROSSING</t>
         </is>
       </c>
-      <c r="D37" s="237" t="inlineStr">
+      <c r="D37" s="239" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E37" s="259" t="inlineStr">
+      <c r="E37" s="261" t="inlineStr">
         <is>
           <t>How the spread rows on Dashboard quote Bid and Ask. CROSSING: sell LegB at the bid and buy LegA at the ask, mirrored for the ask - the Gap is then the true cost of crossing and is always positive. SAME_SIDE: bid-minus-bid and ask-minus-ask, as the original sheet's rows 9 computed. Under SAME_SIDE the Gap is a DIFFERENCE of gaps, which understates the crossing cost and can go negative.</t>
         </is>
       </c>
     </row>
     <row r="38"/>
-    <row r="39" ht="15" customHeight="1" s="143">
-      <c r="A39" s="256" t="inlineStr">
+    <row r="39" ht="15" customHeight="1" s="144">
+      <c r="A39" s="258" t="inlineStr">
         <is>
           <t>SIZING  /  COSTS</t>
         </is>
       </c>
-      <c r="B39" s="256" t="n"/>
-      <c r="C39" s="256" t="n"/>
-      <c r="D39" s="256" t="n"/>
-      <c r="E39" s="256" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="143">
-      <c r="A40" s="257" t="inlineStr">
+      <c r="B39" s="258" t="n"/>
+      <c r="C39" s="258" t="n"/>
+      <c r="D39" s="258" t="n"/>
+      <c r="E39" s="258" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="144">
+      <c r="A40" s="259" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B40" s="257" t="inlineStr">
+      <c r="B40" s="259" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C40" s="257" t="inlineStr">
+      <c r="C40" s="259" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D40" s="257" t="inlineStr">
+      <c r="D40" s="259" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E40" s="257" t="inlineStr">
+      <c r="E40" s="259" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="143">
-      <c r="A41" s="248" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="144">
+      <c r="A41" s="250" t="inlineStr">
         <is>
           <t>LOTS</t>
         </is>
       </c>
-      <c r="B41" s="258" t="n">
+      <c r="B41" s="260" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="237" t="n">
+      <c r="C41" s="239" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="237" t="inlineStr">
+      <c r="D41" s="239" t="inlineStr">
         <is>
           <t>lots</t>
         </is>
       </c>
-      <c r="E41" s="259" t="inlineStr">
+      <c r="E41" s="261" t="inlineStr">
         <is>
           <t>Contracts per leg, for the cost and take-profit maths.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="143">
-      <c r="A42" s="248" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="144">
+      <c r="A42" s="250" t="inlineStr">
         <is>
           <t>TP_MODE</t>
         </is>
       </c>
-      <c r="B42" s="260" t="inlineStr">
+      <c r="B42" s="262" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL</t>
         </is>
       </c>
-      <c r="C42" s="237" t="inlineStr">
+      <c r="C42" s="239" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL</t>
         </is>
       </c>
-      <c r="D42" s="237" t="inlineStr">
+      <c r="D42" s="239" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E42" s="259" t="inlineStr">
+      <c r="E42" s="261" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL: Take Profit = Entry + Costs + (WIN_PCT x Notional). TARGET_USD: the older rule, Take Profit = Entry + Costs + TARGET_NET_USD.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="143">
-      <c r="A43" s="248" t="inlineStr">
+    <row r="43" ht="15" customHeight="1" s="144">
+      <c r="A43" s="250" t="inlineStr">
         <is>
           <t>WIN_PCT</t>
         </is>
       </c>
-      <c r="B43" s="261" t="n">
+      <c r="B43" s="263" t="n">
         <v>0.01</v>
       </c>
-      <c r="C43" s="262" t="n">
+      <c r="C43" s="264" t="n">
         <v>0.01</v>
       </c>
-      <c r="D43" s="237" t="inlineStr">
+      <c r="D43" s="239" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="E43" s="259" t="inlineStr">
+      <c r="E43" s="261" t="inlineStr">
         <is>
           <t>Percentage win, as a FRACTION - 0.01 is 1%, 0.02 is 2%. Used only when TP_MODE = PCT_NOTIONAL.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="143">
-      <c r="A44" s="248" t="inlineStr">
+    <row r="44" ht="15" customHeight="1" s="144">
+      <c r="A44" s="250" t="inlineStr">
         <is>
           <t>NOTIONAL_BASIS</t>
         </is>
       </c>
-      <c r="B44" s="260" t="inlineStr">
+      <c r="B44" s="262" t="inlineStr">
         <is>
           <t>SPREAD_VALUE</t>
         </is>
       </c>
-      <c r="C44" s="237" t="inlineStr">
+      <c r="C44" s="239" t="inlineStr">
         <is>
           <t>SPREAD_VALUE</t>
         </is>
       </c>
-      <c r="D44" s="237" t="inlineStr">
+      <c r="D44" s="239" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E44" s="259" t="inlineStr">
+      <c r="E44" s="261" t="inlineStr">
         <is>
           <t>What WIN_PCT is taken OF. SPREAD_VALUE = |spread| x USD/pt x LOTS. ONE_LEG = the crude leg's full contract value. BOTH_LEGS = both legs' contract value added. These differ by roughly 10x - read the note below the table before changing it.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="143">
-      <c r="A45" s="248" t="inlineStr">
+    <row r="45" ht="15" customHeight="1" s="144">
+      <c r="A45" s="250" t="inlineStr">
         <is>
           <t>TARGET_NET_USD</t>
         </is>
       </c>
-      <c r="B45" s="258" t="n">
+      <c r="B45" s="260" t="n">
         <v>150</v>
       </c>
-      <c r="C45" s="237" t="n">
+      <c r="C45" s="239" t="n">
         <v>150</v>
       </c>
-      <c r="D45" s="237" t="inlineStr">
+      <c r="D45" s="239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E45" s="259" t="inlineStr">
+      <c r="E45" s="261" t="inlineStr">
         <is>
           <t>Desired profit AFTER all costs. Used only when TP_MODE = TARGET_USD.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="143">
-      <c r="A46" s="248" t="inlineStr">
+    <row r="46" ht="15" customHeight="1" s="144">
+      <c r="A46" s="250" t="inlineStr">
         <is>
           <t>EDGE_MULTIPLE</t>
         </is>
       </c>
-      <c r="B46" s="261" t="n">
+      <c r="B46" s="263" t="n">
         <v>1.5</v>
       </c>
-      <c r="C46" s="262" t="n">
+      <c r="C46" s="264" t="n">
         <v>1.5</v>
       </c>
-      <c r="D46" s="237" t="inlineStr">
+      <c r="D46" s="239" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E46" s="259" t="inlineStr">
+      <c r="E46" s="261" t="inlineStr">
         <is>
           <t>Expected capture must clear the round trip by this multiple.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="143">
-      <c r="A47" s="248" t="inlineStr">
+    <row r="47" ht="15" customHeight="1" s="144">
+      <c r="A47" s="250" t="inlineStr">
         <is>
           <t>RATE_ORIENT_PER_SIDE</t>
         </is>
       </c>
-      <c r="B47" s="261" t="n">
+      <c r="B47" s="263" t="n">
         <v>0.35</v>
       </c>
-      <c r="C47" s="262" t="n">
+      <c r="C47" s="264" t="n">
         <v>0.35</v>
       </c>
-      <c r="D47" s="237" t="inlineStr">
+      <c r="D47" s="239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E47" s="259" t="inlineStr">
+      <c r="E47" s="261" t="inlineStr">
         <is>
           <t>Orient clearing + execution, per contract per side. Source: Orient rate card 2026-08-21, Ver.26.8.17.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="143">
-      <c r="A48" s="248" t="inlineStr">
+    <row r="48" ht="15" customHeight="1" s="144">
+      <c r="A48" s="250" t="inlineStr">
         <is>
           <t>RATE_FIX_PER_SIDE</t>
         </is>
       </c>
-      <c r="B48" s="261" t="n">
+      <c r="B48" s="263" t="n">
         <v>0.06</v>
       </c>
-      <c r="C48" s="262" t="n">
+      <c r="C48" s="264" t="n">
         <v>0.06</v>
       </c>
-      <c r="D48" s="237" t="inlineStr">
+      <c r="D48" s="239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E48" s="259" t="inlineStr">
+      <c r="E48" s="261" t="inlineStr">
         <is>
           <t>FIX / platform transaction fee, per contract per side. Same rate card.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="143">
-      <c r="A49" s="248" t="inlineStr">
+    <row r="49" ht="15" customHeight="1" s="144">
+      <c r="A49" s="250" t="inlineStr">
         <is>
           <t>RATE_CME_PER_SIDE</t>
         </is>
       </c>
-      <c r="B49" s="261" t="n">
+      <c r="B49" s="263" t="n">
         <v>1.5</v>
       </c>
-      <c r="C49" s="262" t="n">
+      <c r="C49" s="264" t="n">
         <v>1.5</v>
       </c>
-      <c r="D49" s="237" t="inlineStr">
+      <c r="D49" s="239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E49" s="259" t="inlineStr">
+      <c r="E49" s="261" t="inlineStr">
         <is>
           <t>CME exchange + clearing, per contract per side. Same rate card.</t>
         </is>
       </c>
     </row>
     <row r="50"/>
-    <row r="51" ht="15" customHeight="1" s="143">
-      <c r="A51" s="256" t="inlineStr">
+    <row r="51" ht="15" customHeight="1" s="144">
+      <c r="A51" s="258" t="inlineStr">
         <is>
           <t>AUDIBLE ALERT</t>
         </is>
       </c>
-      <c r="B51" s="256" t="n"/>
-      <c r="C51" s="256" t="n"/>
-      <c r="D51" s="256" t="n"/>
-      <c r="E51" s="256" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="143">
-      <c r="A52" s="257" t="inlineStr">
+      <c r="B51" s="258" t="n"/>
+      <c r="C51" s="258" t="n"/>
+      <c r="D51" s="258" t="n"/>
+      <c r="E51" s="258" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="144">
+      <c r="A52" s="259" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B52" s="257" t="inlineStr">
+      <c r="B52" s="259" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C52" s="257" t="inlineStr">
+      <c r="C52" s="259" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D52" s="257" t="inlineStr">
+      <c r="D52" s="259" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E52" s="257" t="inlineStr">
+      <c r="E52" s="259" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="143">
-      <c r="A53" s="248" t="inlineStr">
+    <row r="53" ht="15" customHeight="1" s="144">
+      <c r="A53" s="250" t="inlineStr">
         <is>
           <t>ALERT_ENABLED</t>
         </is>
       </c>
-      <c r="B53" s="258" t="b">
+      <c r="B53" s="260" t="b">
         <v>1</v>
       </c>
-      <c r="C53" s="237" t="b">
+      <c r="C53" s="239" t="b">
         <v>1</v>
       </c>
-      <c r="D53" s="237" t="inlineStr">
+      <c r="D53" s="239" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E53" s="259" t="inlineStr">
+      <c r="E53" s="261" t="inlineStr">
         <is>
           <t>MASTER MUTE. FALSE silences every sound.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="143">
-      <c r="A54" s="248" t="inlineStr">
+    <row r="54" ht="15" customHeight="1" s="144">
+      <c r="A54" s="250" t="inlineStr">
         <is>
           <t>ALERT_SOUND_PATH</t>
         </is>
       </c>
-      <c r="B54" s="260" t="inlineStr">
+      <c r="B54" s="262" t="inlineStr">
         <is>
           <t>C:\Windows\Media\chimes.wav</t>
         </is>
       </c>
-      <c r="C54" s="237" t="inlineStr">
+      <c r="C54" s="239" t="inlineStr">
         <is>
           <t>C:\Windows\Media\chimes.wav</t>
         </is>
       </c>
-      <c r="D54" s="237" t="inlineStr">
+      <c r="D54" s="239" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E54" s="259" t="inlineStr">
+      <c r="E54" s="261" t="inlineStr">
         <is>
           <t>Single short 'ting' played on an entry-band crossing.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="143">
-      <c r="A55" s="248" t="inlineStr">
+    <row r="55" ht="15" customHeight="1" s="144">
+      <c r="A55" s="250" t="inlineStr">
         <is>
           <t>ALERT_SOUND_PATH_CEILING</t>
         </is>
       </c>
-      <c r="B55" s="260" t="inlineStr">
+      <c r="B55" s="262" t="inlineStr">
         <is>
           <t>C:\Windows\Media\notify.wav</t>
         </is>
       </c>
-      <c r="C55" s="237" t="inlineStr">
+      <c r="C55" s="239" t="inlineStr">
         <is>
           <t>C:\Windows\Media\notify.wav</t>
         </is>
       </c>
-      <c r="D55" s="237" t="inlineStr">
+      <c r="D55" s="239" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E55" s="259" t="inlineStr">
+      <c r="E55" s="261" t="inlineStr">
         <is>
           <t>Distinct tone for crossing MAX_ENTRY_Z. That is 'stand down', not 'get in'.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="143">
-      <c r="A56" s="248" t="inlineStr">
+    <row r="56" ht="15" customHeight="1" s="144">
+      <c r="A56" s="250" t="inlineStr">
         <is>
           <t>ALERT_REARM_MARGIN</t>
         </is>
       </c>
-      <c r="B56" s="261" t="n">
+      <c r="B56" s="263" t="n">
         <v>0.25</v>
       </c>
-      <c r="C56" s="262" t="n">
+      <c r="C56" s="264" t="n">
         <v>0.25</v>
       </c>
-      <c r="D56" s="237" t="inlineStr">
+      <c r="D56" s="239" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E56" s="259" t="inlineStr">
+      <c r="E56" s="261" t="inlineStr">
         <is>
           <t>Hysteresis. Do not re-arm until |z| falls back below ENTRY_Z - this margin.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="143">
-      <c r="A57" s="248" t="inlineStr">
+    <row r="57" ht="15" customHeight="1" s="144">
+      <c r="A57" s="250" t="inlineStr">
         <is>
           <t>ALERT_COOLDOWN_SEC</t>
         </is>
       </c>
-      <c r="B57" s="258" t="n">
+      <c r="B57" s="260" t="n">
         <v>60</v>
       </c>
-      <c r="C57" s="237" t="n">
+      <c r="C57" s="239" t="n">
         <v>60</v>
       </c>
-      <c r="D57" s="237" t="inlineStr">
+      <c r="D57" s="239" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E57" s="259" t="inlineStr">
+      <c r="E57" s="261" t="inlineStr">
         <is>
           <t>Minimum seconds between alerts for the same spread.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="143">
-      <c r="A58" s="248" t="inlineStr">
+    <row r="58" ht="15" customHeight="1" s="144">
+      <c r="A58" s="250" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES</t>
         </is>
       </c>
-      <c r="B58" s="258" t="b">
+      <c r="B58" s="260" t="b">
         <v>0</v>
       </c>
-      <c r="C58" s="237" t="b">
+      <c r="C58" s="239" t="b">
         <v>0</v>
       </c>
-      <c r="D58" s="237" t="inlineStr">
+      <c r="D58" s="239" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E58" s="259" t="inlineStr">
+      <c r="E58" s="261" t="inlineStr">
         <is>
           <t>FALSE = the chime follows ENTRY_Z alone. TRUE = also stay silent when the edge filter fails, on the argument that a sound for a trade you should not take trains you to ignore the sound. Ships FALSE by request; the edge verdict is still shown on Detail.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="143">
-      <c r="A59" s="248" t="inlineStr">
+    <row r="59" ht="15" customHeight="1" s="144">
+      <c r="A59" s="250" t="inlineStr">
         <is>
           <t>ALERT_SPEAK</t>
         </is>
       </c>
-      <c r="B59" s="258" t="b">
+      <c r="B59" s="260" t="b">
         <v>0</v>
       </c>
-      <c r="C59" s="237" t="b">
+      <c r="C59" s="239" t="b">
         <v>0</v>
       </c>
-      <c r="D59" s="237" t="inlineStr">
+      <c r="D59" s="239" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E59" s="259" t="inlineStr">
+      <c r="E59" s="261" t="inlineStr">
         <is>
           <t>TRUE also speaks the spread name (Application.Speech). Useful when watching four at once.</t>
         </is>
       </c>
     </row>
     <row r="60"/>
-    <row r="61" ht="15" customHeight="1" s="143">
-      <c r="A61" s="256" t="inlineStr">
+    <row r="61" ht="15" customHeight="1" s="144">
+      <c r="A61" s="258" t="inlineStr">
         <is>
           <t>PERSISTENCE  /  LOGGING</t>
         </is>
       </c>
-      <c r="B61" s="256" t="n"/>
-      <c r="C61" s="256" t="n"/>
-      <c r="D61" s="256" t="n"/>
-      <c r="E61" s="256" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="143">
-      <c r="A62" s="257" t="inlineStr">
+      <c r="B61" s="258" t="n"/>
+      <c r="C61" s="258" t="n"/>
+      <c r="D61" s="258" t="n"/>
+      <c r="E61" s="258" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="144">
+      <c r="A62" s="259" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B62" s="257" t="inlineStr">
+      <c r="B62" s="259" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C62" s="257" t="inlineStr">
+      <c r="C62" s="259" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D62" s="257" t="inlineStr">
+      <c r="D62" s="259" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E62" s="257" t="inlineStr">
+      <c r="E62" s="259" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="143">
-      <c r="A63" s="248" t="inlineStr">
+    <row r="63" ht="15" customHeight="1" s="144">
+      <c r="A63" s="250" t="inlineStr">
         <is>
           <t>WARM_START_ENABLED</t>
         </is>
       </c>
-      <c r="B63" s="258" t="b">
+      <c r="B63" s="260" t="b">
         <v>1</v>
       </c>
-      <c r="C63" s="237" t="b">
+      <c r="C63" s="239" t="b">
         <v>1</v>
       </c>
-      <c r="D63" s="237" t="inlineStr">
+      <c r="D63" s="239" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E63" s="259" t="inlineStr">
+      <c r="E63" s="261" t="inlineStr">
         <is>
           <t>On open, reload the flushed buffer so a restart does not cost another two hours of warm-up.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="143">
-      <c r="A64" s="248" t="inlineStr">
+    <row r="64" ht="15" customHeight="1" s="144">
+      <c r="A64" s="250" t="inlineStr">
         <is>
           <t>WARM_START_MAX_AGE_MIN</t>
         </is>
       </c>
-      <c r="B64" s="258" t="n">
+      <c r="B64" s="260" t="n">
         <v>180</v>
       </c>
-      <c r="C64" s="237" t="n">
+      <c r="C64" s="239" t="n">
         <v>180</v>
       </c>
-      <c r="D64" s="237" t="inlineStr">
+      <c r="D64" s="239" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E64" s="259" t="inlineStr">
+      <c r="E64" s="261" t="inlineStr">
         <is>
           <t>Only reload if the newest saved sample is younger than this.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="143">
-      <c r="A65" s="248" t="inlineStr">
+    <row r="65" ht="15" customHeight="1" s="144">
+      <c r="A65" s="250" t="inlineStr">
         <is>
           <t>LOG_ENABLED</t>
         </is>
       </c>
-      <c r="B65" s="258" t="b">
+      <c r="B65" s="260" t="b">
         <v>1</v>
       </c>
-      <c r="C65" s="237" t="b">
+      <c r="C65" s="239" t="b">
         <v>1</v>
       </c>
-      <c r="D65" s="237" t="inlineStr">
+      <c r="D65" s="239" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E65" s="259" t="inlineStr">
+      <c r="E65" s="261" t="inlineStr">
         <is>
           <t>Write signal events to the Log sheet.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="143">
-      <c r="A66" s="248" t="inlineStr">
+    <row r="66" ht="15" customHeight="1" s="144">
+      <c r="A66" s="250" t="inlineStr">
         <is>
           <t>LOG_MAX_ROWS</t>
         </is>
       </c>
-      <c r="B66" s="258" t="n">
+      <c r="B66" s="260" t="n">
         <v>20000</v>
       </c>
-      <c r="C66" s="237" t="n">
+      <c r="C66" s="239" t="n">
         <v>20000</v>
       </c>
-      <c r="D66" s="237" t="inlineStr">
+      <c r="D66" s="239" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="E66" s="259" t="inlineStr">
+      <c r="E66" s="261" t="inlineStr">
         <is>
           <t>Log is trimmed to this many rows.</t>
         </is>
       </c>
     </row>
     <row r="67"/>
-    <row r="68" ht="15" customHeight="1" s="143">
-      <c r="A68" s="256" t="inlineStr">
+    <row r="68" ht="15" customHeight="1" s="144">
+      <c r="A68" s="258" t="inlineStr">
         <is>
           <t>DERIVED COMMISSION  (formulas - do not edit)</t>
         </is>
       </c>
-      <c r="B68" s="263" t="n"/>
-      <c r="C68" s="263" t="n"/>
-      <c r="D68" s="263" t="n"/>
-      <c r="E68" s="263" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="143">
-      <c r="A69" s="257" t="inlineStr">
+      <c r="B68" s="265" t="n"/>
+      <c r="C68" s="265" t="n"/>
+      <c r="D68" s="265" t="n"/>
+      <c r="E68" s="265" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="144">
+      <c r="A69" s="259" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B69" s="257" t="inlineStr">
+      <c r="B69" s="259" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C69" s="257" t="inlineStr">
+      <c r="C69" s="259" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D69" s="257" t="inlineStr">
+      <c r="D69" s="259" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E69" s="257" t="inlineStr">
+      <c r="E69" s="259" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="143">
-      <c r="A70" s="248" t="inlineStr">
+    <row r="70" ht="15" customHeight="1" s="144">
+      <c r="A70" s="250" t="inlineStr">
         <is>
           <t>COMMISSION_CONSERVATIVE</t>
         </is>
       </c>
-      <c r="B70" s="249">
+      <c r="B70" s="251">
         <f>2*(B47+B48+B49)</f>
         <v/>
       </c>
-      <c r="E70" s="264" t="inlineStr">
+      <c r="E70" s="266" t="inlineStr">
         <is>
           <t>Per lot PER LEG, round turn, reading CME's 1.50 as per SIDE. This is the conservative reading and the one to use.</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="143">
-      <c r="A71" s="248" t="inlineStr">
+    <row r="71" ht="15" customHeight="1" s="144">
+      <c r="A71" s="250" t="inlineStr">
         <is>
           <t>COMMISSION_IF_CME_PER_RT</t>
         </is>
       </c>
-      <c r="B71" s="245">
+      <c r="B71" s="247">
         <f>2*(B47+B48)+B49</f>
         <v/>
       </c>
-      <c r="E71" s="264" t="inlineStr">
+      <c r="E71" s="266" t="inlineStr">
         <is>
           <t>The same figure if CME's 1.50 turns out to be per ROUND TURN rather than per side.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="143">
-      <c r="A72" s="248" t="inlineStr">
+    <row r="72" ht="15" customHeight="1" s="144">
+      <c r="A72" s="250" t="inlineStr">
         <is>
           <t>COMMISSION_BASIS</t>
         </is>
       </c>
-      <c r="B72" s="258" t="inlineStr">
+      <c r="B72" s="260" t="inlineStr">
         <is>
           <t>CONSERVATIVE</t>
         </is>
       </c>
-      <c r="C72" s="237" t="inlineStr">
+      <c r="C72" s="239" t="inlineStr">
         <is>
           <t>CONSERVATIVE</t>
         </is>
       </c>
-      <c r="E72" s="264" t="inlineStr">
+      <c r="E72" s="266" t="inlineStr">
         <is>
           <t>CONSERVATIVE or CME_PER_RT. An understated cost model approves losing trades invisibly; an overstated one only refuses trades, visibly. Leave it on CONSERVATIVE.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="143">
-      <c r="A73" s="248" t="inlineStr">
+    <row r="73" ht="15" customHeight="1" s="144">
+      <c r="A73" s="250" t="inlineStr">
         <is>
           <t>COMMISSION_PER_LOT_ROUND_TURN</t>
         </is>
       </c>
-      <c r="B73" s="249">
+      <c r="B73" s="251">
         <f>IF(B72="CME_PER_RT",B71,B70)</f>
         <v/>
       </c>
-      <c r="E73" s="264" t="inlineStr">
+      <c r="E73" s="266" t="inlineStr">
         <is>
           <t>USD per lot per leg, round turn. This is what the cost model actually uses.</t>
         </is>
       </c>
     </row>
     <row r="74"/>
-    <row r="75" ht="15" customHeight="1" s="143">
-      <c r="A75" s="256" t="inlineStr">
+    <row r="75" ht="15" customHeight="1" s="144">
+      <c r="A75" s="258" t="inlineStr">
         <is>
           <t>SPREAD_TABLE_START   -   up to 4 monitored spreads, one buffer each</t>
         </is>
       </c>
-      <c r="B75" s="263" t="n"/>
-      <c r="C75" s="263" t="n"/>
-      <c r="D75" s="263" t="n"/>
-      <c r="E75" s="263" t="n"/>
-      <c r="F75" s="263" t="n"/>
-      <c r="G75" s="263" t="n"/>
-      <c r="H75" s="263" t="n"/>
-      <c r="I75" s="263" t="n"/>
-      <c r="J75" s="263" t="n"/>
-      <c r="K75" s="263" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="143">
-      <c r="A76" s="231" t="inlineStr">
+      <c r="B75" s="265" t="n"/>
+      <c r="C75" s="265" t="n"/>
+      <c r="D75" s="265" t="n"/>
+      <c r="E75" s="265" t="n"/>
+      <c r="F75" s="265" t="n"/>
+      <c r="G75" s="265" t="n"/>
+      <c r="H75" s="265" t="n"/>
+      <c r="I75" s="265" t="n"/>
+      <c r="J75" s="265" t="n"/>
+      <c r="K75" s="265" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="144">
+      <c r="A76" s="233" t="inlineStr">
         <is>
           <t>Leg COMPOSITION (which instruments, and their weights) is defined by the labelled formulas in the MONITOR LEGS block on the hidden Feed sheet. Everything below is hot-reloaded each tick.</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="32.8" customHeight="1" s="143">
-      <c r="A77" s="257" t="inlineStr">
+    <row r="77" ht="32.8" customHeight="1" s="144">
+      <c r="A77" s="259" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B77" s="257" t="inlineStr">
+      <c r="B77" s="259" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="C77" s="257" t="inlineStr">
+      <c r="C77" s="259" t="inlineStr">
         <is>
           <t>Display name</t>
         </is>
       </c>
-      <c r="D77" s="257" t="inlineStr">
+      <c r="D77" s="259" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="E77" s="257" t="inlineStr">
+      <c r="E77" s="259" t="inlineStr">
         <is>
           <t>HEDGE_RATIO (beta)</t>
         </is>
       </c>
-      <c r="F77" s="257" t="inlineStr">
+      <c r="F77" s="259" t="inlineStr">
         <is>
           <t>Beta stamped for pair</t>
         </is>
       </c>
-      <c r="G77" s="257" t="inlineStr">
+      <c r="G77" s="259" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread, per lot</t>
         </is>
       </c>
-      <c r="H77" s="257" t="inlineStr">
+      <c r="H77" s="259" t="inlineStr">
         <is>
           <t>Contracts charged commission</t>
         </is>
       </c>
-      <c r="I77" s="257" t="inlineStr">
+      <c r="I77" s="259" t="inlineStr">
         <is>
           <t>Tick size</t>
         </is>
       </c>
-      <c r="J77" s="257" t="inlineStr">
+      <c r="J77" s="259" t="inlineStr">
         <is>
           <t>Decimals</t>
         </is>
       </c>
-      <c r="K77" s="257" t="inlineStr">
+      <c r="K77" s="259" t="inlineStr">
         <is>
           <t>Listed equivalent (cost comparison)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="143">
-      <c r="A78" s="250" t="inlineStr">
+    <row r="78" ht="15" customHeight="1" s="144">
+      <c r="A78" s="252" t="inlineStr">
         <is>
           <t>SPREAD_1</t>
         </is>
       </c>
-      <c r="B78" s="258" t="b">
+      <c r="B78" s="260" t="b">
         <v>1</v>
       </c>
-      <c r="C78" s="260" t="inlineStr">
+      <c r="C78" s="262" t="inlineStr">
         <is>
           <t>BZ - CL  (Brent LDF - WTI)</t>
         </is>
       </c>
-      <c r="D78" s="258" t="inlineStr">
+      <c r="D78" s="260" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E78" s="265" t="n">
+      <c r="E78" s="267" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="260" t="inlineStr">
+      <c r="F78" s="262" t="inlineStr">
         <is>
           <t>BZV6 / CLV6, derived 2026-08 (RELATED pair - no fair value, empirical mean only)</t>
         </is>
       </c>
-      <c r="G78" s="266" t="n">
+      <c r="G78" s="268" t="n">
         <v>1000</v>
       </c>
-      <c r="H78" s="267" t="n">
+      <c r="H78" s="269" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="265" t="n">
+      <c r="I78" s="267" t="n">
         <v>0.01</v>
       </c>
-      <c r="J78" s="267" t="n">
+      <c r="J78" s="269" t="n">
         <v>2</v>
       </c>
-      <c r="K78" s="239" t="inlineStr">
+      <c r="K78" s="241" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="143">
-      <c r="A79" s="250" t="inlineStr">
+    <row r="79" ht="15" customHeight="1" s="144">
+      <c r="A79" s="252" t="inlineStr">
         <is>
           <t>SPREAD_2</t>
         </is>
       </c>
-      <c r="B79" s="258" t="b">
+      <c r="B79" s="260" t="b">
         <v>1</v>
       </c>
-      <c r="C79" s="260" t="inlineStr">
+      <c r="C79" s="262" t="inlineStr">
         <is>
           <t>HO/CL crack  (ULSD - WTI)</t>
         </is>
       </c>
-      <c r="D79" s="258" t="inlineStr">
+      <c r="D79" s="260" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E79" s="265" t="n">
+      <c r="E79" s="267" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="260" t="inlineStr">
+      <c r="F79" s="262" t="inlineStr">
         <is>
           <t>HOV6 x42 / CLV6, 1:1 by design (crack, not a fitted beta)</t>
         </is>
       </c>
-      <c r="G79" s="266" t="n">
+      <c r="G79" s="268" t="n">
         <v>1000</v>
       </c>
-      <c r="H79" s="267" t="n">
+      <c r="H79" s="269" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="265" t="n">
+      <c r="I79" s="267" t="n">
         <v>0.01</v>
       </c>
-      <c r="J79" s="267" t="n">
+      <c r="J79" s="269" t="n">
         <v>2</v>
       </c>
-      <c r="K79" s="239" t="inlineStr">
+      <c r="K79" s="241" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="143">
-      <c r="A80" s="250" t="inlineStr">
+    <row r="80" ht="15" customHeight="1" s="144">
+      <c r="A80" s="252" t="inlineStr">
         <is>
           <t>SPREAD_3</t>
         </is>
       </c>
-      <c r="B80" s="258" t="b">
+      <c r="B80" s="260" t="b">
         <v>1</v>
       </c>
-      <c r="C80" s="260" t="inlineStr">
+      <c r="C80" s="262" t="inlineStr">
         <is>
           <t>3:2:1 crack  (2RB+1HO-3CL)/3</t>
         </is>
       </c>
-      <c r="D80" s="258" t="inlineStr">
+      <c r="D80" s="260" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E80" s="265" t="n">
+      <c r="E80" s="267" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="260" t="inlineStr">
+      <c r="F80" s="262" t="inlineStr">
         <is>
           <t>RBV6/HOV6/CLV6, structural 3:2:1 - not a fitted beta</t>
         </is>
       </c>
-      <c r="G80" s="266" t="n">
+      <c r="G80" s="268" t="n">
         <v>3000</v>
       </c>
-      <c r="H80" s="267" t="n">
+      <c r="H80" s="269" t="n">
         <v>6</v>
       </c>
-      <c r="I80" s="265" t="n">
+      <c r="I80" s="267" t="n">
         <v>0.01</v>
       </c>
-      <c r="J80" s="267" t="n">
+      <c r="J80" s="269" t="n">
         <v>2</v>
       </c>
-      <c r="K80" s="239" t="inlineStr">
+      <c r="K80" s="241" t="inlineStr">
         <is>
           <t>(none listed)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="143">
-      <c r="A81" s="250" t="inlineStr">
+    <row r="81" ht="15" customHeight="1" s="144">
+      <c r="A81" s="252" t="inlineStr">
         <is>
           <t>SPREAD_4</t>
         </is>
       </c>
-      <c r="B81" s="258" t="b">
+      <c r="B81" s="260" t="b">
         <v>1</v>
       </c>
-      <c r="C81" s="260" t="inlineStr">
+      <c r="C81" s="262" t="inlineStr">
         <is>
           <t>CL-BZ Inter-Product (listed)</t>
         </is>
       </c>
-      <c r="D81" s="258" t="inlineStr">
+      <c r="D81" s="260" t="inlineStr">
         <is>
           <t>LISTED</t>
         </is>
       </c>
-      <c r="E81" s="265" t="n">
+      <c r="E81" s="267" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="260" t="inlineStr">
+      <c r="F81" s="262" t="inlineStr">
         <is>
           <t>Exchange-listed spread - beta not applicable</t>
         </is>
       </c>
-      <c r="G81" s="266" t="n">
+      <c r="G81" s="268" t="n">
         <v>1000</v>
       </c>
-      <c r="H81" s="267" t="n">
+      <c r="H81" s="269" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="265" t="n">
+      <c r="I81" s="267" t="n">
         <v>0.01</v>
       </c>
-      <c r="J81" s="267" t="n">
+      <c r="J81" s="269" t="n">
         <v>2</v>
       </c>
-      <c r="K81" s="239" t="inlineStr">
+      <c r="K81" s="241" t="inlineStr">
         <is>
           <t>n/a - this IS the listed spread</t>
         </is>
       </c>
     </row>
     <row r="82"/>
-    <row r="83" ht="15" customHeight="1" s="143">
-      <c r="A83" s="253" t="inlineStr">
+    <row r="83" ht="15" customHeight="1" s="144">
+      <c r="A83" s="255" t="inlineStr">
         <is>
           <t>HEDGE RATIO BELONGS TO THE PAIR. If the instruments change, beta must be re-derived - a stale beta silently redefines the series. Column F stamps what each beta was computed for.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="143">
-      <c r="A84" s="231" t="inlineStr">
+    <row r="84" ht="15" customHeight="1" s="144">
+      <c r="A84" s="233" t="inlineStr">
         <is>
           <t>Contracts charged: BZ-CL and the listed spread are 2 contracts per lot (one per leg); the 3:2:1 crack is 6 (2 RB + 1 HO + 3 CL).</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="143">
-      <c r="A85" s="231" t="inlineStr">
+    <row r="85" ht="15" customHeight="1" s="144">
+      <c r="A85" s="233" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread: NYMEX energy contracts are 1,000 bbl, so one cent of differential is $10 per leg per lot, i.e. $1,000 per 1.00.</t>
         </is>
       </c>
     </row>
     <row r="86"/>
-    <row r="87" ht="15" customHeight="1" s="143">
-      <c r="A87" s="253" t="inlineStr">
+    <row r="87" ht="15" customHeight="1" s="144">
+      <c r="A87" s="255" t="inlineStr">
         <is>
           <t>NOTIONAL_BASIS - read this before changing it:</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="143">
-      <c r="A88" s="231" t="inlineStr">
+    <row r="88" ht="15" customHeight="1" s="144">
+      <c r="A88" s="233" t="inlineStr">
         <is>
           <t>A spread is not an outright, so 'notional' has no single meaning. At 1 lot with CL near $60 and BZ-CL near $7.20:  SPREAD_VALUE ~ $7,200, ONE_LEG ~ $60,000, BOTH_LEGS ~ $127,000.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="143">
-      <c r="A89" s="268" t="inlineStr">
+    <row r="89" ht="15" customHeight="1" s="144">
+      <c r="A89" s="270" t="inlineStr">
         <is>
           <t>1% of those is $72, $600 and $1,270. If sigma on this spread turns out to be ~5 cents ($50), only the first is reachable - the others need the spread to travel 12 or 25 sigma, which it will not do. Watch the TP-in-sigma cell on the Dashboard: above about 1 sigma it turns amber.</t>
         </is>
@@ -5580,315 +5591,315 @@
   <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="40" customWidth="1" style="141" min="1" max="1"/>
-    <col width="34" customWidth="1" style="141" min="2" max="2"/>
-    <col width="13" customWidth="1" style="141" min="3" max="8"/>
-    <col width="60" customWidth="1" style="141" min="9" max="9"/>
+    <col width="40" customWidth="1" style="142" min="1" max="1"/>
+    <col width="34" customWidth="1" style="142" min="2" max="2"/>
+    <col width="13" customWidth="1" style="142" min="3" max="8"/>
+    <col width="60" customWidth="1" style="142" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="143">
-      <c r="A1" s="269" t="inlineStr">
+    <row r="1" ht="16.15" customHeight="1" s="144">
+      <c r="A1" s="271" t="inlineStr">
         <is>
           <t>FEED  -  hidden.  Every RTD() formula lives here.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="143">
-      <c r="A2" s="270" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="144">
+      <c r="A2" s="272" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B2" s="271">
+      <c r="B2" s="273">
         <f>Dashboard!$C$4</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="143">
-      <c r="A3" s="253" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="144">
+      <c r="A3" s="255" t="inlineStr">
         <is>
           <t>Never put an RTD() formula on Dashboard: a cell holding one repaints whenever the feed moves, and that cannot be prevented while the formula is in the cell.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5" ht="15" customHeight="1" s="143">
-      <c r="A5" s="272" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="144">
+      <c r="A5" s="274" t="inlineStr">
         <is>
           <t>INSTRUMENTS</t>
         </is>
       </c>
-      <c r="B5" s="233" t="inlineStr">
+      <c r="B5" s="235" t="inlineStr">
         <is>
           <t>Instrument ID</t>
         </is>
       </c>
-      <c r="C5" s="233" t="inlineStr">
+      <c r="C5" s="235" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="D5" s="233" t="inlineStr">
+      <c r="D5" s="235" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="E5" s="233" t="inlineStr">
+      <c r="E5" s="235" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="233" t="inlineStr">
+      <c r="F5" s="235" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G5" s="233" t="inlineStr">
+      <c r="G5" s="235" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="H5" s="233" t="inlineStr">
+      <c r="H5" s="235" t="inlineStr">
         <is>
           <t>Width</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="143">
-      <c r="A6" s="234" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="144">
+      <c r="A6" s="236" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="B6" s="273">
+      <c r="B6" s="275">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A6)</f>
         <v/>
       </c>
-      <c r="C6" s="273">
-        <f>IFERROR(IF($B6="","",VALUE(RTD("tt.rtd",,$B6,"Bid"))),"")</f>
-        <v/>
-      </c>
-      <c r="D6" s="273">
-        <f>IFERROR(IF($B6="","",VALUE(RTD("tt.rtd",,$B6,"Ask"))),"")</f>
-        <v/>
-      </c>
-      <c r="E6" s="273">
-        <f>IFERROR(IF($B6="","",VALUE(RTD("tt.rtd",,$B6,"High"))),"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="273">
-        <f>IFERROR(IF($B6="","",VALUE(RTD("tt.rtd",,$B6,"Low"))),"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="273">
+      <c r="C6" s="275">
+        <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"Bid"))),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="275">
+        <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"Ask"))),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="275">
+        <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"High"))),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="275">
+        <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"Low"))),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="275">
         <f>IF(OR($C6="",$D6=""),"",($C6+$D6)/2)</f>
         <v/>
       </c>
-      <c r="H6" s="273">
+      <c r="H6" s="275">
         <f>IF(OR($C6="",$D6=""),"",$D6-$C6)</f>
         <v/>
       </c>
-      <c r="I6" s="274" t="inlineStr">
+      <c r="I6" s="276" t="inlineStr">
         <is>
           <t>RBOB Gasoline Oct26</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="143">
-      <c r="A7" s="234" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="144">
+      <c r="A7" s="236" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="B7" s="273">
+      <c r="B7" s="275">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A7)</f>
         <v/>
       </c>
-      <c r="C7" s="273">
-        <f>IFERROR(IF($B7="","",VALUE(RTD("tt.rtd",,$B7,"Bid"))),"")</f>
-        <v/>
-      </c>
-      <c r="D7" s="273">
-        <f>IFERROR(IF($B7="","",VALUE(RTD("tt.rtd",,$B7,"Ask"))),"")</f>
-        <v/>
-      </c>
-      <c r="E7" s="273">
-        <f>IFERROR(IF($B7="","",VALUE(RTD("tt.rtd",,$B7,"High"))),"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="273">
-        <f>IFERROR(IF($B7="","",VALUE(RTD("tt.rtd",,$B7,"Low"))),"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="273">
+      <c r="C7" s="275">
+        <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"Bid"))),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="275">
+        <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"Ask"))),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="275">
+        <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"High"))),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="275">
+        <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"Low"))),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="275">
         <f>IF(OR($C7="",$D7=""),"",($C7+$D7)/2)</f>
         <v/>
       </c>
-      <c r="H7" s="273">
+      <c r="H7" s="275">
         <f>IF(OR($C7="",$D7=""),"",$D7-$C7)</f>
         <v/>
       </c>
-      <c r="I7" s="274" t="inlineStr">
+      <c r="I7" s="276" t="inlineStr">
         <is>
           <t>NY Harbor ULSD Oct26</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="143">
-      <c r="A8" s="234" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="144">
+      <c r="A8" s="236" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="B8" s="273">
+      <c r="B8" s="275">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A8)</f>
         <v/>
       </c>
-      <c r="C8" s="273">
-        <f>IFERROR(IF($B8="","",VALUE(RTD("tt.rtd",,$B8,"Bid"))),"")</f>
-        <v/>
-      </c>
-      <c r="D8" s="273">
-        <f>IFERROR(IF($B8="","",VALUE(RTD("tt.rtd",,$B8,"Ask"))),"")</f>
-        <v/>
-      </c>
-      <c r="E8" s="273">
-        <f>IFERROR(IF($B8="","",VALUE(RTD("tt.rtd",,$B8,"High"))),"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="273">
-        <f>IFERROR(IF($B8="","",VALUE(RTD("tt.rtd",,$B8,"Low"))),"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="273">
+      <c r="C8" s="275">
+        <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"Bid"))),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="275">
+        <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"Ask"))),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="275">
+        <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"High"))),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="275">
+        <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"Low"))),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="275">
         <f>IF(OR($C8="",$D8=""),"",($C8+$D8)/2)</f>
         <v/>
       </c>
-      <c r="H8" s="273">
+      <c r="H8" s="275">
         <f>IF(OR($C8="",$D8=""),"",$D8-$C8)</f>
         <v/>
       </c>
-      <c r="I8" s="274" t="inlineStr">
+      <c r="I8" s="276" t="inlineStr">
         <is>
           <t>WTI Crude Oct26</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="143">
-      <c r="A9" s="234" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="144">
+      <c r="A9" s="236" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="B9" s="273">
+      <c r="B9" s="275">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A9)</f>
         <v/>
       </c>
-      <c r="C9" s="273">
-        <f>IFERROR(IF($B9="","",VALUE(RTD("tt.rtd",,$B9,"Bid"))),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="273">
-        <f>IFERROR(IF($B9="","",VALUE(RTD("tt.rtd",,$B9,"Ask"))),"")</f>
-        <v/>
-      </c>
-      <c r="E9" s="273">
-        <f>IFERROR(IF($B9="","",VALUE(RTD("tt.rtd",,$B9,"High"))),"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="273">
-        <f>IFERROR(IF($B9="","",VALUE(RTD("tt.rtd",,$B9,"Low"))),"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="273">
+      <c r="C9" s="275">
+        <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"Bid"))),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="275">
+        <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"Ask"))),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="275">
+        <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"High"))),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="275">
+        <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"Low"))),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="275">
         <f>IF(OR($C9="",$D9=""),"",($C9+$D9)/2)</f>
         <v/>
       </c>
-      <c r="H9" s="273">
+      <c r="H9" s="275">
         <f>IF(OR($C9="",$D9=""),"",$D9-$C9)</f>
         <v/>
       </c>
-      <c r="I9" s="274" t="inlineStr">
+      <c r="I9" s="276" t="inlineStr">
         <is>
           <t>Brent Last Day Financial Oct26</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="143">
-      <c r="A10" s="234" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="144">
+      <c r="A10" s="236" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="B10" s="273">
+      <c r="B10" s="275">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A10)</f>
         <v/>
       </c>
-      <c r="C10" s="273">
-        <f>IFERROR(IF($B10="","",VALUE(RTD("tt.rtd",,$B10,"Bid"))),"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="273">
-        <f>IFERROR(IF($B10="","",VALUE(RTD("tt.rtd",,$B10,"Ask"))),"")</f>
-        <v/>
-      </c>
-      <c r="E10" s="273">
-        <f>IFERROR(IF($B10="","",VALUE(RTD("tt.rtd",,$B10,"High"))),"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="273">
-        <f>IFERROR(IF($B10="","",VALUE(RTD("tt.rtd",,$B10,"Low"))),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="273">
+      <c r="C10" s="275">
+        <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"Bid"))),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="275">
+        <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"Ask"))),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="275">
+        <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"High"))),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="275">
+        <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"Low"))),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="275">
         <f>IF(OR($C10="",$D10=""),"",($C10+$D10)/2)</f>
         <v/>
       </c>
-      <c r="H10" s="273">
+      <c r="H10" s="275">
         <f>IF(OR($C10="",$D10=""),"",$D10-$C10)</f>
         <v/>
       </c>
-      <c r="I10" s="274" t="inlineStr">
+      <c r="I10" s="276" t="inlineStr">
         <is>
           <t>Exchange-listed inter-product spread</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="143">
-      <c r="A11" s="234" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="144">
+      <c r="A11" s="236" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="B11" s="273">
+      <c r="B11" s="275">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A11)</f>
         <v/>
       </c>
-      <c r="C11" s="273">
-        <f>IFERROR(IF($B11="","",VALUE(RTD("tt.rtd",,$B11,"Bid"))),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="273">
-        <f>IFERROR(IF($B11="","",VALUE(RTD("tt.rtd",,$B11,"Ask"))),"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="273">
-        <f>IFERROR(IF($B11="","",VALUE(RTD("tt.rtd",,$B11,"High"))),"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="273">
-        <f>IFERROR(IF($B11="","",VALUE(RTD("tt.rtd",,$B11,"Low"))),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="273">
+      <c r="C11" s="275">
+        <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"Bid"))),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="275">
+        <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"Ask"))),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="275">
+        <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"High"))),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="275">
+        <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"Low"))),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="275">
         <f>IF(OR($C11="",$D11=""),"",($C11+$D11)/2)</f>
         <v/>
       </c>
-      <c r="H11" s="273">
+      <c r="H11" s="275">
         <f>IF(OR($C11="",$D11=""),"",$D11-$C11)</f>
         <v/>
       </c>
-      <c r="I11" s="274" t="inlineStr">
+      <c r="I11" s="276" t="inlineStr">
         <is>
           <t>Exchange-listed crack spread</t>
         </is>
@@ -5897,516 +5908,516 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
-    <row r="15" ht="15" customHeight="1" s="143">
-      <c r="A15" s="272" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="144">
+      <c r="A15" s="274" t="inlineStr">
         <is>
           <t>DERIVED &amp; LISTED SPREADS (display)</t>
         </is>
       </c>
-      <c r="B15" s="233" t="inlineStr">
+      <c r="B15" s="235" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="C15" s="233" t="inlineStr">
+      <c r="C15" s="235" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="D15" s="233" t="inlineStr">
+      <c r="D15" s="235" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="E15" s="233" t="inlineStr">
+      <c r="E15" s="235" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="F15" s="233" t="inlineStr">
+      <c r="F15" s="235" t="inlineStr">
         <is>
           <t>Width</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="143">
-      <c r="A16" s="234" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="144">
+      <c r="A16" s="236" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="B16" s="241" t="inlineStr">
+      <c r="B16" s="243" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C16" s="273">
+      <c r="C16" s="275">
         <f>IF(OR($C$9="",$D$8=""),"",$C$9-$D$8)</f>
         <v/>
       </c>
-      <c r="D16" s="273">
+      <c r="D16" s="275">
         <f>IF(OR($D$9="",$C$8=""),"",$D$9-$C$8)</f>
         <v/>
       </c>
-      <c r="E16" s="273">
+      <c r="E16" s="275">
         <f>IF(OR($G$9="",$G$8=""),"",$G$9-$G$8)</f>
         <v/>
       </c>
-      <c r="F16" s="273">
+      <c r="F16" s="275">
         <f>IF(OR($C16="",$D16=""),"",$D16-$C16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="143">
-      <c r="A17" s="234" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="144">
+      <c r="A17" s="236" t="inlineStr">
         <is>
           <t>HO/CL crack</t>
         </is>
       </c>
-      <c r="B17" s="241" t="inlineStr">
+      <c r="B17" s="243" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C17" s="273">
+      <c r="C17" s="275">
         <f>IF(OR($C$7="",$D$8=""),"",$C$7*42-$D$8)</f>
         <v/>
       </c>
-      <c r="D17" s="273">
+      <c r="D17" s="275">
         <f>IF(OR($D$7="",$C$8=""),"",$D$7*42-$C$8)</f>
         <v/>
       </c>
-      <c r="E17" s="273">
+      <c r="E17" s="275">
         <f>IF(OR($G$7="",$G$8=""),"",$G$7*42-$G$8)</f>
         <v/>
       </c>
-      <c r="F17" s="273">
+      <c r="F17" s="275">
         <f>IF(OR($C17="",$D17=""),"",$D17-$C17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="143">
-      <c r="A18" s="234" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="144">
+      <c r="A18" s="236" t="inlineStr">
         <is>
           <t>3:2:1 crack</t>
         </is>
       </c>
-      <c r="B18" s="241" t="inlineStr">
+      <c r="B18" s="243" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C18" s="273">
+      <c r="C18" s="275">
         <f>IF(OR($C$6="",$C$7="",$D$8=""),"",(($C$6*2*42)+($C$7*1*42)-($D$8*3))/3)</f>
         <v/>
       </c>
-      <c r="D18" s="273">
+      <c r="D18" s="275">
         <f>IF(OR($D$6="",$D$7="",$C$8=""),"",(($D$6*2*42)+($D$7*1*42)-($C$8*3))/3)</f>
         <v/>
       </c>
-      <c r="E18" s="273">
+      <c r="E18" s="275">
         <f>IF(OR($G$6="",$G$7="",$G$8=""),"",(($G$6*2*42)+($G$7*1*42)-($G$8*3))/3)</f>
         <v/>
       </c>
-      <c r="F18" s="273">
+      <c r="F18" s="275">
         <f>IF(OR($C18="",$D18=""),"",$D18-$C18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="143">
-      <c r="A19" s="234" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="144">
+      <c r="A19" s="236" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="B19" s="241" t="inlineStr">
+      <c r="B19" s="243" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="C19" s="273">
+      <c r="C19" s="275">
         <f>$C$10</f>
         <v/>
       </c>
-      <c r="D19" s="273">
+      <c r="D19" s="275">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="E19" s="273">
+      <c r="E19" s="275">
         <f>$G$10</f>
         <v/>
       </c>
-      <c r="F19" s="273">
+      <c r="F19" s="275">
         <f>IF(OR($C19="",$D19=""),"",$D19-$C19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="143">
-      <c r="A20" s="234" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="144">
+      <c r="A20" s="236" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="B20" s="241" t="inlineStr">
+      <c r="B20" s="243" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="C20" s="273">
+      <c r="C20" s="275">
         <f>$C$11</f>
         <v/>
       </c>
-      <c r="D20" s="273">
+      <c r="D20" s="275">
         <f>$D$11</f>
         <v/>
       </c>
-      <c r="E20" s="273">
+      <c r="E20" s="275">
         <f>$G$11</f>
         <v/>
       </c>
-      <c r="F20" s="273">
+      <c r="F20" s="275">
         <f>IF(OR($C20="",$D20=""),"",$D20-$C20)</f>
         <v/>
       </c>
     </row>
     <row r="21"/>
     <row r="22"/>
-    <row r="23" ht="15" customHeight="1" s="143">
-      <c r="A23" s="275" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="144">
+      <c r="A23" s="277" t="inlineStr">
         <is>
           <t>MONITOR LEGS</t>
         </is>
       </c>
-      <c r="B23" s="231" t="inlineStr">
+      <c r="B23" s="233" t="inlineStr">
         <is>
           <t>Edit these formulas to redefine what a monitored spread is made of. spread = LegB - HEDGE_RATIO x LegA, and nothing else - no carry, no fair-value term.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="143">
-      <c r="A24" s="233" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="144">
+      <c r="A24" s="235" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B24" s="233" t="inlineStr">
+      <c r="B24" s="235" t="inlineStr">
         <is>
           <t>Side</t>
         </is>
       </c>
-      <c r="C24" s="233" t="inlineStr">
+      <c r="C24" s="235" t="inlineStr">
         <is>
           <t>Composition</t>
         </is>
       </c>
-      <c r="D24" s="233" t="inlineStr">
+      <c r="D24" s="235" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="E24" s="233" t="inlineStr">
+      <c r="E24" s="235" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="F24" s="233" t="inlineStr">
+      <c r="F24" s="235" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="143">
-      <c r="A25" s="276" t="n">
+    <row r="25" ht="15" customHeight="1" s="144">
+      <c r="A25" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="250" t="inlineStr">
+      <c r="B25" s="252" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C25" s="277" t="inlineStr">
+      <c r="C25" s="279" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D25" s="273">
+      <c r="D25" s="275">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E25" s="273">
+      <c r="E25" s="275">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F25" s="273">
+      <c r="F25" s="275">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="143">
-      <c r="A26" s="276" t="n">
+    <row r="26" ht="15" customHeight="1" s="144">
+      <c r="A26" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="250" t="inlineStr">
+      <c r="B26" s="252" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C26" s="277" t="inlineStr">
+      <c r="C26" s="279" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="D26" s="273">
+      <c r="D26" s="275">
         <f>$C$9</f>
         <v/>
       </c>
-      <c r="E26" s="273">
+      <c r="E26" s="275">
         <f>$D$9</f>
         <v/>
       </c>
-      <c r="F26" s="273">
+      <c r="F26" s="275">
         <f>$G$9</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="143">
-      <c r="A27" s="276" t="n">
+    <row r="27" ht="15" customHeight="1" s="144">
+      <c r="A27" s="278" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="250" t="inlineStr">
+      <c r="B27" s="252" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C27" s="277" t="inlineStr">
+      <c r="C27" s="279" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D27" s="273">
+      <c r="D27" s="275">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E27" s="273">
+      <c r="E27" s="275">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F27" s="273">
+      <c r="F27" s="275">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="143">
-      <c r="A28" s="276" t="n">
+    <row r="28" ht="15" customHeight="1" s="144">
+      <c r="A28" s="278" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="250" t="inlineStr">
+      <c r="B28" s="252" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C28" s="277" t="inlineStr">
+      <c r="C28" s="279" t="inlineStr">
         <is>
           <t>HOV6 x 42</t>
         </is>
       </c>
-      <c r="D28" s="273">
+      <c r="D28" s="275">
         <f>IF($C$7="","",$C$7*42)</f>
         <v/>
       </c>
-      <c r="E28" s="273">
+      <c r="E28" s="275">
         <f>IF($D$7="","",$D$7*42)</f>
         <v/>
       </c>
-      <c r="F28" s="273">
+      <c r="F28" s="275">
         <f>IF($G$7="","",$G$7*42)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="143">
-      <c r="A29" s="276" t="n">
+    <row r="29" ht="15" customHeight="1" s="144">
+      <c r="A29" s="278" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="250" t="inlineStr">
+      <c r="B29" s="252" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C29" s="277" t="inlineStr">
+      <c r="C29" s="279" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D29" s="273">
+      <c r="D29" s="275">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E29" s="273">
+      <c r="E29" s="275">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F29" s="273">
+      <c r="F29" s="275">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="143">
-      <c r="A30" s="276" t="n">
+    <row r="30" ht="15" customHeight="1" s="144">
+      <c r="A30" s="278" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="250" t="inlineStr">
+      <c r="B30" s="252" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C30" s="277" t="inlineStr">
+      <c r="C30" s="279" t="inlineStr">
         <is>
           <t>(2 x RBV6 + 1 x HOV6) x 42 / 3</t>
         </is>
       </c>
-      <c r="D30" s="273">
+      <c r="D30" s="275">
         <f>IF(OR($C$6="",$C$7=""),"",($C$6*2*42+$C$7*1*42)/3)</f>
         <v/>
       </c>
-      <c r="E30" s="273">
+      <c r="E30" s="275">
         <f>IF(OR($D$6="",$D$7=""),"",($D$6*2*42+$D$7*1*42)/3)</f>
         <v/>
       </c>
-      <c r="F30" s="273">
+      <c r="F30" s="275">
         <f>IF(OR($G$6="",$G$7=""),"",($G$6*2*42+$G$7*1*42)/3)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="143">
-      <c r="A31" s="276" t="n">
+    <row r="31" ht="15" customHeight="1" s="144">
+      <c r="A31" s="278" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="250" t="inlineStr">
+      <c r="B31" s="252" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C31" s="277" t="inlineStr">
+      <c r="C31" s="279" t="inlineStr">
         <is>
           <t>(none - LISTED spread)</t>
         </is>
       </c>
-      <c r="D31" s="273" t="inlineStr"/>
-      <c r="E31" s="273" t="inlineStr"/>
-      <c r="F31" s="273" t="inlineStr"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="143">
-      <c r="A32" s="276" t="n">
+      <c r="D31" s="275" t="inlineStr"/>
+      <c r="E31" s="275" t="inlineStr"/>
+      <c r="F31" s="275" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="144">
+      <c r="A32" s="278" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="250" t="inlineStr">
+      <c r="B32" s="252" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C32" s="277" t="inlineStr">
+      <c r="C32" s="279" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="D32" s="273">
+      <c r="D32" s="275">
         <f>$C$10</f>
         <v/>
       </c>
-      <c r="E32" s="273">
+      <c r="E32" s="275">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="F32" s="273">
+      <c r="F32" s="275">
         <f>$G$10</f>
         <v/>
       </c>
     </row>
     <row r="33"/>
-    <row r="34" ht="15" customHeight="1" s="143">
-      <c r="A34" s="275" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="144">
+      <c r="A34" s="277" t="inlineStr">
         <is>
           <t>LISTED-EQUIVALENT ROW PER SLOT  (for the side-by-side crossing-cost comparison)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="143">
-      <c r="A35" s="233" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="144">
+      <c r="A35" s="235" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B35" s="233" t="inlineStr">
+      <c r="B35" s="235" t="inlineStr">
         <is>
           <t>Feed derived row</t>
         </is>
       </c>
-      <c r="C35" s="233" t="inlineStr">
+      <c r="C35" s="235" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="143">
-      <c r="A36" s="276" t="n">
+    <row r="36" ht="15" customHeight="1" s="144">
+      <c r="A36" s="278" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="276" t="n">
+      <c r="B36" s="278" t="n">
         <v>19</v>
       </c>
-      <c r="C36" s="277" t="inlineStr">
+      <c r="C36" s="279" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="143">
-      <c r="A37" s="276" t="n">
+    <row r="37" ht="15" customHeight="1" s="144">
+      <c r="A37" s="278" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="276" t="n">
+      <c r="B37" s="278" t="n">
         <v>20</v>
       </c>
-      <c r="C37" s="277" t="inlineStr">
+      <c r="C37" s="279" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="143">
-      <c r="A38" s="276" t="n">
+    <row r="38" ht="15" customHeight="1" s="144">
+      <c r="A38" s="278" t="n">
         <v>3</v>
       </c>
-      <c r="B38" s="276" t="n"/>
-      <c r="C38" s="277" t="inlineStr">
+      <c r="B38" s="278" t="n"/>
+      <c r="C38" s="279" t="inlineStr">
         <is>
           <t>(none)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="143">
-      <c r="A39" s="276" t="n">
+    <row r="39" ht="15" customHeight="1" s="144">
+      <c r="A39" s="278" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="276" t="n">
+      <c r="B39" s="278" t="n">
         <v>19</v>
       </c>
-      <c r="C39" s="277" t="inlineStr">
+      <c r="C39" s="279" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
     <row r="40"/>
-    <row r="41" ht="15" customHeight="1" s="143">
-      <c r="A41" s="231" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="144">
+      <c r="A41" s="233" t="inlineStr">
         <is>
           <t>Crossing convention used throughout:  spread bid = LegB bid - beta x LegA ask ; spread ask = LegB ask - beta x LegA bid ; spread mid = LegB mid - beta x LegA mid.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="143">
-      <c r="A42" s="231" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="144">
+      <c r="A42" s="233" t="inlineStr">
         <is>
           <t>For a LISTED slot LegA is empty and is treated as zero, so the listed quote passes straight through untouched.</t>
         </is>
@@ -6428,235 +6439,235 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="15" customWidth="1" style="141" min="1" max="2"/>
-    <col width="3" customWidth="1" style="141" min="3" max="3"/>
-    <col width="15" customWidth="1" style="141" min="4" max="5"/>
-    <col width="3" customWidth="1" style="141" min="6" max="6"/>
-    <col width="15" customWidth="1" style="141" min="7" max="8"/>
-    <col width="3" customWidth="1" style="141" min="9" max="9"/>
-    <col width="15" customWidth="1" style="141" min="10" max="11"/>
-    <col width="26" customWidth="1" style="141" min="13" max="13"/>
-    <col width="30" customWidth="1" style="141" min="14" max="14"/>
+    <col width="15" customWidth="1" style="142" min="1" max="2"/>
+    <col width="3" customWidth="1" style="142" min="3" max="3"/>
+    <col width="15" customWidth="1" style="142" min="4" max="5"/>
+    <col width="3" customWidth="1" style="142" min="6" max="6"/>
+    <col width="15" customWidth="1" style="142" min="7" max="8"/>
+    <col width="3" customWidth="1" style="142" min="9" max="9"/>
+    <col width="15" customWidth="1" style="142" min="10" max="11"/>
+    <col width="26" customWidth="1" style="142" min="13" max="13"/>
+    <col width="30" customWidth="1" style="142" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="143">
-      <c r="A1" s="278" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="144">
+      <c r="A1" s="280" t="inlineStr">
         <is>
           <t>BUFFER  -  hidden.  Flushed circular buffers (crash / restart recovery).</t>
         </is>
       </c>
-      <c r="M1" s="231" t="inlineStr">
+      <c r="M1" s="233" t="inlineStr">
         <is>
           <t>Written by VBA every FLUSH_SEC seconds, so a crash loses at most a minute.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="143">
-      <c r="M2" s="231" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="144">
+      <c r="M2" s="233" t="inlineStr">
         <is>
           <t>On open, WarmStart reloads a slot only if its stamped LOOKBACK_MIN, HEDGE_RATIO and leg labels still match Config, and the newest sample is younger than WARM_START_MAX_AGE_MIN.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="143">
-      <c r="A3" s="275" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="144">
+      <c r="A3" s="277" t="inlineStr">
         <is>
           <t>SLOT 1</t>
         </is>
       </c>
-      <c r="D3" s="275" t="inlineStr">
+      <c r="D3" s="277" t="inlineStr">
         <is>
           <t>SLOT 2</t>
         </is>
       </c>
-      <c r="G3" s="275" t="inlineStr">
+      <c r="G3" s="277" t="inlineStr">
         <is>
           <t>SLOT 3</t>
         </is>
       </c>
-      <c r="J3" s="275" t="inlineStr">
+      <c r="J3" s="277" t="inlineStr">
         <is>
           <t>SLOT 4</t>
         </is>
       </c>
-      <c r="M3" s="231" t="inlineStr">
+      <c r="M3" s="233" t="inlineStr">
         <is>
           <t>Elapsed collection is credited from the OLDEST recovered sample - otherwise every restart costs another two hours before a usable z.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="143">
-      <c r="A4" s="274" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="144">
+      <c r="A4" s="276" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B4" s="273" t="n"/>
-      <c r="D4" s="274" t="inlineStr">
+      <c r="B4" s="275" t="n"/>
+      <c r="D4" s="276" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E4" s="273" t="n"/>
-      <c r="G4" s="274" t="inlineStr">
+      <c r="E4" s="275" t="n"/>
+      <c r="G4" s="276" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="H4" s="273" t="n"/>
-      <c r="J4" s="274" t="inlineStr">
+      <c r="H4" s="275" t="n"/>
+      <c r="J4" s="276" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K4" s="273" t="n"/>
-      <c r="M4" s="231" t="inlineStr">
+      <c r="K4" s="275" t="n"/>
+      <c r="M4" s="233" t="inlineStr">
         <is>
           <t>Seeding drops CONSECUTIVE identical values only. A spread genuinely revisiting a level is a real observation, not a duplicate.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="143">
-      <c r="A5" s="274" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="144">
+      <c r="A5" s="276" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="B5" s="273" t="n"/>
-      <c r="D5" s="274" t="inlineStr">
+      <c r="B5" s="275" t="n"/>
+      <c r="D5" s="276" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="E5" s="273" t="n"/>
-      <c r="G5" s="274" t="inlineStr">
+      <c r="E5" s="275" t="n"/>
+      <c r="G5" s="276" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="H5" s="273" t="n"/>
-      <c r="J5" s="274" t="inlineStr">
+      <c r="H5" s="275" t="n"/>
+      <c r="J5" s="276" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="K5" s="273" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="143">
-      <c r="A6" s="274" t="inlineStr">
+      <c r="K5" s="275" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="144">
+      <c r="A6" s="276" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="B6" s="273" t="n"/>
-      <c r="D6" s="274" t="inlineStr">
+      <c r="B6" s="275" t="n"/>
+      <c r="D6" s="276" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="E6" s="273" t="n"/>
-      <c r="G6" s="274" t="inlineStr">
+      <c r="E6" s="275" t="n"/>
+      <c r="G6" s="276" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="H6" s="273" t="n"/>
-      <c r="J6" s="274" t="inlineStr">
+      <c r="H6" s="275" t="n"/>
+      <c r="J6" s="276" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="K6" s="273" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="143">
-      <c r="A7" s="274" t="inlineStr">
+      <c r="K6" s="275" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="144">
+      <c r="A7" s="276" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="B7" s="273" t="n"/>
-      <c r="D7" s="274" t="inlineStr">
+      <c r="B7" s="275" t="n"/>
+      <c r="D7" s="276" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="E7" s="273" t="n"/>
-      <c r="G7" s="274" t="inlineStr">
+      <c r="E7" s="275" t="n"/>
+      <c r="G7" s="276" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="H7" s="273" t="n"/>
-      <c r="J7" s="274" t="inlineStr">
+      <c r="H7" s="275" t="n"/>
+      <c r="J7" s="276" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="K7" s="273" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="143">
-      <c r="A8" s="274" t="inlineStr">
+      <c r="K7" s="275" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="144">
+      <c r="A8" s="276" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="B8" s="273" t="n"/>
-      <c r="D8" s="274" t="inlineStr">
+      <c r="B8" s="275" t="n"/>
+      <c r="D8" s="276" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="E8" s="273" t="n"/>
-      <c r="G8" s="274" t="inlineStr">
+      <c r="E8" s="275" t="n"/>
+      <c r="G8" s="276" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="H8" s="273" t="n"/>
-      <c r="J8" s="274" t="inlineStr">
+      <c r="H8" s="275" t="n"/>
+      <c r="J8" s="276" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="K8" s="273" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="143">
-      <c r="A9" s="233" t="inlineStr">
+      <c r="K8" s="275" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="144">
+      <c r="A9" s="235" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="B9" s="233" t="inlineStr">
+      <c r="B9" s="235" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="D9" s="233" t="inlineStr">
+      <c r="D9" s="235" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="E9" s="233" t="inlineStr">
+      <c r="E9" s="235" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="G9" s="233" t="inlineStr">
+      <c r="G9" s="235" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="H9" s="233" t="inlineStr">
+      <c r="H9" s="235" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="J9" s="233" t="inlineStr">
+      <c r="J9" s="235" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="K9" s="233" t="inlineStr">
+      <c r="K9" s="235" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
@@ -6678,87 +6689,87 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="20" customWidth="1" style="141" min="1" max="1"/>
-    <col width="30" customWidth="1" style="141" min="2" max="2"/>
-    <col width="20" customWidth="1" style="141" min="3" max="3"/>
-    <col width="9" customWidth="1" style="141" min="4" max="4"/>
-    <col width="12" customWidth="1" style="141" min="5" max="9"/>
-    <col width="16" customWidth="1" style="141" min="10" max="10"/>
-    <col width="10" customWidth="1" style="141" min="11" max="11"/>
-    <col width="60" customWidth="1" style="141" min="12" max="12"/>
+    <col width="20" customWidth="1" style="142" min="1" max="1"/>
+    <col width="30" customWidth="1" style="142" min="2" max="2"/>
+    <col width="20" customWidth="1" style="142" min="3" max="3"/>
+    <col width="9" customWidth="1" style="142" min="4" max="4"/>
+    <col width="12" customWidth="1" style="142" min="5" max="9"/>
+    <col width="16" customWidth="1" style="142" min="10" max="10"/>
+    <col width="10" customWidth="1" style="142" min="11" max="11"/>
+    <col width="60" customWidth="1" style="142" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="143">
-      <c r="A1" s="278" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="144">
+      <c r="A1" s="280" t="inlineStr">
         <is>
           <t>LOG  -  timestamped signal events</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="143">
-      <c r="A2" s="231" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="144">
+      <c r="A2" s="233" t="inlineStr">
         <is>
           <t>One line when a state STARTS and one when it CLEARS - never one per poll. Reviewable after the session.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="143">
-      <c r="A3" s="233" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="144">
+      <c r="A3" s="235" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B3" s="233" t="inlineStr">
+      <c r="B3" s="235" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C3" s="233" t="inlineStr">
+      <c r="C3" s="235" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D3" s="233" t="inlineStr">
+      <c r="D3" s="235" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E3" s="233" t="inlineStr">
+      <c r="E3" s="235" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="F3" s="233" t="inlineStr">
+      <c r="F3" s="235" t="inlineStr">
         <is>
           <t>Sigma</t>
         </is>
       </c>
-      <c r="G3" s="233" t="inlineStr">
+      <c r="G3" s="235" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="H3" s="233" t="inlineStr">
+      <c r="H3" s="235" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I3" s="233" t="inlineStr">
+      <c r="I3" s="235" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J3" s="233" t="inlineStr">
+      <c r="J3" s="235" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="K3" s="233" t="inlineStr">
+      <c r="K3" s="235" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="L3" s="233" t="inlineStr">
+      <c r="L3" s="235" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -6780,307 +6791,307 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="4" customWidth="1" style="141" min="1" max="1"/>
-    <col width="46" customWidth="1" style="141" min="2" max="2"/>
-    <col width="16" customWidth="1" style="141" min="3" max="6"/>
-    <col width="60" customWidth="1" style="141" min="7" max="7"/>
+    <col width="4" customWidth="1" style="142" min="1" max="1"/>
+    <col width="46" customWidth="1" style="142" min="2" max="2"/>
+    <col width="16" customWidth="1" style="142" min="3" max="6"/>
+    <col width="60" customWidth="1" style="142" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.7" customHeight="1" s="143">
-      <c r="B1" s="254" t="inlineStr">
+    <row r="1" ht="19.7" customHeight="1" s="144">
+      <c r="B1" s="256" t="inlineStr">
         <is>
           <t>SETUP  -  turning this .xlsx into the working .xlsm</t>
         </is>
       </c>
     </row>
     <row r="2"/>
-    <row r="3" ht="30" customHeight="1" s="143">
-      <c r="B3" s="279" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="144">
+      <c r="B3" s="281" t="inlineStr">
         <is>
           <t>openpyxl cannot author VBA, so this file ships as an .xlsx carrying all structure and formatting, plus a .bas module to import. Six steps, once.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="143">
-      <c r="B4" s="280" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="144">
+      <c r="B4" s="282" t="inlineStr">
         <is>
           <t>1.  Open TT_ZScore_Monitor.xlsx in Excel on the machine running TT and the TT RTD server.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="143">
-      <c r="B5" s="280" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="144">
+      <c r="B5" s="282" t="inlineStr">
         <is>
           <t>2.  File &gt; Save As &gt; Excel Macro-Enabled Workbook (.xlsm). Keep the same folder.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="143">
-      <c r="B6" s="280" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="144">
+      <c r="B6" s="282" t="inlineStr">
         <is>
           <t>3.  Alt+F11 to open the VBA editor.  File &gt; Import File...  and choose TTZMonitor.bas.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="143">
-      <c r="B7" s="280" t="inlineStr">
+    <row r="7" ht="30" customHeight="1" s="144">
+      <c r="B7" s="282" t="inlineStr">
         <is>
           <t>4.  In the editor, double-click ThisWorkbook and paste the two-line Workbook_Open / Workbook_BeforeClose stub printed at the bottom of TTZMonitor.bas.  (Optional - it just auto-starts the monitor and warm-starts the buffers.)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="143">
-      <c r="B8" s="280" t="inlineStr">
+    <row r="8" ht="30" customHeight="1" s="144">
+      <c r="B8" s="282" t="inlineStr">
         <is>
           <t>5.  Back on Dashboard, insert two shapes over cells N2 and P2 (Insert &gt; Shapes &gt; Rectangle), right-click each &gt; Assign Macro &gt; StartMonitor and StopMonitor. Until you do, run them from Alt+F8.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="143">
-      <c r="B9" s="280" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="144">
+      <c r="B9" s="282" t="inlineStr">
         <is>
           <t>6.  Save. Click START. The Feed sheet stays hidden; you never need to look at it.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="143">
-      <c r="B10" s="279" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="144">
+      <c r="B10" s="281" t="inlineStr">
         <is>
           <t>Step 4 is NOT optional here. The capture timer is a Windows user32 timer, and one that outlives the workbook keeps firing into a module that no longer has its sheets - which crashes Excel. Workbook_BeforeClose calls StopMonitor and kills it.</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="15" customHeight="1" s="143">
-      <c r="B12" s="232" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="144">
+      <c r="B12" s="234" t="inlineStr">
         <is>
           <t>WHAT TO CHECK ON THE FIRST RUN</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="25.5" customHeight="1" s="143">
-      <c r="B13" s="281" t="inlineStr">
+    <row r="13" ht="25.5" customHeight="1" s="144">
+      <c r="B13" s="283" t="inlineStr">
         <is>
           <t>-  Feed sheet column B (instrument ids) fills in. If it stays blank, the TT short name in Feed column A does not match TT, or the market in Dashboard!C4 is wrong.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="25.5" customHeight="1" s="143">
-      <c r="B14" s="281" t="inlineStr">
+    <row r="14" ht="25.5" customHeight="1" s="144">
+      <c r="B14" s="283" t="inlineStr">
         <is>
           <t>-  Dashboard prices move, but the sheet does NOT flash. If it flashes, something volatile has been reintroduced - search the workbook for NOW, TODAY, OFFSET, INDIRECT, RAND.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="25.5" customHeight="1" s="143">
-      <c r="B15" s="281" t="inlineStr">
+    <row r="15" ht="25.5" customHeight="1" s="144">
+      <c r="B15" s="283" t="inlineStr">
         <is>
           <t>-  The samples counter climbs at roughly the quotes/min rate, not at the timer rate. If it climbs at the timer rate, dedupe is not working and every z you see will be fiction.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="25.5" customHeight="1" s="143">
-      <c r="B16" s="281" t="inlineStr">
+    <row r="16" ht="25.5" customHeight="1" s="144">
+      <c r="B16" s="283" t="inlineStr">
         <is>
           <t>-  Warm-up takes MIN_HISTORY_MIN (default 120) minutes on a cold start. That is deliberate.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="25.5" customHeight="1" s="143">
-      <c r="B17" s="281" t="inlineStr">
+    <row r="17" ht="25.5" customHeight="1" s="144">
+      <c r="B17" s="283" t="inlineStr">
         <is>
           <t>-  A 'ticks' folder appears beside the workbook, one CSV per spread per day, holding every changed quote. That is the raw record - keep it for the first week or two.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="25.5" customHeight="1" s="143">
-      <c r="B18" s="281" t="inlineStr">
+    <row r="18" ht="25.5" customHeight="1" s="144">
+      <c r="B18" s="283" t="inlineStr">
         <is>
           <t>-  After a week, run Alt+F8 &gt; CheckSubsamplingLoss. It compares mean and sigma over the live window at full fidelity against 250 / 500 / 1000 / 2000 / 5000 ms subsampling and writes the comparison to the Log. If sigma is materially unchanged, set STORE_MIN_INTERVAL_MS and reclaim the memory.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20" ht="15" customHeight="1" s="143">
-      <c r="B20" s="232" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="144">
+      <c r="B20" s="234" t="inlineStr">
         <is>
           <t>WHAT SIGMA THIS SPREAD MUST HAVE TO BE WORTH TRADING</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="143">
-      <c r="B21" s="231" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="144">
+      <c r="B21" s="233" t="inlineStr">
         <is>
           <t>Live off Config. Edit the two assumed market widths below; everything else follows.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="143">
-      <c r="B22" s="264" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="144">
+      <c r="B22" s="266" t="inlineStr">
         <is>
           <t>Assumed width, each outright leg (spread units)</t>
         </is>
       </c>
-      <c r="C22" s="265" t="n">
+      <c r="C22" s="267" t="n">
         <v>0.02</v>
       </c>
-      <c r="E22" s="264" t="inlineStr">
+      <c r="E22" s="266" t="inlineStr">
         <is>
           <t>Assumed width, listed spread (spread units)</t>
         </is>
       </c>
-      <c r="F22" s="265" t="n">
+      <c r="F22" s="267" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="22.35" customHeight="1" s="143">
-      <c r="B24" s="233" t="inlineStr">
+    <row r="24" ht="22.35" customHeight="1" s="144">
+      <c r="B24" s="235" t="inlineStr">
         <is>
           <t>At LOTS from Config, per leg</t>
         </is>
       </c>
-      <c r="C24" s="233" t="inlineStr">
+      <c r="C24" s="235" t="inlineStr">
         <is>
           <t>Total cost</t>
         </is>
       </c>
-      <c r="D24" s="233" t="inlineStr">
+      <c r="D24" s="235" t="inlineStr">
         <is>
           <t>min sigma @ z = 3.0</t>
         </is>
       </c>
-      <c r="E24" s="233" t="inlineStr">
+      <c r="E24" s="235" t="inlineStr">
         <is>
           <t>min sigma @ z = 2.5</t>
         </is>
       </c>
-      <c r="F24" s="233" t="inlineStr">
+      <c r="F24" s="235" t="inlineStr">
         <is>
           <t>min sigma @ live ENTRY_Z</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="143">
-      <c r="B25" s="270" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="144">
+      <c r="B25" s="272" t="inlineStr">
         <is>
           <t>Legging the outrights</t>
         </is>
       </c>
-      <c r="C25" s="282">
+      <c r="C25" s="284">
         <f>2*Config!$B$73*Config!$B$41+(2*$C$22)*1000*Config!$B$41</f>
         <v/>
       </c>
-      <c r="D25" s="283">
+      <c r="D25" s="285">
         <f>Config!$B$46*$C$25/(0.5*3*1000*Config!$B$41)</f>
         <v/>
       </c>
-      <c r="E25" s="283">
+      <c r="E25" s="285">
         <f>Config!$B$46*$C$25/(0.5*2.5*1000*Config!$B$41)</f>
         <v/>
       </c>
-      <c r="F25" s="283">
+      <c r="F25" s="285">
         <f>Config!$B$46*$C$25/(0.5*Config!$B$34*1000*Config!$B$41)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="143">
-      <c r="B26" s="270" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="144">
+      <c r="B26" s="272" t="inlineStr">
         <is>
           <t>Listed inter-product spread</t>
         </is>
       </c>
-      <c r="C26" s="282">
+      <c r="C26" s="284">
         <f>2*Config!$B$73*Config!$B$41+$F$22*1000*Config!$B$41</f>
         <v/>
       </c>
-      <c r="D26" s="283">
+      <c r="D26" s="285">
         <f>Config!$B$46*$C$26/(0.5*3*1000*Config!$B$41)</f>
         <v/>
       </c>
-      <c r="E26" s="283">
+      <c r="E26" s="285">
         <f>Config!$B$46*$C$26/(0.5*2.5*1000*Config!$B$41)</f>
         <v/>
       </c>
-      <c r="F26" s="283">
+      <c r="F26" s="285">
         <f>Config!$B$46*$C$26/(0.5*Config!$B$34*1000*Config!$B$41)</f>
         <v/>
       </c>
     </row>
     <row r="27"/>
-    <row r="28" ht="15" customHeight="1" s="143">
-      <c r="B28" s="231" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="144">
+      <c r="B28" s="233" t="inlineStr">
         <is>
           <t>capture = 0.5 x |z| x sigma x USD-per-point x LOTS.  An entry passes when capture &gt;= EDGE_MULTIPLE x total cost.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="143">
-      <c r="B29" s="253" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="144">
+      <c r="B29" s="255" t="inlineStr">
         <is>
           <t>A lower ENTRY_Z means less expected capture per entry, so it RAISES the sigma the spread must have. 2.5 instead of 3.0 raises it by about 20%.</t>
         </is>
       </c>
     </row>
     <row r="30"/>
-    <row r="31" ht="15" customHeight="1" s="143">
-      <c r="B31" s="232" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="144">
+      <c r="B31" s="234" t="inlineStr">
         <is>
           <t>ASSUMPTIONS MADE WHILE BUILDING THIS - CHECK THEM</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="39.75" customHeight="1" s="143">
-      <c r="B32" s="281" t="inlineStr">
+    <row r="32" ht="39.75" customHeight="1" s="144">
+      <c r="B32" s="283" t="inlineStr">
         <is>
           <t>-  The repository was empty, so the existing Dashboard layout was reconstructed from the cell references given in the spec (C4, B6, C7, H7/H8, P7/P8, H12/H13/H14/I14, L3). Those coordinates are honoured exactly; the surrounding rows are a best reconstruction. Compare against your live sheet before relying on it.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="39.75" customHeight="1" s="143">
-      <c r="B33" s="281" t="inlineStr">
+    <row r="33" ht="39.75" customHeight="1" s="144">
+      <c r="B33" s="283" t="inlineStr">
         <is>
           <t>-  The 3:2:1 ask row now mirrors the bid row: I15 uses H14 (CL BID), not I14. The bid row is unchanged. This is the convention the spec described; confirm it is the one you want.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="39.75" customHeight="1" s="143">
-      <c r="B34" s="281" t="inlineStr">
+    <row r="34" ht="39.75" customHeight="1" s="144">
+      <c r="B34" s="283" t="inlineStr">
         <is>
           <t>-  COMMISSION_BASIS defaults to CONSERVATIVE ($3.82 per lot per leg round turn, reading CME's $1.50 as per side). Switch it to CME_PER_RT on Config if the rate card proves otherwise.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="39.75" customHeight="1" s="143">
-      <c r="B35" s="281" t="inlineStr">
+    <row r="35" ht="39.75" customHeight="1" s="144">
+      <c r="B35" s="283" t="inlineStr">
         <is>
           <t>-  Contracts charged commission: 2 for BZ-CL and the listed spread, 6 for the 3:2:1 crack (2 RB + 1 HO + 3 CL). Change it in the Config spread table if your clearing differs.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="39.75" customHeight="1" s="143">
-      <c r="B36" s="281" t="inlineStr">
+    <row r="36" ht="39.75" customHeight="1" s="144">
+      <c r="B36" s="283" t="inlineStr">
         <is>
           <t>-  Slot 3 (3:2:1) has no exchange-listed equivalent, so its LISTED crossing-cost column reads n/a.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="39.75" customHeight="1" s="143">
-      <c r="B37" s="281" t="inlineStr">
+    <row r="37" ht="39.75" customHeight="1" s="144">
+      <c r="B37" s="283" t="inlineStr">
         <is>
           <t>-  MIN_SIGMA ships at 0 because sigma on these spreads has never been measured. Set it once you have a session of data - until then the degenerate-window guard rests on MAX_ABS_Z alone.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="39.75" customHeight="1" s="143">
-      <c r="B38" s="281" t="inlineStr">
+    <row r="38" ht="39.75" customHeight="1" s="144">
+      <c r="B38" s="283" t="inlineStr">
         <is>
           <t>-  Application.OnTime cannot go below about one second, so capture at 100 ms runs on a user32 SetTimer with an OnTime watchdog that re-arms it (Excel silently kills API timers when a modal dialog opens). If SetTimer is unavailable, CAPTURE_MS is clamped to 1000 and everything still works - only alert latency changes, not the statistics.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="39.75" customHeight="1" s="143">
-      <c r="B39" s="281" t="inlineStr">
+    <row r="39" ht="39.75" customHeight="1" s="144">
+      <c r="B39" s="283" t="inlineStr">
         <is>
           <t>-  Capturing at 100 ms does not mean storing at 100 ms, and after dedupe it does not change sigma either. The window holds quote CHANGES, not poll ticks; subsampling a mean-reverting level series is unbiased. 100 ms buys latency to the chime, which for manual execution is not measurable in human terms - so the real reason to capture fast is simply that no genuine quote change is missed.</t>
         </is>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -1823,7 +1823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A2:V51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col hidden="1" width="2.14" customWidth="1" style="142" min="1" max="1"/>
@@ -1844,7 +1844,6 @@
     <col width="11.43" customWidth="1" style="142" min="27" max="27"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="68.25" customHeight="1" s="144">
       <c r="A2" s="145" t="n"/>
       <c r="B2" s="146" t="n"/>
@@ -2788,7 +2787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="B1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="142" min="1" max="1"/>
@@ -2814,7 +2813,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="144">
       <c r="B4" s="234" t="inlineStr">
         <is>
@@ -2970,7 +2968,6 @@
       <c r="L9" s="240" t="n"/>
       <c r="M9" s="240" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="144">
       <c r="B11" s="234" t="inlineStr">
         <is>
@@ -3120,7 +3117,6 @@
       <c r="L17" s="240" t="n"/>
       <c r="M17" s="240" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="144">
       <c r="B19" s="234" t="inlineStr">
         <is>
@@ -3639,12 +3635,12 @@
     <row r="57" ht="15" customHeight="1" s="144">
       <c r="B57" s="242" t="inlineStr">
         <is>
-          <t>Break-even spread</t>
+          <t>Break-even spread (mid)</t>
         </is>
       </c>
       <c r="C57" s="241" t="inlineStr">
         <is>
-          <t>absolute level</t>
+          <t>absolute level, mid scale</t>
         </is>
       </c>
       <c r="D57" s="240" t="n"/>
@@ -3655,12 +3651,12 @@
     <row r="58" ht="15" customHeight="1" s="144">
       <c r="B58" s="250" t="inlineStr">
         <is>
-          <t>TAKE-PROFIT spread</t>
+          <t>TAKE-PROFIT spread (mid)</t>
         </is>
       </c>
       <c r="C58" s="241" t="inlineStr">
         <is>
-          <t>absolute level</t>
+          <t>absolute level, mid scale</t>
         </is>
       </c>
       <c r="D58" s="254" t="n"/>
@@ -3676,7 +3672,7 @@
       </c>
       <c r="C59" s="241" t="inlineStr">
         <is>
-          <t>spread units</t>
+          <t>required MID move</t>
         </is>
       </c>
       <c r="D59" s="240" t="n"/>
@@ -3800,7 +3796,6 @@
       <c r="F67" s="240" t="n"/>
       <c r="G67" s="240" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69" ht="15" customHeight="1" s="144">
       <c r="B69" s="255" t="inlineStr">
         <is>
@@ -3812,6 +3807,13 @@
       <c r="B70" s="233" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES on Config decides whether a failing edge filter also silences the chime. It ships FALSE, so the chime follows ENTRY_Z alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="233" t="inlineStr">
+        <is>
+          <t>Break-even and take-profit are MID levels, on the same scale as the mean, sigma and z - a mid move of the cost is exactly what pays the round trip. The entry reference above them is the TOUCH you actually get filled at. To work the exit order, cross back: add half the Bid-Ask Gap to close a short, subtract half to close a long.</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4654,7 @@
       </c>
       <c r="E42" s="261" t="inlineStr">
         <is>
-          <t>PCT_NOTIONAL: Take Profit = Entry + Costs + (WIN_PCT x Notional). TARGET_USD: the older rule, Take Profit = Entry + Costs + TARGET_NET_USD.</t>
+          <t>PCT_NOTIONAL: Take Profit = Mid + Costs + (WIN_PCT x Notional). TARGET_USD: the older rule, Take Profit = Mid + Costs + TARGET_NET_USD. The level is anchored to the MID, not the entry touch - the touch already carries half the width.</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5624,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="144">
       <c r="A5" s="274" t="inlineStr">
         <is>
@@ -5905,9 +5906,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="144">
       <c r="A15" s="274" t="inlineStr">
         <is>
@@ -6080,8 +6078,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="144">
       <c r="A23" s="277" t="inlineStr">
         <is>
@@ -6333,7 +6329,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="144">
       <c r="A34" s="277" t="inlineStr">
         <is>
@@ -6408,7 +6403,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="15" customHeight="1" s="144">
       <c r="A41" s="233" t="inlineStr">
         <is>
@@ -6788,7 +6782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="B1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="142" min="1" max="1"/>
@@ -6804,7 +6798,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1" s="144">
       <c r="B3" s="281" t="inlineStr">
         <is>
@@ -6861,7 +6854,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="144">
       <c r="B12" s="234" t="inlineStr">
         <is>
@@ -6911,7 +6903,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="144">
       <c r="B20" s="234" t="inlineStr">
         <is>
@@ -6944,7 +6935,6 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="22.35" customHeight="1" s="144">
       <c r="B24" s="235" t="inlineStr">
         <is>
@@ -7018,7 +7008,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="144">
       <c r="B28" s="233" t="inlineStr">
         <is>
@@ -7033,7 +7022,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="144">
       <c r="B31" s="234" t="inlineStr">
         <is>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -4384,7 +4384,7 @@
       </c>
       <c r="E28" s="261" t="inlineStr">
         <is>
-          <t>Warm-up gate 2. Elapsed collection needed before any z is shown. BOTH gates must pass.</t>
+          <t>Warm-up gate 2. Elapsed collection needed before any z is shown. BOTH gates must pass. MUST BE BELOW LOOKBACK_MIN: eviction caps the window span at the lookback, so a value at or above it can never be met and the monitor warms up forever. Set at or above it and the engine clamps to 99% of LOOKBACK_MIN and says so on the Dashboard status strip.</t>
         </is>
       </c>
     </row>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B43" s="263" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="C43" s="264" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="D43" s="239" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="E43" s="261" t="inlineStr">
         <is>
-          <t>Percentage win, as a FRACTION - 0.01 is 1%, 0.02 is 2%. Used only when TP_MODE = PCT_NOTIONAL.</t>
+          <t>Percentage win, as a FRACTION - 0.01 is 1%, 0.004 is 0.4%. Used only when TP_MODE = PCT_NOTIONAL. 0.004 targets about 1.25 sigma, the same capture the edge filter assumes at ENTRY_Z, which keeps the take-profit inside the mean on all three legged spreads. Re-derive it once sigma has been measured over more than a single window.</t>
         </is>
       </c>
     </row>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -2787,7 +2787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M71"/>
+  <dimension ref="B1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="142" min="1" max="1"/>
@@ -3797,21 +3797,65 @@
       <c r="G67" s="240" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1" s="144">
-      <c r="B69" s="255" t="inlineStr">
+      <c r="B69" s="245" t="inlineStr">
+        <is>
+          <t>THE MEAN AT THE TOUCH  (live Gap - what you would actually deal at)</t>
+        </is>
+      </c>
+      <c r="C69" s="246" t="n"/>
+      <c r="D69" s="246" t="n"/>
+      <c r="E69" s="246" t="n"/>
+      <c r="F69" s="246" t="n"/>
+      <c r="G69" s="246" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="144">
+      <c r="B70" s="250" t="inlineStr">
+        <is>
+          <t>Mean for SHORTING the spread</t>
+        </is>
+      </c>
+      <c r="C70" s="241" t="inlineStr">
+        <is>
+          <t>mean - Gap/2   (you sell the bid)</t>
+        </is>
+      </c>
+      <c r="D70" s="254" t="n"/>
+      <c r="E70" s="254" t="n"/>
+      <c r="F70" s="254" t="n"/>
+      <c r="G70" s="254" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="250" t="inlineStr">
+        <is>
+          <t>Mean for LONGING the spread</t>
+        </is>
+      </c>
+      <c r="C71" s="241" t="inlineStr">
+        <is>
+          <t>mean + Gap/2   (you buy the ask)</t>
+        </is>
+      </c>
+      <c r="D71" s="254" t="n"/>
+      <c r="E71" s="254" t="n"/>
+      <c r="F71" s="254" t="n"/>
+      <c r="G71" s="254" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="255" t="inlineStr">
         <is>
           <t>The EDGE FILTER is a different gate from ENTRY_Z. ENTRY_Z decides when the chime fires; the edge filter asks whether the expected capture clears the round trip by EDGE_MULTIPLE. A highlighted z that fails the edge filter is still not a trade worth taking.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="144">
-      <c r="B70" s="233" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="233" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES on Config decides whether a failing edge filter also silences the chime. It ships FALSE, so the chime follows ENTRY_Z alone.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="233" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="233" t="inlineStr">
         <is>
           <t>Break-even and take-profit are MID levels, on the same scale as the mean, sigma and z - a mid move of the cost is exactly what pays the round trip. The entry reference above them is the TOUCH you actually get filled at. To work the exit order, cross back: add half the Bid-Ask Gap to close a short, subtract half to close a long.</t>
         </is>
@@ -3923,7 +3967,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="15" customHeight="1" s="144">
       <c r="A7" s="258" t="inlineStr">
         <is>
@@ -4257,7 +4300,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="15" customHeight="1" s="144">
       <c r="A23" s="258" t="inlineStr">
         <is>
@@ -4434,7 +4476,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="144">
       <c r="A32" s="258" t="inlineStr">
         <is>
@@ -4569,7 +4610,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="15" customHeight="1" s="144">
       <c r="A39" s="258" t="inlineStr">
         <is>
@@ -4823,7 +4863,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51" ht="15" customHeight="1" s="144">
       <c r="A51" s="258" t="inlineStr">
         <is>
@@ -5031,7 +5070,6 @@
         </is>
       </c>
     </row>
-    <row r="60"/>
     <row r="61" ht="15" customHeight="1" s="144">
       <c r="A61" s="258" t="inlineStr">
         <is>
@@ -5162,7 +5200,6 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
     <row r="68" ht="15" customHeight="1" s="144">
       <c r="A68" s="258" t="inlineStr">
         <is>
@@ -5271,7 +5308,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
     <row r="75" ht="15" customHeight="1" s="144">
       <c r="A75" s="258" t="inlineStr">
         <is>
@@ -5533,7 +5569,6 @@
         </is>
       </c>
     </row>
-    <row r="82"/>
     <row r="83" ht="15" customHeight="1" s="144">
       <c r="A83" s="255" t="inlineStr">
         <is>
@@ -5555,7 +5590,6 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
     <row r="87" ht="15" customHeight="1" s="144">
       <c r="A87" s="255" t="inlineStr">
         <is>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -2787,7 +2787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M75"/>
+  <dimension ref="B1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="142" min="1" max="1"/>
@@ -3799,7 +3799,7 @@
     <row r="69" ht="15" customHeight="1" s="144">
       <c r="B69" s="245" t="inlineStr">
         <is>
-          <t>THE MEAN AT THE TOUCH  (live Gap - what you would actually deal at)</t>
+          <t>THE MEAN AT THE TOUCH  (live Gap - the price each side actually deals at)</t>
         </is>
       </c>
       <c r="C69" s="246" t="n"/>
@@ -3809,30 +3809,30 @@
       <c r="G69" s="246" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1" s="144">
-      <c r="B70" s="250" t="inlineStr">
-        <is>
-          <t>Mean for SHORTING the spread</t>
+      <c r="B70" s="242" t="inlineStr">
+        <is>
+          <t>SHORT (high to low)  ENTER</t>
         </is>
       </c>
       <c r="C70" s="241" t="inlineStr">
         <is>
-          <t>mean - Gap/2   (you sell the bid)</t>
-        </is>
-      </c>
-      <c r="D70" s="254" t="n"/>
-      <c r="E70" s="254" t="n"/>
-      <c r="F70" s="254" t="n"/>
-      <c r="G70" s="254" t="n"/>
+          <t>sell the bid     mean - Gap/2</t>
+        </is>
+      </c>
+      <c r="D70" s="240" t="n"/>
+      <c r="E70" s="240" t="n"/>
+      <c r="F70" s="240" t="n"/>
+      <c r="G70" s="240" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="250" t="inlineStr">
         <is>
-          <t>Mean for LONGING the spread</t>
+          <t>SHORT (high to low)  EXIT at the mean</t>
         </is>
       </c>
       <c r="C71" s="241" t="inlineStr">
         <is>
-          <t>mean + Gap/2   (you buy the ask)</t>
+          <t>buy the ask      mean + Gap/2</t>
         </is>
       </c>
       <c r="D71" s="254" t="n"/>
@@ -3840,22 +3840,57 @@
       <c r="F71" s="254" t="n"/>
       <c r="G71" s="254" t="n"/>
     </row>
+    <row r="72">
+      <c r="B72" s="242" t="inlineStr">
+        <is>
+          <t>LONG (low to high)  ENTER</t>
+        </is>
+      </c>
+      <c r="C72" s="241" t="inlineStr">
+        <is>
+          <t>buy the ask      mean + Gap/2</t>
+        </is>
+      </c>
+      <c r="D72" s="240" t="n"/>
+      <c r="E72" s="240" t="n"/>
+      <c r="F72" s="240" t="n"/>
+      <c r="G72" s="240" t="n"/>
+    </row>
     <row r="73">
-      <c r="B73" s="255" t="inlineStr">
+      <c r="B73" s="250" t="inlineStr">
+        <is>
+          <t>LONG (low to high)  EXIT at the mean</t>
+        </is>
+      </c>
+      <c r="C73" s="241" t="inlineStr">
+        <is>
+          <t>sell the bid     mean - Gap/2</t>
+        </is>
+      </c>
+      <c r="D73" s="254" t="n"/>
+      <c r="E73" s="254" t="n"/>
+      <c r="F73" s="254" t="n"/>
+      <c r="G73" s="254" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="233" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="255" t="inlineStr">
         <is>
           <t>The EDGE FILTER is a different gate from ENTRY_Z. ENTRY_Z decides when the chime fires; the edge filter asks whether the expected capture clears the round trip by EDGE_MULTIPLE. A highlighted z that fails the edge filter is still not a trade worth taking.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="233" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="233" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES on Config decides whether a failing edge filter also silences the chime. It ships FALSE, so the chime follows ENTRY_Z alone.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="233" t="inlineStr">
+    <row r="77">
+      <c r="B77" s="233" t="inlineStr">
         <is>
           <t>Break-even and take-profit are MID levels, on the same scale as the mean, sigma and z - a mid move of the cost is exactly what pays the round trip. The entry reference above them is the TOUCH you actually get filled at. To work the exit order, cross back: add half the Bid-Ask Gap to close a short, subtract half to close a long.</t>
         </is>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -6898,14 +6898,14 @@
     <row r="7" ht="30" customHeight="1" s="144">
       <c r="B7" s="282" t="inlineStr">
         <is>
-          <t>4.  In the editor, double-click ThisWorkbook and paste the two-line Workbook_Open / Workbook_BeforeClose stub printed at the bottom of TTZMonitor.bas.  (Optional - it just auto-starts the monitor and warm-starts the buffers.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="144">
+          <t>4.  In the editor, double-click ThisWorkbook and paste the two-line Workbook_Open / Workbook_BeforeClose stub printed at the bottom of TTZMonitor.bas.  REQUIRED - see the note below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" s="144">
       <c r="B8" s="282" t="inlineStr">
         <is>
-          <t>5.  Back on Dashboard, insert two shapes over cells N2 and P2 (Insert &gt; Shapes &gt; Rectangle), right-click each &gt; Assign Macro &gt; StartMonitor and StopMonitor. Until you do, run them from Alt+F8.</t>
+          <t>5.  Back on Dashboard, the control strip is ROW 23. Insert three shapes (Insert &gt; Shapes &gt; Rectangle) over the labelled cells N23 ("&gt; START"), P23 ("# STOP") and R23 ("TEST CHIME"), then right-click each &gt; Assign Macro &gt; StartMonitor, StopMonitor and TestChime. A shape is not bound to the cell it sits on - only the assigned macro matters - so the position is cosmetic. Until you draw them, run all three from Alt+F8.</t>
         </is>
       </c>
     </row>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="144">
+    <row r="10" ht="90" customHeight="1" s="144">
       <c r="B10" s="281" t="inlineStr">
         <is>
-          <t>Step 4 is NOT optional here. The capture timer is a Windows user32 timer, and one that outlives the workbook keeps firing into a module that no longer has its sheets - which crashes Excel. Workbook_BeforeClose calls StopMonitor and kills it.</t>
+          <t>Step 4 is NOT optional. The capture timer is a Windows user32 timer, and one that outlives the workbook keeps firing into a module that no longer has its sheets - which crashes Excel. Workbook_BeforeClose calls StopMonitor and kills it.     F23 and H23 ARE hard-coded in the module - F23 holds RUNNING / STOPPED, H23 the rate strip, both rewritten on every paint - so do not move them. N23, P23 and R23 are only labelled backing cells for the shapes; the engine never touches them.     Run TestChime before going live: it plays the entry tone then the ceiling tone, so the sound path is verified without waiting for warm-up and a real crossing. On a headless or remote-desktop machine with no audio device PlaySound fails silently, so TestChime can report success having played nothing.</t>
         </is>
       </c>
     </row>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -4382,7 +4382,7 @@
       </c>
       <c r="E28" s="261" t="inlineStr">
         <is>
-          <t>Warm-up gate 2. Elapsed collection needed before any z is shown. BOTH gates must pass.</t>
+          <t>Warm-up gate 2. Window span needed before any z is shown. BOTH gates must pass. MUST BE LESS THAN LOOKBACK_MIN: eviction drops samples older than the lookback, so the span approaches it but never reaches it, and a value at or above LOOKBACK_MIN would never be satisfied. Anything above 98% of LOOKBACK_MIN is clamped to that, and the clamp is noted once in the Log.</t>
         </is>
       </c>
     </row>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -6836,7 +6836,7 @@
     <row r="7" ht="30" customHeight="1" s="144">
       <c r="B7" s="282" t="inlineStr">
         <is>
-          <t>4.  In the editor, double-click ThisWorkbook and paste the two-line Workbook_Open / Workbook_BeforeClose stub printed at the bottom of TTZMonitor.bas.  (Optional - it just auto-starts the monitor and warm-starts the buffers.)</t>
+          <t>4.  In the editor, double-click ThisWorkbook, clear the pane with Ctrl+A then Delete, and paste the contents of ThisWorkbook.txt verbatim. Do NOT copy it out of TTZMonitor.bas - the copy there is inside a comment block, and pasting it with the apostrophes attached gives 'Compile error: Expected End Sub'.</t>
         </is>
       </c>
     </row>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -601,7 +601,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="282">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -797,46 +797,40 @@
     <xf numFmtId="0" fontId="28" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="28" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="28" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1226,46 +1220,40 @@
     <xf numFmtId="0" fontId="28" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="28" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="28" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="31" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1826,845 +1814,853 @@
   <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col hidden="1" width="2.14" customWidth="1" style="142" min="1" max="1"/>
-    <col hidden="1" width="11" customWidth="1" style="142" min="2" max="2"/>
-    <col hidden="1" width="30.43" customWidth="1" style="142" min="3" max="3"/>
-    <col width="3.43" customWidth="1" style="142" min="4" max="5"/>
-    <col width="16.14" customWidth="1" style="143" min="6" max="6"/>
-    <col hidden="1" width="30.57" customWidth="1" style="142" min="7" max="7"/>
-    <col width="17" customWidth="1" style="142" min="8" max="10"/>
-    <col width="17.43" customWidth="1" style="142" min="11" max="12"/>
-    <col width="2" customWidth="1" style="142" min="13" max="13"/>
-    <col width="17.57" customWidth="1" style="142" min="14" max="14"/>
-    <col hidden="1" width="16.72" customWidth="1" style="142" min="15" max="15"/>
-    <col width="18.29" customWidth="1" style="142" min="16" max="18"/>
-    <col width="16.43" customWidth="1" style="142" min="19" max="20"/>
-    <col width="17.29" customWidth="1" style="142" min="24" max="24"/>
-    <col width="14.29" customWidth="1" style="142" min="25" max="26"/>
-    <col width="11.43" customWidth="1" style="142" min="27" max="27"/>
+    <col hidden="1" width="2.14" customWidth="1" style="140" min="1" max="1"/>
+    <col hidden="1" width="11" customWidth="1" style="140" min="2" max="2"/>
+    <col hidden="1" width="30.43" customWidth="1" style="140" min="3" max="3"/>
+    <col width="3.43" customWidth="1" style="140" min="4" max="5"/>
+    <col width="16.14" customWidth="1" style="141" min="6" max="6"/>
+    <col hidden="1" width="30.57" customWidth="1" style="140" min="7" max="7"/>
+    <col width="17" customWidth="1" style="140" min="8" max="10"/>
+    <col width="17.43" customWidth="1" style="140" min="11" max="12"/>
+    <col width="2" customWidth="1" style="140" min="13" max="13"/>
+    <col width="17.57" customWidth="1" style="140" min="14" max="14"/>
+    <col hidden="1" width="16.72" customWidth="1" style="140" min="15" max="15"/>
+    <col width="18.29" customWidth="1" style="140" min="16" max="18"/>
+    <col width="16.43" customWidth="1" style="140" min="19" max="20"/>
+    <col width="17.29" customWidth="1" style="140" min="24" max="24"/>
+    <col width="14.29" customWidth="1" style="140" min="25" max="26"/>
+    <col width="11.43" customWidth="1" style="140" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2" ht="68.25" customHeight="1" s="144">
-      <c r="A2" s="145" t="n"/>
-      <c r="B2" s="146" t="n"/>
-      <c r="C2" s="147" t="inlineStr">
+    <row r="2" ht="68.25" customHeight="1" s="142">
+      <c r="A2" s="143" t="n"/>
+      <c r="B2" s="144" t="n"/>
+      <c r="C2" s="145" t="inlineStr">
         <is>
           <t>ENERGY FUTURES BID / ASK SPREAD MONITOR</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="144">
-      <c r="A3" s="145" t="n"/>
-      <c r="B3" s="148" t="n"/>
-      <c r="C3" s="149" t="n"/>
-      <c r="F3" s="150" t="n"/>
-      <c r="G3" s="151" t="n"/>
-      <c r="L3" s="152" t="n"/>
-    </row>
-    <row r="4" ht="6.75" customHeight="1" s="144">
-      <c r="A4" s="145" t="n"/>
-      <c r="B4" s="153" t="inlineStr">
+    <row r="3" ht="21.75" customHeight="1" s="142">
+      <c r="A3" s="143" t="n"/>
+      <c r="B3" s="146" t="n"/>
+      <c r="C3" s="147" t="n"/>
+      <c r="F3" s="148" t="n"/>
+      <c r="G3" s="149" t="n"/>
+      <c r="L3" s="150" t="n"/>
+    </row>
+    <row r="4" ht="6.75" customHeight="1" s="142">
+      <c r="A4" s="143" t="n"/>
+      <c r="B4" s="151" t="inlineStr">
         <is>
           <t>TT MARKET</t>
         </is>
       </c>
-      <c r="C4" s="153" t="inlineStr">
+      <c r="C4" s="151" t="inlineStr">
         <is>
           <t>CME</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="6.75" customHeight="1" s="144">
-      <c r="A5" s="145" t="n"/>
-      <c r="B5" s="154" t="inlineStr">
+    <row r="5" ht="6.75" customHeight="1" s="142">
+      <c r="A5" s="143" t="n"/>
+      <c r="B5" s="152" t="inlineStr">
         <is>
           <t>TT SHORT NAME</t>
         </is>
       </c>
-      <c r="C5" s="154" t="inlineStr">
+      <c r="C5" s="152" t="inlineStr">
         <is>
           <t>INSTRUMENT ID</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="23.25" customHeight="1" s="144">
-      <c r="A6" s="145" t="n"/>
-      <c r="B6" s="153" t="inlineStr">
+    <row r="6" ht="23.25" customHeight="1" s="142">
+      <c r="A6" s="143" t="n"/>
+      <c r="B6" s="151" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="C6" s="155" t="n"/>
-      <c r="F6" s="156" t="inlineStr">
+      <c r="C6" s="153" t="n"/>
+      <c r="F6" s="154" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="G6" s="157" t="inlineStr">
+      <c r="G6" s="155" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H6" s="157" t="inlineStr">
+      <c r="H6" s="155" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I6" s="157" t="inlineStr">
+      <c r="I6" s="155" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J6" s="157" t="inlineStr">
+      <c r="J6" s="155" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="K6" s="157" t="inlineStr">
+      <c r="K6" s="155" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L6" s="158" t="inlineStr">
+      <c r="L6" s="156" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M6" s="159" t="n"/>
-      <c r="N6" s="156" t="inlineStr">
+      <c r="M6" s="157" t="n"/>
+      <c r="N6" s="154" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="O6" s="157" t="inlineStr">
+      <c r="O6" s="155" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="P6" s="157" t="inlineStr">
+      <c r="P6" s="155" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="Q6" s="157" t="inlineStr">
+      <c r="Q6" s="155" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="R6" s="157" t="inlineStr">
+      <c r="R6" s="155" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="S6" s="157" t="inlineStr">
+      <c r="S6" s="155" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T6" s="158" t="inlineStr">
+      <c r="T6" s="156" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U6" s="160" t="n"/>
-      <c r="V6" s="160" t="n"/>
-    </row>
-    <row r="7" ht="55.5" customHeight="1" s="144">
-      <c r="A7" s="145" t="n"/>
-      <c r="B7" s="153" t="inlineStr">
+      <c r="U6" s="158" t="n"/>
+      <c r="V6" s="158" t="n"/>
+    </row>
+    <row r="7" ht="55.5" customHeight="1" s="142">
+      <c r="A7" s="143" t="n"/>
+      <c r="B7" s="151" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="C7" s="155" t="n"/>
-      <c r="D7" s="161" t="n"/>
-      <c r="E7" s="161" t="n"/>
-      <c r="F7" s="162" t="inlineStr">
+      <c r="C7" s="153" t="n"/>
+      <c r="D7" s="159" t="n"/>
+      <c r="E7" s="159" t="n"/>
+      <c r="F7" s="160" t="inlineStr">
         <is>
           <t>HOV26
 HO Oct 26</t>
         </is>
       </c>
-      <c r="G7" s="163" t="inlineStr">
+      <c r="G7" s="161" t="inlineStr">
         <is>
           <t>HO Oct 26</t>
         </is>
       </c>
-      <c r="H7" s="164" t="n"/>
-      <c r="I7" s="165" t="n"/>
-      <c r="J7" s="166" t="n"/>
-      <c r="K7" s="167" t="n"/>
-      <c r="L7" s="168" t="n"/>
-      <c r="M7" s="169" t="n"/>
-      <c r="N7" s="162" t="inlineStr">
+      <c r="H7" s="162" t="n"/>
+      <c r="I7" s="163" t="n"/>
+      <c r="J7" s="164" t="n"/>
+      <c r="K7" s="165" t="n"/>
+      <c r="L7" s="166" t="n"/>
+      <c r="M7" s="167" t="n"/>
+      <c r="N7" s="160" t="inlineStr">
         <is>
           <t>BZV26
 BZ Oct 26</t>
         </is>
       </c>
-      <c r="O7" s="163" t="inlineStr">
+      <c r="O7" s="161" t="inlineStr">
         <is>
           <t>BZ Oct 26</t>
         </is>
       </c>
-      <c r="P7" s="164" t="n"/>
-      <c r="Q7" s="164" t="n"/>
-      <c r="R7" s="170" t="n"/>
-      <c r="S7" s="167" t="n"/>
-      <c r="T7" s="168" t="n"/>
-      <c r="U7" s="160" t="n"/>
-      <c r="V7" s="160" t="n"/>
-    </row>
-    <row r="8" ht="55.5" customHeight="1" s="144">
-      <c r="A8" s="145" t="n"/>
-      <c r="B8" s="153" t="inlineStr">
+      <c r="P7" s="162" t="n"/>
+      <c r="Q7" s="162" t="n"/>
+      <c r="R7" s="168" t="n"/>
+      <c r="S7" s="165" t="n"/>
+      <c r="T7" s="166" t="n"/>
+      <c r="U7" s="158" t="n"/>
+      <c r="V7" s="158" t="n"/>
+    </row>
+    <row r="8" ht="55.5" customHeight="1" s="142">
+      <c r="A8" s="143" t="n"/>
+      <c r="B8" s="151" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="C8" s="155" t="n"/>
-      <c r="D8" s="161" t="n"/>
-      <c r="E8" s="161" t="n"/>
-      <c r="F8" s="171" t="inlineStr">
+      <c r="C8" s="153" t="n"/>
+      <c r="D8" s="159" t="n"/>
+      <c r="E8" s="159" t="n"/>
+      <c r="F8" s="169" t="inlineStr">
         <is>
           <t>CLV26
 CL Oct 26</t>
         </is>
       </c>
-      <c r="G8" s="172" t="inlineStr">
+      <c r="G8" s="170" t="inlineStr">
         <is>
           <t>CL Oct 26</t>
         </is>
       </c>
-      <c r="H8" s="173" t="n"/>
-      <c r="I8" s="173" t="n"/>
-      <c r="J8" s="174" t="n"/>
-      <c r="K8" s="175" t="n"/>
-      <c r="L8" s="176" t="n"/>
-      <c r="M8" s="169" t="n"/>
-      <c r="N8" s="171" t="inlineStr">
+      <c r="H8" s="171" t="n"/>
+      <c r="I8" s="171" t="n"/>
+      <c r="J8" s="172" t="n"/>
+      <c r="K8" s="173" t="n"/>
+      <c r="L8" s="174" t="n"/>
+      <c r="M8" s="167" t="n"/>
+      <c r="N8" s="169" t="inlineStr">
         <is>
           <t>CLV26
 CL Oct 26</t>
         </is>
       </c>
-      <c r="O8" s="172" t="inlineStr">
+      <c r="O8" s="170" t="inlineStr">
         <is>
           <t>CL Oct 26</t>
         </is>
       </c>
-      <c r="P8" s="173" t="n"/>
-      <c r="Q8" s="173" t="n"/>
-      <c r="R8" s="174" t="n"/>
-      <c r="S8" s="175" t="n"/>
-      <c r="T8" s="176" t="n"/>
-      <c r="U8" s="160" t="n"/>
-      <c r="V8" s="160" t="n"/>
-    </row>
-    <row r="9" ht="55.5" customHeight="1" s="144">
-      <c r="A9" s="145" t="n"/>
-      <c r="B9" s="153" t="inlineStr">
+      <c r="P8" s="171" t="n"/>
+      <c r="Q8" s="171" t="n"/>
+      <c r="R8" s="172" t="n"/>
+      <c r="S8" s="173" t="n"/>
+      <c r="T8" s="174" t="n"/>
+      <c r="U8" s="158" t="n"/>
+      <c r="V8" s="158" t="n"/>
+    </row>
+    <row r="9" ht="55.5" customHeight="1" s="142">
+      <c r="A9" s="143" t="n"/>
+      <c r="B9" s="151" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="C9" s="155" t="n"/>
-      <c r="D9" s="161" t="n"/>
-      <c r="E9" s="161" t="n"/>
-      <c r="F9" s="177" t="inlineStr">
+      <c r="C9" s="153" t="n"/>
+      <c r="D9" s="159" t="n"/>
+      <c r="E9" s="159" t="n"/>
+      <c r="F9" s="175" t="inlineStr">
         <is>
           <t>HO | CL Oct 26 Crack</t>
         </is>
       </c>
-      <c r="G9" s="178" t="n"/>
-      <c r="H9" s="179" t="n"/>
-      <c r="I9" s="179" t="n"/>
-      <c r="J9" s="180" t="n"/>
-      <c r="K9" s="179" t="n"/>
-      <c r="L9" s="181" t="n"/>
-      <c r="M9" s="169" t="n"/>
-      <c r="N9" s="182" t="inlineStr">
+      <c r="G9" s="176" t="n"/>
+      <c r="H9" s="177" t="n"/>
+      <c r="I9" s="177" t="n"/>
+      <c r="J9" s="178" t="n"/>
+      <c r="K9" s="177" t="n"/>
+      <c r="L9" s="179" t="n"/>
+      <c r="M9" s="167" t="n"/>
+      <c r="N9" s="180" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="O9" s="183" t="n"/>
-      <c r="P9" s="179" t="n"/>
-      <c r="Q9" s="179" t="n"/>
-      <c r="R9" s="180" t="n"/>
-      <c r="S9" s="179" t="n"/>
-      <c r="T9" s="181" t="n"/>
-      <c r="U9" s="160" t="n"/>
-      <c r="V9" s="160" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="144">
-      <c r="A10" s="145" t="n"/>
-      <c r="B10" s="184" t="inlineStr">
+      <c r="O9" s="181" t="n"/>
+      <c r="P9" s="177" t="n"/>
+      <c r="Q9" s="177" t="n"/>
+      <c r="R9" s="178" t="n"/>
+      <c r="S9" s="177" t="n"/>
+      <c r="T9" s="179" t="n"/>
+      <c r="U9" s="158" t="n"/>
+      <c r="V9" s="158" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="142">
+      <c r="A10" s="143" t="n"/>
+      <c r="B10" s="182" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="C10" s="155" t="n"/>
-      <c r="D10" s="161" t="n"/>
-      <c r="E10" s="161" t="n"/>
-      <c r="F10" s="169" t="n"/>
-      <c r="G10" s="169" t="n"/>
-      <c r="H10" s="169" t="n"/>
-      <c r="I10" s="169" t="n"/>
-      <c r="J10" s="169" t="n"/>
-      <c r="K10" s="169" t="n"/>
-      <c r="L10" s="169" t="n"/>
-      <c r="M10" s="169" t="n"/>
-      <c r="N10" s="160" t="n"/>
-      <c r="O10" s="160" t="n"/>
-      <c r="P10" s="160" t="n"/>
-      <c r="Q10" s="160" t="n"/>
-      <c r="R10" s="160" t="n"/>
-      <c r="S10" s="160" t="n"/>
-      <c r="T10" s="160" t="n"/>
-      <c r="U10" s="160" t="n"/>
-      <c r="V10" s="160" t="n"/>
-    </row>
-    <row r="11" ht="42" customHeight="1" s="144">
-      <c r="A11" s="145" t="n"/>
-      <c r="B11" s="184" t="n"/>
-      <c r="C11" s="155" t="n"/>
-      <c r="D11" s="161" t="n"/>
-      <c r="E11" s="161" t="n"/>
-      <c r="F11" s="156" t="inlineStr">
+      <c r="C10" s="153" t="n"/>
+      <c r="D10" s="159" t="n"/>
+      <c r="E10" s="159" t="n"/>
+      <c r="F10" s="167" t="n"/>
+      <c r="G10" s="167" t="n"/>
+      <c r="H10" s="167" t="n"/>
+      <c r="I10" s="167" t="n"/>
+      <c r="J10" s="167" t="n"/>
+      <c r="K10" s="167" t="n"/>
+      <c r="L10" s="167" t="n"/>
+      <c r="M10" s="167" t="n"/>
+      <c r="N10" s="158" t="n"/>
+      <c r="O10" s="158" t="n"/>
+      <c r="P10" s="158" t="n"/>
+      <c r="Q10" s="158" t="n"/>
+      <c r="R10" s="158" t="n"/>
+      <c r="S10" s="158" t="n"/>
+      <c r="T10" s="158" t="n"/>
+      <c r="U10" s="158" t="n"/>
+      <c r="V10" s="158" t="n"/>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="142">
+      <c r="A11" s="143" t="n"/>
+      <c r="B11" s="182" t="n"/>
+      <c r="C11" s="153" t="n"/>
+      <c r="D11" s="159" t="n"/>
+      <c r="E11" s="159" t="n"/>
+      <c r="F11" s="154" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="G11" s="157" t="inlineStr">
+      <c r="G11" s="155" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H11" s="157" t="inlineStr">
+      <c r="H11" s="155" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I11" s="157" t="inlineStr">
+      <c r="I11" s="155" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J11" s="157" t="inlineStr">
+      <c r="J11" s="155" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="K11" s="157" t="inlineStr">
+      <c r="K11" s="155" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L11" s="158" t="inlineStr">
+      <c r="L11" s="156" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M11" s="169" t="n"/>
-      <c r="N11" s="185" t="n"/>
-      <c r="O11" s="186" t="n"/>
-      <c r="P11" s="187" t="n"/>
-      <c r="Q11" s="187" t="n"/>
-      <c r="R11" s="174" t="n"/>
-      <c r="S11" s="188" t="n"/>
-      <c r="T11" s="188" t="n"/>
-      <c r="U11" s="160" t="n"/>
-      <c r="V11" s="160" t="n"/>
-    </row>
-    <row r="12" ht="50.25" customHeight="1" s="144">
-      <c r="A12" s="145" t="n"/>
-      <c r="B12" s="184" t="inlineStr">
+      <c r="M11" s="167" t="n"/>
+      <c r="N11" s="183" t="n"/>
+      <c r="O11" s="184" t="n"/>
+      <c r="P11" s="185" t="n"/>
+      <c r="Q11" s="185" t="n"/>
+      <c r="R11" s="172" t="n"/>
+      <c r="S11" s="186" t="n"/>
+      <c r="T11" s="186" t="n"/>
+      <c r="U11" s="158" t="n"/>
+      <c r="V11" s="158" t="n"/>
+    </row>
+    <row r="12" ht="50.25" customHeight="1" s="142">
+      <c r="A12" s="143" t="n"/>
+      <c r="B12" s="182" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="C12" s="155" t="n"/>
-      <c r="D12" s="161" t="n"/>
-      <c r="E12" s="161" t="n"/>
-      <c r="F12" s="189" t="inlineStr">
+      <c r="C12" s="153" t="n"/>
+      <c r="D12" s="159" t="n"/>
+      <c r="E12" s="159" t="n"/>
+      <c r="F12" s="187" t="inlineStr">
         <is>
           <t>RBV26</t>
         </is>
       </c>
-      <c r="G12" s="163" t="inlineStr">
+      <c r="G12" s="161" t="inlineStr">
         <is>
           <t>RB Oct 26</t>
         </is>
       </c>
-      <c r="H12" s="164" t="n"/>
-      <c r="I12" s="164" t="n"/>
-      <c r="J12" s="166" t="n"/>
-      <c r="K12" s="167" t="n"/>
-      <c r="L12" s="168" t="n"/>
-      <c r="M12" s="169" t="n"/>
-      <c r="N12" s="169" t="n"/>
-      <c r="O12" s="169" t="n"/>
-      <c r="P12" s="169" t="n"/>
-      <c r="Q12" s="169" t="n"/>
-      <c r="R12" s="169" t="n"/>
-      <c r="S12" s="190" t="n"/>
-      <c r="T12" s="190" t="n"/>
-      <c r="U12" s="160" t="n"/>
-      <c r="V12" s="160" t="n"/>
-    </row>
-    <row r="13" ht="50.25" customHeight="1" s="144">
-      <c r="A13" s="145" t="n"/>
-      <c r="D13" s="161" t="n"/>
-      <c r="E13" s="161" t="n"/>
-      <c r="F13" s="191" t="inlineStr">
+      <c r="H12" s="162" t="n"/>
+      <c r="I12" s="162" t="n"/>
+      <c r="J12" s="164" t="n"/>
+      <c r="K12" s="165" t="n"/>
+      <c r="L12" s="166" t="n"/>
+      <c r="M12" s="167" t="n"/>
+      <c r="N12" s="167" t="n"/>
+      <c r="O12" s="167" t="n"/>
+      <c r="P12" s="167" t="n"/>
+      <c r="Q12" s="167" t="n"/>
+      <c r="R12" s="167" t="n"/>
+      <c r="S12" s="188" t="n"/>
+      <c r="T12" s="188" t="n"/>
+      <c r="U12" s="158" t="n"/>
+      <c r="V12" s="158" t="n"/>
+    </row>
+    <row r="13" ht="50.25" customHeight="1" s="142">
+      <c r="A13" s="143" t="n"/>
+      <c r="D13" s="159" t="n"/>
+      <c r="E13" s="159" t="n"/>
+      <c r="F13" s="189" t="inlineStr">
         <is>
           <t>HOV26</t>
         </is>
       </c>
-      <c r="G13" s="172" t="inlineStr">
+      <c r="G13" s="170" t="inlineStr">
         <is>
           <t>HO Oct 26</t>
         </is>
       </c>
-      <c r="H13" s="173" t="n"/>
-      <c r="I13" s="173" t="n"/>
-      <c r="J13" s="192" t="n"/>
-      <c r="K13" s="175" t="n"/>
-      <c r="L13" s="176" t="n"/>
-      <c r="M13" s="169" t="n"/>
-      <c r="N13" s="193" t="n"/>
-      <c r="O13" s="193" t="n"/>
-      <c r="P13" s="193" t="n"/>
-      <c r="Q13" s="193" t="n"/>
-      <c r="R13" s="193" t="n"/>
-      <c r="S13" s="193" t="n"/>
-      <c r="T13" s="193" t="n"/>
-      <c r="U13" s="160" t="n"/>
-      <c r="V13" s="160" t="n"/>
-    </row>
-    <row r="14" ht="50.25" customHeight="1" s="144">
-      <c r="A14" s="145" t="n"/>
-      <c r="D14" s="161" t="n"/>
-      <c r="E14" s="161" t="n"/>
-      <c r="F14" s="189" t="inlineStr">
+      <c r="H13" s="171" t="n"/>
+      <c r="I13" s="171" t="n"/>
+      <c r="J13" s="190" t="n"/>
+      <c r="K13" s="173" t="n"/>
+      <c r="L13" s="174" t="n"/>
+      <c r="M13" s="167" t="n"/>
+      <c r="N13" s="191" t="n"/>
+      <c r="O13" s="191" t="n"/>
+      <c r="P13" s="191" t="n"/>
+      <c r="Q13" s="191" t="n"/>
+      <c r="R13" s="191" t="n"/>
+      <c r="S13" s="191" t="n"/>
+      <c r="T13" s="191" t="n"/>
+      <c r="U13" s="158" t="n"/>
+      <c r="V13" s="158" t="n"/>
+    </row>
+    <row r="14" ht="50.25" customHeight="1" s="142">
+      <c r="A14" s="143" t="n"/>
+      <c r="D14" s="159" t="n"/>
+      <c r="E14" s="159" t="n"/>
+      <c r="F14" s="187" t="inlineStr">
         <is>
           <t>CLV26</t>
         </is>
       </c>
-      <c r="G14" s="163" t="inlineStr">
+      <c r="G14" s="161" t="inlineStr">
         <is>
           <t>CL Oct 26</t>
         </is>
       </c>
-      <c r="H14" s="164" t="n"/>
-      <c r="I14" s="164" t="n"/>
-      <c r="J14" s="170" t="n"/>
-      <c r="K14" s="167" t="n"/>
-      <c r="L14" s="168" t="n"/>
-      <c r="M14" s="169" t="n"/>
-      <c r="N14" s="194" t="n"/>
-      <c r="O14" s="195" t="n"/>
-      <c r="P14" s="196" t="n"/>
-      <c r="Q14" s="196" t="n"/>
-      <c r="R14" s="197" t="n"/>
-      <c r="S14" s="198" t="n"/>
-      <c r="T14" s="198" t="n"/>
-      <c r="U14" s="160" t="n"/>
-      <c r="V14" s="160" t="n"/>
-    </row>
-    <row r="15" ht="50.25" customHeight="1" s="144">
-      <c r="A15" s="145" t="n"/>
-      <c r="D15" s="161" t="n"/>
-      <c r="E15" s="161" t="n"/>
-      <c r="F15" s="199" t="inlineStr">
+      <c r="H14" s="162" t="n"/>
+      <c r="I14" s="162" t="n"/>
+      <c r="J14" s="168" t="n"/>
+      <c r="K14" s="165" t="n"/>
+      <c r="L14" s="166" t="n"/>
+      <c r="M14" s="167" t="n"/>
+      <c r="N14" s="192" t="n"/>
+      <c r="O14" s="193" t="n"/>
+      <c r="P14" s="194" t="n"/>
+      <c r="Q14" s="194" t="n"/>
+      <c r="R14" s="195" t="n"/>
+      <c r="S14" s="196" t="n"/>
+      <c r="T14" s="196" t="n"/>
+      <c r="U14" s="158" t="n"/>
+      <c r="V14" s="158" t="n"/>
+    </row>
+    <row r="15" ht="50.25" customHeight="1" s="142">
+      <c r="A15" s="143" t="n"/>
+      <c r="D15" s="159" t="n"/>
+      <c r="E15" s="159" t="n"/>
+      <c r="F15" s="197" t="inlineStr">
         <is>
           <t>3:2:1</t>
         </is>
       </c>
-      <c r="G15" s="200" t="n"/>
-      <c r="H15" s="201" t="n"/>
-      <c r="I15" s="201" t="n"/>
-      <c r="J15" s="202" t="n"/>
-      <c r="K15" s="201" t="n"/>
-      <c r="L15" s="203" t="n"/>
-      <c r="M15" s="169" t="n"/>
-      <c r="N15" s="194" t="n"/>
-      <c r="O15" s="195" t="n"/>
-      <c r="P15" s="196" t="n"/>
-      <c r="Q15" s="196" t="n"/>
-      <c r="R15" s="197" t="n"/>
-      <c r="S15" s="198" t="n"/>
-      <c r="T15" s="198" t="n"/>
-      <c r="U15" s="160" t="n"/>
-      <c r="V15" s="160" t="n"/>
-    </row>
-    <row r="16" ht="42" customHeight="1" s="144">
-      <c r="A16" s="145" t="n"/>
-      <c r="D16" s="161" t="n"/>
-      <c r="E16" s="161" t="n"/>
-      <c r="F16" s="204" t="n"/>
-      <c r="G16" s="205" t="n"/>
-      <c r="H16" s="205" t="n"/>
-      <c r="I16" s="205" t="n"/>
-      <c r="J16" s="205" t="n"/>
-      <c r="K16" s="205" t="n"/>
-      <c r="L16" s="205" t="n"/>
-      <c r="M16" s="205" t="n"/>
-      <c r="S16" s="206" t="n"/>
-      <c r="T16" s="206" t="n"/>
-    </row>
-    <row r="17" ht="44.25" customHeight="1" s="144">
-      <c r="A17" s="145" t="n"/>
-      <c r="F17" s="207" t="inlineStr">
+      <c r="G15" s="198" t="n"/>
+      <c r="H15" s="199" t="n"/>
+      <c r="I15" s="199" t="n"/>
+      <c r="J15" s="200" t="n"/>
+      <c r="K15" s="199" t="n"/>
+      <c r="L15" s="201" t="n"/>
+      <c r="M15" s="167" t="n"/>
+      <c r="N15" s="192" t="n"/>
+      <c r="O15" s="193" t="n"/>
+      <c r="P15" s="194" t="n"/>
+      <c r="Q15" s="194" t="n"/>
+      <c r="R15" s="195" t="n"/>
+      <c r="S15" s="196" t="n"/>
+      <c r="T15" s="196" t="n"/>
+      <c r="U15" s="158" t="n"/>
+      <c r="V15" s="158" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="142">
+      <c r="A16" s="143" t="n"/>
+      <c r="D16" s="159" t="n"/>
+      <c r="E16" s="159" t="n"/>
+      <c r="F16" s="202" t="n"/>
+      <c r="G16" s="203" t="n"/>
+      <c r="H16" s="203" t="n"/>
+      <c r="I16" s="203" t="n"/>
+      <c r="J16" s="203" t="n"/>
+      <c r="K16" s="203" t="n"/>
+      <c r="L16" s="203" t="n"/>
+      <c r="M16" s="203" t="n"/>
+      <c r="S16" s="204" t="n"/>
+      <c r="T16" s="204" t="n"/>
+    </row>
+    <row r="17" ht="44.25" customHeight="1" s="142">
+      <c r="A17" s="143" t="n"/>
+      <c r="F17" s="205" t="inlineStr">
         <is>
           <t>Z-SCORE MONITOR      z is for ENTRIES only - exits act on money, never on z.      The chime fires on the CROSSING of ENTRY_Z, once.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="23.25" customHeight="1" s="144">
-      <c r="A18" s="145" t="n"/>
-      <c r="F18" s="208" t="inlineStr">
+    <row r="18" ht="23.25" customHeight="1" s="142">
+      <c r="A18" s="143" t="n"/>
+      <c r="F18" s="206" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="H18" s="208" t="inlineStr">
+      <c r="H18" s="206" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="I18" s="206" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="J18" s="206" t="inlineStr">
         <is>
           <t>Z-score</t>
         </is>
       </c>
-      <c r="I18" s="208" t="inlineStr">
+      <c r="K18" s="206" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="J18" s="208" t="inlineStr">
+      <c r="L18" s="206" t="inlineStr">
         <is>
           <t>Std Dev</t>
         </is>
       </c>
-      <c r="K18" s="208" t="inlineStr">
+      <c r="N18" s="206" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="L18" s="208" t="inlineStr">
+      <c r="P18" s="206" t="inlineStr">
         <is>
           <t>Window</t>
         </is>
       </c>
-      <c r="N18" s="208" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="P18" s="208" t="inlineStr">
+      <c r="Q18" s="206" t="inlineStr">
         <is>
           <t>Costs $</t>
         </is>
       </c>
-      <c r="Q18" s="208" t="inlineStr">
+      <c r="R18" s="206" t="inlineStr">
         <is>
           <t>Win $</t>
         </is>
       </c>
-      <c r="R18" s="208" t="inlineStr">
+      <c r="S18" s="206" t="inlineStr">
         <is>
           <t>TAKE PROFIT</t>
         </is>
       </c>
-      <c r="S18" s="208" t="inlineStr">
+      <c r="T18" s="206" t="inlineStr">
         <is>
           <t>TP in sigma</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="50.25" customHeight="1" s="144">
-      <c r="A19" s="145" t="n"/>
-      <c r="F19" s="209" t="inlineStr">
+    <row r="19" ht="50.25" customHeight="1" s="142">
+      <c r="A19" s="143" t="n"/>
+      <c r="F19" s="207" t="inlineStr">
         <is>
           <t>HO | CL Crack</t>
         </is>
       </c>
-      <c r="H19" s="210" t="n"/>
-      <c r="I19" s="211" t="n"/>
-      <c r="J19" s="211" t="n"/>
-      <c r="K19" s="212" t="n"/>
-      <c r="L19" s="212" t="n"/>
-      <c r="N19" s="213" t="n"/>
-      <c r="P19" s="214" t="n"/>
-      <c r="Q19" s="214" t="n"/>
-      <c r="R19" s="215" t="n"/>
-      <c r="S19" s="216" t="n"/>
-    </row>
-    <row r="20" ht="50.25" customHeight="1" s="144">
-      <c r="A20" s="145" t="n"/>
-      <c r="F20" s="209" t="inlineStr">
+      <c r="H19" s="208" t="n"/>
+      <c r="I19" s="209" t="n"/>
+      <c r="J19" s="210" t="n"/>
+      <c r="K19" s="211" t="n"/>
+      <c r="L19" s="211" t="n"/>
+      <c r="N19" s="209" t="n"/>
+      <c r="P19" s="209" t="n"/>
+      <c r="Q19" s="212" t="n"/>
+      <c r="R19" s="212" t="n"/>
+      <c r="S19" s="208" t="n"/>
+      <c r="T19" s="213" t="n"/>
+    </row>
+    <row r="20" ht="50.25" customHeight="1" s="142">
+      <c r="A20" s="143" t="n"/>
+      <c r="F20" s="207" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="H20" s="210" t="n"/>
-      <c r="I20" s="211" t="n"/>
-      <c r="J20" s="211" t="n"/>
-      <c r="K20" s="212" t="n"/>
-      <c r="L20" s="212" t="n"/>
-      <c r="N20" s="213" t="n"/>
-      <c r="P20" s="214" t="n"/>
-      <c r="Q20" s="214" t="n"/>
-      <c r="R20" s="215" t="n"/>
-      <c r="S20" s="216" t="n"/>
-    </row>
-    <row r="21" ht="50.25" customHeight="1" s="144">
-      <c r="A21" s="145" t="n"/>
-      <c r="F21" s="217" t="inlineStr">
+      <c r="H20" s="208" t="n"/>
+      <c r="I20" s="209" t="n"/>
+      <c r="J20" s="210" t="n"/>
+      <c r="K20" s="211" t="n"/>
+      <c r="L20" s="211" t="n"/>
+      <c r="N20" s="209" t="n"/>
+      <c r="P20" s="209" t="n"/>
+      <c r="Q20" s="212" t="n"/>
+      <c r="R20" s="212" t="n"/>
+      <c r="S20" s="208" t="n"/>
+      <c r="T20" s="213" t="n"/>
+    </row>
+    <row r="21" ht="50.25" customHeight="1" s="142">
+      <c r="A21" s="143" t="n"/>
+      <c r="F21" s="214" t="inlineStr">
         <is>
           <t>3:2:1</t>
         </is>
       </c>
-      <c r="H21" s="218" t="n"/>
-      <c r="I21" s="219" t="n"/>
-      <c r="J21" s="219" t="n"/>
-      <c r="K21" s="220" t="n"/>
-      <c r="L21" s="220" t="n"/>
-      <c r="N21" s="221" t="n"/>
-      <c r="P21" s="222" t="n"/>
-      <c r="Q21" s="222" t="n"/>
-      <c r="R21" s="223" t="n"/>
-      <c r="S21" s="224" t="n"/>
-    </row>
-    <row r="22" ht="36" customHeight="1" s="144">
-      <c r="A22" s="145" t="n"/>
-      <c r="F22" s="225" t="n"/>
-      <c r="G22" s="226" t="n"/>
-      <c r="H22" s="226" t="n"/>
-      <c r="I22" s="226" t="n"/>
-      <c r="J22" s="226" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1" s="144">
-      <c r="A23" s="145" t="n"/>
-      <c r="F23" s="227" t="inlineStr">
+      <c r="H21" s="215" t="n"/>
+      <c r="I21" s="216" t="n"/>
+      <c r="J21" s="217" t="n"/>
+      <c r="K21" s="218" t="n"/>
+      <c r="L21" s="218" t="n"/>
+      <c r="N21" s="216" t="n"/>
+      <c r="P21" s="216" t="n"/>
+      <c r="Q21" s="219" t="n"/>
+      <c r="R21" s="219" t="n"/>
+      <c r="S21" s="215" t="n"/>
+      <c r="T21" s="220" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="142">
+      <c r="A22" s="143" t="n"/>
+      <c r="F22" s="221" t="n"/>
+      <c r="G22" s="222" t="n"/>
+      <c r="H22" s="222" t="n"/>
+      <c r="I22" s="222" t="n"/>
+      <c r="J22" s="222" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="142">
+      <c r="A23" s="143" t="n"/>
+      <c r="F23" s="223" t="inlineStr">
         <is>
           <t>STOPPED</t>
         </is>
       </c>
-      <c r="G23" s="226" t="n"/>
-      <c r="H23" s="228" t="inlineStr">
+      <c r="G23" s="222" t="n"/>
+      <c r="H23" s="224" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="226" t="n"/>
-      <c r="J23" s="226" t="n"/>
-      <c r="N23" s="229" t="inlineStr">
+      <c r="I23" s="222" t="n"/>
+      <c r="J23" s="222" t="n"/>
+      <c r="N23" s="225" t="inlineStr">
         <is>
           <t xml:space="preserve">  &gt;  START  </t>
         </is>
       </c>
-      <c r="P23" s="230" t="inlineStr">
+      <c r="P23" s="226" t="inlineStr">
         <is>
           <t xml:space="preserve">  #  STOP  </t>
         </is>
       </c>
-      <c r="R23" s="231" t="inlineStr">
+      <c r="R23" s="227" t="inlineStr">
         <is>
           <t xml:space="preserve">  TEST CHIME  </t>
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1" s="144">
-      <c r="A24" s="145" t="n"/>
-      <c r="F24" s="225" t="n"/>
-      <c r="G24" s="226" t="n"/>
-      <c r="H24" s="226" t="n"/>
-      <c r="I24" s="226" t="n"/>
-      <c r="J24" s="226" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="144">
-      <c r="A25" s="145" t="n"/>
-    </row>
-    <row r="26" ht="39.75" customHeight="1" s="144">
-      <c r="A26" s="145" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="144">
-      <c r="A27" s="145" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="144">
-      <c r="A28" s="145" t="n"/>
-    </row>
-    <row r="29" ht="36" customHeight="1" s="144">
-      <c r="A29" s="145" t="n"/>
-      <c r="F29" s="225" t="n"/>
-      <c r="G29" s="226" t="n"/>
-      <c r="H29" s="226" t="n"/>
-      <c r="I29" s="226" t="n"/>
-      <c r="J29" s="226" t="n"/>
-    </row>
-    <row r="30" ht="36" customHeight="1" s="144">
-      <c r="A30" s="145" t="n"/>
-      <c r="F30" s="225" t="n"/>
-      <c r="G30" s="226" t="n"/>
-      <c r="H30" s="226" t="n"/>
-      <c r="I30" s="226" t="n"/>
-      <c r="J30" s="226" t="n"/>
-    </row>
-    <row r="31" ht="36" customHeight="1" s="144">
-      <c r="A31" s="145" t="n"/>
-      <c r="F31" s="225" t="n"/>
-      <c r="G31" s="226" t="n"/>
-      <c r="H31" s="226" t="n"/>
-      <c r="I31" s="226" t="n"/>
-      <c r="J31" s="226" t="n"/>
-    </row>
-    <row r="32" ht="36" customHeight="1" s="144">
-      <c r="A32" s="145" t="n"/>
-      <c r="F32" s="225" t="n"/>
-      <c r="G32" s="226" t="n"/>
-      <c r="H32" s="226" t="n"/>
-      <c r="I32" s="226" t="n"/>
-      <c r="J32" s="226" t="n"/>
-    </row>
-    <row r="33" ht="36" customHeight="1" s="144">
-      <c r="A33" s="145" t="n"/>
-      <c r="F33" s="225" t="n"/>
-      <c r="G33" s="226" t="n"/>
-      <c r="H33" s="226" t="n"/>
-      <c r="I33" s="226" t="n"/>
-      <c r="J33" s="226" t="n"/>
-    </row>
-    <row r="34" ht="36" customHeight="1" s="144">
-      <c r="A34" s="145" t="n"/>
-      <c r="F34" s="225" t="n"/>
-      <c r="G34" s="226" t="n"/>
-      <c r="H34" s="226" t="n"/>
-      <c r="I34" s="226" t="n"/>
-      <c r="J34" s="226" t="n"/>
-    </row>
-    <row r="35" ht="36" customHeight="1" s="144">
-      <c r="A35" s="145" t="n"/>
-      <c r="F35" s="225" t="n"/>
-      <c r="G35" s="226" t="n"/>
-      <c r="H35" s="226" t="n"/>
-      <c r="I35" s="226" t="n"/>
-      <c r="J35" s="226" t="n"/>
-    </row>
-    <row r="36" ht="36" customHeight="1" s="144">
-      <c r="A36" s="145" t="n"/>
-      <c r="F36" s="225" t="n"/>
-      <c r="G36" s="226" t="n"/>
-      <c r="H36" s="226" t="n"/>
-      <c r="I36" s="226" t="n"/>
-      <c r="J36" s="226" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1" s="144">
-      <c r="A37" s="145" t="n"/>
-      <c r="F37" s="225" t="n"/>
-      <c r="G37" s="226" t="n"/>
-      <c r="H37" s="226" t="n"/>
-      <c r="I37" s="226" t="n"/>
-      <c r="J37" s="226" t="n"/>
-    </row>
-    <row r="38" ht="36" customHeight="1" s="144">
-      <c r="A38" s="145" t="n"/>
-      <c r="F38" s="225" t="n"/>
-      <c r="G38" s="226" t="n"/>
-      <c r="H38" s="226" t="n"/>
-      <c r="I38" s="226" t="n"/>
-      <c r="J38" s="226" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1" s="144">
-      <c r="A39" s="145" t="n"/>
-      <c r="F39" s="225" t="n"/>
-      <c r="G39" s="226" t="n"/>
-      <c r="H39" s="226" t="n"/>
-      <c r="I39" s="226" t="n"/>
-      <c r="J39" s="226" t="n"/>
-    </row>
-    <row r="40" ht="36" customHeight="1" s="144">
-      <c r="F40" s="225" t="n"/>
-      <c r="G40" s="226" t="n"/>
-      <c r="H40" s="226" t="n"/>
-      <c r="I40" s="226" t="n"/>
-      <c r="J40" s="226" t="n"/>
-    </row>
-    <row r="41" ht="36" customHeight="1" s="144">
-      <c r="F41" s="225" t="n"/>
-      <c r="G41" s="226" t="n"/>
-      <c r="H41" s="226" t="n"/>
-      <c r="I41" s="226" t="n"/>
-      <c r="J41" s="226" t="n"/>
-    </row>
-    <row r="42" ht="36" customHeight="1" s="144">
-      <c r="F42" s="225" t="n"/>
-      <c r="G42" s="226" t="n"/>
-      <c r="H42" s="226" t="n"/>
-      <c r="I42" s="226" t="n"/>
-      <c r="J42" s="226" t="n"/>
-    </row>
-    <row r="43" ht="36" customHeight="1" s="144">
-      <c r="F43" s="225" t="n"/>
-      <c r="G43" s="226" t="n"/>
-      <c r="H43" s="226" t="n"/>
-      <c r="I43" s="226" t="n"/>
-      <c r="J43" s="226" t="n"/>
-    </row>
-    <row r="44" ht="36" customHeight="1" s="144">
-      <c r="F44" s="225" t="n"/>
-      <c r="G44" s="226" t="n"/>
-      <c r="H44" s="226" t="n"/>
-      <c r="I44" s="226" t="n"/>
-      <c r="J44" s="226" t="n"/>
-    </row>
-    <row r="45" ht="36" customHeight="1" s="144">
-      <c r="F45" s="225" t="n"/>
-      <c r="G45" s="226" t="n"/>
-      <c r="H45" s="226" t="n"/>
-      <c r="I45" s="226" t="n"/>
-      <c r="J45" s="226" t="n"/>
-    </row>
-    <row r="46" ht="36" customHeight="1" s="144">
-      <c r="F46" s="225" t="n"/>
-      <c r="G46" s="226" t="n"/>
-      <c r="H46" s="226" t="n"/>
-      <c r="I46" s="226" t="n"/>
-      <c r="J46" s="226" t="n"/>
-    </row>
-    <row r="47" ht="36" customHeight="1" s="144">
-      <c r="F47" s="225" t="n"/>
-      <c r="G47" s="226" t="n"/>
-      <c r="H47" s="226" t="n"/>
-      <c r="I47" s="226" t="n"/>
-      <c r="J47" s="226" t="n"/>
-    </row>
-    <row r="48" ht="36" customHeight="1" s="144">
-      <c r="F48" s="225" t="n"/>
-      <c r="G48" s="226" t="n"/>
-      <c r="H48" s="226" t="n"/>
-      <c r="I48" s="226" t="n"/>
-      <c r="J48" s="226" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1" s="144">
-      <c r="F49" s="225" t="n"/>
-      <c r="G49" s="226" t="n"/>
-      <c r="H49" s="226" t="n"/>
-      <c r="I49" s="226" t="n"/>
-      <c r="J49" s="226" t="n"/>
-    </row>
-    <row r="50" ht="36" customHeight="1" s="144">
-      <c r="F50" s="225" t="n"/>
-      <c r="G50" s="226" t="n"/>
-      <c r="H50" s="226" t="n"/>
-      <c r="I50" s="226" t="n"/>
-      <c r="J50" s="226" t="n"/>
-    </row>
-    <row r="51" ht="36" customHeight="1" s="144">
-      <c r="F51" s="225" t="n"/>
-      <c r="G51" s="226" t="n"/>
-      <c r="H51" s="226" t="n"/>
-      <c r="I51" s="226" t="n"/>
-      <c r="J51" s="226" t="n"/>
+    <row r="24" ht="36" customHeight="1" s="142">
+      <c r="A24" s="143" t="n"/>
+      <c r="F24" s="221" t="n"/>
+      <c r="G24" s="222" t="n"/>
+      <c r="H24" s="222" t="n"/>
+      <c r="I24" s="222" t="n"/>
+      <c r="J24" s="222" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="142">
+      <c r="A25" s="143" t="n"/>
+    </row>
+    <row r="26" ht="39.75" customHeight="1" s="142">
+      <c r="A26" s="143" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="142">
+      <c r="A27" s="143" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="142">
+      <c r="A28" s="143" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="142">
+      <c r="A29" s="143" t="n"/>
+      <c r="F29" s="221" t="n"/>
+      <c r="G29" s="222" t="n"/>
+      <c r="H29" s="222" t="n"/>
+      <c r="I29" s="222" t="n"/>
+      <c r="J29" s="222" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1" s="142">
+      <c r="A30" s="143" t="n"/>
+      <c r="F30" s="221" t="n"/>
+      <c r="G30" s="222" t="n"/>
+      <c r="H30" s="222" t="n"/>
+      <c r="I30" s="222" t="n"/>
+      <c r="J30" s="222" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="142">
+      <c r="A31" s="143" t="n"/>
+      <c r="F31" s="221" t="n"/>
+      <c r="G31" s="222" t="n"/>
+      <c r="H31" s="222" t="n"/>
+      <c r="I31" s="222" t="n"/>
+      <c r="J31" s="222" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="142">
+      <c r="A32" s="143" t="n"/>
+      <c r="F32" s="221" t="n"/>
+      <c r="G32" s="222" t="n"/>
+      <c r="H32" s="222" t="n"/>
+      <c r="I32" s="222" t="n"/>
+      <c r="J32" s="222" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1" s="142">
+      <c r="A33" s="143" t="n"/>
+      <c r="F33" s="221" t="n"/>
+      <c r="G33" s="222" t="n"/>
+      <c r="H33" s="222" t="n"/>
+      <c r="I33" s="222" t="n"/>
+      <c r="J33" s="222" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="142">
+      <c r="A34" s="143" t="n"/>
+      <c r="F34" s="221" t="n"/>
+      <c r="G34" s="222" t="n"/>
+      <c r="H34" s="222" t="n"/>
+      <c r="I34" s="222" t="n"/>
+      <c r="J34" s="222" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="142">
+      <c r="A35" s="143" t="n"/>
+      <c r="F35" s="221" t="n"/>
+      <c r="G35" s="222" t="n"/>
+      <c r="H35" s="222" t="n"/>
+      <c r="I35" s="222" t="n"/>
+      <c r="J35" s="222" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1" s="142">
+      <c r="A36" s="143" t="n"/>
+      <c r="F36" s="221" t="n"/>
+      <c r="G36" s="222" t="n"/>
+      <c r="H36" s="222" t="n"/>
+      <c r="I36" s="222" t="n"/>
+      <c r="J36" s="222" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1" s="142">
+      <c r="A37" s="143" t="n"/>
+      <c r="F37" s="221" t="n"/>
+      <c r="G37" s="222" t="n"/>
+      <c r="H37" s="222" t="n"/>
+      <c r="I37" s="222" t="n"/>
+      <c r="J37" s="222" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1" s="142">
+      <c r="A38" s="143" t="n"/>
+      <c r="F38" s="221" t="n"/>
+      <c r="G38" s="222" t="n"/>
+      <c r="H38" s="222" t="n"/>
+      <c r="I38" s="222" t="n"/>
+      <c r="J38" s="222" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="142">
+      <c r="A39" s="143" t="n"/>
+      <c r="F39" s="221" t="n"/>
+      <c r="G39" s="222" t="n"/>
+      <c r="H39" s="222" t="n"/>
+      <c r="I39" s="222" t="n"/>
+      <c r="J39" s="222" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="142">
+      <c r="F40" s="221" t="n"/>
+      <c r="G40" s="222" t="n"/>
+      <c r="H40" s="222" t="n"/>
+      <c r="I40" s="222" t="n"/>
+      <c r="J40" s="222" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1" s="142">
+      <c r="F41" s="221" t="n"/>
+      <c r="G41" s="222" t="n"/>
+      <c r="H41" s="222" t="n"/>
+      <c r="I41" s="222" t="n"/>
+      <c r="J41" s="222" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="142">
+      <c r="F42" s="221" t="n"/>
+      <c r="G42" s="222" t="n"/>
+      <c r="H42" s="222" t="n"/>
+      <c r="I42" s="222" t="n"/>
+      <c r="J42" s="222" t="n"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" s="142">
+      <c r="F43" s="221" t="n"/>
+      <c r="G43" s="222" t="n"/>
+      <c r="H43" s="222" t="n"/>
+      <c r="I43" s="222" t="n"/>
+      <c r="J43" s="222" t="n"/>
+    </row>
+    <row r="44" ht="36" customHeight="1" s="142">
+      <c r="F44" s="221" t="n"/>
+      <c r="G44" s="222" t="n"/>
+      <c r="H44" s="222" t="n"/>
+      <c r="I44" s="222" t="n"/>
+      <c r="J44" s="222" t="n"/>
+    </row>
+    <row r="45" ht="36" customHeight="1" s="142">
+      <c r="F45" s="221" t="n"/>
+      <c r="G45" s="222" t="n"/>
+      <c r="H45" s="222" t="n"/>
+      <c r="I45" s="222" t="n"/>
+      <c r="J45" s="222" t="n"/>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="142">
+      <c r="F46" s="221" t="n"/>
+      <c r="G46" s="222" t="n"/>
+      <c r="H46" s="222" t="n"/>
+      <c r="I46" s="222" t="n"/>
+      <c r="J46" s="222" t="n"/>
+    </row>
+    <row r="47" ht="36" customHeight="1" s="142">
+      <c r="F47" s="221" t="n"/>
+      <c r="G47" s="222" t="n"/>
+      <c r="H47" s="222" t="n"/>
+      <c r="I47" s="222" t="n"/>
+      <c r="J47" s="222" t="n"/>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="142">
+      <c r="F48" s="221" t="n"/>
+      <c r="G48" s="222" t="n"/>
+      <c r="H48" s="222" t="n"/>
+      <c r="I48" s="222" t="n"/>
+      <c r="J48" s="222" t="n"/>
+    </row>
+    <row r="49" ht="36" customHeight="1" s="142">
+      <c r="F49" s="221" t="n"/>
+      <c r="G49" s="222" t="n"/>
+      <c r="H49" s="222" t="n"/>
+      <c r="I49" s="222" t="n"/>
+      <c r="J49" s="222" t="n"/>
+    </row>
+    <row r="50" ht="36" customHeight="1" s="142">
+      <c r="F50" s="221" t="n"/>
+      <c r="G50" s="222" t="n"/>
+      <c r="H50" s="222" t="n"/>
+      <c r="I50" s="222" t="n"/>
+      <c r="J50" s="222" t="n"/>
+    </row>
+    <row r="51" ht="36" customHeight="1" s="142">
+      <c r="F51" s="221" t="n"/>
+      <c r="G51" s="222" t="n"/>
+      <c r="H51" s="222" t="n"/>
+      <c r="I51" s="222" t="n"/>
+      <c r="J51" s="222" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2673,103 +2669,103 @@
     <mergeCell ref="C2:T2"/>
     <mergeCell ref="F17:T17"/>
   </mergeCells>
-  <conditionalFormatting sqref="H19">
+  <conditionalFormatting sqref="J19">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$19="NO USABLE Z",$K$19="STALE FEED")</formula>
+      <formula>OR($N$19="NO USABLE Z",$N$19="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$19="WARMING UP"</formula>
+      <formula>$N$19="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$19="ABOVE CEILING"</formula>
+      <formula>$N$19="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$19="ENTRY BAND"</formula>
+      <formula>$N$19="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K19">
+  <conditionalFormatting sqref="N19">
     <cfRule type="expression" rank="0" priority="6" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$19="NO USABLE Z",$K$19="STALE FEED")</formula>
+      <formula>OR($N$19="NO USABLE Z",$N$19="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="7" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$19="WARMING UP"</formula>
+      <formula>$N$19="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="8" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$19="ABOVE CEILING"</formula>
+      <formula>$N$19="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="9" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$19="ENTRY BAND"</formula>
+      <formula>$N$19="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S19">
+  <conditionalFormatting sqref="T19">
     <cfRule type="expression" rank="0" priority="10" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>AND(ISNUMBER($S$19),ISNUMBER($H$19),$S$19&gt;ABS($H$19))</formula>
+      <formula>AND(ISNUMBER($T$19),ISNUMBER($J$19),$T$19&gt;ABS($J$19))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20">
+  <conditionalFormatting sqref="J20">
     <cfRule type="expression" rank="0" priority="11" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$20="NO USABLE Z",$K$20="STALE FEED")</formula>
+      <formula>OR($N$20="NO USABLE Z",$N$20="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="12" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$20="WARMING UP"</formula>
+      <formula>$N$20="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="13" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$20="ABOVE CEILING"</formula>
+      <formula>$N$20="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="14" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$20="ENTRY BAND"</formula>
+      <formula>$N$20="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K20">
+  <conditionalFormatting sqref="N20">
     <cfRule type="expression" rank="0" priority="15" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$20="NO USABLE Z",$K$20="STALE FEED")</formula>
+      <formula>OR($N$20="NO USABLE Z",$N$20="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="16" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$20="WARMING UP"</formula>
+      <formula>$N$20="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="17" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$20="ABOVE CEILING"</formula>
+      <formula>$N$20="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="18" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$20="ENTRY BAND"</formula>
+      <formula>$N$20="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S20">
+  <conditionalFormatting sqref="T20">
     <cfRule type="expression" rank="0" priority="19" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>AND(ISNUMBER($S$20),ISNUMBER($H$20),$S$20&gt;ABS($H$20))</formula>
+      <formula>AND(ISNUMBER($T$20),ISNUMBER($J$20),$T$20&gt;ABS($J$20))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21">
+  <conditionalFormatting sqref="J21">
     <cfRule type="expression" rank="0" priority="20" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$21="NO USABLE Z",$K$21="STALE FEED")</formula>
+      <formula>OR($N$21="NO USABLE Z",$N$21="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="21" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$21="WARMING UP"</formula>
+      <formula>$N$21="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="22" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$21="ABOVE CEILING"</formula>
+      <formula>$N$21="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="23" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$21="ENTRY BAND"</formula>
+      <formula>$N$21="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K21">
+  <conditionalFormatting sqref="N21">
     <cfRule type="expression" rank="0" priority="24" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>OR($K$21="NO USABLE Z",$K$21="STALE FEED")</formula>
+      <formula>OR($N$21="NO USABLE Z",$N$21="STALE FEED")</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="25" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>$K$21="WARMING UP"</formula>
+      <formula>$N$21="WARMING UP"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="26" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>$K$21="ABOVE CEILING"</formula>
+      <formula>$N$21="ABOVE CEILING"</formula>
     </cfRule>
     <cfRule type="expression" rank="0" priority="27" equalAverage="0" aboveAverage="0" dxfId="3" text="" percent="0" bottom="0">
-      <formula>$K$21="ENTRY BAND"</formula>
+      <formula>$N$21="ENTRY BAND"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S21">
+  <conditionalFormatting sqref="T21">
     <cfRule type="expression" rank="0" priority="28" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
-      <formula>AND(ISNUMBER($S$21),ISNUMBER($H$21),$S$21&gt;ABS($H$21))</formula>
+      <formula>AND(ISNUMBER($T$21),ISNUMBER($J$21),$T$21&gt;ABS($J$21))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
@@ -2791,1025 +2787,1025 @@
   <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="3" customWidth="1" style="142" min="1" max="1"/>
-    <col width="32" customWidth="1" style="142" min="2" max="2"/>
-    <col width="20" customWidth="1" style="142" min="3" max="3"/>
-    <col width="18" customWidth="1" style="142" min="4" max="7"/>
-    <col width="12" customWidth="1" style="142" min="8" max="11"/>
-    <col width="14" customWidth="1" style="142" min="12" max="12"/>
-    <col width="46" customWidth="1" style="142" min="13" max="13"/>
+    <col width="3" customWidth="1" style="140" min="1" max="1"/>
+    <col width="32" customWidth="1" style="140" min="2" max="2"/>
+    <col width="20" customWidth="1" style="140" min="3" max="3"/>
+    <col width="18" customWidth="1" style="140" min="4" max="7"/>
+    <col width="12" customWidth="1" style="140" min="8" max="11"/>
+    <col width="14" customWidth="1" style="140" min="12" max="12"/>
+    <col width="46" customWidth="1" style="140" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.35" customHeight="1" s="144">
-      <c r="B1" s="232" t="inlineStr">
+    <row r="1" ht="17.35" customHeight="1" s="142">
+      <c r="B1" s="228" t="inlineStr">
         <is>
           <t>DETAIL   -   full breakdown behind the Dashboard</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="144">
-      <c r="B2" s="233" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="142">
+      <c r="B2" s="229" t="inlineStr">
         <is>
           <t>Same engine, same numbers. The Dashboard shows the three spreads you trade from; this sheet shows everything that stands behind them, for all four slots.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="15" customHeight="1" s="144">
-      <c r="B4" s="234" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="142">
+      <c r="B4" s="230" t="inlineStr">
         <is>
           <t>OUTRIGHT LEGS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="144">
-      <c r="B5" s="235" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="142">
+      <c r="B5" s="231" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C5" s="235" t="inlineStr">
+      <c r="C5" s="231" t="inlineStr">
         <is>
           <t>Instrument ID</t>
         </is>
       </c>
-      <c r="D5" s="235" t="inlineStr">
+      <c r="D5" s="231" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="235" t="inlineStr">
+      <c r="E5" s="231" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H5" s="235" t="inlineStr">
+      <c r="H5" s="231" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I5" s="235" t="inlineStr">
+      <c r="I5" s="231" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J5" s="235" t="inlineStr">
+      <c r="J5" s="231" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K5" s="235" t="inlineStr">
+      <c r="K5" s="231" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L5" s="235" t="inlineStr">
+      <c r="L5" s="231" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="M5" s="235" t="inlineStr">
+      <c r="M5" s="231" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="144">
-      <c r="B6" s="236" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="142">
+      <c r="B6" s="232" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="C6" s="237" t="n"/>
-      <c r="D6" s="238" t="inlineStr">
+      <c r="C6" s="233" t="n"/>
+      <c r="D6" s="234" t="inlineStr">
         <is>
           <t>RBOB Gasoline Oct26</t>
         </is>
       </c>
-      <c r="E6" s="239" t="inlineStr">
+      <c r="E6" s="235" t="inlineStr">
         <is>
           <t>42,000 gal</t>
         </is>
       </c>
-      <c r="H6" s="240" t="n"/>
-      <c r="I6" s="240" t="n"/>
-      <c r="J6" s="240" t="n"/>
-      <c r="K6" s="240" t="n"/>
-      <c r="L6" s="240" t="n"/>
-      <c r="M6" s="240" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="144">
-      <c r="B7" s="236" t="inlineStr">
+      <c r="H6" s="236" t="n"/>
+      <c r="I6" s="236" t="n"/>
+      <c r="J6" s="236" t="n"/>
+      <c r="K6" s="236" t="n"/>
+      <c r="L6" s="236" t="n"/>
+      <c r="M6" s="236" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="142">
+      <c r="B7" s="232" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="C7" s="237" t="n"/>
-      <c r="D7" s="238" t="inlineStr">
+      <c r="C7" s="233" t="n"/>
+      <c r="D7" s="234" t="inlineStr">
         <is>
           <t>NY Harbor ULSD Oct26</t>
         </is>
       </c>
-      <c r="E7" s="239" t="inlineStr">
+      <c r="E7" s="235" t="inlineStr">
         <is>
           <t>42,000 gal</t>
         </is>
       </c>
-      <c r="H7" s="240" t="n"/>
-      <c r="I7" s="240" t="n"/>
-      <c r="J7" s="240" t="n"/>
-      <c r="K7" s="240" t="n"/>
-      <c r="L7" s="240" t="n"/>
-      <c r="M7" s="240" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="144">
-      <c r="B8" s="236" t="inlineStr">
+      <c r="H7" s="236" t="n"/>
+      <c r="I7" s="236" t="n"/>
+      <c r="J7" s="236" t="n"/>
+      <c r="K7" s="236" t="n"/>
+      <c r="L7" s="236" t="n"/>
+      <c r="M7" s="236" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="142">
+      <c r="B8" s="232" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="C8" s="237" t="n"/>
-      <c r="D8" s="238" t="inlineStr">
+      <c r="C8" s="233" t="n"/>
+      <c r="D8" s="234" t="inlineStr">
         <is>
           <t>WTI Crude Oct26</t>
         </is>
       </c>
-      <c r="E8" s="239" t="inlineStr">
+      <c r="E8" s="235" t="inlineStr">
         <is>
           <t>1,000 bbl</t>
         </is>
       </c>
-      <c r="H8" s="240" t="n"/>
-      <c r="I8" s="240" t="n"/>
-      <c r="J8" s="240" t="n"/>
-      <c r="K8" s="240" t="n"/>
-      <c r="L8" s="240" t="n"/>
-      <c r="M8" s="240" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="144">
-      <c r="B9" s="236" t="inlineStr">
+      <c r="H8" s="236" t="n"/>
+      <c r="I8" s="236" t="n"/>
+      <c r="J8" s="236" t="n"/>
+      <c r="K8" s="236" t="n"/>
+      <c r="L8" s="236" t="n"/>
+      <c r="M8" s="236" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="142">
+      <c r="B9" s="232" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="C9" s="237" t="n"/>
-      <c r="D9" s="238" t="inlineStr">
+      <c r="C9" s="233" t="n"/>
+      <c r="D9" s="234" t="inlineStr">
         <is>
           <t>Brent Last Day Fin Oct26</t>
         </is>
       </c>
-      <c r="E9" s="239" t="inlineStr">
+      <c r="E9" s="235" t="inlineStr">
         <is>
           <t>1,000 bbl</t>
         </is>
       </c>
-      <c r="H9" s="240" t="n"/>
-      <c r="I9" s="240" t="n"/>
-      <c r="J9" s="240" t="n"/>
-      <c r="K9" s="240" t="n"/>
-      <c r="L9" s="240" t="n"/>
-      <c r="M9" s="240" t="n"/>
+      <c r="H9" s="236" t="n"/>
+      <c r="I9" s="236" t="n"/>
+      <c r="J9" s="236" t="n"/>
+      <c r="K9" s="236" t="n"/>
+      <c r="L9" s="236" t="n"/>
+      <c r="M9" s="236" t="n"/>
     </row>
     <row r="10"/>
-    <row r="11" ht="15" customHeight="1" s="144">
-      <c r="B11" s="234" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="142">
+      <c r="B11" s="230" t="inlineStr">
         <is>
           <t>DERIVED &amp; LISTED SPREADS</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="144">
-      <c r="B12" s="235" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="142">
+      <c r="B12" s="231" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C12" s="235" t="inlineStr">
+      <c r="C12" s="231" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="D12" s="235" t="inlineStr">
+      <c r="D12" s="231" t="inlineStr">
         <is>
           <t>Crossing convention</t>
         </is>
       </c>
-      <c r="H12" s="235" t="inlineStr">
+      <c r="H12" s="231" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I12" s="235" t="inlineStr">
+      <c r="I12" s="231" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="L12" s="235" t="inlineStr">
+      <c r="L12" s="231" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="M12" s="235" t="inlineStr">
+      <c r="M12" s="231" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="144">
-      <c r="B13" s="236" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="142">
+      <c r="B13" s="232" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="C13" s="239" t="inlineStr">
+      <c r="C13" s="235" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D13" s="241" t="inlineStr">
+      <c r="D13" s="237" t="inlineStr">
         <is>
           <t>bid = BZ bid - CL ask ; ask = BZ ask - CL bid</t>
         </is>
       </c>
-      <c r="H13" s="240" t="n"/>
-      <c r="I13" s="240" t="n"/>
-      <c r="L13" s="240" t="n"/>
-      <c r="M13" s="240" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="144">
-      <c r="B14" s="236" t="inlineStr">
+      <c r="H13" s="236" t="n"/>
+      <c r="I13" s="236" t="n"/>
+      <c r="L13" s="236" t="n"/>
+      <c r="M13" s="236" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="142">
+      <c r="B14" s="232" t="inlineStr">
         <is>
           <t>HO/CL crack</t>
         </is>
       </c>
-      <c r="C14" s="239" t="inlineStr">
+      <c r="C14" s="235" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D14" s="241" t="inlineStr">
+      <c r="D14" s="237" t="inlineStr">
         <is>
           <t>bid = HO bid x42 - CL ask ; ask = HO ask x42 - CL bid</t>
         </is>
       </c>
-      <c r="H14" s="240" t="n"/>
-      <c r="I14" s="240" t="n"/>
-      <c r="L14" s="240" t="n"/>
-      <c r="M14" s="240" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="144">
-      <c r="B15" s="236" t="inlineStr">
+      <c r="H14" s="236" t="n"/>
+      <c r="I14" s="236" t="n"/>
+      <c r="L14" s="236" t="n"/>
+      <c r="M14" s="236" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="142">
+      <c r="B15" s="232" t="inlineStr">
         <is>
           <t>3:2:1 crack</t>
         </is>
       </c>
-      <c r="C15" s="239" t="inlineStr">
+      <c r="C15" s="235" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D15" s="241" t="inlineStr">
+      <c r="D15" s="237" t="inlineStr">
         <is>
           <t>bid sells products at the bid and buys crude at the ask; ask mirrors it</t>
         </is>
       </c>
-      <c r="H15" s="240" t="n"/>
-      <c r="I15" s="240" t="n"/>
-      <c r="L15" s="240" t="n"/>
-      <c r="M15" s="240" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="144">
-      <c r="B16" s="236" t="inlineStr">
+      <c r="H15" s="236" t="n"/>
+      <c r="I15" s="236" t="n"/>
+      <c r="L15" s="236" t="n"/>
+      <c r="M15" s="236" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="142">
+      <c r="B16" s="232" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="C16" s="239" t="inlineStr">
+      <c r="C16" s="235" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="D16" s="241" t="inlineStr">
+      <c r="D16" s="237" t="inlineStr">
         <is>
           <t>exchange-listed - one quote, no leg risk</t>
         </is>
       </c>
-      <c r="H16" s="240" t="n"/>
-      <c r="I16" s="240" t="n"/>
-      <c r="L16" s="240" t="n"/>
-      <c r="M16" s="240" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="144">
-      <c r="B17" s="236" t="inlineStr">
+      <c r="H16" s="236" t="n"/>
+      <c r="I16" s="236" t="n"/>
+      <c r="L16" s="236" t="n"/>
+      <c r="M16" s="236" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="142">
+      <c r="B17" s="232" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="C17" s="239" t="inlineStr">
+      <c r="C17" s="235" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="D17" s="241" t="inlineStr">
+      <c r="D17" s="237" t="inlineStr">
         <is>
           <t>exchange-listed - one quote, no leg risk</t>
         </is>
       </c>
-      <c r="H17" s="240" t="n"/>
-      <c r="I17" s="240" t="n"/>
-      <c r="L17" s="240" t="n"/>
-      <c r="M17" s="240" t="n"/>
+      <c r="H17" s="236" t="n"/>
+      <c r="I17" s="236" t="n"/>
+      <c r="L17" s="236" t="n"/>
+      <c r="M17" s="236" t="n"/>
     </row>
     <row r="18"/>
-    <row r="19" ht="15" customHeight="1" s="144">
-      <c r="B19" s="234" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="142">
+      <c r="B19" s="230" t="inlineStr">
         <is>
           <t>PER-SPREAD BREAKDOWN</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="144">
-      <c r="B20" s="235" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="142">
+      <c r="B20" s="231" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C20" s="235" t="inlineStr">
+      <c r="C20" s="231" t="inlineStr">
         <is>
           <t>Unit / note</t>
         </is>
       </c>
-      <c r="D20" s="235" t="inlineStr">
+      <c r="D20" s="231" t="inlineStr">
         <is>
           <t>SPREAD 1</t>
         </is>
       </c>
-      <c r="E20" s="235" t="inlineStr">
+      <c r="E20" s="231" t="inlineStr">
         <is>
           <t>SPREAD 2</t>
         </is>
       </c>
-      <c r="F20" s="235" t="inlineStr">
+      <c r="F20" s="231" t="inlineStr">
         <is>
           <t>SPREAD 3</t>
         </is>
       </c>
-      <c r="G20" s="235" t="inlineStr">
+      <c r="G20" s="231" t="inlineStr">
         <is>
           <t>SPREAD 4</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="144">
-      <c r="B21" s="242" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="142">
+      <c r="B21" s="238" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C21" s="241" t="n"/>
-      <c r="D21" s="243" t="n"/>
-      <c r="E21" s="243" t="n"/>
-      <c r="F21" s="243" t="n"/>
-      <c r="G21" s="243" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="144">
-      <c r="B22" s="242" t="inlineStr">
+      <c r="C21" s="237" t="n"/>
+      <c r="D21" s="239" t="n"/>
+      <c r="E21" s="239" t="n"/>
+      <c r="F21" s="239" t="n"/>
+      <c r="G21" s="239" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="142">
+      <c r="B22" s="238" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C22" s="241" t="inlineStr">
+      <c r="C22" s="237" t="inlineStr">
         <is>
           <t>LegB - beta x LegA</t>
         </is>
       </c>
-      <c r="D22" s="243" t="n"/>
-      <c r="E22" s="243" t="n"/>
-      <c r="F22" s="243" t="n"/>
-      <c r="G22" s="243" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="144">
-      <c r="B23" s="242" t="inlineStr">
+      <c r="D22" s="239" t="n"/>
+      <c r="E22" s="239" t="n"/>
+      <c r="F22" s="239" t="n"/>
+      <c r="G22" s="239" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="142">
+      <c r="B23" s="238" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="C23" s="241" t="n"/>
-      <c r="D23" s="243" t="n"/>
-      <c r="E23" s="243" t="n"/>
-      <c r="F23" s="243" t="n"/>
-      <c r="G23" s="243" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="144">
-      <c r="B24" s="242" t="inlineStr">
+      <c r="C23" s="237" t="n"/>
+      <c r="D23" s="239" t="n"/>
+      <c r="E23" s="239" t="n"/>
+      <c r="F23" s="239" t="n"/>
+      <c r="G23" s="239" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="142">
+      <c r="B24" s="238" t="inlineStr">
         <is>
           <t>HEDGE_RATIO (beta)</t>
         </is>
       </c>
-      <c r="C24" s="241" t="inlineStr">
+      <c r="C24" s="237" t="inlineStr">
         <is>
           <t>stamped pair -&gt;</t>
         </is>
       </c>
-      <c r="D24" s="243" t="n"/>
-      <c r="E24" s="243" t="n"/>
-      <c r="F24" s="243" t="n"/>
-      <c r="G24" s="243" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="144">
-      <c r="B25" s="242" t="inlineStr">
+      <c r="D24" s="239" t="n"/>
+      <c r="E24" s="239" t="n"/>
+      <c r="F24" s="239" t="n"/>
+      <c r="G24" s="239" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="142">
+      <c r="B25" s="238" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread</t>
         </is>
       </c>
-      <c r="C25" s="241" t="inlineStr">
+      <c r="C25" s="237" t="inlineStr">
         <is>
           <t>per lot</t>
         </is>
       </c>
-      <c r="D25" s="244" t="n"/>
-      <c r="E25" s="244" t="n"/>
-      <c r="F25" s="244" t="n"/>
-      <c r="G25" s="244" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="144">
-      <c r="B26" s="245" t="inlineStr">
+      <c r="D25" s="240" t="n"/>
+      <c r="E25" s="240" t="n"/>
+      <c r="F25" s="240" t="n"/>
+      <c r="G25" s="240" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="142">
+      <c r="B26" s="241" t="inlineStr">
         <is>
           <t>MARKET  (touch, shown separately from the statistic)</t>
         </is>
       </c>
-      <c r="C26" s="246" t="n"/>
-      <c r="D26" s="246" t="n"/>
-      <c r="E26" s="246" t="n"/>
-      <c r="F26" s="246" t="n"/>
-      <c r="G26" s="246" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="144">
-      <c r="B27" s="242" t="inlineStr">
+      <c r="C26" s="242" t="n"/>
+      <c r="D26" s="242" t="n"/>
+      <c r="E26" s="242" t="n"/>
+      <c r="F26" s="242" t="n"/>
+      <c r="G26" s="242" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="142">
+      <c r="B27" s="238" t="inlineStr">
         <is>
           <t>Spread bid</t>
         </is>
       </c>
-      <c r="C27" s="241" t="n"/>
-      <c r="D27" s="240" t="n"/>
-      <c r="E27" s="240" t="n"/>
-      <c r="F27" s="240" t="n"/>
-      <c r="G27" s="240" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="144">
-      <c r="B28" s="242" t="inlineStr">
+      <c r="C27" s="237" t="n"/>
+      <c r="D27" s="236" t="n"/>
+      <c r="E27" s="236" t="n"/>
+      <c r="F27" s="236" t="n"/>
+      <c r="G27" s="236" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="142">
+      <c r="B28" s="238" t="inlineStr">
         <is>
           <t>Spread ask</t>
         </is>
       </c>
-      <c r="C28" s="241" t="n"/>
-      <c r="D28" s="240" t="n"/>
-      <c r="E28" s="240" t="n"/>
-      <c r="F28" s="240" t="n"/>
-      <c r="G28" s="240" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="144">
-      <c r="B29" s="242" t="inlineStr">
+      <c r="C28" s="237" t="n"/>
+      <c r="D28" s="236" t="n"/>
+      <c r="E28" s="236" t="n"/>
+      <c r="F28" s="236" t="n"/>
+      <c r="G28" s="236" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="142">
+      <c r="B29" s="238" t="inlineStr">
         <is>
           <t>Spread mid   &lt;- feeds the statistic</t>
         </is>
       </c>
-      <c r="C29" s="241" t="n"/>
-      <c r="D29" s="240" t="n"/>
-      <c r="E29" s="240" t="n"/>
-      <c r="F29" s="240" t="n"/>
-      <c r="G29" s="240" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="144">
-      <c r="B30" s="242" t="inlineStr">
+      <c r="C29" s="237" t="n"/>
+      <c r="D29" s="236" t="n"/>
+      <c r="E29" s="236" t="n"/>
+      <c r="F29" s="236" t="n"/>
+      <c r="G29" s="236" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="142">
+      <c r="B30" s="238" t="inlineStr">
         <is>
           <t>Bid-Ask Gap</t>
         </is>
       </c>
-      <c r="C30" s="241" t="inlineStr">
+      <c r="C30" s="237" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D30" s="240" t="n"/>
-      <c r="E30" s="240" t="n"/>
-      <c r="F30" s="240" t="n"/>
-      <c r="G30" s="240" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="144">
-      <c r="B31" s="245" t="inlineStr">
+      <c r="D30" s="236" t="n"/>
+      <c r="E30" s="236" t="n"/>
+      <c r="F30" s="236" t="n"/>
+      <c r="G30" s="236" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="142">
+      <c r="B31" s="241" t="inlineStr">
         <is>
           <t>WINDOW</t>
         </is>
       </c>
-      <c r="C31" s="246" t="n"/>
-      <c r="D31" s="246" t="n"/>
-      <c r="E31" s="246" t="n"/>
-      <c r="F31" s="246" t="n"/>
-      <c r="G31" s="246" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="144">
-      <c r="B32" s="242" t="inlineStr">
+      <c r="C31" s="242" t="n"/>
+      <c r="D31" s="242" t="n"/>
+      <c r="E31" s="242" t="n"/>
+      <c r="F31" s="242" t="n"/>
+      <c r="G31" s="242" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="142">
+      <c r="B32" s="238" t="inlineStr">
         <is>
           <t>Stored samples in window</t>
         </is>
       </c>
-      <c r="C32" s="241" t="inlineStr">
+      <c r="C32" s="237" t="inlineStr">
         <is>
           <t>after dedupe + store gate</t>
         </is>
       </c>
-      <c r="D32" s="244" t="n"/>
-      <c r="E32" s="244" t="n"/>
-      <c r="F32" s="244" t="n"/>
-      <c r="G32" s="244" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="144">
-      <c r="B33" s="242" t="inlineStr">
+      <c r="D32" s="240" t="n"/>
+      <c r="E32" s="240" t="n"/>
+      <c r="F32" s="240" t="n"/>
+      <c r="G32" s="240" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="142">
+      <c r="B33" s="238" t="inlineStr">
         <is>
           <t>Window elapsed</t>
         </is>
       </c>
-      <c r="C33" s="241" t="inlineStr">
+      <c r="C33" s="237" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D33" s="247" t="n"/>
-      <c r="E33" s="247" t="n"/>
-      <c r="F33" s="247" t="n"/>
-      <c r="G33" s="247" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="144">
-      <c r="B34" s="242" t="inlineStr">
+      <c r="D33" s="243" t="n"/>
+      <c r="E33" s="243" t="n"/>
+      <c r="F33" s="243" t="n"/>
+      <c r="G33" s="243" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="142">
+      <c r="B34" s="238" t="inlineStr">
         <is>
           <t>Warm-up gate</t>
         </is>
       </c>
-      <c r="C34" s="241" t="inlineStr">
+      <c r="C34" s="237" t="inlineStr">
         <is>
           <t>binding gate</t>
         </is>
       </c>
-      <c r="D34" s="243" t="n"/>
-      <c r="E34" s="243" t="n"/>
-      <c r="F34" s="243" t="n"/>
-      <c r="G34" s="243" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="144">
-      <c r="B35" s="242" t="inlineStr">
+      <c r="D34" s="239" t="n"/>
+      <c r="E34" s="239" t="n"/>
+      <c r="F34" s="239" t="n"/>
+      <c r="G34" s="239" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="142">
+      <c r="B35" s="238" t="inlineStr">
         <is>
           <t>Feed rate</t>
         </is>
       </c>
-      <c r="C35" s="241" t="inlineStr">
+      <c r="C35" s="237" t="inlineStr">
         <is>
           <t>quote CHANGES / min</t>
         </is>
       </c>
-      <c r="D35" s="248" t="n"/>
-      <c r="E35" s="248" t="n"/>
-      <c r="F35" s="248" t="n"/>
-      <c r="G35" s="248" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="144">
-      <c r="B36" s="242" t="inlineStr">
+      <c r="D35" s="244" t="n"/>
+      <c r="E35" s="244" t="n"/>
+      <c r="F35" s="244" t="n"/>
+      <c r="G35" s="244" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="142">
+      <c r="B36" s="238" t="inlineStr">
         <is>
           <t>Feed status</t>
         </is>
       </c>
-      <c r="C36" s="241" t="n"/>
-      <c r="D36" s="243" t="n"/>
-      <c r="E36" s="243" t="n"/>
-      <c r="F36" s="243" t="n"/>
-      <c r="G36" s="243" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="144">
-      <c r="B37" s="245" t="inlineStr">
+      <c r="C36" s="237" t="n"/>
+      <c r="D36" s="239" t="n"/>
+      <c r="E36" s="239" t="n"/>
+      <c r="F36" s="239" t="n"/>
+      <c r="G36" s="239" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="142">
+      <c r="B37" s="241" t="inlineStr">
         <is>
           <t>STATISTICS  (FROZEN - republished every STATS_REFRESH_MIN)</t>
         </is>
       </c>
-      <c r="C37" s="246" t="n"/>
-      <c r="D37" s="246" t="n"/>
-      <c r="E37" s="246" t="n"/>
-      <c r="F37" s="246" t="n"/>
-      <c r="G37" s="246" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="144">
-      <c r="B38" s="242" t="inlineStr">
+      <c r="C37" s="242" t="n"/>
+      <c r="D37" s="242" t="n"/>
+      <c r="E37" s="242" t="n"/>
+      <c r="F37" s="242" t="n"/>
+      <c r="G37" s="242" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="142">
+      <c r="B38" s="238" t="inlineStr">
         <is>
           <t>Mean (frozen)</t>
         </is>
       </c>
-      <c r="C38" s="241" t="n"/>
-      <c r="D38" s="240" t="n"/>
-      <c r="E38" s="240" t="n"/>
-      <c r="F38" s="240" t="n"/>
-      <c r="G38" s="240" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="144">
-      <c r="B39" s="242" t="inlineStr">
+      <c r="C38" s="237" t="n"/>
+      <c r="D38" s="236" t="n"/>
+      <c r="E38" s="236" t="n"/>
+      <c r="F38" s="236" t="n"/>
+      <c r="G38" s="236" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="142">
+      <c r="B39" s="238" t="inlineStr">
         <is>
           <t>Std Dev (frozen)</t>
         </is>
       </c>
-      <c r="C39" s="241" t="n"/>
-      <c r="D39" s="240" t="n"/>
-      <c r="E39" s="240" t="n"/>
-      <c r="F39" s="240" t="n"/>
-      <c r="G39" s="240" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="144">
-      <c r="B40" s="242" t="inlineStr">
+      <c r="C39" s="237" t="n"/>
+      <c r="D39" s="236" t="n"/>
+      <c r="E39" s="236" t="n"/>
+      <c r="F39" s="236" t="n"/>
+      <c r="G39" s="236" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="142">
+      <c r="B40" s="238" t="inlineStr">
         <is>
           <t>Std Dev in dollars</t>
         </is>
       </c>
-      <c r="C40" s="241" t="inlineStr">
+      <c r="C40" s="237" t="inlineStr">
         <is>
           <t>sigma x USD/pt x LOTS</t>
         </is>
       </c>
-      <c r="D40" s="249" t="n"/>
-      <c r="E40" s="249" t="n"/>
-      <c r="F40" s="249" t="n"/>
-      <c r="G40" s="249" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="144">
-      <c r="B41" s="242" t="inlineStr">
+      <c r="D40" s="245" t="n"/>
+      <c r="E40" s="245" t="n"/>
+      <c r="F40" s="245" t="n"/>
+      <c r="G40" s="245" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="142">
+      <c r="B41" s="238" t="inlineStr">
         <is>
           <t>Stats age / next refresh</t>
         </is>
       </c>
-      <c r="C41" s="241" t="inlineStr">
+      <c r="C41" s="237" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D41" s="243" t="n"/>
-      <c r="E41" s="243" t="n"/>
-      <c r="F41" s="243" t="n"/>
-      <c r="G41" s="243" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="144">
-      <c r="B42" s="250" t="inlineStr">
+      <c r="D41" s="239" t="n"/>
+      <c r="E41" s="239" t="n"/>
+      <c r="F41" s="239" t="n"/>
+      <c r="G41" s="239" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="142">
+      <c r="B42" s="246" t="inlineStr">
         <is>
           <t>Z  (live, vs frozen mean &amp; sigma)</t>
         </is>
       </c>
-      <c r="C42" s="241" t="n"/>
-      <c r="D42" s="251" t="n"/>
-      <c r="E42" s="251" t="n"/>
-      <c r="F42" s="251" t="n"/>
-      <c r="G42" s="251" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="144">
-      <c r="B43" s="250" t="inlineStr">
+      <c r="C42" s="237" t="n"/>
+      <c r="D42" s="247" t="n"/>
+      <c r="E42" s="247" t="n"/>
+      <c r="F42" s="247" t="n"/>
+      <c r="G42" s="247" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="142">
+      <c r="B43" s="246" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="C43" s="241" t="n"/>
-      <c r="D43" s="252" t="n"/>
-      <c r="E43" s="252" t="n"/>
-      <c r="F43" s="252" t="n"/>
-      <c r="G43" s="252" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="144">
-      <c r="B44" s="245" t="inlineStr">
+      <c r="C43" s="237" t="n"/>
+      <c r="D43" s="248" t="n"/>
+      <c r="E43" s="248" t="n"/>
+      <c r="F43" s="248" t="n"/>
+      <c r="G43" s="248" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="142">
+      <c r="B44" s="241" t="inlineStr">
         <is>
           <t>COST OF THE ROUND TRIP</t>
         </is>
       </c>
-      <c r="C44" s="246" t="n"/>
-      <c r="D44" s="246" t="n"/>
-      <c r="E44" s="246" t="n"/>
-      <c r="F44" s="246" t="n"/>
-      <c r="G44" s="246" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="144">
-      <c r="B45" s="242" t="inlineStr">
+      <c r="C44" s="242" t="n"/>
+      <c r="D44" s="242" t="n"/>
+      <c r="E44" s="242" t="n"/>
+      <c r="F44" s="242" t="n"/>
+      <c r="G44" s="242" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="142">
+      <c r="B45" s="238" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C45" s="241" t="n"/>
-      <c r="D45" s="243" t="n"/>
-      <c r="E45" s="243" t="n"/>
-      <c r="F45" s="243" t="n"/>
-      <c r="G45" s="243" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="144">
-      <c r="B46" s="242" t="inlineStr">
+      <c r="C45" s="237" t="n"/>
+      <c r="D45" s="239" t="n"/>
+      <c r="E45" s="239" t="n"/>
+      <c r="F45" s="239" t="n"/>
+      <c r="G45" s="239" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="142">
+      <c r="B46" s="238" t="inlineStr">
         <is>
           <t>Entry reference (touch)</t>
         </is>
       </c>
-      <c r="C46" s="241" t="n"/>
-      <c r="D46" s="240" t="n"/>
-      <c r="E46" s="240" t="n"/>
-      <c r="F46" s="240" t="n"/>
-      <c r="G46" s="240" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="144">
-      <c r="B47" s="242" t="inlineStr">
+      <c r="C46" s="237" t="n"/>
+      <c r="D46" s="236" t="n"/>
+      <c r="E46" s="236" t="n"/>
+      <c r="F46" s="236" t="n"/>
+      <c r="G46" s="236" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="142">
+      <c r="B47" s="238" t="inlineStr">
         <is>
           <t>Commission</t>
         </is>
       </c>
-      <c r="C47" s="241" t="inlineStr">
+      <c r="C47" s="237" t="inlineStr">
         <is>
           <t>contracts x rate x LOTS</t>
         </is>
       </c>
-      <c r="D47" s="249" t="n"/>
-      <c r="E47" s="249" t="n"/>
-      <c r="F47" s="249" t="n"/>
-      <c r="G47" s="249" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="144">
-      <c r="B48" s="242" t="inlineStr">
+      <c r="D47" s="245" t="n"/>
+      <c r="E47" s="245" t="n"/>
+      <c r="F47" s="245" t="n"/>
+      <c r="G47" s="245" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="142">
+      <c r="B48" s="238" t="inlineStr">
         <is>
           <t>Crossing cost - LEGGING</t>
         </is>
       </c>
-      <c r="C48" s="241" t="n"/>
-      <c r="D48" s="249" t="n"/>
-      <c r="E48" s="249" t="n"/>
-      <c r="F48" s="249" t="n"/>
-      <c r="G48" s="249" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="144">
-      <c r="B49" s="242" t="inlineStr">
+      <c r="C48" s="237" t="n"/>
+      <c r="D48" s="245" t="n"/>
+      <c r="E48" s="245" t="n"/>
+      <c r="F48" s="245" t="n"/>
+      <c r="G48" s="245" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="142">
+      <c r="B49" s="238" t="inlineStr">
         <is>
           <t>Crossing cost - LISTED</t>
         </is>
       </c>
-      <c r="C49" s="241" t="n"/>
-      <c r="D49" s="249" t="n"/>
-      <c r="E49" s="249" t="n"/>
-      <c r="F49" s="249" t="n"/>
-      <c r="G49" s="249" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="144">
-      <c r="B50" s="250" t="inlineStr">
+      <c r="C49" s="237" t="n"/>
+      <c r="D49" s="245" t="n"/>
+      <c r="E49" s="245" t="n"/>
+      <c r="F49" s="245" t="n"/>
+      <c r="G49" s="245" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="142">
+      <c r="B50" s="246" t="inlineStr">
         <is>
           <t>TOTAL COST (this mode)</t>
         </is>
       </c>
-      <c r="C50" s="241" t="n"/>
-      <c r="D50" s="253" t="n"/>
-      <c r="E50" s="253" t="n"/>
-      <c r="F50" s="253" t="n"/>
-      <c r="G50" s="253" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="144">
-      <c r="B51" s="245" t="inlineStr">
+      <c r="C50" s="237" t="n"/>
+      <c r="D50" s="249" t="n"/>
+      <c r="E50" s="249" t="n"/>
+      <c r="F50" s="249" t="n"/>
+      <c r="G50" s="249" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="142">
+      <c r="B51" s="241" t="inlineStr">
         <is>
           <t>TAKE PROFIT  (exits act on MONEY, never on z)</t>
         </is>
       </c>
-      <c r="C51" s="246" t="n"/>
-      <c r="D51" s="246" t="n"/>
-      <c r="E51" s="246" t="n"/>
-      <c r="F51" s="246" t="n"/>
-      <c r="G51" s="246" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="144">
-      <c r="B52" s="242" t="inlineStr">
+      <c r="C51" s="242" t="n"/>
+      <c r="D51" s="242" t="n"/>
+      <c r="E51" s="242" t="n"/>
+      <c r="F51" s="242" t="n"/>
+      <c r="G51" s="242" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="142">
+      <c r="B52" s="238" t="inlineStr">
         <is>
           <t>TP rule in force</t>
         </is>
       </c>
-      <c r="C52" s="241" t="n"/>
-      <c r="D52" s="243" t="n"/>
-      <c r="E52" s="243" t="n"/>
-      <c r="F52" s="243" t="n"/>
-      <c r="G52" s="243" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="144">
-      <c r="B53" s="242" t="inlineStr">
+      <c r="C52" s="237" t="n"/>
+      <c r="D52" s="239" t="n"/>
+      <c r="E52" s="239" t="n"/>
+      <c r="F52" s="239" t="n"/>
+      <c r="G52" s="239" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="142">
+      <c r="B53" s="238" t="inlineStr">
         <is>
           <t>Notional (per NOTIONAL_BASIS)</t>
         </is>
       </c>
-      <c r="C53" s="241" t="n"/>
-      <c r="D53" s="249" t="n"/>
-      <c r="E53" s="249" t="n"/>
-      <c r="F53" s="249" t="n"/>
-      <c r="G53" s="249" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="144">
-      <c r="B54" s="242" t="inlineStr">
+      <c r="C53" s="237" t="n"/>
+      <c r="D53" s="245" t="n"/>
+      <c r="E53" s="245" t="n"/>
+      <c r="F53" s="245" t="n"/>
+      <c r="G53" s="245" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="142">
+      <c r="B54" s="238" t="inlineStr">
         <is>
           <t>Win target (WIN_PCT x notional)</t>
         </is>
       </c>
-      <c r="C54" s="241" t="n"/>
-      <c r="D54" s="249" t="n"/>
-      <c r="E54" s="249" t="n"/>
-      <c r="F54" s="249" t="n"/>
-      <c r="G54" s="249" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="144">
-      <c r="B55" s="242" t="inlineStr">
+      <c r="C54" s="237" t="n"/>
+      <c r="D54" s="245" t="n"/>
+      <c r="E54" s="245" t="n"/>
+      <c r="F54" s="245" t="n"/>
+      <c r="G54" s="245" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="142">
+      <c r="B55" s="238" t="inlineStr">
         <is>
           <t>Costs in spread units</t>
         </is>
       </c>
-      <c r="C55" s="241" t="n"/>
-      <c r="D55" s="240" t="n"/>
-      <c r="E55" s="240" t="n"/>
-      <c r="F55" s="240" t="n"/>
-      <c r="G55" s="240" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="144">
-      <c r="B56" s="242" t="inlineStr">
+      <c r="C55" s="237" t="n"/>
+      <c r="D55" s="236" t="n"/>
+      <c r="E55" s="236" t="n"/>
+      <c r="F55" s="236" t="n"/>
+      <c r="G55" s="236" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="142">
+      <c r="B56" s="238" t="inlineStr">
         <is>
           <t>Win in spread units</t>
         </is>
       </c>
-      <c r="C56" s="241" t="n"/>
-      <c r="D56" s="240" t="n"/>
-      <c r="E56" s="240" t="n"/>
-      <c r="F56" s="240" t="n"/>
-      <c r="G56" s="240" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="144">
-      <c r="B57" s="242" t="inlineStr">
+      <c r="C56" s="237" t="n"/>
+      <c r="D56" s="236" t="n"/>
+      <c r="E56" s="236" t="n"/>
+      <c r="F56" s="236" t="n"/>
+      <c r="G56" s="236" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="142">
+      <c r="B57" s="238" t="inlineStr">
         <is>
           <t>Break-even spread</t>
         </is>
       </c>
-      <c r="C57" s="241" t="inlineStr">
+      <c r="C57" s="237" t="inlineStr">
         <is>
           <t>absolute level</t>
         </is>
       </c>
-      <c r="D57" s="240" t="n"/>
-      <c r="E57" s="240" t="n"/>
-      <c r="F57" s="240" t="n"/>
-      <c r="G57" s="240" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="144">
-      <c r="B58" s="250" t="inlineStr">
+      <c r="D57" s="236" t="n"/>
+      <c r="E57" s="236" t="n"/>
+      <c r="F57" s="236" t="n"/>
+      <c r="G57" s="236" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="142">
+      <c r="B58" s="246" t="inlineStr">
         <is>
           <t>TAKE-PROFIT spread</t>
         </is>
       </c>
-      <c r="C58" s="241" t="inlineStr">
+      <c r="C58" s="237" t="inlineStr">
         <is>
           <t>absolute level</t>
         </is>
       </c>
-      <c r="D58" s="254" t="n"/>
-      <c r="E58" s="254" t="n"/>
-      <c r="F58" s="254" t="n"/>
-      <c r="G58" s="254" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="144">
-      <c r="B59" s="242" t="inlineStr">
+      <c r="D58" s="250" t="n"/>
+      <c r="E58" s="250" t="n"/>
+      <c r="F58" s="250" t="n"/>
+      <c r="G58" s="250" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="142">
+      <c r="B59" s="238" t="inlineStr">
         <is>
           <t>TP distance</t>
         </is>
       </c>
-      <c r="C59" s="241" t="inlineStr">
+      <c r="C59" s="237" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D59" s="240" t="n"/>
-      <c r="E59" s="240" t="n"/>
-      <c r="F59" s="240" t="n"/>
-      <c r="G59" s="240" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="144">
-      <c r="B60" s="242" t="inlineStr">
+      <c r="D59" s="236" t="n"/>
+      <c r="E59" s="236" t="n"/>
+      <c r="F59" s="236" t="n"/>
+      <c r="G59" s="236" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="142">
+      <c r="B60" s="238" t="inlineStr">
         <is>
           <t>TP in sigma</t>
         </is>
       </c>
-      <c r="C60" s="241" t="inlineStr">
+      <c r="C60" s="237" t="inlineStr">
         <is>
           <t>x sigma</t>
         </is>
       </c>
-      <c r="D60" s="247" t="n"/>
-      <c r="E60" s="247" t="n"/>
-      <c r="F60" s="247" t="n"/>
-      <c r="G60" s="247" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="144">
-      <c r="B61" s="242" t="inlineStr">
+      <c r="D60" s="243" t="n"/>
+      <c r="E60" s="243" t="n"/>
+      <c r="F60" s="243" t="n"/>
+      <c r="G60" s="243" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="142">
+      <c r="B61" s="238" t="inlineStr">
         <is>
           <t>Target z</t>
         </is>
       </c>
-      <c r="C61" s="241" t="inlineStr">
+      <c r="C61" s="237" t="inlineStr">
         <is>
           <t>z at the TP level</t>
         </is>
       </c>
-      <c r="D61" s="247" t="n"/>
-      <c r="E61" s="247" t="n"/>
-      <c r="F61" s="247" t="n"/>
-      <c r="G61" s="247" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="144">
-      <c r="B62" s="242" t="inlineStr">
+      <c r="D61" s="243" t="n"/>
+      <c r="E61" s="243" t="n"/>
+      <c r="F61" s="243" t="n"/>
+      <c r="G61" s="243" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="142">
+      <c r="B62" s="238" t="inlineStr">
         <is>
           <t>TP beyond the mean?</t>
         </is>
       </c>
-      <c r="C62" s="241" t="n"/>
-      <c r="D62" s="243" t="n"/>
-      <c r="E62" s="243" t="n"/>
-      <c r="F62" s="243" t="n"/>
-      <c r="G62" s="243" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="144">
-      <c r="B63" s="245" t="inlineStr">
+      <c r="C62" s="237" t="n"/>
+      <c r="D62" s="239" t="n"/>
+      <c r="E62" s="239" t="n"/>
+      <c r="F62" s="239" t="n"/>
+      <c r="G62" s="239" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="142">
+      <c r="B63" s="241" t="inlineStr">
         <is>
           <t>EDGE FILTER  (a separate gate from ENTRY_Z)</t>
         </is>
       </c>
-      <c r="C63" s="246" t="n"/>
-      <c r="D63" s="246" t="n"/>
-      <c r="E63" s="246" t="n"/>
-      <c r="F63" s="246" t="n"/>
-      <c r="G63" s="246" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="144">
-      <c r="B64" s="242" t="inlineStr">
+      <c r="C63" s="242" t="n"/>
+      <c r="D63" s="242" t="n"/>
+      <c r="E63" s="242" t="n"/>
+      <c r="F63" s="242" t="n"/>
+      <c r="G63" s="242" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="142">
+      <c r="B64" s="238" t="inlineStr">
         <is>
           <t>Expected capture</t>
         </is>
       </c>
-      <c r="C64" s="241" t="inlineStr">
+      <c r="C64" s="237" t="inlineStr">
         <is>
           <t>0.5 x |z| x sigma x USD/pt x LOTS</t>
         </is>
       </c>
-      <c r="D64" s="249" t="n"/>
-      <c r="E64" s="249" t="n"/>
-      <c r="F64" s="249" t="n"/>
-      <c r="G64" s="249" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="144">
-      <c r="B65" s="242" t="inlineStr">
+      <c r="D64" s="245" t="n"/>
+      <c r="E64" s="245" t="n"/>
+      <c r="F64" s="245" t="n"/>
+      <c r="G64" s="245" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="142">
+      <c r="B65" s="238" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C65" s="241" t="inlineStr">
+      <c r="C65" s="237" t="inlineStr">
         <is>
           <t>EDGE_MULTIPLE x total cost</t>
         </is>
       </c>
-      <c r="D65" s="249" t="n"/>
-      <c r="E65" s="249" t="n"/>
-      <c r="F65" s="249" t="n"/>
-      <c r="G65" s="249" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="144">
-      <c r="B66" s="250" t="inlineStr">
+      <c r="D65" s="245" t="n"/>
+      <c r="E65" s="245" t="n"/>
+      <c r="F65" s="245" t="n"/>
+      <c r="G65" s="245" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="142">
+      <c r="B66" s="246" t="inlineStr">
         <is>
           <t>EDGE VERDICT</t>
         </is>
       </c>
-      <c r="C66" s="241" t="n"/>
-      <c r="D66" s="252" t="n"/>
-      <c r="E66" s="252" t="n"/>
-      <c r="F66" s="252" t="n"/>
-      <c r="G66" s="252" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="144">
-      <c r="B67" s="242" t="inlineStr">
+      <c r="C66" s="237" t="n"/>
+      <c r="D66" s="248" t="n"/>
+      <c r="E66" s="248" t="n"/>
+      <c r="F66" s="248" t="n"/>
+      <c r="G66" s="248" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="142">
+      <c r="B67" s="238" t="inlineStr">
         <is>
           <t>Min sigma to pass at live z</t>
         </is>
       </c>
-      <c r="C67" s="241" t="inlineStr">
+      <c r="C67" s="237" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D67" s="240" t="n"/>
-      <c r="E67" s="240" t="n"/>
-      <c r="F67" s="240" t="n"/>
-      <c r="G67" s="240" t="n"/>
+      <c r="D67" s="236" t="n"/>
+      <c r="E67" s="236" t="n"/>
+      <c r="F67" s="236" t="n"/>
+      <c r="G67" s="236" t="n"/>
     </row>
     <row r="68"/>
-    <row r="69" ht="15" customHeight="1" s="144">
-      <c r="B69" s="255" t="inlineStr">
+    <row r="69" ht="15" customHeight="1" s="142">
+      <c r="B69" s="251" t="inlineStr">
         <is>
           <t>The EDGE FILTER is a different gate from ENTRY_Z. ENTRY_Z decides when the chime fires; the edge filter asks whether the expected capture clears the round trip by EDGE_MULTIPLE. A highlighted z that fails the edge filter is still not a trade worth taking.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="144">
-      <c r="B70" s="233" t="inlineStr">
+    <row r="70" ht="15" customHeight="1" s="142">
+      <c r="B70" s="229" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES on Config decides whether a failing edge filter also silences the chime. It ships FALSE, so the chime follows ENTRY_Z alone.</t>
         </is>
@@ -3871,1705 +3867,1732 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="142" min="1" max="1"/>
-    <col width="34" customWidth="1" style="142" min="2" max="2"/>
-    <col width="14" customWidth="1" style="142" min="3" max="3"/>
-    <col width="10" customWidth="1" style="142" min="4" max="4"/>
-    <col width="96" customWidth="1" style="142" min="5" max="5"/>
-    <col width="30" customWidth="1" style="142" min="6" max="6"/>
-    <col width="12" customWidth="1" style="142" min="7" max="8"/>
-    <col width="10" customWidth="1" style="142" min="9" max="9"/>
-    <col width="8" customWidth="1" style="142" min="10" max="10"/>
-    <col width="34" customWidth="1" style="142" min="11" max="11"/>
+    <col width="30" customWidth="1" style="140" min="1" max="1"/>
+    <col width="34" customWidth="1" style="140" min="2" max="2"/>
+    <col width="14" customWidth="1" style="140" min="3" max="3"/>
+    <col width="10" customWidth="1" style="140" min="4" max="4"/>
+    <col width="96" customWidth="1" style="140" min="5" max="5"/>
+    <col width="30" customWidth="1" style="140" min="6" max="6"/>
+    <col width="12" customWidth="1" style="140" min="7" max="8"/>
+    <col width="10" customWidth="1" style="140" min="9" max="9"/>
+    <col width="8" customWidth="1" style="140" min="10" max="10"/>
+    <col width="34" customWidth="1" style="140" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.7" customHeight="1" s="144">
-      <c r="A1" s="256" t="inlineStr">
+    <row r="1" ht="19.7" customHeight="1" s="142">
+      <c r="A1" s="252" t="inlineStr">
         <is>
           <t>CONFIG  -  every parameter in its own labelled cell</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="144">
-      <c r="A2" s="257" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="142">
+      <c r="A2" s="253" t="inlineStr">
         <is>
           <t>LEGEND:  yellow / blue = EDIT THESE.  black = formula, do not edit.  A changed value takes effect on the NEXT TIMER TICK - no restart, no VBA edit.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="144">
-      <c r="A3" s="233" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="142">
+      <c r="A3" s="229" t="inlineStr">
         <is>
           <t>Exception: LOOKBACK_MIN redefines the window, so stored history is re-evaluated against the new width on the next stats refresh and the warm-up gates re-apply.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="144">
-      <c r="A4" s="233" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="142">
+      <c r="A4" s="229" t="inlineStr">
         <is>
           <t>VBA finds a parameter by matching column A exactly, so you may insert or reorder rows freely - but never rename a parameter in column A.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="144">
-      <c r="A5" s="257" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="142">
+      <c r="A5" s="253" t="inlineStr">
         <is>
           <t>FOUR DECOUPLED RATES:  CAPTURE_MS (poll for a changed quote)  &gt;  STORE_MIN_INTERVAL_MS (what reaches the window)  &gt;  PRICE_REFRESH_MS (what repaints)  &gt;  STATS_REFRESH_MIN (when mean and sigma are republished).  Capturing fast buys alert latency, not a better sigma.</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="7" ht="15" customHeight="1" s="144">
-      <c r="A7" s="258" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="142">
+      <c r="A7" s="254" t="inlineStr">
         <is>
           <t>ENGINE  /  SAMPLING</t>
         </is>
       </c>
-      <c r="B7" s="258" t="n"/>
-      <c r="C7" s="258" t="n"/>
-      <c r="D7" s="258" t="n"/>
-      <c r="E7" s="258" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="144">
-      <c r="A8" s="259" t="inlineStr">
+      <c r="B7" s="254" t="n"/>
+      <c r="C7" s="254" t="n"/>
+      <c r="D7" s="254" t="n"/>
+      <c r="E7" s="254" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="142">
+      <c r="A8" s="255" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B8" s="259" t="inlineStr">
+      <c r="B8" s="255" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C8" s="259" t="inlineStr">
+      <c r="C8" s="255" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D8" s="259" t="inlineStr">
+      <c r="D8" s="255" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E8" s="259" t="inlineStr">
+      <c r="E8" s="255" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="144">
-      <c r="A9" s="250" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="142">
+      <c r="A9" s="246" t="inlineStr">
         <is>
           <t>CAPTURE_MS</t>
         </is>
       </c>
-      <c r="B9" s="260" t="n">
+      <c r="B9" s="256" t="n">
         <v>100</v>
       </c>
-      <c r="C9" s="239" t="n">
+      <c r="C9" s="235" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="239" t="inlineStr">
+      <c r="D9" s="235" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E9" s="261" t="inlineStr">
+      <c r="E9" s="257" t="inlineStr">
         <is>
           <t>RATE 1 of 4. How often the feed is POLLED for a changed quote. Drives latency to the chime, NOT sigma - after dedupe the window holds quote changes, not poll ticks. Sub-second needs the user32 timer; at 1000+ the module falls back to Application.OnTime.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="144">
-      <c r="A10" s="250" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="142">
+      <c r="A10" s="246" t="inlineStr">
         <is>
           <t>STORE_MIN_INTERVAL_MS</t>
         </is>
       </c>
-      <c r="B10" s="260" t="n">
+      <c r="B10" s="256" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="239" t="n">
+      <c r="C10" s="235" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="239" t="inlineStr">
+      <c r="D10" s="235" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E10" s="261" t="inlineStr">
+      <c r="E10" s="257" t="inlineStr">
         <is>
           <t>RATE 2 of 4. Minimum spacing between STORED samples. 0 = full fidelity. Leave it at 0 for the first week or two to characterise the microstructure, then set 250-1000: subsampling a mean-reverting level series is unbiased, so it is 3-10x less memory for the same mean and sigma.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="144">
-      <c r="A11" s="250" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="142">
+      <c r="A11" s="246" t="inlineStr">
         <is>
           <t>PRICE_REFRESH_MS</t>
         </is>
       </c>
-      <c r="B11" s="260" t="n">
+      <c r="B11" s="256" t="n">
         <v>500</v>
       </c>
-      <c r="C11" s="239" t="n">
+      <c r="C11" s="235" t="n">
         <v>500</v>
       </c>
-      <c r="D11" s="239" t="inlineStr">
+      <c r="D11" s="235" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E11" s="261" t="inlineStr">
+      <c r="E11" s="257" t="inlineStr">
         <is>
           <t>RATE 3 of 4. How often the display may repaint. Independent of capture and of storage - a number showing more digits than the market moves in will appear to change constantly.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="144">
-      <c r="A12" s="250" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="142">
+      <c r="A12" s="246" t="inlineStr">
         <is>
           <t>CONFIG_REFRESH_MS</t>
         </is>
       </c>
-      <c r="B12" s="260" t="n">
+      <c r="B12" s="256" t="n">
         <v>1000</v>
       </c>
-      <c r="C12" s="239" t="n">
+      <c r="C12" s="235" t="n">
         <v>1000</v>
       </c>
-      <c r="D12" s="239" t="inlineStr">
+      <c r="D12" s="235" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E12" s="261" t="inlineStr">
+      <c r="E12" s="257" t="inlineStr">
         <is>
           <t>How often this sheet is re-read. A value changed here takes effect within this long - no restart, no VBA edit.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="144">
-      <c r="A13" s="250" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="142">
+      <c r="A13" s="246" t="inlineStr">
         <is>
           <t>RTD_THROTTLE_MS</t>
         </is>
       </c>
-      <c r="B13" s="260" t="n">
+      <c r="B13" s="256" t="n">
         <v>100</v>
       </c>
-      <c r="C13" s="239" t="n">
+      <c r="C13" s="235" t="n">
         <v>100</v>
       </c>
-      <c r="D13" s="239" t="inlineStr">
+      <c r="D13" s="235" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E13" s="261" t="inlineStr">
+      <c r="E13" s="257" t="inlineStr">
         <is>
           <t>Application.RTD.ThrottleInterval set on start. Match it to CAPTURE_MS. Excel's default is 2000.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="144">
-      <c r="A14" s="250" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="142">
+      <c r="A14" s="246" t="inlineStr">
         <is>
           <t>WATCHDOG_SEC</t>
         </is>
       </c>
-      <c r="B14" s="260" t="n">
+      <c r="B14" s="256" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="239" t="n">
+      <c r="C14" s="235" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="239" t="inlineStr">
+      <c r="D14" s="235" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E14" s="261" t="inlineStr">
+      <c r="E14" s="257" t="inlineStr">
         <is>
           <t>Application.OnTime watchdog. Re-arms the high-resolution timer if Excel killed it (a modal dialog will) and picks up a changed CAPTURE_MS.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="144">
-      <c r="A15" s="250" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="142">
+      <c r="A15" s="246" t="inlineStr">
         <is>
           <t>STALE_SEC</t>
         </is>
       </c>
-      <c r="B15" s="260" t="n">
+      <c r="B15" s="256" t="n">
         <v>15</v>
       </c>
-      <c r="C15" s="239" t="n">
+      <c r="C15" s="235" t="n">
         <v>15</v>
       </c>
-      <c r="D15" s="239" t="inlineStr">
+      <c r="D15" s="235" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E15" s="261" t="inlineStr">
+      <c r="E15" s="257" t="inlineStr">
         <is>
           <t>No new quote id for this long =&gt; feed marked STALE and alerts go silent.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="144">
-      <c r="A16" s="250" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="142">
+      <c r="A16" s="246" t="inlineStr">
         <is>
           <t>FLUSH_SEC</t>
         </is>
       </c>
-      <c r="B16" s="260" t="n">
+      <c r="B16" s="256" t="n">
         <v>60</v>
       </c>
-      <c r="C16" s="239" t="n">
+      <c r="C16" s="235" t="n">
         <v>60</v>
       </c>
-      <c r="D16" s="239" t="inlineStr">
+      <c r="D16" s="235" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E16" s="261" t="inlineStr">
+      <c r="E16" s="257" t="inlineStr">
         <is>
           <t>How often the recovery snapshot is written to the hidden Buffer sheet.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="144">
-      <c r="A17" s="250" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="142">
+      <c r="A17" s="246" t="inlineStr">
         <is>
           <t>FLUSH_DECIMATE_MS</t>
         </is>
       </c>
-      <c r="B17" s="260" t="n">
+      <c r="B17" s="256" t="n">
         <v>1000</v>
       </c>
-      <c r="C17" s="239" t="n">
+      <c r="C17" s="235" t="n">
         <v>1000</v>
       </c>
-      <c r="D17" s="239" t="inlineStr">
+      <c r="D17" s="235" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E17" s="261" t="inlineStr">
+      <c r="E17" s="257" t="inlineStr">
         <is>
           <t>The recovery snapshot is decimated to this spacing. Unbiased for mean and sigma, and it keeps a 120-minute window near 7,200 rows instead of tens of thousands.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="144">
-      <c r="A18" s="250" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="142">
+      <c r="A18" s="246" t="inlineStr">
         <is>
           <t>BUFFER_CAPACITY</t>
         </is>
       </c>
-      <c r="B18" s="260" t="n">
+      <c r="B18" s="256" t="n">
         <v>80000</v>
       </c>
-      <c r="C18" s="239" t="n">
+      <c r="C18" s="235" t="n">
         <v>80000</v>
       </c>
-      <c r="D18" s="239" t="inlineStr">
+      <c r="D18" s="235" t="inlineStr">
         <is>
           <t>samples</t>
         </is>
       </c>
-      <c r="E18" s="261" t="inlineStr">
+      <c r="E18" s="257" t="inlineStr">
         <is>
           <t>Circular-buffer capacity per spread. 4 spreads x 80,000 x 16 bytes is about 5 MB of VBA array, held in memory, not in cells.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="144">
-      <c r="A19" s="250" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="142">
+      <c r="A19" s="246" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_ENABLED</t>
         </is>
       </c>
-      <c r="B19" s="260" t="b">
+      <c r="B19" s="256" t="b">
         <v>1</v>
       </c>
-      <c r="C19" s="239" t="b">
+      <c r="C19" s="235" t="b">
         <v>1</v>
       </c>
-      <c r="D19" s="239" t="inlineStr">
+      <c r="D19" s="235" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E19" s="261" t="inlineStr">
+      <c r="E19" s="257" t="inlineStr">
         <is>
           <t>Write every CHANGED quote to a CSV on disk. This is the one chance to characterise the spread's microstructure and to verify that coarser storage loses nothing real. Turn it off once STORE_MIN_INTERVAL_MS is set.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="144">
-      <c r="A20" s="250" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="142">
+      <c r="A20" s="246" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_PATH</t>
         </is>
       </c>
-      <c r="B20" s="262" t="n"/>
-      <c r="C20" s="239" t="n"/>
-      <c r="D20" s="239" t="inlineStr">
+      <c r="B20" s="258" t="n"/>
+      <c r="C20" s="235" t="n"/>
+      <c r="D20" s="235" t="inlineStr">
         <is>
           <t>folder</t>
         </is>
       </c>
-      <c r="E20" s="261" t="inlineStr">
+      <c r="E20" s="257" t="inlineStr">
         <is>
           <t>Folder for the tick CSVs. Blank = a 'ticks' folder beside the workbook. One file per spread per day.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="144">
-      <c r="A21" s="250" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="142">
+      <c r="A21" s="246" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_BATCH</t>
         </is>
       </c>
-      <c r="B21" s="260" t="n">
+      <c r="B21" s="256" t="n">
         <v>500</v>
       </c>
-      <c r="C21" s="239" t="n">
+      <c r="C21" s="235" t="n">
         <v>500</v>
       </c>
-      <c r="D21" s="239" t="inlineStr">
+      <c r="D21" s="235" t="inlineStr">
         <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="E21" s="261" t="inlineStr">
+      <c r="E21" s="257" t="inlineStr">
         <is>
           <t>Lines buffered in memory before a file write, so archiving never stalls the capture timer.</t>
         </is>
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="15" customHeight="1" s="144">
-      <c r="A23" s="258" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="142">
+      <c r="A23" s="254" t="inlineStr">
         <is>
           <t>WINDOW  /  STATISTICS</t>
         </is>
       </c>
-      <c r="B23" s="258" t="n"/>
-      <c r="C23" s="258" t="n"/>
-      <c r="D23" s="258" t="n"/>
-      <c r="E23" s="258" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="144">
-      <c r="A24" s="259" t="inlineStr">
+      <c r="B23" s="254" t="n"/>
+      <c r="C23" s="254" t="n"/>
+      <c r="D23" s="254" t="n"/>
+      <c r="E23" s="254" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="142">
+      <c r="A24" s="255" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B24" s="259" t="inlineStr">
+      <c r="B24" s="255" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C24" s="259" t="inlineStr">
+      <c r="C24" s="255" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D24" s="259" t="inlineStr">
+      <c r="D24" s="255" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E24" s="259" t="inlineStr">
+      <c r="E24" s="255" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="144">
-      <c r="A25" s="250" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="142">
+      <c r="A25" s="246" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="B25" s="260" t="n">
+      <c r="B25" s="256" t="n">
         <v>120</v>
       </c>
-      <c r="C25" s="239" t="n">
+      <c r="C25" s="235" t="n">
         <v>120</v>
       </c>
-      <c r="D25" s="239" t="inlineStr">
+      <c r="D25" s="235" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E25" s="261" t="inlineStr">
+      <c r="E25" s="257" t="inlineStr">
         <is>
           <t>Rolling window width (90 or 120). Changing it re-evaluates stored history on the next stats refresh and re-applies the warm-up gates.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="144">
-      <c r="A26" s="250" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="142">
+      <c r="A26" s="246" t="inlineStr">
         <is>
           <t>STATS_REFRESH_MIN</t>
         </is>
       </c>
-      <c r="B26" s="260" t="n">
+      <c r="B26" s="256" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="239" t="n">
+      <c r="C26" s="235" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="239" t="inlineStr">
+      <c r="D26" s="235" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E26" s="261" t="inlineStr">
+      <c r="E26" s="257" t="inlineStr">
         <is>
           <t>How often mean/sigma are recomputed and re-published. Held FROZEN in between; live z is measured against the frozen values.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="144">
-      <c r="A27" s="250" t="inlineStr">
+    <row r="27" ht="15" customHeight="1" s="142">
+      <c r="A27" s="246" t="inlineStr">
         <is>
           <t>MIN_SAMPLES</t>
         </is>
       </c>
-      <c r="B27" s="260" t="n">
+      <c r="B27" s="256" t="n">
         <v>300</v>
       </c>
-      <c r="C27" s="239" t="n">
+      <c r="C27" s="235" t="n">
         <v>300</v>
       </c>
-      <c r="D27" s="239" t="inlineStr">
+      <c r="D27" s="235" t="inlineStr">
         <is>
           <t>quotes</t>
         </is>
       </c>
-      <c r="E27" s="261" t="inlineStr">
+      <c r="E27" s="257" t="inlineStr">
         <is>
           <t>Warm-up gate 1. Quotes needed before any z is shown.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="144">
-      <c r="A28" s="250" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="142">
+      <c r="A28" s="246" t="inlineStr">
         <is>
           <t>MIN_HISTORY_MIN</t>
         </is>
       </c>
-      <c r="B28" s="260" t="n">
+      <c r="B28" s="256" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="239" t="n">
+      <c r="C28" s="235" t="n">
         <v>120</v>
       </c>
-      <c r="D28" s="239" t="inlineStr">
+      <c r="D28" s="235" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E28" s="261" t="inlineStr">
+      <c r="E28" s="257" t="inlineStr">
         <is>
           <t>Warm-up gate 2. Window span needed before any z is shown. BOTH gates must pass. MUST BE LESS THAN LOOKBACK_MIN: eviction drops samples older than the lookback, so the span approaches it but never reaches it, and a value at or above LOOKBACK_MIN would never be satisfied. Anything above 98% of LOOKBACK_MIN is clamped to that, and the clamp is noted once in the Log.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="144">
-      <c r="A29" s="250" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="142">
+      <c r="A29" s="246" t="inlineStr">
         <is>
           <t>MIN_SIGMA</t>
         </is>
       </c>
-      <c r="B29" s="260" t="n">
+      <c r="B29" s="256" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="239" t="n">
+      <c r="C29" s="235" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="239" t="inlineStr">
+      <c r="D29" s="235" t="inlineStr">
         <is>
           <t>spread</t>
         </is>
       </c>
-      <c r="E29" s="261" t="inlineStr">
+      <c r="E29" s="257" t="inlineStr">
         <is>
           <t>Sigma floor. Below this the window is degenerate and NO z is shown. Set once sigma has actually been measured.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="144">
-      <c r="A30" s="250" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="142">
+      <c r="A30" s="246" t="inlineStr">
         <is>
           <t>MAX_ABS_Z</t>
         </is>
       </c>
-      <c r="B30" s="260" t="n">
+      <c r="B30" s="256" t="n">
         <v>25</v>
       </c>
-      <c r="C30" s="239" t="n">
+      <c r="C30" s="235" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="239" t="inlineStr">
+      <c r="D30" s="235" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E30" s="261" t="inlineStr">
+      <c r="E30" s="257" t="inlineStr">
         <is>
           <t>Absurd-z guard. Above this, show 'no usable z' rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="31"/>
-    <row r="32" ht="15" customHeight="1" s="144">
-      <c r="A32" s="258" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="142">
+      <c r="A32" s="254" t="inlineStr">
         <is>
           <t>SIGNAL THRESHOLDS</t>
         </is>
       </c>
-      <c r="B32" s="258" t="n"/>
-      <c r="C32" s="258" t="n"/>
-      <c r="D32" s="258" t="n"/>
-      <c r="E32" s="258" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="144">
-      <c r="A33" s="259" t="inlineStr">
+      <c r="B32" s="254" t="n"/>
+      <c r="C32" s="254" t="n"/>
+      <c r="D32" s="254" t="n"/>
+      <c r="E32" s="254" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="142">
+      <c r="A33" s="255" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B33" s="259" t="inlineStr">
+      <c r="B33" s="255" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C33" s="259" t="inlineStr">
+      <c r="C33" s="255" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D33" s="259" t="inlineStr">
+      <c r="D33" s="255" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E33" s="259" t="inlineStr">
+      <c r="E33" s="255" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="144">
-      <c r="A34" s="250" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="142">
+      <c r="A34" s="246" t="inlineStr">
         <is>
           <t>ENTRY_Z</t>
         </is>
       </c>
-      <c r="B34" s="263" t="n">
+      <c r="B34" s="259" t="n">
         <v>2.5</v>
       </c>
-      <c r="C34" s="264" t="n">
+      <c r="C34" s="260" t="n">
         <v>2.5</v>
       </c>
-      <c r="D34" s="239" t="inlineStr">
+      <c r="D34" s="235" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E34" s="261" t="inlineStr">
+      <c r="E34" s="257" t="inlineStr">
         <is>
           <t>Highlight and chime at or above this |z|. 2.0 and 2.5 are both reasonable; 2.0 fires more often and needs a larger sigma to stay worth trading.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="144">
-      <c r="A35" s="250" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="142">
+      <c r="A35" s="246" t="inlineStr">
         <is>
           <t>MAX_ENTRY_Z</t>
         </is>
       </c>
-      <c r="B35" s="263" t="n">
+      <c r="B35" s="259" t="n">
         <v>4.5</v>
       </c>
-      <c r="C35" s="264" t="n">
+      <c r="C35" s="260" t="n">
         <v>4.5</v>
       </c>
-      <c r="D35" s="239" t="inlineStr">
+      <c r="D35" s="235" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E35" s="261" t="inlineStr">
+      <c r="E35" s="257" t="inlineStr">
         <is>
           <t>Entry CEILING. At or above this, do NOT highlight - that is a momentum spike, not a reversion setup. Keep the band at least 1 sigma wide.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="144">
-      <c r="A36" s="250" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="142">
+      <c r="A36" s="246" t="inlineStr">
         <is>
           <t>THIN_FEED_QPM</t>
         </is>
       </c>
-      <c r="B36" s="260" t="n">
+      <c r="B36" s="256" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="239" t="n">
+      <c r="C36" s="235" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="239" t="inlineStr">
+      <c r="D36" s="235" t="inlineStr">
         <is>
           <t>q/min</t>
         </is>
       </c>
-      <c r="E36" s="261" t="inlineStr">
+      <c r="E36" s="257" t="inlineStr">
         <is>
           <t>Feed rate at or below which the quotes/min display turns amber.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="144">
-      <c r="A37" s="250" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="142">
+      <c r="A37" s="246" t="inlineStr">
         <is>
           <t>SPREAD_QUOTE_CONVENTION</t>
         </is>
       </c>
-      <c r="B37" s="262" t="inlineStr">
+      <c r="B37" s="258" t="inlineStr">
         <is>
           <t>CROSSING</t>
         </is>
       </c>
-      <c r="C37" s="239" t="inlineStr">
+      <c r="C37" s="235" t="inlineStr">
         <is>
           <t>CROSSING</t>
         </is>
       </c>
-      <c r="D37" s="239" t="inlineStr">
+      <c r="D37" s="235" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E37" s="261" t="inlineStr">
+      <c r="E37" s="257" t="inlineStr">
         <is>
           <t>How the spread rows on Dashboard quote Bid and Ask. CROSSING: sell LegB at the bid and buy LegA at the ask, mirrored for the ask - the Gap is then the true cost of crossing and is always positive. SAME_SIDE: bid-minus-bid and ask-minus-ask, as the original sheet's rows 9 computed. Under SAME_SIDE the Gap is a DIFFERENCE of gaps, which understates the crossing cost and can go negative.</t>
         </is>
       </c>
     </row>
     <row r="38"/>
-    <row r="39" ht="15" customHeight="1" s="144">
-      <c r="A39" s="258" t="inlineStr">
+    <row r="39" ht="15" customHeight="1" s="142">
+      <c r="A39" s="254" t="inlineStr">
         <is>
           <t>SIZING  /  COSTS</t>
         </is>
       </c>
-      <c r="B39" s="258" t="n"/>
-      <c r="C39" s="258" t="n"/>
-      <c r="D39" s="258" t="n"/>
-      <c r="E39" s="258" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="144">
-      <c r="A40" s="259" t="inlineStr">
+      <c r="B39" s="254" t="n"/>
+      <c r="C39" s="254" t="n"/>
+      <c r="D39" s="254" t="n"/>
+      <c r="E39" s="254" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="142">
+      <c r="A40" s="255" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B40" s="259" t="inlineStr">
+      <c r="B40" s="255" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C40" s="259" t="inlineStr">
+      <c r="C40" s="255" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D40" s="259" t="inlineStr">
+      <c r="D40" s="255" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E40" s="259" t="inlineStr">
+      <c r="E40" s="255" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="144">
-      <c r="A41" s="250" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="142">
+      <c r="A41" s="246" t="inlineStr">
         <is>
           <t>LOTS</t>
         </is>
       </c>
-      <c r="B41" s="260" t="n">
+      <c r="B41" s="256" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="239" t="n">
+      <c r="C41" s="235" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="239" t="inlineStr">
+      <c r="D41" s="235" t="inlineStr">
         <is>
           <t>lots</t>
         </is>
       </c>
-      <c r="E41" s="261" t="inlineStr">
+      <c r="E41" s="257" t="inlineStr">
         <is>
           <t>Contracts per leg, for the cost and take-profit maths.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="144">
-      <c r="A42" s="250" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="142">
+      <c r="A42" s="246" t="inlineStr">
         <is>
           <t>TP_MODE</t>
         </is>
       </c>
-      <c r="B42" s="262" t="inlineStr">
+      <c r="B42" s="258" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL</t>
         </is>
       </c>
-      <c r="C42" s="239" t="inlineStr">
+      <c r="C42" s="235" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL</t>
         </is>
       </c>
-      <c r="D42" s="239" t="inlineStr">
+      <c r="D42" s="235" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E42" s="261" t="inlineStr">
+      <c r="E42" s="257" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL: Take Profit = Entry + Costs + (WIN_PCT x Notional). TARGET_USD: the older rule, Take Profit = Entry + Costs + TARGET_NET_USD.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="144">
-      <c r="A43" s="250" t="inlineStr">
+    <row r="43" ht="15" customHeight="1" s="142">
+      <c r="A43" s="246" t="inlineStr">
         <is>
           <t>WIN_PCT</t>
         </is>
       </c>
-      <c r="B43" s="263" t="n">
+      <c r="B43" s="259" t="n">
         <v>0.01</v>
       </c>
-      <c r="C43" s="264" t="n">
+      <c r="C43" s="260" t="n">
         <v>0.01</v>
       </c>
-      <c r="D43" s="239" t="inlineStr">
+      <c r="D43" s="235" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="E43" s="261" t="inlineStr">
+      <c r="E43" s="257" t="inlineStr">
         <is>
           <t>Percentage win, as a FRACTION - 0.01 is 1%, 0.02 is 2%. Used only when TP_MODE = PCT_NOTIONAL.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="144">
-      <c r="A44" s="250" t="inlineStr">
+    <row r="44" ht="15" customHeight="1" s="142">
+      <c r="A44" s="246" t="inlineStr">
         <is>
           <t>NOTIONAL_BASIS</t>
         </is>
       </c>
-      <c r="B44" s="262" t="inlineStr">
+      <c r="B44" s="258" t="inlineStr">
         <is>
           <t>SPREAD_VALUE</t>
         </is>
       </c>
-      <c r="C44" s="239" t="inlineStr">
+      <c r="C44" s="235" t="inlineStr">
         <is>
           <t>SPREAD_VALUE</t>
         </is>
       </c>
-      <c r="D44" s="239" t="inlineStr">
+      <c r="D44" s="235" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E44" s="261" t="inlineStr">
+      <c r="E44" s="257" t="inlineStr">
         <is>
           <t>What WIN_PCT is taken OF. SPREAD_VALUE = |spread| x USD/pt x LOTS. ONE_LEG = the crude leg's full contract value. BOTH_LEGS = both legs' contract value added. These differ by roughly 10x - read the note below the table before changing it.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="144">
-      <c r="A45" s="250" t="inlineStr">
+    <row r="45" ht="15" customHeight="1" s="142">
+      <c r="A45" s="246" t="inlineStr">
+        <is>
+          <t>TP_ENTRY_BASIS</t>
+        </is>
+      </c>
+      <c r="B45" s="258" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="C45" s="235" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D45" s="235" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E45" s="257" t="inlineStr">
+        <is>
+          <t>Which price the take-profit is measured from. BID: always the bid, the price you sell at - exact for a High-to-Low trade, optimistic by the spread's own gap on a Low-to-High one. TOUCH: prices each direction at the side it really trades on (bid when selling, ask when buying).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="142">
+      <c r="A46" s="246" t="inlineStr">
         <is>
           <t>TARGET_NET_USD</t>
         </is>
       </c>
-      <c r="B45" s="260" t="n">
+      <c r="B46" s="256" t="n">
         <v>150</v>
       </c>
-      <c r="C45" s="239" t="n">
+      <c r="C46" s="235" t="n">
         <v>150</v>
       </c>
-      <c r="D45" s="239" t="inlineStr">
+      <c r="D46" s="235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E45" s="261" t="inlineStr">
+      <c r="E46" s="257" t="inlineStr">
         <is>
           <t>Desired profit AFTER all costs. Used only when TP_MODE = TARGET_USD.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="144">
-      <c r="A46" s="250" t="inlineStr">
+    <row r="47" ht="15" customHeight="1" s="142">
+      <c r="A47" s="246" t="inlineStr">
         <is>
           <t>EDGE_MULTIPLE</t>
         </is>
       </c>
-      <c r="B46" s="263" t="n">
+      <c r="B47" s="259" t="n">
         <v>1.5</v>
       </c>
-      <c r="C46" s="264" t="n">
+      <c r="C47" s="260" t="n">
         <v>1.5</v>
       </c>
-      <c r="D46" s="239" t="inlineStr">
+      <c r="D47" s="235" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E46" s="261" t="inlineStr">
+      <c r="E47" s="257" t="inlineStr">
         <is>
           <t>Expected capture must clear the round trip by this multiple.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="144">
-      <c r="A47" s="250" t="inlineStr">
+    <row r="48" ht="15" customHeight="1" s="142">
+      <c r="A48" s="246" t="inlineStr">
         <is>
           <t>RATE_ORIENT_PER_SIDE</t>
         </is>
       </c>
-      <c r="B47" s="263" t="n">
+      <c r="B48" s="259" t="n">
         <v>0.35</v>
       </c>
-      <c r="C47" s="264" t="n">
+      <c r="C48" s="260" t="n">
         <v>0.35</v>
       </c>
-      <c r="D47" s="239" t="inlineStr">
+      <c r="D48" s="235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E47" s="261" t="inlineStr">
+      <c r="E48" s="257" t="inlineStr">
         <is>
           <t>Orient clearing + execution, per contract per side. Source: Orient rate card 2026-08-21, Ver.26.8.17.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="144">
-      <c r="A48" s="250" t="inlineStr">
+    <row r="49" ht="15" customHeight="1" s="142">
+      <c r="A49" s="246" t="inlineStr">
         <is>
           <t>RATE_FIX_PER_SIDE</t>
         </is>
       </c>
-      <c r="B48" s="263" t="n">
+      <c r="B49" s="259" t="n">
         <v>0.06</v>
       </c>
-      <c r="C48" s="264" t="n">
+      <c r="C49" s="260" t="n">
         <v>0.06</v>
       </c>
-      <c r="D48" s="239" t="inlineStr">
+      <c r="D49" s="235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E48" s="261" t="inlineStr">
+      <c r="E49" s="257" t="inlineStr">
         <is>
           <t>FIX / platform transaction fee, per contract per side. Same rate card.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="144">
-      <c r="A49" s="250" t="inlineStr">
+    <row r="50" ht="15" customHeight="1" s="142">
+      <c r="A50" s="246" t="inlineStr">
         <is>
           <t>RATE_CME_PER_SIDE</t>
         </is>
       </c>
-      <c r="B49" s="263" t="n">
+      <c r="B50" s="259" t="n">
         <v>1.5</v>
       </c>
-      <c r="C49" s="264" t="n">
+      <c r="C50" s="260" t="n">
         <v>1.5</v>
       </c>
-      <c r="D49" s="239" t="inlineStr">
+      <c r="D50" s="235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E49" s="261" t="inlineStr">
+      <c r="E50" s="257" t="inlineStr">
         <is>
           <t>CME exchange + clearing, per contract per side. Same rate card.</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51" ht="15" customHeight="1" s="144">
-      <c r="A51" s="258" t="inlineStr">
+    <row r="51"/>
+    <row r="52" ht="15" customHeight="1" s="142">
+      <c r="A52" s="254" t="inlineStr">
         <is>
           <t>AUDIBLE ALERT</t>
         </is>
       </c>
-      <c r="B51" s="258" t="n"/>
-      <c r="C51" s="258" t="n"/>
-      <c r="D51" s="258" t="n"/>
-      <c r="E51" s="258" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="144">
-      <c r="A52" s="259" t="inlineStr">
+      <c r="B52" s="254" t="n"/>
+      <c r="C52" s="254" t="n"/>
+      <c r="D52" s="254" t="n"/>
+      <c r="E52" s="254" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="142">
+      <c r="A53" s="255" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B52" s="259" t="inlineStr">
+      <c r="B53" s="255" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C52" s="259" t="inlineStr">
+      <c r="C53" s="255" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D52" s="259" t="inlineStr">
+      <c r="D53" s="255" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E52" s="259" t="inlineStr">
+      <c r="E53" s="255" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="144">
-      <c r="A53" s="250" t="inlineStr">
+    <row r="54" ht="15" customHeight="1" s="142">
+      <c r="A54" s="246" t="inlineStr">
         <is>
           <t>ALERT_ENABLED</t>
         </is>
       </c>
-      <c r="B53" s="260" t="b">
+      <c r="B54" s="256" t="b">
         <v>1</v>
       </c>
-      <c r="C53" s="239" t="b">
+      <c r="C54" s="235" t="b">
         <v>1</v>
       </c>
-      <c r="D53" s="239" t="inlineStr">
+      <c r="D54" s="235" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E53" s="261" t="inlineStr">
+      <c r="E54" s="257" t="inlineStr">
         <is>
           <t>MASTER MUTE. FALSE silences every sound.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="144">
-      <c r="A54" s="250" t="inlineStr">
+    <row r="55" ht="15" customHeight="1" s="142">
+      <c r="A55" s="246" t="inlineStr">
         <is>
           <t>ALERT_SOUND_PATH</t>
         </is>
       </c>
-      <c r="B54" s="262" t="inlineStr">
+      <c r="B55" s="258" t="inlineStr">
         <is>
           <t>C:\Windows\Media\chimes.wav</t>
         </is>
       </c>
-      <c r="C54" s="239" t="inlineStr">
+      <c r="C55" s="235" t="inlineStr">
         <is>
           <t>C:\Windows\Media\chimes.wav</t>
         </is>
       </c>
-      <c r="D54" s="239" t="inlineStr">
+      <c r="D55" s="235" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E54" s="261" t="inlineStr">
+      <c r="E55" s="257" t="inlineStr">
         <is>
           <t>Single short 'ting' played on an entry-band crossing.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="144">
-      <c r="A55" s="250" t="inlineStr">
+    <row r="56" ht="15" customHeight="1" s="142">
+      <c r="A56" s="246" t="inlineStr">
         <is>
           <t>ALERT_SOUND_PATH_CEILING</t>
         </is>
       </c>
-      <c r="B55" s="262" t="inlineStr">
+      <c r="B56" s="258" t="inlineStr">
         <is>
           <t>C:\Windows\Media\notify.wav</t>
         </is>
       </c>
-      <c r="C55" s="239" t="inlineStr">
+      <c r="C56" s="235" t="inlineStr">
         <is>
           <t>C:\Windows\Media\notify.wav</t>
         </is>
       </c>
-      <c r="D55" s="239" t="inlineStr">
+      <c r="D56" s="235" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E55" s="261" t="inlineStr">
+      <c r="E56" s="257" t="inlineStr">
         <is>
           <t>Distinct tone for crossing MAX_ENTRY_Z. That is 'stand down', not 'get in'.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="144">
-      <c r="A56" s="250" t="inlineStr">
+    <row r="57" ht="15" customHeight="1" s="142">
+      <c r="A57" s="246" t="inlineStr">
         <is>
           <t>ALERT_REARM_MARGIN</t>
         </is>
       </c>
-      <c r="B56" s="263" t="n">
+      <c r="B57" s="259" t="n">
         <v>0.25</v>
       </c>
-      <c r="C56" s="264" t="n">
+      <c r="C57" s="260" t="n">
         <v>0.25</v>
       </c>
-      <c r="D56" s="239" t="inlineStr">
+      <c r="D57" s="235" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E56" s="261" t="inlineStr">
+      <c r="E57" s="257" t="inlineStr">
         <is>
           <t>Hysteresis. Do not re-arm until |z| falls back below ENTRY_Z - this margin.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="144">
-      <c r="A57" s="250" t="inlineStr">
+    <row r="58" ht="15" customHeight="1" s="142">
+      <c r="A58" s="246" t="inlineStr">
         <is>
           <t>ALERT_COOLDOWN_SEC</t>
         </is>
       </c>
-      <c r="B57" s="260" t="n">
+      <c r="B58" s="256" t="n">
         <v>60</v>
       </c>
-      <c r="C57" s="239" t="n">
+      <c r="C58" s="235" t="n">
         <v>60</v>
       </c>
-      <c r="D57" s="239" t="inlineStr">
+      <c r="D58" s="235" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E57" s="261" t="inlineStr">
+      <c r="E58" s="257" t="inlineStr">
         <is>
           <t>Minimum seconds between alerts for the same spread.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="144">
-      <c r="A58" s="250" t="inlineStr">
+    <row r="59" ht="15" customHeight="1" s="142">
+      <c r="A59" s="246" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES</t>
         </is>
       </c>
-      <c r="B58" s="260" t="b">
+      <c r="B59" s="256" t="b">
         <v>0</v>
       </c>
-      <c r="C58" s="239" t="b">
+      <c r="C59" s="235" t="b">
         <v>0</v>
       </c>
-      <c r="D58" s="239" t="inlineStr">
+      <c r="D59" s="235" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E58" s="261" t="inlineStr">
+      <c r="E59" s="257" t="inlineStr">
         <is>
           <t>FALSE = the chime follows ENTRY_Z alone. TRUE = also stay silent when the edge filter fails, on the argument that a sound for a trade you should not take trains you to ignore the sound. Ships FALSE by request; the edge verdict is still shown on Detail.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="144">
-      <c r="A59" s="250" t="inlineStr">
+    <row r="60" ht="15" customHeight="1" s="142">
+      <c r="A60" s="246" t="inlineStr">
         <is>
           <t>ALERT_SPEAK</t>
         </is>
       </c>
-      <c r="B59" s="260" t="b">
+      <c r="B60" s="256" t="b">
         <v>0</v>
       </c>
-      <c r="C59" s="239" t="b">
+      <c r="C60" s="235" t="b">
         <v>0</v>
       </c>
-      <c r="D59" s="239" t="inlineStr">
+      <c r="D60" s="235" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E59" s="261" t="inlineStr">
+      <c r="E60" s="257" t="inlineStr">
         <is>
           <t>TRUE also speaks the spread name (Application.Speech). Useful when watching four at once.</t>
         </is>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61" ht="15" customHeight="1" s="144">
-      <c r="A61" s="258" t="inlineStr">
+    <row r="61"/>
+    <row r="62" ht="15" customHeight="1" s="142">
+      <c r="A62" s="254" t="inlineStr">
         <is>
           <t>PERSISTENCE  /  LOGGING</t>
         </is>
       </c>
-      <c r="B61" s="258" t="n"/>
-      <c r="C61" s="258" t="n"/>
-      <c r="D61" s="258" t="n"/>
-      <c r="E61" s="258" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="144">
-      <c r="A62" s="259" t="inlineStr">
+      <c r="B62" s="254" t="n"/>
+      <c r="C62" s="254" t="n"/>
+      <c r="D62" s="254" t="n"/>
+      <c r="E62" s="254" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="142">
+      <c r="A63" s="255" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B62" s="259" t="inlineStr">
+      <c r="B63" s="255" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C62" s="259" t="inlineStr">
+      <c r="C63" s="255" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D62" s="259" t="inlineStr">
+      <c r="D63" s="255" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E62" s="259" t="inlineStr">
+      <c r="E63" s="255" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="144">
-      <c r="A63" s="250" t="inlineStr">
+    <row r="64" ht="15" customHeight="1" s="142">
+      <c r="A64" s="246" t="inlineStr">
         <is>
           <t>WARM_START_ENABLED</t>
         </is>
       </c>
-      <c r="B63" s="260" t="b">
+      <c r="B64" s="256" t="b">
         <v>1</v>
       </c>
-      <c r="C63" s="239" t="b">
+      <c r="C64" s="235" t="b">
         <v>1</v>
       </c>
-      <c r="D63" s="239" t="inlineStr">
+      <c r="D64" s="235" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E63" s="261" t="inlineStr">
+      <c r="E64" s="257" t="inlineStr">
         <is>
           <t>On open, reload the flushed buffer so a restart does not cost another two hours of warm-up.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="144">
-      <c r="A64" s="250" t="inlineStr">
+    <row r="65" ht="15" customHeight="1" s="142">
+      <c r="A65" s="246" t="inlineStr">
         <is>
           <t>WARM_START_MAX_AGE_MIN</t>
         </is>
       </c>
-      <c r="B64" s="260" t="n">
+      <c r="B65" s="256" t="n">
         <v>180</v>
       </c>
-      <c r="C64" s="239" t="n">
+      <c r="C65" s="235" t="n">
         <v>180</v>
       </c>
-      <c r="D64" s="239" t="inlineStr">
+      <c r="D65" s="235" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E64" s="261" t="inlineStr">
+      <c r="E65" s="257" t="inlineStr">
         <is>
           <t>Only reload if the newest saved sample is younger than this.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="144">
-      <c r="A65" s="250" t="inlineStr">
+    <row r="66" ht="15" customHeight="1" s="142">
+      <c r="A66" s="246" t="inlineStr">
         <is>
           <t>LOG_ENABLED</t>
         </is>
       </c>
-      <c r="B65" s="260" t="b">
+      <c r="B66" s="256" t="b">
         <v>1</v>
       </c>
-      <c r="C65" s="239" t="b">
+      <c r="C66" s="235" t="b">
         <v>1</v>
       </c>
-      <c r="D65" s="239" t="inlineStr">
+      <c r="D66" s="235" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E65" s="261" t="inlineStr">
+      <c r="E66" s="257" t="inlineStr">
         <is>
           <t>Write signal events to the Log sheet.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="144">
-      <c r="A66" s="250" t="inlineStr">
+    <row r="67" ht="15" customHeight="1" s="142">
+      <c r="A67" s="246" t="inlineStr">
         <is>
           <t>LOG_MAX_ROWS</t>
         </is>
       </c>
-      <c r="B66" s="260" t="n">
+      <c r="B67" s="256" t="n">
         <v>20000</v>
       </c>
-      <c r="C66" s="239" t="n">
+      <c r="C67" s="235" t="n">
         <v>20000</v>
       </c>
-      <c r="D66" s="239" t="inlineStr">
+      <c r="D67" s="235" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="E66" s="261" t="inlineStr">
+      <c r="E67" s="257" t="inlineStr">
         <is>
           <t>Log is trimmed to this many rows.</t>
         </is>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68" ht="15" customHeight="1" s="144">
-      <c r="A68" s="258" t="inlineStr">
+    <row r="68"/>
+    <row r="69" ht="15" customHeight="1" s="142">
+      <c r="A69" s="254" t="inlineStr">
         <is>
           <t>DERIVED COMMISSION  (formulas - do not edit)</t>
         </is>
       </c>
-      <c r="B68" s="265" t="n"/>
-      <c r="C68" s="265" t="n"/>
-      <c r="D68" s="265" t="n"/>
-      <c r="E68" s="265" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="144">
-      <c r="A69" s="259" t="inlineStr">
+      <c r="B69" s="261" t="n"/>
+      <c r="C69" s="261" t="n"/>
+      <c r="D69" s="261" t="n"/>
+      <c r="E69" s="261" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="142">
+      <c r="A70" s="255" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B69" s="259" t="inlineStr">
+      <c r="B70" s="255" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C69" s="259" t="inlineStr">
+      <c r="C70" s="255" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D69" s="259" t="inlineStr">
+      <c r="D70" s="255" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E69" s="259" t="inlineStr">
+      <c r="E70" s="255" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="144">
-      <c r="A70" s="250" t="inlineStr">
+    <row r="71" ht="15" customHeight="1" s="142">
+      <c r="A71" s="246" t="inlineStr">
         <is>
           <t>COMMISSION_CONSERVATIVE</t>
         </is>
       </c>
-      <c r="B70" s="251">
-        <f>2*(B47+B48+B49)</f>
-        <v/>
-      </c>
-      <c r="E70" s="266" t="inlineStr">
+      <c r="B71" s="247">
+        <f>2*(B48+B49+B50)</f>
+        <v/>
+      </c>
+      <c r="E71" s="262" t="inlineStr">
         <is>
           <t>Per lot PER LEG, round turn, reading CME's 1.50 as per SIDE. This is the conservative reading and the one to use.</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="144">
-      <c r="A71" s="250" t="inlineStr">
+    <row r="72" ht="15" customHeight="1" s="142">
+      <c r="A72" s="246" t="inlineStr">
         <is>
           <t>COMMISSION_IF_CME_PER_RT</t>
         </is>
       </c>
-      <c r="B71" s="247">
-        <f>2*(B47+B48)+B49</f>
-        <v/>
-      </c>
-      <c r="E71" s="266" t="inlineStr">
+      <c r="B72" s="243">
+        <f>2*(B48+B49)+B50</f>
+        <v/>
+      </c>
+      <c r="E72" s="262" t="inlineStr">
         <is>
           <t>The same figure if CME's 1.50 turns out to be per ROUND TURN rather than per side.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="144">
-      <c r="A72" s="250" t="inlineStr">
+    <row r="73" ht="15" customHeight="1" s="142">
+      <c r="A73" s="246" t="inlineStr">
         <is>
           <t>COMMISSION_BASIS</t>
         </is>
       </c>
-      <c r="B72" s="260" t="inlineStr">
+      <c r="B73" s="256" t="inlineStr">
         <is>
           <t>CONSERVATIVE</t>
         </is>
       </c>
-      <c r="C72" s="239" t="inlineStr">
+      <c r="C73" s="235" t="inlineStr">
         <is>
           <t>CONSERVATIVE</t>
         </is>
       </c>
-      <c r="E72" s="266" t="inlineStr">
+      <c r="E73" s="262" t="inlineStr">
         <is>
           <t>CONSERVATIVE or CME_PER_RT. An understated cost model approves losing trades invisibly; an overstated one only refuses trades, visibly. Leave it on CONSERVATIVE.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="144">
-      <c r="A73" s="250" t="inlineStr">
+    <row r="74" ht="15" customHeight="1" s="142">
+      <c r="A74" s="246" t="inlineStr">
         <is>
           <t>COMMISSION_PER_LOT_ROUND_TURN</t>
         </is>
       </c>
-      <c r="B73" s="251">
-        <f>IF(B72="CME_PER_RT",B71,B70)</f>
-        <v/>
-      </c>
-      <c r="E73" s="266" t="inlineStr">
+      <c r="B74" s="247">
+        <f>IF(B73="CME_PER_RT",B72,B71)</f>
+        <v/>
+      </c>
+      <c r="E74" s="262" t="inlineStr">
         <is>
           <t>USD per lot per leg, round turn. This is what the cost model actually uses.</t>
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75" ht="15" customHeight="1" s="144">
-      <c r="A75" s="258" t="inlineStr">
+    <row r="75"/>
+    <row r="76" ht="15" customHeight="1" s="142">
+      <c r="A76" s="254" t="inlineStr">
         <is>
           <t>SPREAD_TABLE_START   -   up to 4 monitored spreads, one buffer each</t>
         </is>
       </c>
-      <c r="B75" s="265" t="n"/>
-      <c r="C75" s="265" t="n"/>
-      <c r="D75" s="265" t="n"/>
-      <c r="E75" s="265" t="n"/>
-      <c r="F75" s="265" t="n"/>
-      <c r="G75" s="265" t="n"/>
-      <c r="H75" s="265" t="n"/>
-      <c r="I75" s="265" t="n"/>
-      <c r="J75" s="265" t="n"/>
-      <c r="K75" s="265" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="144">
-      <c r="A76" s="233" t="inlineStr">
+      <c r="B76" s="261" t="n"/>
+      <c r="C76" s="261" t="n"/>
+      <c r="D76" s="261" t="n"/>
+      <c r="E76" s="261" t="n"/>
+      <c r="F76" s="261" t="n"/>
+      <c r="G76" s="261" t="n"/>
+      <c r="H76" s="261" t="n"/>
+      <c r="I76" s="261" t="n"/>
+      <c r="J76" s="261" t="n"/>
+      <c r="K76" s="261" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="142">
+      <c r="A77" s="229" t="inlineStr">
         <is>
           <t>Leg COMPOSITION (which instruments, and their weights) is defined by the labelled formulas in the MONITOR LEGS block on the hidden Feed sheet. Everything below is hot-reloaded each tick.</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="32.8" customHeight="1" s="144">
-      <c r="A77" s="259" t="inlineStr">
+    <row r="78" ht="32.8" customHeight="1" s="142">
+      <c r="A78" s="255" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B77" s="259" t="inlineStr">
+      <c r="B78" s="255" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="C77" s="259" t="inlineStr">
+      <c r="C78" s="255" t="inlineStr">
         <is>
           <t>Display name</t>
         </is>
       </c>
-      <c r="D77" s="259" t="inlineStr">
+      <c r="D78" s="255" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="E77" s="259" t="inlineStr">
+      <c r="E78" s="255" t="inlineStr">
         <is>
           <t>HEDGE_RATIO (beta)</t>
         </is>
       </c>
-      <c r="F77" s="259" t="inlineStr">
+      <c r="F78" s="255" t="inlineStr">
         <is>
           <t>Beta stamped for pair</t>
         </is>
       </c>
-      <c r="G77" s="259" t="inlineStr">
+      <c r="G78" s="255" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread, per lot</t>
         </is>
       </c>
-      <c r="H77" s="259" t="inlineStr">
+      <c r="H78" s="255" t="inlineStr">
         <is>
           <t>Contracts charged commission</t>
         </is>
       </c>
-      <c r="I77" s="259" t="inlineStr">
+      <c r="I78" s="255" t="inlineStr">
         <is>
           <t>Tick size</t>
         </is>
       </c>
-      <c r="J77" s="259" t="inlineStr">
+      <c r="J78" s="255" t="inlineStr">
         <is>
           <t>Decimals</t>
         </is>
       </c>
-      <c r="K77" s="259" t="inlineStr">
+      <c r="K78" s="255" t="inlineStr">
         <is>
           <t>Listed equivalent (cost comparison)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="144">
-      <c r="A78" s="252" t="inlineStr">
+    <row r="79" ht="15" customHeight="1" s="142">
+      <c r="A79" s="248" t="inlineStr">
         <is>
           <t>SPREAD_1</t>
         </is>
       </c>
-      <c r="B78" s="260" t="b">
+      <c r="B79" s="256" t="b">
         <v>1</v>
       </c>
-      <c r="C78" s="262" t="inlineStr">
+      <c r="C79" s="258" t="inlineStr">
         <is>
           <t>BZ - CL  (Brent LDF - WTI)</t>
         </is>
       </c>
-      <c r="D78" s="260" t="inlineStr">
+      <c r="D79" s="256" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E78" s="267" t="n">
+      <c r="E79" s="263" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="262" t="inlineStr">
+      <c r="F79" s="258" t="inlineStr">
         <is>
           <t>BZV6 / CLV6, derived 2026-08 (RELATED pair - no fair value, empirical mean only)</t>
         </is>
       </c>
-      <c r="G78" s="268" t="n">
+      <c r="G79" s="264" t="n">
         <v>1000</v>
       </c>
-      <c r="H78" s="269" t="n">
+      <c r="H79" s="265" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="267" t="n">
+      <c r="I79" s="263" t="n">
         <v>0.01</v>
       </c>
-      <c r="J78" s="269" t="n">
+      <c r="J79" s="265" t="n">
         <v>2</v>
       </c>
-      <c r="K78" s="241" t="inlineStr">
+      <c r="K79" s="237" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="144">
-      <c r="A79" s="252" t="inlineStr">
+    <row r="80" ht="15" customHeight="1" s="142">
+      <c r="A80" s="248" t="inlineStr">
         <is>
           <t>SPREAD_2</t>
         </is>
       </c>
-      <c r="B79" s="260" t="b">
+      <c r="B80" s="256" t="b">
         <v>1</v>
       </c>
-      <c r="C79" s="262" t="inlineStr">
+      <c r="C80" s="258" t="inlineStr">
         <is>
           <t>HO/CL crack  (ULSD - WTI)</t>
         </is>
       </c>
-      <c r="D79" s="260" t="inlineStr">
+      <c r="D80" s="256" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E79" s="267" t="n">
+      <c r="E80" s="263" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="262" t="inlineStr">
+      <c r="F80" s="258" t="inlineStr">
         <is>
           <t>HOV6 x42 / CLV6, 1:1 by design (crack, not a fitted beta)</t>
         </is>
       </c>
-      <c r="G79" s="268" t="n">
+      <c r="G80" s="264" t="n">
         <v>1000</v>
       </c>
-      <c r="H79" s="269" t="n">
+      <c r="H80" s="265" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="267" t="n">
+      <c r="I80" s="263" t="n">
         <v>0.01</v>
       </c>
-      <c r="J79" s="269" t="n">
+      <c r="J80" s="265" t="n">
         <v>2</v>
       </c>
-      <c r="K79" s="241" t="inlineStr">
+      <c r="K80" s="237" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="144">
-      <c r="A80" s="252" t="inlineStr">
+    <row r="81" ht="15" customHeight="1" s="142">
+      <c r="A81" s="248" t="inlineStr">
         <is>
           <t>SPREAD_3</t>
         </is>
       </c>
-      <c r="B80" s="260" t="b">
+      <c r="B81" s="256" t="b">
         <v>1</v>
       </c>
-      <c r="C80" s="262" t="inlineStr">
+      <c r="C81" s="258" t="inlineStr">
         <is>
           <t>3:2:1 crack  (2RB+1HO-3CL)/3</t>
         </is>
       </c>
-      <c r="D80" s="260" t="inlineStr">
+      <c r="D81" s="256" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E80" s="267" t="n">
+      <c r="E81" s="263" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="262" t="inlineStr">
+      <c r="F81" s="258" t="inlineStr">
         <is>
           <t>RBV6/HOV6/CLV6, structural 3:2:1 - not a fitted beta</t>
         </is>
       </c>
-      <c r="G80" s="268" t="n">
+      <c r="G81" s="264" t="n">
         <v>3000</v>
       </c>
-      <c r="H80" s="269" t="n">
+      <c r="H81" s="265" t="n">
         <v>6</v>
       </c>
-      <c r="I80" s="267" t="n">
+      <c r="I81" s="263" t="n">
         <v>0.01</v>
       </c>
-      <c r="J80" s="269" t="n">
+      <c r="J81" s="265" t="n">
         <v>2</v>
       </c>
-      <c r="K80" s="241" t="inlineStr">
+      <c r="K81" s="237" t="inlineStr">
         <is>
           <t>(none listed)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="144">
-      <c r="A81" s="252" t="inlineStr">
+    <row r="82" ht="15" customHeight="1" s="142">
+      <c r="A82" s="248" t="inlineStr">
         <is>
           <t>SPREAD_4</t>
         </is>
       </c>
-      <c r="B81" s="260" t="b">
+      <c r="B82" s="256" t="b">
         <v>1</v>
       </c>
-      <c r="C81" s="262" t="inlineStr">
+      <c r="C82" s="258" t="inlineStr">
         <is>
           <t>CL-BZ Inter-Product (listed)</t>
         </is>
       </c>
-      <c r="D81" s="260" t="inlineStr">
+      <c r="D82" s="256" t="inlineStr">
         <is>
           <t>LISTED</t>
         </is>
       </c>
-      <c r="E81" s="267" t="n">
+      <c r="E82" s="263" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="262" t="inlineStr">
+      <c r="F82" s="258" t="inlineStr">
         <is>
           <t>Exchange-listed spread - beta not applicable</t>
         </is>
       </c>
-      <c r="G81" s="268" t="n">
+      <c r="G82" s="264" t="n">
         <v>1000</v>
       </c>
-      <c r="H81" s="269" t="n">
+      <c r="H82" s="265" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="267" t="n">
+      <c r="I82" s="263" t="n">
         <v>0.01</v>
       </c>
-      <c r="J81" s="269" t="n">
+      <c r="J82" s="265" t="n">
         <v>2</v>
       </c>
-      <c r="K81" s="241" t="inlineStr">
+      <c r="K82" s="237" t="inlineStr">
         <is>
           <t>n/a - this IS the listed spread</t>
         </is>
       </c>
     </row>
-    <row r="82"/>
-    <row r="83" ht="15" customHeight="1" s="144">
-      <c r="A83" s="255" t="inlineStr">
+    <row r="83"/>
+    <row r="84" ht="15" customHeight="1" s="142">
+      <c r="A84" s="251" t="inlineStr">
         <is>
           <t>HEDGE RATIO BELONGS TO THE PAIR. If the instruments change, beta must be re-derived - a stale beta silently redefines the series. Column F stamps what each beta was computed for.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="144">
-      <c r="A84" s="233" t="inlineStr">
+    <row r="85" ht="15" customHeight="1" s="142">
+      <c r="A85" s="229" t="inlineStr">
         <is>
           <t>Contracts charged: BZ-CL and the listed spread are 2 contracts per lot (one per leg); the 3:2:1 crack is 6 (2 RB + 1 HO + 3 CL).</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="144">
-      <c r="A85" s="233" t="inlineStr">
+    <row r="86" ht="15" customHeight="1" s="142">
+      <c r="A86" s="229" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread: NYMEX energy contracts are 1,000 bbl, so one cent of differential is $10 per leg per lot, i.e. $1,000 per 1.00.</t>
         </is>
       </c>
     </row>
-    <row r="86"/>
-    <row r="87" ht="15" customHeight="1" s="144">
-      <c r="A87" s="255" t="inlineStr">
+    <row r="87"/>
+    <row r="88" ht="15" customHeight="1" s="142">
+      <c r="A88" s="251" t="inlineStr">
         <is>
           <t>NOTIONAL_BASIS - read this before changing it:</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="144">
-      <c r="A88" s="233" t="inlineStr">
+    <row r="89" ht="15" customHeight="1" s="142">
+      <c r="A89" s="229" t="inlineStr">
         <is>
           <t>A spread is not an outright, so 'notional' has no single meaning. At 1 lot with CL near $60 and BZ-CL near $7.20:  SPREAD_VALUE ~ $7,200, ONE_LEG ~ $60,000, BOTH_LEGS ~ $127,000.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="144">
-      <c r="A89" s="270" t="inlineStr">
+    <row r="90" ht="15" customHeight="1" s="142">
+      <c r="A90" s="266" t="inlineStr">
         <is>
           <t>1% of those is $72, $600 and $1,270. If sigma on this spread turns out to be ~5 cents ($50), only the first is reachable - the others need the spread to travel 12 or 25 sigma, which it will not do. Watch the TP-in-sigma cell on the Dashboard: above about 1 sigma it turns amber.</t>
         </is>
@@ -5591,315 +5614,315 @@
   <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="40" customWidth="1" style="142" min="1" max="1"/>
-    <col width="34" customWidth="1" style="142" min="2" max="2"/>
-    <col width="13" customWidth="1" style="142" min="3" max="8"/>
-    <col width="60" customWidth="1" style="142" min="9" max="9"/>
+    <col width="40" customWidth="1" style="140" min="1" max="1"/>
+    <col width="34" customWidth="1" style="140" min="2" max="2"/>
+    <col width="13" customWidth="1" style="140" min="3" max="8"/>
+    <col width="60" customWidth="1" style="140" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="144">
-      <c r="A1" s="271" t="inlineStr">
+    <row r="1" ht="16.15" customHeight="1" s="142">
+      <c r="A1" s="267" t="inlineStr">
         <is>
           <t>FEED  -  hidden.  Every RTD() formula lives here.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="144">
-      <c r="A2" s="272" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="142">
+      <c r="A2" s="268" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B2" s="273">
+      <c r="B2" s="269">
         <f>Dashboard!$C$4</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="144">
-      <c r="A3" s="255" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="142">
+      <c r="A3" s="251" t="inlineStr">
         <is>
           <t>Never put an RTD() formula on Dashboard: a cell holding one repaints whenever the feed moves, and that cannot be prevented while the formula is in the cell.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5" ht="15" customHeight="1" s="144">
-      <c r="A5" s="274" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="142">
+      <c r="A5" s="270" t="inlineStr">
         <is>
           <t>INSTRUMENTS</t>
         </is>
       </c>
-      <c r="B5" s="235" t="inlineStr">
+      <c r="B5" s="231" t="inlineStr">
         <is>
           <t>Instrument ID</t>
         </is>
       </c>
-      <c r="C5" s="235" t="inlineStr">
+      <c r="C5" s="231" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="D5" s="235" t="inlineStr">
+      <c r="D5" s="231" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="E5" s="235" t="inlineStr">
+      <c r="E5" s="231" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="235" t="inlineStr">
+      <c r="F5" s="231" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G5" s="235" t="inlineStr">
+      <c r="G5" s="231" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="H5" s="235" t="inlineStr">
+      <c r="H5" s="231" t="inlineStr">
         <is>
           <t>Width</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="144">
-      <c r="A6" s="236" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="142">
+      <c r="A6" s="232" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="B6" s="275">
+      <c r="B6" s="271">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A6)</f>
         <v/>
       </c>
-      <c r="C6" s="275">
+      <c r="C6" s="271">
         <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D6" s="275">
+      <c r="D6" s="271">
         <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E6" s="275">
+      <c r="E6" s="271">
         <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="275">
+      <c r="F6" s="271">
         <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G6" s="275">
+      <c r="G6" s="271">
         <f>IF(OR($C6="",$D6=""),"",($C6+$D6)/2)</f>
         <v/>
       </c>
-      <c r="H6" s="275">
+      <c r="H6" s="271">
         <f>IF(OR($C6="",$D6=""),"",$D6-$C6)</f>
         <v/>
       </c>
-      <c r="I6" s="276" t="inlineStr">
+      <c r="I6" s="272" t="inlineStr">
         <is>
           <t>RBOB Gasoline Oct26</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="144">
-      <c r="A7" s="236" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="142">
+      <c r="A7" s="232" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="B7" s="275">
+      <c r="B7" s="271">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A7)</f>
         <v/>
       </c>
-      <c r="C7" s="275">
+      <c r="C7" s="271">
         <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D7" s="275">
+      <c r="D7" s="271">
         <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E7" s="275">
+      <c r="E7" s="271">
         <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="275">
+      <c r="F7" s="271">
         <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G7" s="275">
+      <c r="G7" s="271">
         <f>IF(OR($C7="",$D7=""),"",($C7+$D7)/2)</f>
         <v/>
       </c>
-      <c r="H7" s="275">
+      <c r="H7" s="271">
         <f>IF(OR($C7="",$D7=""),"",$D7-$C7)</f>
         <v/>
       </c>
-      <c r="I7" s="276" t="inlineStr">
+      <c r="I7" s="272" t="inlineStr">
         <is>
           <t>NY Harbor ULSD Oct26</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="144">
-      <c r="A8" s="236" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="142">
+      <c r="A8" s="232" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="B8" s="275">
+      <c r="B8" s="271">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A8)</f>
         <v/>
       </c>
-      <c r="C8" s="275">
+      <c r="C8" s="271">
         <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D8" s="275">
+      <c r="D8" s="271">
         <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E8" s="275">
+      <c r="E8" s="271">
         <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="275">
+      <c r="F8" s="271">
         <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G8" s="275">
+      <c r="G8" s="271">
         <f>IF(OR($C8="",$D8=""),"",($C8+$D8)/2)</f>
         <v/>
       </c>
-      <c r="H8" s="275">
+      <c r="H8" s="271">
         <f>IF(OR($C8="",$D8=""),"",$D8-$C8)</f>
         <v/>
       </c>
-      <c r="I8" s="276" t="inlineStr">
+      <c r="I8" s="272" t="inlineStr">
         <is>
           <t>WTI Crude Oct26</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="144">
-      <c r="A9" s="236" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="142">
+      <c r="A9" s="232" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="B9" s="275">
+      <c r="B9" s="271">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A9)</f>
         <v/>
       </c>
-      <c r="C9" s="275">
+      <c r="C9" s="271">
         <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D9" s="275">
+      <c r="D9" s="271">
         <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E9" s="275">
+      <c r="E9" s="271">
         <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="275">
+      <c r="F9" s="271">
         <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G9" s="275">
+      <c r="G9" s="271">
         <f>IF(OR($C9="",$D9=""),"",($C9+$D9)/2)</f>
         <v/>
       </c>
-      <c r="H9" s="275">
+      <c r="H9" s="271">
         <f>IF(OR($C9="",$D9=""),"",$D9-$C9)</f>
         <v/>
       </c>
-      <c r="I9" s="276" t="inlineStr">
+      <c r="I9" s="272" t="inlineStr">
         <is>
           <t>Brent Last Day Financial Oct26</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="144">
-      <c r="A10" s="236" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="142">
+      <c r="A10" s="232" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="B10" s="275">
+      <c r="B10" s="271">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A10)</f>
         <v/>
       </c>
-      <c r="C10" s="275">
+      <c r="C10" s="271">
         <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D10" s="275">
+      <c r="D10" s="271">
         <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E10" s="275">
+      <c r="E10" s="271">
         <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="275">
+      <c r="F10" s="271">
         <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G10" s="275">
+      <c r="G10" s="271">
         <f>IF(OR($C10="",$D10=""),"",($C10+$D10)/2)</f>
         <v/>
       </c>
-      <c r="H10" s="275">
+      <c r="H10" s="271">
         <f>IF(OR($C10="",$D10=""),"",$D10-$C10)</f>
         <v/>
       </c>
-      <c r="I10" s="276" t="inlineStr">
+      <c r="I10" s="272" t="inlineStr">
         <is>
           <t>Exchange-listed inter-product spread</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="144">
-      <c r="A11" s="236" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="142">
+      <c r="A11" s="232" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="B11" s="275">
+      <c r="B11" s="271">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A11)</f>
         <v/>
       </c>
-      <c r="C11" s="275">
+      <c r="C11" s="271">
         <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D11" s="275">
+      <c r="D11" s="271">
         <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E11" s="275">
+      <c r="E11" s="271">
         <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="275">
+      <c r="F11" s="271">
         <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G11" s="275">
+      <c r="G11" s="271">
         <f>IF(OR($C11="",$D11=""),"",($C11+$D11)/2)</f>
         <v/>
       </c>
-      <c r="H11" s="275">
+      <c r="H11" s="271">
         <f>IF(OR($C11="",$D11=""),"",$D11-$C11)</f>
         <v/>
       </c>
-      <c r="I11" s="276" t="inlineStr">
+      <c r="I11" s="272" t="inlineStr">
         <is>
           <t>Exchange-listed crack spread</t>
         </is>
@@ -5908,516 +5931,516 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
-    <row r="15" ht="15" customHeight="1" s="144">
-      <c r="A15" s="274" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="142">
+      <c r="A15" s="270" t="inlineStr">
         <is>
           <t>DERIVED &amp; LISTED SPREADS (display)</t>
         </is>
       </c>
-      <c r="B15" s="235" t="inlineStr">
+      <c r="B15" s="231" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="C15" s="235" t="inlineStr">
+      <c r="C15" s="231" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="D15" s="235" t="inlineStr">
+      <c r="D15" s="231" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="E15" s="235" t="inlineStr">
+      <c r="E15" s="231" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="F15" s="235" t="inlineStr">
+      <c r="F15" s="231" t="inlineStr">
         <is>
           <t>Width</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="144">
-      <c r="A16" s="236" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="142">
+      <c r="A16" s="232" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="B16" s="243" t="inlineStr">
+      <c r="B16" s="239" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C16" s="275">
+      <c r="C16" s="271">
         <f>IF(OR($C$9="",$D$8=""),"",$C$9-$D$8)</f>
         <v/>
       </c>
-      <c r="D16" s="275">
+      <c r="D16" s="271">
         <f>IF(OR($D$9="",$C$8=""),"",$D$9-$C$8)</f>
         <v/>
       </c>
-      <c r="E16" s="275">
+      <c r="E16" s="271">
         <f>IF(OR($G$9="",$G$8=""),"",$G$9-$G$8)</f>
         <v/>
       </c>
-      <c r="F16" s="275">
+      <c r="F16" s="271">
         <f>IF(OR($C16="",$D16=""),"",$D16-$C16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="144">
-      <c r="A17" s="236" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="142">
+      <c r="A17" s="232" t="inlineStr">
         <is>
           <t>HO/CL crack</t>
         </is>
       </c>
-      <c r="B17" s="243" t="inlineStr">
+      <c r="B17" s="239" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C17" s="275">
+      <c r="C17" s="271">
         <f>IF(OR($C$7="",$D$8=""),"",$C$7*42-$D$8)</f>
         <v/>
       </c>
-      <c r="D17" s="275">
+      <c r="D17" s="271">
         <f>IF(OR($D$7="",$C$8=""),"",$D$7*42-$C$8)</f>
         <v/>
       </c>
-      <c r="E17" s="275">
+      <c r="E17" s="271">
         <f>IF(OR($G$7="",$G$8=""),"",$G$7*42-$G$8)</f>
         <v/>
       </c>
-      <c r="F17" s="275">
+      <c r="F17" s="271">
         <f>IF(OR($C17="",$D17=""),"",$D17-$C17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="144">
-      <c r="A18" s="236" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="142">
+      <c r="A18" s="232" t="inlineStr">
         <is>
           <t>3:2:1 crack</t>
         </is>
       </c>
-      <c r="B18" s="243" t="inlineStr">
+      <c r="B18" s="239" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C18" s="275">
+      <c r="C18" s="271">
         <f>IF(OR($C$6="",$C$7="",$D$8=""),"",(($C$6*2*42)+($C$7*1*42)-($D$8*3))/3)</f>
         <v/>
       </c>
-      <c r="D18" s="275">
+      <c r="D18" s="271">
         <f>IF(OR($D$6="",$D$7="",$C$8=""),"",(($D$6*2*42)+($D$7*1*42)-($C$8*3))/3)</f>
         <v/>
       </c>
-      <c r="E18" s="275">
+      <c r="E18" s="271">
         <f>IF(OR($G$6="",$G$7="",$G$8=""),"",(($G$6*2*42)+($G$7*1*42)-($G$8*3))/3)</f>
         <v/>
       </c>
-      <c r="F18" s="275">
+      <c r="F18" s="271">
         <f>IF(OR($C18="",$D18=""),"",$D18-$C18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="144">
-      <c r="A19" s="236" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="142">
+      <c r="A19" s="232" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="B19" s="243" t="inlineStr">
+      <c r="B19" s="239" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="C19" s="275">
+      <c r="C19" s="271">
         <f>$C$10</f>
         <v/>
       </c>
-      <c r="D19" s="275">
+      <c r="D19" s="271">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="E19" s="275">
+      <c r="E19" s="271">
         <f>$G$10</f>
         <v/>
       </c>
-      <c r="F19" s="275">
+      <c r="F19" s="271">
         <f>IF(OR($C19="",$D19=""),"",$D19-$C19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="144">
-      <c r="A20" s="236" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="142">
+      <c r="A20" s="232" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="B20" s="243" t="inlineStr">
+      <c r="B20" s="239" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="C20" s="275">
+      <c r="C20" s="271">
         <f>$C$11</f>
         <v/>
       </c>
-      <c r="D20" s="275">
+      <c r="D20" s="271">
         <f>$D$11</f>
         <v/>
       </c>
-      <c r="E20" s="275">
+      <c r="E20" s="271">
         <f>$G$11</f>
         <v/>
       </c>
-      <c r="F20" s="275">
+      <c r="F20" s="271">
         <f>IF(OR($C20="",$D20=""),"",$D20-$C20)</f>
         <v/>
       </c>
     </row>
     <row r="21"/>
     <row r="22"/>
-    <row r="23" ht="15" customHeight="1" s="144">
-      <c r="A23" s="277" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="142">
+      <c r="A23" s="273" t="inlineStr">
         <is>
           <t>MONITOR LEGS</t>
         </is>
       </c>
-      <c r="B23" s="233" t="inlineStr">
+      <c r="B23" s="229" t="inlineStr">
         <is>
           <t>Edit these formulas to redefine what a monitored spread is made of. spread = LegB - HEDGE_RATIO x LegA, and nothing else - no carry, no fair-value term.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="144">
-      <c r="A24" s="235" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="142">
+      <c r="A24" s="231" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B24" s="235" t="inlineStr">
+      <c r="B24" s="231" t="inlineStr">
         <is>
           <t>Side</t>
         </is>
       </c>
-      <c r="C24" s="235" t="inlineStr">
+      <c r="C24" s="231" t="inlineStr">
         <is>
           <t>Composition</t>
         </is>
       </c>
-      <c r="D24" s="235" t="inlineStr">
+      <c r="D24" s="231" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="E24" s="235" t="inlineStr">
+      <c r="E24" s="231" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="F24" s="235" t="inlineStr">
+      <c r="F24" s="231" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="144">
-      <c r="A25" s="278" t="n">
+    <row r="25" ht="15" customHeight="1" s="142">
+      <c r="A25" s="274" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="252" t="inlineStr">
+      <c r="B25" s="248" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C25" s="279" t="inlineStr">
+      <c r="C25" s="275" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D25" s="275">
+      <c r="D25" s="271">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E25" s="275">
+      <c r="E25" s="271">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F25" s="275">
+      <c r="F25" s="271">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="144">
-      <c r="A26" s="278" t="n">
+    <row r="26" ht="15" customHeight="1" s="142">
+      <c r="A26" s="274" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="252" t="inlineStr">
+      <c r="B26" s="248" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C26" s="279" t="inlineStr">
+      <c r="C26" s="275" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="D26" s="275">
+      <c r="D26" s="271">
         <f>$C$9</f>
         <v/>
       </c>
-      <c r="E26" s="275">
+      <c r="E26" s="271">
         <f>$D$9</f>
         <v/>
       </c>
-      <c r="F26" s="275">
+      <c r="F26" s="271">
         <f>$G$9</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="144">
-      <c r="A27" s="278" t="n">
+    <row r="27" ht="15" customHeight="1" s="142">
+      <c r="A27" s="274" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="252" t="inlineStr">
+      <c r="B27" s="248" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C27" s="279" t="inlineStr">
+      <c r="C27" s="275" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D27" s="275">
+      <c r="D27" s="271">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E27" s="275">
+      <c r="E27" s="271">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F27" s="275">
+      <c r="F27" s="271">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="144">
-      <c r="A28" s="278" t="n">
+    <row r="28" ht="15" customHeight="1" s="142">
+      <c r="A28" s="274" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="252" t="inlineStr">
+      <c r="B28" s="248" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C28" s="279" t="inlineStr">
+      <c r="C28" s="275" t="inlineStr">
         <is>
           <t>HOV6 x 42</t>
         </is>
       </c>
-      <c r="D28" s="275">
+      <c r="D28" s="271">
         <f>IF($C$7="","",$C$7*42)</f>
         <v/>
       </c>
-      <c r="E28" s="275">
+      <c r="E28" s="271">
         <f>IF($D$7="","",$D$7*42)</f>
         <v/>
       </c>
-      <c r="F28" s="275">
+      <c r="F28" s="271">
         <f>IF($G$7="","",$G$7*42)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="144">
-      <c r="A29" s="278" t="n">
+    <row r="29" ht="15" customHeight="1" s="142">
+      <c r="A29" s="274" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="252" t="inlineStr">
+      <c r="B29" s="248" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C29" s="279" t="inlineStr">
+      <c r="C29" s="275" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D29" s="275">
+      <c r="D29" s="271">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E29" s="275">
+      <c r="E29" s="271">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F29" s="275">
+      <c r="F29" s="271">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="144">
-      <c r="A30" s="278" t="n">
+    <row r="30" ht="15" customHeight="1" s="142">
+      <c r="A30" s="274" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="252" t="inlineStr">
+      <c r="B30" s="248" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C30" s="279" t="inlineStr">
+      <c r="C30" s="275" t="inlineStr">
         <is>
           <t>(2 x RBV6 + 1 x HOV6) x 42 / 3</t>
         </is>
       </c>
-      <c r="D30" s="275">
+      <c r="D30" s="271">
         <f>IF(OR($C$6="",$C$7=""),"",($C$6*2*42+$C$7*1*42)/3)</f>
         <v/>
       </c>
-      <c r="E30" s="275">
+      <c r="E30" s="271">
         <f>IF(OR($D$6="",$D$7=""),"",($D$6*2*42+$D$7*1*42)/3)</f>
         <v/>
       </c>
-      <c r="F30" s="275">
+      <c r="F30" s="271">
         <f>IF(OR($G$6="",$G$7=""),"",($G$6*2*42+$G$7*1*42)/3)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="144">
-      <c r="A31" s="278" t="n">
+    <row r="31" ht="15" customHeight="1" s="142">
+      <c r="A31" s="274" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="252" t="inlineStr">
+      <c r="B31" s="248" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C31" s="279" t="inlineStr">
+      <c r="C31" s="275" t="inlineStr">
         <is>
           <t>(none - LISTED spread)</t>
         </is>
       </c>
-      <c r="D31" s="275" t="inlineStr"/>
-      <c r="E31" s="275" t="inlineStr"/>
-      <c r="F31" s="275" t="inlineStr"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="144">
-      <c r="A32" s="278" t="n">
+      <c r="D31" s="271" t="inlineStr"/>
+      <c r="E31" s="271" t="inlineStr"/>
+      <c r="F31" s="271" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="142">
+      <c r="A32" s="274" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="252" t="inlineStr">
+      <c r="B32" s="248" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C32" s="279" t="inlineStr">
+      <c r="C32" s="275" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="D32" s="275">
+      <c r="D32" s="271">
         <f>$C$10</f>
         <v/>
       </c>
-      <c r="E32" s="275">
+      <c r="E32" s="271">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="F32" s="275">
+      <c r="F32" s="271">
         <f>$G$10</f>
         <v/>
       </c>
     </row>
     <row r="33"/>
-    <row r="34" ht="15" customHeight="1" s="144">
-      <c r="A34" s="277" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="142">
+      <c r="A34" s="273" t="inlineStr">
         <is>
           <t>LISTED-EQUIVALENT ROW PER SLOT  (for the side-by-side crossing-cost comparison)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="144">
-      <c r="A35" s="235" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="142">
+      <c r="A35" s="231" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B35" s="235" t="inlineStr">
+      <c r="B35" s="231" t="inlineStr">
         <is>
           <t>Feed derived row</t>
         </is>
       </c>
-      <c r="C35" s="235" t="inlineStr">
+      <c r="C35" s="231" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="144">
-      <c r="A36" s="278" t="n">
+    <row r="36" ht="15" customHeight="1" s="142">
+      <c r="A36" s="274" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="278" t="n">
+      <c r="B36" s="274" t="n">
         <v>19</v>
       </c>
-      <c r="C36" s="279" t="inlineStr">
+      <c r="C36" s="275" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="144">
-      <c r="A37" s="278" t="n">
+    <row r="37" ht="15" customHeight="1" s="142">
+      <c r="A37" s="274" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="278" t="n">
+      <c r="B37" s="274" t="n">
         <v>20</v>
       </c>
-      <c r="C37" s="279" t="inlineStr">
+      <c r="C37" s="275" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="144">
-      <c r="A38" s="278" t="n">
+    <row r="38" ht="15" customHeight="1" s="142">
+      <c r="A38" s="274" t="n">
         <v>3</v>
       </c>
-      <c r="B38" s="278" t="n"/>
-      <c r="C38" s="279" t="inlineStr">
+      <c r="B38" s="274" t="n"/>
+      <c r="C38" s="275" t="inlineStr">
         <is>
           <t>(none)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="144">
-      <c r="A39" s="278" t="n">
+    <row r="39" ht="15" customHeight="1" s="142">
+      <c r="A39" s="274" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="278" t="n">
+      <c r="B39" s="274" t="n">
         <v>19</v>
       </c>
-      <c r="C39" s="279" t="inlineStr">
+      <c r="C39" s="275" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
     <row r="40"/>
-    <row r="41" ht="15" customHeight="1" s="144">
-      <c r="A41" s="233" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="142">
+      <c r="A41" s="229" t="inlineStr">
         <is>
           <t>Crossing convention used throughout:  spread bid = LegB bid - beta x LegA ask ; spread ask = LegB ask - beta x LegA bid ; spread mid = LegB mid - beta x LegA mid.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="144">
-      <c r="A42" s="233" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="142">
+      <c r="A42" s="229" t="inlineStr">
         <is>
           <t>For a LISTED slot LegA is empty and is treated as zero, so the listed quote passes straight through untouched.</t>
         </is>
@@ -6439,235 +6462,235 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="15" customWidth="1" style="142" min="1" max="2"/>
-    <col width="3" customWidth="1" style="142" min="3" max="3"/>
-    <col width="15" customWidth="1" style="142" min="4" max="5"/>
-    <col width="3" customWidth="1" style="142" min="6" max="6"/>
-    <col width="15" customWidth="1" style="142" min="7" max="8"/>
-    <col width="3" customWidth="1" style="142" min="9" max="9"/>
-    <col width="15" customWidth="1" style="142" min="10" max="11"/>
-    <col width="26" customWidth="1" style="142" min="13" max="13"/>
-    <col width="30" customWidth="1" style="142" min="14" max="14"/>
+    <col width="15" customWidth="1" style="140" min="1" max="2"/>
+    <col width="3" customWidth="1" style="140" min="3" max="3"/>
+    <col width="15" customWidth="1" style="140" min="4" max="5"/>
+    <col width="3" customWidth="1" style="140" min="6" max="6"/>
+    <col width="15" customWidth="1" style="140" min="7" max="8"/>
+    <col width="3" customWidth="1" style="140" min="9" max="9"/>
+    <col width="15" customWidth="1" style="140" min="10" max="11"/>
+    <col width="26" customWidth="1" style="140" min="13" max="13"/>
+    <col width="30" customWidth="1" style="140" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="144">
-      <c r="A1" s="280" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="142">
+      <c r="A1" s="276" t="inlineStr">
         <is>
           <t>BUFFER  -  hidden.  Flushed circular buffers (crash / restart recovery).</t>
         </is>
       </c>
-      <c r="M1" s="233" t="inlineStr">
+      <c r="M1" s="229" t="inlineStr">
         <is>
           <t>Written by VBA every FLUSH_SEC seconds, so a crash loses at most a minute.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="144">
-      <c r="M2" s="233" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="142">
+      <c r="M2" s="229" t="inlineStr">
         <is>
           <t>On open, WarmStart reloads a slot only if its stamped LOOKBACK_MIN, HEDGE_RATIO and leg labels still match Config, and the newest sample is younger than WARM_START_MAX_AGE_MIN.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="144">
-      <c r="A3" s="277" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="142">
+      <c r="A3" s="273" t="inlineStr">
         <is>
           <t>SLOT 1</t>
         </is>
       </c>
-      <c r="D3" s="277" t="inlineStr">
+      <c r="D3" s="273" t="inlineStr">
         <is>
           <t>SLOT 2</t>
         </is>
       </c>
-      <c r="G3" s="277" t="inlineStr">
+      <c r="G3" s="273" t="inlineStr">
         <is>
           <t>SLOT 3</t>
         </is>
       </c>
-      <c r="J3" s="277" t="inlineStr">
+      <c r="J3" s="273" t="inlineStr">
         <is>
           <t>SLOT 4</t>
         </is>
       </c>
-      <c r="M3" s="233" t="inlineStr">
+      <c r="M3" s="229" t="inlineStr">
         <is>
           <t>Elapsed collection is credited from the OLDEST recovered sample - otherwise every restart costs another two hours before a usable z.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="144">
-      <c r="A4" s="276" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="142">
+      <c r="A4" s="272" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B4" s="275" t="n"/>
-      <c r="D4" s="276" t="inlineStr">
+      <c r="B4" s="271" t="n"/>
+      <c r="D4" s="272" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E4" s="275" t="n"/>
-      <c r="G4" s="276" t="inlineStr">
+      <c r="E4" s="271" t="n"/>
+      <c r="G4" s="272" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="H4" s="275" t="n"/>
-      <c r="J4" s="276" t="inlineStr">
+      <c r="H4" s="271" t="n"/>
+      <c r="J4" s="272" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K4" s="275" t="n"/>
-      <c r="M4" s="233" t="inlineStr">
+      <c r="K4" s="271" t="n"/>
+      <c r="M4" s="229" t="inlineStr">
         <is>
           <t>Seeding drops CONSECUTIVE identical values only. A spread genuinely revisiting a level is a real observation, not a duplicate.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="144">
-      <c r="A5" s="276" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="142">
+      <c r="A5" s="272" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="B5" s="275" t="n"/>
-      <c r="D5" s="276" t="inlineStr">
+      <c r="B5" s="271" t="n"/>
+      <c r="D5" s="272" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="E5" s="275" t="n"/>
-      <c r="G5" s="276" t="inlineStr">
+      <c r="E5" s="271" t="n"/>
+      <c r="G5" s="272" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="H5" s="275" t="n"/>
-      <c r="J5" s="276" t="inlineStr">
+      <c r="H5" s="271" t="n"/>
+      <c r="J5" s="272" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="K5" s="275" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="144">
-      <c r="A6" s="276" t="inlineStr">
+      <c r="K5" s="271" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="142">
+      <c r="A6" s="272" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="B6" s="275" t="n"/>
-      <c r="D6" s="276" t="inlineStr">
+      <c r="B6" s="271" t="n"/>
+      <c r="D6" s="272" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="E6" s="275" t="n"/>
-      <c r="G6" s="276" t="inlineStr">
+      <c r="E6" s="271" t="n"/>
+      <c r="G6" s="272" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="H6" s="275" t="n"/>
-      <c r="J6" s="276" t="inlineStr">
+      <c r="H6" s="271" t="n"/>
+      <c r="J6" s="272" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="K6" s="275" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="144">
-      <c r="A7" s="276" t="inlineStr">
+      <c r="K6" s="271" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="142">
+      <c r="A7" s="272" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="B7" s="275" t="n"/>
-      <c r="D7" s="276" t="inlineStr">
+      <c r="B7" s="271" t="n"/>
+      <c r="D7" s="272" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="E7" s="275" t="n"/>
-      <c r="G7" s="276" t="inlineStr">
+      <c r="E7" s="271" t="n"/>
+      <c r="G7" s="272" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="H7" s="275" t="n"/>
-      <c r="J7" s="276" t="inlineStr">
+      <c r="H7" s="271" t="n"/>
+      <c r="J7" s="272" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="K7" s="275" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="144">
-      <c r="A8" s="276" t="inlineStr">
+      <c r="K7" s="271" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="142">
+      <c r="A8" s="272" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="B8" s="275" t="n"/>
-      <c r="D8" s="276" t="inlineStr">
+      <c r="B8" s="271" t="n"/>
+      <c r="D8" s="272" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="E8" s="275" t="n"/>
-      <c r="G8" s="276" t="inlineStr">
+      <c r="E8" s="271" t="n"/>
+      <c r="G8" s="272" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="H8" s="275" t="n"/>
-      <c r="J8" s="276" t="inlineStr">
+      <c r="H8" s="271" t="n"/>
+      <c r="J8" s="272" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="K8" s="275" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="144">
-      <c r="A9" s="235" t="inlineStr">
+      <c r="K8" s="271" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="142">
+      <c r="A9" s="231" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="B9" s="235" t="inlineStr">
+      <c r="B9" s="231" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="D9" s="235" t="inlineStr">
+      <c r="D9" s="231" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="E9" s="235" t="inlineStr">
+      <c r="E9" s="231" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="G9" s="235" t="inlineStr">
+      <c r="G9" s="231" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="H9" s="235" t="inlineStr">
+      <c r="H9" s="231" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="J9" s="235" t="inlineStr">
+      <c r="J9" s="231" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="K9" s="235" t="inlineStr">
+      <c r="K9" s="231" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
@@ -6689,87 +6712,87 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="20" customWidth="1" style="142" min="1" max="1"/>
-    <col width="30" customWidth="1" style="142" min="2" max="2"/>
-    <col width="20" customWidth="1" style="142" min="3" max="3"/>
-    <col width="9" customWidth="1" style="142" min="4" max="4"/>
-    <col width="12" customWidth="1" style="142" min="5" max="9"/>
-    <col width="16" customWidth="1" style="142" min="10" max="10"/>
-    <col width="10" customWidth="1" style="142" min="11" max="11"/>
-    <col width="60" customWidth="1" style="142" min="12" max="12"/>
+    <col width="20" customWidth="1" style="140" min="1" max="1"/>
+    <col width="30" customWidth="1" style="140" min="2" max="2"/>
+    <col width="20" customWidth="1" style="140" min="3" max="3"/>
+    <col width="9" customWidth="1" style="140" min="4" max="4"/>
+    <col width="12" customWidth="1" style="140" min="5" max="9"/>
+    <col width="16" customWidth="1" style="140" min="10" max="10"/>
+    <col width="10" customWidth="1" style="140" min="11" max="11"/>
+    <col width="60" customWidth="1" style="140" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="144">
-      <c r="A1" s="280" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="142">
+      <c r="A1" s="276" t="inlineStr">
         <is>
           <t>LOG  -  timestamped signal events</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="144">
-      <c r="A2" s="233" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="142">
+      <c r="A2" s="229" t="inlineStr">
         <is>
           <t>One line when a state STARTS and one when it CLEARS - never one per poll. Reviewable after the session.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="144">
-      <c r="A3" s="235" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="142">
+      <c r="A3" s="231" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B3" s="235" t="inlineStr">
+      <c r="B3" s="231" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C3" s="235" t="inlineStr">
+      <c r="C3" s="231" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D3" s="235" t="inlineStr">
+      <c r="D3" s="231" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E3" s="235" t="inlineStr">
+      <c r="E3" s="231" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="F3" s="235" t="inlineStr">
+      <c r="F3" s="231" t="inlineStr">
         <is>
           <t>Sigma</t>
         </is>
       </c>
-      <c r="G3" s="235" t="inlineStr">
+      <c r="G3" s="231" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="H3" s="235" t="inlineStr">
+      <c r="H3" s="231" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I3" s="235" t="inlineStr">
+      <c r="I3" s="231" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J3" s="235" t="inlineStr">
+      <c r="J3" s="231" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="K3" s="235" t="inlineStr">
+      <c r="K3" s="231" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="L3" s="235" t="inlineStr">
+      <c r="L3" s="231" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -6791,307 +6814,307 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="4" customWidth="1" style="142" min="1" max="1"/>
-    <col width="46" customWidth="1" style="142" min="2" max="2"/>
-    <col width="16" customWidth="1" style="142" min="3" max="6"/>
-    <col width="60" customWidth="1" style="142" min="7" max="7"/>
+    <col width="4" customWidth="1" style="140" min="1" max="1"/>
+    <col width="46" customWidth="1" style="140" min="2" max="2"/>
+    <col width="16" customWidth="1" style="140" min="3" max="6"/>
+    <col width="60" customWidth="1" style="140" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.7" customHeight="1" s="144">
-      <c r="B1" s="256" t="inlineStr">
+    <row r="1" ht="19.7" customHeight="1" s="142">
+      <c r="B1" s="252" t="inlineStr">
         <is>
           <t>SETUP  -  turning this .xlsx into the working .xlsm</t>
         </is>
       </c>
     </row>
     <row r="2"/>
-    <row r="3" ht="30" customHeight="1" s="144">
-      <c r="B3" s="281" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="142">
+      <c r="B3" s="277" t="inlineStr">
         <is>
           <t>openpyxl cannot author VBA, so this file ships as an .xlsx carrying all structure and formatting, plus a .bas module to import. Six steps, once.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="144">
-      <c r="B4" s="282" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="142">
+      <c r="B4" s="278" t="inlineStr">
         <is>
           <t>1.  Open TT_ZScore_Monitor.xlsx in Excel on the machine running TT and the TT RTD server.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="144">
-      <c r="B5" s="282" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="142">
+      <c r="B5" s="278" t="inlineStr">
         <is>
           <t>2.  File &gt; Save As &gt; Excel Macro-Enabled Workbook (.xlsm). Keep the same folder.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="144">
-      <c r="B6" s="282" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="142">
+      <c r="B6" s="278" t="inlineStr">
         <is>
           <t>3.  Alt+F11 to open the VBA editor.  File &gt; Import File...  and choose TTZMonitor.bas.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="144">
-      <c r="B7" s="282" t="inlineStr">
+    <row r="7" ht="30" customHeight="1" s="142">
+      <c r="B7" s="278" t="inlineStr">
         <is>
           <t>4.  In the editor, double-click ThisWorkbook, clear the pane with Ctrl+A then Delete, and paste the contents of ThisWorkbook.txt verbatim. Do NOT copy it out of TTZMonitor.bas - the copy there is inside a comment block, and pasting it with the apostrophes attached gives 'Compile error: Expected End Sub'.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="144">
-      <c r="B8" s="282" t="inlineStr">
+    <row r="8" ht="30" customHeight="1" s="142">
+      <c r="B8" s="278" t="inlineStr">
         <is>
           <t>5.  Back on Dashboard, insert two shapes over cells N2 and P2 (Insert &gt; Shapes &gt; Rectangle), right-click each &gt; Assign Macro &gt; StartMonitor and StopMonitor. Until you do, run them from Alt+F8.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="144">
-      <c r="B9" s="282" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="142">
+      <c r="B9" s="278" t="inlineStr">
         <is>
           <t>6.  Save. Click START. The Feed sheet stays hidden; you never need to look at it.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="144">
-      <c r="B10" s="281" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="142">
+      <c r="B10" s="277" t="inlineStr">
         <is>
           <t>Step 4 is NOT optional here. The capture timer is a Windows user32 timer, and one that outlives the workbook keeps firing into a module that no longer has its sheets - which crashes Excel. Workbook_BeforeClose calls StopMonitor and kills it.</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="15" customHeight="1" s="144">
-      <c r="B12" s="234" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="142">
+      <c r="B12" s="230" t="inlineStr">
         <is>
           <t>WHAT TO CHECK ON THE FIRST RUN</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="25.5" customHeight="1" s="144">
-      <c r="B13" s="283" t="inlineStr">
+    <row r="13" ht="25.5" customHeight="1" s="142">
+      <c r="B13" s="279" t="inlineStr">
         <is>
           <t>-  Feed sheet column B (instrument ids) fills in. If it stays blank, the TT short name in Feed column A does not match TT, or the market in Dashboard!C4 is wrong.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="25.5" customHeight="1" s="144">
-      <c r="B14" s="283" t="inlineStr">
+    <row r="14" ht="25.5" customHeight="1" s="142">
+      <c r="B14" s="279" t="inlineStr">
         <is>
           <t>-  Dashboard prices move, but the sheet does NOT flash. If it flashes, something volatile has been reintroduced - search the workbook for NOW, TODAY, OFFSET, INDIRECT, RAND.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="25.5" customHeight="1" s="144">
-      <c r="B15" s="283" t="inlineStr">
+    <row r="15" ht="25.5" customHeight="1" s="142">
+      <c r="B15" s="279" t="inlineStr">
         <is>
           <t>-  The samples counter climbs at roughly the quotes/min rate, not at the timer rate. If it climbs at the timer rate, dedupe is not working and every z you see will be fiction.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="25.5" customHeight="1" s="144">
-      <c r="B16" s="283" t="inlineStr">
+    <row r="16" ht="25.5" customHeight="1" s="142">
+      <c r="B16" s="279" t="inlineStr">
         <is>
           <t>-  Warm-up takes MIN_HISTORY_MIN (default 120) minutes on a cold start. That is deliberate.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="25.5" customHeight="1" s="144">
-      <c r="B17" s="283" t="inlineStr">
+    <row r="17" ht="25.5" customHeight="1" s="142">
+      <c r="B17" s="279" t="inlineStr">
         <is>
           <t>-  A 'ticks' folder appears beside the workbook, one CSV per spread per day, holding every changed quote. That is the raw record - keep it for the first week or two.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="25.5" customHeight="1" s="144">
-      <c r="B18" s="283" t="inlineStr">
+    <row r="18" ht="25.5" customHeight="1" s="142">
+      <c r="B18" s="279" t="inlineStr">
         <is>
           <t>-  After a week, run Alt+F8 &gt; CheckSubsamplingLoss. It compares mean and sigma over the live window at full fidelity against 250 / 500 / 1000 / 2000 / 5000 ms subsampling and writes the comparison to the Log. If sigma is materially unchanged, set STORE_MIN_INTERVAL_MS and reclaim the memory.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20" ht="15" customHeight="1" s="144">
-      <c r="B20" s="234" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="142">
+      <c r="B20" s="230" t="inlineStr">
         <is>
           <t>WHAT SIGMA THIS SPREAD MUST HAVE TO BE WORTH TRADING</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="144">
-      <c r="B21" s="233" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="142">
+      <c r="B21" s="229" t="inlineStr">
         <is>
           <t>Live off Config. Edit the two assumed market widths below; everything else follows.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="144">
-      <c r="B22" s="266" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="142">
+      <c r="B22" s="262" t="inlineStr">
         <is>
           <t>Assumed width, each outright leg (spread units)</t>
         </is>
       </c>
-      <c r="C22" s="267" t="n">
+      <c r="C22" s="263" t="n">
         <v>0.02</v>
       </c>
-      <c r="E22" s="266" t="inlineStr">
+      <c r="E22" s="262" t="inlineStr">
         <is>
           <t>Assumed width, listed spread (spread units)</t>
         </is>
       </c>
-      <c r="F22" s="267" t="n">
+      <c r="F22" s="263" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="22.35" customHeight="1" s="144">
-      <c r="B24" s="235" t="inlineStr">
+    <row r="24" ht="22.35" customHeight="1" s="142">
+      <c r="B24" s="231" t="inlineStr">
         <is>
           <t>At LOTS from Config, per leg</t>
         </is>
       </c>
-      <c r="C24" s="235" t="inlineStr">
+      <c r="C24" s="231" t="inlineStr">
         <is>
           <t>Total cost</t>
         </is>
       </c>
-      <c r="D24" s="235" t="inlineStr">
+      <c r="D24" s="231" t="inlineStr">
         <is>
           <t>min sigma @ z = 3.0</t>
         </is>
       </c>
-      <c r="E24" s="235" t="inlineStr">
+      <c r="E24" s="231" t="inlineStr">
         <is>
           <t>min sigma @ z = 2.5</t>
         </is>
       </c>
-      <c r="F24" s="235" t="inlineStr">
+      <c r="F24" s="231" t="inlineStr">
         <is>
           <t>min sigma @ live ENTRY_Z</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="144">
-      <c r="B25" s="272" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="142">
+      <c r="B25" s="268" t="inlineStr">
         <is>
           <t>Legging the outrights</t>
         </is>
       </c>
-      <c r="C25" s="284">
-        <f>2*Config!$B$73*Config!$B$41+(2*$C$22)*1000*Config!$B$41</f>
-        <v/>
-      </c>
-      <c r="D25" s="285">
-        <f>Config!$B$46*$C$25/(0.5*3*1000*Config!$B$41)</f>
-        <v/>
-      </c>
-      <c r="E25" s="285">
-        <f>Config!$B$46*$C$25/(0.5*2.5*1000*Config!$B$41)</f>
-        <v/>
-      </c>
-      <c r="F25" s="285">
-        <f>Config!$B$46*$C$25/(0.5*Config!$B$34*1000*Config!$B$41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="144">
-      <c r="B26" s="272" t="inlineStr">
+      <c r="C25" s="280">
+        <f>2*Config!$B$74*Config!$B$41+(2*$C$22)*1000*Config!$B$41</f>
+        <v/>
+      </c>
+      <c r="D25" s="281">
+        <f>Config!$B$47*$C$25/(0.5*3*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+      <c r="E25" s="281">
+        <f>Config!$B$47*$C$25/(0.5*2.5*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+      <c r="F25" s="281">
+        <f>Config!$B$47*$C$25/(0.5*Config!$B$34*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="142">
+      <c r="B26" s="268" t="inlineStr">
         <is>
           <t>Listed inter-product spread</t>
         </is>
       </c>
-      <c r="C26" s="284">
-        <f>2*Config!$B$73*Config!$B$41+$F$22*1000*Config!$B$41</f>
-        <v/>
-      </c>
-      <c r="D26" s="285">
-        <f>Config!$B$46*$C$26/(0.5*3*1000*Config!$B$41)</f>
-        <v/>
-      </c>
-      <c r="E26" s="285">
-        <f>Config!$B$46*$C$26/(0.5*2.5*1000*Config!$B$41)</f>
-        <v/>
-      </c>
-      <c r="F26" s="285">
-        <f>Config!$B$46*$C$26/(0.5*Config!$B$34*1000*Config!$B$41)</f>
+      <c r="C26" s="280">
+        <f>2*Config!$B$74*Config!$B$41+$F$22*1000*Config!$B$41</f>
+        <v/>
+      </c>
+      <c r="D26" s="281">
+        <f>Config!$B$47*$C$26/(0.5*3*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+      <c r="E26" s="281">
+        <f>Config!$B$47*$C$26/(0.5*2.5*1000*Config!$B$41)</f>
+        <v/>
+      </c>
+      <c r="F26" s="281">
+        <f>Config!$B$47*$C$26/(0.5*Config!$B$34*1000*Config!$B$41)</f>
         <v/>
       </c>
     </row>
     <row r="27"/>
-    <row r="28" ht="15" customHeight="1" s="144">
-      <c r="B28" s="233" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="142">
+      <c r="B28" s="229" t="inlineStr">
         <is>
           <t>capture = 0.5 x |z| x sigma x USD-per-point x LOTS.  An entry passes when capture &gt;= EDGE_MULTIPLE x total cost.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="144">
-      <c r="B29" s="255" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="142">
+      <c r="B29" s="251" t="inlineStr">
         <is>
           <t>A lower ENTRY_Z means less expected capture per entry, so it RAISES the sigma the spread must have. 2.5 instead of 3.0 raises it by about 20%.</t>
         </is>
       </c>
     </row>
     <row r="30"/>
-    <row r="31" ht="15" customHeight="1" s="144">
-      <c r="B31" s="234" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="142">
+      <c r="B31" s="230" t="inlineStr">
         <is>
           <t>ASSUMPTIONS MADE WHILE BUILDING THIS - CHECK THEM</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="39.75" customHeight="1" s="144">
-      <c r="B32" s="283" t="inlineStr">
+    <row r="32" ht="39.75" customHeight="1" s="142">
+      <c r="B32" s="279" t="inlineStr">
         <is>
           <t>-  The repository was empty, so the existing Dashboard layout was reconstructed from the cell references given in the spec (C4, B6, C7, H7/H8, P7/P8, H12/H13/H14/I14, L3). Those coordinates are honoured exactly; the surrounding rows are a best reconstruction. Compare against your live sheet before relying on it.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="39.75" customHeight="1" s="144">
-      <c r="B33" s="283" t="inlineStr">
+    <row r="33" ht="39.75" customHeight="1" s="142">
+      <c r="B33" s="279" t="inlineStr">
         <is>
           <t>-  The 3:2:1 ask row now mirrors the bid row: I15 uses H14 (CL BID), not I14. The bid row is unchanged. This is the convention the spec described; confirm it is the one you want.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="39.75" customHeight="1" s="144">
-      <c r="B34" s="283" t="inlineStr">
+    <row r="34" ht="39.75" customHeight="1" s="142">
+      <c r="B34" s="279" t="inlineStr">
         <is>
           <t>-  COMMISSION_BASIS defaults to CONSERVATIVE ($3.82 per lot per leg round turn, reading CME's $1.50 as per side). Switch it to CME_PER_RT on Config if the rate card proves otherwise.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="39.75" customHeight="1" s="144">
-      <c r="B35" s="283" t="inlineStr">
+    <row r="35" ht="39.75" customHeight="1" s="142">
+      <c r="B35" s="279" t="inlineStr">
         <is>
           <t>-  Contracts charged commission: 2 for BZ-CL and the listed spread, 6 for the 3:2:1 crack (2 RB + 1 HO + 3 CL). Change it in the Config spread table if your clearing differs.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="39.75" customHeight="1" s="144">
-      <c r="B36" s="283" t="inlineStr">
+    <row r="36" ht="39.75" customHeight="1" s="142">
+      <c r="B36" s="279" t="inlineStr">
         <is>
           <t>-  Slot 3 (3:2:1) has no exchange-listed equivalent, so its LISTED crossing-cost column reads n/a.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="39.75" customHeight="1" s="144">
-      <c r="B37" s="283" t="inlineStr">
+    <row r="37" ht="39.75" customHeight="1" s="142">
+      <c r="B37" s="279" t="inlineStr">
         <is>
           <t>-  MIN_SIGMA ships at 0 because sigma on these spreads has never been measured. Set it once you have a session of data - until then the degenerate-window guard rests on MAX_ABS_Z alone.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="39.75" customHeight="1" s="144">
-      <c r="B38" s="283" t="inlineStr">
+    <row r="38" ht="39.75" customHeight="1" s="142">
+      <c r="B38" s="279" t="inlineStr">
         <is>
           <t>-  Application.OnTime cannot go below about one second, so capture at 100 ms runs on a user32 SetTimer with an OnTime watchdog that re-arms it (Excel silently kills API timers when a modal dialog opens). If SetTimer is unavailable, CAPTURE_MS is clamped to 1000 and everything still works - only alert latency changes, not the statistics.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="39.75" customHeight="1" s="144">
-      <c r="B39" s="283" t="inlineStr">
+    <row r="39" ht="39.75" customHeight="1" s="142">
+      <c r="B39" s="279" t="inlineStr">
         <is>
           <t>-  Capturing at 100 ms does not mean storing at 100 ms, and after dedupe it does not change sigma either. The window holds quote CHANGES, not poll ticks; subsampling a mean-reverting level series is unbiased. 100 ms buys latency to the chime, which for manual execution is not measurable in human terms - so the real reason to capture fast is simply that no genuine quote change is missed.</t>
         </is>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -416,6 +416,14 @@
       <charset val="1"/>
       <family val="0"/>
       <b val="1"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
       <color rgb="FF1F3864"/>
       <sz val="10"/>
     </font>
@@ -601,7 +609,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="282">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -968,6 +976,9 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="164" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
@@ -989,13 +1000,13 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="1" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1004,7 +1015,7 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1385,6 +1396,9 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="164" fontId="47" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
@@ -1403,17 +1417,17 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="1" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1422,7 +1436,7 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1814,853 +1828,853 @@
   <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col hidden="1" width="2.14" customWidth="1" style="140" min="1" max="1"/>
-    <col hidden="1" width="11" customWidth="1" style="140" min="2" max="2"/>
-    <col hidden="1" width="30.43" customWidth="1" style="140" min="3" max="3"/>
-    <col width="3.43" customWidth="1" style="140" min="4" max="5"/>
-    <col width="16.14" customWidth="1" style="141" min="6" max="6"/>
-    <col hidden="1" width="30.57" customWidth="1" style="140" min="7" max="7"/>
-    <col width="17" customWidth="1" style="140" min="8" max="10"/>
-    <col width="17.43" customWidth="1" style="140" min="11" max="12"/>
-    <col width="2" customWidth="1" style="140" min="13" max="13"/>
-    <col width="17.57" customWidth="1" style="140" min="14" max="14"/>
-    <col hidden="1" width="16.72" customWidth="1" style="140" min="15" max="15"/>
-    <col width="18.29" customWidth="1" style="140" min="16" max="18"/>
-    <col width="16.43" customWidth="1" style="140" min="19" max="20"/>
-    <col width="17.29" customWidth="1" style="140" min="24" max="24"/>
-    <col width="14.29" customWidth="1" style="140" min="25" max="26"/>
-    <col width="11.43" customWidth="1" style="140" min="27" max="27"/>
+    <col hidden="1" width="2.14" customWidth="1" style="141" min="1" max="1"/>
+    <col hidden="1" width="11" customWidth="1" style="141" min="2" max="2"/>
+    <col hidden="1" width="30.43" customWidth="1" style="141" min="3" max="3"/>
+    <col width="3.43" customWidth="1" style="141" min="4" max="5"/>
+    <col width="16.14" customWidth="1" style="142" min="6" max="6"/>
+    <col hidden="1" width="30.57" customWidth="1" style="141" min="7" max="7"/>
+    <col width="17" customWidth="1" style="141" min="8" max="10"/>
+    <col width="17.43" customWidth="1" style="141" min="11" max="12"/>
+    <col width="2" customWidth="1" style="141" min="13" max="13"/>
+    <col width="17.57" customWidth="1" style="141" min="14" max="14"/>
+    <col hidden="1" width="16.72" customWidth="1" style="141" min="15" max="15"/>
+    <col width="18.29" customWidth="1" style="141" min="16" max="18"/>
+    <col width="16.43" customWidth="1" style="141" min="19" max="20"/>
+    <col width="17.29" customWidth="1" style="141" min="24" max="24"/>
+    <col width="14.29" customWidth="1" style="141" min="25" max="26"/>
+    <col width="11.43" customWidth="1" style="141" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2" ht="68.25" customHeight="1" s="142">
-      <c r="A2" s="143" t="n"/>
-      <c r="B2" s="144" t="n"/>
-      <c r="C2" s="145" t="inlineStr">
+    <row r="2" ht="68.25" customHeight="1" s="143">
+      <c r="A2" s="144" t="n"/>
+      <c r="B2" s="145" t="n"/>
+      <c r="C2" s="146" t="inlineStr">
         <is>
           <t>ENERGY FUTURES BID / ASK SPREAD MONITOR</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="142">
-      <c r="A3" s="143" t="n"/>
-      <c r="B3" s="146" t="n"/>
-      <c r="C3" s="147" t="n"/>
-      <c r="F3" s="148" t="n"/>
-      <c r="G3" s="149" t="n"/>
-      <c r="L3" s="150" t="n"/>
-    </row>
-    <row r="4" ht="6.75" customHeight="1" s="142">
-      <c r="A4" s="143" t="n"/>
-      <c r="B4" s="151" t="inlineStr">
+    <row r="3" ht="21.75" customHeight="1" s="143">
+      <c r="A3" s="144" t="n"/>
+      <c r="B3" s="147" t="n"/>
+      <c r="C3" s="148" t="n"/>
+      <c r="F3" s="149" t="n"/>
+      <c r="G3" s="150" t="n"/>
+      <c r="L3" s="151" t="n"/>
+    </row>
+    <row r="4" ht="6.75" customHeight="1" s="143">
+      <c r="A4" s="144" t="n"/>
+      <c r="B4" s="152" t="inlineStr">
         <is>
           <t>TT MARKET</t>
         </is>
       </c>
-      <c r="C4" s="151" t="inlineStr">
+      <c r="C4" s="152" t="inlineStr">
         <is>
           <t>CME</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="6.75" customHeight="1" s="142">
-      <c r="A5" s="143" t="n"/>
-      <c r="B5" s="152" t="inlineStr">
+    <row r="5" ht="6.75" customHeight="1" s="143">
+      <c r="A5" s="144" t="n"/>
+      <c r="B5" s="153" t="inlineStr">
         <is>
           <t>TT SHORT NAME</t>
         </is>
       </c>
-      <c r="C5" s="152" t="inlineStr">
+      <c r="C5" s="153" t="inlineStr">
         <is>
           <t>INSTRUMENT ID</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="23.25" customHeight="1" s="142">
-      <c r="A6" s="143" t="n"/>
-      <c r="B6" s="151" t="inlineStr">
+    <row r="6" ht="23.25" customHeight="1" s="143">
+      <c r="A6" s="144" t="n"/>
+      <c r="B6" s="152" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="C6" s="153" t="n"/>
-      <c r="F6" s="154" t="inlineStr">
+      <c r="C6" s="154" t="n"/>
+      <c r="F6" s="155" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="G6" s="155" t="inlineStr">
+      <c r="G6" s="156" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H6" s="155" t="inlineStr">
+      <c r="H6" s="156" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I6" s="155" t="inlineStr">
+      <c r="I6" s="156" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J6" s="155" t="inlineStr">
+      <c r="J6" s="156" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="K6" s="155" t="inlineStr">
+      <c r="K6" s="156" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L6" s="156" t="inlineStr">
+      <c r="L6" s="157" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M6" s="157" t="n"/>
-      <c r="N6" s="154" t="inlineStr">
+      <c r="M6" s="158" t="n"/>
+      <c r="N6" s="155" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="O6" s="155" t="inlineStr">
+      <c r="O6" s="156" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="P6" s="155" t="inlineStr">
+      <c r="P6" s="156" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="Q6" s="155" t="inlineStr">
+      <c r="Q6" s="156" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="R6" s="155" t="inlineStr">
+      <c r="R6" s="156" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="S6" s="155" t="inlineStr">
+      <c r="S6" s="156" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T6" s="156" t="inlineStr">
+      <c r="T6" s="157" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="U6" s="158" t="n"/>
-      <c r="V6" s="158" t="n"/>
-    </row>
-    <row r="7" ht="55.5" customHeight="1" s="142">
-      <c r="A7" s="143" t="n"/>
-      <c r="B7" s="151" t="inlineStr">
+      <c r="U6" s="159" t="n"/>
+      <c r="V6" s="159" t="n"/>
+    </row>
+    <row r="7" ht="55.5" customHeight="1" s="143">
+      <c r="A7" s="144" t="n"/>
+      <c r="B7" s="152" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="C7" s="153" t="n"/>
-      <c r="D7" s="159" t="n"/>
-      <c r="E7" s="159" t="n"/>
-      <c r="F7" s="160" t="inlineStr">
+      <c r="C7" s="154" t="n"/>
+      <c r="D7" s="160" t="n"/>
+      <c r="E7" s="160" t="n"/>
+      <c r="F7" s="161" t="inlineStr">
         <is>
           <t>HOV26
 HO Oct 26</t>
         </is>
       </c>
-      <c r="G7" s="161" t="inlineStr">
+      <c r="G7" s="162" t="inlineStr">
         <is>
           <t>HO Oct 26</t>
         </is>
       </c>
-      <c r="H7" s="162" t="n"/>
-      <c r="I7" s="163" t="n"/>
-      <c r="J7" s="164" t="n"/>
-      <c r="K7" s="165" t="n"/>
-      <c r="L7" s="166" t="n"/>
-      <c r="M7" s="167" t="n"/>
-      <c r="N7" s="160" t="inlineStr">
+      <c r="H7" s="163" t="n"/>
+      <c r="I7" s="164" t="n"/>
+      <c r="J7" s="165" t="n"/>
+      <c r="K7" s="166" t="n"/>
+      <c r="L7" s="167" t="n"/>
+      <c r="M7" s="168" t="n"/>
+      <c r="N7" s="161" t="inlineStr">
         <is>
           <t>BZV26
 BZ Oct 26</t>
         </is>
       </c>
-      <c r="O7" s="161" t="inlineStr">
+      <c r="O7" s="162" t="inlineStr">
         <is>
           <t>BZ Oct 26</t>
         </is>
       </c>
-      <c r="P7" s="162" t="n"/>
-      <c r="Q7" s="162" t="n"/>
-      <c r="R7" s="168" t="n"/>
-      <c r="S7" s="165" t="n"/>
-      <c r="T7" s="166" t="n"/>
-      <c r="U7" s="158" t="n"/>
-      <c r="V7" s="158" t="n"/>
-    </row>
-    <row r="8" ht="55.5" customHeight="1" s="142">
-      <c r="A8" s="143" t="n"/>
-      <c r="B8" s="151" t="inlineStr">
+      <c r="P7" s="163" t="n"/>
+      <c r="Q7" s="163" t="n"/>
+      <c r="R7" s="169" t="n"/>
+      <c r="S7" s="166" t="n"/>
+      <c r="T7" s="167" t="n"/>
+      <c r="U7" s="159" t="n"/>
+      <c r="V7" s="159" t="n"/>
+    </row>
+    <row r="8" ht="55.5" customHeight="1" s="143">
+      <c r="A8" s="144" t="n"/>
+      <c r="B8" s="152" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="C8" s="153" t="n"/>
-      <c r="D8" s="159" t="n"/>
-      <c r="E8" s="159" t="n"/>
-      <c r="F8" s="169" t="inlineStr">
+      <c r="C8" s="154" t="n"/>
+      <c r="D8" s="160" t="n"/>
+      <c r="E8" s="160" t="n"/>
+      <c r="F8" s="170" t="inlineStr">
         <is>
           <t>CLV26
 CL Oct 26</t>
         </is>
       </c>
-      <c r="G8" s="170" t="inlineStr">
+      <c r="G8" s="171" t="inlineStr">
         <is>
           <t>CL Oct 26</t>
         </is>
       </c>
-      <c r="H8" s="171" t="n"/>
-      <c r="I8" s="171" t="n"/>
-      <c r="J8" s="172" t="n"/>
-      <c r="K8" s="173" t="n"/>
-      <c r="L8" s="174" t="n"/>
-      <c r="M8" s="167" t="n"/>
-      <c r="N8" s="169" t="inlineStr">
+      <c r="H8" s="172" t="n"/>
+      <c r="I8" s="172" t="n"/>
+      <c r="J8" s="173" t="n"/>
+      <c r="K8" s="174" t="n"/>
+      <c r="L8" s="175" t="n"/>
+      <c r="M8" s="168" t="n"/>
+      <c r="N8" s="170" t="inlineStr">
         <is>
           <t>CLV26
 CL Oct 26</t>
         </is>
       </c>
-      <c r="O8" s="170" t="inlineStr">
+      <c r="O8" s="171" t="inlineStr">
         <is>
           <t>CL Oct 26</t>
         </is>
       </c>
-      <c r="P8" s="171" t="n"/>
-      <c r="Q8" s="171" t="n"/>
-      <c r="R8" s="172" t="n"/>
-      <c r="S8" s="173" t="n"/>
-      <c r="T8" s="174" t="n"/>
-      <c r="U8" s="158" t="n"/>
-      <c r="V8" s="158" t="n"/>
-    </row>
-    <row r="9" ht="55.5" customHeight="1" s="142">
-      <c r="A9" s="143" t="n"/>
-      <c r="B9" s="151" t="inlineStr">
+      <c r="P8" s="172" t="n"/>
+      <c r="Q8" s="172" t="n"/>
+      <c r="R8" s="173" t="n"/>
+      <c r="S8" s="174" t="n"/>
+      <c r="T8" s="175" t="n"/>
+      <c r="U8" s="159" t="n"/>
+      <c r="V8" s="159" t="n"/>
+    </row>
+    <row r="9" ht="55.5" customHeight="1" s="143">
+      <c r="A9" s="144" t="n"/>
+      <c r="B9" s="152" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="C9" s="153" t="n"/>
-      <c r="D9" s="159" t="n"/>
-      <c r="E9" s="159" t="n"/>
-      <c r="F9" s="175" t="inlineStr">
+      <c r="C9" s="154" t="n"/>
+      <c r="D9" s="160" t="n"/>
+      <c r="E9" s="160" t="n"/>
+      <c r="F9" s="176" t="inlineStr">
         <is>
           <t>HO | CL Oct 26 Crack</t>
         </is>
       </c>
-      <c r="G9" s="176" t="n"/>
-      <c r="H9" s="177" t="n"/>
-      <c r="I9" s="177" t="n"/>
-      <c r="J9" s="178" t="n"/>
-      <c r="K9" s="177" t="n"/>
-      <c r="L9" s="179" t="n"/>
-      <c r="M9" s="167" t="n"/>
-      <c r="N9" s="180" t="inlineStr">
+      <c r="G9" s="177" t="n"/>
+      <c r="H9" s="178" t="n"/>
+      <c r="I9" s="178" t="n"/>
+      <c r="J9" s="179" t="n"/>
+      <c r="K9" s="178" t="n"/>
+      <c r="L9" s="180" t="n"/>
+      <c r="M9" s="168" t="n"/>
+      <c r="N9" s="181" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="O9" s="181" t="n"/>
-      <c r="P9" s="177" t="n"/>
-      <c r="Q9" s="177" t="n"/>
-      <c r="R9" s="178" t="n"/>
-      <c r="S9" s="177" t="n"/>
-      <c r="T9" s="179" t="n"/>
-      <c r="U9" s="158" t="n"/>
-      <c r="V9" s="158" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" s="142">
-      <c r="A10" s="143" t="n"/>
-      <c r="B10" s="182" t="inlineStr">
+      <c r="O9" s="182" t="n"/>
+      <c r="P9" s="178" t="n"/>
+      <c r="Q9" s="178" t="n"/>
+      <c r="R9" s="179" t="n"/>
+      <c r="S9" s="178" t="n"/>
+      <c r="T9" s="180" t="n"/>
+      <c r="U9" s="159" t="n"/>
+      <c r="V9" s="159" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="143">
+      <c r="A10" s="144" t="n"/>
+      <c r="B10" s="183" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="C10" s="153" t="n"/>
-      <c r="D10" s="159" t="n"/>
-      <c r="E10" s="159" t="n"/>
-      <c r="F10" s="167" t="n"/>
-      <c r="G10" s="167" t="n"/>
-      <c r="H10" s="167" t="n"/>
-      <c r="I10" s="167" t="n"/>
-      <c r="J10" s="167" t="n"/>
-      <c r="K10" s="167" t="n"/>
-      <c r="L10" s="167" t="n"/>
-      <c r="M10" s="167" t="n"/>
-      <c r="N10" s="158" t="n"/>
-      <c r="O10" s="158" t="n"/>
-      <c r="P10" s="158" t="n"/>
-      <c r="Q10" s="158" t="n"/>
-      <c r="R10" s="158" t="n"/>
-      <c r="S10" s="158" t="n"/>
-      <c r="T10" s="158" t="n"/>
-      <c r="U10" s="158" t="n"/>
-      <c r="V10" s="158" t="n"/>
-    </row>
-    <row r="11" ht="42" customHeight="1" s="142">
-      <c r="A11" s="143" t="n"/>
-      <c r="B11" s="182" t="n"/>
-      <c r="C11" s="153" t="n"/>
-      <c r="D11" s="159" t="n"/>
-      <c r="E11" s="159" t="n"/>
-      <c r="F11" s="154" t="inlineStr">
+      <c r="C10" s="154" t="n"/>
+      <c r="D10" s="160" t="n"/>
+      <c r="E10" s="160" t="n"/>
+      <c r="F10" s="168" t="n"/>
+      <c r="G10" s="168" t="n"/>
+      <c r="H10" s="168" t="n"/>
+      <c r="I10" s="168" t="n"/>
+      <c r="J10" s="168" t="n"/>
+      <c r="K10" s="168" t="n"/>
+      <c r="L10" s="168" t="n"/>
+      <c r="M10" s="168" t="n"/>
+      <c r="N10" s="159" t="n"/>
+      <c r="O10" s="159" t="n"/>
+      <c r="P10" s="159" t="n"/>
+      <c r="Q10" s="159" t="n"/>
+      <c r="R10" s="159" t="n"/>
+      <c r="S10" s="159" t="n"/>
+      <c r="T10" s="159" t="n"/>
+      <c r="U10" s="159" t="n"/>
+      <c r="V10" s="159" t="n"/>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="143">
+      <c r="A11" s="144" t="n"/>
+      <c r="B11" s="183" t="n"/>
+      <c r="C11" s="154" t="n"/>
+      <c r="D11" s="160" t="n"/>
+      <c r="E11" s="160" t="n"/>
+      <c r="F11" s="155" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="G11" s="155" t="inlineStr">
+      <c r="G11" s="156" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H11" s="155" t="inlineStr">
+      <c r="H11" s="156" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I11" s="155" t="inlineStr">
+      <c r="I11" s="156" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J11" s="155" t="inlineStr">
+      <c r="J11" s="156" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="K11" s="155" t="inlineStr">
+      <c r="K11" s="156" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L11" s="156" t="inlineStr">
+      <c r="L11" s="157" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M11" s="167" t="n"/>
-      <c r="N11" s="183" t="n"/>
-      <c r="O11" s="184" t="n"/>
-      <c r="P11" s="185" t="n"/>
-      <c r="Q11" s="185" t="n"/>
-      <c r="R11" s="172" t="n"/>
-      <c r="S11" s="186" t="n"/>
-      <c r="T11" s="186" t="n"/>
-      <c r="U11" s="158" t="n"/>
-      <c r="V11" s="158" t="n"/>
-    </row>
-    <row r="12" ht="50.25" customHeight="1" s="142">
-      <c r="A12" s="143" t="n"/>
-      <c r="B12" s="182" t="inlineStr">
+      <c r="M11" s="168" t="n"/>
+      <c r="N11" s="184" t="n"/>
+      <c r="O11" s="185" t="n"/>
+      <c r="P11" s="186" t="n"/>
+      <c r="Q11" s="186" t="n"/>
+      <c r="R11" s="173" t="n"/>
+      <c r="S11" s="187" t="n"/>
+      <c r="T11" s="187" t="n"/>
+      <c r="U11" s="159" t="n"/>
+      <c r="V11" s="159" t="n"/>
+    </row>
+    <row r="12" ht="50.25" customHeight="1" s="143">
+      <c r="A12" s="144" t="n"/>
+      <c r="B12" s="183" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="C12" s="153" t="n"/>
-      <c r="D12" s="159" t="n"/>
-      <c r="E12" s="159" t="n"/>
-      <c r="F12" s="187" t="inlineStr">
+      <c r="C12" s="154" t="n"/>
+      <c r="D12" s="160" t="n"/>
+      <c r="E12" s="160" t="n"/>
+      <c r="F12" s="188" t="inlineStr">
         <is>
           <t>RBV26</t>
         </is>
       </c>
-      <c r="G12" s="161" t="inlineStr">
+      <c r="G12" s="162" t="inlineStr">
         <is>
           <t>RB Oct 26</t>
         </is>
       </c>
-      <c r="H12" s="162" t="n"/>
-      <c r="I12" s="162" t="n"/>
-      <c r="J12" s="164" t="n"/>
-      <c r="K12" s="165" t="n"/>
-      <c r="L12" s="166" t="n"/>
-      <c r="M12" s="167" t="n"/>
-      <c r="N12" s="167" t="n"/>
-      <c r="O12" s="167" t="n"/>
-      <c r="P12" s="167" t="n"/>
-      <c r="Q12" s="167" t="n"/>
-      <c r="R12" s="167" t="n"/>
-      <c r="S12" s="188" t="n"/>
-      <c r="T12" s="188" t="n"/>
-      <c r="U12" s="158" t="n"/>
-      <c r="V12" s="158" t="n"/>
-    </row>
-    <row r="13" ht="50.25" customHeight="1" s="142">
-      <c r="A13" s="143" t="n"/>
-      <c r="D13" s="159" t="n"/>
-      <c r="E13" s="159" t="n"/>
-      <c r="F13" s="189" t="inlineStr">
+      <c r="H12" s="163" t="n"/>
+      <c r="I12" s="163" t="n"/>
+      <c r="J12" s="165" t="n"/>
+      <c r="K12" s="166" t="n"/>
+      <c r="L12" s="167" t="n"/>
+      <c r="M12" s="168" t="n"/>
+      <c r="N12" s="168" t="n"/>
+      <c r="O12" s="168" t="n"/>
+      <c r="P12" s="168" t="n"/>
+      <c r="Q12" s="168" t="n"/>
+      <c r="R12" s="168" t="n"/>
+      <c r="S12" s="189" t="n"/>
+      <c r="T12" s="189" t="n"/>
+      <c r="U12" s="159" t="n"/>
+      <c r="V12" s="159" t="n"/>
+    </row>
+    <row r="13" ht="50.25" customHeight="1" s="143">
+      <c r="A13" s="144" t="n"/>
+      <c r="D13" s="160" t="n"/>
+      <c r="E13" s="160" t="n"/>
+      <c r="F13" s="190" t="inlineStr">
         <is>
           <t>HOV26</t>
         </is>
       </c>
-      <c r="G13" s="170" t="inlineStr">
+      <c r="G13" s="171" t="inlineStr">
         <is>
           <t>HO Oct 26</t>
         </is>
       </c>
-      <c r="H13" s="171" t="n"/>
-      <c r="I13" s="171" t="n"/>
-      <c r="J13" s="190" t="n"/>
-      <c r="K13" s="173" t="n"/>
-      <c r="L13" s="174" t="n"/>
-      <c r="M13" s="167" t="n"/>
-      <c r="N13" s="191" t="n"/>
-      <c r="O13" s="191" t="n"/>
-      <c r="P13" s="191" t="n"/>
-      <c r="Q13" s="191" t="n"/>
-      <c r="R13" s="191" t="n"/>
-      <c r="S13" s="191" t="n"/>
-      <c r="T13" s="191" t="n"/>
-      <c r="U13" s="158" t="n"/>
-      <c r="V13" s="158" t="n"/>
-    </row>
-    <row r="14" ht="50.25" customHeight="1" s="142">
-      <c r="A14" s="143" t="n"/>
-      <c r="D14" s="159" t="n"/>
-      <c r="E14" s="159" t="n"/>
-      <c r="F14" s="187" t="inlineStr">
+      <c r="H13" s="172" t="n"/>
+      <c r="I13" s="172" t="n"/>
+      <c r="J13" s="191" t="n"/>
+      <c r="K13" s="174" t="n"/>
+      <c r="L13" s="175" t="n"/>
+      <c r="M13" s="168" t="n"/>
+      <c r="N13" s="192" t="n"/>
+      <c r="O13" s="192" t="n"/>
+      <c r="P13" s="192" t="n"/>
+      <c r="Q13" s="192" t="n"/>
+      <c r="R13" s="192" t="n"/>
+      <c r="S13" s="192" t="n"/>
+      <c r="T13" s="192" t="n"/>
+      <c r="U13" s="159" t="n"/>
+      <c r="V13" s="159" t="n"/>
+    </row>
+    <row r="14" ht="50.25" customHeight="1" s="143">
+      <c r="A14" s="144" t="n"/>
+      <c r="D14" s="160" t="n"/>
+      <c r="E14" s="160" t="n"/>
+      <c r="F14" s="188" t="inlineStr">
         <is>
           <t>CLV26</t>
         </is>
       </c>
-      <c r="G14" s="161" t="inlineStr">
+      <c r="G14" s="162" t="inlineStr">
         <is>
           <t>CL Oct 26</t>
         </is>
       </c>
-      <c r="H14" s="162" t="n"/>
-      <c r="I14" s="162" t="n"/>
-      <c r="J14" s="168" t="n"/>
-      <c r="K14" s="165" t="n"/>
-      <c r="L14" s="166" t="n"/>
-      <c r="M14" s="167" t="n"/>
-      <c r="N14" s="192" t="n"/>
-      <c r="O14" s="193" t="n"/>
-      <c r="P14" s="194" t="n"/>
-      <c r="Q14" s="194" t="n"/>
-      <c r="R14" s="195" t="n"/>
-      <c r="S14" s="196" t="n"/>
-      <c r="T14" s="196" t="n"/>
-      <c r="U14" s="158" t="n"/>
-      <c r="V14" s="158" t="n"/>
-    </row>
-    <row r="15" ht="50.25" customHeight="1" s="142">
-      <c r="A15" s="143" t="n"/>
-      <c r="D15" s="159" t="n"/>
-      <c r="E15" s="159" t="n"/>
-      <c r="F15" s="197" t="inlineStr">
+      <c r="H14" s="163" t="n"/>
+      <c r="I14" s="163" t="n"/>
+      <c r="J14" s="169" t="n"/>
+      <c r="K14" s="166" t="n"/>
+      <c r="L14" s="167" t="n"/>
+      <c r="M14" s="168" t="n"/>
+      <c r="N14" s="193" t="n"/>
+      <c r="O14" s="194" t="n"/>
+      <c r="P14" s="195" t="n"/>
+      <c r="Q14" s="195" t="n"/>
+      <c r="R14" s="196" t="n"/>
+      <c r="S14" s="197" t="n"/>
+      <c r="T14" s="197" t="n"/>
+      <c r="U14" s="159" t="n"/>
+      <c r="V14" s="159" t="n"/>
+    </row>
+    <row r="15" ht="50.25" customHeight="1" s="143">
+      <c r="A15" s="144" t="n"/>
+      <c r="D15" s="160" t="n"/>
+      <c r="E15" s="160" t="n"/>
+      <c r="F15" s="198" t="inlineStr">
         <is>
           <t>3:2:1</t>
         </is>
       </c>
-      <c r="G15" s="198" t="n"/>
-      <c r="H15" s="199" t="n"/>
-      <c r="I15" s="199" t="n"/>
-      <c r="J15" s="200" t="n"/>
-      <c r="K15" s="199" t="n"/>
-      <c r="L15" s="201" t="n"/>
-      <c r="M15" s="167" t="n"/>
-      <c r="N15" s="192" t="n"/>
-      <c r="O15" s="193" t="n"/>
-      <c r="P15" s="194" t="n"/>
-      <c r="Q15" s="194" t="n"/>
-      <c r="R15" s="195" t="n"/>
-      <c r="S15" s="196" t="n"/>
-      <c r="T15" s="196" t="n"/>
-      <c r="U15" s="158" t="n"/>
-      <c r="V15" s="158" t="n"/>
-    </row>
-    <row r="16" ht="42" customHeight="1" s="142">
-      <c r="A16" s="143" t="n"/>
-      <c r="D16" s="159" t="n"/>
-      <c r="E16" s="159" t="n"/>
-      <c r="F16" s="202" t="n"/>
-      <c r="G16" s="203" t="n"/>
-      <c r="H16" s="203" t="n"/>
-      <c r="I16" s="203" t="n"/>
-      <c r="J16" s="203" t="n"/>
-      <c r="K16" s="203" t="n"/>
-      <c r="L16" s="203" t="n"/>
-      <c r="M16" s="203" t="n"/>
-      <c r="S16" s="204" t="n"/>
-      <c r="T16" s="204" t="n"/>
-    </row>
-    <row r="17" ht="44.25" customHeight="1" s="142">
-      <c r="A17" s="143" t="n"/>
-      <c r="F17" s="205" t="inlineStr">
+      <c r="G15" s="199" t="n"/>
+      <c r="H15" s="200" t="n"/>
+      <c r="I15" s="200" t="n"/>
+      <c r="J15" s="201" t="n"/>
+      <c r="K15" s="200" t="n"/>
+      <c r="L15" s="202" t="n"/>
+      <c r="M15" s="168" t="n"/>
+      <c r="N15" s="193" t="n"/>
+      <c r="O15" s="194" t="n"/>
+      <c r="P15" s="195" t="n"/>
+      <c r="Q15" s="195" t="n"/>
+      <c r="R15" s="196" t="n"/>
+      <c r="S15" s="197" t="n"/>
+      <c r="T15" s="197" t="n"/>
+      <c r="U15" s="159" t="n"/>
+      <c r="V15" s="159" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1" s="143">
+      <c r="A16" s="144" t="n"/>
+      <c r="D16" s="160" t="n"/>
+      <c r="E16" s="160" t="n"/>
+      <c r="F16" s="203" t="n"/>
+      <c r="G16" s="204" t="n"/>
+      <c r="H16" s="204" t="n"/>
+      <c r="I16" s="204" t="n"/>
+      <c r="J16" s="204" t="n"/>
+      <c r="K16" s="204" t="n"/>
+      <c r="L16" s="204" t="n"/>
+      <c r="M16" s="204" t="n"/>
+      <c r="S16" s="205" t="n"/>
+      <c r="T16" s="205" t="n"/>
+    </row>
+    <row r="17" ht="44.25" customHeight="1" s="143">
+      <c r="A17" s="144" t="n"/>
+      <c r="F17" s="206" t="inlineStr">
         <is>
           <t>Z-SCORE MONITOR      z is for ENTRIES only - exits act on money, never on z.      The chime fires on the CROSSING of ENTRY_Z, once.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="23.25" customHeight="1" s="142">
-      <c r="A18" s="143" t="n"/>
-      <c r="F18" s="206" t="inlineStr">
+    <row r="18" ht="23.25" customHeight="1" s="143">
+      <c r="A18" s="144" t="n"/>
+      <c r="F18" s="207" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="H18" s="206" t="inlineStr">
+      <c r="H18" s="207" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I18" s="206" t="inlineStr">
+      <c r="I18" s="207" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="J18" s="206" t="inlineStr">
+      <c r="J18" s="207" t="inlineStr">
         <is>
           <t>Z-score</t>
         </is>
       </c>
-      <c r="K18" s="206" t="inlineStr">
+      <c r="K18" s="207" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="L18" s="206" t="inlineStr">
+      <c r="L18" s="207" t="inlineStr">
         <is>
           <t>Std Dev</t>
         </is>
       </c>
-      <c r="N18" s="206" t="inlineStr">
+      <c r="N18" s="207" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="P18" s="206" t="inlineStr">
+      <c r="P18" s="207" t="inlineStr">
         <is>
           <t>Window</t>
         </is>
       </c>
-      <c r="Q18" s="206" t="inlineStr">
+      <c r="Q18" s="207" t="inlineStr">
         <is>
           <t>Costs $</t>
         </is>
       </c>
-      <c r="R18" s="206" t="inlineStr">
+      <c r="R18" s="207" t="inlineStr">
         <is>
           <t>Win $</t>
         </is>
       </c>
-      <c r="S18" s="206" t="inlineStr">
+      <c r="S18" s="207" t="inlineStr">
         <is>
           <t>TAKE PROFIT</t>
         </is>
       </c>
-      <c r="T18" s="206" t="inlineStr">
+      <c r="T18" s="207" t="inlineStr">
         <is>
           <t>TP in sigma</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="50.25" customHeight="1" s="142">
-      <c r="A19" s="143" t="n"/>
-      <c r="F19" s="207" t="inlineStr">
+    <row r="19" ht="50.25" customHeight="1" s="143">
+      <c r="A19" s="144" t="n"/>
+      <c r="F19" s="208" t="inlineStr">
         <is>
           <t>HO | CL Crack</t>
         </is>
       </c>
-      <c r="H19" s="208" t="n"/>
-      <c r="I19" s="209" t="n"/>
-      <c r="J19" s="210" t="n"/>
-      <c r="K19" s="211" t="n"/>
-      <c r="L19" s="211" t="n"/>
-      <c r="N19" s="209" t="n"/>
-      <c r="P19" s="209" t="n"/>
-      <c r="Q19" s="212" t="n"/>
-      <c r="R19" s="212" t="n"/>
-      <c r="S19" s="208" t="n"/>
-      <c r="T19" s="213" t="n"/>
-    </row>
-    <row r="20" ht="50.25" customHeight="1" s="142">
-      <c r="A20" s="143" t="n"/>
-      <c r="F20" s="207" t="inlineStr">
+      <c r="H19" s="209" t="n"/>
+      <c r="I19" s="210" t="n"/>
+      <c r="J19" s="211" t="n"/>
+      <c r="K19" s="212" t="n"/>
+      <c r="L19" s="212" t="n"/>
+      <c r="N19" s="210" t="n"/>
+      <c r="P19" s="210" t="n"/>
+      <c r="Q19" s="213" t="n"/>
+      <c r="R19" s="213" t="n"/>
+      <c r="S19" s="209" t="n"/>
+      <c r="T19" s="214" t="n"/>
+    </row>
+    <row r="20" ht="50.25" customHeight="1" s="143">
+      <c r="A20" s="144" t="n"/>
+      <c r="F20" s="208" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="H20" s="208" t="n"/>
-      <c r="I20" s="209" t="n"/>
-      <c r="J20" s="210" t="n"/>
-      <c r="K20" s="211" t="n"/>
-      <c r="L20" s="211" t="n"/>
-      <c r="N20" s="209" t="n"/>
-      <c r="P20" s="209" t="n"/>
-      <c r="Q20" s="212" t="n"/>
-      <c r="R20" s="212" t="n"/>
-      <c r="S20" s="208" t="n"/>
-      <c r="T20" s="213" t="n"/>
-    </row>
-    <row r="21" ht="50.25" customHeight="1" s="142">
-      <c r="A21" s="143" t="n"/>
-      <c r="F21" s="214" t="inlineStr">
+      <c r="H20" s="209" t="n"/>
+      <c r="I20" s="210" t="n"/>
+      <c r="J20" s="211" t="n"/>
+      <c r="K20" s="212" t="n"/>
+      <c r="L20" s="212" t="n"/>
+      <c r="N20" s="210" t="n"/>
+      <c r="P20" s="210" t="n"/>
+      <c r="Q20" s="213" t="n"/>
+      <c r="R20" s="213" t="n"/>
+      <c r="S20" s="209" t="n"/>
+      <c r="T20" s="214" t="n"/>
+    </row>
+    <row r="21" ht="50.25" customHeight="1" s="143">
+      <c r="A21" s="144" t="n"/>
+      <c r="F21" s="215" t="inlineStr">
         <is>
           <t>3:2:1</t>
         </is>
       </c>
-      <c r="H21" s="215" t="n"/>
-      <c r="I21" s="216" t="n"/>
-      <c r="J21" s="217" t="n"/>
-      <c r="K21" s="218" t="n"/>
-      <c r="L21" s="218" t="n"/>
-      <c r="N21" s="216" t="n"/>
-      <c r="P21" s="216" t="n"/>
-      <c r="Q21" s="219" t="n"/>
-      <c r="R21" s="219" t="n"/>
-      <c r="S21" s="215" t="n"/>
-      <c r="T21" s="220" t="n"/>
-    </row>
-    <row r="22" ht="36" customHeight="1" s="142">
-      <c r="A22" s="143" t="n"/>
-      <c r="F22" s="221" t="n"/>
-      <c r="G22" s="222" t="n"/>
-      <c r="H22" s="222" t="n"/>
-      <c r="I22" s="222" t="n"/>
-      <c r="J22" s="222" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1" s="142">
-      <c r="A23" s="143" t="n"/>
-      <c r="F23" s="223" t="inlineStr">
+      <c r="H21" s="216" t="n"/>
+      <c r="I21" s="217" t="n"/>
+      <c r="J21" s="218" t="n"/>
+      <c r="K21" s="219" t="n"/>
+      <c r="L21" s="219" t="n"/>
+      <c r="N21" s="217" t="n"/>
+      <c r="P21" s="217" t="n"/>
+      <c r="Q21" s="220" t="n"/>
+      <c r="R21" s="220" t="n"/>
+      <c r="S21" s="216" t="n"/>
+      <c r="T21" s="221" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="143">
+      <c r="A22" s="144" t="n"/>
+      <c r="F22" s="222" t="n"/>
+      <c r="G22" s="223" t="n"/>
+      <c r="H22" s="223" t="n"/>
+      <c r="I22" s="223" t="n"/>
+      <c r="J22" s="223" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="143">
+      <c r="A23" s="144" t="n"/>
+      <c r="F23" s="224" t="inlineStr">
         <is>
           <t>STOPPED</t>
         </is>
       </c>
-      <c r="G23" s="222" t="n"/>
-      <c r="H23" s="224" t="inlineStr">
+      <c r="G23" s="223" t="n"/>
+      <c r="H23" s="225" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="222" t="n"/>
-      <c r="J23" s="222" t="n"/>
-      <c r="N23" s="225" t="inlineStr">
+      <c r="I23" s="223" t="n"/>
+      <c r="J23" s="223" t="n"/>
+      <c r="N23" s="226" t="inlineStr">
         <is>
           <t xml:space="preserve">  &gt;  START  </t>
         </is>
       </c>
-      <c r="P23" s="226" t="inlineStr">
+      <c r="P23" s="227" t="inlineStr">
         <is>
           <t xml:space="preserve">  #  STOP  </t>
         </is>
       </c>
-      <c r="R23" s="227" t="inlineStr">
+      <c r="R23" s="228" t="inlineStr">
         <is>
           <t xml:space="preserve">  TEST CHIME  </t>
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1" s="142">
-      <c r="A24" s="143" t="n"/>
-      <c r="F24" s="221" t="n"/>
-      <c r="G24" s="222" t="n"/>
-      <c r="H24" s="222" t="n"/>
-      <c r="I24" s="222" t="n"/>
-      <c r="J24" s="222" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="142">
-      <c r="A25" s="143" t="n"/>
-    </row>
-    <row r="26" ht="39.75" customHeight="1" s="142">
-      <c r="A26" s="143" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="142">
-      <c r="A27" s="143" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="142">
-      <c r="A28" s="143" t="n"/>
-    </row>
-    <row r="29" ht="36" customHeight="1" s="142">
-      <c r="A29" s="143" t="n"/>
-      <c r="F29" s="221" t="n"/>
-      <c r="G29" s="222" t="n"/>
-      <c r="H29" s="222" t="n"/>
-      <c r="I29" s="222" t="n"/>
-      <c r="J29" s="222" t="n"/>
-    </row>
-    <row r="30" ht="36" customHeight="1" s="142">
-      <c r="A30" s="143" t="n"/>
-      <c r="F30" s="221" t="n"/>
-      <c r="G30" s="222" t="n"/>
-      <c r="H30" s="222" t="n"/>
-      <c r="I30" s="222" t="n"/>
-      <c r="J30" s="222" t="n"/>
-    </row>
-    <row r="31" ht="36" customHeight="1" s="142">
-      <c r="A31" s="143" t="n"/>
-      <c r="F31" s="221" t="n"/>
-      <c r="G31" s="222" t="n"/>
-      <c r="H31" s="222" t="n"/>
-      <c r="I31" s="222" t="n"/>
-      <c r="J31" s="222" t="n"/>
-    </row>
-    <row r="32" ht="36" customHeight="1" s="142">
-      <c r="A32" s="143" t="n"/>
-      <c r="F32" s="221" t="n"/>
-      <c r="G32" s="222" t="n"/>
-      <c r="H32" s="222" t="n"/>
-      <c r="I32" s="222" t="n"/>
-      <c r="J32" s="222" t="n"/>
-    </row>
-    <row r="33" ht="36" customHeight="1" s="142">
-      <c r="A33" s="143" t="n"/>
-      <c r="F33" s="221" t="n"/>
-      <c r="G33" s="222" t="n"/>
-      <c r="H33" s="222" t="n"/>
-      <c r="I33" s="222" t="n"/>
-      <c r="J33" s="222" t="n"/>
-    </row>
-    <row r="34" ht="36" customHeight="1" s="142">
-      <c r="A34" s="143" t="n"/>
-      <c r="F34" s="221" t="n"/>
-      <c r="G34" s="222" t="n"/>
-      <c r="H34" s="222" t="n"/>
-      <c r="I34" s="222" t="n"/>
-      <c r="J34" s="222" t="n"/>
-    </row>
-    <row r="35" ht="36" customHeight="1" s="142">
-      <c r="A35" s="143" t="n"/>
-      <c r="F35" s="221" t="n"/>
-      <c r="G35" s="222" t="n"/>
-      <c r="H35" s="222" t="n"/>
-      <c r="I35" s="222" t="n"/>
-      <c r="J35" s="222" t="n"/>
-    </row>
-    <row r="36" ht="36" customHeight="1" s="142">
-      <c r="A36" s="143" t="n"/>
-      <c r="F36" s="221" t="n"/>
-      <c r="G36" s="222" t="n"/>
-      <c r="H36" s="222" t="n"/>
-      <c r="I36" s="222" t="n"/>
-      <c r="J36" s="222" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1" s="142">
-      <c r="A37" s="143" t="n"/>
-      <c r="F37" s="221" t="n"/>
-      <c r="G37" s="222" t="n"/>
-      <c r="H37" s="222" t="n"/>
-      <c r="I37" s="222" t="n"/>
-      <c r="J37" s="222" t="n"/>
-    </row>
-    <row r="38" ht="36" customHeight="1" s="142">
-      <c r="A38" s="143" t="n"/>
-      <c r="F38" s="221" t="n"/>
-      <c r="G38" s="222" t="n"/>
-      <c r="H38" s="222" t="n"/>
-      <c r="I38" s="222" t="n"/>
-      <c r="J38" s="222" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1" s="142">
-      <c r="A39" s="143" t="n"/>
-      <c r="F39" s="221" t="n"/>
-      <c r="G39" s="222" t="n"/>
-      <c r="H39" s="222" t="n"/>
-      <c r="I39" s="222" t="n"/>
-      <c r="J39" s="222" t="n"/>
-    </row>
-    <row r="40" ht="36" customHeight="1" s="142">
-      <c r="F40" s="221" t="n"/>
-      <c r="G40" s="222" t="n"/>
-      <c r="H40" s="222" t="n"/>
-      <c r="I40" s="222" t="n"/>
-      <c r="J40" s="222" t="n"/>
-    </row>
-    <row r="41" ht="36" customHeight="1" s="142">
-      <c r="F41" s="221" t="n"/>
-      <c r="G41" s="222" t="n"/>
-      <c r="H41" s="222" t="n"/>
-      <c r="I41" s="222" t="n"/>
-      <c r="J41" s="222" t="n"/>
-    </row>
-    <row r="42" ht="36" customHeight="1" s="142">
-      <c r="F42" s="221" t="n"/>
-      <c r="G42" s="222" t="n"/>
-      <c r="H42" s="222" t="n"/>
-      <c r="I42" s="222" t="n"/>
-      <c r="J42" s="222" t="n"/>
-    </row>
-    <row r="43" ht="36" customHeight="1" s="142">
-      <c r="F43" s="221" t="n"/>
-      <c r="G43" s="222" t="n"/>
-      <c r="H43" s="222" t="n"/>
-      <c r="I43" s="222" t="n"/>
-      <c r="J43" s="222" t="n"/>
-    </row>
-    <row r="44" ht="36" customHeight="1" s="142">
-      <c r="F44" s="221" t="n"/>
-      <c r="G44" s="222" t="n"/>
-      <c r="H44" s="222" t="n"/>
-      <c r="I44" s="222" t="n"/>
-      <c r="J44" s="222" t="n"/>
-    </row>
-    <row r="45" ht="36" customHeight="1" s="142">
-      <c r="F45" s="221" t="n"/>
-      <c r="G45" s="222" t="n"/>
-      <c r="H45" s="222" t="n"/>
-      <c r="I45" s="222" t="n"/>
-      <c r="J45" s="222" t="n"/>
-    </row>
-    <row r="46" ht="36" customHeight="1" s="142">
-      <c r="F46" s="221" t="n"/>
-      <c r="G46" s="222" t="n"/>
-      <c r="H46" s="222" t="n"/>
-      <c r="I46" s="222" t="n"/>
-      <c r="J46" s="222" t="n"/>
-    </row>
-    <row r="47" ht="36" customHeight="1" s="142">
-      <c r="F47" s="221" t="n"/>
-      <c r="G47" s="222" t="n"/>
-      <c r="H47" s="222" t="n"/>
-      <c r="I47" s="222" t="n"/>
-      <c r="J47" s="222" t="n"/>
-    </row>
-    <row r="48" ht="36" customHeight="1" s="142">
-      <c r="F48" s="221" t="n"/>
-      <c r="G48" s="222" t="n"/>
-      <c r="H48" s="222" t="n"/>
-      <c r="I48" s="222" t="n"/>
-      <c r="J48" s="222" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1" s="142">
-      <c r="F49" s="221" t="n"/>
-      <c r="G49" s="222" t="n"/>
-      <c r="H49" s="222" t="n"/>
-      <c r="I49" s="222" t="n"/>
-      <c r="J49" s="222" t="n"/>
-    </row>
-    <row r="50" ht="36" customHeight="1" s="142">
-      <c r="F50" s="221" t="n"/>
-      <c r="G50" s="222" t="n"/>
-      <c r="H50" s="222" t="n"/>
-      <c r="I50" s="222" t="n"/>
-      <c r="J50" s="222" t="n"/>
-    </row>
-    <row r="51" ht="36" customHeight="1" s="142">
-      <c r="F51" s="221" t="n"/>
-      <c r="G51" s="222" t="n"/>
-      <c r="H51" s="222" t="n"/>
-      <c r="I51" s="222" t="n"/>
-      <c r="J51" s="222" t="n"/>
+    <row r="24" ht="36" customHeight="1" s="143">
+      <c r="A24" s="144" t="n"/>
+      <c r="F24" s="222" t="n"/>
+      <c r="G24" s="223" t="n"/>
+      <c r="H24" s="223" t="n"/>
+      <c r="I24" s="223" t="n"/>
+      <c r="J24" s="223" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="A25" s="144" t="n"/>
+    </row>
+    <row r="26" ht="39.75" customHeight="1" s="143">
+      <c r="A26" s="144" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="143">
+      <c r="A27" s="144" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="A28" s="144" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="143">
+      <c r="A29" s="144" t="n"/>
+      <c r="F29" s="222" t="n"/>
+      <c r="G29" s="223" t="n"/>
+      <c r="H29" s="223" t="n"/>
+      <c r="I29" s="223" t="n"/>
+      <c r="J29" s="223" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1" s="143">
+      <c r="A30" s="144" t="n"/>
+      <c r="F30" s="222" t="n"/>
+      <c r="G30" s="223" t="n"/>
+      <c r="H30" s="223" t="n"/>
+      <c r="I30" s="223" t="n"/>
+      <c r="J30" s="223" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="143">
+      <c r="A31" s="144" t="n"/>
+      <c r="F31" s="222" t="n"/>
+      <c r="G31" s="223" t="n"/>
+      <c r="H31" s="223" t="n"/>
+      <c r="I31" s="223" t="n"/>
+      <c r="J31" s="223" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="143">
+      <c r="A32" s="144" t="n"/>
+      <c r="F32" s="222" t="n"/>
+      <c r="G32" s="223" t="n"/>
+      <c r="H32" s="223" t="n"/>
+      <c r="I32" s="223" t="n"/>
+      <c r="J32" s="223" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1" s="143">
+      <c r="A33" s="144" t="n"/>
+      <c r="F33" s="222" t="n"/>
+      <c r="G33" s="223" t="n"/>
+      <c r="H33" s="223" t="n"/>
+      <c r="I33" s="223" t="n"/>
+      <c r="J33" s="223" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="143">
+      <c r="A34" s="144" t="n"/>
+      <c r="F34" s="222" t="n"/>
+      <c r="G34" s="223" t="n"/>
+      <c r="H34" s="223" t="n"/>
+      <c r="I34" s="223" t="n"/>
+      <c r="J34" s="223" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="143">
+      <c r="A35" s="144" t="n"/>
+      <c r="F35" s="222" t="n"/>
+      <c r="G35" s="223" t="n"/>
+      <c r="H35" s="223" t="n"/>
+      <c r="I35" s="223" t="n"/>
+      <c r="J35" s="223" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1" s="143">
+      <c r="A36" s="144" t="n"/>
+      <c r="F36" s="222" t="n"/>
+      <c r="G36" s="223" t="n"/>
+      <c r="H36" s="223" t="n"/>
+      <c r="I36" s="223" t="n"/>
+      <c r="J36" s="223" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1" s="143">
+      <c r="A37" s="144" t="n"/>
+      <c r="F37" s="222" t="n"/>
+      <c r="G37" s="223" t="n"/>
+      <c r="H37" s="223" t="n"/>
+      <c r="I37" s="223" t="n"/>
+      <c r="J37" s="223" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1" s="143">
+      <c r="A38" s="144" t="n"/>
+      <c r="F38" s="222" t="n"/>
+      <c r="G38" s="223" t="n"/>
+      <c r="H38" s="223" t="n"/>
+      <c r="I38" s="223" t="n"/>
+      <c r="J38" s="223" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="143">
+      <c r="A39" s="144" t="n"/>
+      <c r="F39" s="222" t="n"/>
+      <c r="G39" s="223" t="n"/>
+      <c r="H39" s="223" t="n"/>
+      <c r="I39" s="223" t="n"/>
+      <c r="J39" s="223" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="143">
+      <c r="F40" s="222" t="n"/>
+      <c r="G40" s="223" t="n"/>
+      <c r="H40" s="223" t="n"/>
+      <c r="I40" s="223" t="n"/>
+      <c r="J40" s="223" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1" s="143">
+      <c r="F41" s="222" t="n"/>
+      <c r="G41" s="223" t="n"/>
+      <c r="H41" s="223" t="n"/>
+      <c r="I41" s="223" t="n"/>
+      <c r="J41" s="223" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="143">
+      <c r="F42" s="222" t="n"/>
+      <c r="G42" s="223" t="n"/>
+      <c r="H42" s="223" t="n"/>
+      <c r="I42" s="223" t="n"/>
+      <c r="J42" s="223" t="n"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" s="143">
+      <c r="F43" s="222" t="n"/>
+      <c r="G43" s="223" t="n"/>
+      <c r="H43" s="223" t="n"/>
+      <c r="I43" s="223" t="n"/>
+      <c r="J43" s="223" t="n"/>
+    </row>
+    <row r="44" ht="36" customHeight="1" s="143">
+      <c r="F44" s="222" t="n"/>
+      <c r="G44" s="223" t="n"/>
+      <c r="H44" s="223" t="n"/>
+      <c r="I44" s="223" t="n"/>
+      <c r="J44" s="223" t="n"/>
+    </row>
+    <row r="45" ht="36" customHeight="1" s="143">
+      <c r="F45" s="222" t="n"/>
+      <c r="G45" s="223" t="n"/>
+      <c r="H45" s="223" t="n"/>
+      <c r="I45" s="223" t="n"/>
+      <c r="J45" s="223" t="n"/>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="143">
+      <c r="F46" s="222" t="n"/>
+      <c r="G46" s="223" t="n"/>
+      <c r="H46" s="223" t="n"/>
+      <c r="I46" s="223" t="n"/>
+      <c r="J46" s="223" t="n"/>
+    </row>
+    <row r="47" ht="36" customHeight="1" s="143">
+      <c r="F47" s="222" t="n"/>
+      <c r="G47" s="223" t="n"/>
+      <c r="H47" s="223" t="n"/>
+      <c r="I47" s="223" t="n"/>
+      <c r="J47" s="223" t="n"/>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="143">
+      <c r="F48" s="222" t="n"/>
+      <c r="G48" s="223" t="n"/>
+      <c r="H48" s="223" t="n"/>
+      <c r="I48" s="223" t="n"/>
+      <c r="J48" s="223" t="n"/>
+    </row>
+    <row r="49" ht="36" customHeight="1" s="143">
+      <c r="F49" s="222" t="n"/>
+      <c r="G49" s="223" t="n"/>
+      <c r="H49" s="223" t="n"/>
+      <c r="I49" s="223" t="n"/>
+      <c r="J49" s="223" t="n"/>
+    </row>
+    <row r="50" ht="36" customHeight="1" s="143">
+      <c r="F50" s="222" t="n"/>
+      <c r="G50" s="223" t="n"/>
+      <c r="H50" s="223" t="n"/>
+      <c r="I50" s="223" t="n"/>
+      <c r="J50" s="223" t="n"/>
+    </row>
+    <row r="51" ht="36" customHeight="1" s="143">
+      <c r="F51" s="222" t="n"/>
+      <c r="G51" s="223" t="n"/>
+      <c r="H51" s="223" t="n"/>
+      <c r="I51" s="223" t="n"/>
+      <c r="J51" s="223" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2787,1025 +2801,1025 @@
   <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="3" customWidth="1" style="140" min="1" max="1"/>
-    <col width="32" customWidth="1" style="140" min="2" max="2"/>
-    <col width="20" customWidth="1" style="140" min="3" max="3"/>
-    <col width="18" customWidth="1" style="140" min="4" max="7"/>
-    <col width="12" customWidth="1" style="140" min="8" max="11"/>
-    <col width="14" customWidth="1" style="140" min="12" max="12"/>
-    <col width="46" customWidth="1" style="140" min="13" max="13"/>
+    <col width="3" customWidth="1" style="141" min="1" max="1"/>
+    <col width="32" customWidth="1" style="141" min="2" max="2"/>
+    <col width="20" customWidth="1" style="141" min="3" max="3"/>
+    <col width="18" customWidth="1" style="141" min="4" max="7"/>
+    <col width="12" customWidth="1" style="141" min="8" max="11"/>
+    <col width="14" customWidth="1" style="141" min="12" max="12"/>
+    <col width="46" customWidth="1" style="141" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.35" customHeight="1" s="142">
-      <c r="B1" s="228" t="inlineStr">
+    <row r="1" ht="17.35" customHeight="1" s="143">
+      <c r="B1" s="229" t="inlineStr">
         <is>
           <t>DETAIL   -   full breakdown behind the Dashboard</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="142">
-      <c r="B2" s="229" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="B2" s="230" t="inlineStr">
         <is>
           <t>Same engine, same numbers. The Dashboard shows the three spreads you trade from; this sheet shows everything that stands behind them, for all four slots.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="15" customHeight="1" s="142">
-      <c r="B4" s="230" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="143">
+      <c r="B4" s="231" t="inlineStr">
         <is>
           <t>OUTRIGHT LEGS</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="142">
-      <c r="B5" s="231" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="B5" s="232" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C5" s="231" t="inlineStr">
+      <c r="C5" s="232" t="inlineStr">
         <is>
           <t>Instrument ID</t>
         </is>
       </c>
-      <c r="D5" s="231" t="inlineStr">
+      <c r="D5" s="232" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="231" t="inlineStr">
+      <c r="E5" s="232" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="H5" s="231" t="inlineStr">
+      <c r="H5" s="232" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I5" s="231" t="inlineStr">
+      <c r="I5" s="232" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J5" s="231" t="inlineStr">
+      <c r="J5" s="232" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K5" s="231" t="inlineStr">
+      <c r="K5" s="232" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L5" s="231" t="inlineStr">
+      <c r="L5" s="232" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="M5" s="231" t="inlineStr">
+      <c r="M5" s="232" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="142">
-      <c r="B6" s="232" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="143">
+      <c r="B6" s="233" t="inlineStr">
         <is>
           <t>RBV6</t>
         </is>
       </c>
-      <c r="C6" s="233" t="n"/>
-      <c r="D6" s="234" t="inlineStr">
+      <c r="C6" s="234" t="n"/>
+      <c r="D6" s="235" t="inlineStr">
         <is>
           <t>RBOB Gasoline Oct26</t>
         </is>
       </c>
-      <c r="E6" s="235" t="inlineStr">
+      <c r="E6" s="236" t="inlineStr">
         <is>
           <t>42,000 gal</t>
         </is>
       </c>
-      <c r="H6" s="236" t="n"/>
-      <c r="I6" s="236" t="n"/>
-      <c r="J6" s="236" t="n"/>
-      <c r="K6" s="236" t="n"/>
-      <c r="L6" s="236" t="n"/>
-      <c r="M6" s="236" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="142">
-      <c r="B7" s="232" t="inlineStr">
+      <c r="H6" s="237" t="n"/>
+      <c r="I6" s="237" t="n"/>
+      <c r="J6" s="237" t="n"/>
+      <c r="K6" s="237" t="n"/>
+      <c r="L6" s="237" t="n"/>
+      <c r="M6" s="237" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="143">
+      <c r="B7" s="233" t="inlineStr">
         <is>
           <t>HOV6</t>
         </is>
       </c>
-      <c r="C7" s="233" t="n"/>
-      <c r="D7" s="234" t="inlineStr">
+      <c r="C7" s="234" t="n"/>
+      <c r="D7" s="235" t="inlineStr">
         <is>
           <t>NY Harbor ULSD Oct26</t>
         </is>
       </c>
-      <c r="E7" s="235" t="inlineStr">
+      <c r="E7" s="236" t="inlineStr">
         <is>
           <t>42,000 gal</t>
         </is>
       </c>
-      <c r="H7" s="236" t="n"/>
-      <c r="I7" s="236" t="n"/>
-      <c r="J7" s="236" t="n"/>
-      <c r="K7" s="236" t="n"/>
-      <c r="L7" s="236" t="n"/>
-      <c r="M7" s="236" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="142">
-      <c r="B8" s="232" t="inlineStr">
+      <c r="H7" s="237" t="n"/>
+      <c r="I7" s="237" t="n"/>
+      <c r="J7" s="237" t="n"/>
+      <c r="K7" s="237" t="n"/>
+      <c r="L7" s="237" t="n"/>
+      <c r="M7" s="237" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="143">
+      <c r="B8" s="233" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="C8" s="233" t="n"/>
-      <c r="D8" s="234" t="inlineStr">
+      <c r="C8" s="234" t="n"/>
+      <c r="D8" s="235" t="inlineStr">
         <is>
           <t>WTI Crude Oct26</t>
         </is>
       </c>
-      <c r="E8" s="235" t="inlineStr">
+      <c r="E8" s="236" t="inlineStr">
         <is>
           <t>1,000 bbl</t>
         </is>
       </c>
-      <c r="H8" s="236" t="n"/>
-      <c r="I8" s="236" t="n"/>
-      <c r="J8" s="236" t="n"/>
-      <c r="K8" s="236" t="n"/>
-      <c r="L8" s="236" t="n"/>
-      <c r="M8" s="236" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="142">
-      <c r="B9" s="232" t="inlineStr">
+      <c r="H8" s="237" t="n"/>
+      <c r="I8" s="237" t="n"/>
+      <c r="J8" s="237" t="n"/>
+      <c r="K8" s="237" t="n"/>
+      <c r="L8" s="237" t="n"/>
+      <c r="M8" s="237" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="B9" s="233" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="C9" s="233" t="n"/>
-      <c r="D9" s="234" t="inlineStr">
+      <c r="C9" s="234" t="n"/>
+      <c r="D9" s="235" t="inlineStr">
         <is>
           <t>Brent Last Day Fin Oct26</t>
         </is>
       </c>
-      <c r="E9" s="235" t="inlineStr">
+      <c r="E9" s="236" t="inlineStr">
         <is>
           <t>1,000 bbl</t>
         </is>
       </c>
-      <c r="H9" s="236" t="n"/>
-      <c r="I9" s="236" t="n"/>
-      <c r="J9" s="236" t="n"/>
-      <c r="K9" s="236" t="n"/>
-      <c r="L9" s="236" t="n"/>
-      <c r="M9" s="236" t="n"/>
+      <c r="H9" s="237" t="n"/>
+      <c r="I9" s="237" t="n"/>
+      <c r="J9" s="237" t="n"/>
+      <c r="K9" s="237" t="n"/>
+      <c r="L9" s="237" t="n"/>
+      <c r="M9" s="237" t="n"/>
     </row>
     <row r="10"/>
-    <row r="11" ht="15" customHeight="1" s="142">
-      <c r="B11" s="230" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="143">
+      <c r="B11" s="231" t="inlineStr">
         <is>
           <t>DERIVED &amp; LISTED SPREADS</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="142">
-      <c r="B12" s="231" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="143">
+      <c r="B12" s="232" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C12" s="231" t="inlineStr">
+      <c r="C12" s="232" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="D12" s="231" t="inlineStr">
+      <c r="D12" s="232" t="inlineStr">
         <is>
           <t>Crossing convention</t>
         </is>
       </c>
-      <c r="H12" s="231" t="inlineStr">
+      <c r="H12" s="232" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I12" s="231" t="inlineStr">
+      <c r="I12" s="232" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="L12" s="231" t="inlineStr">
+      <c r="L12" s="232" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="M12" s="231" t="inlineStr">
+      <c r="M12" s="232" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="142">
-      <c r="B13" s="232" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="143">
+      <c r="B13" s="233" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="C13" s="235" t="inlineStr">
+      <c r="C13" s="236" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D13" s="237" t="inlineStr">
+      <c r="D13" s="238" t="inlineStr">
         <is>
           <t>bid = BZ bid - CL ask ; ask = BZ ask - CL bid</t>
         </is>
       </c>
-      <c r="H13" s="236" t="n"/>
-      <c r="I13" s="236" t="n"/>
-      <c r="L13" s="236" t="n"/>
-      <c r="M13" s="236" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="142">
-      <c r="B14" s="232" t="inlineStr">
+      <c r="H13" s="237" t="n"/>
+      <c r="I13" s="237" t="n"/>
+      <c r="L13" s="237" t="n"/>
+      <c r="M13" s="237" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="143">
+      <c r="B14" s="233" t="inlineStr">
         <is>
           <t>HO/CL crack</t>
         </is>
       </c>
-      <c r="C14" s="235" t="inlineStr">
+      <c r="C14" s="236" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D14" s="237" t="inlineStr">
+      <c r="D14" s="238" t="inlineStr">
         <is>
           <t>bid = HO bid x42 - CL ask ; ask = HO ask x42 - CL bid</t>
         </is>
       </c>
-      <c r="H14" s="236" t="n"/>
-      <c r="I14" s="236" t="n"/>
-      <c r="L14" s="236" t="n"/>
-      <c r="M14" s="236" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="142">
-      <c r="B15" s="232" t="inlineStr">
+      <c r="H14" s="237" t="n"/>
+      <c r="I14" s="237" t="n"/>
+      <c r="L14" s="237" t="n"/>
+      <c r="M14" s="237" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="143">
+      <c r="B15" s="233" t="inlineStr">
         <is>
           <t>3:2:1 crack</t>
         </is>
       </c>
-      <c r="C15" s="235" t="inlineStr">
+      <c r="C15" s="236" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="D15" s="237" t="inlineStr">
+      <c r="D15" s="238" t="inlineStr">
         <is>
           <t>bid sells products at the bid and buys crude at the ask; ask mirrors it</t>
         </is>
       </c>
-      <c r="H15" s="236" t="n"/>
-      <c r="I15" s="236" t="n"/>
-      <c r="L15" s="236" t="n"/>
-      <c r="M15" s="236" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="142">
-      <c r="B16" s="232" t="inlineStr">
+      <c r="H15" s="237" t="n"/>
+      <c r="I15" s="237" t="n"/>
+      <c r="L15" s="237" t="n"/>
+      <c r="M15" s="237" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="143">
+      <c r="B16" s="233" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="C16" s="235" t="inlineStr">
+      <c r="C16" s="236" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="D16" s="237" t="inlineStr">
+      <c r="D16" s="238" t="inlineStr">
         <is>
           <t>exchange-listed - one quote, no leg risk</t>
         </is>
       </c>
-      <c r="H16" s="236" t="n"/>
-      <c r="I16" s="236" t="n"/>
-      <c r="L16" s="236" t="n"/>
-      <c r="M16" s="236" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="142">
-      <c r="B17" s="232" t="inlineStr">
+      <c r="H16" s="237" t="n"/>
+      <c r="I16" s="237" t="n"/>
+      <c r="L16" s="237" t="n"/>
+      <c r="M16" s="237" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="143">
+      <c r="B17" s="233" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="C17" s="235" t="inlineStr">
+      <c r="C17" s="236" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="D17" s="237" t="inlineStr">
+      <c r="D17" s="238" t="inlineStr">
         <is>
           <t>exchange-listed - one quote, no leg risk</t>
         </is>
       </c>
-      <c r="H17" s="236" t="n"/>
-      <c r="I17" s="236" t="n"/>
-      <c r="L17" s="236" t="n"/>
-      <c r="M17" s="236" t="n"/>
+      <c r="H17" s="237" t="n"/>
+      <c r="I17" s="237" t="n"/>
+      <c r="L17" s="237" t="n"/>
+      <c r="M17" s="237" t="n"/>
     </row>
     <row r="18"/>
-    <row r="19" ht="15" customHeight="1" s="142">
-      <c r="B19" s="230" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="143">
+      <c r="B19" s="231" t="inlineStr">
         <is>
           <t>PER-SPREAD BREAKDOWN</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="142">
-      <c r="B20" s="231" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="143">
+      <c r="B20" s="232" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C20" s="231" t="inlineStr">
+      <c r="C20" s="232" t="inlineStr">
         <is>
           <t>Unit / note</t>
         </is>
       </c>
-      <c r="D20" s="231" t="inlineStr">
+      <c r="D20" s="232" t="inlineStr">
         <is>
           <t>SPREAD 1</t>
         </is>
       </c>
-      <c r="E20" s="231" t="inlineStr">
+      <c r="E20" s="232" t="inlineStr">
         <is>
           <t>SPREAD 2</t>
         </is>
       </c>
-      <c r="F20" s="231" t="inlineStr">
+      <c r="F20" s="232" t="inlineStr">
         <is>
           <t>SPREAD 3</t>
         </is>
       </c>
-      <c r="G20" s="231" t="inlineStr">
+      <c r="G20" s="232" t="inlineStr">
         <is>
           <t>SPREAD 4</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="142">
-      <c r="B21" s="238" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="143">
+      <c r="B21" s="239" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C21" s="237" t="n"/>
-      <c r="D21" s="239" t="n"/>
-      <c r="E21" s="239" t="n"/>
-      <c r="F21" s="239" t="n"/>
-      <c r="G21" s="239" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="142">
-      <c r="B22" s="238" t="inlineStr">
+      <c r="C21" s="238" t="n"/>
+      <c r="D21" s="240" t="n"/>
+      <c r="E21" s="240" t="n"/>
+      <c r="F21" s="240" t="n"/>
+      <c r="G21" s="240" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="143">
+      <c r="B22" s="239" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C22" s="237" t="inlineStr">
+      <c r="C22" s="238" t="inlineStr">
         <is>
           <t>LegB - beta x LegA</t>
         </is>
       </c>
-      <c r="D22" s="239" t="n"/>
-      <c r="E22" s="239" t="n"/>
-      <c r="F22" s="239" t="n"/>
-      <c r="G22" s="239" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="142">
-      <c r="B23" s="238" t="inlineStr">
+      <c r="D22" s="240" t="n"/>
+      <c r="E22" s="240" t="n"/>
+      <c r="F22" s="240" t="n"/>
+      <c r="G22" s="240" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="143">
+      <c r="B23" s="239" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="C23" s="237" t="n"/>
-      <c r="D23" s="239" t="n"/>
-      <c r="E23" s="239" t="n"/>
-      <c r="F23" s="239" t="n"/>
-      <c r="G23" s="239" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="142">
-      <c r="B24" s="238" t="inlineStr">
+      <c r="C23" s="238" t="n"/>
+      <c r="D23" s="240" t="n"/>
+      <c r="E23" s="240" t="n"/>
+      <c r="F23" s="240" t="n"/>
+      <c r="G23" s="240" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="143">
+      <c r="B24" s="239" t="inlineStr">
         <is>
           <t>HEDGE_RATIO (beta)</t>
         </is>
       </c>
-      <c r="C24" s="237" t="inlineStr">
+      <c r="C24" s="238" t="inlineStr">
         <is>
           <t>stamped pair -&gt;</t>
         </is>
       </c>
-      <c r="D24" s="239" t="n"/>
-      <c r="E24" s="239" t="n"/>
-      <c r="F24" s="239" t="n"/>
-      <c r="G24" s="239" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="142">
-      <c r="B25" s="238" t="inlineStr">
+      <c r="D24" s="240" t="n"/>
+      <c r="E24" s="240" t="n"/>
+      <c r="F24" s="240" t="n"/>
+      <c r="G24" s="240" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="B25" s="239" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread</t>
         </is>
       </c>
-      <c r="C25" s="237" t="inlineStr">
+      <c r="C25" s="238" t="inlineStr">
         <is>
           <t>per lot</t>
         </is>
       </c>
-      <c r="D25" s="240" t="n"/>
-      <c r="E25" s="240" t="n"/>
-      <c r="F25" s="240" t="n"/>
-      <c r="G25" s="240" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="142">
-      <c r="B26" s="241" t="inlineStr">
+      <c r="D25" s="241" t="n"/>
+      <c r="E25" s="241" t="n"/>
+      <c r="F25" s="241" t="n"/>
+      <c r="G25" s="241" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="143">
+      <c r="B26" s="242" t="inlineStr">
         <is>
           <t>MARKET  (touch, shown separately from the statistic)</t>
         </is>
       </c>
-      <c r="C26" s="242" t="n"/>
-      <c r="D26" s="242" t="n"/>
-      <c r="E26" s="242" t="n"/>
-      <c r="F26" s="242" t="n"/>
-      <c r="G26" s="242" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="142">
-      <c r="B27" s="238" t="inlineStr">
+      <c r="C26" s="243" t="n"/>
+      <c r="D26" s="243" t="n"/>
+      <c r="E26" s="243" t="n"/>
+      <c r="F26" s="243" t="n"/>
+      <c r="G26" s="243" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="143">
+      <c r="B27" s="239" t="inlineStr">
         <is>
           <t>Spread bid</t>
         </is>
       </c>
-      <c r="C27" s="237" t="n"/>
-      <c r="D27" s="236" t="n"/>
-      <c r="E27" s="236" t="n"/>
-      <c r="F27" s="236" t="n"/>
-      <c r="G27" s="236" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="142">
-      <c r="B28" s="238" t="inlineStr">
+      <c r="C27" s="238" t="n"/>
+      <c r="D27" s="237" t="n"/>
+      <c r="E27" s="237" t="n"/>
+      <c r="F27" s="237" t="n"/>
+      <c r="G27" s="237" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="B28" s="239" t="inlineStr">
         <is>
           <t>Spread ask</t>
         </is>
       </c>
-      <c r="C28" s="237" t="n"/>
-      <c r="D28" s="236" t="n"/>
-      <c r="E28" s="236" t="n"/>
-      <c r="F28" s="236" t="n"/>
-      <c r="G28" s="236" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="142">
-      <c r="B29" s="238" t="inlineStr">
+      <c r="C28" s="238" t="n"/>
+      <c r="D28" s="237" t="n"/>
+      <c r="E28" s="237" t="n"/>
+      <c r="F28" s="237" t="n"/>
+      <c r="G28" s="237" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="143">
+      <c r="B29" s="239" t="inlineStr">
         <is>
           <t>Spread mid   &lt;- feeds the statistic</t>
         </is>
       </c>
-      <c r="C29" s="237" t="n"/>
-      <c r="D29" s="236" t="n"/>
-      <c r="E29" s="236" t="n"/>
-      <c r="F29" s="236" t="n"/>
-      <c r="G29" s="236" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="142">
-      <c r="B30" s="238" t="inlineStr">
+      <c r="C29" s="238" t="n"/>
+      <c r="D29" s="237" t="n"/>
+      <c r="E29" s="237" t="n"/>
+      <c r="F29" s="237" t="n"/>
+      <c r="G29" s="237" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="143">
+      <c r="B30" s="239" t="inlineStr">
         <is>
           <t>Bid-Ask Gap</t>
         </is>
       </c>
-      <c r="C30" s="237" t="inlineStr">
+      <c r="C30" s="238" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D30" s="236" t="n"/>
-      <c r="E30" s="236" t="n"/>
-      <c r="F30" s="236" t="n"/>
-      <c r="G30" s="236" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="142">
-      <c r="B31" s="241" t="inlineStr">
+      <c r="D30" s="237" t="n"/>
+      <c r="E30" s="237" t="n"/>
+      <c r="F30" s="237" t="n"/>
+      <c r="G30" s="237" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="143">
+      <c r="B31" s="242" t="inlineStr">
         <is>
           <t>WINDOW</t>
         </is>
       </c>
-      <c r="C31" s="242" t="n"/>
-      <c r="D31" s="242" t="n"/>
-      <c r="E31" s="242" t="n"/>
-      <c r="F31" s="242" t="n"/>
-      <c r="G31" s="242" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="142">
-      <c r="B32" s="238" t="inlineStr">
+      <c r="C31" s="243" t="n"/>
+      <c r="D31" s="243" t="n"/>
+      <c r="E31" s="243" t="n"/>
+      <c r="F31" s="243" t="n"/>
+      <c r="G31" s="243" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="143">
+      <c r="B32" s="239" t="inlineStr">
         <is>
           <t>Stored samples in window</t>
         </is>
       </c>
-      <c r="C32" s="237" t="inlineStr">
+      <c r="C32" s="238" t="inlineStr">
         <is>
           <t>after dedupe + store gate</t>
         </is>
       </c>
-      <c r="D32" s="240" t="n"/>
-      <c r="E32" s="240" t="n"/>
-      <c r="F32" s="240" t="n"/>
-      <c r="G32" s="240" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="142">
-      <c r="B33" s="238" t="inlineStr">
+      <c r="D32" s="241" t="n"/>
+      <c r="E32" s="241" t="n"/>
+      <c r="F32" s="241" t="n"/>
+      <c r="G32" s="241" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="143">
+      <c r="B33" s="239" t="inlineStr">
         <is>
           <t>Window elapsed</t>
         </is>
       </c>
-      <c r="C33" s="237" t="inlineStr">
+      <c r="C33" s="238" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D33" s="243" t="n"/>
-      <c r="E33" s="243" t="n"/>
-      <c r="F33" s="243" t="n"/>
-      <c r="G33" s="243" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="142">
-      <c r="B34" s="238" t="inlineStr">
+      <c r="D33" s="244" t="n"/>
+      <c r="E33" s="244" t="n"/>
+      <c r="F33" s="244" t="n"/>
+      <c r="G33" s="244" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="143">
+      <c r="B34" s="239" t="inlineStr">
         <is>
           <t>Warm-up gate</t>
         </is>
       </c>
-      <c r="C34" s="237" t="inlineStr">
+      <c r="C34" s="238" t="inlineStr">
         <is>
           <t>binding gate</t>
         </is>
       </c>
-      <c r="D34" s="239" t="n"/>
-      <c r="E34" s="239" t="n"/>
-      <c r="F34" s="239" t="n"/>
-      <c r="G34" s="239" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="142">
-      <c r="B35" s="238" t="inlineStr">
+      <c r="D34" s="240" t="n"/>
+      <c r="E34" s="240" t="n"/>
+      <c r="F34" s="240" t="n"/>
+      <c r="G34" s="240" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="143">
+      <c r="B35" s="239" t="inlineStr">
         <is>
           <t>Feed rate</t>
         </is>
       </c>
-      <c r="C35" s="237" t="inlineStr">
+      <c r="C35" s="238" t="inlineStr">
         <is>
           <t>quote CHANGES / min</t>
         </is>
       </c>
-      <c r="D35" s="244" t="n"/>
-      <c r="E35" s="244" t="n"/>
-      <c r="F35" s="244" t="n"/>
-      <c r="G35" s="244" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="142">
-      <c r="B36" s="238" t="inlineStr">
+      <c r="D35" s="245" t="n"/>
+      <c r="E35" s="245" t="n"/>
+      <c r="F35" s="245" t="n"/>
+      <c r="G35" s="245" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="143">
+      <c r="B36" s="239" t="inlineStr">
         <is>
           <t>Feed status</t>
         </is>
       </c>
-      <c r="C36" s="237" t="n"/>
-      <c r="D36" s="239" t="n"/>
-      <c r="E36" s="239" t="n"/>
-      <c r="F36" s="239" t="n"/>
-      <c r="G36" s="239" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="142">
-      <c r="B37" s="241" t="inlineStr">
+      <c r="C36" s="238" t="n"/>
+      <c r="D36" s="240" t="n"/>
+      <c r="E36" s="240" t="n"/>
+      <c r="F36" s="240" t="n"/>
+      <c r="G36" s="240" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="143">
+      <c r="B37" s="242" t="inlineStr">
         <is>
           <t>STATISTICS  (FROZEN - republished every STATS_REFRESH_MIN)</t>
         </is>
       </c>
-      <c r="C37" s="242" t="n"/>
-      <c r="D37" s="242" t="n"/>
-      <c r="E37" s="242" t="n"/>
-      <c r="F37" s="242" t="n"/>
-      <c r="G37" s="242" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="142">
-      <c r="B38" s="238" t="inlineStr">
+      <c r="C37" s="243" t="n"/>
+      <c r="D37" s="243" t="n"/>
+      <c r="E37" s="243" t="n"/>
+      <c r="F37" s="243" t="n"/>
+      <c r="G37" s="243" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="143">
+      <c r="B38" s="239" t="inlineStr">
         <is>
           <t>Mean (frozen)</t>
         </is>
       </c>
-      <c r="C38" s="237" t="n"/>
-      <c r="D38" s="236" t="n"/>
-      <c r="E38" s="236" t="n"/>
-      <c r="F38" s="236" t="n"/>
-      <c r="G38" s="236" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="142">
-      <c r="B39" s="238" t="inlineStr">
+      <c r="C38" s="238" t="n"/>
+      <c r="D38" s="237" t="n"/>
+      <c r="E38" s="237" t="n"/>
+      <c r="F38" s="237" t="n"/>
+      <c r="G38" s="237" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="143">
+      <c r="B39" s="239" t="inlineStr">
         <is>
           <t>Std Dev (frozen)</t>
         </is>
       </c>
-      <c r="C39" s="237" t="n"/>
-      <c r="D39" s="236" t="n"/>
-      <c r="E39" s="236" t="n"/>
-      <c r="F39" s="236" t="n"/>
-      <c r="G39" s="236" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="142">
-      <c r="B40" s="238" t="inlineStr">
+      <c r="C39" s="238" t="n"/>
+      <c r="D39" s="237" t="n"/>
+      <c r="E39" s="237" t="n"/>
+      <c r="F39" s="237" t="n"/>
+      <c r="G39" s="237" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="143">
+      <c r="B40" s="239" t="inlineStr">
         <is>
           <t>Std Dev in dollars</t>
         </is>
       </c>
-      <c r="C40" s="237" t="inlineStr">
+      <c r="C40" s="238" t="inlineStr">
         <is>
           <t>sigma x USD/pt x LOTS</t>
         </is>
       </c>
-      <c r="D40" s="245" t="n"/>
-      <c r="E40" s="245" t="n"/>
-      <c r="F40" s="245" t="n"/>
-      <c r="G40" s="245" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="142">
-      <c r="B41" s="238" t="inlineStr">
+      <c r="D40" s="246" t="n"/>
+      <c r="E40" s="246" t="n"/>
+      <c r="F40" s="246" t="n"/>
+      <c r="G40" s="246" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="143">
+      <c r="B41" s="239" t="inlineStr">
         <is>
           <t>Stats age / next refresh</t>
         </is>
       </c>
-      <c r="C41" s="237" t="inlineStr">
+      <c r="C41" s="238" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="D41" s="239" t="n"/>
-      <c r="E41" s="239" t="n"/>
-      <c r="F41" s="239" t="n"/>
-      <c r="G41" s="239" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="142">
-      <c r="B42" s="246" t="inlineStr">
+      <c r="D41" s="240" t="n"/>
+      <c r="E41" s="240" t="n"/>
+      <c r="F41" s="240" t="n"/>
+      <c r="G41" s="240" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="143">
+      <c r="B42" s="247" t="inlineStr">
         <is>
           <t>Z  (live, vs frozen mean &amp; sigma)</t>
         </is>
       </c>
-      <c r="C42" s="237" t="n"/>
-      <c r="D42" s="247" t="n"/>
-      <c r="E42" s="247" t="n"/>
-      <c r="F42" s="247" t="n"/>
-      <c r="G42" s="247" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="142">
-      <c r="B43" s="246" t="inlineStr">
+      <c r="C42" s="238" t="n"/>
+      <c r="D42" s="248" t="n"/>
+      <c r="E42" s="248" t="n"/>
+      <c r="F42" s="248" t="n"/>
+      <c r="G42" s="248" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="143">
+      <c r="B43" s="247" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="C43" s="237" t="n"/>
-      <c r="D43" s="248" t="n"/>
-      <c r="E43" s="248" t="n"/>
-      <c r="F43" s="248" t="n"/>
-      <c r="G43" s="248" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="142">
-      <c r="B44" s="241" t="inlineStr">
+      <c r="C43" s="238" t="n"/>
+      <c r="D43" s="249" t="n"/>
+      <c r="E43" s="249" t="n"/>
+      <c r="F43" s="249" t="n"/>
+      <c r="G43" s="249" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="143">
+      <c r="B44" s="242" t="inlineStr">
         <is>
           <t>COST OF THE ROUND TRIP</t>
         </is>
       </c>
-      <c r="C44" s="242" t="n"/>
-      <c r="D44" s="242" t="n"/>
-      <c r="E44" s="242" t="n"/>
-      <c r="F44" s="242" t="n"/>
-      <c r="G44" s="242" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="142">
-      <c r="B45" s="238" t="inlineStr">
+      <c r="C44" s="243" t="n"/>
+      <c r="D44" s="243" t="n"/>
+      <c r="E44" s="243" t="n"/>
+      <c r="F44" s="243" t="n"/>
+      <c r="G44" s="243" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="143">
+      <c r="B45" s="239" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C45" s="237" t="n"/>
-      <c r="D45" s="239" t="n"/>
-      <c r="E45" s="239" t="n"/>
-      <c r="F45" s="239" t="n"/>
-      <c r="G45" s="239" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="142">
-      <c r="B46" s="238" t="inlineStr">
+      <c r="C45" s="238" t="n"/>
+      <c r="D45" s="240" t="n"/>
+      <c r="E45" s="240" t="n"/>
+      <c r="F45" s="240" t="n"/>
+      <c r="G45" s="240" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="143">
+      <c r="B46" s="239" t="inlineStr">
         <is>
           <t>Entry reference (touch)</t>
         </is>
       </c>
-      <c r="C46" s="237" t="n"/>
-      <c r="D46" s="236" t="n"/>
-      <c r="E46" s="236" t="n"/>
-      <c r="F46" s="236" t="n"/>
-      <c r="G46" s="236" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="142">
-      <c r="B47" s="238" t="inlineStr">
+      <c r="C46" s="238" t="n"/>
+      <c r="D46" s="237" t="n"/>
+      <c r="E46" s="237" t="n"/>
+      <c r="F46" s="237" t="n"/>
+      <c r="G46" s="237" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="143">
+      <c r="B47" s="239" t="inlineStr">
         <is>
           <t>Commission</t>
         </is>
       </c>
-      <c r="C47" s="237" t="inlineStr">
+      <c r="C47" s="238" t="inlineStr">
         <is>
           <t>contracts x rate x LOTS</t>
         </is>
       </c>
-      <c r="D47" s="245" t="n"/>
-      <c r="E47" s="245" t="n"/>
-      <c r="F47" s="245" t="n"/>
-      <c r="G47" s="245" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="142">
-      <c r="B48" s="238" t="inlineStr">
+      <c r="D47" s="246" t="n"/>
+      <c r="E47" s="246" t="n"/>
+      <c r="F47" s="246" t="n"/>
+      <c r="G47" s="246" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="143">
+      <c r="B48" s="239" t="inlineStr">
         <is>
           <t>Crossing cost - LEGGING</t>
         </is>
       </c>
-      <c r="C48" s="237" t="n"/>
-      <c r="D48" s="245" t="n"/>
-      <c r="E48" s="245" t="n"/>
-      <c r="F48" s="245" t="n"/>
-      <c r="G48" s="245" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="142">
-      <c r="B49" s="238" t="inlineStr">
+      <c r="C48" s="238" t="n"/>
+      <c r="D48" s="246" t="n"/>
+      <c r="E48" s="246" t="n"/>
+      <c r="F48" s="246" t="n"/>
+      <c r="G48" s="246" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="143">
+      <c r="B49" s="239" t="inlineStr">
         <is>
           <t>Crossing cost - LISTED</t>
         </is>
       </c>
-      <c r="C49" s="237" t="n"/>
-      <c r="D49" s="245" t="n"/>
-      <c r="E49" s="245" t="n"/>
-      <c r="F49" s="245" t="n"/>
-      <c r="G49" s="245" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="142">
-      <c r="B50" s="246" t="inlineStr">
+      <c r="C49" s="238" t="n"/>
+      <c r="D49" s="246" t="n"/>
+      <c r="E49" s="246" t="n"/>
+      <c r="F49" s="246" t="n"/>
+      <c r="G49" s="246" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="143">
+      <c r="B50" s="247" t="inlineStr">
         <is>
           <t>TOTAL COST (this mode)</t>
         </is>
       </c>
-      <c r="C50" s="237" t="n"/>
-      <c r="D50" s="249" t="n"/>
-      <c r="E50" s="249" t="n"/>
-      <c r="F50" s="249" t="n"/>
-      <c r="G50" s="249" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="142">
-      <c r="B51" s="241" t="inlineStr">
+      <c r="C50" s="238" t="n"/>
+      <c r="D50" s="250" t="n"/>
+      <c r="E50" s="250" t="n"/>
+      <c r="F50" s="250" t="n"/>
+      <c r="G50" s="250" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="143">
+      <c r="B51" s="242" t="inlineStr">
         <is>
           <t>TAKE PROFIT  (exits act on MONEY, never on z)</t>
         </is>
       </c>
-      <c r="C51" s="242" t="n"/>
-      <c r="D51" s="242" t="n"/>
-      <c r="E51" s="242" t="n"/>
-      <c r="F51" s="242" t="n"/>
-      <c r="G51" s="242" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="142">
-      <c r="B52" s="238" t="inlineStr">
+      <c r="C51" s="243" t="n"/>
+      <c r="D51" s="243" t="n"/>
+      <c r="E51" s="243" t="n"/>
+      <c r="F51" s="243" t="n"/>
+      <c r="G51" s="243" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="143">
+      <c r="B52" s="239" t="inlineStr">
         <is>
           <t>TP rule in force</t>
         </is>
       </c>
-      <c r="C52" s="237" t="n"/>
-      <c r="D52" s="239" t="n"/>
-      <c r="E52" s="239" t="n"/>
-      <c r="F52" s="239" t="n"/>
-      <c r="G52" s="239" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="142">
-      <c r="B53" s="238" t="inlineStr">
+      <c r="C52" s="238" t="n"/>
+      <c r="D52" s="240" t="n"/>
+      <c r="E52" s="240" t="n"/>
+      <c r="F52" s="240" t="n"/>
+      <c r="G52" s="240" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="143">
+      <c r="B53" s="239" t="inlineStr">
         <is>
           <t>Notional (per NOTIONAL_BASIS)</t>
         </is>
       </c>
-      <c r="C53" s="237" t="n"/>
-      <c r="D53" s="245" t="n"/>
-      <c r="E53" s="245" t="n"/>
-      <c r="F53" s="245" t="n"/>
-      <c r="G53" s="245" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="142">
-      <c r="B54" s="238" t="inlineStr">
+      <c r="C53" s="238" t="n"/>
+      <c r="D53" s="246" t="n"/>
+      <c r="E53" s="246" t="n"/>
+      <c r="F53" s="246" t="n"/>
+      <c r="G53" s="246" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="143">
+      <c r="B54" s="239" t="inlineStr">
         <is>
           <t>Win target (WIN_PCT x notional)</t>
         </is>
       </c>
-      <c r="C54" s="237" t="n"/>
-      <c r="D54" s="245" t="n"/>
-      <c r="E54" s="245" t="n"/>
-      <c r="F54" s="245" t="n"/>
-      <c r="G54" s="245" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="142">
-      <c r="B55" s="238" t="inlineStr">
+      <c r="C54" s="238" t="n"/>
+      <c r="D54" s="246" t="n"/>
+      <c r="E54" s="246" t="n"/>
+      <c r="F54" s="246" t="n"/>
+      <c r="G54" s="246" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="143">
+      <c r="B55" s="239" t="inlineStr">
         <is>
           <t>Costs in spread units</t>
         </is>
       </c>
-      <c r="C55" s="237" t="n"/>
-      <c r="D55" s="236" t="n"/>
-      <c r="E55" s="236" t="n"/>
-      <c r="F55" s="236" t="n"/>
-      <c r="G55" s="236" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="142">
-      <c r="B56" s="238" t="inlineStr">
+      <c r="C55" s="238" t="n"/>
+      <c r="D55" s="237" t="n"/>
+      <c r="E55" s="237" t="n"/>
+      <c r="F55" s="237" t="n"/>
+      <c r="G55" s="237" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="143">
+      <c r="B56" s="239" t="inlineStr">
         <is>
           <t>Win in spread units</t>
         </is>
       </c>
-      <c r="C56" s="237" t="n"/>
-      <c r="D56" s="236" t="n"/>
-      <c r="E56" s="236" t="n"/>
-      <c r="F56" s="236" t="n"/>
-      <c r="G56" s="236" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="142">
-      <c r="B57" s="238" t="inlineStr">
+      <c r="C56" s="238" t="n"/>
+      <c r="D56" s="237" t="n"/>
+      <c r="E56" s="237" t="n"/>
+      <c r="F56" s="237" t="n"/>
+      <c r="G56" s="237" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="143">
+      <c r="B57" s="239" t="inlineStr">
         <is>
           <t>Break-even spread</t>
         </is>
       </c>
-      <c r="C57" s="237" t="inlineStr">
+      <c r="C57" s="238" t="inlineStr">
         <is>
           <t>absolute level</t>
         </is>
       </c>
-      <c r="D57" s="236" t="n"/>
-      <c r="E57" s="236" t="n"/>
-      <c r="F57" s="236" t="n"/>
-      <c r="G57" s="236" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="142">
-      <c r="B58" s="246" t="inlineStr">
+      <c r="D57" s="237" t="n"/>
+      <c r="E57" s="237" t="n"/>
+      <c r="F57" s="237" t="n"/>
+      <c r="G57" s="237" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="143">
+      <c r="B58" s="247" t="inlineStr">
         <is>
           <t>TAKE-PROFIT spread</t>
         </is>
       </c>
-      <c r="C58" s="237" t="inlineStr">
+      <c r="C58" s="238" t="inlineStr">
         <is>
           <t>absolute level</t>
         </is>
       </c>
-      <c r="D58" s="250" t="n"/>
-      <c r="E58" s="250" t="n"/>
-      <c r="F58" s="250" t="n"/>
-      <c r="G58" s="250" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="142">
-      <c r="B59" s="238" t="inlineStr">
+      <c r="D58" s="251" t="n"/>
+      <c r="E58" s="251" t="n"/>
+      <c r="F58" s="251" t="n"/>
+      <c r="G58" s="251" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="143">
+      <c r="B59" s="239" t="inlineStr">
         <is>
           <t>TP distance</t>
         </is>
       </c>
-      <c r="C59" s="237" t="inlineStr">
+      <c r="C59" s="238" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D59" s="236" t="n"/>
-      <c r="E59" s="236" t="n"/>
-      <c r="F59" s="236" t="n"/>
-      <c r="G59" s="236" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="142">
-      <c r="B60" s="238" t="inlineStr">
+      <c r="D59" s="237" t="n"/>
+      <c r="E59" s="237" t="n"/>
+      <c r="F59" s="237" t="n"/>
+      <c r="G59" s="237" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="143">
+      <c r="B60" s="239" t="inlineStr">
         <is>
           <t>TP in sigma</t>
         </is>
       </c>
-      <c r="C60" s="237" t="inlineStr">
+      <c r="C60" s="238" t="inlineStr">
         <is>
           <t>x sigma</t>
         </is>
       </c>
-      <c r="D60" s="243" t="n"/>
-      <c r="E60" s="243" t="n"/>
-      <c r="F60" s="243" t="n"/>
-      <c r="G60" s="243" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="142">
-      <c r="B61" s="238" t="inlineStr">
+      <c r="D60" s="244" t="n"/>
+      <c r="E60" s="244" t="n"/>
+      <c r="F60" s="244" t="n"/>
+      <c r="G60" s="244" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="143">
+      <c r="B61" s="239" t="inlineStr">
         <is>
           <t>Target z</t>
         </is>
       </c>
-      <c r="C61" s="237" t="inlineStr">
+      <c r="C61" s="238" t="inlineStr">
         <is>
           <t>z at the TP level</t>
         </is>
       </c>
-      <c r="D61" s="243" t="n"/>
-      <c r="E61" s="243" t="n"/>
-      <c r="F61" s="243" t="n"/>
-      <c r="G61" s="243" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="142">
-      <c r="B62" s="238" t="inlineStr">
+      <c r="D61" s="244" t="n"/>
+      <c r="E61" s="244" t="n"/>
+      <c r="F61" s="244" t="n"/>
+      <c r="G61" s="244" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="143">
+      <c r="B62" s="239" t="inlineStr">
         <is>
           <t>TP beyond the mean?</t>
         </is>
       </c>
-      <c r="C62" s="237" t="n"/>
-      <c r="D62" s="239" t="n"/>
-      <c r="E62" s="239" t="n"/>
-      <c r="F62" s="239" t="n"/>
-      <c r="G62" s="239" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="142">
-      <c r="B63" s="241" t="inlineStr">
+      <c r="C62" s="238" t="n"/>
+      <c r="D62" s="240" t="n"/>
+      <c r="E62" s="240" t="n"/>
+      <c r="F62" s="240" t="n"/>
+      <c r="G62" s="240" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="143">
+      <c r="B63" s="242" t="inlineStr">
         <is>
           <t>EDGE FILTER  (a separate gate from ENTRY_Z)</t>
         </is>
       </c>
-      <c r="C63" s="242" t="n"/>
-      <c r="D63" s="242" t="n"/>
-      <c r="E63" s="242" t="n"/>
-      <c r="F63" s="242" t="n"/>
-      <c r="G63" s="242" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="142">
-      <c r="B64" s="238" t="inlineStr">
+      <c r="C63" s="243" t="n"/>
+      <c r="D63" s="243" t="n"/>
+      <c r="E63" s="243" t="n"/>
+      <c r="F63" s="243" t="n"/>
+      <c r="G63" s="243" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="143">
+      <c r="B64" s="239" t="inlineStr">
         <is>
           <t>Expected capture</t>
         </is>
       </c>
-      <c r="C64" s="237" t="inlineStr">
+      <c r="C64" s="238" t="inlineStr">
         <is>
           <t>0.5 x |z| x sigma x USD/pt x LOTS</t>
         </is>
       </c>
-      <c r="D64" s="245" t="n"/>
-      <c r="E64" s="245" t="n"/>
-      <c r="F64" s="245" t="n"/>
-      <c r="G64" s="245" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="142">
-      <c r="B65" s="238" t="inlineStr">
+      <c r="D64" s="246" t="n"/>
+      <c r="E64" s="246" t="n"/>
+      <c r="F64" s="246" t="n"/>
+      <c r="G64" s="246" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="143">
+      <c r="B65" s="239" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C65" s="237" t="inlineStr">
+      <c r="C65" s="238" t="inlineStr">
         <is>
           <t>EDGE_MULTIPLE x total cost</t>
         </is>
       </c>
-      <c r="D65" s="245" t="n"/>
-      <c r="E65" s="245" t="n"/>
-      <c r="F65" s="245" t="n"/>
-      <c r="G65" s="245" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="142">
-      <c r="B66" s="246" t="inlineStr">
+      <c r="D65" s="246" t="n"/>
+      <c r="E65" s="246" t="n"/>
+      <c r="F65" s="246" t="n"/>
+      <c r="G65" s="246" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="143">
+      <c r="B66" s="247" t="inlineStr">
         <is>
           <t>EDGE VERDICT</t>
         </is>
       </c>
-      <c r="C66" s="237" t="n"/>
-      <c r="D66" s="248" t="n"/>
-      <c r="E66" s="248" t="n"/>
-      <c r="F66" s="248" t="n"/>
-      <c r="G66" s="248" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="142">
-      <c r="B67" s="238" t="inlineStr">
+      <c r="C66" s="238" t="n"/>
+      <c r="D66" s="249" t="n"/>
+      <c r="E66" s="249" t="n"/>
+      <c r="F66" s="249" t="n"/>
+      <c r="G66" s="249" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="143">
+      <c r="B67" s="239" t="inlineStr">
         <is>
           <t>Min sigma to pass at live z</t>
         </is>
       </c>
-      <c r="C67" s="237" t="inlineStr">
+      <c r="C67" s="238" t="inlineStr">
         <is>
           <t>spread units</t>
         </is>
       </c>
-      <c r="D67" s="236" t="n"/>
-      <c r="E67" s="236" t="n"/>
-      <c r="F67" s="236" t="n"/>
-      <c r="G67" s="236" t="n"/>
+      <c r="D67" s="237" t="n"/>
+      <c r="E67" s="237" t="n"/>
+      <c r="F67" s="237" t="n"/>
+      <c r="G67" s="237" t="n"/>
     </row>
     <row r="68"/>
-    <row r="69" ht="15" customHeight="1" s="142">
-      <c r="B69" s="251" t="inlineStr">
+    <row r="69" ht="15" customHeight="1" s="143">
+      <c r="B69" s="252" t="inlineStr">
         <is>
           <t>The EDGE FILTER is a different gate from ENTRY_Z. ENTRY_Z decides when the chime fires; the edge filter asks whether the expected capture clears the round trip by EDGE_MULTIPLE. A highlighted z that fails the edge filter is still not a trade worth taking.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="142">
-      <c r="B70" s="229" t="inlineStr">
+    <row r="70" ht="15" customHeight="1" s="143">
+      <c r="B70" s="230" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES on Config decides whether a failing edge filter also silences the chime. It ships FALSE, so the chime follows ENTRY_Z alone.</t>
         </is>
@@ -3867,1732 +3881,1921 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="140" min="1" max="1"/>
-    <col width="34" customWidth="1" style="140" min="2" max="2"/>
-    <col width="14" customWidth="1" style="140" min="3" max="3"/>
-    <col width="10" customWidth="1" style="140" min="4" max="4"/>
-    <col width="96" customWidth="1" style="140" min="5" max="5"/>
-    <col width="30" customWidth="1" style="140" min="6" max="6"/>
-    <col width="12" customWidth="1" style="140" min="7" max="8"/>
-    <col width="10" customWidth="1" style="140" min="9" max="9"/>
-    <col width="8" customWidth="1" style="140" min="10" max="10"/>
-    <col width="34" customWidth="1" style="140" min="11" max="11"/>
+    <col width="30" customWidth="1" style="141" min="1" max="1"/>
+    <col width="34" customWidth="1" style="141" min="2" max="2"/>
+    <col width="14" customWidth="1" style="141" min="3" max="3"/>
+    <col width="10" customWidth="1" style="141" min="4" max="4"/>
+    <col width="96" customWidth="1" style="141" min="5" max="5"/>
+    <col width="30" customWidth="1" style="141" min="6" max="6"/>
+    <col width="12" customWidth="1" style="141" min="7" max="8"/>
+    <col width="10" customWidth="1" style="141" min="9" max="9"/>
+    <col width="8" customWidth="1" style="141" min="10" max="10"/>
+    <col width="34" customWidth="1" style="141" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.7" customHeight="1" s="142">
-      <c r="A1" s="252" t="inlineStr">
+    <row r="1" ht="19.7" customHeight="1" s="143">
+      <c r="A1" s="253" t="inlineStr">
         <is>
           <t>CONFIG  -  every parameter in its own labelled cell</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="142">
-      <c r="A2" s="253" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="A2" s="254" t="inlineStr">
         <is>
           <t>LEGEND:  yellow / blue = EDIT THESE.  black = formula, do not edit.  A changed value takes effect on the NEXT TIMER TICK - no restart, no VBA edit.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="142">
-      <c r="A3" s="229" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="143">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Exception: LOOKBACK_MIN redefines the window, so stored history is re-evaluated against the new width on the next stats refresh and the warm-up gates re-apply.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="142">
-      <c r="A4" s="229" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="143">
+      <c r="A4" s="230" t="inlineStr">
         <is>
           <t>VBA finds a parameter by matching column A exactly, so you may insert or reorder rows freely - but never rename a parameter in column A.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="142">
-      <c r="A5" s="253" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="A5" s="254" t="inlineStr">
         <is>
           <t>FOUR DECOUPLED RATES:  CAPTURE_MS (poll for a changed quote)  &gt;  STORE_MIN_INTERVAL_MS (what reaches the window)  &gt;  PRICE_REFRESH_MS (what repaints)  &gt;  STATS_REFRESH_MIN (when mean and sigma are republished).  Capturing fast buys alert latency, not a better sigma.</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="7" ht="15" customHeight="1" s="142">
-      <c r="A7" s="254" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="143">
+      <c r="A7" s="255" t="inlineStr">
         <is>
           <t>ENGINE  /  SAMPLING</t>
         </is>
       </c>
-      <c r="B7" s="254" t="n"/>
-      <c r="C7" s="254" t="n"/>
-      <c r="D7" s="254" t="n"/>
-      <c r="E7" s="254" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="142">
-      <c r="A8" s="255" t="inlineStr">
+      <c r="B7" s="255" t="n"/>
+      <c r="C7" s="255" t="n"/>
+      <c r="D7" s="255" t="n"/>
+      <c r="E7" s="255" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="143">
+      <c r="A8" s="256" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B8" s="255" t="inlineStr">
+      <c r="B8" s="256" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C8" s="255" t="inlineStr">
+      <c r="C8" s="256" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D8" s="255" t="inlineStr">
+      <c r="D8" s="256" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E8" s="255" t="inlineStr">
+      <c r="E8" s="256" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="142">
-      <c r="A9" s="246" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="A9" s="247" t="inlineStr">
         <is>
           <t>CAPTURE_MS</t>
         </is>
       </c>
-      <c r="B9" s="256" t="n">
+      <c r="B9" s="257" t="n">
         <v>100</v>
       </c>
-      <c r="C9" s="235" t="n">
+      <c r="C9" s="236" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="235" t="inlineStr">
+      <c r="D9" s="236" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E9" s="257" t="inlineStr">
+      <c r="E9" s="258" t="inlineStr">
         <is>
           <t>RATE 1 of 4. How often the feed is POLLED for a changed quote. Drives latency to the chime, NOT sigma - after dedupe the window holds quote changes, not poll ticks. Sub-second needs the user32 timer; at 1000+ the module falls back to Application.OnTime.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="142">
-      <c r="A10" s="246" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="143">
+      <c r="A10" s="247" t="inlineStr">
         <is>
           <t>STORE_MIN_INTERVAL_MS</t>
         </is>
       </c>
-      <c r="B10" s="256" t="n">
+      <c r="B10" s="257" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="235" t="n">
+      <c r="C10" s="236" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="235" t="inlineStr">
+      <c r="D10" s="236" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E10" s="257" t="inlineStr">
+      <c r="E10" s="258" t="inlineStr">
         <is>
           <t>RATE 2 of 4. Minimum spacing between STORED samples. 0 = full fidelity. Leave it at 0 for the first week or two to characterise the microstructure, then set 250-1000: subsampling a mean-reverting level series is unbiased, so it is 3-10x less memory for the same mean and sigma.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="142">
-      <c r="A11" s="246" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="143">
+      <c r="A11" s="247" t="inlineStr">
         <is>
           <t>PRICE_REFRESH_MS</t>
         </is>
       </c>
-      <c r="B11" s="256" t="n">
+      <c r="B11" s="257" t="n">
         <v>500</v>
       </c>
-      <c r="C11" s="235" t="n">
+      <c r="C11" s="236" t="n">
         <v>500</v>
       </c>
-      <c r="D11" s="235" t="inlineStr">
+      <c r="D11" s="236" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E11" s="257" t="inlineStr">
+      <c r="E11" s="258" t="inlineStr">
         <is>
           <t>RATE 3 of 4. How often the display may repaint. Independent of capture and of storage - a number showing more digits than the market moves in will appear to change constantly.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="142">
-      <c r="A12" s="246" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="143">
+      <c r="A12" s="247" t="inlineStr">
         <is>
           <t>CONFIG_REFRESH_MS</t>
         </is>
       </c>
-      <c r="B12" s="256" t="n">
+      <c r="B12" s="257" t="n">
         <v>1000</v>
       </c>
-      <c r="C12" s="235" t="n">
+      <c r="C12" s="236" t="n">
         <v>1000</v>
       </c>
-      <c r="D12" s="235" t="inlineStr">
+      <c r="D12" s="236" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E12" s="257" t="inlineStr">
+      <c r="E12" s="258" t="inlineStr">
         <is>
           <t>How often this sheet is re-read. A value changed here takes effect within this long - no restart, no VBA edit.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="142">
-      <c r="A13" s="246" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="143">
+      <c r="A13" s="247" t="inlineStr">
         <is>
           <t>RTD_THROTTLE_MS</t>
         </is>
       </c>
-      <c r="B13" s="256" t="n">
+      <c r="B13" s="257" t="n">
         <v>100</v>
       </c>
-      <c r="C13" s="235" t="n">
+      <c r="C13" s="236" t="n">
         <v>100</v>
       </c>
-      <c r="D13" s="235" t="inlineStr">
+      <c r="D13" s="236" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E13" s="257" t="inlineStr">
+      <c r="E13" s="258" t="inlineStr">
         <is>
           <t>Application.RTD.ThrottleInterval set on start. Match it to CAPTURE_MS. Excel's default is 2000.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="142">
-      <c r="A14" s="246" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="143">
+      <c r="A14" s="247" t="inlineStr">
         <is>
           <t>WATCHDOG_SEC</t>
         </is>
       </c>
-      <c r="B14" s="256" t="n">
+      <c r="B14" s="257" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="235" t="n">
+      <c r="C14" s="236" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="235" t="inlineStr">
+      <c r="D14" s="236" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E14" s="257" t="inlineStr">
+      <c r="E14" s="258" t="inlineStr">
         <is>
           <t>Application.OnTime watchdog. Re-arms the high-resolution timer if Excel killed it (a modal dialog will) and picks up a changed CAPTURE_MS.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="142">
-      <c r="A15" s="246" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="143">
+      <c r="A15" s="247" t="inlineStr">
         <is>
           <t>STALE_SEC</t>
         </is>
       </c>
-      <c r="B15" s="256" t="n">
+      <c r="B15" s="257" t="n">
         <v>15</v>
       </c>
-      <c r="C15" s="235" t="n">
+      <c r="C15" s="236" t="n">
         <v>15</v>
       </c>
-      <c r="D15" s="235" t="inlineStr">
+      <c r="D15" s="236" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E15" s="257" t="inlineStr">
+      <c r="E15" s="258" t="inlineStr">
         <is>
           <t>No new quote id for this long =&gt; feed marked STALE and alerts go silent.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="142">
-      <c r="A16" s="246" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="143">
+      <c r="A16" s="247" t="inlineStr">
         <is>
           <t>FLUSH_SEC</t>
         </is>
       </c>
-      <c r="B16" s="256" t="n">
+      <c r="B16" s="257" t="n">
         <v>60</v>
       </c>
-      <c r="C16" s="235" t="n">
+      <c r="C16" s="236" t="n">
         <v>60</v>
       </c>
-      <c r="D16" s="235" t="inlineStr">
+      <c r="D16" s="236" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E16" s="257" t="inlineStr">
+      <c r="E16" s="258" t="inlineStr">
         <is>
           <t>How often the recovery snapshot is written to the hidden Buffer sheet.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="142">
-      <c r="A17" s="246" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="143">
+      <c r="A17" s="247" t="inlineStr">
         <is>
           <t>FLUSH_DECIMATE_MS</t>
         </is>
       </c>
-      <c r="B17" s="256" t="n">
+      <c r="B17" s="257" t="n">
         <v>1000</v>
       </c>
-      <c r="C17" s="235" t="n">
+      <c r="C17" s="236" t="n">
         <v>1000</v>
       </c>
-      <c r="D17" s="235" t="inlineStr">
+      <c r="D17" s="236" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="E17" s="257" t="inlineStr">
+      <c r="E17" s="258" t="inlineStr">
         <is>
           <t>The recovery snapshot is decimated to this spacing. Unbiased for mean and sigma, and it keeps a 120-minute window near 7,200 rows instead of tens of thousands.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="142">
-      <c r="A18" s="246" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="143">
+      <c r="A18" s="247" t="inlineStr">
         <is>
           <t>BUFFER_CAPACITY</t>
         </is>
       </c>
-      <c r="B18" s="256" t="n">
+      <c r="B18" s="257" t="n">
         <v>80000</v>
       </c>
-      <c r="C18" s="235" t="n">
+      <c r="C18" s="236" t="n">
         <v>80000</v>
       </c>
-      <c r="D18" s="235" t="inlineStr">
+      <c r="D18" s="236" t="inlineStr">
         <is>
           <t>samples</t>
         </is>
       </c>
-      <c r="E18" s="257" t="inlineStr">
+      <c r="E18" s="258" t="inlineStr">
         <is>
           <t>Circular-buffer capacity per spread. 4 spreads x 80,000 x 16 bytes is about 5 MB of VBA array, held in memory, not in cells.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="142">
-      <c r="A19" s="246" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="143">
+      <c r="A19" s="247" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_ENABLED</t>
         </is>
       </c>
-      <c r="B19" s="256" t="b">
+      <c r="B19" s="257" t="b">
         <v>1</v>
       </c>
-      <c r="C19" s="235" t="b">
+      <c r="C19" s="236" t="b">
         <v>1</v>
       </c>
-      <c r="D19" s="235" t="inlineStr">
+      <c r="D19" s="236" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E19" s="257" t="inlineStr">
+      <c r="E19" s="258" t="inlineStr">
         <is>
           <t>Write every CHANGED quote to a CSV on disk. This is the one chance to characterise the spread's microstructure and to verify that coarser storage loses nothing real. Turn it off once STORE_MIN_INTERVAL_MS is set.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="142">
-      <c r="A20" s="246" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="143">
+      <c r="A20" s="247" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_PATH</t>
         </is>
       </c>
-      <c r="B20" s="258" t="n"/>
-      <c r="C20" s="235" t="n"/>
-      <c r="D20" s="235" t="inlineStr">
+      <c r="B20" s="259" t="n"/>
+      <c r="C20" s="236" t="n"/>
+      <c r="D20" s="236" t="inlineStr">
         <is>
           <t>folder</t>
         </is>
       </c>
-      <c r="E20" s="257" t="inlineStr">
+      <c r="E20" s="258" t="inlineStr">
         <is>
           <t>Folder for the tick CSVs. Blank = a 'ticks' folder beside the workbook. One file per spread per day.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="142">
-      <c r="A21" s="246" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="143">
+      <c r="A21" s="247" t="inlineStr">
         <is>
           <t>TICK_ARCHIVE_BATCH</t>
         </is>
       </c>
-      <c r="B21" s="256" t="n">
+      <c r="B21" s="257" t="n">
         <v>500</v>
       </c>
-      <c r="C21" s="235" t="n">
+      <c r="C21" s="236" t="n">
         <v>500</v>
       </c>
-      <c r="D21" s="235" t="inlineStr">
+      <c r="D21" s="236" t="inlineStr">
         <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="E21" s="257" t="inlineStr">
+      <c r="E21" s="258" t="inlineStr">
         <is>
           <t>Lines buffered in memory before a file write, so archiving never stalls the capture timer.</t>
         </is>
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="15" customHeight="1" s="142">
-      <c r="A23" s="254" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="143">
+      <c r="A23" s="255" t="inlineStr">
         <is>
           <t>WINDOW  /  STATISTICS</t>
         </is>
       </c>
-      <c r="B23" s="254" t="n"/>
-      <c r="C23" s="254" t="n"/>
-      <c r="D23" s="254" t="n"/>
-      <c r="E23" s="254" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="142">
-      <c r="A24" s="255" t="inlineStr">
+      <c r="B23" s="255" t="n"/>
+      <c r="C23" s="255" t="n"/>
+      <c r="D23" s="255" t="n"/>
+      <c r="E23" s="255" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="143">
+      <c r="A24" s="256" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B24" s="255" t="inlineStr">
+      <c r="B24" s="256" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C24" s="255" t="inlineStr">
+      <c r="C24" s="256" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D24" s="255" t="inlineStr">
+      <c r="D24" s="256" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E24" s="255" t="inlineStr">
+      <c r="E24" s="256" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="142">
-      <c r="A25" s="246" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="A25" s="247" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="B25" s="256" t="n">
+      <c r="B25" s="257" t="n">
         <v>120</v>
       </c>
-      <c r="C25" s="235" t="n">
+      <c r="C25" s="236" t="n">
         <v>120</v>
       </c>
-      <c r="D25" s="235" t="inlineStr">
+      <c r="D25" s="236" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E25" s="257" t="inlineStr">
+      <c r="E25" s="258" t="inlineStr">
         <is>
           <t>Rolling window width (90 or 120). Changing it re-evaluates stored history on the next stats refresh and re-applies the warm-up gates.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="142">
-      <c r="A26" s="246" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="143">
+      <c r="A26" s="247" t="inlineStr">
         <is>
           <t>STATS_REFRESH_MIN</t>
         </is>
       </c>
-      <c r="B26" s="256" t="n">
+      <c r="B26" s="257" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="235" t="n">
+      <c r="C26" s="236" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="235" t="inlineStr">
+      <c r="D26" s="236" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E26" s="257" t="inlineStr">
+      <c r="E26" s="258" t="inlineStr">
         <is>
           <t>How often mean/sigma are recomputed and re-published. Held FROZEN in between; live z is measured against the frozen values.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="142">
-      <c r="A27" s="246" t="inlineStr">
+    <row r="27" ht="15" customHeight="1" s="143">
+      <c r="A27" s="247" t="inlineStr">
         <is>
           <t>MIN_SAMPLES</t>
         </is>
       </c>
-      <c r="B27" s="256" t="n">
+      <c r="B27" s="257" t="n">
         <v>300</v>
       </c>
-      <c r="C27" s="235" t="n">
+      <c r="C27" s="236" t="n">
         <v>300</v>
       </c>
-      <c r="D27" s="235" t="inlineStr">
+      <c r="D27" s="236" t="inlineStr">
         <is>
           <t>quotes</t>
         </is>
       </c>
-      <c r="E27" s="257" t="inlineStr">
+      <c r="E27" s="258" t="inlineStr">
         <is>
           <t>Warm-up gate 1. Quotes needed before any z is shown.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="142">
-      <c r="A28" s="246" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="A28" s="247" t="inlineStr">
         <is>
           <t>MIN_HISTORY_MIN</t>
         </is>
       </c>
-      <c r="B28" s="256" t="n">
+      <c r="B28" s="257" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="235" t="n">
+      <c r="C28" s="236" t="n">
         <v>120</v>
       </c>
-      <c r="D28" s="235" t="inlineStr">
+      <c r="D28" s="236" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E28" s="257" t="inlineStr">
+      <c r="E28" s="258" t="inlineStr">
         <is>
           <t>Warm-up gate 2. Window span needed before any z is shown. BOTH gates must pass. MUST BE LESS THAN LOOKBACK_MIN: eviction drops samples older than the lookback, so the span approaches it but never reaches it, and a value at or above LOOKBACK_MIN would never be satisfied. Anything above 98% of LOOKBACK_MIN is clamped to that, and the clamp is noted once in the Log.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="142">
-      <c r="A29" s="246" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="143">
+      <c r="A29" s="247" t="inlineStr">
         <is>
           <t>MIN_SIGMA</t>
         </is>
       </c>
-      <c r="B29" s="256" t="n">
+      <c r="B29" s="257" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="235" t="n">
+      <c r="C29" s="236" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="235" t="inlineStr">
+      <c r="D29" s="236" t="inlineStr">
         <is>
           <t>spread</t>
         </is>
       </c>
-      <c r="E29" s="257" t="inlineStr">
+      <c r="E29" s="258" t="inlineStr">
         <is>
           <t>Sigma floor. Below this the window is degenerate and NO z is shown. Set once sigma has actually been measured.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="142">
-      <c r="A30" s="246" t="inlineStr">
+    <row r="30" ht="15" customHeight="1" s="143">
+      <c r="A30" s="247" t="inlineStr">
         <is>
           <t>MAX_ABS_Z</t>
         </is>
       </c>
-      <c r="B30" s="256" t="n">
+      <c r="B30" s="257" t="n">
         <v>25</v>
       </c>
-      <c r="C30" s="235" t="n">
+      <c r="C30" s="236" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="235" t="inlineStr">
+      <c r="D30" s="236" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E30" s="257" t="inlineStr">
+      <c r="E30" s="258" t="inlineStr">
         <is>
           <t>Absurd-z guard. Above this, show 'no usable z' rather than a number.</t>
         </is>
       </c>
     </row>
     <row r="31"/>
-    <row r="32" ht="15" customHeight="1" s="142">
-      <c r="A32" s="254" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="143">
+      <c r="A32" s="255" t="inlineStr">
         <is>
           <t>SIGNAL THRESHOLDS</t>
         </is>
       </c>
-      <c r="B32" s="254" t="n"/>
-      <c r="C32" s="254" t="n"/>
-      <c r="D32" s="254" t="n"/>
-      <c r="E32" s="254" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="142">
-      <c r="A33" s="255" t="inlineStr">
+      <c r="B32" s="255" t="n"/>
+      <c r="C32" s="255" t="n"/>
+      <c r="D32" s="255" t="n"/>
+      <c r="E32" s="255" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="143">
+      <c r="A33" s="256" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B33" s="255" t="inlineStr">
+      <c r="B33" s="256" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C33" s="255" t="inlineStr">
+      <c r="C33" s="256" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D33" s="255" t="inlineStr">
+      <c r="D33" s="256" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E33" s="255" t="inlineStr">
+      <c r="E33" s="256" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="142">
-      <c r="A34" s="246" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="143">
+      <c r="A34" s="247" t="inlineStr">
         <is>
           <t>ENTRY_Z</t>
         </is>
       </c>
-      <c r="B34" s="259" t="n">
+      <c r="B34" s="260" t="n">
         <v>2.5</v>
       </c>
-      <c r="C34" s="260" t="n">
+      <c r="C34" s="261" t="n">
         <v>2.5</v>
       </c>
-      <c r="D34" s="235" t="inlineStr">
+      <c r="D34" s="236" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E34" s="257" t="inlineStr">
+      <c r="E34" s="258" t="inlineStr">
         <is>
           <t>Highlight and chime at or above this |z|. 2.0 and 2.5 are both reasonable; 2.0 fires more often and needs a larger sigma to stay worth trading.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="142">
-      <c r="A35" s="246" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="143">
+      <c r="A35" s="247" t="inlineStr">
         <is>
           <t>MAX_ENTRY_Z</t>
         </is>
       </c>
-      <c r="B35" s="259" t="n">
+      <c r="B35" s="260" t="n">
         <v>4.5</v>
       </c>
-      <c r="C35" s="260" t="n">
+      <c r="C35" s="261" t="n">
         <v>4.5</v>
       </c>
-      <c r="D35" s="235" t="inlineStr">
+      <c r="D35" s="236" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E35" s="257" t="inlineStr">
+      <c r="E35" s="258" t="inlineStr">
         <is>
           <t>Entry CEILING. At or above this, do NOT highlight - that is a momentum spike, not a reversion setup. Keep the band at least 1 sigma wide.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="142">
-      <c r="A36" s="246" t="inlineStr">
+    <row r="36" ht="15" customHeight="1" s="143">
+      <c r="A36" s="247" t="inlineStr">
         <is>
           <t>THIN_FEED_QPM</t>
         </is>
       </c>
-      <c r="B36" s="256" t="n">
+      <c r="B36" s="257" t="n">
         <v>6</v>
       </c>
-      <c r="C36" s="235" t="n">
+      <c r="C36" s="236" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="235" t="inlineStr">
+      <c r="D36" s="236" t="inlineStr">
         <is>
           <t>q/min</t>
         </is>
       </c>
-      <c r="E36" s="257" t="inlineStr">
+      <c r="E36" s="258" t="inlineStr">
         <is>
           <t>Feed rate at or below which the quotes/min display turns amber.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="142">
-      <c r="A37" s="246" t="inlineStr">
+    <row r="37" ht="15" customHeight="1" s="143">
+      <c r="A37" s="247" t="inlineStr">
         <is>
           <t>SPREAD_QUOTE_CONVENTION</t>
         </is>
       </c>
-      <c r="B37" s="258" t="inlineStr">
+      <c r="B37" s="259" t="inlineStr">
         <is>
           <t>CROSSING</t>
         </is>
       </c>
-      <c r="C37" s="235" t="inlineStr">
+      <c r="C37" s="236" t="inlineStr">
         <is>
           <t>CROSSING</t>
         </is>
       </c>
-      <c r="D37" s="235" t="inlineStr">
+      <c r="D37" s="236" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E37" s="257" t="inlineStr">
+      <c r="E37" s="258" t="inlineStr">
         <is>
           <t>How the spread rows on Dashboard quote Bid and Ask. CROSSING: sell LegB at the bid and buy LegA at the ask, mirrored for the ask - the Gap is then the true cost of crossing and is always positive. SAME_SIDE: bid-minus-bid and ask-minus-ask, as the original sheet's rows 9 computed. Under SAME_SIDE the Gap is a DIFFERENCE of gaps, which understates the crossing cost and can go negative.</t>
         </is>
       </c>
     </row>
     <row r="38"/>
-    <row r="39" ht="15" customHeight="1" s="142">
-      <c r="A39" s="254" t="inlineStr">
+    <row r="39" ht="15" customHeight="1" s="143">
+      <c r="A39" s="255" t="inlineStr">
         <is>
           <t>SIZING  /  COSTS</t>
         </is>
       </c>
-      <c r="B39" s="254" t="n"/>
-      <c r="C39" s="254" t="n"/>
-      <c r="D39" s="254" t="n"/>
-      <c r="E39" s="254" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="142">
-      <c r="A40" s="255" t="inlineStr">
+      <c r="B39" s="255" t="n"/>
+      <c r="C39" s="255" t="n"/>
+      <c r="D39" s="255" t="n"/>
+      <c r="E39" s="255" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="143">
+      <c r="A40" s="256" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B40" s="255" t="inlineStr">
+      <c r="B40" s="256" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C40" s="255" t="inlineStr">
+      <c r="C40" s="256" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D40" s="255" t="inlineStr">
+      <c r="D40" s="256" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E40" s="255" t="inlineStr">
+      <c r="E40" s="256" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="142">
-      <c r="A41" s="246" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="143">
+      <c r="A41" s="247" t="inlineStr">
         <is>
           <t>LOTS</t>
         </is>
       </c>
-      <c r="B41" s="256" t="n">
+      <c r="B41" s="257" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="235" t="n">
+      <c r="C41" s="236" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="235" t="inlineStr">
+      <c r="D41" s="236" t="inlineStr">
         <is>
           <t>lots</t>
         </is>
       </c>
-      <c r="E41" s="257" t="inlineStr">
+      <c r="E41" s="258" t="inlineStr">
         <is>
           <t>Contracts per leg, for the cost and take-profit maths.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="142">
-      <c r="A42" s="246" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="143">
+      <c r="A42" s="247" t="inlineStr">
         <is>
           <t>TP_MODE</t>
         </is>
       </c>
-      <c r="B42" s="258" t="inlineStr">
+      <c r="B42" s="259" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL</t>
         </is>
       </c>
-      <c r="C42" s="235" t="inlineStr">
+      <c r="C42" s="236" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL</t>
         </is>
       </c>
-      <c r="D42" s="235" t="inlineStr">
+      <c r="D42" s="236" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E42" s="257" t="inlineStr">
+      <c r="E42" s="258" t="inlineStr">
         <is>
           <t>PCT_NOTIONAL: Take Profit = Entry + Costs + (WIN_PCT x Notional). TARGET_USD: the older rule, Take Profit = Entry + Costs + TARGET_NET_USD.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="142">
-      <c r="A43" s="246" t="inlineStr">
+    <row r="43" ht="15" customHeight="1" s="143">
+      <c r="A43" s="247" t="inlineStr">
         <is>
           <t>WIN_PCT</t>
         </is>
       </c>
-      <c r="B43" s="259" t="n">
+      <c r="B43" s="260" t="n">
         <v>0.01</v>
       </c>
-      <c r="C43" s="260" t="n">
+      <c r="C43" s="261" t="n">
         <v>0.01</v>
       </c>
-      <c r="D43" s="235" t="inlineStr">
+      <c r="D43" s="236" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="E43" s="257" t="inlineStr">
+      <c r="E43" s="258" t="inlineStr">
         <is>
           <t>Percentage win, as a FRACTION - 0.01 is 1%, 0.02 is 2%. Used only when TP_MODE = PCT_NOTIONAL.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="142">
-      <c r="A44" s="246" t="inlineStr">
+    <row r="44" ht="15" customHeight="1" s="143">
+      <c r="A44" s="247" t="inlineStr">
         <is>
           <t>NOTIONAL_BASIS</t>
         </is>
       </c>
-      <c r="B44" s="258" t="inlineStr">
+      <c r="B44" s="259" t="inlineStr">
         <is>
           <t>SPREAD_VALUE</t>
         </is>
       </c>
-      <c r="C44" s="235" t="inlineStr">
+      <c r="C44" s="236" t="inlineStr">
         <is>
           <t>SPREAD_VALUE</t>
         </is>
       </c>
-      <c r="D44" s="235" t="inlineStr">
+      <c r="D44" s="236" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E44" s="257" t="inlineStr">
+      <c r="E44" s="258" t="inlineStr">
         <is>
           <t>What WIN_PCT is taken OF. SPREAD_VALUE = |spread| x USD/pt x LOTS. ONE_LEG = the crude leg's full contract value. BOTH_LEGS = both legs' contract value added. These differ by roughly 10x - read the note below the table before changing it.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="142">
-      <c r="A45" s="246" t="inlineStr">
+    <row r="45" ht="15" customHeight="1" s="143">
+      <c r="A45" s="247" t="inlineStr">
         <is>
           <t>TP_ENTRY_BASIS</t>
         </is>
       </c>
-      <c r="B45" s="258" t="inlineStr">
+      <c r="B45" s="259" t="inlineStr">
         <is>
           <t>BID</t>
         </is>
       </c>
-      <c r="C45" s="235" t="inlineStr">
+      <c r="C45" s="236" t="inlineStr">
         <is>
           <t>BID</t>
         </is>
       </c>
-      <c r="D45" s="235" t="inlineStr">
+      <c r="D45" s="236" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E45" s="257" t="inlineStr">
+      <c r="E45" s="258" t="inlineStr">
         <is>
           <t>Which price the take-profit is measured from. BID: always the bid, the price you sell at - exact for a High-to-Low trade, optimistic by the spread's own gap on a Low-to-High one. TOUCH: prices each direction at the side it really trades on (bid when selling, ask when buying).</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="142">
-      <c r="A46" s="246" t="inlineStr">
+    <row r="46" ht="15" customHeight="1" s="143">
+      <c r="A46" s="247" t="inlineStr">
         <is>
           <t>TARGET_NET_USD</t>
         </is>
       </c>
-      <c r="B46" s="256" t="n">
+      <c r="B46" s="257" t="n">
         <v>150</v>
       </c>
-      <c r="C46" s="235" t="n">
+      <c r="C46" s="236" t="n">
         <v>150</v>
       </c>
-      <c r="D46" s="235" t="inlineStr">
+      <c r="D46" s="236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E46" s="257" t="inlineStr">
+      <c r="E46" s="258" t="inlineStr">
         <is>
           <t>Desired profit AFTER all costs. Used only when TP_MODE = TARGET_USD.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="142">
-      <c r="A47" s="246" t="inlineStr">
+    <row r="47" ht="15" customHeight="1" s="143">
+      <c r="A47" s="247" t="inlineStr">
         <is>
           <t>EDGE_MULTIPLE</t>
         </is>
       </c>
-      <c r="B47" s="259" t="n">
+      <c r="B47" s="260" t="n">
         <v>1.5</v>
       </c>
-      <c r="C47" s="260" t="n">
+      <c r="C47" s="261" t="n">
         <v>1.5</v>
       </c>
-      <c r="D47" s="235" t="inlineStr">
+      <c r="D47" s="236" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E47" s="257" t="inlineStr">
+      <c r="E47" s="258" t="inlineStr">
         <is>
           <t>Expected capture must clear the round trip by this multiple.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="142">
-      <c r="A48" s="246" t="inlineStr">
+    <row r="48" ht="15" customHeight="1" s="143">
+      <c r="A48" s="247" t="inlineStr">
         <is>
           <t>RATE_ORIENT_PER_SIDE</t>
         </is>
       </c>
-      <c r="B48" s="259" t="n">
+      <c r="B48" s="260" t="n">
         <v>0.35</v>
       </c>
-      <c r="C48" s="260" t="n">
+      <c r="C48" s="261" t="n">
         <v>0.35</v>
       </c>
-      <c r="D48" s="235" t="inlineStr">
+      <c r="D48" s="236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E48" s="257" t="inlineStr">
+      <c r="E48" s="258" t="inlineStr">
         <is>
           <t>Orient clearing + execution, per contract per side. Source: Orient rate card 2026-08-21, Ver.26.8.17.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="142">
-      <c r="A49" s="246" t="inlineStr">
+    <row r="49" ht="15" customHeight="1" s="143">
+      <c r="A49" s="247" t="inlineStr">
         <is>
           <t>RATE_FIX_PER_SIDE</t>
         </is>
       </c>
-      <c r="B49" s="259" t="n">
+      <c r="B49" s="260" t="n">
         <v>0.06</v>
       </c>
-      <c r="C49" s="260" t="n">
+      <c r="C49" s="261" t="n">
         <v>0.06</v>
       </c>
-      <c r="D49" s="235" t="inlineStr">
+      <c r="D49" s="236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E49" s="257" t="inlineStr">
+      <c r="E49" s="258" t="inlineStr">
         <is>
           <t>FIX / platform transaction fee, per contract per side. Same rate card.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="142">
-      <c r="A50" s="246" t="inlineStr">
+    <row r="50" ht="15" customHeight="1" s="143">
+      <c r="A50" s="247" t="inlineStr">
         <is>
           <t>RATE_CME_PER_SIDE</t>
         </is>
       </c>
-      <c r="B50" s="259" t="n">
+      <c r="B50" s="260" t="n">
         <v>1.5</v>
       </c>
-      <c r="C50" s="260" t="n">
+      <c r="C50" s="261" t="n">
         <v>1.5</v>
       </c>
-      <c r="D50" s="235" t="inlineStr">
+      <c r="D50" s="236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E50" s="257" t="inlineStr">
+      <c r="E50" s="258" t="inlineStr">
         <is>
           <t>CME exchange + clearing, per contract per side. Same rate card.</t>
         </is>
       </c>
     </row>
     <row r="51"/>
-    <row r="52" ht="15" customHeight="1" s="142">
-      <c r="A52" s="254" t="inlineStr">
+    <row r="52" ht="15" customHeight="1" s="143">
+      <c r="A52" s="255" t="inlineStr">
         <is>
           <t>AUDIBLE ALERT</t>
         </is>
       </c>
-      <c r="B52" s="254" t="n"/>
-      <c r="C52" s="254" t="n"/>
-      <c r="D52" s="254" t="n"/>
-      <c r="E52" s="254" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="142">
-      <c r="A53" s="255" t="inlineStr">
+      <c r="B52" s="255" t="n"/>
+      <c r="C52" s="255" t="n"/>
+      <c r="D52" s="255" t="n"/>
+      <c r="E52" s="255" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="143">
+      <c r="A53" s="256" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B53" s="255" t="inlineStr">
+      <c r="B53" s="256" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C53" s="255" t="inlineStr">
+      <c r="C53" s="256" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D53" s="255" t="inlineStr">
+      <c r="D53" s="256" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E53" s="255" t="inlineStr">
+      <c r="E53" s="256" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="142">
-      <c r="A54" s="246" t="inlineStr">
+    <row r="54" ht="15" customHeight="1" s="143">
+      <c r="A54" s="247" t="inlineStr">
         <is>
           <t>ALERT_ENABLED</t>
         </is>
       </c>
-      <c r="B54" s="256" t="b">
+      <c r="B54" s="257" t="b">
         <v>1</v>
       </c>
-      <c r="C54" s="235" t="b">
+      <c r="C54" s="236" t="b">
         <v>1</v>
       </c>
-      <c r="D54" s="235" t="inlineStr">
+      <c r="D54" s="236" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E54" s="257" t="inlineStr">
+      <c r="E54" s="258" t="inlineStr">
         <is>
           <t>MASTER MUTE. FALSE silences every sound.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="142">
-      <c r="A55" s="246" t="inlineStr">
+    <row r="55" ht="15" customHeight="1" s="143">
+      <c r="A55" s="247" t="inlineStr">
         <is>
           <t>ALERT_SOUND_PATH</t>
         </is>
       </c>
-      <c r="B55" s="258" t="inlineStr">
+      <c r="B55" s="259" t="inlineStr">
         <is>
           <t>C:\Windows\Media\chimes.wav</t>
         </is>
       </c>
-      <c r="C55" s="235" t="inlineStr">
+      <c r="C55" s="236" t="inlineStr">
         <is>
           <t>C:\Windows\Media\chimes.wav</t>
         </is>
       </c>
-      <c r="D55" s="235" t="inlineStr">
+      <c r="D55" s="236" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E55" s="257" t="inlineStr">
+      <c r="E55" s="258" t="inlineStr">
         <is>
           <t>Single short 'ting' played on an entry-band crossing.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="142">
-      <c r="A56" s="246" t="inlineStr">
+    <row r="56" ht="15" customHeight="1" s="143">
+      <c r="A56" s="247" t="inlineStr">
         <is>
           <t>ALERT_SOUND_PATH_CEILING</t>
         </is>
       </c>
-      <c r="B56" s="258" t="inlineStr">
+      <c r="B56" s="259" t="inlineStr">
         <is>
           <t>C:\Windows\Media\notify.wav</t>
         </is>
       </c>
-      <c r="C56" s="235" t="inlineStr">
+      <c r="C56" s="236" t="inlineStr">
         <is>
           <t>C:\Windows\Media\notify.wav</t>
         </is>
       </c>
-      <c r="D56" s="235" t="inlineStr">
+      <c r="D56" s="236" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="E56" s="257" t="inlineStr">
+      <c r="E56" s="258" t="inlineStr">
         <is>
           <t>Distinct tone for crossing MAX_ENTRY_Z. That is 'stand down', not 'get in'.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="142">
-      <c r="A57" s="246" t="inlineStr">
+    <row r="57" ht="15" customHeight="1" s="143">
+      <c r="A57" s="247" t="inlineStr">
         <is>
           <t>ALERT_REARM_MARGIN</t>
         </is>
       </c>
-      <c r="B57" s="259" t="n">
+      <c r="B57" s="260" t="n">
         <v>0.25</v>
       </c>
-      <c r="C57" s="260" t="n">
+      <c r="C57" s="261" t="n">
         <v>0.25</v>
       </c>
-      <c r="D57" s="235" t="inlineStr">
+      <c r="D57" s="236" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E57" s="257" t="inlineStr">
+      <c r="E57" s="258" t="inlineStr">
         <is>
           <t>Hysteresis. Do not re-arm until |z| falls back below ENTRY_Z - this margin.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="142">
-      <c r="A58" s="246" t="inlineStr">
+    <row r="58" ht="15" customHeight="1" s="143">
+      <c r="A58" s="247" t="inlineStr">
         <is>
           <t>ALERT_COOLDOWN_SEC</t>
         </is>
       </c>
-      <c r="B58" s="256" t="n">
+      <c r="B58" s="257" t="n">
         <v>60</v>
       </c>
-      <c r="C58" s="235" t="n">
+      <c r="C58" s="236" t="n">
         <v>60</v>
       </c>
-      <c r="D58" s="235" t="inlineStr">
+      <c r="D58" s="236" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E58" s="257" t="inlineStr">
+      <c r="E58" s="258" t="inlineStr">
         <is>
           <t>Minimum seconds between alerts for the same spread.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="142">
-      <c r="A59" s="246" t="inlineStr">
+    <row r="59" ht="15" customHeight="1" s="143">
+      <c r="A59" s="247" t="inlineStr">
         <is>
           <t>ALERT_ONLY_IF_EDGE_PASSES</t>
         </is>
       </c>
-      <c r="B59" s="256" t="b">
+      <c r="B59" s="257" t="b">
         <v>0</v>
       </c>
-      <c r="C59" s="235" t="b">
+      <c r="C59" s="236" t="b">
         <v>0</v>
       </c>
-      <c r="D59" s="235" t="inlineStr">
+      <c r="D59" s="236" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E59" s="257" t="inlineStr">
+      <c r="E59" s="258" t="inlineStr">
         <is>
           <t>FALSE = the chime follows ENTRY_Z alone. TRUE = also stay silent when the edge filter fails, on the argument that a sound for a trade you should not take trains you to ignore the sound. Ships FALSE by request; the edge verdict is still shown on Detail.</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="142">
-      <c r="A60" s="246" t="inlineStr">
+    <row r="60" ht="15" customHeight="1" s="143">
+      <c r="A60" s="247" t="inlineStr">
         <is>
           <t>ALERT_SPEAK</t>
         </is>
       </c>
-      <c r="B60" s="256" t="b">
+      <c r="B60" s="257" t="b">
         <v>0</v>
       </c>
-      <c r="C60" s="235" t="b">
+      <c r="C60" s="236" t="b">
         <v>0</v>
       </c>
-      <c r="D60" s="235" t="inlineStr">
+      <c r="D60" s="236" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E60" s="257" t="inlineStr">
+      <c r="E60" s="258" t="inlineStr">
         <is>
           <t>TRUE also speaks the spread name (Application.Speech). Useful when watching four at once.</t>
         </is>
       </c>
     </row>
     <row r="61"/>
-    <row r="62" ht="15" customHeight="1" s="142">
-      <c r="A62" s="254" t="inlineStr">
+    <row r="62" ht="15" customHeight="1" s="143">
+      <c r="A62" s="255" t="inlineStr">
         <is>
           <t>PERSISTENCE  /  LOGGING</t>
         </is>
       </c>
-      <c r="B62" s="254" t="n"/>
-      <c r="C62" s="254" t="n"/>
-      <c r="D62" s="254" t="n"/>
-      <c r="E62" s="254" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="142">
-      <c r="A63" s="255" t="inlineStr">
+      <c r="B62" s="255" t="n"/>
+      <c r="C62" s="255" t="n"/>
+      <c r="D62" s="255" t="n"/>
+      <c r="E62" s="255" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="143">
+      <c r="A63" s="256" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B63" s="255" t="inlineStr">
+      <c r="B63" s="256" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C63" s="255" t="inlineStr">
+      <c r="C63" s="256" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D63" s="255" t="inlineStr">
+      <c r="D63" s="256" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E63" s="255" t="inlineStr">
+      <c r="E63" s="256" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="142">
-      <c r="A64" s="246" t="inlineStr">
+    <row r="64" ht="15" customHeight="1" s="143">
+      <c r="A64" s="247" t="inlineStr">
         <is>
           <t>WARM_START_ENABLED</t>
         </is>
       </c>
-      <c r="B64" s="256" t="b">
+      <c r="B64" s="257" t="b">
         <v>1</v>
       </c>
-      <c r="C64" s="235" t="b">
+      <c r="C64" s="236" t="b">
         <v>1</v>
       </c>
-      <c r="D64" s="235" t="inlineStr">
+      <c r="D64" s="236" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E64" s="257" t="inlineStr">
+      <c r="E64" s="258" t="inlineStr">
         <is>
           <t>On open, reload the flushed buffer so a restart does not cost another two hours of warm-up.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="142">
-      <c r="A65" s="246" t="inlineStr">
+    <row r="65" ht="15" customHeight="1" s="143">
+      <c r="A65" s="247" t="inlineStr">
         <is>
           <t>WARM_START_MAX_AGE_MIN</t>
         </is>
       </c>
-      <c r="B65" s="256" t="n">
+      <c r="B65" s="257" t="n">
         <v>180</v>
       </c>
-      <c r="C65" s="235" t="n">
+      <c r="C65" s="236" t="n">
         <v>180</v>
       </c>
-      <c r="D65" s="235" t="inlineStr">
+      <c r="D65" s="236" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="E65" s="257" t="inlineStr">
+      <c r="E65" s="258" t="inlineStr">
         <is>
           <t>Only reload if the newest saved sample is younger than this.</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="142">
-      <c r="A66" s="246" t="inlineStr">
+    <row r="66" ht="15" customHeight="1" s="143">
+      <c r="A66" s="247" t="inlineStr">
         <is>
           <t>LOG_ENABLED</t>
         </is>
       </c>
-      <c r="B66" s="256" t="b">
+      <c r="B66" s="257" t="b">
         <v>1</v>
       </c>
-      <c r="C66" s="235" t="b">
+      <c r="C66" s="236" t="b">
         <v>1</v>
       </c>
-      <c r="D66" s="235" t="inlineStr">
+      <c r="D66" s="236" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="E66" s="257" t="inlineStr">
+      <c r="E66" s="258" t="inlineStr">
         <is>
           <t>Write signal events to the Log sheet.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="142">
-      <c r="A67" s="246" t="inlineStr">
+    <row r="67" ht="15" customHeight="1" s="143">
+      <c r="A67" s="247" t="inlineStr">
         <is>
           <t>LOG_MAX_ROWS</t>
         </is>
       </c>
-      <c r="B67" s="256" t="n">
+      <c r="B67" s="257" t="n">
         <v>20000</v>
       </c>
-      <c r="C67" s="235" t="n">
+      <c r="C67" s="236" t="n">
         <v>20000</v>
       </c>
-      <c r="D67" s="235" t="inlineStr">
+      <c r="D67" s="236" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="E67" s="257" t="inlineStr">
+      <c r="E67" s="258" t="inlineStr">
         <is>
           <t>Log is trimmed to this many rows.</t>
         </is>
       </c>
     </row>
     <row r="68"/>
-    <row r="69" ht="15" customHeight="1" s="142">
-      <c r="A69" s="254" t="inlineStr">
+    <row r="69" ht="15" customHeight="1" s="143">
+      <c r="A69" s="255" t="inlineStr">
         <is>
           <t>DERIVED COMMISSION  (formulas - do not edit)</t>
         </is>
       </c>
-      <c r="B69" s="261" t="n"/>
-      <c r="C69" s="261" t="n"/>
-      <c r="D69" s="261" t="n"/>
-      <c r="E69" s="261" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="142">
-      <c r="A70" s="255" t="inlineStr">
+      <c r="B69" s="262" t="n"/>
+      <c r="C69" s="262" t="n"/>
+      <c r="D69" s="262" t="n"/>
+      <c r="E69" s="262" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="143">
+      <c r="A70" s="256" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B70" s="255" t="inlineStr">
+      <c r="B70" s="256" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C70" s="255" t="inlineStr">
+      <c r="C70" s="256" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="D70" s="255" t="inlineStr">
+      <c r="D70" s="256" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E70" s="255" t="inlineStr">
+      <c r="E70" s="256" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="142">
-      <c r="A71" s="246" t="inlineStr">
+    <row r="71" ht="15" customHeight="1" s="143">
+      <c r="A71" s="247" t="inlineStr">
         <is>
           <t>COMMISSION_CONSERVATIVE</t>
         </is>
       </c>
-      <c r="B71" s="247">
+      <c r="B71" s="248">
         <f>2*(B48+B49+B50)</f>
         <v/>
       </c>
-      <c r="E71" s="262" t="inlineStr">
+      <c r="E71" s="263" t="inlineStr">
         <is>
           <t>Per lot PER LEG, round turn, reading CME's 1.50 as per SIDE. This is the conservative reading and the one to use.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="142">
-      <c r="A72" s="246" t="inlineStr">
+    <row r="72" ht="15" customHeight="1" s="143">
+      <c r="A72" s="247" t="inlineStr">
         <is>
           <t>COMMISSION_IF_CME_PER_RT</t>
         </is>
       </c>
-      <c r="B72" s="243">
+      <c r="B72" s="244">
         <f>2*(B48+B49)+B50</f>
         <v/>
       </c>
-      <c r="E72" s="262" t="inlineStr">
+      <c r="E72" s="263" t="inlineStr">
         <is>
           <t>The same figure if CME's 1.50 turns out to be per ROUND TURN rather than per side.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="142">
-      <c r="A73" s="246" t="inlineStr">
+    <row r="73" ht="15" customHeight="1" s="143">
+      <c r="A73" s="247" t="inlineStr">
         <is>
           <t>COMMISSION_BASIS</t>
         </is>
       </c>
-      <c r="B73" s="256" t="inlineStr">
+      <c r="B73" s="257" t="inlineStr">
         <is>
           <t>CONSERVATIVE</t>
         </is>
       </c>
-      <c r="C73" s="235" t="inlineStr">
+      <c r="C73" s="236" t="inlineStr">
         <is>
           <t>CONSERVATIVE</t>
         </is>
       </c>
-      <c r="E73" s="262" t="inlineStr">
+      <c r="E73" s="263" t="inlineStr">
         <is>
           <t>CONSERVATIVE or CME_PER_RT. An understated cost model approves losing trades invisibly; an overstated one only refuses trades, visibly. Leave it on CONSERVATIVE.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="142">
-      <c r="A74" s="246" t="inlineStr">
+    <row r="74" ht="15" customHeight="1" s="143">
+      <c r="A74" s="247" t="inlineStr">
         <is>
           <t>COMMISSION_PER_LOT_ROUND_TURN</t>
         </is>
       </c>
-      <c r="B74" s="247">
+      <c r="B74" s="248">
         <f>IF(B73="CME_PER_RT",B72,B71)</f>
         <v/>
       </c>
-      <c r="E74" s="262" t="inlineStr">
+      <c r="E74" s="263" t="inlineStr">
         <is>
           <t>USD per lot per leg, round turn. This is what the cost model actually uses.</t>
         </is>
       </c>
     </row>
     <row r="75"/>
-    <row r="76" ht="15" customHeight="1" s="142">
-      <c r="A76" s="254" t="inlineStr">
+    <row r="76" ht="15" customHeight="1" s="143">
+      <c r="A76" s="255" t="inlineStr">
+        <is>
+          <t>INSTRUMENTS   -   CONTRACT ROLL</t>
+        </is>
+      </c>
+      <c r="B76" s="262" t="n"/>
+      <c r="C76" s="262" t="n"/>
+      <c r="D76" s="262" t="n"/>
+      <c r="E76" s="262" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="143">
+      <c r="A77" s="254" t="inlineStr">
+        <is>
+          <t>These six cells are the ONLY place a TT short name appears. Every RTD call on the hidden Feed sheet reads them, and the Dashboard's own symbol column is written back from them, so the two can never disagree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="143">
+      <c r="A78" s="230" t="inlineStr">
+        <is>
+          <t>CME month codes:  F Jan  G Feb  H Mar  J Apr  K May  M Jun  N Jul  Q Aug  U Sep  V Oct  X Nov  Z Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="143">
+      <c r="A79" s="252" t="inlineStr">
+        <is>
+          <t>Roll every leg of a spread together. A November Brent against an October WTI is a different instrument from the one whose mean and sigma you measured, and the window should be cleared when you change one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="143">
+      <c r="A80" s="256" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="B80" s="256" t="inlineStr">
+        <is>
+          <t>TT short name</t>
+        </is>
+      </c>
+      <c r="C80" s="256" t="inlineStr">
+        <is>
+          <t>Instrument</t>
+        </is>
+      </c>
+      <c r="D80" s="256" t="n"/>
+      <c r="E80" s="256" t="inlineStr">
+        <is>
+          <t>Used as</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="143">
+      <c r="A81" s="249" t="inlineStr">
+        <is>
+          <t>INSTRUMENT_1</t>
+        </is>
+      </c>
+      <c r="B81" s="259" t="inlineStr">
+        <is>
+          <t>RBV6</t>
+        </is>
+      </c>
+      <c r="C81" s="235" t="inlineStr">
+        <is>
+          <t>RBOB Gasoline</t>
+        </is>
+      </c>
+      <c r="E81" s="264" t="inlineStr">
+        <is>
+          <t>leg of the 3:2:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1" s="143">
+      <c r="A82" s="249" t="inlineStr">
+        <is>
+          <t>INSTRUMENT_2</t>
+        </is>
+      </c>
+      <c r="B82" s="259" t="inlineStr">
+        <is>
+          <t>HOV6</t>
+        </is>
+      </c>
+      <c r="C82" s="235" t="inlineStr">
+        <is>
+          <t>NY Harbor ULSD</t>
+        </is>
+      </c>
+      <c r="E82" s="264" t="inlineStr">
+        <is>
+          <t>leg of HO/CL and the 3:2:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1" s="143">
+      <c r="A83" s="249" t="inlineStr">
+        <is>
+          <t>INSTRUMENT_3</t>
+        </is>
+      </c>
+      <c r="B83" s="259" t="inlineStr">
+        <is>
+          <t>CLV6</t>
+        </is>
+      </c>
+      <c r="C83" s="235" t="inlineStr">
+        <is>
+          <t>WTI Crude</t>
+        </is>
+      </c>
+      <c r="E83" s="264" t="inlineStr">
+        <is>
+          <t>leg of every spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="143">
+      <c r="A84" s="249" t="inlineStr">
+        <is>
+          <t>INSTRUMENT_4</t>
+        </is>
+      </c>
+      <c r="B84" s="259" t="inlineStr">
+        <is>
+          <t>BZV6</t>
+        </is>
+      </c>
+      <c r="C84" s="235" t="inlineStr">
+        <is>
+          <t>Brent Last Day Financial</t>
+        </is>
+      </c>
+      <c r="E84" s="264" t="inlineStr">
+        <is>
+          <t>leg B of BZ - CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="143">
+      <c r="A85" s="249" t="inlineStr">
+        <is>
+          <t>INSTRUMENT_5</t>
+        </is>
+      </c>
+      <c r="B85" s="259" t="inlineStr">
+        <is>
+          <t>CL Oct26 - BZ Oct26 Inter-Product</t>
+        </is>
+      </c>
+      <c r="C85" s="235" t="inlineStr">
+        <is>
+          <t>Exchange-listed inter-product</t>
+        </is>
+      </c>
+      <c r="E85" s="264" t="inlineStr">
+        <is>
+          <t>listed comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1" s="143">
+      <c r="A86" s="249" t="inlineStr">
+        <is>
+          <t>INSTRUMENT_6</t>
+        </is>
+      </c>
+      <c r="B86" s="259" t="inlineStr">
+        <is>
+          <t>Oct26 HO-CL Crack</t>
+        </is>
+      </c>
+      <c r="C86" s="235" t="inlineStr">
+        <is>
+          <t>Exchange-listed crack</t>
+        </is>
+      </c>
+      <c r="E86" s="264" t="inlineStr">
+        <is>
+          <t>listed comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89" ht="15" customHeight="1" s="143">
+      <c r="A89" s="255" t="inlineStr">
         <is>
           <t>SPREAD_TABLE_START   -   up to 4 monitored spreads, one buffer each</t>
         </is>
       </c>
-      <c r="B76" s="261" t="n"/>
-      <c r="C76" s="261" t="n"/>
-      <c r="D76" s="261" t="n"/>
-      <c r="E76" s="261" t="n"/>
-      <c r="F76" s="261" t="n"/>
-      <c r="G76" s="261" t="n"/>
-      <c r="H76" s="261" t="n"/>
-      <c r="I76" s="261" t="n"/>
-      <c r="J76" s="261" t="n"/>
-      <c r="K76" s="261" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="142">
-      <c r="A77" s="229" t="inlineStr">
+      <c r="B89" s="262" t="n"/>
+      <c r="C89" s="262" t="n"/>
+      <c r="D89" s="262" t="n"/>
+      <c r="E89" s="262" t="n"/>
+      <c r="F89" s="262" t="n"/>
+      <c r="G89" s="262" t="n"/>
+      <c r="H89" s="262" t="n"/>
+      <c r="I89" s="262" t="n"/>
+      <c r="J89" s="262" t="n"/>
+      <c r="K89" s="262" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="143">
+      <c r="A90" s="230" t="inlineStr">
         <is>
           <t>Leg COMPOSITION (which instruments, and their weights) is defined by the labelled formulas in the MONITOR LEGS block on the hidden Feed sheet. Everything below is hot-reloaded each tick.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="32.8" customHeight="1" s="142">
-      <c r="A78" s="255" t="inlineStr">
+    <row r="91" ht="32.8" customHeight="1" s="143">
+      <c r="A91" s="256" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B78" s="255" t="inlineStr">
+      <c r="B91" s="256" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="C78" s="255" t="inlineStr">
+      <c r="C91" s="256" t="inlineStr">
         <is>
           <t>Display name</t>
         </is>
       </c>
-      <c r="D78" s="255" t="inlineStr">
+      <c r="D91" s="256" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="E78" s="255" t="inlineStr">
+      <c r="E91" s="256" t="inlineStr">
         <is>
           <t>HEDGE_RATIO (beta)</t>
         </is>
       </c>
-      <c r="F78" s="255" t="inlineStr">
+      <c r="F91" s="256" t="inlineStr">
         <is>
           <t>Beta stamped for pair</t>
         </is>
       </c>
-      <c r="G78" s="255" t="inlineStr">
+      <c r="G91" s="256" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread, per lot</t>
         </is>
       </c>
-      <c r="H78" s="255" t="inlineStr">
+      <c r="H91" s="256" t="inlineStr">
         <is>
           <t>Contracts charged commission</t>
         </is>
       </c>
-      <c r="I78" s="255" t="inlineStr">
+      <c r="I91" s="256" t="inlineStr">
         <is>
           <t>Tick size</t>
         </is>
       </c>
-      <c r="J78" s="255" t="inlineStr">
+      <c r="J91" s="256" t="inlineStr">
         <is>
           <t>Decimals</t>
         </is>
       </c>
-      <c r="K78" s="255" t="inlineStr">
+      <c r="K91" s="256" t="inlineStr">
         <is>
           <t>Listed equivalent (cost comparison)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="142">
-      <c r="A79" s="248" t="inlineStr">
+    <row r="92" ht="15" customHeight="1" s="143">
+      <c r="A92" s="249" t="inlineStr">
         <is>
           <t>SPREAD_1</t>
         </is>
       </c>
-      <c r="B79" s="256" t="b">
+      <c r="B92" s="257" t="b">
         <v>1</v>
       </c>
-      <c r="C79" s="258" t="inlineStr">
+      <c r="C92" s="259" t="inlineStr">
         <is>
           <t>BZ - CL  (Brent LDF - WTI)</t>
         </is>
       </c>
-      <c r="D79" s="256" t="inlineStr">
+      <c r="D92" s="257" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E79" s="263" t="n">
+      <c r="E92" s="265" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="258" t="inlineStr">
+      <c r="F92" s="259" t="inlineStr">
         <is>
           <t>BZV6 / CLV6, derived 2026-08 (RELATED pair - no fair value, empirical mean only)</t>
         </is>
       </c>
-      <c r="G79" s="264" t="n">
+      <c r="G92" s="266" t="n">
         <v>1000</v>
       </c>
-      <c r="H79" s="265" t="n">
+      <c r="H92" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="263" t="n">
+      <c r="I92" s="265" t="n">
         <v>0.01</v>
       </c>
-      <c r="J79" s="265" t="n">
+      <c r="J92" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="K79" s="237" t="inlineStr">
+      <c r="K92" s="238" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="142">
-      <c r="A80" s="248" t="inlineStr">
+    <row r="93" ht="15" customHeight="1" s="143">
+      <c r="A93" s="249" t="inlineStr">
         <is>
           <t>SPREAD_2</t>
         </is>
       </c>
-      <c r="B80" s="256" t="b">
+      <c r="B93" s="257" t="b">
         <v>1</v>
       </c>
-      <c r="C80" s="258" t="inlineStr">
+      <c r="C93" s="259" t="inlineStr">
         <is>
           <t>HO/CL crack  (ULSD - WTI)</t>
         </is>
       </c>
-      <c r="D80" s="256" t="inlineStr">
+      <c r="D93" s="257" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E80" s="263" t="n">
+      <c r="E93" s="265" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="258" t="inlineStr">
+      <c r="F93" s="259" t="inlineStr">
         <is>
           <t>HOV6 x42 / CLV6, 1:1 by design (crack, not a fitted beta)</t>
         </is>
       </c>
-      <c r="G80" s="264" t="n">
+      <c r="G93" s="266" t="n">
         <v>1000</v>
       </c>
-      <c r="H80" s="265" t="n">
+      <c r="H93" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="I80" s="263" t="n">
+      <c r="I93" s="265" t="n">
         <v>0.01</v>
       </c>
-      <c r="J80" s="265" t="n">
+      <c r="J93" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="K80" s="237" t="inlineStr">
+      <c r="K93" s="238" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="142">
-      <c r="A81" s="248" t="inlineStr">
+    <row r="94" ht="15" customHeight="1" s="143">
+      <c r="A94" s="249" t="inlineStr">
         <is>
           <t>SPREAD_3</t>
         </is>
       </c>
-      <c r="B81" s="256" t="b">
+      <c r="B94" s="257" t="b">
         <v>1</v>
       </c>
-      <c r="C81" s="258" t="inlineStr">
+      <c r="C94" s="259" t="inlineStr">
         <is>
           <t>3:2:1 crack  (2RB+1HO-3CL)/3</t>
         </is>
       </c>
-      <c r="D81" s="256" t="inlineStr">
+      <c r="D94" s="257" t="inlineStr">
         <is>
           <t>LEGGED</t>
         </is>
       </c>
-      <c r="E81" s="263" t="n">
+      <c r="E94" s="265" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="258" t="inlineStr">
+      <c r="F94" s="259" t="inlineStr">
         <is>
           <t>RBV6/HOV6/CLV6, structural 3:2:1 - not a fitted beta</t>
         </is>
       </c>
-      <c r="G81" s="264" t="n">
+      <c r="G94" s="266" t="n">
         <v>3000</v>
       </c>
-      <c r="H81" s="265" t="n">
+      <c r="H94" s="267" t="n">
         <v>6</v>
       </c>
-      <c r="I81" s="263" t="n">
+      <c r="I94" s="265" t="n">
         <v>0.01</v>
       </c>
-      <c r="J81" s="265" t="n">
+      <c r="J94" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="K81" s="237" t="inlineStr">
+      <c r="K94" s="238" t="inlineStr">
         <is>
           <t>(none listed)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="142">
-      <c r="A82" s="248" t="inlineStr">
+    <row r="95" ht="15" customHeight="1" s="143">
+      <c r="A95" s="249" t="inlineStr">
         <is>
           <t>SPREAD_4</t>
         </is>
       </c>
-      <c r="B82" s="256" t="b">
+      <c r="B95" s="257" t="b">
         <v>1</v>
       </c>
-      <c r="C82" s="258" t="inlineStr">
+      <c r="C95" s="259" t="inlineStr">
         <is>
           <t>CL-BZ Inter-Product (listed)</t>
         </is>
       </c>
-      <c r="D82" s="256" t="inlineStr">
+      <c r="D95" s="257" t="inlineStr">
         <is>
           <t>LISTED</t>
         </is>
       </c>
-      <c r="E82" s="263" t="n">
+      <c r="E95" s="265" t="n">
         <v>1</v>
       </c>
-      <c r="F82" s="258" t="inlineStr">
+      <c r="F95" s="259" t="inlineStr">
         <is>
           <t>Exchange-listed spread - beta not applicable</t>
         </is>
       </c>
-      <c r="G82" s="264" t="n">
+      <c r="G95" s="266" t="n">
         <v>1000</v>
       </c>
-      <c r="H82" s="265" t="n">
+      <c r="H95" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="263" t="n">
+      <c r="I95" s="265" t="n">
         <v>0.01</v>
       </c>
-      <c r="J82" s="265" t="n">
+      <c r="J95" s="267" t="n">
         <v>2</v>
       </c>
-      <c r="K82" s="237" t="inlineStr">
+      <c r="K95" s="238" t="inlineStr">
         <is>
           <t>n/a - this IS the listed spread</t>
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84" ht="15" customHeight="1" s="142">
-      <c r="A84" s="251" t="inlineStr">
+    <row r="96"/>
+    <row r="97" ht="15" customHeight="1" s="143">
+      <c r="A97" s="252" t="inlineStr">
         <is>
           <t>HEDGE RATIO BELONGS TO THE PAIR. If the instruments change, beta must be re-derived - a stale beta silently redefines the series. Column F stamps what each beta was computed for.</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="142">
-      <c r="A85" s="229" t="inlineStr">
+    <row r="98" ht="15" customHeight="1" s="143">
+      <c r="A98" s="230" t="inlineStr">
         <is>
           <t>Contracts charged: BZ-CL and the listed spread are 2 contracts per lot (one per leg); the 3:2:1 crack is 6 (2 RB + 1 HO + 3 CL).</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="142">
-      <c r="A86" s="229" t="inlineStr">
+    <row r="99" ht="15" customHeight="1" s="143">
+      <c r="A99" s="230" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread: NYMEX energy contracts are 1,000 bbl, so one cent of differential is $10 per leg per lot, i.e. $1,000 per 1.00.</t>
         </is>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88" ht="15" customHeight="1" s="142">
-      <c r="A88" s="251" t="inlineStr">
+    <row r="100"/>
+    <row r="101" ht="15" customHeight="1" s="143">
+      <c r="A101" s="252" t="inlineStr">
         <is>
           <t>NOTIONAL_BASIS - read this before changing it:</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="142">
-      <c r="A89" s="229" t="inlineStr">
+    <row r="102" ht="15" customHeight="1" s="143">
+      <c r="A102" s="230" t="inlineStr">
         <is>
           <t>A spread is not an outright, so 'notional' has no single meaning. At 1 lot with CL near $60 and BZ-CL near $7.20:  SPREAD_VALUE ~ $7,200, ONE_LEG ~ $60,000, BOTH_LEGS ~ $127,000.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="142">
-      <c r="A90" s="266" t="inlineStr">
+    <row r="103" ht="15" customHeight="1" s="143">
+      <c r="A103" s="268" t="inlineStr">
         <is>
           <t>1% of those is $72, $600 and $1,270. If sigma on this spread turns out to be ~5 cents ($50), only the first is reachable - the others need the spread to travel 12 or 25 sigma, which it will not do. Watch the TP-in-sigma cell on the Dashboard: above about 1 sigma it turns amber.</t>
         </is>
@@ -5614,315 +5817,309 @@
   <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="40" customWidth="1" style="140" min="1" max="1"/>
-    <col width="34" customWidth="1" style="140" min="2" max="2"/>
-    <col width="13" customWidth="1" style="140" min="3" max="8"/>
-    <col width="60" customWidth="1" style="140" min="9" max="9"/>
+    <col width="40" customWidth="1" style="141" min="1" max="1"/>
+    <col width="34" customWidth="1" style="141" min="2" max="2"/>
+    <col width="13" customWidth="1" style="141" min="3" max="8"/>
+    <col width="60" customWidth="1" style="141" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="142">
-      <c r="A1" s="267" t="inlineStr">
+    <row r="1" ht="16.15" customHeight="1" s="143">
+      <c r="A1" s="269" t="inlineStr">
         <is>
           <t>FEED  -  hidden.  Every RTD() formula lives here.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="142">
-      <c r="A2" s="268" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="A2" s="270" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B2" s="269">
+      <c r="B2" s="271">
         <f>Dashboard!$C$4</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="142">
-      <c r="A3" s="251" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="143">
+      <c r="A3" s="252" t="inlineStr">
         <is>
           <t>Never put an RTD() formula on Dashboard: a cell holding one repaints whenever the feed moves, and that cannot be prevented while the formula is in the cell.</t>
         </is>
       </c>
     </row>
     <row r="4"/>
-    <row r="5" ht="15" customHeight="1" s="142">
-      <c r="A5" s="270" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="A5" s="272" t="inlineStr">
         <is>
           <t>INSTRUMENTS</t>
         </is>
       </c>
-      <c r="B5" s="231" t="inlineStr">
+      <c r="B5" s="232" t="inlineStr">
         <is>
           <t>Instrument ID</t>
         </is>
       </c>
-      <c r="C5" s="231" t="inlineStr">
+      <c r="C5" s="232" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="D5" s="231" t="inlineStr">
+      <c r="D5" s="232" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="E5" s="231" t="inlineStr">
+      <c r="E5" s="232" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="231" t="inlineStr">
+      <c r="F5" s="232" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G5" s="231" t="inlineStr">
+      <c r="G5" s="232" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="H5" s="231" t="inlineStr">
+      <c r="H5" s="232" t="inlineStr">
         <is>
           <t>Width</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="142">
-      <c r="A6" s="232" t="inlineStr">
-        <is>
-          <t>RBV6</t>
-        </is>
-      </c>
-      <c r="B6" s="271">
+    <row r="6" ht="15" customHeight="1" s="143">
+      <c r="A6" s="273">
+        <f>Config!$B$81</f>
+        <v/>
+      </c>
+      <c r="B6" s="274">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A6)</f>
         <v/>
       </c>
-      <c r="C6" s="271">
+      <c r="C6" s="274">
         <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D6" s="271">
+      <c r="D6" s="274">
         <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E6" s="271">
+      <c r="E6" s="274">
         <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F6" s="271">
+      <c r="F6" s="274">
         <f>IFERROR(IF(OR($B6="",LEFT($B6,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B6,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G6" s="271">
+      <c r="G6" s="274">
         <f>IF(OR($C6="",$D6=""),"",($C6+$D6)/2)</f>
         <v/>
       </c>
-      <c r="H6" s="271">
+      <c r="H6" s="274">
         <f>IF(OR($C6="",$D6=""),"",$D6-$C6)</f>
         <v/>
       </c>
-      <c r="I6" s="272" t="inlineStr">
+      <c r="I6" s="264" t="inlineStr">
         <is>
           <t>RBOB Gasoline Oct26</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="142">
-      <c r="A7" s="232" t="inlineStr">
-        <is>
-          <t>HOV6</t>
-        </is>
-      </c>
-      <c r="B7" s="271">
+    <row r="7" ht="15" customHeight="1" s="143">
+      <c r="A7" s="273">
+        <f>Config!$B$82</f>
+        <v/>
+      </c>
+      <c r="B7" s="274">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A7)</f>
         <v/>
       </c>
-      <c r="C7" s="271">
+      <c r="C7" s="274">
         <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D7" s="271">
+      <c r="D7" s="274">
         <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E7" s="271">
+      <c r="E7" s="274">
         <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F7" s="271">
+      <c r="F7" s="274">
         <f>IFERROR(IF(OR($B7="",LEFT($B7,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B7,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G7" s="271">
+      <c r="G7" s="274">
         <f>IF(OR($C7="",$D7=""),"",($C7+$D7)/2)</f>
         <v/>
       </c>
-      <c r="H7" s="271">
+      <c r="H7" s="274">
         <f>IF(OR($C7="",$D7=""),"",$D7-$C7)</f>
         <v/>
       </c>
-      <c r="I7" s="272" t="inlineStr">
+      <c r="I7" s="264" t="inlineStr">
         <is>
           <t>NY Harbor ULSD Oct26</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="142">
-      <c r="A8" s="232" t="inlineStr">
-        <is>
-          <t>CLV6</t>
-        </is>
-      </c>
-      <c r="B8" s="271">
+    <row r="8" ht="15" customHeight="1" s="143">
+      <c r="A8" s="273">
+        <f>Config!$B$83</f>
+        <v/>
+      </c>
+      <c r="B8" s="274">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A8)</f>
         <v/>
       </c>
-      <c r="C8" s="271">
+      <c r="C8" s="274">
         <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D8" s="271">
+      <c r="D8" s="274">
         <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E8" s="271">
+      <c r="E8" s="274">
         <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F8" s="271">
+      <c r="F8" s="274">
         <f>IFERROR(IF(OR($B8="",LEFT($B8,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B8,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G8" s="271">
+      <c r="G8" s="274">
         <f>IF(OR($C8="",$D8=""),"",($C8+$D8)/2)</f>
         <v/>
       </c>
-      <c r="H8" s="271">
+      <c r="H8" s="274">
         <f>IF(OR($C8="",$D8=""),"",$D8-$C8)</f>
         <v/>
       </c>
-      <c r="I8" s="272" t="inlineStr">
+      <c r="I8" s="264" t="inlineStr">
         <is>
           <t>WTI Crude Oct26</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="142">
-      <c r="A9" s="232" t="inlineStr">
-        <is>
-          <t>BZV6</t>
-        </is>
-      </c>
-      <c r="B9" s="271">
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="A9" s="273">
+        <f>Config!$B$84</f>
+        <v/>
+      </c>
+      <c r="B9" s="274">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A9)</f>
         <v/>
       </c>
-      <c r="C9" s="271">
+      <c r="C9" s="274">
         <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D9" s="271">
+      <c r="D9" s="274">
         <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E9" s="271">
+      <c r="E9" s="274">
         <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F9" s="271">
+      <c r="F9" s="274">
         <f>IFERROR(IF(OR($B9="",LEFT($B9,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B9,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G9" s="271">
+      <c r="G9" s="274">
         <f>IF(OR($C9="",$D9=""),"",($C9+$D9)/2)</f>
         <v/>
       </c>
-      <c r="H9" s="271">
+      <c r="H9" s="274">
         <f>IF(OR($C9="",$D9=""),"",$D9-$C9)</f>
         <v/>
       </c>
-      <c r="I9" s="272" t="inlineStr">
+      <c r="I9" s="264" t="inlineStr">
         <is>
           <t>Brent Last Day Financial Oct26</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="142">
-      <c r="A10" s="232" t="inlineStr">
-        <is>
-          <t>CL Oct26 - BZ Oct26 Inter-Product</t>
-        </is>
-      </c>
-      <c r="B10" s="271">
+    <row r="10" ht="15" customHeight="1" s="143">
+      <c r="A10" s="273">
+        <f>Config!$B$85</f>
+        <v/>
+      </c>
+      <c r="B10" s="274">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A10)</f>
         <v/>
       </c>
-      <c r="C10" s="271">
+      <c r="C10" s="274">
         <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D10" s="271">
+      <c r="D10" s="274">
         <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E10" s="271">
+      <c r="E10" s="274">
         <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F10" s="271">
+      <c r="F10" s="274">
         <f>IFERROR(IF(OR($B10="",LEFT($B10,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B10,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G10" s="271">
+      <c r="G10" s="274">
         <f>IF(OR($C10="",$D10=""),"",($C10+$D10)/2)</f>
         <v/>
       </c>
-      <c r="H10" s="271">
+      <c r="H10" s="274">
         <f>IF(OR($C10="",$D10=""),"",$D10-$C10)</f>
         <v/>
       </c>
-      <c r="I10" s="272" t="inlineStr">
+      <c r="I10" s="264" t="inlineStr">
         <is>
           <t>Exchange-listed inter-product spread</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="142">
-      <c r="A11" s="232" t="inlineStr">
-        <is>
-          <t>Oct26 HO-CL Crack</t>
-        </is>
-      </c>
-      <c r="B11" s="271">
+    <row r="11" ht="15" customHeight="1" s="143">
+      <c r="A11" s="273">
+        <f>Config!$B$86</f>
+        <v/>
+      </c>
+      <c r="B11" s="274">
         <f>RTD("tt.rtd",,"Inst",$B$2,$A11)</f>
         <v/>
       </c>
-      <c r="C11" s="271">
+      <c r="C11" s="274">
         <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"Bid"))),"")</f>
         <v/>
       </c>
-      <c r="D11" s="271">
+      <c r="D11" s="274">
         <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"Ask"))),"")</f>
         <v/>
       </c>
-      <c r="E11" s="271">
+      <c r="E11" s="274">
         <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"High"))),"")</f>
         <v/>
       </c>
-      <c r="F11" s="271">
+      <c r="F11" s="274">
         <f>IFERROR(IF(OR($B11="",LEFT($B11,4)="Not_"),"",VALUE(RTD("tt.rtd",,$B11,"Low"))),"")</f>
         <v/>
       </c>
-      <c r="G11" s="271">
+      <c r="G11" s="274">
         <f>IF(OR($C11="",$D11=""),"",($C11+$D11)/2)</f>
         <v/>
       </c>
-      <c r="H11" s="271">
+      <c r="H11" s="274">
         <f>IF(OR($C11="",$D11=""),"",$D11-$C11)</f>
         <v/>
       </c>
-      <c r="I11" s="272" t="inlineStr">
+      <c r="I11" s="264" t="inlineStr">
         <is>
           <t>Exchange-listed crack spread</t>
         </is>
@@ -5931,516 +6128,516 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
-    <row r="15" ht="15" customHeight="1" s="142">
-      <c r="A15" s="270" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="143">
+      <c r="A15" s="272" t="inlineStr">
         <is>
           <t>DERIVED &amp; LISTED SPREADS (display)</t>
         </is>
       </c>
-      <c r="B15" s="231" t="inlineStr">
+      <c r="B15" s="232" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="C15" s="231" t="inlineStr">
+      <c r="C15" s="232" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="D15" s="231" t="inlineStr">
+      <c r="D15" s="232" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="E15" s="231" t="inlineStr">
+      <c r="E15" s="232" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
-      <c r="F15" s="231" t="inlineStr">
+      <c r="F15" s="232" t="inlineStr">
         <is>
           <t>Width</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="142">
-      <c r="A16" s="232" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="143">
+      <c r="A16" s="233" t="inlineStr">
         <is>
           <t>BZ - CL</t>
         </is>
       </c>
-      <c r="B16" s="239" t="inlineStr">
+      <c r="B16" s="240" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C16" s="271">
+      <c r="C16" s="274">
         <f>IF(OR($C$9="",$D$8=""),"",$C$9-$D$8)</f>
         <v/>
       </c>
-      <c r="D16" s="271">
+      <c r="D16" s="274">
         <f>IF(OR($D$9="",$C$8=""),"",$D$9-$C$8)</f>
         <v/>
       </c>
-      <c r="E16" s="271">
+      <c r="E16" s="274">
         <f>IF(OR($G$9="",$G$8=""),"",$G$9-$G$8)</f>
         <v/>
       </c>
-      <c r="F16" s="271">
+      <c r="F16" s="274">
         <f>IF(OR($C16="",$D16=""),"",$D16-$C16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="142">
-      <c r="A17" s="232" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="143">
+      <c r="A17" s="233" t="inlineStr">
         <is>
           <t>HO/CL crack</t>
         </is>
       </c>
-      <c r="B17" s="239" t="inlineStr">
+      <c r="B17" s="240" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C17" s="271">
+      <c r="C17" s="274">
         <f>IF(OR($C$7="",$D$8=""),"",$C$7*42-$D$8)</f>
         <v/>
       </c>
-      <c r="D17" s="271">
+      <c r="D17" s="274">
         <f>IF(OR($D$7="",$C$8=""),"",$D$7*42-$C$8)</f>
         <v/>
       </c>
-      <c r="E17" s="271">
+      <c r="E17" s="274">
         <f>IF(OR($G$7="",$G$8=""),"",$G$7*42-$G$8)</f>
         <v/>
       </c>
-      <c r="F17" s="271">
+      <c r="F17" s="274">
         <f>IF(OR($C17="",$D17=""),"",$D17-$C17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="142">
-      <c r="A18" s="232" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="143">
+      <c r="A18" s="233" t="inlineStr">
         <is>
           <t>3:2:1 crack</t>
         </is>
       </c>
-      <c r="B18" s="239" t="inlineStr">
+      <c r="B18" s="240" t="inlineStr">
         <is>
           <t>legged</t>
         </is>
       </c>
-      <c r="C18" s="271">
+      <c r="C18" s="274">
         <f>IF(OR($C$6="",$C$7="",$D$8=""),"",(($C$6*2*42)+($C$7*1*42)-($D$8*3))/3)</f>
         <v/>
       </c>
-      <c r="D18" s="271">
+      <c r="D18" s="274">
         <f>IF(OR($D$6="",$D$7="",$C$8=""),"",(($D$6*2*42)+($D$7*1*42)-($C$8*3))/3)</f>
         <v/>
       </c>
-      <c r="E18" s="271">
+      <c r="E18" s="274">
         <f>IF(OR($G$6="",$G$7="",$G$8=""),"",(($G$6*2*42)+($G$7*1*42)-($G$8*3))/3)</f>
         <v/>
       </c>
-      <c r="F18" s="271">
+      <c r="F18" s="274">
         <f>IF(OR($C18="",$D18=""),"",$D18-$C18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="142">
-      <c r="A19" s="232" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="143">
+      <c r="A19" s="233" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="B19" s="239" t="inlineStr">
+      <c r="B19" s="240" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="C19" s="271">
+      <c r="C19" s="274">
         <f>$C$10</f>
         <v/>
       </c>
-      <c r="D19" s="271">
+      <c r="D19" s="274">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="E19" s="271">
+      <c r="E19" s="274">
         <f>$G$10</f>
         <v/>
       </c>
-      <c r="F19" s="271">
+      <c r="F19" s="274">
         <f>IF(OR($C19="",$D19=""),"",$D19-$C19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="142">
-      <c r="A20" s="232" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="143">
+      <c r="A20" s="233" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="B20" s="239" t="inlineStr">
+      <c r="B20" s="240" t="inlineStr">
         <is>
           <t>listed</t>
         </is>
       </c>
-      <c r="C20" s="271">
+      <c r="C20" s="274">
         <f>$C$11</f>
         <v/>
       </c>
-      <c r="D20" s="271">
+      <c r="D20" s="274">
         <f>$D$11</f>
         <v/>
       </c>
-      <c r="E20" s="271">
+      <c r="E20" s="274">
         <f>$G$11</f>
         <v/>
       </c>
-      <c r="F20" s="271">
+      <c r="F20" s="274">
         <f>IF(OR($C20="",$D20=""),"",$D20-$C20)</f>
         <v/>
       </c>
     </row>
     <row r="21"/>
     <row r="22"/>
-    <row r="23" ht="15" customHeight="1" s="142">
-      <c r="A23" s="273" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="143">
+      <c r="A23" s="275" t="inlineStr">
         <is>
           <t>MONITOR LEGS</t>
         </is>
       </c>
-      <c r="B23" s="229" t="inlineStr">
+      <c r="B23" s="230" t="inlineStr">
         <is>
           <t>Edit these formulas to redefine what a monitored spread is made of. spread = LegB - HEDGE_RATIO x LegA, and nothing else - no carry, no fair-value term.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="142">
-      <c r="A24" s="231" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="143">
+      <c r="A24" s="232" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B24" s="231" t="inlineStr">
+      <c r="B24" s="232" t="inlineStr">
         <is>
           <t>Side</t>
         </is>
       </c>
-      <c r="C24" s="231" t="inlineStr">
+      <c r="C24" s="232" t="inlineStr">
         <is>
           <t>Composition</t>
         </is>
       </c>
-      <c r="D24" s="231" t="inlineStr">
+      <c r="D24" s="232" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="E24" s="231" t="inlineStr">
+      <c r="E24" s="232" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="F24" s="231" t="inlineStr">
+      <c r="F24" s="232" t="inlineStr">
         <is>
           <t>Mid</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="142">
-      <c r="A25" s="274" t="n">
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="A25" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="248" t="inlineStr">
+      <c r="B25" s="249" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C25" s="275" t="inlineStr">
+      <c r="C25" s="277" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D25" s="271">
+      <c r="D25" s="274">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E25" s="271">
+      <c r="E25" s="274">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F25" s="271">
+      <c r="F25" s="274">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="142">
-      <c r="A26" s="274" t="n">
+    <row r="26" ht="15" customHeight="1" s="143">
+      <c r="A26" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="248" t="inlineStr">
+      <c r="B26" s="249" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C26" s="275" t="inlineStr">
+      <c r="C26" s="277" t="inlineStr">
         <is>
           <t>BZV6</t>
         </is>
       </c>
-      <c r="D26" s="271">
+      <c r="D26" s="274">
         <f>$C$9</f>
         <v/>
       </c>
-      <c r="E26" s="271">
+      <c r="E26" s="274">
         <f>$D$9</f>
         <v/>
       </c>
-      <c r="F26" s="271">
+      <c r="F26" s="274">
         <f>$G$9</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="142">
-      <c r="A27" s="274" t="n">
+    <row r="27" ht="15" customHeight="1" s="143">
+      <c r="A27" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="248" t="inlineStr">
+      <c r="B27" s="249" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C27" s="275" t="inlineStr">
+      <c r="C27" s="277" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D27" s="271">
+      <c r="D27" s="274">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E27" s="271">
+      <c r="E27" s="274">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F27" s="271">
+      <c r="F27" s="274">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="142">
-      <c r="A28" s="274" t="n">
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="A28" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="248" t="inlineStr">
+      <c r="B28" s="249" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C28" s="275" t="inlineStr">
+      <c r="C28" s="277" t="inlineStr">
         <is>
           <t>HOV6 x 42</t>
         </is>
       </c>
-      <c r="D28" s="271">
+      <c r="D28" s="274">
         <f>IF($C$7="","",$C$7*42)</f>
         <v/>
       </c>
-      <c r="E28" s="271">
+      <c r="E28" s="274">
         <f>IF($D$7="","",$D$7*42)</f>
         <v/>
       </c>
-      <c r="F28" s="271">
+      <c r="F28" s="274">
         <f>IF($G$7="","",$G$7*42)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="142">
-      <c r="A29" s="274" t="n">
+    <row r="29" ht="15" customHeight="1" s="143">
+      <c r="A29" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="248" t="inlineStr">
+      <c r="B29" s="249" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C29" s="275" t="inlineStr">
+      <c r="C29" s="277" t="inlineStr">
         <is>
           <t>CLV6</t>
         </is>
       </c>
-      <c r="D29" s="271">
+      <c r="D29" s="274">
         <f>$C$8</f>
         <v/>
       </c>
-      <c r="E29" s="271">
+      <c r="E29" s="274">
         <f>$D$8</f>
         <v/>
       </c>
-      <c r="F29" s="271">
+      <c r="F29" s="274">
         <f>$G$8</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="142">
-      <c r="A30" s="274" t="n">
+    <row r="30" ht="15" customHeight="1" s="143">
+      <c r="A30" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="248" t="inlineStr">
+      <c r="B30" s="249" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C30" s="275" t="inlineStr">
+      <c r="C30" s="277" t="inlineStr">
         <is>
           <t>(2 x RBV6 + 1 x HOV6) x 42 / 3</t>
         </is>
       </c>
-      <c r="D30" s="271">
+      <c r="D30" s="274">
         <f>IF(OR($C$6="",$C$7=""),"",($C$6*2*42+$C$7*1*42)/3)</f>
         <v/>
       </c>
-      <c r="E30" s="271">
+      <c r="E30" s="274">
         <f>IF(OR($D$6="",$D$7=""),"",($D$6*2*42+$D$7*1*42)/3)</f>
         <v/>
       </c>
-      <c r="F30" s="271">
+      <c r="F30" s="274">
         <f>IF(OR($G$6="",$G$7=""),"",($G$6*2*42+$G$7*1*42)/3)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="142">
-      <c r="A31" s="274" t="n">
+    <row r="31" ht="15" customHeight="1" s="143">
+      <c r="A31" s="276" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="248" t="inlineStr">
+      <c r="B31" s="249" t="inlineStr">
         <is>
           <t>LegA</t>
         </is>
       </c>
-      <c r="C31" s="275" t="inlineStr">
+      <c r="C31" s="277" t="inlineStr">
         <is>
           <t>(none - LISTED spread)</t>
         </is>
       </c>
-      <c r="D31" s="271" t="inlineStr"/>
-      <c r="E31" s="271" t="inlineStr"/>
-      <c r="F31" s="271" t="inlineStr"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="142">
-      <c r="A32" s="274" t="n">
+      <c r="D31" s="274" t="inlineStr"/>
+      <c r="E31" s="274" t="inlineStr"/>
+      <c r="F31" s="274" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="143">
+      <c r="A32" s="276" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="248" t="inlineStr">
+      <c r="B32" s="249" t="inlineStr">
         <is>
           <t>LegB</t>
         </is>
       </c>
-      <c r="C32" s="275" t="inlineStr">
+      <c r="C32" s="277" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
-      <c r="D32" s="271">
+      <c r="D32" s="274">
         <f>$C$10</f>
         <v/>
       </c>
-      <c r="E32" s="271">
+      <c r="E32" s="274">
         <f>$D$10</f>
         <v/>
       </c>
-      <c r="F32" s="271">
+      <c r="F32" s="274">
         <f>$G$10</f>
         <v/>
       </c>
     </row>
     <row r="33"/>
-    <row r="34" ht="15" customHeight="1" s="142">
-      <c r="A34" s="273" t="inlineStr">
+    <row r="34" ht="15" customHeight="1" s="143">
+      <c r="A34" s="275" t="inlineStr">
         <is>
           <t>LISTED-EQUIVALENT ROW PER SLOT  (for the side-by-side crossing-cost comparison)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="142">
-      <c r="A35" s="231" t="inlineStr">
+    <row r="35" ht="15" customHeight="1" s="143">
+      <c r="A35" s="232" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B35" s="231" t="inlineStr">
+      <c r="B35" s="232" t="inlineStr">
         <is>
           <t>Feed derived row</t>
         </is>
       </c>
-      <c r="C35" s="231" t="inlineStr">
+      <c r="C35" s="232" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="142">
-      <c r="A36" s="274" t="n">
+    <row r="36" ht="15" customHeight="1" s="143">
+      <c r="A36" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="274" t="n">
+      <c r="B36" s="276" t="n">
         <v>19</v>
       </c>
-      <c r="C36" s="275" t="inlineStr">
+      <c r="C36" s="277" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="142">
-      <c r="A37" s="274" t="n">
+    <row r="37" ht="15" customHeight="1" s="143">
+      <c r="A37" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="274" t="n">
+      <c r="B37" s="276" t="n">
         <v>20</v>
       </c>
-      <c r="C37" s="275" t="inlineStr">
+      <c r="C37" s="277" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="142">
-      <c r="A38" s="274" t="n">
+    <row r="38" ht="15" customHeight="1" s="143">
+      <c r="A38" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="B38" s="274" t="n"/>
-      <c r="C38" s="275" t="inlineStr">
+      <c r="B38" s="276" t="n"/>
+      <c r="C38" s="277" t="inlineStr">
         <is>
           <t>(none)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="142">
-      <c r="A39" s="274" t="n">
+    <row r="39" ht="15" customHeight="1" s="143">
+      <c r="A39" s="276" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="274" t="n">
+      <c r="B39" s="276" t="n">
         <v>19</v>
       </c>
-      <c r="C39" s="275" t="inlineStr">
+      <c r="C39" s="277" t="inlineStr">
         <is>
           <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
     <row r="40"/>
-    <row r="41" ht="15" customHeight="1" s="142">
-      <c r="A41" s="229" t="inlineStr">
+    <row r="41" ht="15" customHeight="1" s="143">
+      <c r="A41" s="230" t="inlineStr">
         <is>
           <t>Crossing convention used throughout:  spread bid = LegB bid - beta x LegA ask ; spread ask = LegB ask - beta x LegA bid ; spread mid = LegB mid - beta x LegA mid.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="142">
-      <c r="A42" s="229" t="inlineStr">
+    <row r="42" ht="15" customHeight="1" s="143">
+      <c r="A42" s="230" t="inlineStr">
         <is>
           <t>For a LISTED slot LegA is empty and is treated as zero, so the listed quote passes straight through untouched.</t>
         </is>
@@ -6462,235 +6659,235 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="15" customWidth="1" style="140" min="1" max="2"/>
-    <col width="3" customWidth="1" style="140" min="3" max="3"/>
-    <col width="15" customWidth="1" style="140" min="4" max="5"/>
-    <col width="3" customWidth="1" style="140" min="6" max="6"/>
-    <col width="15" customWidth="1" style="140" min="7" max="8"/>
-    <col width="3" customWidth="1" style="140" min="9" max="9"/>
-    <col width="15" customWidth="1" style="140" min="10" max="11"/>
-    <col width="26" customWidth="1" style="140" min="13" max="13"/>
-    <col width="30" customWidth="1" style="140" min="14" max="14"/>
+    <col width="15" customWidth="1" style="141" min="1" max="2"/>
+    <col width="3" customWidth="1" style="141" min="3" max="3"/>
+    <col width="15" customWidth="1" style="141" min="4" max="5"/>
+    <col width="3" customWidth="1" style="141" min="6" max="6"/>
+    <col width="15" customWidth="1" style="141" min="7" max="8"/>
+    <col width="3" customWidth="1" style="141" min="9" max="9"/>
+    <col width="15" customWidth="1" style="141" min="10" max="11"/>
+    <col width="26" customWidth="1" style="141" min="13" max="13"/>
+    <col width="30" customWidth="1" style="141" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="142">
-      <c r="A1" s="276" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="143">
+      <c r="A1" s="278" t="inlineStr">
         <is>
           <t>BUFFER  -  hidden.  Flushed circular buffers (crash / restart recovery).</t>
         </is>
       </c>
-      <c r="M1" s="229" t="inlineStr">
+      <c r="M1" s="230" t="inlineStr">
         <is>
           <t>Written by VBA every FLUSH_SEC seconds, so a crash loses at most a minute.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="142">
-      <c r="M2" s="229" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="M2" s="230" t="inlineStr">
         <is>
           <t>On open, WarmStart reloads a slot only if its stamped LOOKBACK_MIN, HEDGE_RATIO and leg labels still match Config, and the newest sample is younger than WARM_START_MAX_AGE_MIN.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="142">
-      <c r="A3" s="273" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="143">
+      <c r="A3" s="275" t="inlineStr">
         <is>
           <t>SLOT 1</t>
         </is>
       </c>
-      <c r="D3" s="273" t="inlineStr">
+      <c r="D3" s="275" t="inlineStr">
         <is>
           <t>SLOT 2</t>
         </is>
       </c>
-      <c r="G3" s="273" t="inlineStr">
+      <c r="G3" s="275" t="inlineStr">
         <is>
           <t>SLOT 3</t>
         </is>
       </c>
-      <c r="J3" s="273" t="inlineStr">
+      <c r="J3" s="275" t="inlineStr">
         <is>
           <t>SLOT 4</t>
         </is>
       </c>
-      <c r="M3" s="229" t="inlineStr">
+      <c r="M3" s="230" t="inlineStr">
         <is>
           <t>Elapsed collection is credited from the OLDEST recovered sample - otherwise every restart costs another two hours before a usable z.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="142">
-      <c r="A4" s="272" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="143">
+      <c r="A4" s="264" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B4" s="271" t="n"/>
-      <c r="D4" s="272" t="inlineStr">
+      <c r="B4" s="274" t="n"/>
+      <c r="D4" s="264" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E4" s="271" t="n"/>
-      <c r="G4" s="272" t="inlineStr">
+      <c r="E4" s="274" t="n"/>
+      <c r="G4" s="264" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="H4" s="271" t="n"/>
-      <c r="J4" s="272" t="inlineStr">
+      <c r="H4" s="274" t="n"/>
+      <c r="J4" s="264" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="K4" s="271" t="n"/>
-      <c r="M4" s="229" t="inlineStr">
+      <c r="K4" s="274" t="n"/>
+      <c r="M4" s="230" t="inlineStr">
         <is>
           <t>Seeding drops CONSECUTIVE identical values only. A spread genuinely revisiting a level is a real observation, not a duplicate.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="142">
-      <c r="A5" s="272" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="A5" s="264" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="B5" s="271" t="n"/>
-      <c r="D5" s="272" t="inlineStr">
+      <c r="B5" s="274" t="n"/>
+      <c r="D5" s="264" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="E5" s="271" t="n"/>
-      <c r="G5" s="272" t="inlineStr">
+      <c r="E5" s="274" t="n"/>
+      <c r="G5" s="264" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="H5" s="271" t="n"/>
-      <c r="J5" s="272" t="inlineStr">
+      <c r="H5" s="274" t="n"/>
+      <c r="J5" s="264" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="K5" s="271" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="142">
-      <c r="A6" s="272" t="inlineStr">
+      <c r="K5" s="274" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="143">
+      <c r="A6" s="264" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="B6" s="271" t="n"/>
-      <c r="D6" s="272" t="inlineStr">
+      <c r="B6" s="274" t="n"/>
+      <c r="D6" s="264" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="E6" s="271" t="n"/>
-      <c r="G6" s="272" t="inlineStr">
+      <c r="E6" s="274" t="n"/>
+      <c r="G6" s="264" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="H6" s="271" t="n"/>
-      <c r="J6" s="272" t="inlineStr">
+      <c r="H6" s="274" t="n"/>
+      <c r="J6" s="264" t="inlineStr">
         <is>
           <t>HEDGE_RATIO</t>
         </is>
       </c>
-      <c r="K6" s="271" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="142">
-      <c r="A7" s="272" t="inlineStr">
+      <c r="K6" s="274" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="143">
+      <c r="A7" s="264" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="B7" s="271" t="n"/>
-      <c r="D7" s="272" t="inlineStr">
+      <c r="B7" s="274" t="n"/>
+      <c r="D7" s="264" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="E7" s="271" t="n"/>
-      <c r="G7" s="272" t="inlineStr">
+      <c r="E7" s="274" t="n"/>
+      <c r="G7" s="264" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="H7" s="271" t="n"/>
-      <c r="J7" s="272" t="inlineStr">
+      <c r="H7" s="274" t="n"/>
+      <c r="J7" s="264" t="inlineStr">
         <is>
           <t>LOOKBACK_MIN</t>
         </is>
       </c>
-      <c r="K7" s="271" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="142">
-      <c r="A8" s="272" t="inlineStr">
+      <c r="K7" s="274" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="143">
+      <c r="A8" s="264" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="B8" s="271" t="n"/>
-      <c r="D8" s="272" t="inlineStr">
+      <c r="B8" s="274" t="n"/>
+      <c r="D8" s="264" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="E8" s="271" t="n"/>
-      <c r="G8" s="272" t="inlineStr">
+      <c r="E8" s="274" t="n"/>
+      <c r="G8" s="264" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="H8" s="271" t="n"/>
-      <c r="J8" s="272" t="inlineStr">
+      <c r="H8" s="274" t="n"/>
+      <c r="J8" s="264" t="inlineStr">
         <is>
           <t>Count / last flush</t>
         </is>
       </c>
-      <c r="K8" s="271" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="142">
-      <c r="A9" s="231" t="inlineStr">
+      <c r="K8" s="274" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="A9" s="232" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="B9" s="231" t="inlineStr">
+      <c r="B9" s="232" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="D9" s="231" t="inlineStr">
+      <c r="D9" s="232" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="E9" s="231" t="inlineStr">
+      <c r="E9" s="232" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="G9" s="231" t="inlineStr">
+      <c r="G9" s="232" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="H9" s="231" t="inlineStr">
+      <c r="H9" s="232" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
       </c>
-      <c r="J9" s="231" t="inlineStr">
+      <c r="J9" s="232" t="inlineStr">
         <is>
           <t>Time (serial)</t>
         </is>
       </c>
-      <c r="K9" s="231" t="inlineStr">
+      <c r="K9" s="232" t="inlineStr">
         <is>
           <t>Spread value</t>
         </is>
@@ -6712,87 +6909,87 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="20" customWidth="1" style="140" min="1" max="1"/>
-    <col width="30" customWidth="1" style="140" min="2" max="2"/>
-    <col width="20" customWidth="1" style="140" min="3" max="3"/>
-    <col width="9" customWidth="1" style="140" min="4" max="4"/>
-    <col width="12" customWidth="1" style="140" min="5" max="9"/>
-    <col width="16" customWidth="1" style="140" min="10" max="10"/>
-    <col width="10" customWidth="1" style="140" min="11" max="11"/>
-    <col width="60" customWidth="1" style="140" min="12" max="12"/>
+    <col width="20" customWidth="1" style="141" min="1" max="1"/>
+    <col width="30" customWidth="1" style="141" min="2" max="2"/>
+    <col width="20" customWidth="1" style="141" min="3" max="3"/>
+    <col width="9" customWidth="1" style="141" min="4" max="4"/>
+    <col width="12" customWidth="1" style="141" min="5" max="9"/>
+    <col width="16" customWidth="1" style="141" min="10" max="10"/>
+    <col width="10" customWidth="1" style="141" min="11" max="11"/>
+    <col width="60" customWidth="1" style="141" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="142">
-      <c r="A1" s="276" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="143">
+      <c r="A1" s="278" t="inlineStr">
         <is>
           <t>LOG  -  timestamped signal events</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="142">
-      <c r="A2" s="229" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="143">
+      <c r="A2" s="230" t="inlineStr">
         <is>
           <t>One line when a state STARTS and one when it CLEARS - never one per poll. Reviewable after the session.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="142">
-      <c r="A3" s="231" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="143">
+      <c r="A3" s="232" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B3" s="231" t="inlineStr">
+      <c r="B3" s="232" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="C3" s="231" t="inlineStr">
+      <c r="C3" s="232" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D3" s="231" t="inlineStr">
+      <c r="D3" s="232" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="E3" s="231" t="inlineStr">
+      <c r="E3" s="232" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="F3" s="231" t="inlineStr">
+      <c r="F3" s="232" t="inlineStr">
         <is>
           <t>Sigma</t>
         </is>
       </c>
-      <c r="G3" s="231" t="inlineStr">
+      <c r="G3" s="232" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="H3" s="231" t="inlineStr">
+      <c r="H3" s="232" t="inlineStr">
         <is>
           <t>Bid</t>
         </is>
       </c>
-      <c r="I3" s="231" t="inlineStr">
+      <c r="I3" s="232" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="J3" s="231" t="inlineStr">
+      <c r="J3" s="232" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="K3" s="231" t="inlineStr">
+      <c r="K3" s="232" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="L3" s="231" t="inlineStr">
+      <c r="L3" s="232" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -6814,307 +7011,307 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="4" customWidth="1" style="140" min="1" max="1"/>
-    <col width="46" customWidth="1" style="140" min="2" max="2"/>
-    <col width="16" customWidth="1" style="140" min="3" max="6"/>
-    <col width="60" customWidth="1" style="140" min="7" max="7"/>
+    <col width="4" customWidth="1" style="141" min="1" max="1"/>
+    <col width="46" customWidth="1" style="141" min="2" max="2"/>
+    <col width="16" customWidth="1" style="141" min="3" max="6"/>
+    <col width="60" customWidth="1" style="141" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.7" customHeight="1" s="142">
-      <c r="B1" s="252" t="inlineStr">
+    <row r="1" ht="19.7" customHeight="1" s="143">
+      <c r="B1" s="253" t="inlineStr">
         <is>
           <t>SETUP  -  turning this .xlsx into the working .xlsm</t>
         </is>
       </c>
     </row>
     <row r="2"/>
-    <row r="3" ht="30" customHeight="1" s="142">
-      <c r="B3" s="277" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="143">
+      <c r="B3" s="279" t="inlineStr">
         <is>
           <t>openpyxl cannot author VBA, so this file ships as an .xlsx carrying all structure and formatting, plus a .bas module to import. Six steps, once.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="142">
-      <c r="B4" s="278" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="143">
+      <c r="B4" s="280" t="inlineStr">
         <is>
           <t>1.  Open TT_ZScore_Monitor.xlsx in Excel on the machine running TT and the TT RTD server.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="142">
-      <c r="B5" s="278" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="143">
+      <c r="B5" s="280" t="inlineStr">
         <is>
           <t>2.  File &gt; Save As &gt; Excel Macro-Enabled Workbook (.xlsm). Keep the same folder.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="142">
-      <c r="B6" s="278" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="143">
+      <c r="B6" s="280" t="inlineStr">
         <is>
           <t>3.  Alt+F11 to open the VBA editor.  File &gt; Import File...  and choose TTZMonitor.bas.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="142">
-      <c r="B7" s="278" t="inlineStr">
+    <row r="7" ht="30" customHeight="1" s="143">
+      <c r="B7" s="280" t="inlineStr">
         <is>
           <t>4.  In the editor, double-click ThisWorkbook, clear the pane with Ctrl+A then Delete, and paste the contents of ThisWorkbook.txt verbatim. Do NOT copy it out of TTZMonitor.bas - the copy there is inside a comment block, and pasting it with the apostrophes attached gives 'Compile error: Expected End Sub'.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="142">
-      <c r="B8" s="278" t="inlineStr">
+    <row r="8" ht="30" customHeight="1" s="143">
+      <c r="B8" s="280" t="inlineStr">
         <is>
           <t>5.  Back on Dashboard, insert two shapes over cells N2 and P2 (Insert &gt; Shapes &gt; Rectangle), right-click each &gt; Assign Macro &gt; StartMonitor and StopMonitor. Until you do, run them from Alt+F8.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="142">
-      <c r="B9" s="278" t="inlineStr">
+    <row r="9" ht="15" customHeight="1" s="143">
+      <c r="B9" s="280" t="inlineStr">
         <is>
           <t>6.  Save. Click START. The Feed sheet stays hidden; you never need to look at it.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="142">
-      <c r="B10" s="277" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="143">
+      <c r="B10" s="279" t="inlineStr">
         <is>
           <t>Step 4 is NOT optional here. The capture timer is a Windows user32 timer, and one that outlives the workbook keeps firing into a module that no longer has its sheets - which crashes Excel. Workbook_BeforeClose calls StopMonitor and kills it.</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12" ht="15" customHeight="1" s="142">
-      <c r="B12" s="230" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="143">
+      <c r="B12" s="231" t="inlineStr">
         <is>
           <t>WHAT TO CHECK ON THE FIRST RUN</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="25.5" customHeight="1" s="142">
-      <c r="B13" s="279" t="inlineStr">
+    <row r="13" ht="25.5" customHeight="1" s="143">
+      <c r="B13" s="281" t="inlineStr">
         <is>
           <t>-  Feed sheet column B (instrument ids) fills in. If it stays blank, the TT short name in Feed column A does not match TT, or the market in Dashboard!C4 is wrong.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="25.5" customHeight="1" s="142">
-      <c r="B14" s="279" t="inlineStr">
+    <row r="14" ht="25.5" customHeight="1" s="143">
+      <c r="B14" s="281" t="inlineStr">
         <is>
           <t>-  Dashboard prices move, but the sheet does NOT flash. If it flashes, something volatile has been reintroduced - search the workbook for NOW, TODAY, OFFSET, INDIRECT, RAND.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="25.5" customHeight="1" s="142">
-      <c r="B15" s="279" t="inlineStr">
+    <row r="15" ht="25.5" customHeight="1" s="143">
+      <c r="B15" s="281" t="inlineStr">
         <is>
           <t>-  The samples counter climbs at roughly the quotes/min rate, not at the timer rate. If it climbs at the timer rate, dedupe is not working and every z you see will be fiction.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="25.5" customHeight="1" s="142">
-      <c r="B16" s="279" t="inlineStr">
+    <row r="16" ht="25.5" customHeight="1" s="143">
+      <c r="B16" s="281" t="inlineStr">
         <is>
           <t>-  Warm-up takes MIN_HISTORY_MIN (default 120) minutes on a cold start. That is deliberate.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="25.5" customHeight="1" s="142">
-      <c r="B17" s="279" t="inlineStr">
+    <row r="17" ht="25.5" customHeight="1" s="143">
+      <c r="B17" s="281" t="inlineStr">
         <is>
           <t>-  A 'ticks' folder appears beside the workbook, one CSV per spread per day, holding every changed quote. That is the raw record - keep it for the first week or two.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="25.5" customHeight="1" s="142">
-      <c r="B18" s="279" t="inlineStr">
+    <row r="18" ht="25.5" customHeight="1" s="143">
+      <c r="B18" s="281" t="inlineStr">
         <is>
           <t>-  After a week, run Alt+F8 &gt; CheckSubsamplingLoss. It compares mean and sigma over the live window at full fidelity against 250 / 500 / 1000 / 2000 / 5000 ms subsampling and writes the comparison to the Log. If sigma is materially unchanged, set STORE_MIN_INTERVAL_MS and reclaim the memory.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20" ht="15" customHeight="1" s="142">
-      <c r="B20" s="230" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="143">
+      <c r="B20" s="231" t="inlineStr">
         <is>
           <t>WHAT SIGMA THIS SPREAD MUST HAVE TO BE WORTH TRADING</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="142">
-      <c r="B21" s="229" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="143">
+      <c r="B21" s="230" t="inlineStr">
         <is>
           <t>Live off Config. Edit the two assumed market widths below; everything else follows.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="142">
-      <c r="B22" s="262" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="143">
+      <c r="B22" s="263" t="inlineStr">
         <is>
           <t>Assumed width, each outright leg (spread units)</t>
         </is>
       </c>
-      <c r="C22" s="263" t="n">
+      <c r="C22" s="265" t="n">
         <v>0.02</v>
       </c>
-      <c r="E22" s="262" t="inlineStr">
+      <c r="E22" s="263" t="inlineStr">
         <is>
           <t>Assumed width, listed spread (spread units)</t>
         </is>
       </c>
-      <c r="F22" s="263" t="n">
+      <c r="F22" s="265" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="22.35" customHeight="1" s="142">
-      <c r="B24" s="231" t="inlineStr">
+    <row r="24" ht="22.35" customHeight="1" s="143">
+      <c r="B24" s="232" t="inlineStr">
         <is>
           <t>At LOTS from Config, per leg</t>
         </is>
       </c>
-      <c r="C24" s="231" t="inlineStr">
+      <c r="C24" s="232" t="inlineStr">
         <is>
           <t>Total cost</t>
         </is>
       </c>
-      <c r="D24" s="231" t="inlineStr">
+      <c r="D24" s="232" t="inlineStr">
         <is>
           <t>min sigma @ z = 3.0</t>
         </is>
       </c>
-      <c r="E24" s="231" t="inlineStr">
+      <c r="E24" s="232" t="inlineStr">
         <is>
           <t>min sigma @ z = 2.5</t>
         </is>
       </c>
-      <c r="F24" s="231" t="inlineStr">
+      <c r="F24" s="232" t="inlineStr">
         <is>
           <t>min sigma @ live ENTRY_Z</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="142">
-      <c r="B25" s="268" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="143">
+      <c r="B25" s="270" t="inlineStr">
         <is>
           <t>Legging the outrights</t>
         </is>
       </c>
-      <c r="C25" s="280">
+      <c r="C25" s="282">
         <f>2*Config!$B$74*Config!$B$41+(2*$C$22)*1000*Config!$B$41</f>
         <v/>
       </c>
-      <c r="D25" s="281">
+      <c r="D25" s="283">
         <f>Config!$B$47*$C$25/(0.5*3*1000*Config!$B$41)</f>
         <v/>
       </c>
-      <c r="E25" s="281">
+      <c r="E25" s="283">
         <f>Config!$B$47*$C$25/(0.5*2.5*1000*Config!$B$41)</f>
         <v/>
       </c>
-      <c r="F25" s="281">
+      <c r="F25" s="283">
         <f>Config!$B$47*$C$25/(0.5*Config!$B$34*1000*Config!$B$41)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="142">
-      <c r="B26" s="268" t="inlineStr">
+    <row r="26" ht="15" customHeight="1" s="143">
+      <c r="B26" s="270" t="inlineStr">
         <is>
           <t>Listed inter-product spread</t>
         </is>
       </c>
-      <c r="C26" s="280">
+      <c r="C26" s="282">
         <f>2*Config!$B$74*Config!$B$41+$F$22*1000*Config!$B$41</f>
         <v/>
       </c>
-      <c r="D26" s="281">
+      <c r="D26" s="283">
         <f>Config!$B$47*$C$26/(0.5*3*1000*Config!$B$41)</f>
         <v/>
       </c>
-      <c r="E26" s="281">
+      <c r="E26" s="283">
         <f>Config!$B$47*$C$26/(0.5*2.5*1000*Config!$B$41)</f>
         <v/>
       </c>
-      <c r="F26" s="281">
+      <c r="F26" s="283">
         <f>Config!$B$47*$C$26/(0.5*Config!$B$34*1000*Config!$B$41)</f>
         <v/>
       </c>
     </row>
     <row r="27"/>
-    <row r="28" ht="15" customHeight="1" s="142">
-      <c r="B28" s="229" t="inlineStr">
+    <row r="28" ht="15" customHeight="1" s="143">
+      <c r="B28" s="230" t="inlineStr">
         <is>
           <t>capture = 0.5 x |z| x sigma x USD-per-point x LOTS.  An entry passes when capture &gt;= EDGE_MULTIPLE x total cost.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="142">
-      <c r="B29" s="251" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="143">
+      <c r="B29" s="252" t="inlineStr">
         <is>
           <t>A lower ENTRY_Z means less expected capture per entry, so it RAISES the sigma the spread must have. 2.5 instead of 3.0 raises it by about 20%.</t>
         </is>
       </c>
     </row>
     <row r="30"/>
-    <row r="31" ht="15" customHeight="1" s="142">
-      <c r="B31" s="230" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="143">
+      <c r="B31" s="231" t="inlineStr">
         <is>
           <t>ASSUMPTIONS MADE WHILE BUILDING THIS - CHECK THEM</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="39.75" customHeight="1" s="142">
-      <c r="B32" s="279" t="inlineStr">
+    <row r="32" ht="39.75" customHeight="1" s="143">
+      <c r="B32" s="281" t="inlineStr">
         <is>
           <t>-  The repository was empty, so the existing Dashboard layout was reconstructed from the cell references given in the spec (C4, B6, C7, H7/H8, P7/P8, H12/H13/H14/I14, L3). Those coordinates are honoured exactly; the surrounding rows are a best reconstruction. Compare against your live sheet before relying on it.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="39.75" customHeight="1" s="142">
-      <c r="B33" s="279" t="inlineStr">
+    <row r="33" ht="39.75" customHeight="1" s="143">
+      <c r="B33" s="281" t="inlineStr">
         <is>
           <t>-  The 3:2:1 ask row now mirrors the bid row: I15 uses H14 (CL BID), not I14. The bid row is unchanged. This is the convention the spec described; confirm it is the one you want.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="39.75" customHeight="1" s="142">
-      <c r="B34" s="279" t="inlineStr">
+    <row r="34" ht="39.75" customHeight="1" s="143">
+      <c r="B34" s="281" t="inlineStr">
         <is>
           <t>-  COMMISSION_BASIS defaults to CONSERVATIVE ($3.82 per lot per leg round turn, reading CME's $1.50 as per side). Switch it to CME_PER_RT on Config if the rate card proves otherwise.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="39.75" customHeight="1" s="142">
-      <c r="B35" s="279" t="inlineStr">
+    <row r="35" ht="39.75" customHeight="1" s="143">
+      <c r="B35" s="281" t="inlineStr">
         <is>
           <t>-  Contracts charged commission: 2 for BZ-CL and the listed spread, 6 for the 3:2:1 crack (2 RB + 1 HO + 3 CL). Change it in the Config spread table if your clearing differs.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="39.75" customHeight="1" s="142">
-      <c r="B36" s="279" t="inlineStr">
+    <row r="36" ht="39.75" customHeight="1" s="143">
+      <c r="B36" s="281" t="inlineStr">
         <is>
           <t>-  Slot 3 (3:2:1) has no exchange-listed equivalent, so its LISTED crossing-cost column reads n/a.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="39.75" customHeight="1" s="142">
-      <c r="B37" s="279" t="inlineStr">
+    <row r="37" ht="39.75" customHeight="1" s="143">
+      <c r="B37" s="281" t="inlineStr">
         <is>
           <t>-  MIN_SIGMA ships at 0 because sigma on these spreads has never been measured. Set it once you have a session of data - until then the degenerate-window guard rests on MAX_ABS_Z alone.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="39.75" customHeight="1" s="142">
-      <c r="B38" s="279" t="inlineStr">
+    <row r="38" ht="39.75" customHeight="1" s="143">
+      <c r="B38" s="281" t="inlineStr">
         <is>
           <t>-  Application.OnTime cannot go below about one second, so capture at 100 ms runs on a user32 SetTimer with an OnTime watchdog that re-arms it (Excel silently kills API timers when a modal dialog opens). If SetTimer is unavailable, CAPTURE_MS is clamped to 1000 and everything still works - only alert latency changes, not the statistics.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="39.75" customHeight="1" s="142">
-      <c r="B39" s="279" t="inlineStr">
+    <row r="39" ht="39.75" customHeight="1" s="143">
+      <c r="B39" s="281" t="inlineStr">
         <is>
           <t>-  Capturing at 100 ms does not mean storing at 100 ms, and after dedupe it does not change sigma either. The window holds quote CHANGES, not poll ticks; subsampling a mean-reverting level series is unbiased. 100 ms buys latency to the chime, which for manual execution is not measurable in human terms - so the real reason to capture fast is simply that no genuine quote change is missed.</t>
         </is>

--- a/TT_ZScore_Monitor.xlsx
+++ b/TT_ZScore_Monitor.xlsx
@@ -3881,7 +3881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="141" min="1" max="1"/>
@@ -5340,292 +5340,254 @@
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="143">
-      <c r="A80" s="256" t="inlineStr">
+      <c r="A80" s="252" t="inlineStr">
+        <is>
+          <t>CL is a leg of ALL THREE spreads. Moving it to November while RBOB and ULSD stay in October turns the cracks into a crack PLUS a calendar spread - not the thing the z-score was measuring. Roll RBOB and ULSD with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="143">
+      <c r="A81" s="256" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B80" s="256" t="inlineStr">
+      <c r="B81" s="256" t="inlineStr">
         <is>
           <t>TT short name</t>
         </is>
       </c>
-      <c r="C80" s="256" t="inlineStr">
+      <c r="C81" s="256" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="D80" s="256" t="n"/>
-      <c r="E80" s="256" t="inlineStr">
+      <c r="D81" s="256" t="n"/>
+      <c r="E81" s="256" t="inlineStr">
         <is>
           <t>Used as</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="143">
-      <c r="A81" s="249" t="inlineStr">
-        <is>
-          <t>INSTRUMENT_1</t>
-        </is>
-      </c>
-      <c r="B81" s="259" t="inlineStr">
-        <is>
-          <t>RBV6</t>
-        </is>
-      </c>
-      <c r="C81" s="235" t="inlineStr">
-        <is>
-          <t>RBOB Gasoline</t>
-        </is>
-      </c>
-      <c r="E81" s="264" t="inlineStr">
-        <is>
-          <t>leg of the 3:2:1</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="143">
       <c r="A82" s="249" t="inlineStr">
         <is>
-          <t>INSTRUMENT_2</t>
+          <t>INSTRUMENT_1</t>
         </is>
       </c>
       <c r="B82" s="259" t="inlineStr">
         <is>
-          <t>HOV6</t>
+          <t>RBV6</t>
         </is>
       </c>
       <c r="C82" s="235" t="inlineStr">
         <is>
-          <t>NY Harbor ULSD</t>
+          <t>RBOB Gasoline</t>
         </is>
       </c>
       <c r="E82" s="264" t="inlineStr">
         <is>
-          <t>leg of HO/CL and the 3:2:1</t>
+          <t>leg of the 3:2:1</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="143">
       <c r="A83" s="249" t="inlineStr">
         <is>
-          <t>INSTRUMENT_3</t>
+          <t>INSTRUMENT_2</t>
         </is>
       </c>
       <c r="B83" s="259" t="inlineStr">
         <is>
-          <t>CLV6</t>
+          <t>HOV6</t>
         </is>
       </c>
       <c r="C83" s="235" t="inlineStr">
         <is>
-          <t>WTI Crude</t>
+          <t>NY Harbor ULSD</t>
         </is>
       </c>
       <c r="E83" s="264" t="inlineStr">
         <is>
-          <t>leg of every spread</t>
+          <t>leg of HO/CL and the 3:2:1</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="143">
       <c r="A84" s="249" t="inlineStr">
         <is>
-          <t>INSTRUMENT_4</t>
+          <t>INSTRUMENT_3</t>
         </is>
       </c>
       <c r="B84" s="259" t="inlineStr">
         <is>
-          <t>BZV6</t>
+          <t>CLX6</t>
         </is>
       </c>
       <c r="C84" s="235" t="inlineStr">
         <is>
-          <t>Brent Last Day Financial</t>
+          <t>WTI Crude</t>
         </is>
       </c>
       <c r="E84" s="264" t="inlineStr">
         <is>
-          <t>leg B of BZ - CL</t>
+          <t>leg of every spread</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="143">
       <c r="A85" s="249" t="inlineStr">
         <is>
-          <t>INSTRUMENT_5</t>
+          <t>INSTRUMENT_4</t>
         </is>
       </c>
       <c r="B85" s="259" t="inlineStr">
         <is>
-          <t>CL Oct26 - BZ Oct26 Inter-Product</t>
+          <t>BZX6</t>
         </is>
       </c>
       <c r="C85" s="235" t="inlineStr">
         <is>
-          <t>Exchange-listed inter-product</t>
+          <t>Brent Last Day Financial</t>
         </is>
       </c>
       <c r="E85" s="264" t="inlineStr">
         <is>
-          <t>listed comparison</t>
+          <t>leg B of BZ - CL</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="143">
       <c r="A86" s="249" t="inlineStr">
         <is>
+          <t>INSTRUMENT_5</t>
+        </is>
+      </c>
+      <c r="B86" s="259" t="inlineStr">
+        <is>
+          <t>CL Oct26 - BZ Oct26 Inter-Product</t>
+        </is>
+      </c>
+      <c r="C86" s="235" t="inlineStr">
+        <is>
+          <t>Exchange-listed inter-product</t>
+        </is>
+      </c>
+      <c r="E86" s="264" t="inlineStr">
+        <is>
+          <t>listed comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="143">
+      <c r="A87" s="249" t="inlineStr">
+        <is>
           <t>INSTRUMENT_6</t>
         </is>
       </c>
-      <c r="B86" s="259" t="inlineStr">
+      <c r="B87" s="259" t="inlineStr">
         <is>
           <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
-      <c r="C86" s="235" t="inlineStr">
+      <c r="C87" s="235" t="inlineStr">
         <is>
           <t>Exchange-listed crack</t>
         </is>
       </c>
-      <c r="E86" s="264" t="inlineStr">
+      <c r="E87" s="264" t="inlineStr">
         <is>
           <t>listed comparison</t>
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88"/>
-    <row r="89" ht="15" customHeight="1" s="143">
-      <c r="A89" s="255" t="inlineStr">
+    <row r="89"/>
+    <row r="90" ht="15" customHeight="1" s="143">
+      <c r="A90" s="255" t="inlineStr">
         <is>
           <t>SPREAD_TABLE_START   -   up to 4 monitored spreads, one buffer each</t>
         </is>
       </c>
-      <c r="B89" s="262" t="n"/>
-      <c r="C89" s="262" t="n"/>
-      <c r="D89" s="262" t="n"/>
-      <c r="E89" s="262" t="n"/>
-      <c r="F89" s="262" t="n"/>
-      <c r="G89" s="262" t="n"/>
-      <c r="H89" s="262" t="n"/>
-      <c r="I89" s="262" t="n"/>
-      <c r="J89" s="262" t="n"/>
-      <c r="K89" s="262" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1" s="143">
-      <c r="A90" s="230" t="inlineStr">
+      <c r="B90" s="262" t="n"/>
+      <c r="C90" s="262" t="n"/>
+      <c r="D90" s="262" t="n"/>
+      <c r="E90" s="262" t="n"/>
+      <c r="F90" s="262" t="n"/>
+      <c r="G90" s="262" t="n"/>
+      <c r="H90" s="262" t="n"/>
+      <c r="I90" s="262" t="n"/>
+      <c r="J90" s="262" t="n"/>
+      <c r="K90" s="262" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="143">
+      <c r="A91" s="230" t="inlineStr">
         <is>
           <t>Leg COMPOSITION (which instruments, and their weights) is defined by the labelled formulas in the MONITOR LEGS block on the hidden Feed sheet. Everything below is hot-reloaded each tick.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="32.8" customHeight="1" s="143">
-      <c r="A91" s="256" t="inlineStr">
+    <row r="92" ht="32.8" customHeight="1" s="143">
+      <c r="A92" s="256" t="inlineStr">
         <is>
           <t>Slot</t>
         </is>
       </c>
-      <c r="B91" s="256" t="inlineStr">
+      <c r="B92" s="256" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="C91" s="256" t="inlineStr">
+      <c r="C92" s="256" t="inlineStr">
         <is>
           <t>Display name</t>
         </is>
       </c>
-      <c r="D91" s="256" t="inlineStr">
+      <c r="D92" s="256" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="E91" s="256" t="inlineStr">
+      <c r="E92" s="256" t="inlineStr">
         <is>
           <t>HEDGE_RATIO (beta)</t>
         </is>
       </c>
-      <c r="F91" s="256" t="inlineStr">
+      <c r="F92" s="256" t="inlineStr">
         <is>
           <t>Beta stamped for pair</t>
         </is>
       </c>
-      <c r="G91" s="256" t="inlineStr">
+      <c r="G92" s="256" t="inlineStr">
         <is>
           <t>USD per 1.00 of spread, per lot</t>
         </is>
       </c>
-      <c r="H91" s="256" t="inlineStr">
+      <c r="H92" s="256" t="inlineStr">
         <is>
           <t>Contracts charged commission</t>
         </is>
       </c>
-      <c r="I91" s="256" t="inlineStr">
+      <c r="I92" s="256" t="inlineStr">
         <is>
           <t>Tick size</t>
         </is>
       </c>
-      <c r="J91" s="256" t="inlineStr">
+      <c r="J92" s="256" t="inlineStr">
         <is>
           <t>Decimals</t>
         </is>
       </c>
-      <c r="K91" s="256" t="inlineStr">
+      <c r="K92" s="256" t="inlineStr">
         <is>
           <t>Listed equivalent (cost comparison)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1" s="143">
-      <c r="A92" s="249" t="inlineStr">
-        <is>
-          <t>SPREAD_1</t>
-        </is>
-      </c>
-      <c r="B92" s="257" t="b">
-        <v>1</v>
-      </c>
-      <c r="C92" s="259" t="inlineStr">
-        <is>
-          <t>BZ - CL  (Brent LDF - WTI)</t>
-        </is>
-      </c>
-      <c r="D92" s="257" t="inlineStr">
-        <is>
-          <t>LEGGED</t>
-        </is>
-      </c>
-      <c r="E92" s="265" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="259" t="inlineStr">
-        <is>
-          <t>BZV6 / CLV6, derived 2026-08 (RELATED pair - no fair value, empirical mean only)</t>
-        </is>
-      </c>
-      <c r="G92" s="266" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H92" s="267" t="n">
-        <v>2</v>
-      </c>
-      <c r="I92" s="265" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J92" s="267" t="n">
-        <v>2</v>
-      </c>
-      <c r="K92" s="238" t="inlineStr">
-        <is>
-          <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="143">
       <c r="A93" s="249" t="inlineStr">
         <is>
-          <t>SPREAD_2</t>
+          <t>SPREAD_1</t>
         </is>
       </c>
       <c r="B93" s="257" t="b">
@@ -5633,7 +5595,7 @@
       </c>
       <c r="C93" s="259" t="inlineStr">
         <is>
-          <t>HO/CL crack  (ULSD - WTI)</t>
+          <t>BZ - CL  (Brent LDF - WTI)</t>
         </is>
       </c>
       <c r="D93" s="257" t="inlineStr">
@@ -5646,7 +5608,7 @@
       </c>
       <c r="F93" s="259" t="inlineStr">
         <is>
-          <t>HOV6 x42 / CLV6, 1:1 by design (crack, not a fitted beta)</t>
+          <t>BZV6 / CLV6, derived 2026-08 (RELATED pair - no fair value, empirical mean only)</t>
         </is>
       </c>
       <c r="G93" s="266" t="n">
@@ -5663,14 +5625,14 @@
       </c>
       <c r="K93" s="238" t="inlineStr">
         <is>
-          <t>Oct26 HO-CL Crack</t>
+          <t>CL Oct26 - BZ Oct26 Inter-Product</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="143">
       <c r="A94" s="249" t="inlineStr">
         <is>
-          <t>SPREAD_3</t>
+          <t>SPREAD_2</t>
         </is>
       </c>
       <c r="B94" s="257" t="b">
@@ -5678,7 +5640,7 @@
       </c>
       <c r="C94" s="259" t="inlineStr">
         <is>
-          <t>3:2:1 crack  (2RB+1HO-3CL)/3</t>
+          <t>HO/CL crack  (ULSD - WTI)</t>
         </is>
       </c>
       <c r="D94" s="257" t="inlineStr">
@@ -5691,14 +5653,14 @@
       </c>
       <c r="F94" s="259" t="inlineStr">
         <is>
-          <t>RBV6/HOV6/CLV6, structural 3:2:1 - not a fitted beta</t>
+          <t>HOV6 x42 / CLV6, 1:1 by design (crack, not a fitted beta)</t>
         </is>
       </c>
       <c r="G94" s="266" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="H94" s="267" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I94" s="265" t="n">
         <v>0.01</v>
@@ -5708,14 +5670,14 @@
       </c>
       <c r="K94" s="238" t="inlineStr">
         <is>
-          <t>(none listed)</t>
+          <t>Oct26 HO-CL Crack</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="143">
       <c r="A95" s="249" t="inlineStr">
         <is>
-          <t>SPREAD_4</t>
+          <t>SPREAD_3</t>
         </is>
       </c>
       <c r="B95" s="257" t="b">
@@ -5723,12 +5685,12 @@
       </c>
       <c r="C95" s="259" t="inlineStr">
         <is>
-          <t>CL-BZ Inter-Product (listed)</t>
+          <t>3:2:1 crack  (2RB+1HO-3CL)/3</t>
         </is>
       </c>
       <c r="D95" s="257" t="inlineStr">
         <is>
-          <t>LISTED</t>
+          <t>LEGGED</t>
         </is>
       </c>
       <c r="E95" s="265" t="n">
@@ -5736,14 +5698,14 @@
       </c>
       <c r="F95" s="259" t="inlineStr">
         <is>
-          <t>Exchange-listed spread - beta not applicable</t>
+          <t>RBV6/HOV6/CLV6, structural 3:2:1 - not a fitted beta</t>
         </is>
       </c>
       <c r="G95" s="266" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="H95" s="267" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I95" s="265" t="n">
         <v>0.01</v>
@@ -5753,49 +5715,94 @@
       </c>
       <c r="K95" s="238" t="inlineStr">
         <is>
+          <t>(none listed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="143">
+      <c r="A96" s="249" t="inlineStr">
+        <is>
+          <t>SPREAD_4</t>
+        </is>
+      </c>
+      <c r="B96" s="257" t="b">
+        <v>1</v>
+      </c>
+      <c r="C96" s="259" t="inlineStr">
+        <is>
+          <t>CL-BZ Inter-Product (listed)</t>
+        </is>
+      </c>
+      <c r="D96" s="257" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="E96" s="265" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="259" t="inlineStr">
+        <is>
+          <t>Exchange-listed spread - beta not applicable</t>
+        </is>
+      </c>
+      <c r="G96" s="266" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H96" s="267" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="265" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J96" s="267" t="n">
+        <v>2</v>
+      </c>
+      <c r="K96" s="238" t="inlineStr">
+        <is>
           <t>n/a - this IS the listed spread</t>
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97" ht="15" customHeight="1" s="143">
-      <c r="A97" s="252" t="inlineStr">
+    <row r="97"/>
+    <row r="98" ht="15" customHeight="1" s="143">
+      <c r="A98" s="252" t="inlineStr">
         <is>
           <t>HEDGE RATIO BELONGS TO THE PAIR. If the instruments change, beta must be re-derived - a stale beta silently redefines the series. Column F stamps what each beta was computed for.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="143">
-      <c r="A98" s="230" t="inlineStr">
-        <is>
-          <t>Contracts charged: BZ-CL and the listed spread are 2 contracts per lot (one per leg); the 3:2:1 crack is 6 (2 RB + 1 HO + 3 CL).</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="143">
       <c r="A99" s="230" t="inlineStr">
         <is>
+          <t>Contracts charged: BZ-CL and the listed spread are 2 contracts per lot (one per leg); the 3:2:1 crack is 6 (2 RB + 1 HO + 3 CL).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="143">
+      <c r="A100" s="230" t="inlineStr">
+        <is>
           <t>USD per 1.00 of spread: NYMEX energy contracts are 1,000 bbl, so one cent of differential is $10 per leg per lot, i.e. $1,000 per 1.00.</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101" ht="15" customHeight="1" s="143">
-      <c r="A101" s="252" t="inlineStr">
+    <row r="101"/>
+    <row r="102" ht="15" customHeight="1" s="143">
+      <c r="A102" s="252" t="inlineStr">
         <is>
           <t>NOTIONAL_BASIS - read this before changing it:</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="15" customHeight="1" s="143">
-      <c r="A102" s="230" t="inlineStr">
+    <row r="103" ht="15" customHeight="1" s="143">
+      <c r="A103" s="230" t="inlineStr">
         <is>
           <t>A spread is not an outright, so 'notional' has no single meaning. At 1 lot with CL near $60 and BZ-CL near $7.20:  SPREAD_VALUE ~ $7,200, ONE_LEG ~ $60,000, BOTH_LEGS ~ $127,000.</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="15" customHeight="1" s="143">
-      <c r="A103" s="268" t="inlineStr">
+    <row r="104" ht="15" customHeight="1" s="143">
+      <c r="A104" s="268" t="inlineStr">
         <is>
           <t>1% of those is $72, $600 and $1,270. If sigma on this spread turns out to be ~5 cents ($50), only the first is reachable - the others need the spread to travel 12 or 25 sigma, which it will not do. Watch the TP-in-sigma cell on the Dashboard: above about 1 sigma it turns amber.</t>
         </is>
@@ -5893,7 +5900,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" s="143">
       <c r="A6" s="273">
-        <f>Config!$B$81</f>
+        <f>Config!$B$82</f>
         <v/>
       </c>
       <c r="B6" s="274">
@@ -5932,7 +5939,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="143">
       <c r="A7" s="273">
-        <f>Config!$B$82</f>
+        <f>Config!$B$83</f>
         <v/>
       </c>
       <c r="B7" s="274">
@@ -5971,7 +5978,7 @@
     </row>
     <row r="8" ht="15" customHeight="1" s="143">
       <c r="A8" s="273">
-        <f>Config!$B$83</f>
+        <f>Config!$B$84</f>
         <v/>
       </c>
       <c r="B8" s="274">
@@ -6010,7 +6017,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" s="143">
       <c r="A9" s="273">
-        <f>Config!$B$84</f>
+        <f>Config!$B$85</f>
         <v/>
       </c>
       <c r="B9" s="274">
@@ -6049,7 +6056,7 @@
     </row>
     <row r="10" ht="15" customHeight="1" s="143">
       <c r="A10" s="273">
-        <f>Config!$B$85</f>
+        <f>Config!$B$86</f>
         <v/>
       </c>
       <c r="B10" s="274">
@@ -6088,7 +6095,7 @@
     </row>
     <row r="11" ht="15" customHeight="1" s="143">
       <c r="A11" s="273">
-        <f>Config!$B$86</f>
+        <f>Config!$B$87</f>
         <v/>
       </c>
       <c r="B11" s="274">
